--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8710" activeTab="4"/>
+    <workbookView windowWidth="18350" windowHeight="8710" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
@@ -12,7 +12,11 @@
     <sheet name="Sheet9" sheetId="9" r:id="rId3"/>
     <sheet name="ROR_has_no_regulation_cap" sheetId="10" r:id="rId4"/>
     <sheet name="Ramp_rate_constraints" sheetId="11" r:id="rId5"/>
+    <sheet name="Growth_rate" sheetId="12" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="IQ_FWD_Q" hidden="1">501</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -239,7 +243,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="132">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -407,6 +411,234 @@
   </si>
   <si>
     <t>ENCAN01_SMR</t>
+  </si>
+  <si>
+    <t>~UC_Sets: R_S: AllRegions</t>
+  </si>
+  <si>
+    <t>~UC_Sets: T_SUC:</t>
+  </si>
+  <si>
+    <t>~UC_T</t>
+  </si>
+  <si>
+    <t>UC_N</t>
+  </si>
+  <si>
+    <t>Pset_Set</t>
+  </si>
+  <si>
+    <t>UC_ATTR~RHS</t>
+  </si>
+  <si>
+    <t>UC_CAP</t>
+  </si>
+  <si>
+    <t>UC_CAP~RHS</t>
+  </si>
+  <si>
+    <t>UC_RHSTS</t>
+  </si>
+  <si>
+    <t>UC_RHSTS~0</t>
+  </si>
+  <si>
+    <t>UC_Desc</t>
+  </si>
+  <si>
+    <t>UC_Grow_LI</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_LI</t>
+  </si>
+  <si>
+    <t>CAP,GROWTH</t>
+  </si>
+  <si>
+    <t>2025, 2150</t>
+  </si>
+  <si>
+    <t>UP</t>
+  </si>
+  <si>
+    <t>UC_Grow_GR</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_GR</t>
+  </si>
+  <si>
+    <t>UC_Grow_NI</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_NI</t>
+  </si>
+  <si>
+    <t>UC_Grow_COB_byCop</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_COB_byCop</t>
+  </si>
+  <si>
+    <t>UC_Grow_MN</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_MN</t>
+  </si>
+  <si>
+    <t>UC_Grow_COP</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_COP</t>
+  </si>
+  <si>
+    <t>UC_Grow_AL</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_AL</t>
+  </si>
+  <si>
+    <t>UC_Grow_COB_byNI_HPAL</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_COB_byNI_HPAL</t>
+  </si>
+  <si>
+    <t>UC_Grow_COB_byNI_sulfide</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_COB_byNI_sulfide</t>
+  </si>
+  <si>
+    <t>UC_Grow_COB_direct</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_COB_direct</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy1</t>
+  </si>
+  <si>
+    <t>PyroRecy-LFP</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy2</t>
+  </si>
+  <si>
+    <t>PyroRecy-LMO</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy3</t>
+  </si>
+  <si>
+    <t>PyroRecy-NCA</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy4</t>
+  </si>
+  <si>
+    <t>PyroRecy-NMC111</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy5</t>
+  </si>
+  <si>
+    <t>PyroRecy-NMC532</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy6</t>
+  </si>
+  <si>
+    <t>PyroRecy-NMC622</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy7</t>
+  </si>
+  <si>
+    <t>PyroRecy-NMC811</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy8</t>
+  </si>
+  <si>
+    <t>HydRecy-LFP</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy9</t>
+  </si>
+  <si>
+    <t>HydRecy-LMO</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy10</t>
+  </si>
+  <si>
+    <t>HydRecy-NCA</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy11</t>
+  </si>
+  <si>
+    <t>HydRecy-NMC111</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy12</t>
+  </si>
+  <si>
+    <t>HydRecy-NMC532</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy13</t>
+  </si>
+  <si>
+    <t>HydRecy-NMC622</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy14</t>
+  </si>
+  <si>
+    <t>HydRecy-NMC811</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy15</t>
+  </si>
+  <si>
+    <t>DirRecy-LFP</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy16</t>
+  </si>
+  <si>
+    <t>DirRecy-LMO</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy17</t>
+  </si>
+  <si>
+    <t>DirRecy-NCA</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy18</t>
+  </si>
+  <si>
+    <t>DirRecy-NMC111</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy19</t>
+  </si>
+  <si>
+    <t>DirRecy-NMC532</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy20</t>
+  </si>
+  <si>
+    <t>DirRecy-NMC622</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy21</t>
+  </si>
+  <si>
+    <t>DirRecy-NMC811</t>
   </si>
 </sst>
 </file>
@@ -419,7 +651,7 @@
     <numFmt numFmtId="176" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -428,14 +660,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.2"/>
       <color rgb="FF212529"/>
       <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -635,12 +875,18 @@
       <charset val="0"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.799860000610352"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -853,11 +1099,39 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -977,55 +1251,52 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1040,97 +1311,108 @@
     <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="49" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="53">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1664,7 +1946,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="20">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -1721,7 +2003,7 @@
       </c>
     </row>
     <row r="4" ht="16" spans="1:11">
-      <c r="A4" s="6"/>
+      <c r="A4" s="3"/>
     </row>
     <row r="7" spans="1:11">
       <c r="D7" t="s">
@@ -1778,10 +2060,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="15"/>
+      <c r="K10" s="19"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="15"/>
+      <c r="K11" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1802,12 +2084,12 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:14">
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="3"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="2:14">
       <c r="B6" t="s">
@@ -1822,7 +2104,7 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="9" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1830,13 +2112,13 @@
       <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="10">
         <v>10</v>
       </c>
     </row>
@@ -1844,29 +2126,29 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="10">
         <v>7</v>
       </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
     </row>
     <row r="9" ht="16" spans="2:14">
       <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="10">
         <v>10</v>
       </c>
       <c r="J9" t="s">
@@ -1889,19 +2171,19 @@
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="10">
         <v>8</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="K10" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L10" s="8" t="s">
+      <c r="L10" s="12" t="s">
         <v>40</v>
       </c>
       <c r="M10">
@@ -1915,13 +2197,13 @@
       <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="7">
         <v>1.5</v>
       </c>
     </row>
@@ -1929,13 +2211,13 @@
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="7">
         <v>1.5</v>
       </c>
     </row>
@@ -1943,13 +2225,13 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="8">
         <v>2</v>
       </c>
     </row>
@@ -1957,13 +2239,13 @@
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1971,13 +2253,13 @@
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1985,13 +2267,13 @@
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="14">
         <v>12</v>
       </c>
     </row>
@@ -1999,550 +2281,1653 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="16">
         <v>0.2</v>
       </c>
-      <c r="F17" s="3"/>
+      <c r="F17" s="8"/>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="16">
         <v>0.2</v>
       </c>
-      <c r="F18" s="3"/>
+      <c r="F18" s="8"/>
     </row>
     <row r="19" ht="16" spans="2:6">
       <c r="B19" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="16">
         <v>0.2</v>
       </c>
-      <c r="F19" s="3"/>
+      <c r="F19" s="8"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="16">
         <v>0.5</v>
       </c>
-      <c r="F20" s="3"/>
+      <c r="F20" s="8"/>
     </row>
     <row r="21" ht="16" spans="2:6">
       <c r="B21" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="16">
         <v>0.8</v>
       </c>
-      <c r="F21" s="3"/>
+      <c r="F21" s="8"/>
     </row>
     <row r="22" ht="16" spans="2:6">
       <c r="B22" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="3"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="8"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="3">
-        <v>1</v>
-      </c>
-      <c r="F23" s="3"/>
+      <c r="E23" s="8">
+        <v>1</v>
+      </c>
+      <c r="F23" s="8"/>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E24" s="3">
-        <v>1</v>
-      </c>
-      <c r="F24" s="3"/>
+      <c r="E24" s="8">
+        <v>1</v>
+      </c>
+      <c r="F24" s="8"/>
     </row>
     <row r="25" ht="16" spans="2:6">
       <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E25" s="3">
-        <v>1</v>
-      </c>
-      <c r="F25" s="3"/>
+      <c r="E25" s="8">
+        <v>1</v>
+      </c>
+      <c r="F25" s="8"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="7">
         <v>0.05</v>
       </c>
-      <c r="F26" s="3"/>
+      <c r="F26" s="8"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="3"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="8"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
     </row>
     <row r="38" spans="3:5">
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="14" t="s">
+      <c r="C54" s="18" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="14"/>
-      <c r="J56" s="14"/>
-      <c r="K56" s="14"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="18"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D57" s="14" t="s">
+      <c r="D57" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="14" t="s">
+      <c r="E57" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="F57" s="14" t="s">
+      <c r="F57" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="G57" s="14" t="s">
+      <c r="G57" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="H57" s="14" t="s">
+      <c r="H57" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="I57" s="14" t="s">
+      <c r="I57" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="J57" s="14" t="s">
+      <c r="J57" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="K57" s="14" t="s">
+      <c r="K57" s="18" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="14"/>
-      <c r="J58" s="14"/>
-      <c r="K58" s="14"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="18"/>
+      <c r="H58" s="18"/>
+      <c r="I58" s="18"/>
+      <c r="J58" s="18"/>
+      <c r="K58" s="18"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="14"/>
-      <c r="J59" s="14"/>
-      <c r="K59" s="14"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="18"/>
+      <c r="H59" s="18"/>
+      <c r="I59" s="18"/>
+      <c r="J59" s="18"/>
+      <c r="K59" s="18"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="14"/>
-      <c r="J60" s="14"/>
-      <c r="K60" s="14"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="18"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="18"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="14"/>
-      <c r="J61" s="14"/>
-      <c r="K61" s="14"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="18"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="18"/>
+      <c r="H61" s="18"/>
+      <c r="I61" s="18"/>
+      <c r="J61" s="18"/>
+      <c r="K61" s="18"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="14"/>
-      <c r="J62" s="14"/>
-      <c r="K62" s="14"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="18"/>
+      <c r="H62" s="18"/>
+      <c r="I62" s="18"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="18"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="14"/>
-      <c r="J63" s="14"/>
-      <c r="K63" s="14"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="18"/>
+      <c r="F63" s="18"/>
+      <c r="G63" s="18"/>
+      <c r="H63" s="18"/>
+      <c r="I63" s="18"/>
+      <c r="J63" s="18"/>
+      <c r="K63" s="18"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="14"/>
-      <c r="J64" s="14"/>
-      <c r="K64" s="14"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="18"/>
+      <c r="F64" s="18"/>
+      <c r="G64" s="18"/>
+      <c r="H64" s="18"/>
+      <c r="I64" s="18"/>
+      <c r="J64" s="18"/>
+      <c r="K64" s="18"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="14"/>
-      <c r="J65" s="14"/>
-      <c r="K65" s="14"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="18"/>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18"/>
+      <c r="H65" s="18"/>
+      <c r="I65" s="18"/>
+      <c r="J65" s="18"/>
+      <c r="K65" s="18"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="14"/>
-      <c r="J66" s="14"/>
-      <c r="K66" s="14"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="18"/>
+      <c r="H66" s="18"/>
+      <c r="I66" s="18"/>
+      <c r="J66" s="18"/>
+      <c r="K66" s="18"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="14"/>
-      <c r="J67" s="14"/>
-      <c r="K67" s="14"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="18"/>
+      <c r="E67" s="18"/>
+      <c r="F67" s="18"/>
+      <c r="G67" s="18"/>
+      <c r="H67" s="18"/>
+      <c r="I67" s="18"/>
+      <c r="J67" s="18"/>
+      <c r="K67" s="18"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="14"/>
-      <c r="J68" s="14"/>
-      <c r="K68" s="14"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="18"/>
+      <c r="E68" s="18"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="18"/>
+      <c r="H68" s="18"/>
+      <c r="I68" s="18"/>
+      <c r="J68" s="18"/>
+      <c r="K68" s="18"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="14"/>
-      <c r="J69" s="14"/>
-      <c r="K69" s="14"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="18"/>
+      <c r="E69" s="18"/>
+      <c r="F69" s="18"/>
+      <c r="G69" s="18"/>
+      <c r="H69" s="18"/>
+      <c r="I69" s="18"/>
+      <c r="J69" s="18"/>
+      <c r="K69" s="18"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="14"/>
-      <c r="J70" s="14"/>
-      <c r="K70" s="14"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="18"/>
+      <c r="H70" s="18"/>
+      <c r="I70" s="18"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="18"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="14"/>
-      <c r="J71" s="14"/>
-      <c r="K71" s="14"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="18"/>
+      <c r="E71" s="18"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="18"/>
+      <c r="H71" s="18"/>
+      <c r="I71" s="18"/>
+      <c r="J71" s="18"/>
+      <c r="K71" s="18"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="14"/>
-      <c r="J72" s="14"/>
-      <c r="K72" s="14"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="18"/>
+      <c r="E72" s="18"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="18"/>
+      <c r="H72" s="18"/>
+      <c r="I72" s="18"/>
+      <c r="J72" s="18"/>
+      <c r="K72" s="18"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="14"/>
-      <c r="J73" s="14"/>
-      <c r="K73" s="14"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="18"/>
+      <c r="H73" s="18"/>
+      <c r="I73" s="18"/>
+      <c r="J73" s="18"/>
+      <c r="K73" s="18"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="14"/>
-      <c r="J74" s="14"/>
-      <c r="K74" s="14"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="18"/>
+      <c r="E74" s="18"/>
+      <c r="F74" s="18"/>
+      <c r="G74" s="18"/>
+      <c r="H74" s="18"/>
+      <c r="I74" s="18"/>
+      <c r="J74" s="18"/>
+      <c r="K74" s="18"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="14"/>
-      <c r="J75" s="14"/>
-      <c r="K75" s="14"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="18"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="18"/>
+      <c r="H75" s="18"/>
+      <c r="I75" s="18"/>
+      <c r="J75" s="18"/>
+      <c r="K75" s="18"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="14"/>
-      <c r="J76" s="14"/>
-      <c r="K76" s="14"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="18"/>
+      <c r="E76" s="18"/>
+      <c r="F76" s="18"/>
+      <c r="G76" s="18"/>
+      <c r="H76" s="18"/>
+      <c r="I76" s="18"/>
+      <c r="J76" s="18"/>
+      <c r="K76" s="18"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="14"/>
-      <c r="J77" s="14"/>
-      <c r="K77" s="14"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="18"/>
+      <c r="F77" s="18"/>
+      <c r="G77" s="18"/>
+      <c r="H77" s="18"/>
+      <c r="I77" s="18"/>
+      <c r="J77" s="18"/>
+      <c r="K77" s="18"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="14"/>
-      <c r="J78" s="14"/>
-      <c r="K78" s="14"/>
+      <c r="C78" s="18"/>
+      <c r="D78" s="18"/>
+      <c r="E78" s="18"/>
+      <c r="F78" s="18"/>
+      <c r="G78" s="18"/>
+      <c r="H78" s="18"/>
+      <c r="I78" s="18"/>
+      <c r="J78" s="18"/>
+      <c r="K78" s="18"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="14"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="14"/>
-      <c r="J79" s="14"/>
-      <c r="K79" s="14"/>
+      <c r="C79" s="18"/>
+      <c r="D79" s="18"/>
+      <c r="E79" s="18"/>
+      <c r="F79" s="18"/>
+      <c r="G79" s="18"/>
+      <c r="H79" s="18"/>
+      <c r="I79" s="18"/>
+      <c r="J79" s="18"/>
+      <c r="K79" s="18"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="14"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
-      <c r="I80" s="14"/>
-      <c r="J80" s="14"/>
-      <c r="K80" s="14"/>
+      <c r="C80" s="18"/>
+      <c r="D80" s="18"/>
+      <c r="E80" s="18"/>
+      <c r="F80" s="18"/>
+      <c r="G80" s="18"/>
+      <c r="H80" s="18"/>
+      <c r="I80" s="18"/>
+      <c r="J80" s="18"/>
+      <c r="K80" s="18"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="14"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="14"/>
-      <c r="J81" s="14"/>
-      <c r="K81" s="14"/>
+      <c r="C81" s="18"/>
+      <c r="D81" s="18"/>
+      <c r="E81" s="18"/>
+      <c r="F81" s="18"/>
+      <c r="G81" s="18"/>
+      <c r="H81" s="18"/>
+      <c r="I81" s="18"/>
+      <c r="J81" s="18"/>
+      <c r="K81" s="18"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="14"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="14"/>
-      <c r="J82" s="14"/>
-      <c r="K82" s="14"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="18"/>
+      <c r="F82" s="18"/>
+      <c r="G82" s="18"/>
+      <c r="H82" s="18"/>
+      <c r="I82" s="18"/>
+      <c r="J82" s="18"/>
+      <c r="K82" s="18"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="14"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
-      <c r="H83" s="14"/>
-      <c r="I83" s="14"/>
-      <c r="J83" s="14"/>
-      <c r="K83" s="14"/>
+      <c r="C83" s="18"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="18"/>
+      <c r="F83" s="18"/>
+      <c r="G83" s="18"/>
+      <c r="H83" s="18"/>
+      <c r="I83" s="18"/>
+      <c r="J83" s="18"/>
+      <c r="K83" s="18"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="14" t="s">
+      <c r="C84" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D84" s="14">
-        <v>1</v>
-      </c>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="14"/>
-      <c r="I84" s="14"/>
-      <c r="J84" s="14"/>
-      <c r="K84" s="14"/>
+      <c r="D84" s="18">
+        <v>1</v>
+      </c>
+      <c r="E84" s="18"/>
+      <c r="F84" s="18"/>
+      <c r="G84" s="18"/>
+      <c r="H84" s="18"/>
+      <c r="I84" s="18"/>
+      <c r="J84" s="18"/>
+      <c r="K84" s="18"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="14"/>
-      <c r="D85" s="14"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
-      <c r="H85" s="14"/>
-      <c r="I85" s="14"/>
-      <c r="J85" s="14"/>
-      <c r="K85" s="14"/>
+      <c r="C85" s="18"/>
+      <c r="D85" s="18"/>
+      <c r="E85" s="18"/>
+      <c r="F85" s="18"/>
+      <c r="G85" s="18"/>
+      <c r="H85" s="18"/>
+      <c r="I85" s="18"/>
+      <c r="J85" s="18"/>
+      <c r="K85" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B2:N50"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="4" max="4" width="27.1636363636364" customWidth="1"/>
+    <col min="6" max="6" width="31.9090909090909" customWidth="1"/>
+    <col min="7" max="7" width="19.5272727272727" customWidth="1"/>
+    <col min="8" max="8" width="16.7545454545455" customWidth="1"/>
+    <col min="9" max="10" width="8.72727272727273" customWidth="1"/>
+    <col min="11" max="11" width="12.8181818181818" customWidth="1"/>
+    <col min="12" max="12" width="10.1818181818182" customWidth="1"/>
+    <col min="13" max="13" width="12.3636363636364" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14">
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14">
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14">
+      <c r="H4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14">
+      <c r="D8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14">
+      <c r="D9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="L9">
+        <v>0.05</v>
+      </c>
+      <c r="M9" s="2">
+        <v>1</v>
+      </c>
+      <c r="N9" s="2"/>
+    </row>
+    <row r="10" spans="2:14">
+      <c r="D10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1.11</v>
+      </c>
+      <c r="L10">
+        <v>0.05</v>
+      </c>
+      <c r="M10" s="2">
+        <v>1</v>
+      </c>
+      <c r="N10" s="2"/>
+    </row>
+    <row r="11" spans="2:14">
+      <c r="D11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1.15</v>
+      </c>
+      <c r="L11">
+        <v>0.08</v>
+      </c>
+      <c r="M11" s="2">
+        <v>1</v>
+      </c>
+      <c r="N11" s="2"/>
+    </row>
+    <row r="12" ht="16" spans="2:14">
+      <c r="D12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1.12</v>
+      </c>
+      <c r="L12">
+        <v>0.03</v>
+      </c>
+      <c r="M12" s="2">
+        <v>1</v>
+      </c>
+      <c r="N12" s="2"/>
+    </row>
+    <row r="13" spans="2:14">
+      <c r="D13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="L13">
+        <v>0.1</v>
+      </c>
+      <c r="M13" s="2">
+        <v>1</v>
+      </c>
+      <c r="N13" s="2"/>
+    </row>
+    <row r="14" spans="2:14">
+      <c r="D14" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="2">
+        <v>1.06</v>
+      </c>
+      <c r="L14">
+        <v>0.15</v>
+      </c>
+      <c r="M14" s="2">
+        <v>1</v>
+      </c>
+      <c r="N14" s="2"/>
+    </row>
+    <row r="15" spans="2:14">
+      <c r="D15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1.06</v>
+      </c>
+      <c r="L15">
+        <v>0.3</v>
+      </c>
+      <c r="M15" s="2">
+        <v>1</v>
+      </c>
+      <c r="N15" s="2"/>
+    </row>
+    <row r="16" ht="16" spans="2:14">
+      <c r="D16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" t="str">
+        <f>G15</f>
+        <v>CAP,GROWTH</v>
+      </c>
+      <c r="H16" t="str">
+        <f>H15</f>
+        <v>2025, 2150</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J16">
+        <f t="shared" ref="J16:L16" si="0">J12</f>
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="0"/>
+        <v>1.12</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="0"/>
+        <v>0.03</v>
+      </c>
+      <c r="M16">
+        <f>M15</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="16" spans="4:14">
+      <c r="D17" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" t="str">
+        <f t="shared" ref="G17:M17" si="1">G16</f>
+        <v>CAP,GROWTH</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="1"/>
+        <v>2025, 2150</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="1"/>
+        <v>1.12</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="1"/>
+        <v>0.03</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="16" spans="4:14">
+      <c r="D18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G18" t="str">
+        <f>G17</f>
+        <v>CAP,GROWTH</v>
+      </c>
+      <c r="H18" t="str">
+        <f>H17</f>
+        <v>2025, 2150</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="4:14">
+      <c r="H28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="4:14">
+      <c r="D29" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" t="s">
+        <v>60</v>
+      </c>
+      <c r="F29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G29" t="s">
+        <v>61</v>
+      </c>
+      <c r="H29" t="s">
+        <v>4</v>
+      </c>
+      <c r="I29" t="s">
+        <v>2</v>
+      </c>
+      <c r="J29" t="s">
+        <v>62</v>
+      </c>
+      <c r="K29" t="s">
+        <v>63</v>
+      </c>
+      <c r="L29" t="s">
+        <v>64</v>
+      </c>
+      <c r="M29" t="s">
+        <v>65</v>
+      </c>
+      <c r="N29" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="4:14">
+      <c r="D30" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G30" t="s">
+        <v>69</v>
+      </c>
+      <c r="H30" t="s">
+        <v>70</v>
+      </c>
+      <c r="I30" t="s">
+        <v>71</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>0.2</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="4:14">
+      <c r="D31" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G31" t="s">
+        <v>69</v>
+      </c>
+      <c r="H31" t="s">
+        <v>70</v>
+      </c>
+      <c r="I31" t="s">
+        <v>71</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31">
+        <v>0.2</v>
+      </c>
+      <c r="M31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="4:14">
+      <c r="D32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G32" t="s">
+        <v>69</v>
+      </c>
+      <c r="H32" t="s">
+        <v>70</v>
+      </c>
+      <c r="I32" t="s">
+        <v>71</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32">
+        <f t="shared" ref="K32:K50" si="2">K31</f>
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <f t="shared" ref="L32:L50" si="3">L31</f>
+        <v>0.2</v>
+      </c>
+      <c r="M32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="4:13">
+      <c r="D33" t="s">
+        <v>96</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G33" t="s">
+        <v>69</v>
+      </c>
+      <c r="H33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I33" t="s">
+        <v>71</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="M33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="4:13">
+      <c r="D34" t="s">
+        <v>98</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G34" t="s">
+        <v>69</v>
+      </c>
+      <c r="H34" t="s">
+        <v>70</v>
+      </c>
+      <c r="I34" t="s">
+        <v>71</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="M34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="4:13">
+      <c r="D35" t="s">
+        <v>100</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G35" t="s">
+        <v>69</v>
+      </c>
+      <c r="H35" t="s">
+        <v>70</v>
+      </c>
+      <c r="I35" t="s">
+        <v>71</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="M35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="4:13">
+      <c r="D36" t="s">
+        <v>102</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G36" t="s">
+        <v>69</v>
+      </c>
+      <c r="H36" t="s">
+        <v>70</v>
+      </c>
+      <c r="I36" t="s">
+        <v>71</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="M36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="4:13">
+      <c r="D37" t="s">
+        <v>104</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G37" t="s">
+        <v>69</v>
+      </c>
+      <c r="H37" t="s">
+        <v>70</v>
+      </c>
+      <c r="I37" t="s">
+        <v>71</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="M37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="4:13">
+      <c r="D38" t="s">
+        <v>106</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G38" t="s">
+        <v>69</v>
+      </c>
+      <c r="H38" t="s">
+        <v>70</v>
+      </c>
+      <c r="I38" t="s">
+        <v>71</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="M38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="4:13">
+      <c r="D39" t="s">
+        <v>108</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G39" t="s">
+        <v>69</v>
+      </c>
+      <c r="H39" t="s">
+        <v>70</v>
+      </c>
+      <c r="I39" t="s">
+        <v>71</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="M39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="4:13">
+      <c r="D40" t="s">
+        <v>110</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G40" t="s">
+        <v>69</v>
+      </c>
+      <c r="H40" t="str">
+        <f t="shared" ref="H40:M40" si="4">H39</f>
+        <v>2025, 2150</v>
+      </c>
+      <c r="I40" t="s">
+        <v>71</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="4:13">
+      <c r="D41" t="s">
+        <v>112</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G41" t="s">
+        <v>69</v>
+      </c>
+      <c r="H41" t="str">
+        <f t="shared" ref="H41:M41" si="5">H40</f>
+        <v>2025, 2150</v>
+      </c>
+      <c r="I41" t="s">
+        <v>71</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L41">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="4:13">
+      <c r="D42" t="s">
+        <v>114</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G42" t="s">
+        <v>69</v>
+      </c>
+      <c r="H42" t="str">
+        <f t="shared" ref="H42:M42" si="6">H41</f>
+        <v>2025, 2150</v>
+      </c>
+      <c r="I42" t="s">
+        <v>71</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="4:13">
+      <c r="D43" t="s">
+        <v>116</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G43" t="s">
+        <v>69</v>
+      </c>
+      <c r="H43" t="str">
+        <f t="shared" ref="H43:M43" si="7">H42</f>
+        <v>2025, 2150</v>
+      </c>
+      <c r="I43" t="s">
+        <v>71</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L43">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="4:13">
+      <c r="D44" t="s">
+        <v>118</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G44" t="s">
+        <v>69</v>
+      </c>
+      <c r="H44" t="str">
+        <f t="shared" ref="H44:M44" si="8">H43</f>
+        <v>2025, 2150</v>
+      </c>
+      <c r="I44" t="s">
+        <v>71</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L44">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="4:13">
+      <c r="D45" t="s">
+        <v>120</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G45" t="s">
+        <v>69</v>
+      </c>
+      <c r="H45" t="str">
+        <f t="shared" ref="H45:M45" si="9">H44</f>
+        <v>2025, 2150</v>
+      </c>
+      <c r="I45" t="s">
+        <v>71</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L45">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="M45">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="4:13">
+      <c r="D46" t="s">
+        <v>122</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G46" t="s">
+        <v>69</v>
+      </c>
+      <c r="H46" t="str">
+        <f t="shared" ref="H46:M46" si="10">H45</f>
+        <v>2025, 2150</v>
+      </c>
+      <c r="I46" t="s">
+        <v>71</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L46">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="M46">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="4:13">
+      <c r="D47" t="s">
+        <v>124</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G47" t="s">
+        <v>69</v>
+      </c>
+      <c r="H47" t="str">
+        <f t="shared" ref="H47:M47" si="11">H46</f>
+        <v>2025, 2150</v>
+      </c>
+      <c r="I47" t="s">
+        <v>71</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L47">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="M47">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="4:13">
+      <c r="D48" t="s">
+        <v>126</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G48" t="s">
+        <v>69</v>
+      </c>
+      <c r="H48" t="str">
+        <f t="shared" ref="H48:M48" si="12">H47</f>
+        <v>2025, 2150</v>
+      </c>
+      <c r="I48" t="s">
+        <v>71</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L48">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="M48">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="4:13">
+      <c r="D49" t="s">
+        <v>128</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G49" t="s">
+        <v>69</v>
+      </c>
+      <c r="H49" t="str">
+        <f t="shared" ref="H49:M49" si="13">H48</f>
+        <v>2025, 2150</v>
+      </c>
+      <c r="I49" t="s">
+        <v>71</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L49">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="M49">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="4:13">
+      <c r="D50" t="s">
+        <v>130</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G50" t="s">
+        <v>69</v>
+      </c>
+      <c r="H50" t="str">
+        <f t="shared" ref="H50:M50" si="14">H49</f>
+        <v>2025, 2150</v>
+      </c>
+      <c r="I50" t="s">
+        <v>71</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L50">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="M50">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -853,12 +853,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -3266,10 +3266,10 @@
         <v>1</v>
       </c>
       <c r="K30">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L30">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="M30">
         <v>1</v>
@@ -3295,10 +3295,11 @@
         <v>1</v>
       </c>
       <c r="K31">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L31">
-        <v>0.2</v>
+        <f>L30</f>
+        <v>0.01</v>
       </c>
       <c r="M31">
         <v>1</v>
@@ -3325,11 +3326,11 @@
       </c>
       <c r="K32">
         <f t="shared" ref="K32:K50" si="2">K31</f>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L32">
         <f t="shared" ref="L32:L50" si="3">L31</f>
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="M32">
         <v>1</v>
@@ -3356,11 +3357,11 @@
       </c>
       <c r="K33">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L33">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="M33">
         <v>1</v>
@@ -3387,11 +3388,11 @@
       </c>
       <c r="K34">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L34">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="M34">
         <v>1</v>
@@ -3418,11 +3419,11 @@
       </c>
       <c r="K35">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L35">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="M35">
         <v>1</v>
@@ -3449,11 +3450,11 @@
       </c>
       <c r="K36">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L36">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="M36">
         <v>1</v>
@@ -3480,11 +3481,11 @@
       </c>
       <c r="K37">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L37">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="M37">
         <v>1</v>
@@ -3511,11 +3512,11 @@
       </c>
       <c r="K38">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L38">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="M38">
         <v>1</v>
@@ -3542,11 +3543,11 @@
       </c>
       <c r="K39">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L39">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="M39">
         <v>1</v>
@@ -3575,11 +3576,11 @@
       </c>
       <c r="K40">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L40">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="M40">
         <f t="shared" si="4"/>
@@ -3609,11 +3610,11 @@
       </c>
       <c r="K41">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L41">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="M41">
         <f t="shared" si="5"/>
@@ -3643,11 +3644,11 @@
       </c>
       <c r="K42">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L42">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="M42">
         <f t="shared" si="6"/>
@@ -3677,11 +3678,11 @@
       </c>
       <c r="K43">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L43">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="M43">
         <f t="shared" si="7"/>
@@ -3711,11 +3712,11 @@
       </c>
       <c r="K44">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L44">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="M44">
         <f t="shared" si="8"/>
@@ -3745,11 +3746,11 @@
       </c>
       <c r="K45">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L45">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="M45">
         <f t="shared" si="9"/>
@@ -3779,11 +3780,11 @@
       </c>
       <c r="K46">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L46">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="M46">
         <f t="shared" si="10"/>
@@ -3813,11 +3814,11 @@
       </c>
       <c r="K47">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L47">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="M47">
         <f t="shared" si="11"/>
@@ -3847,11 +3848,11 @@
       </c>
       <c r="K48">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L48">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="M48">
         <f t="shared" si="12"/>
@@ -3881,11 +3882,11 @@
       </c>
       <c r="K49">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L49">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="M49">
         <f t="shared" si="13"/>
@@ -3915,11 +3916,11 @@
       </c>
       <c r="K50">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L50">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="M50">
         <f t="shared" si="14"/>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -853,12 +853,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -3206,8 +3206,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="4:14">
-      <c r="H28" t="s">
+    <row r="25" spans="4:14">
+      <c r="H25" t="s">
         <v>58</v>
       </c>
     </row>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -243,7 +243,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="133">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -519,6 +519,9 @@
   </si>
   <si>
     <t>PyroRecy-LFP</t>
+  </si>
+  <si>
+    <t>LO</t>
   </si>
   <si>
     <t>UC_Grow_Recy2</t>
@@ -860,16 +863,16 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="0"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -3206,8 +3209,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="4:14">
-      <c r="H25" t="s">
+    <row r="28" spans="4:14">
+      <c r="H28" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3260,13 +3263,13 @@
         <v>70</v>
       </c>
       <c r="I30" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J30">
         <v>1</v>
       </c>
       <c r="K30">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L30">
         <v>0.01</v>
@@ -3277,10 +3280,10 @@
     </row>
     <row r="31" spans="4:14">
       <c r="D31" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G31" t="s">
         <v>69</v>
@@ -3289,13 +3292,13 @@
         <v>70</v>
       </c>
       <c r="I31" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J31">
         <v>1</v>
       </c>
       <c r="K31">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L31">
         <f>L30</f>
@@ -3307,10 +3310,10 @@
     </row>
     <row r="32" spans="4:14">
       <c r="D32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G32" t="s">
         <v>69</v>
@@ -3319,17 +3322,16 @@
         <v>70</v>
       </c>
       <c r="I32" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J32">
         <v>1</v>
       </c>
       <c r="K32">
-        <f t="shared" ref="K32:K50" si="2">K31</f>
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L32">
-        <f t="shared" ref="L32:L50" si="3">L31</f>
+        <f t="shared" ref="L32:L50" si="2">L31</f>
         <v>0.01</v>
       </c>
       <c r="M32">
@@ -3338,10 +3340,10 @@
     </row>
     <row r="33" spans="4:13">
       <c r="D33" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G33" t="s">
         <v>69</v>
@@ -3350,17 +3352,17 @@
         <v>70</v>
       </c>
       <c r="I33" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
       <c r="K33">
+        <f t="shared" ref="K32:K50" si="3">K32</f>
+        <v>1</v>
+      </c>
+      <c r="L33">
         <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="L33">
-        <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
       <c r="M33">
@@ -3369,10 +3371,10 @@
     </row>
     <row r="34" spans="4:13">
       <c r="D34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G34" t="s">
         <v>69</v>
@@ -3381,17 +3383,17 @@
         <v>70</v>
       </c>
       <c r="I34" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J34">
         <v>1</v>
       </c>
       <c r="K34">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L34">
         <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="L34">
-        <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
       <c r="M34">
@@ -3400,10 +3402,10 @@
     </row>
     <row r="35" spans="4:13">
       <c r="D35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G35" t="s">
         <v>69</v>
@@ -3412,17 +3414,17 @@
         <v>70</v>
       </c>
       <c r="I35" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J35">
         <v>1</v>
       </c>
       <c r="K35">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L35">
         <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="L35">
-        <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
       <c r="M35">
@@ -3431,10 +3433,10 @@
     </row>
     <row r="36" spans="4:13">
       <c r="D36" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G36" t="s">
         <v>69</v>
@@ -3443,17 +3445,17 @@
         <v>70</v>
       </c>
       <c r="I36" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J36">
         <v>1</v>
       </c>
       <c r="K36">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L36">
         <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="L36">
-        <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
       <c r="M36">
@@ -3462,10 +3464,10 @@
     </row>
     <row r="37" spans="4:13">
       <c r="D37" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G37" t="s">
         <v>69</v>
@@ -3474,17 +3476,17 @@
         <v>70</v>
       </c>
       <c r="I37" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J37">
         <v>1</v>
       </c>
       <c r="K37">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L37">
         <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="L37">
-        <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
       <c r="M37">
@@ -3493,10 +3495,10 @@
     </row>
     <row r="38" spans="4:13">
       <c r="D38" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G38" t="s">
         <v>69</v>
@@ -3505,17 +3507,17 @@
         <v>70</v>
       </c>
       <c r="I38" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J38">
         <v>1</v>
       </c>
       <c r="K38">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L38">
         <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="L38">
-        <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
       <c r="M38">
@@ -3524,10 +3526,10 @@
     </row>
     <row r="39" spans="4:13">
       <c r="D39" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G39" t="s">
         <v>69</v>
@@ -3536,17 +3538,17 @@
         <v>70</v>
       </c>
       <c r="I39" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J39">
         <v>1</v>
       </c>
       <c r="K39">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L39">
         <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="L39">
-        <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
       <c r="M39">
@@ -3555,10 +3557,10 @@
     </row>
     <row r="40" spans="4:13">
       <c r="D40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G40" t="s">
         <v>69</v>
@@ -3568,18 +3570,18 @@
         <v>2025, 2150</v>
       </c>
       <c r="I40" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J40">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K40">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L40">
         <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="L40">
-        <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
       <c r="M40">
@@ -3589,10 +3591,10 @@
     </row>
     <row r="41" spans="4:13">
       <c r="D41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G41" t="s">
         <v>69</v>
@@ -3602,18 +3604,18 @@
         <v>2025, 2150</v>
       </c>
       <c r="I41" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J41">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K41">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L41">
         <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="L41">
-        <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
       <c r="M41">
@@ -3623,10 +3625,10 @@
     </row>
     <row r="42" spans="4:13">
       <c r="D42" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G42" t="s">
         <v>69</v>
@@ -3636,18 +3638,18 @@
         <v>2025, 2150</v>
       </c>
       <c r="I42" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J42">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K42">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L42">
         <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="L42">
-        <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
       <c r="M42">
@@ -3657,10 +3659,10 @@
     </row>
     <row r="43" spans="4:13">
       <c r="D43" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G43" t="s">
         <v>69</v>
@@ -3670,18 +3672,18 @@
         <v>2025, 2150</v>
       </c>
       <c r="I43" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J43">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K43">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L43">
         <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="L43">
-        <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
       <c r="M43">
@@ -3691,10 +3693,10 @@
     </row>
     <row r="44" spans="4:13">
       <c r="D44" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G44" t="s">
         <v>69</v>
@@ -3704,18 +3706,18 @@
         <v>2025, 2150</v>
       </c>
       <c r="I44" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J44">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K44">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L44">
         <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="L44">
-        <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
       <c r="M44">
@@ -3725,10 +3727,10 @@
     </row>
     <row r="45" spans="4:13">
       <c r="D45" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G45" t="s">
         <v>69</v>
@@ -3738,18 +3740,18 @@
         <v>2025, 2150</v>
       </c>
       <c r="I45" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J45">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="K45">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L45">
         <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="L45">
-        <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
       <c r="M45">
@@ -3759,10 +3761,10 @@
     </row>
     <row r="46" spans="4:13">
       <c r="D46" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G46" t="s">
         <v>69</v>
@@ -3772,18 +3774,18 @@
         <v>2025, 2150</v>
       </c>
       <c r="I46" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J46">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="K46">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L46">
         <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="L46">
-        <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
       <c r="M46">
@@ -3793,10 +3795,10 @@
     </row>
     <row r="47" spans="4:13">
       <c r="D47" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G47" t="s">
         <v>69</v>
@@ -3806,18 +3808,18 @@
         <v>2025, 2150</v>
       </c>
       <c r="I47" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J47">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="K47">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L47">
         <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="L47">
-        <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
       <c r="M47">
@@ -3827,10 +3829,10 @@
     </row>
     <row r="48" spans="4:13">
       <c r="D48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G48" t="s">
         <v>69</v>
@@ -3840,18 +3842,18 @@
         <v>2025, 2150</v>
       </c>
       <c r="I48" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J48">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K48">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L48">
         <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="L48">
-        <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
       <c r="M48">
@@ -3861,10 +3863,10 @@
     </row>
     <row r="49" spans="4:13">
       <c r="D49" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G49" t="s">
         <v>69</v>
@@ -3874,18 +3876,18 @@
         <v>2025, 2150</v>
       </c>
       <c r="I49" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J49">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="K49">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L49">
         <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="L49">
-        <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
       <c r="M49">
@@ -3895,10 +3897,10 @@
     </row>
     <row r="50" spans="4:13">
       <c r="D50" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G50" t="s">
         <v>69</v>
@@ -3908,18 +3910,18 @@
         <v>2025, 2150</v>
       </c>
       <c r="I50" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="J50">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="K50">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L50">
         <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="L50">
-        <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
       <c r="M50">

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -243,7 +243,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="106">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -518,7 +518,10 @@
     <t>UC_Grow_Recy1</t>
   </si>
   <si>
-    <t>PyroRecy-LFP</t>
+    <t>Tra_EV_Batt-LFP_fromrecy</t>
+  </si>
+  <si>
+    <t>2030, 2150</t>
   </si>
   <si>
     <t>LO</t>
@@ -527,121 +530,37 @@
     <t>UC_Grow_Recy2</t>
   </si>
   <si>
-    <t>PyroRecy-LMO</t>
+    <t>Tra_EV_Batt-LMO_fromrecy</t>
   </si>
   <si>
     <t>UC_Grow_Recy3</t>
   </si>
   <si>
-    <t>PyroRecy-NCA</t>
+    <t>Tra_EV_Batt-NCA_fromrecy</t>
   </si>
   <si>
     <t>UC_Grow_Recy4</t>
   </si>
   <si>
-    <t>PyroRecy-NMC111</t>
+    <t>Tra_EV_Batt-NMC111_fromrecy</t>
   </si>
   <si>
     <t>UC_Grow_Recy5</t>
   </si>
   <si>
-    <t>PyroRecy-NMC532</t>
+    <t>Tra_EV_Batt-NMC532_fromrecy</t>
   </si>
   <si>
     <t>UC_Grow_Recy6</t>
   </si>
   <si>
-    <t>PyroRecy-NMC622</t>
+    <t>Tra_EV_Batt-NMC622_fromrecy</t>
   </si>
   <si>
     <t>UC_Grow_Recy7</t>
   </si>
   <si>
-    <t>PyroRecy-NMC811</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy8</t>
-  </si>
-  <si>
-    <t>HydRecy-LFP</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy9</t>
-  </si>
-  <si>
-    <t>HydRecy-LMO</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy10</t>
-  </si>
-  <si>
-    <t>HydRecy-NCA</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy11</t>
-  </si>
-  <si>
-    <t>HydRecy-NMC111</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy12</t>
-  </si>
-  <si>
-    <t>HydRecy-NMC532</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy13</t>
-  </si>
-  <si>
-    <t>HydRecy-NMC622</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy14</t>
-  </si>
-  <si>
-    <t>HydRecy-NMC811</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy15</t>
-  </si>
-  <si>
-    <t>DirRecy-LFP</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy16</t>
-  </si>
-  <si>
-    <t>DirRecy-LMO</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy17</t>
-  </si>
-  <si>
-    <t>DirRecy-NCA</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy18</t>
-  </si>
-  <si>
-    <t>DirRecy-NMC111</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy19</t>
-  </si>
-  <si>
-    <t>DirRecy-NMC532</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy20</t>
-  </si>
-  <si>
-    <t>DirRecy-NMC622</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy21</t>
-  </si>
-  <si>
-    <t>DirRecy-NMC811</t>
+    <t>Tra_EV_Batt-NMC811_fromrecy</t>
   </si>
 </sst>
 </file>
@@ -856,12 +775,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -874,11 +787,17 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -887,7 +806,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.799860000610352"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -899,12 +818,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="3"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1102,9 +1015,18 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE2E6"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -1260,7 +1182,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1272,123 +1194,123 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1397,25 +1319,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="49" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="53">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1949,7 +1876,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="23">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -2063,10 +1990,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="19"/>
+      <c r="K10" s="22"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="19"/>
+      <c r="K11" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2087,12 +2014,12 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:14">
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="11"/>
     </row>
     <row r="6" spans="2:14">
       <c r="B6" t="s">
@@ -2107,7 +2034,7 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="12" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2115,13 +2042,13 @@
       <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="13">
         <v>10</v>
       </c>
     </row>
@@ -2129,17 +2056,17 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="13">
         <v>7</v>
       </c>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
     </row>
     <row r="9" ht="16" spans="2:14">
       <c r="B9" t="s">
@@ -2148,10 +2075,10 @@
       <c r="C9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="13">
         <v>10</v>
       </c>
       <c r="J9" t="s">
@@ -2174,19 +2101,19 @@
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="13">
         <v>8</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="L10" s="12" t="s">
+      <c r="L10" s="15" t="s">
         <v>40</v>
       </c>
       <c r="M10">
@@ -2203,10 +2130,10 @@
       <c r="C11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="10">
         <v>1.5</v>
       </c>
     </row>
@@ -2217,10 +2144,10 @@
       <c r="C12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="10">
         <v>1.5</v>
       </c>
     </row>
@@ -2228,13 +2155,13 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="11">
         <v>2</v>
       </c>
     </row>
@@ -2242,13 +2169,13 @@
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2256,13 +2183,13 @@
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2270,13 +2197,13 @@
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="17">
         <v>12</v>
       </c>
     </row>
@@ -2284,31 +2211,31 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="19">
         <v>0.2</v>
       </c>
-      <c r="F17" s="8"/>
+      <c r="F17" s="11"/>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="19">
         <v>0.2</v>
       </c>
-      <c r="F18" s="8"/>
+      <c r="F18" s="11"/>
     </row>
     <row r="19" ht="16" spans="2:6">
       <c r="B19" t="s">
@@ -2317,28 +2244,28 @@
       <c r="C19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="19">
         <v>0.2</v>
       </c>
-      <c r="F19" s="8"/>
+      <c r="F19" s="11"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="19">
         <v>0.5</v>
       </c>
-      <c r="F20" s="8"/>
+      <c r="F20" s="11"/>
     </row>
     <row r="21" ht="16" spans="2:6">
       <c r="B21" t="s">
@@ -2347,13 +2274,13 @@
       <c r="C21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="19">
         <v>0.8</v>
       </c>
-      <c r="F21" s="8"/>
+      <c r="F21" s="11"/>
     </row>
     <row r="22" ht="16" spans="2:6">
       <c r="B22" t="s">
@@ -2362,468 +2289,468 @@
       <c r="C22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="8"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="11"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="8">
-        <v>1</v>
-      </c>
-      <c r="F23" s="8"/>
+      <c r="E23" s="11">
+        <v>1</v>
+      </c>
+      <c r="F23" s="11"/>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E24" s="8">
-        <v>1</v>
-      </c>
-      <c r="F24" s="8"/>
+      <c r="E24" s="11">
+        <v>1</v>
+      </c>
+      <c r="F24" s="11"/>
     </row>
     <row r="25" ht="16" spans="2:6">
       <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E25" s="8">
-        <v>1</v>
-      </c>
-      <c r="F25" s="8"/>
+      <c r="E25" s="11">
+        <v>1</v>
+      </c>
+      <c r="F25" s="11"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="10">
         <v>0.05</v>
       </c>
-      <c r="F26" s="8"/>
+      <c r="F26" s="11"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="8"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="11"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
     </row>
     <row r="38" spans="3:5">
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="18" t="s">
+      <c r="C54" s="21" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="18"/>
-      <c r="E56" s="18"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="18"/>
-      <c r="I56" s="18"/>
-      <c r="J56" s="18"/>
-      <c r="K56" s="18"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="21"/>
+      <c r="G56" s="21"/>
+      <c r="H56" s="21"/>
+      <c r="I56" s="21"/>
+      <c r="J56" s="21"/>
+      <c r="K56" s="21"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="18" t="s">
+      <c r="C57" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="D57" s="18" t="s">
+      <c r="D57" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="18" t="s">
+      <c r="E57" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="F57" s="18" t="s">
+      <c r="F57" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G57" s="18" t="s">
+      <c r="G57" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="H57" s="18" t="s">
+      <c r="H57" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="I57" s="18" t="s">
+      <c r="I57" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J57" s="18" t="s">
+      <c r="J57" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="K57" s="18" t="s">
+      <c r="K57" s="21" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="18"/>
-      <c r="D58" s="18"/>
-      <c r="E58" s="18"/>
-      <c r="F58" s="18"/>
-      <c r="G58" s="18"/>
-      <c r="H58" s="18"/>
-      <c r="I58" s="18"/>
-      <c r="J58" s="18"/>
-      <c r="K58" s="18"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="21"/>
+      <c r="H58" s="21"/>
+      <c r="I58" s="21"/>
+      <c r="J58" s="21"/>
+      <c r="K58" s="21"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="18"/>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18"/>
-      <c r="F59" s="18"/>
-      <c r="G59" s="18"/>
-      <c r="H59" s="18"/>
-      <c r="I59" s="18"/>
-      <c r="J59" s="18"/>
-      <c r="K59" s="18"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="21"/>
+      <c r="G59" s="21"/>
+      <c r="H59" s="21"/>
+      <c r="I59" s="21"/>
+      <c r="J59" s="21"/>
+      <c r="K59" s="21"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="18"/>
-      <c r="D60" s="18"/>
-      <c r="E60" s="18"/>
-      <c r="F60" s="18"/>
-      <c r="G60" s="18"/>
-      <c r="H60" s="18"/>
-      <c r="I60" s="18"/>
-      <c r="J60" s="18"/>
-      <c r="K60" s="18"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="21"/>
+      <c r="G60" s="21"/>
+      <c r="H60" s="21"/>
+      <c r="I60" s="21"/>
+      <c r="J60" s="21"/>
+      <c r="K60" s="21"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="18"/>
-      <c r="D61" s="18"/>
-      <c r="E61" s="18"/>
-      <c r="F61" s="18"/>
-      <c r="G61" s="18"/>
-      <c r="H61" s="18"/>
-      <c r="I61" s="18"/>
-      <c r="J61" s="18"/>
-      <c r="K61" s="18"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="21"/>
+      <c r="G61" s="21"/>
+      <c r="H61" s="21"/>
+      <c r="I61" s="21"/>
+      <c r="J61" s="21"/>
+      <c r="K61" s="21"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="18"/>
-      <c r="D62" s="18"/>
-      <c r="E62" s="18"/>
-      <c r="F62" s="18"/>
-      <c r="G62" s="18"/>
-      <c r="H62" s="18"/>
-      <c r="I62" s="18"/>
-      <c r="J62" s="18"/>
-      <c r="K62" s="18"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="21"/>
+      <c r="G62" s="21"/>
+      <c r="H62" s="21"/>
+      <c r="I62" s="21"/>
+      <c r="J62" s="21"/>
+      <c r="K62" s="21"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="18"/>
-      <c r="D63" s="18"/>
-      <c r="E63" s="18"/>
-      <c r="F63" s="18"/>
-      <c r="G63" s="18"/>
-      <c r="H63" s="18"/>
-      <c r="I63" s="18"/>
-      <c r="J63" s="18"/>
-      <c r="K63" s="18"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="21"/>
+      <c r="G63" s="21"/>
+      <c r="H63" s="21"/>
+      <c r="I63" s="21"/>
+      <c r="J63" s="21"/>
+      <c r="K63" s="21"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="18"/>
-      <c r="D64" s="18"/>
-      <c r="E64" s="18"/>
-      <c r="F64" s="18"/>
-      <c r="G64" s="18"/>
-      <c r="H64" s="18"/>
-      <c r="I64" s="18"/>
-      <c r="J64" s="18"/>
-      <c r="K64" s="18"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="21"/>
+      <c r="G64" s="21"/>
+      <c r="H64" s="21"/>
+      <c r="I64" s="21"/>
+      <c r="J64" s="21"/>
+      <c r="K64" s="21"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="18"/>
-      <c r="D65" s="18"/>
-      <c r="E65" s="18"/>
-      <c r="F65" s="18"/>
-      <c r="G65" s="18"/>
-      <c r="H65" s="18"/>
-      <c r="I65" s="18"/>
-      <c r="J65" s="18"/>
-      <c r="K65" s="18"/>
+      <c r="C65" s="21"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="21"/>
+      <c r="G65" s="21"/>
+      <c r="H65" s="21"/>
+      <c r="I65" s="21"/>
+      <c r="J65" s="21"/>
+      <c r="K65" s="21"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="18"/>
-      <c r="D66" s="18"/>
-      <c r="E66" s="18"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="18"/>
-      <c r="H66" s="18"/>
-      <c r="I66" s="18"/>
-      <c r="J66" s="18"/>
-      <c r="K66" s="18"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="21"/>
+      <c r="G66" s="21"/>
+      <c r="H66" s="21"/>
+      <c r="I66" s="21"/>
+      <c r="J66" s="21"/>
+      <c r="K66" s="21"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="18"/>
-      <c r="D67" s="18"/>
-      <c r="E67" s="18"/>
-      <c r="F67" s="18"/>
-      <c r="G67" s="18"/>
-      <c r="H67" s="18"/>
-      <c r="I67" s="18"/>
-      <c r="J67" s="18"/>
-      <c r="K67" s="18"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="21"/>
+      <c r="G67" s="21"/>
+      <c r="H67" s="21"/>
+      <c r="I67" s="21"/>
+      <c r="J67" s="21"/>
+      <c r="K67" s="21"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="18"/>
-      <c r="D68" s="18"/>
-      <c r="E68" s="18"/>
-      <c r="F68" s="18"/>
-      <c r="G68" s="18"/>
-      <c r="H68" s="18"/>
-      <c r="I68" s="18"/>
-      <c r="J68" s="18"/>
-      <c r="K68" s="18"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="21"/>
+      <c r="H68" s="21"/>
+      <c r="I68" s="21"/>
+      <c r="J68" s="21"/>
+      <c r="K68" s="21"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="18"/>
-      <c r="D69" s="18"/>
-      <c r="E69" s="18"/>
-      <c r="F69" s="18"/>
-      <c r="G69" s="18"/>
-      <c r="H69" s="18"/>
-      <c r="I69" s="18"/>
-      <c r="J69" s="18"/>
-      <c r="K69" s="18"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="21"/>
+      <c r="H69" s="21"/>
+      <c r="I69" s="21"/>
+      <c r="J69" s="21"/>
+      <c r="K69" s="21"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="18"/>
-      <c r="D70" s="18"/>
-      <c r="E70" s="18"/>
-      <c r="F70" s="18"/>
-      <c r="G70" s="18"/>
-      <c r="H70" s="18"/>
-      <c r="I70" s="18"/>
-      <c r="J70" s="18"/>
-      <c r="K70" s="18"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="21"/>
+      <c r="H70" s="21"/>
+      <c r="I70" s="21"/>
+      <c r="J70" s="21"/>
+      <c r="K70" s="21"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="18"/>
-      <c r="D71" s="18"/>
-      <c r="E71" s="18"/>
-      <c r="F71" s="18"/>
-      <c r="G71" s="18"/>
-      <c r="H71" s="18"/>
-      <c r="I71" s="18"/>
-      <c r="J71" s="18"/>
-      <c r="K71" s="18"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="21"/>
+      <c r="H71" s="21"/>
+      <c r="I71" s="21"/>
+      <c r="J71" s="21"/>
+      <c r="K71" s="21"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="18"/>
-      <c r="D72" s="18"/>
-      <c r="E72" s="18"/>
-      <c r="F72" s="18"/>
-      <c r="G72" s="18"/>
-      <c r="H72" s="18"/>
-      <c r="I72" s="18"/>
-      <c r="J72" s="18"/>
-      <c r="K72" s="18"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="21"/>
+      <c r="H72" s="21"/>
+      <c r="I72" s="21"/>
+      <c r="J72" s="21"/>
+      <c r="K72" s="21"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="18"/>
-      <c r="D73" s="18"/>
-      <c r="E73" s="18"/>
-      <c r="F73" s="18"/>
-      <c r="G73" s="18"/>
-      <c r="H73" s="18"/>
-      <c r="I73" s="18"/>
-      <c r="J73" s="18"/>
-      <c r="K73" s="18"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="21"/>
+      <c r="I73" s="21"/>
+      <c r="J73" s="21"/>
+      <c r="K73" s="21"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="18"/>
-      <c r="D74" s="18"/>
-      <c r="E74" s="18"/>
-      <c r="F74" s="18"/>
-      <c r="G74" s="18"/>
-      <c r="H74" s="18"/>
-      <c r="I74" s="18"/>
-      <c r="J74" s="18"/>
-      <c r="K74" s="18"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="21"/>
+      <c r="G74" s="21"/>
+      <c r="H74" s="21"/>
+      <c r="I74" s="21"/>
+      <c r="J74" s="21"/>
+      <c r="K74" s="21"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="18"/>
-      <c r="D75" s="18"/>
-      <c r="E75" s="18"/>
-      <c r="F75" s="18"/>
-      <c r="G75" s="18"/>
-      <c r="H75" s="18"/>
-      <c r="I75" s="18"/>
-      <c r="J75" s="18"/>
-      <c r="K75" s="18"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="21"/>
+      <c r="G75" s="21"/>
+      <c r="H75" s="21"/>
+      <c r="I75" s="21"/>
+      <c r="J75" s="21"/>
+      <c r="K75" s="21"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="18"/>
-      <c r="D76" s="18"/>
-      <c r="E76" s="18"/>
-      <c r="F76" s="18"/>
-      <c r="G76" s="18"/>
-      <c r="H76" s="18"/>
-      <c r="I76" s="18"/>
-      <c r="J76" s="18"/>
-      <c r="K76" s="18"/>
+      <c r="C76" s="21"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="21"/>
+      <c r="F76" s="21"/>
+      <c r="G76" s="21"/>
+      <c r="H76" s="21"/>
+      <c r="I76" s="21"/>
+      <c r="J76" s="21"/>
+      <c r="K76" s="21"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="18"/>
-      <c r="F77" s="18"/>
-      <c r="G77" s="18"/>
-      <c r="H77" s="18"/>
-      <c r="I77" s="18"/>
-      <c r="J77" s="18"/>
-      <c r="K77" s="18"/>
+      <c r="C77" s="21"/>
+      <c r="D77" s="21"/>
+      <c r="E77" s="21"/>
+      <c r="F77" s="21"/>
+      <c r="G77" s="21"/>
+      <c r="H77" s="21"/>
+      <c r="I77" s="21"/>
+      <c r="J77" s="21"/>
+      <c r="K77" s="21"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="18"/>
-      <c r="D78" s="18"/>
-      <c r="E78" s="18"/>
-      <c r="F78" s="18"/>
-      <c r="G78" s="18"/>
-      <c r="H78" s="18"/>
-      <c r="I78" s="18"/>
-      <c r="J78" s="18"/>
-      <c r="K78" s="18"/>
+      <c r="C78" s="21"/>
+      <c r="D78" s="21"/>
+      <c r="E78" s="21"/>
+      <c r="F78" s="21"/>
+      <c r="G78" s="21"/>
+      <c r="H78" s="21"/>
+      <c r="I78" s="21"/>
+      <c r="J78" s="21"/>
+      <c r="K78" s="21"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="18"/>
-      <c r="D79" s="18"/>
-      <c r="E79" s="18"/>
-      <c r="F79" s="18"/>
-      <c r="G79" s="18"/>
-      <c r="H79" s="18"/>
-      <c r="I79" s="18"/>
-      <c r="J79" s="18"/>
-      <c r="K79" s="18"/>
+      <c r="C79" s="21"/>
+      <c r="D79" s="21"/>
+      <c r="E79" s="21"/>
+      <c r="F79" s="21"/>
+      <c r="G79" s="21"/>
+      <c r="H79" s="21"/>
+      <c r="I79" s="21"/>
+      <c r="J79" s="21"/>
+      <c r="K79" s="21"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="18"/>
-      <c r="D80" s="18"/>
-      <c r="E80" s="18"/>
-      <c r="F80" s="18"/>
-      <c r="G80" s="18"/>
-      <c r="H80" s="18"/>
-      <c r="I80" s="18"/>
-      <c r="J80" s="18"/>
-      <c r="K80" s="18"/>
+      <c r="C80" s="21"/>
+      <c r="D80" s="21"/>
+      <c r="E80" s="21"/>
+      <c r="F80" s="21"/>
+      <c r="G80" s="21"/>
+      <c r="H80" s="21"/>
+      <c r="I80" s="21"/>
+      <c r="J80" s="21"/>
+      <c r="K80" s="21"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="18"/>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
-      <c r="F81" s="18"/>
-      <c r="G81" s="18"/>
-      <c r="H81" s="18"/>
-      <c r="I81" s="18"/>
-      <c r="J81" s="18"/>
-      <c r="K81" s="18"/>
+      <c r="C81" s="21"/>
+      <c r="D81" s="21"/>
+      <c r="E81" s="21"/>
+      <c r="F81" s="21"/>
+      <c r="G81" s="21"/>
+      <c r="H81" s="21"/>
+      <c r="I81" s="21"/>
+      <c r="J81" s="21"/>
+      <c r="K81" s="21"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="18"/>
-      <c r="D82" s="18"/>
-      <c r="E82" s="18"/>
-      <c r="F82" s="18"/>
-      <c r="G82" s="18"/>
-      <c r="H82" s="18"/>
-      <c r="I82" s="18"/>
-      <c r="J82" s="18"/>
-      <c r="K82" s="18"/>
+      <c r="C82" s="21"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="21"/>
+      <c r="F82" s="21"/>
+      <c r="G82" s="21"/>
+      <c r="H82" s="21"/>
+      <c r="I82" s="21"/>
+      <c r="J82" s="21"/>
+      <c r="K82" s="21"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="18"/>
-      <c r="D83" s="18"/>
-      <c r="E83" s="18"/>
-      <c r="F83" s="18"/>
-      <c r="G83" s="18"/>
-      <c r="H83" s="18"/>
-      <c r="I83" s="18"/>
-      <c r="J83" s="18"/>
-      <c r="K83" s="18"/>
+      <c r="C83" s="21"/>
+      <c r="D83" s="21"/>
+      <c r="E83" s="21"/>
+      <c r="F83" s="21"/>
+      <c r="G83" s="21"/>
+      <c r="H83" s="21"/>
+      <c r="I83" s="21"/>
+      <c r="J83" s="21"/>
+      <c r="K83" s="21"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="18" t="s">
+      <c r="C84" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="D84" s="18">
-        <v>1</v>
-      </c>
-      <c r="E84" s="18"/>
-      <c r="F84" s="18"/>
-      <c r="G84" s="18"/>
-      <c r="H84" s="18"/>
-      <c r="I84" s="18"/>
-      <c r="J84" s="18"/>
-      <c r="K84" s="18"/>
+      <c r="D84" s="21">
+        <v>1</v>
+      </c>
+      <c r="E84" s="21"/>
+      <c r="F84" s="21"/>
+      <c r="G84" s="21"/>
+      <c r="H84" s="21"/>
+      <c r="I84" s="21"/>
+      <c r="J84" s="21"/>
+      <c r="K84" s="21"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="18"/>
-      <c r="D85" s="18"/>
-      <c r="E85" s="18"/>
-      <c r="F85" s="18"/>
-      <c r="G85" s="18"/>
-      <c r="H85" s="18"/>
-      <c r="I85" s="18"/>
-      <c r="J85" s="18"/>
-      <c r="K85" s="18"/>
+      <c r="C85" s="21"/>
+      <c r="D85" s="21"/>
+      <c r="E85" s="21"/>
+      <c r="F85" s="21"/>
+      <c r="G85" s="21"/>
+      <c r="H85" s="21"/>
+      <c r="I85" s="21"/>
+      <c r="J85" s="21"/>
+      <c r="K85" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2835,7 +2762,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:N50"/>
+  <dimension ref="B2:N52"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="4" max="4" width="27.1636363636364" customWidth="1"/>
@@ -3249,7 +3176,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="4:14">
+    <row r="30" ht="16" spans="4:14">
       <c r="D30" t="s">
         <v>90</v>
       </c>
@@ -3260,10 +3187,10 @@
         <v>69</v>
       </c>
       <c r="H30" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="I30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -3278,21 +3205,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="4:14">
+    <row r="31" ht="16" spans="4:14">
       <c r="D31" t="s">
-        <v>93</v>
-      </c>
-      <c r="F31" s="4" t="s">
         <v>94</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="G31" t="s">
         <v>69</v>
       </c>
       <c r="H31" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="I31" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -3308,21 +3235,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="4:14">
+    <row r="32" ht="16" spans="4:14">
       <c r="D32" t="s">
-        <v>95</v>
-      </c>
-      <c r="F32" s="4" t="s">
         <v>96</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="G32" t="s">
         <v>69</v>
       </c>
       <c r="H32" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="I32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -3331,131 +3258,131 @@
         <v>1</v>
       </c>
       <c r="L32">
-        <f t="shared" ref="L32:L50" si="2">L31</f>
+        <f>L31</f>
         <v>0.01</v>
       </c>
       <c r="M32">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="4:13">
+    <row r="33" ht="16" spans="4:13">
       <c r="D33" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G33" t="s">
         <v>69</v>
       </c>
       <c r="H33" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="I33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
       <c r="K33">
-        <f t="shared" ref="K32:K50" si="3">K32</f>
+        <f>K32</f>
         <v>1</v>
       </c>
       <c r="L33">
-        <f t="shared" si="2"/>
+        <f>L32</f>
         <v>0.01</v>
       </c>
       <c r="M33">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="4:13">
+    <row r="34" ht="16" spans="4:13">
       <c r="D34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G34" t="s">
         <v>69</v>
       </c>
       <c r="H34" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="I34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J34">
         <v>1</v>
       </c>
       <c r="K34">
-        <f t="shared" si="3"/>
+        <f>K33</f>
         <v>1</v>
       </c>
       <c r="L34">
-        <f t="shared" si="2"/>
+        <f>L33</f>
         <v>0.01</v>
       </c>
       <c r="M34">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="4:13">
+    <row r="35" ht="16" spans="4:13">
       <c r="D35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G35" t="s">
         <v>69</v>
       </c>
       <c r="H35" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="I35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J35">
         <v>1</v>
       </c>
       <c r="K35">
-        <f t="shared" si="3"/>
+        <f>K34</f>
         <v>1</v>
       </c>
       <c r="L35">
-        <f t="shared" si="2"/>
+        <f>L34</f>
         <v>0.01</v>
       </c>
       <c r="M35">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="4:13">
+    <row r="36" ht="16" spans="4:13">
       <c r="D36" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G36" t="s">
         <v>69</v>
       </c>
       <c r="H36" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="I36" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J36">
         <v>1</v>
       </c>
       <c r="K36">
-        <f t="shared" si="3"/>
+        <f>K35</f>
         <v>1</v>
       </c>
       <c r="L36">
-        <f t="shared" si="2"/>
+        <f>L35</f>
         <v>0.01</v>
       </c>
       <c r="M36">
@@ -3463,471 +3390,52 @@
       </c>
     </row>
     <row r="37" spans="4:13">
-      <c r="D37" t="s">
-        <v>105</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G37" t="s">
-        <v>69</v>
-      </c>
-      <c r="H37" t="s">
-        <v>70</v>
-      </c>
-      <c r="I37" t="s">
-        <v>92</v>
-      </c>
-      <c r="J37">
-        <v>1</v>
-      </c>
-      <c r="K37">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L37">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-      <c r="M37">
-        <v>1</v>
-      </c>
+      <c r="F37" s="6"/>
     </row>
     <row r="38" spans="4:13">
-      <c r="D38" t="s">
-        <v>107</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="G38" t="s">
-        <v>69</v>
-      </c>
-      <c r="H38" t="s">
-        <v>70</v>
-      </c>
-      <c r="I38" t="s">
-        <v>92</v>
-      </c>
-      <c r="J38">
-        <v>1</v>
-      </c>
-      <c r="K38">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L38">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-      <c r="M38">
-        <v>1</v>
-      </c>
+      <c r="F38" s="6"/>
     </row>
     <row r="39" spans="4:13">
-      <c r="D39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G39" t="s">
-        <v>69</v>
-      </c>
-      <c r="H39" t="s">
-        <v>70</v>
-      </c>
-      <c r="I39" t="s">
-        <v>92</v>
-      </c>
-      <c r="J39">
-        <v>1</v>
-      </c>
-      <c r="K39">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L39">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-      <c r="M39">
-        <v>1</v>
-      </c>
+      <c r="F39" s="6"/>
     </row>
     <row r="40" spans="4:13">
-      <c r="D40" t="s">
-        <v>111</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="G40" t="s">
-        <v>69</v>
-      </c>
-      <c r="H40" t="str">
-        <f t="shared" ref="H40:M40" si="4">H39</f>
-        <v>2025, 2150</v>
-      </c>
-      <c r="I40" t="s">
-        <v>92</v>
-      </c>
-      <c r="J40">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="K40">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L40">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-      <c r="M40">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
+      <c r="F40" s="6"/>
     </row>
     <row r="41" spans="4:13">
-      <c r="D41" t="s">
-        <v>113</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G41" t="s">
-        <v>69</v>
-      </c>
-      <c r="H41" t="str">
-        <f t="shared" ref="H41:M41" si="5">H40</f>
-        <v>2025, 2150</v>
-      </c>
-      <c r="I41" t="s">
-        <v>92</v>
-      </c>
-      <c r="J41">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="K41">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L41">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-      <c r="M41">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
+      <c r="F41" s="6"/>
     </row>
     <row r="42" spans="4:13">
-      <c r="D42" t="s">
-        <v>115</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G42" t="s">
-        <v>69</v>
-      </c>
-      <c r="H42" t="str">
-        <f t="shared" ref="H42:M42" si="6">H41</f>
-        <v>2025, 2150</v>
-      </c>
-      <c r="I42" t="s">
-        <v>92</v>
-      </c>
-      <c r="J42">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="K42">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L42">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-      <c r="M42">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
+      <c r="F42" s="6"/>
     </row>
     <row r="43" spans="4:13">
-      <c r="D43" t="s">
-        <v>117</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="G43" t="s">
-        <v>69</v>
-      </c>
-      <c r="H43" t="str">
-        <f t="shared" ref="H43:M43" si="7">H42</f>
-        <v>2025, 2150</v>
-      </c>
-      <c r="I43" t="s">
-        <v>92</v>
-      </c>
-      <c r="J43">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="K43">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L43">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-      <c r="M43">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
+      <c r="F43" s="6"/>
     </row>
     <row r="44" spans="4:13">
-      <c r="D44" t="s">
-        <v>119</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G44" t="s">
-        <v>69</v>
-      </c>
-      <c r="H44" t="str">
-        <f t="shared" ref="H44:M44" si="8">H43</f>
-        <v>2025, 2150</v>
-      </c>
-      <c r="I44" t="s">
-        <v>92</v>
-      </c>
-      <c r="J44">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="K44">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L44">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-      <c r="M44">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
+      <c r="F44" s="6"/>
     </row>
     <row r="45" spans="4:13">
-      <c r="D45" t="s">
-        <v>121</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="G45" t="s">
-        <v>69</v>
-      </c>
-      <c r="H45" t="str">
-        <f t="shared" ref="H45:M45" si="9">H44</f>
-        <v>2025, 2150</v>
-      </c>
-      <c r="I45" t="s">
-        <v>92</v>
-      </c>
-      <c r="J45">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="K45">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L45">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-      <c r="M45">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
+      <c r="F45" s="6"/>
     </row>
     <row r="46" spans="4:13">
-      <c r="D46" t="s">
-        <v>123</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G46" t="s">
-        <v>69</v>
-      </c>
-      <c r="H46" t="str">
-        <f t="shared" ref="H46:M46" si="10">H45</f>
-        <v>2025, 2150</v>
-      </c>
-      <c r="I46" t="s">
-        <v>92</v>
-      </c>
-      <c r="J46">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="K46">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L46">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-      <c r="M46">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
+      <c r="F46" s="6"/>
     </row>
     <row r="47" spans="4:13">
-      <c r="D47" t="s">
-        <v>125</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="G47" t="s">
-        <v>69</v>
-      </c>
-      <c r="H47" t="str">
-        <f t="shared" ref="H47:M47" si="11">H46</f>
-        <v>2025, 2150</v>
-      </c>
-      <c r="I47" t="s">
-        <v>92</v>
-      </c>
-      <c r="J47">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="K47">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L47">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-      <c r="M47">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
+      <c r="F47" s="6"/>
     </row>
     <row r="48" spans="4:13">
-      <c r="D48" t="s">
-        <v>127</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G48" t="s">
-        <v>69</v>
-      </c>
-      <c r="H48" t="str">
-        <f t="shared" ref="H48:M48" si="12">H47</f>
-        <v>2025, 2150</v>
-      </c>
-      <c r="I48" t="s">
-        <v>92</v>
-      </c>
-      <c r="J48">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="K48">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L48">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-      <c r="M48">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="4:13">
-      <c r="D49" t="s">
-        <v>129</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="G49" t="s">
-        <v>69</v>
-      </c>
-      <c r="H49" t="str">
-        <f t="shared" ref="H49:M49" si="13">H48</f>
-        <v>2025, 2150</v>
-      </c>
-      <c r="I49" t="s">
-        <v>92</v>
-      </c>
-      <c r="J49">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="K49">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L49">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-      <c r="M49">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="4:13">
-      <c r="D50" t="s">
-        <v>131</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="G50" t="s">
-        <v>69</v>
-      </c>
-      <c r="H50" t="str">
-        <f t="shared" ref="H50:M50" si="14">H49</f>
-        <v>2025, 2150</v>
-      </c>
-      <c r="I50" t="s">
-        <v>92</v>
-      </c>
-      <c r="J50">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="K50">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L50">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-      <c r="M50">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
+      <c r="F48" s="6"/>
+    </row>
+    <row r="49" spans="6:6">
+      <c r="F49" s="6"/>
+    </row>
+    <row r="50" spans="6:6">
+      <c r="F50" s="7"/>
+    </row>
+    <row r="51" spans="6:6">
+      <c r="F51" s="8"/>
+    </row>
+    <row r="52" spans="6:6">
+      <c r="F52" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8710" activeTab="5"/>
+    <workbookView windowWidth="18350" windowHeight="8710" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
@@ -243,7 +243,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="107">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -381,6 +381,9 @@
   </si>
   <si>
     <t>ACT_UPS</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt*, Tra_BEV_Batt_VtoG</t>
   </si>
   <si>
     <t>~TFM_AVA</t>
@@ -775,17 +778,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -1310,7 +1313,7 @@
     <xf numFmtId="0" fontId="27" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1318,7 +1321,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1339,7 +1341,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -1876,7 +1877,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="21">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -1990,10 +1991,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="22"/>
+      <c r="K10" s="20"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="22"/>
+      <c r="K11" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2008,18 +2009,18 @@
   <dimension ref="B5:N85"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="24.1818181818182" customWidth="1"/>
+    <col min="3" max="3" width="35.6363636363636" customWidth="1"/>
     <col min="4" max="4" width="14.0909090909091" customWidth="1"/>
     <col min="5" max="5" width="10.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="5" spans="2:14">
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="11"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="10"/>
     </row>
     <row r="6" spans="2:14">
       <c r="B6" t="s">
@@ -2034,7 +2035,7 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="11" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2042,13 +2043,13 @@
       <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="12">
         <v>10</v>
       </c>
     </row>
@@ -2056,17 +2057,17 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <v>7</v>
       </c>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
     </row>
     <row r="9" ht="16" spans="2:14">
       <c r="B9" t="s">
@@ -2075,10 +2076,10 @@
       <c r="C9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <v>10</v>
       </c>
       <c r="J9" t="s">
@@ -2101,19 +2102,19 @@
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="12">
         <v>8</v>
       </c>
-      <c r="K10" s="14" t="s">
+      <c r="K10" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="L10" s="15" t="s">
+      <c r="L10" s="14" t="s">
         <v>40</v>
       </c>
       <c r="M10">
@@ -2130,10 +2131,10 @@
       <c r="C11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="9">
         <v>1.5</v>
       </c>
     </row>
@@ -2144,10 +2145,10 @@
       <c r="C12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="9">
         <v>1.5</v>
       </c>
     </row>
@@ -2155,13 +2156,13 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="10">
         <v>2</v>
       </c>
     </row>
@@ -2169,13 +2170,13 @@
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2183,13 +2184,13 @@
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2197,13 +2198,13 @@
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="16">
         <v>12</v>
       </c>
     </row>
@@ -2211,31 +2212,31 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="18">
         <v>0.2</v>
       </c>
-      <c r="F17" s="11"/>
+      <c r="F17" s="10"/>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="18">
         <v>0.2</v>
       </c>
-      <c r="F18" s="11"/>
+      <c r="F18" s="10"/>
     </row>
     <row r="19" ht="16" spans="2:6">
       <c r="B19" t="s">
@@ -2244,28 +2245,28 @@
       <c r="C19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="18">
         <v>0.2</v>
       </c>
-      <c r="F19" s="11"/>
+      <c r="F19" s="10"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="18">
         <v>0.5</v>
       </c>
-      <c r="F20" s="11"/>
+      <c r="F20" s="10"/>
     </row>
     <row r="21" ht="16" spans="2:6">
       <c r="B21" t="s">
@@ -2274,13 +2275,13 @@
       <c r="C21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="18">
         <v>0.8</v>
       </c>
-      <c r="F21" s="11"/>
+      <c r="F21" s="10"/>
     </row>
     <row r="22" ht="16" spans="2:6">
       <c r="B22" t="s">
@@ -2289,468 +2290,468 @@
       <c r="C22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="10"/>
-      <c r="F22" s="11"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="10"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="11">
-        <v>1</v>
-      </c>
-      <c r="F23" s="11"/>
+      <c r="E23" s="10">
+        <v>1</v>
+      </c>
+      <c r="F23" s="10"/>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="18" t="s">
+      <c r="C24" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E24" s="11">
-        <v>1</v>
-      </c>
-      <c r="F24" s="11"/>
+      <c r="E24" s="10">
+        <v>1</v>
+      </c>
+      <c r="F24" s="10"/>
     </row>
     <row r="25" ht="16" spans="2:6">
       <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E25" s="11">
-        <v>1</v>
-      </c>
-      <c r="F25" s="11"/>
+      <c r="E25" s="10">
+        <v>1</v>
+      </c>
+      <c r="F25" s="10"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="9">
         <v>0.05</v>
       </c>
-      <c r="F26" s="11"/>
+      <c r="F26" s="10"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="11"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="10"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
     </row>
     <row r="38" spans="3:5">
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="21" t="s">
-        <v>46</v>
+      <c r="C54" s="19" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="21"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="21"/>
-      <c r="G56" s="21"/>
-      <c r="H56" s="21"/>
-      <c r="I56" s="21"/>
-      <c r="J56" s="21"/>
-      <c r="K56" s="21"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="19"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="19"/>
+      <c r="H56" s="19"/>
+      <c r="I56" s="19"/>
+      <c r="J56" s="19"/>
+      <c r="K56" s="19"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="D57" s="21" t="s">
+      <c r="C57" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D57" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="F57" s="21" t="s">
+      <c r="E57" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="G57" s="21" t="s">
+      <c r="F57" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="H57" s="21" t="s">
+      <c r="G57" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="I57" s="21" t="s">
+      <c r="H57" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="J57" s="21" t="s">
+      <c r="I57" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="K57" s="21" t="s">
+      <c r="J57" s="19" t="s">
         <v>54</v>
       </c>
+      <c r="K57" s="19" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="21"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21"/>
-      <c r="H58" s="21"/>
-      <c r="I58" s="21"/>
-      <c r="J58" s="21"/>
-      <c r="K58" s="21"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="19"/>
+      <c r="G58" s="19"/>
+      <c r="H58" s="19"/>
+      <c r="I58" s="19"/>
+      <c r="J58" s="19"/>
+      <c r="K58" s="19"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="21"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="21"/>
-      <c r="G59" s="21"/>
-      <c r="H59" s="21"/>
-      <c r="I59" s="21"/>
-      <c r="J59" s="21"/>
-      <c r="K59" s="21"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="19"/>
+      <c r="H59" s="19"/>
+      <c r="I59" s="19"/>
+      <c r="J59" s="19"/>
+      <c r="K59" s="19"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="21"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21"/>
-      <c r="G60" s="21"/>
-      <c r="H60" s="21"/>
-      <c r="I60" s="21"/>
-      <c r="J60" s="21"/>
-      <c r="K60" s="21"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="19"/>
+      <c r="F60" s="19"/>
+      <c r="G60" s="19"/>
+      <c r="H60" s="19"/>
+      <c r="I60" s="19"/>
+      <c r="J60" s="19"/>
+      <c r="K60" s="19"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="21"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="21"/>
-      <c r="G61" s="21"/>
-      <c r="H61" s="21"/>
-      <c r="I61" s="21"/>
-      <c r="J61" s="21"/>
-      <c r="K61" s="21"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="19"/>
+      <c r="K61" s="19"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="21"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="21"/>
-      <c r="G62" s="21"/>
-      <c r="H62" s="21"/>
-      <c r="I62" s="21"/>
-      <c r="J62" s="21"/>
-      <c r="K62" s="21"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="19"/>
+      <c r="F62" s="19"/>
+      <c r="G62" s="19"/>
+      <c r="H62" s="19"/>
+      <c r="I62" s="19"/>
+      <c r="J62" s="19"/>
+      <c r="K62" s="19"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="21"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21"/>
-      <c r="H63" s="21"/>
-      <c r="I63" s="21"/>
-      <c r="J63" s="21"/>
-      <c r="K63" s="21"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="19"/>
+      <c r="E63" s="19"/>
+      <c r="F63" s="19"/>
+      <c r="G63" s="19"/>
+      <c r="H63" s="19"/>
+      <c r="I63" s="19"/>
+      <c r="J63" s="19"/>
+      <c r="K63" s="19"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="21"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="21"/>
-      <c r="G64" s="21"/>
-      <c r="H64" s="21"/>
-      <c r="I64" s="21"/>
-      <c r="J64" s="21"/>
-      <c r="K64" s="21"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="19"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
+      <c r="K64" s="19"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="21"/>
-      <c r="H65" s="21"/>
-      <c r="I65" s="21"/>
-      <c r="J65" s="21"/>
-      <c r="K65" s="21"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="19"/>
+      <c r="K65" s="19"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21"/>
-      <c r="G66" s="21"/>
-      <c r="H66" s="21"/>
-      <c r="I66" s="21"/>
-      <c r="J66" s="21"/>
-      <c r="K66" s="21"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="19"/>
+      <c r="E66" s="19"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="19"/>
+      <c r="I66" s="19"/>
+      <c r="J66" s="19"/>
+      <c r="K66" s="19"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="21"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="21"/>
-      <c r="G67" s="21"/>
-      <c r="H67" s="21"/>
-      <c r="I67" s="21"/>
-      <c r="J67" s="21"/>
-      <c r="K67" s="21"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="19"/>
+      <c r="E67" s="19"/>
+      <c r="F67" s="19"/>
+      <c r="G67" s="19"/>
+      <c r="H67" s="19"/>
+      <c r="I67" s="19"/>
+      <c r="J67" s="19"/>
+      <c r="K67" s="19"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="21"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="21"/>
-      <c r="I68" s="21"/>
-      <c r="J68" s="21"/>
-      <c r="K68" s="21"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="19"/>
+      <c r="F68" s="19"/>
+      <c r="G68" s="19"/>
+      <c r="H68" s="19"/>
+      <c r="I68" s="19"/>
+      <c r="J68" s="19"/>
+      <c r="K68" s="19"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="21"/>
-      <c r="H69" s="21"/>
-      <c r="I69" s="21"/>
-      <c r="J69" s="21"/>
-      <c r="K69" s="21"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="19"/>
+      <c r="K69" s="19"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="21"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
-      <c r="H70" s="21"/>
-      <c r="I70" s="21"/>
-      <c r="J70" s="21"/>
-      <c r="K70" s="21"/>
+      <c r="C70" s="19"/>
+      <c r="D70" s="19"/>
+      <c r="E70" s="19"/>
+      <c r="F70" s="19"/>
+      <c r="G70" s="19"/>
+      <c r="H70" s="19"/>
+      <c r="I70" s="19"/>
+      <c r="J70" s="19"/>
+      <c r="K70" s="19"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-      <c r="I71" s="21"/>
-      <c r="J71" s="21"/>
-      <c r="K71" s="21"/>
+      <c r="C71" s="19"/>
+      <c r="D71" s="19"/>
+      <c r="E71" s="19"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="19"/>
+      <c r="H71" s="19"/>
+      <c r="I71" s="19"/>
+      <c r="J71" s="19"/>
+      <c r="K71" s="19"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="21"/>
-      <c r="I72" s="21"/>
-      <c r="J72" s="21"/>
-      <c r="K72" s="21"/>
+      <c r="C72" s="19"/>
+      <c r="D72" s="19"/>
+      <c r="E72" s="19"/>
+      <c r="F72" s="19"/>
+      <c r="G72" s="19"/>
+      <c r="H72" s="19"/>
+      <c r="I72" s="19"/>
+      <c r="J72" s="19"/>
+      <c r="K72" s="19"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
-      <c r="I73" s="21"/>
-      <c r="J73" s="21"/>
-      <c r="K73" s="21"/>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="19"/>
+      <c r="K73" s="19"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="21"/>
-      <c r="I74" s="21"/>
-      <c r="J74" s="21"/>
-      <c r="K74" s="21"/>
+      <c r="C74" s="19"/>
+      <c r="D74" s="19"/>
+      <c r="E74" s="19"/>
+      <c r="F74" s="19"/>
+      <c r="G74" s="19"/>
+      <c r="H74" s="19"/>
+      <c r="I74" s="19"/>
+      <c r="J74" s="19"/>
+      <c r="K74" s="19"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="21"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="21"/>
-      <c r="H75" s="21"/>
-      <c r="I75" s="21"/>
-      <c r="J75" s="21"/>
-      <c r="K75" s="21"/>
+      <c r="C75" s="19"/>
+      <c r="D75" s="19"/>
+      <c r="E75" s="19"/>
+      <c r="F75" s="19"/>
+      <c r="G75" s="19"/>
+      <c r="H75" s="19"/>
+      <c r="I75" s="19"/>
+      <c r="J75" s="19"/>
+      <c r="K75" s="19"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="21"/>
-      <c r="H76" s="21"/>
-      <c r="I76" s="21"/>
-      <c r="J76" s="21"/>
-      <c r="K76" s="21"/>
+      <c r="C76" s="19"/>
+      <c r="D76" s="19"/>
+      <c r="E76" s="19"/>
+      <c r="F76" s="19"/>
+      <c r="G76" s="19"/>
+      <c r="H76" s="19"/>
+      <c r="I76" s="19"/>
+      <c r="J76" s="19"/>
+      <c r="K76" s="19"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="21"/>
-      <c r="D77" s="21"/>
-      <c r="E77" s="21"/>
-      <c r="F77" s="21"/>
-      <c r="G77" s="21"/>
-      <c r="H77" s="21"/>
-      <c r="I77" s="21"/>
-      <c r="J77" s="21"/>
-      <c r="K77" s="21"/>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="19"/>
+      <c r="K77" s="19"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="21"/>
-      <c r="D78" s="21"/>
-      <c r="E78" s="21"/>
-      <c r="F78" s="21"/>
-      <c r="G78" s="21"/>
-      <c r="H78" s="21"/>
-      <c r="I78" s="21"/>
-      <c r="J78" s="21"/>
-      <c r="K78" s="21"/>
+      <c r="C78" s="19"/>
+      <c r="D78" s="19"/>
+      <c r="E78" s="19"/>
+      <c r="F78" s="19"/>
+      <c r="G78" s="19"/>
+      <c r="H78" s="19"/>
+      <c r="I78" s="19"/>
+      <c r="J78" s="19"/>
+      <c r="K78" s="19"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="21"/>
-      <c r="D79" s="21"/>
-      <c r="E79" s="21"/>
-      <c r="F79" s="21"/>
-      <c r="G79" s="21"/>
-      <c r="H79" s="21"/>
-      <c r="I79" s="21"/>
-      <c r="J79" s="21"/>
-      <c r="K79" s="21"/>
+      <c r="C79" s="19"/>
+      <c r="D79" s="19"/>
+      <c r="E79" s="19"/>
+      <c r="F79" s="19"/>
+      <c r="G79" s="19"/>
+      <c r="H79" s="19"/>
+      <c r="I79" s="19"/>
+      <c r="J79" s="19"/>
+      <c r="K79" s="19"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="21"/>
-      <c r="D80" s="21"/>
-      <c r="E80" s="21"/>
-      <c r="F80" s="21"/>
-      <c r="G80" s="21"/>
-      <c r="H80" s="21"/>
-      <c r="I80" s="21"/>
-      <c r="J80" s="21"/>
-      <c r="K80" s="21"/>
+      <c r="C80" s="19"/>
+      <c r="D80" s="19"/>
+      <c r="E80" s="19"/>
+      <c r="F80" s="19"/>
+      <c r="G80" s="19"/>
+      <c r="H80" s="19"/>
+      <c r="I80" s="19"/>
+      <c r="J80" s="19"/>
+      <c r="K80" s="19"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="21"/>
-      <c r="D81" s="21"/>
-      <c r="E81" s="21"/>
-      <c r="F81" s="21"/>
-      <c r="G81" s="21"/>
-      <c r="H81" s="21"/>
-      <c r="I81" s="21"/>
-      <c r="J81" s="21"/>
-      <c r="K81" s="21"/>
+      <c r="C81" s="19"/>
+      <c r="D81" s="19"/>
+      <c r="E81" s="19"/>
+      <c r="F81" s="19"/>
+      <c r="G81" s="19"/>
+      <c r="H81" s="19"/>
+      <c r="I81" s="19"/>
+      <c r="J81" s="19"/>
+      <c r="K81" s="19"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="21"/>
-      <c r="D82" s="21"/>
-      <c r="E82" s="21"/>
-      <c r="F82" s="21"/>
-      <c r="G82" s="21"/>
-      <c r="H82" s="21"/>
-      <c r="I82" s="21"/>
-      <c r="J82" s="21"/>
-      <c r="K82" s="21"/>
+      <c r="C82" s="19"/>
+      <c r="D82" s="19"/>
+      <c r="E82" s="19"/>
+      <c r="F82" s="19"/>
+      <c r="G82" s="19"/>
+      <c r="H82" s="19"/>
+      <c r="I82" s="19"/>
+      <c r="J82" s="19"/>
+      <c r="K82" s="19"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="21"/>
-      <c r="D83" s="21"/>
-      <c r="E83" s="21"/>
-      <c r="F83" s="21"/>
-      <c r="G83" s="21"/>
-      <c r="H83" s="21"/>
-      <c r="I83" s="21"/>
-      <c r="J83" s="21"/>
-      <c r="K83" s="21"/>
+      <c r="C83" s="19"/>
+      <c r="D83" s="19"/>
+      <c r="E83" s="19"/>
+      <c r="F83" s="19"/>
+      <c r="G83" s="19"/>
+      <c r="H83" s="19"/>
+      <c r="I83" s="19"/>
+      <c r="J83" s="19"/>
+      <c r="K83" s="19"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="D84" s="21">
-        <v>1</v>
-      </c>
-      <c r="E84" s="21"/>
-      <c r="F84" s="21"/>
-      <c r="G84" s="21"/>
-      <c r="H84" s="21"/>
-      <c r="I84" s="21"/>
-      <c r="J84" s="21"/>
-      <c r="K84" s="21"/>
+      <c r="C84" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D84" s="19">
+        <v>1</v>
+      </c>
+      <c r="E84" s="19"/>
+      <c r="F84" s="19"/>
+      <c r="G84" s="19"/>
+      <c r="H84" s="19"/>
+      <c r="I84" s="19"/>
+      <c r="J84" s="19"/>
+      <c r="K84" s="19"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="21"/>
-      <c r="D85" s="21"/>
-      <c r="E85" s="21"/>
-      <c r="F85" s="21"/>
-      <c r="G85" s="21"/>
-      <c r="H85" s="21"/>
-      <c r="I85" s="21"/>
-      <c r="J85" s="21"/>
-      <c r="K85" s="21"/>
+      <c r="C85" s="19"/>
+      <c r="D85" s="19"/>
+      <c r="E85" s="19"/>
+      <c r="F85" s="19"/>
+      <c r="G85" s="19"/>
+      <c r="H85" s="19"/>
+      <c r="I85" s="19"/>
+      <c r="J85" s="19"/>
+      <c r="K85" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2777,31 +2778,31 @@
   <sheetData>
     <row r="2" spans="2:14">
       <c r="B2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:14">
       <c r="B3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="2:14">
       <c r="H4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="2:14">
       <c r="D8" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>4</v>
@@ -2810,36 +2811,36 @@
         <v>2</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="2:14">
       <c r="D9" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -2857,19 +2858,19 @@
     </row>
     <row r="10" spans="2:14">
       <c r="D10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -2887,19 +2888,19 @@
     </row>
     <row r="11" spans="2:14">
       <c r="D11" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -2917,19 +2918,19 @@
     </row>
     <row r="12" ht="16" spans="2:14">
       <c r="D12" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -2947,19 +2948,19 @@
     </row>
     <row r="13" spans="2:14">
       <c r="D13" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -2977,19 +2978,19 @@
     </row>
     <row r="14" spans="2:14">
       <c r="D14" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -3007,19 +3008,19 @@
     </row>
     <row r="15" spans="2:14">
       <c r="D15" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -3037,10 +3038,10 @@
     </row>
     <row r="16" ht="16" spans="2:14">
       <c r="D16" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G16" t="str">
         <f>G15</f>
@@ -3051,7 +3052,7 @@
         <v>2025, 2150</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J16">
         <f t="shared" ref="J16:L16" si="0">J12</f>
@@ -3072,10 +3073,10 @@
     </row>
     <row r="17" ht="16" spans="4:14">
       <c r="D17" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" ref="G17:M17" si="1">G16</f>
@@ -3086,7 +3087,7 @@
         <v>2025, 2150</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J17">
         <f t="shared" si="1"/>
@@ -3107,10 +3108,10 @@
     </row>
     <row r="18" ht="16" spans="4:14">
       <c r="D18" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G18" t="str">
         <f>G17</f>
@@ -3121,7 +3122,7 @@
         <v>2025, 2150</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -3138,21 +3139,21 @@
     </row>
     <row r="28" spans="4:14">
       <c r="H28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="4:14">
       <c r="D29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F29" t="s">
         <v>6</v>
       </c>
       <c r="G29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H29" t="s">
         <v>4</v>
@@ -3161,36 +3162,36 @@
         <v>2</v>
       </c>
       <c r="J29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" ht="16" spans="4:14">
       <c r="D30" t="s">
-        <v>90</v>
-      </c>
-      <c r="F30" s="4" t="s">
         <v>91</v>
       </c>
+      <c r="F30" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="G30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -3207,20 +3208,20 @@
     </row>
     <row r="31" ht="16" spans="4:14">
       <c r="D31" t="s">
+        <v>95</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G31" t="s">
+        <v>70</v>
+      </c>
+      <c r="H31" t="s">
+        <v>93</v>
+      </c>
+      <c r="I31" t="s">
         <v>94</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="G31" t="s">
-        <v>69</v>
-      </c>
-      <c r="H31" t="s">
-        <v>92</v>
-      </c>
-      <c r="I31" t="s">
-        <v>93</v>
-      </c>
       <c r="J31">
         <v>1</v>
       </c>
@@ -3228,7 +3229,7 @@
         <v>1</v>
       </c>
       <c r="L31">
-        <f>L30</f>
+        <f t="shared" ref="L31:L36" si="2">L30</f>
         <v>0.01</v>
       </c>
       <c r="M31">
@@ -3237,19 +3238,19 @@
     </row>
     <row r="32" ht="16" spans="4:14">
       <c r="D32" t="s">
-        <v>96</v>
-      </c>
-      <c r="F32" s="5" t="s">
         <v>97</v>
       </c>
+      <c r="F32" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="G32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -3258,7 +3259,7 @@
         <v>1</v>
       </c>
       <c r="L32">
-        <f>L31</f>
+        <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
       <c r="M32">
@@ -3267,19 +3268,19 @@
     </row>
     <row r="33" ht="16" spans="4:13">
       <c r="D33" t="s">
-        <v>98</v>
-      </c>
-      <c r="F33" s="4" t="s">
         <v>99</v>
       </c>
+      <c r="F33" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="G33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -3289,7 +3290,7 @@
         <v>1</v>
       </c>
       <c r="L33">
-        <f>L32</f>
+        <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
       <c r="M33">
@@ -3298,19 +3299,19 @@
     </row>
     <row r="34" ht="16" spans="4:13">
       <c r="D34" t="s">
-        <v>100</v>
-      </c>
-      <c r="F34" s="4" t="s">
         <v>101</v>
       </c>
+      <c r="F34" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="G34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -3320,7 +3321,7 @@
         <v>1</v>
       </c>
       <c r="L34">
-        <f>L33</f>
+        <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
       <c r="M34">
@@ -3329,19 +3330,19 @@
     </row>
     <row r="35" ht="16" spans="4:13">
       <c r="D35" t="s">
-        <v>102</v>
-      </c>
-      <c r="F35" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="F35" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="G35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -3351,7 +3352,7 @@
         <v>1</v>
       </c>
       <c r="L35">
-        <f>L34</f>
+        <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
       <c r="M35">
@@ -3360,19 +3361,19 @@
     </row>
     <row r="36" ht="16" spans="4:13">
       <c r="D36" t="s">
-        <v>104</v>
-      </c>
-      <c r="F36" s="4" t="s">
         <v>105</v>
       </c>
+      <c r="F36" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="G36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H36" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I36" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -3382,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="L36">
-        <f>L35</f>
+        <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
       <c r="M36">
@@ -3390,52 +3391,52 @@
       </c>
     </row>
     <row r="37" spans="4:13">
-      <c r="F37" s="6"/>
+      <c r="F37" s="5"/>
     </row>
     <row r="38" spans="4:13">
-      <c r="F38" s="6"/>
+      <c r="F38" s="5"/>
     </row>
     <row r="39" spans="4:13">
-      <c r="F39" s="6"/>
+      <c r="F39" s="5"/>
     </row>
     <row r="40" spans="4:13">
-      <c r="F40" s="6"/>
+      <c r="F40" s="5"/>
     </row>
     <row r="41" spans="4:13">
-      <c r="F41" s="6"/>
+      <c r="F41" s="5"/>
     </row>
     <row r="42" spans="4:13">
-      <c r="F42" s="6"/>
+      <c r="F42" s="5"/>
     </row>
     <row r="43" spans="4:13">
-      <c r="F43" s="6"/>
+      <c r="F43" s="5"/>
     </row>
     <row r="44" spans="4:13">
-      <c r="F44" s="6"/>
+      <c r="F44" s="5"/>
     </row>
     <row r="45" spans="4:13">
-      <c r="F45" s="6"/>
+      <c r="F45" s="5"/>
     </row>
     <row r="46" spans="4:13">
-      <c r="F46" s="6"/>
+      <c r="F46" s="5"/>
     </row>
     <row r="47" spans="4:13">
-      <c r="F47" s="6"/>
+      <c r="F47" s="5"/>
     </row>
     <row r="48" spans="4:13">
-      <c r="F48" s="6"/>
+      <c r="F48" s="5"/>
     </row>
     <row r="49" spans="6:6">
-      <c r="F49" s="6"/>
+      <c r="F49" s="5"/>
     </row>
     <row r="50" spans="6:6">
-      <c r="F50" s="7"/>
+      <c r="F50" s="6"/>
     </row>
     <row r="51" spans="6:6">
-      <c r="F51" s="8"/>
+      <c r="F51" s="7"/>
     </row>
     <row r="52" spans="6:6">
-      <c r="F52" s="8"/>
+      <c r="F52" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -780,11 +780,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
     </font>
@@ -795,6 +790,11 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -2006,7 +2006,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B5:N85"/>
+  <dimension ref="B3:N85"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="35.6363636363636" customWidth="1"/>
@@ -2014,10 +2014,12 @@
     <col min="5" max="5" width="10.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="3" spans="2:14">
+      <c r="C3" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
     <row r="5" spans="2:14">
-      <c r="C5" s="8" t="s">
-        <v>23</v>
-      </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="10"/>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8710" activeTab="4"/>
+    <workbookView windowWidth="18350" windowHeight="8710" firstSheet="1" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
@@ -778,12 +778,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="0"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -795,6 +789,12 @@
       <charset val="0"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -2006,7 +2006,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:N85"/>
+  <dimension ref="B5:N85"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="35.6363636363636" customWidth="1"/>
@@ -2014,12 +2014,10 @@
     <col min="5" max="5" width="10.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:14">
-      <c r="C3" s="8" t="s">
+    <row r="5" spans="2:14">
+      <c r="C5" s="8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="2:14">
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="10"/>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -2006,7 +2006,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B5:N85"/>
+  <dimension ref="B3:N85"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="35.6363636363636" customWidth="1"/>
@@ -2014,10 +2014,12 @@
     <col min="5" max="5" width="10.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="3" spans="2:14">
+      <c r="C3" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
     <row r="5" spans="2:14">
-      <c r="C5" s="8" t="s">
-        <v>23</v>
-      </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="10"/>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -243,7 +243,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="105">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -359,13 +359,7 @@
     <t>EA_OIL*, EP_OIL*</t>
   </si>
   <si>
-    <t>China</t>
-  </si>
-  <si>
     <t>en_gas*, ea_gas*, ep_gas*</t>
-  </si>
-  <si>
-    <t>CAP_BND</t>
   </si>
   <si>
     <t>*HPS*</t>
@@ -778,6 +772,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -785,16 +780,15 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -2006,7 +2000,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:N85"/>
+  <dimension ref="B5:M85"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="35.6363636363636" customWidth="1"/>
@@ -2014,17 +2008,15 @@
     <col min="5" max="5" width="10.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:14">
-      <c r="C3" s="8" t="s">
+    <row r="5" spans="2:13">
+      <c r="C5" s="8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="2:14">
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="10"/>
     </row>
-    <row r="6" spans="2:14">
+    <row r="6" spans="2:13">
       <c r="B6" t="s">
         <v>33</v>
       </c>
@@ -2037,11 +2029,9 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="11" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14">
+      <c r="K6" s="11"/>
+    </row>
+    <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>17</v>
       </c>
@@ -2055,7 +2045,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:14">
+    <row r="8" spans="2:13">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -2071,7 +2061,7 @@
       <c r="L8" s="9"/>
       <c r="M8" s="9"/>
     </row>
-    <row r="9" ht="16" spans="2:14">
+    <row r="9" ht="16" spans="2:13">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -2084,28 +2074,13 @@
       <c r="E9" s="12">
         <v>10</v>
       </c>
-      <c r="J9" t="s">
-        <v>33</v>
-      </c>
-      <c r="K9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9" t="s">
-        <v>5</v>
-      </c>
-      <c r="N9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" ht="32" spans="2:14">
+    </row>
+    <row r="10" ht="16" spans="2:13">
       <c r="B10" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>35</v>
@@ -2113,20 +2088,10 @@
       <c r="E10" s="12">
         <v>8</v>
       </c>
-      <c r="K10" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="M10">
-        <v>50</v>
-      </c>
-      <c r="N10">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="11" ht="16" spans="2:14">
+      <c r="K10" s="13"/>
+      <c r="L10" s="14"/>
+    </row>
+    <row r="11" ht="16" spans="2:13">
       <c r="B11" t="s">
         <v>17</v>
       </c>
@@ -2140,7 +2105,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="12" ht="16" spans="2:14">
+    <row r="12" ht="16" spans="2:13">
       <c r="B12" t="s">
         <v>17</v>
       </c>
@@ -2154,12 +2119,12 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="13" spans="2:14">
+    <row r="13" spans="2:13">
       <c r="B13" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>35</v>
@@ -2168,12 +2133,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="2:14">
+    <row r="14" spans="2:13">
       <c r="B14" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>35</v>
@@ -2182,12 +2147,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="16" spans="2:14">
+    <row r="15" ht="16" spans="2:13">
       <c r="B15" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>35</v>
@@ -2196,12 +2161,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:14">
+    <row r="16" spans="2:13">
       <c r="B16" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>35</v>
@@ -2218,7 +2183,7 @@
         <v>34</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E17" s="18">
         <v>0.2</v>
@@ -2233,7 +2198,7 @@
         <v>36</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E18" s="18">
         <v>0.2</v>
@@ -2248,7 +2213,7 @@
         <v>37</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E19" s="18">
         <v>0.2</v>
@@ -2260,10 +2225,10 @@
         <v>17</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E20" s="18">
         <v>0.5</v>
@@ -2278,7 +2243,7 @@
         <v>31</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E21" s="18">
         <v>0.8</v>
@@ -2293,7 +2258,7 @@
         <v>32</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E22" s="9"/>
       <c r="F22" s="10"/>
@@ -2303,10 +2268,10 @@
         <v>17</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E23" s="10">
         <v>1</v>
@@ -2318,10 +2283,10 @@
         <v>17</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E24" s="10">
         <v>1</v>
@@ -2333,10 +2298,10 @@
         <v>17</v>
       </c>
       <c r="C25" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="17" t="s">
         <v>43</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>45</v>
       </c>
       <c r="E25" s="10">
         <v>1</v>
@@ -2348,10 +2313,10 @@
         <v>17</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E26" s="9">
         <v>0.05</v>
@@ -2401,7 +2366,7 @@
     </row>
     <row r="54" spans="3:11">
       <c r="C54" s="19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="3:11">
@@ -2416,31 +2381,31 @@
     </row>
     <row r="57" spans="3:11">
       <c r="C57" s="19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D57" s="19" t="s">
         <v>5</v>
       </c>
       <c r="E57" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F57" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="G57" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="F57" s="19" t="s">
+      <c r="H57" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="G57" s="19" t="s">
+      <c r="I57" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="19" t="s">
+      <c r="J57" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="19" t="s">
+      <c r="K57" s="19" t="s">
         <v>53</v>
-      </c>
-      <c r="J57" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="K57" s="19" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="58" spans="3:11">
@@ -2731,7 +2696,7 @@
     </row>
     <row r="84" spans="3:11">
       <c r="C84" s="19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D84" s="19">
         <v>1</v>
@@ -2780,31 +2745,31 @@
   <sheetData>
     <row r="2" spans="2:14">
       <c r="B2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="2:14">
       <c r="B3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="2:14">
       <c r="H4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="2:14">
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>4</v>
@@ -2813,36 +2778,36 @@
         <v>2</v>
       </c>
       <c r="J8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="M8" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="N8" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="9" spans="2:14">
       <c r="D9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -2860,19 +2825,19 @@
     </row>
     <row r="10" spans="2:14">
       <c r="D10" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -2890,19 +2855,19 @@
     </row>
     <row r="11" spans="2:14">
       <c r="D11" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -2920,19 +2885,19 @@
     </row>
     <row r="12" ht="16" spans="2:14">
       <c r="D12" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -2950,19 +2915,19 @@
     </row>
     <row r="13" spans="2:14">
       <c r="D13" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -2980,19 +2945,19 @@
     </row>
     <row r="14" spans="2:14">
       <c r="D14" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -3010,19 +2975,19 @@
     </row>
     <row r="15" spans="2:14">
       <c r="D15" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -3040,10 +3005,10 @@
     </row>
     <row r="16" ht="16" spans="2:14">
       <c r="D16" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G16" t="str">
         <f>G15</f>
@@ -3054,7 +3019,7 @@
         <v>2025, 2150</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J16">
         <f t="shared" ref="J16:L16" si="0">J12</f>
@@ -3075,10 +3040,10 @@
     </row>
     <row r="17" ht="16" spans="4:14">
       <c r="D17" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" ref="G17:M17" si="1">G16</f>
@@ -3089,7 +3054,7 @@
         <v>2025, 2150</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J17">
         <f t="shared" si="1"/>
@@ -3110,10 +3075,10 @@
     </row>
     <row r="18" ht="16" spans="4:14">
       <c r="D18" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G18" t="str">
         <f>G17</f>
@@ -3124,7 +3089,7 @@
         <v>2025, 2150</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -3141,21 +3106,21 @@
     </row>
     <row r="28" spans="4:14">
       <c r="H28" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="4:14">
       <c r="D29" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F29" t="s">
         <v>6</v>
       </c>
       <c r="G29" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H29" t="s">
         <v>4</v>
@@ -3164,36 +3129,36 @@
         <v>2</v>
       </c>
       <c r="J29" t="s">
+        <v>61</v>
+      </c>
+      <c r="K29" t="s">
+        <v>62</v>
+      </c>
+      <c r="L29" t="s">
         <v>63</v>
       </c>
-      <c r="K29" t="s">
+      <c r="M29" t="s">
         <v>64</v>
       </c>
-      <c r="L29" t="s">
+      <c r="N29" t="s">
         <v>65</v>
-      </c>
-      <c r="M29" t="s">
-        <v>66</v>
-      </c>
-      <c r="N29" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="30" ht="16" spans="4:14">
       <c r="D30" t="s">
+        <v>89</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G30" t="s">
+        <v>68</v>
+      </c>
+      <c r="H30" t="s">
         <v>91</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="I30" t="s">
         <v>92</v>
-      </c>
-      <c r="G30" t="s">
-        <v>70</v>
-      </c>
-      <c r="H30" t="s">
-        <v>93</v>
-      </c>
-      <c r="I30" t="s">
-        <v>94</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -3210,19 +3175,19 @@
     </row>
     <row r="31" ht="16" spans="4:14">
       <c r="D31" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G31" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H31" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -3240,19 +3205,19 @@
     </row>
     <row r="32" ht="16" spans="4:14">
       <c r="D32" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G32" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H32" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I32" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -3270,19 +3235,19 @@
     </row>
     <row r="33" ht="16" spans="4:13">
       <c r="D33" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G33" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H33" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I33" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -3301,19 +3266,19 @@
     </row>
     <row r="34" ht="16" spans="4:13">
       <c r="D34" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G34" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H34" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I34" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -3332,19 +3297,19 @@
     </row>
     <row r="35" ht="16" spans="4:13">
       <c r="D35" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G35" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H35" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I35" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -3363,19 +3328,19 @@
     </row>
     <row r="36" ht="16" spans="4:13">
       <c r="D36" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H36" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I36" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J36">
         <v>1</v>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8710" firstSheet="1" activeTab="4"/>
+    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="1" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
@@ -243,7 +243,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="106">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -378,6 +378,9 @@
   </si>
   <si>
     <t>EN_STG_4hBatt*, Tra_BEV_Batt_VtoG</t>
+  </si>
+  <si>
+    <t>START</t>
   </si>
   <si>
     <t>~TFM_AVA</t>
@@ -772,6 +775,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
@@ -786,11 +794,6 @@
     <font>
       <sz val="9"/>
       <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
       <charset val="0"/>
     </font>
   </fonts>
@@ -1307,7 +1310,7 @@
     <xf numFmtId="0" fontId="27" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1335,9 +1338,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="53">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1871,7 +1875,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="19">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -1985,10 +1989,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="20"/>
+      <c r="K10" s="22"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="20"/>
+      <c r="K11" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2324,9 +2328,18 @@
       <c r="F26" s="10"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
+      <c r="B27" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="20">
+        <v>2025</v>
+      </c>
       <c r="F27" s="10"/>
     </row>
     <row r="28" spans="2:6">
@@ -2365,360 +2378,360 @@
       <c r="E38" s="7"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="19" t="s">
-        <v>45</v>
+      <c r="C54" s="21" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="19"/>
-      <c r="E56" s="19"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="19"/>
-      <c r="I56" s="19"/>
-      <c r="J56" s="19"/>
-      <c r="K56" s="19"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="21"/>
+      <c r="G56" s="21"/>
+      <c r="H56" s="21"/>
+      <c r="I56" s="21"/>
+      <c r="J56" s="21"/>
+      <c r="K56" s="21"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D57" s="19" t="s">
+      <c r="C57" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D57" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="F57" s="19" t="s">
+      <c r="E57" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="G57" s="19" t="s">
+      <c r="F57" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="H57" s="19" t="s">
+      <c r="G57" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="I57" s="19" t="s">
+      <c r="H57" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="J57" s="19" t="s">
+      <c r="I57" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="K57" s="19" t="s">
+      <c r="J57" s="21" t="s">
         <v>53</v>
       </c>
+      <c r="K57" s="21" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19"/>
-      <c r="F58" s="19"/>
-      <c r="G58" s="19"/>
-      <c r="H58" s="19"/>
-      <c r="I58" s="19"/>
-      <c r="J58" s="19"/>
-      <c r="K58" s="19"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="21"/>
+      <c r="H58" s="21"/>
+      <c r="I58" s="21"/>
+      <c r="J58" s="21"/>
+      <c r="K58" s="21"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="19"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="19"/>
-      <c r="I59" s="19"/>
-      <c r="J59" s="19"/>
-      <c r="K59" s="19"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="21"/>
+      <c r="G59" s="21"/>
+      <c r="H59" s="21"/>
+      <c r="I59" s="21"/>
+      <c r="J59" s="21"/>
+      <c r="K59" s="21"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19"/>
-      <c r="G60" s="19"/>
-      <c r="H60" s="19"/>
-      <c r="I60" s="19"/>
-      <c r="J60" s="19"/>
-      <c r="K60" s="19"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="21"/>
+      <c r="G60" s="21"/>
+      <c r="H60" s="21"/>
+      <c r="I60" s="21"/>
+      <c r="J60" s="21"/>
+      <c r="K60" s="21"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
-      <c r="F61" s="19"/>
-      <c r="G61" s="19"/>
-      <c r="H61" s="19"/>
-      <c r="I61" s="19"/>
-      <c r="J61" s="19"/>
-      <c r="K61" s="19"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="21"/>
+      <c r="G61" s="21"/>
+      <c r="H61" s="21"/>
+      <c r="I61" s="21"/>
+      <c r="J61" s="21"/>
+      <c r="K61" s="21"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="19"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="19"/>
-      <c r="F62" s="19"/>
-      <c r="G62" s="19"/>
-      <c r="H62" s="19"/>
-      <c r="I62" s="19"/>
-      <c r="J62" s="19"/>
-      <c r="K62" s="19"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="21"/>
+      <c r="G62" s="21"/>
+      <c r="H62" s="21"/>
+      <c r="I62" s="21"/>
+      <c r="J62" s="21"/>
+      <c r="K62" s="21"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="19"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="19"/>
-      <c r="F63" s="19"/>
-      <c r="G63" s="19"/>
-      <c r="H63" s="19"/>
-      <c r="I63" s="19"/>
-      <c r="J63" s="19"/>
-      <c r="K63" s="19"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="21"/>
+      <c r="G63" s="21"/>
+      <c r="H63" s="21"/>
+      <c r="I63" s="21"/>
+      <c r="J63" s="21"/>
+      <c r="K63" s="21"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="19"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
-      <c r="F64" s="19"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="19"/>
-      <c r="J64" s="19"/>
-      <c r="K64" s="19"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="21"/>
+      <c r="G64" s="21"/>
+      <c r="H64" s="21"/>
+      <c r="I64" s="21"/>
+      <c r="J64" s="21"/>
+      <c r="K64" s="21"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="19"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="19"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="19"/>
-      <c r="J65" s="19"/>
-      <c r="K65" s="19"/>
+      <c r="C65" s="21"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="21"/>
+      <c r="G65" s="21"/>
+      <c r="H65" s="21"/>
+      <c r="I65" s="21"/>
+      <c r="J65" s="21"/>
+      <c r="K65" s="21"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="19"/>
-      <c r="D66" s="19"/>
-      <c r="E66" s="19"/>
-      <c r="F66" s="19"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="19"/>
-      <c r="I66" s="19"/>
-      <c r="J66" s="19"/>
-      <c r="K66" s="19"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="21"/>
+      <c r="G66" s="21"/>
+      <c r="H66" s="21"/>
+      <c r="I66" s="21"/>
+      <c r="J66" s="21"/>
+      <c r="K66" s="21"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="19"/>
-      <c r="D67" s="19"/>
-      <c r="E67" s="19"/>
-      <c r="F67" s="19"/>
-      <c r="G67" s="19"/>
-      <c r="H67" s="19"/>
-      <c r="I67" s="19"/>
-      <c r="J67" s="19"/>
-      <c r="K67" s="19"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="21"/>
+      <c r="G67" s="21"/>
+      <c r="H67" s="21"/>
+      <c r="I67" s="21"/>
+      <c r="J67" s="21"/>
+      <c r="K67" s="21"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="19"/>
-      <c r="D68" s="19"/>
-      <c r="E68" s="19"/>
-      <c r="F68" s="19"/>
-      <c r="G68" s="19"/>
-      <c r="H68" s="19"/>
-      <c r="I68" s="19"/>
-      <c r="J68" s="19"/>
-      <c r="K68" s="19"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="21"/>
+      <c r="H68" s="21"/>
+      <c r="I68" s="21"/>
+      <c r="J68" s="21"/>
+      <c r="K68" s="21"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="19"/>
-      <c r="D69" s="19"/>
-      <c r="E69" s="19"/>
-      <c r="F69" s="19"/>
-      <c r="G69" s="19"/>
-      <c r="H69" s="19"/>
-      <c r="I69" s="19"/>
-      <c r="J69" s="19"/>
-      <c r="K69" s="19"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="21"/>
+      <c r="H69" s="21"/>
+      <c r="I69" s="21"/>
+      <c r="J69" s="21"/>
+      <c r="K69" s="21"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="19"/>
-      <c r="D70" s="19"/>
-      <c r="E70" s="19"/>
-      <c r="F70" s="19"/>
-      <c r="G70" s="19"/>
-      <c r="H70" s="19"/>
-      <c r="I70" s="19"/>
-      <c r="J70" s="19"/>
-      <c r="K70" s="19"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="21"/>
+      <c r="H70" s="21"/>
+      <c r="I70" s="21"/>
+      <c r="J70" s="21"/>
+      <c r="K70" s="21"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="19"/>
-      <c r="D71" s="19"/>
-      <c r="E71" s="19"/>
-      <c r="F71" s="19"/>
-      <c r="G71" s="19"/>
-      <c r="H71" s="19"/>
-      <c r="I71" s="19"/>
-      <c r="J71" s="19"/>
-      <c r="K71" s="19"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="21"/>
+      <c r="H71" s="21"/>
+      <c r="I71" s="21"/>
+      <c r="J71" s="21"/>
+      <c r="K71" s="21"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="19"/>
-      <c r="D72" s="19"/>
-      <c r="E72" s="19"/>
-      <c r="F72" s="19"/>
-      <c r="G72" s="19"/>
-      <c r="H72" s="19"/>
-      <c r="I72" s="19"/>
-      <c r="J72" s="19"/>
-      <c r="K72" s="19"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="21"/>
+      <c r="H72" s="21"/>
+      <c r="I72" s="21"/>
+      <c r="J72" s="21"/>
+      <c r="K72" s="21"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="19"/>
-      <c r="D73" s="19"/>
-      <c r="E73" s="19"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="19"/>
-      <c r="H73" s="19"/>
-      <c r="I73" s="19"/>
-      <c r="J73" s="19"/>
-      <c r="K73" s="19"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="21"/>
+      <c r="I73" s="21"/>
+      <c r="J73" s="21"/>
+      <c r="K73" s="21"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="19"/>
-      <c r="D74" s="19"/>
-      <c r="E74" s="19"/>
-      <c r="F74" s="19"/>
-      <c r="G74" s="19"/>
-      <c r="H74" s="19"/>
-      <c r="I74" s="19"/>
-      <c r="J74" s="19"/>
-      <c r="K74" s="19"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="21"/>
+      <c r="G74" s="21"/>
+      <c r="H74" s="21"/>
+      <c r="I74" s="21"/>
+      <c r="J74" s="21"/>
+      <c r="K74" s="21"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="19"/>
-      <c r="D75" s="19"/>
-      <c r="E75" s="19"/>
-      <c r="F75" s="19"/>
-      <c r="G75" s="19"/>
-      <c r="H75" s="19"/>
-      <c r="I75" s="19"/>
-      <c r="J75" s="19"/>
-      <c r="K75" s="19"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="21"/>
+      <c r="G75" s="21"/>
+      <c r="H75" s="21"/>
+      <c r="I75" s="21"/>
+      <c r="J75" s="21"/>
+      <c r="K75" s="21"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="19"/>
-      <c r="D76" s="19"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="19"/>
-      <c r="G76" s="19"/>
-      <c r="H76" s="19"/>
-      <c r="I76" s="19"/>
-      <c r="J76" s="19"/>
-      <c r="K76" s="19"/>
+      <c r="C76" s="21"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="21"/>
+      <c r="F76" s="21"/>
+      <c r="G76" s="21"/>
+      <c r="H76" s="21"/>
+      <c r="I76" s="21"/>
+      <c r="J76" s="21"/>
+      <c r="K76" s="21"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="19"/>
-      <c r="D77" s="19"/>
-      <c r="E77" s="19"/>
-      <c r="F77" s="19"/>
-      <c r="G77" s="19"/>
-      <c r="H77" s="19"/>
-      <c r="I77" s="19"/>
-      <c r="J77" s="19"/>
-      <c r="K77" s="19"/>
+      <c r="C77" s="21"/>
+      <c r="D77" s="21"/>
+      <c r="E77" s="21"/>
+      <c r="F77" s="21"/>
+      <c r="G77" s="21"/>
+      <c r="H77" s="21"/>
+      <c r="I77" s="21"/>
+      <c r="J77" s="21"/>
+      <c r="K77" s="21"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="19"/>
-      <c r="D78" s="19"/>
-      <c r="E78" s="19"/>
-      <c r="F78" s="19"/>
-      <c r="G78" s="19"/>
-      <c r="H78" s="19"/>
-      <c r="I78" s="19"/>
-      <c r="J78" s="19"/>
-      <c r="K78" s="19"/>
+      <c r="C78" s="21"/>
+      <c r="D78" s="21"/>
+      <c r="E78" s="21"/>
+      <c r="F78" s="21"/>
+      <c r="G78" s="21"/>
+      <c r="H78" s="21"/>
+      <c r="I78" s="21"/>
+      <c r="J78" s="21"/>
+      <c r="K78" s="21"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="19"/>
-      <c r="D79" s="19"/>
-      <c r="E79" s="19"/>
-      <c r="F79" s="19"/>
-      <c r="G79" s="19"/>
-      <c r="H79" s="19"/>
-      <c r="I79" s="19"/>
-      <c r="J79" s="19"/>
-      <c r="K79" s="19"/>
+      <c r="C79" s="21"/>
+      <c r="D79" s="21"/>
+      <c r="E79" s="21"/>
+      <c r="F79" s="21"/>
+      <c r="G79" s="21"/>
+      <c r="H79" s="21"/>
+      <c r="I79" s="21"/>
+      <c r="J79" s="21"/>
+      <c r="K79" s="21"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="19"/>
-      <c r="D80" s="19"/>
-      <c r="E80" s="19"/>
-      <c r="F80" s="19"/>
-      <c r="G80" s="19"/>
-      <c r="H80" s="19"/>
-      <c r="I80" s="19"/>
-      <c r="J80" s="19"/>
-      <c r="K80" s="19"/>
+      <c r="C80" s="21"/>
+      <c r="D80" s="21"/>
+      <c r="E80" s="21"/>
+      <c r="F80" s="21"/>
+      <c r="G80" s="21"/>
+      <c r="H80" s="21"/>
+      <c r="I80" s="21"/>
+      <c r="J80" s="21"/>
+      <c r="K80" s="21"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="19"/>
-      <c r="D81" s="19"/>
-      <c r="E81" s="19"/>
-      <c r="F81" s="19"/>
-      <c r="G81" s="19"/>
-      <c r="H81" s="19"/>
-      <c r="I81" s="19"/>
-      <c r="J81" s="19"/>
-      <c r="K81" s="19"/>
+      <c r="C81" s="21"/>
+      <c r="D81" s="21"/>
+      <c r="E81" s="21"/>
+      <c r="F81" s="21"/>
+      <c r="G81" s="21"/>
+      <c r="H81" s="21"/>
+      <c r="I81" s="21"/>
+      <c r="J81" s="21"/>
+      <c r="K81" s="21"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="19"/>
-      <c r="D82" s="19"/>
-      <c r="E82" s="19"/>
-      <c r="F82" s="19"/>
-      <c r="G82" s="19"/>
-      <c r="H82" s="19"/>
-      <c r="I82" s="19"/>
-      <c r="J82" s="19"/>
-      <c r="K82" s="19"/>
+      <c r="C82" s="21"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="21"/>
+      <c r="F82" s="21"/>
+      <c r="G82" s="21"/>
+      <c r="H82" s="21"/>
+      <c r="I82" s="21"/>
+      <c r="J82" s="21"/>
+      <c r="K82" s="21"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="19"/>
-      <c r="D83" s="19"/>
-      <c r="E83" s="19"/>
-      <c r="F83" s="19"/>
-      <c r="G83" s="19"/>
-      <c r="H83" s="19"/>
-      <c r="I83" s="19"/>
-      <c r="J83" s="19"/>
-      <c r="K83" s="19"/>
+      <c r="C83" s="21"/>
+      <c r="D83" s="21"/>
+      <c r="E83" s="21"/>
+      <c r="F83" s="21"/>
+      <c r="G83" s="21"/>
+      <c r="H83" s="21"/>
+      <c r="I83" s="21"/>
+      <c r="J83" s="21"/>
+      <c r="K83" s="21"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D84" s="19">
-        <v>1</v>
-      </c>
-      <c r="E84" s="19"/>
-      <c r="F84" s="19"/>
-      <c r="G84" s="19"/>
-      <c r="H84" s="19"/>
-      <c r="I84" s="19"/>
-      <c r="J84" s="19"/>
-      <c r="K84" s="19"/>
+      <c r="C84" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D84" s="21">
+        <v>1</v>
+      </c>
+      <c r="E84" s="21"/>
+      <c r="F84" s="21"/>
+      <c r="G84" s="21"/>
+      <c r="H84" s="21"/>
+      <c r="I84" s="21"/>
+      <c r="J84" s="21"/>
+      <c r="K84" s="21"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="19"/>
-      <c r="D85" s="19"/>
-      <c r="E85" s="19"/>
-      <c r="F85" s="19"/>
-      <c r="G85" s="19"/>
-      <c r="H85" s="19"/>
-      <c r="I85" s="19"/>
-      <c r="J85" s="19"/>
-      <c r="K85" s="19"/>
+      <c r="C85" s="21"/>
+      <c r="D85" s="21"/>
+      <c r="E85" s="21"/>
+      <c r="F85" s="21"/>
+      <c r="G85" s="21"/>
+      <c r="H85" s="21"/>
+      <c r="I85" s="21"/>
+      <c r="J85" s="21"/>
+      <c r="K85" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2745,31 +2758,31 @@
   <sheetData>
     <row r="2" spans="2:14">
       <c r="B2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="2:14">
       <c r="B3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="2:14">
       <c r="H4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="2:14">
       <c r="D8" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>4</v>
@@ -2778,36 +2791,36 @@
         <v>2</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="2:14">
       <c r="D9" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -2825,19 +2838,19 @@
     </row>
     <row r="10" spans="2:14">
       <c r="D10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -2855,19 +2868,19 @@
     </row>
     <row r="11" spans="2:14">
       <c r="D11" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -2885,19 +2898,19 @@
     </row>
     <row r="12" ht="16" spans="2:14">
       <c r="D12" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -2915,19 +2928,19 @@
     </row>
     <row r="13" spans="2:14">
       <c r="D13" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -2945,19 +2958,19 @@
     </row>
     <row r="14" spans="2:14">
       <c r="D14" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -2975,19 +2988,19 @@
     </row>
     <row r="15" spans="2:14">
       <c r="D15" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -3005,10 +3018,10 @@
     </row>
     <row r="16" ht="16" spans="2:14">
       <c r="D16" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G16" t="str">
         <f>G15</f>
@@ -3019,7 +3032,7 @@
         <v>2025, 2150</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J16">
         <f t="shared" ref="J16:L16" si="0">J12</f>
@@ -3040,10 +3053,10 @@
     </row>
     <row r="17" ht="16" spans="4:14">
       <c r="D17" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" ref="G17:M17" si="1">G16</f>
@@ -3054,7 +3067,7 @@
         <v>2025, 2150</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J17">
         <f t="shared" si="1"/>
@@ -3075,10 +3088,10 @@
     </row>
     <row r="18" ht="16" spans="4:14">
       <c r="D18" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G18" t="str">
         <f>G17</f>
@@ -3089,7 +3102,7 @@
         <v>2025, 2150</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -3106,21 +3119,21 @@
     </row>
     <row r="28" spans="4:14">
       <c r="H28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="4:14">
       <c r="D29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F29" t="s">
         <v>6</v>
       </c>
       <c r="G29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H29" t="s">
         <v>4</v>
@@ -3129,36 +3142,36 @@
         <v>2</v>
       </c>
       <c r="J29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" ht="16" spans="4:14">
       <c r="D30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -3175,19 +3188,19 @@
     </row>
     <row r="31" ht="16" spans="4:14">
       <c r="D31" t="s">
+        <v>94</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G31" t="s">
+        <v>69</v>
+      </c>
+      <c r="H31" t="s">
+        <v>92</v>
+      </c>
+      <c r="I31" t="s">
         <v>93</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G31" t="s">
-        <v>68</v>
-      </c>
-      <c r="H31" t="s">
-        <v>91</v>
-      </c>
-      <c r="I31" t="s">
-        <v>92</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -3205,19 +3218,19 @@
     </row>
     <row r="32" ht="16" spans="4:14">
       <c r="D32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H32" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -3235,19 +3248,19 @@
     </row>
     <row r="33" ht="16" spans="4:13">
       <c r="D33" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G33" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -3266,19 +3279,19 @@
     </row>
     <row r="34" ht="16" spans="4:13">
       <c r="D34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G34" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H34" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -3297,19 +3310,19 @@
     </row>
     <row r="35" ht="16" spans="4:13">
       <c r="D35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -3328,19 +3341,19 @@
     </row>
     <row r="36" ht="16" spans="4:13">
       <c r="D36" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H36" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I36" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J36">
         <v>1</v>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -775,11 +775,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="0"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
@@ -794,6 +789,11 @@
     <font>
       <sz val="9"/>
       <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
       <charset val="0"/>
     </font>
   </fonts>
@@ -2338,7 +2338,7 @@
         <v>45</v>
       </c>
       <c r="E27" s="20">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="F27" s="10"/>
     </row>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="1" activeTab="4"/>
+    <workbookView windowWidth="13120" windowHeight="8980" firstSheet="1" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
@@ -243,7 +243,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="107">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -381,6 +381,9 @@
   </si>
   <si>
     <t>START</t>
+  </si>
+  <si>
+    <t>Tra_EV_Bat*virgi*</t>
   </si>
   <si>
     <t>~TFM_AVA</t>
@@ -1310,7 +1313,7 @@
     <xf numFmtId="0" fontId="27" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1340,6 +1343,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -1989,10 +1993,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="22"/>
+      <c r="K10" s="23"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="22"/>
+      <c r="K11" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2343,9 +2347,15 @@
       <c r="F27" s="10"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
+      <c r="C28" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="21">
+        <v>2020</v>
+      </c>
       <c r="F28" s="10"/>
     </row>
     <row r="29" spans="2:6">
@@ -2378,360 +2388,360 @@
       <c r="E38" s="7"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="21" t="s">
-        <v>46</v>
+      <c r="C54" s="22" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="21"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="21"/>
-      <c r="G56" s="21"/>
-      <c r="H56" s="21"/>
-      <c r="I56" s="21"/>
-      <c r="J56" s="21"/>
-      <c r="K56" s="21"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="22"/>
+      <c r="H56" s="22"/>
+      <c r="I56" s="22"/>
+      <c r="J56" s="22"/>
+      <c r="K56" s="22"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="D57" s="21" t="s">
+      <c r="C57" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D57" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="F57" s="21" t="s">
+      <c r="E57" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="G57" s="21" t="s">
+      <c r="F57" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="H57" s="21" t="s">
+      <c r="G57" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="I57" s="21" t="s">
+      <c r="H57" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="J57" s="21" t="s">
+      <c r="I57" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="K57" s="21" t="s">
+      <c r="J57" s="22" t="s">
         <v>54</v>
       </c>
+      <c r="K57" s="22" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="21"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21"/>
-      <c r="H58" s="21"/>
-      <c r="I58" s="21"/>
-      <c r="J58" s="21"/>
-      <c r="K58" s="21"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="22"/>
+      <c r="J58" s="22"/>
+      <c r="K58" s="22"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="21"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="21"/>
-      <c r="G59" s="21"/>
-      <c r="H59" s="21"/>
-      <c r="I59" s="21"/>
-      <c r="J59" s="21"/>
-      <c r="K59" s="21"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="22"/>
+      <c r="H59" s="22"/>
+      <c r="I59" s="22"/>
+      <c r="J59" s="22"/>
+      <c r="K59" s="22"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="21"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21"/>
-      <c r="G60" s="21"/>
-      <c r="H60" s="21"/>
-      <c r="I60" s="21"/>
-      <c r="J60" s="21"/>
-      <c r="K60" s="21"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="22"/>
+      <c r="H60" s="22"/>
+      <c r="I60" s="22"/>
+      <c r="J60" s="22"/>
+      <c r="K60" s="22"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="21"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="21"/>
-      <c r="G61" s="21"/>
-      <c r="H61" s="21"/>
-      <c r="I61" s="21"/>
-      <c r="J61" s="21"/>
-      <c r="K61" s="21"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="22"/>
+      <c r="I61" s="22"/>
+      <c r="J61" s="22"/>
+      <c r="K61" s="22"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="21"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="21"/>
-      <c r="G62" s="21"/>
-      <c r="H62" s="21"/>
-      <c r="I62" s="21"/>
-      <c r="J62" s="21"/>
-      <c r="K62" s="21"/>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="22"/>
+      <c r="I62" s="22"/>
+      <c r="J62" s="22"/>
+      <c r="K62" s="22"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="21"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21"/>
-      <c r="H63" s="21"/>
-      <c r="I63" s="21"/>
-      <c r="J63" s="21"/>
-      <c r="K63" s="21"/>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="22"/>
+      <c r="K63" s="22"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="21"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="21"/>
-      <c r="G64" s="21"/>
-      <c r="H64" s="21"/>
-      <c r="I64" s="21"/>
-      <c r="J64" s="21"/>
-      <c r="K64" s="21"/>
+      <c r="C64" s="22"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="22"/>
+      <c r="H64" s="22"/>
+      <c r="I64" s="22"/>
+      <c r="J64" s="22"/>
+      <c r="K64" s="22"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="21"/>
-      <c r="H65" s="21"/>
-      <c r="I65" s="21"/>
-      <c r="J65" s="21"/>
-      <c r="K65" s="21"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
+      <c r="H65" s="22"/>
+      <c r="I65" s="22"/>
+      <c r="J65" s="22"/>
+      <c r="K65" s="22"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21"/>
-      <c r="G66" s="21"/>
-      <c r="H66" s="21"/>
-      <c r="I66" s="21"/>
-      <c r="J66" s="21"/>
-      <c r="K66" s="21"/>
+      <c r="C66" s="22"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="22"/>
+      <c r="G66" s="22"/>
+      <c r="H66" s="22"/>
+      <c r="I66" s="22"/>
+      <c r="J66" s="22"/>
+      <c r="K66" s="22"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="21"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="21"/>
-      <c r="G67" s="21"/>
-      <c r="H67" s="21"/>
-      <c r="I67" s="21"/>
-      <c r="J67" s="21"/>
-      <c r="K67" s="21"/>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="22"/>
+      <c r="K67" s="22"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="21"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="21"/>
-      <c r="I68" s="21"/>
-      <c r="J68" s="21"/>
-      <c r="K68" s="21"/>
+      <c r="C68" s="22"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="22"/>
+      <c r="I68" s="22"/>
+      <c r="J68" s="22"/>
+      <c r="K68" s="22"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="21"/>
-      <c r="H69" s="21"/>
-      <c r="I69" s="21"/>
-      <c r="J69" s="21"/>
-      <c r="K69" s="21"/>
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
+      <c r="H69" s="22"/>
+      <c r="I69" s="22"/>
+      <c r="J69" s="22"/>
+      <c r="K69" s="22"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="21"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
-      <c r="H70" s="21"/>
-      <c r="I70" s="21"/>
-      <c r="J70" s="21"/>
-      <c r="K70" s="21"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22"/>
+      <c r="J70" s="22"/>
+      <c r="K70" s="22"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-      <c r="I71" s="21"/>
-      <c r="J71" s="21"/>
-      <c r="K71" s="21"/>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="22"/>
+      <c r="K71" s="22"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="21"/>
-      <c r="I72" s="21"/>
-      <c r="J72" s="21"/>
-      <c r="K72" s="21"/>
+      <c r="C72" s="22"/>
+      <c r="D72" s="22"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="22"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="22"/>
+      <c r="I72" s="22"/>
+      <c r="J72" s="22"/>
+      <c r="K72" s="22"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
-      <c r="I73" s="21"/>
-      <c r="J73" s="21"/>
-      <c r="K73" s="21"/>
+      <c r="C73" s="22"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="22"/>
+      <c r="J73" s="22"/>
+      <c r="K73" s="22"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="21"/>
-      <c r="I74" s="21"/>
-      <c r="J74" s="21"/>
-      <c r="K74" s="21"/>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
+      <c r="H74" s="22"/>
+      <c r="I74" s="22"/>
+      <c r="J74" s="22"/>
+      <c r="K74" s="22"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="21"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="21"/>
-      <c r="H75" s="21"/>
-      <c r="I75" s="21"/>
-      <c r="J75" s="21"/>
-      <c r="K75" s="21"/>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="22"/>
+      <c r="K75" s="22"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="21"/>
-      <c r="H76" s="21"/>
-      <c r="I76" s="21"/>
-      <c r="J76" s="21"/>
-      <c r="K76" s="21"/>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="F76" s="22"/>
+      <c r="G76" s="22"/>
+      <c r="H76" s="22"/>
+      <c r="I76" s="22"/>
+      <c r="J76" s="22"/>
+      <c r="K76" s="22"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="21"/>
-      <c r="D77" s="21"/>
-      <c r="E77" s="21"/>
-      <c r="F77" s="21"/>
-      <c r="G77" s="21"/>
-      <c r="H77" s="21"/>
-      <c r="I77" s="21"/>
-      <c r="J77" s="21"/>
-      <c r="K77" s="21"/>
+      <c r="C77" s="22"/>
+      <c r="D77" s="22"/>
+      <c r="E77" s="22"/>
+      <c r="F77" s="22"/>
+      <c r="G77" s="22"/>
+      <c r="H77" s="22"/>
+      <c r="I77" s="22"/>
+      <c r="J77" s="22"/>
+      <c r="K77" s="22"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="21"/>
-      <c r="D78" s="21"/>
-      <c r="E78" s="21"/>
-      <c r="F78" s="21"/>
-      <c r="G78" s="21"/>
-      <c r="H78" s="21"/>
-      <c r="I78" s="21"/>
-      <c r="J78" s="21"/>
-      <c r="K78" s="21"/>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="F78" s="22"/>
+      <c r="G78" s="22"/>
+      <c r="H78" s="22"/>
+      <c r="I78" s="22"/>
+      <c r="J78" s="22"/>
+      <c r="K78" s="22"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="21"/>
-      <c r="D79" s="21"/>
-      <c r="E79" s="21"/>
-      <c r="F79" s="21"/>
-      <c r="G79" s="21"/>
-      <c r="H79" s="21"/>
-      <c r="I79" s="21"/>
-      <c r="J79" s="21"/>
-      <c r="K79" s="21"/>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="22"/>
+      <c r="K79" s="22"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="21"/>
-      <c r="D80" s="21"/>
-      <c r="E80" s="21"/>
-      <c r="F80" s="21"/>
-      <c r="G80" s="21"/>
-      <c r="H80" s="21"/>
-      <c r="I80" s="21"/>
-      <c r="J80" s="21"/>
-      <c r="K80" s="21"/>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="F80" s="22"/>
+      <c r="G80" s="22"/>
+      <c r="H80" s="22"/>
+      <c r="I80" s="22"/>
+      <c r="J80" s="22"/>
+      <c r="K80" s="22"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="21"/>
-      <c r="D81" s="21"/>
-      <c r="E81" s="21"/>
-      <c r="F81" s="21"/>
-      <c r="G81" s="21"/>
-      <c r="H81" s="21"/>
-      <c r="I81" s="21"/>
-      <c r="J81" s="21"/>
-      <c r="K81" s="21"/>
+      <c r="C81" s="22"/>
+      <c r="D81" s="22"/>
+      <c r="E81" s="22"/>
+      <c r="F81" s="22"/>
+      <c r="G81" s="22"/>
+      <c r="H81" s="22"/>
+      <c r="I81" s="22"/>
+      <c r="J81" s="22"/>
+      <c r="K81" s="22"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="21"/>
-      <c r="D82" s="21"/>
-      <c r="E82" s="21"/>
-      <c r="F82" s="21"/>
-      <c r="G82" s="21"/>
-      <c r="H82" s="21"/>
-      <c r="I82" s="21"/>
-      <c r="J82" s="21"/>
-      <c r="K82" s="21"/>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="F82" s="22"/>
+      <c r="G82" s="22"/>
+      <c r="H82" s="22"/>
+      <c r="I82" s="22"/>
+      <c r="J82" s="22"/>
+      <c r="K82" s="22"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="21"/>
-      <c r="D83" s="21"/>
-      <c r="E83" s="21"/>
-      <c r="F83" s="21"/>
-      <c r="G83" s="21"/>
-      <c r="H83" s="21"/>
-      <c r="I83" s="21"/>
-      <c r="J83" s="21"/>
-      <c r="K83" s="21"/>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="F83" s="22"/>
+      <c r="G83" s="22"/>
+      <c r="H83" s="22"/>
+      <c r="I83" s="22"/>
+      <c r="J83" s="22"/>
+      <c r="K83" s="22"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="D84" s="21">
-        <v>1</v>
-      </c>
-      <c r="E84" s="21"/>
-      <c r="F84" s="21"/>
-      <c r="G84" s="21"/>
-      <c r="H84" s="21"/>
-      <c r="I84" s="21"/>
-      <c r="J84" s="21"/>
-      <c r="K84" s="21"/>
+      <c r="C84" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D84" s="22">
+        <v>1</v>
+      </c>
+      <c r="E84" s="22"/>
+      <c r="F84" s="22"/>
+      <c r="G84" s="22"/>
+      <c r="H84" s="22"/>
+      <c r="I84" s="22"/>
+      <c r="J84" s="22"/>
+      <c r="K84" s="22"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="21"/>
-      <c r="D85" s="21"/>
-      <c r="E85" s="21"/>
-      <c r="F85" s="21"/>
-      <c r="G85" s="21"/>
-      <c r="H85" s="21"/>
-      <c r="I85" s="21"/>
-      <c r="J85" s="21"/>
-      <c r="K85" s="21"/>
+      <c r="C85" s="22"/>
+      <c r="D85" s="22"/>
+      <c r="E85" s="22"/>
+      <c r="F85" s="22"/>
+      <c r="G85" s="22"/>
+      <c r="H85" s="22"/>
+      <c r="I85" s="22"/>
+      <c r="J85" s="22"/>
+      <c r="K85" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2758,31 +2768,31 @@
   <sheetData>
     <row r="2" spans="2:14">
       <c r="B2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:14">
       <c r="B3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="2:14">
       <c r="H4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="2:14">
       <c r="D8" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>4</v>
@@ -2791,36 +2801,36 @@
         <v>2</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="2:14">
       <c r="D9" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -2838,19 +2848,19 @@
     </row>
     <row r="10" spans="2:14">
       <c r="D10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -2868,19 +2878,19 @@
     </row>
     <row r="11" spans="2:14">
       <c r="D11" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -2898,19 +2908,19 @@
     </row>
     <row r="12" ht="16" spans="2:14">
       <c r="D12" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -2928,19 +2938,19 @@
     </row>
     <row r="13" spans="2:14">
       <c r="D13" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -2958,19 +2968,19 @@
     </row>
     <row r="14" spans="2:14">
       <c r="D14" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -2988,19 +2998,19 @@
     </row>
     <row r="15" spans="2:14">
       <c r="D15" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -3018,10 +3028,10 @@
     </row>
     <row r="16" ht="16" spans="2:14">
       <c r="D16" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G16" t="str">
         <f>G15</f>
@@ -3032,7 +3042,7 @@
         <v>2025, 2150</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J16">
         <f t="shared" ref="J16:L16" si="0">J12</f>
@@ -3053,10 +3063,10 @@
     </row>
     <row r="17" ht="16" spans="4:14">
       <c r="D17" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" ref="G17:M17" si="1">G16</f>
@@ -3067,7 +3077,7 @@
         <v>2025, 2150</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J17">
         <f t="shared" si="1"/>
@@ -3088,10 +3098,10 @@
     </row>
     <row r="18" ht="16" spans="4:14">
       <c r="D18" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G18" t="str">
         <f>G17</f>
@@ -3102,7 +3112,7 @@
         <v>2025, 2150</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -3119,21 +3129,21 @@
     </row>
     <row r="28" spans="4:14">
       <c r="H28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="4:14">
       <c r="D29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F29" t="s">
         <v>6</v>
       </c>
       <c r="G29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H29" t="s">
         <v>4</v>
@@ -3142,36 +3152,36 @@
         <v>2</v>
       </c>
       <c r="J29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" ht="16" spans="4:14">
       <c r="D30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -3188,19 +3198,19 @@
     </row>
     <row r="31" ht="16" spans="4:14">
       <c r="D31" t="s">
+        <v>95</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G31" t="s">
+        <v>70</v>
+      </c>
+      <c r="H31" t="s">
+        <v>93</v>
+      </c>
+      <c r="I31" t="s">
         <v>94</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G31" t="s">
-        <v>69</v>
-      </c>
-      <c r="H31" t="s">
-        <v>92</v>
-      </c>
-      <c r="I31" t="s">
-        <v>93</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -3218,19 +3228,19 @@
     </row>
     <row r="32" ht="16" spans="4:14">
       <c r="D32" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -3248,19 +3258,19 @@
     </row>
     <row r="33" ht="16" spans="4:13">
       <c r="D33" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -3279,19 +3289,19 @@
     </row>
     <row r="34" ht="16" spans="4:13">
       <c r="D34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -3310,19 +3320,19 @@
     </row>
     <row r="35" ht="16" spans="4:13">
       <c r="D35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -3341,19 +3351,19 @@
     </row>
     <row r="36" ht="16" spans="4:13">
       <c r="D36" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H36" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I36" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J36">
         <v>1</v>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13120" windowHeight="8980" firstSheet="1" activeTab="4"/>
+    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="ROR_has_no_regulation_cap" sheetId="10" r:id="rId4"/>
     <sheet name="Ramp_rate_constraints" sheetId="11" r:id="rId5"/>
     <sheet name="Growth_rate" sheetId="12" r:id="rId6"/>
+    <sheet name="Peak_demand_limit_battery" sheetId="13" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="IQ_FWD_Q" hidden="1">501</definedName>
@@ -242,8 +243,40 @@
 </comments>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>xli9</author>
+  </authors>
+  <commentList>
+    <comment ref="M20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t>xli9:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">
+Bca the capacity unit is GWh</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="137">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -564,6 +597,96 @@
   </si>
   <si>
     <t>Tra_EV_Batt-NMC811_fromrecy</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy8</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt</t>
+  </si>
+  <si>
+    <t>2020, 2150</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy9</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_LMO</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy10</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_NCA</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy11</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_NMC111</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy12</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_NMC532</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy13</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_NMC622</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy14</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_NMC811</t>
+  </si>
+  <si>
+    <t>~UC_Sets: R_E: AllRegions</t>
+  </si>
+  <si>
+    <t>~UC_T: UP</t>
+  </si>
+  <si>
+    <t>Pset_CI</t>
+  </si>
+  <si>
+    <t>Cset_CN</t>
+  </si>
+  <si>
+    <t>UC_FLO</t>
+  </si>
+  <si>
+    <t>UC_COMPRD</t>
+  </si>
+  <si>
+    <t>UC_RHSRTS</t>
+  </si>
+  <si>
+    <t>UC_RHSRTS~0</t>
+  </si>
+  <si>
+    <t>UCE_Min-DispatchablePrd</t>
+  </si>
+  <si>
+    <t>ELE,CHP</t>
+  </si>
+  <si>
+    <t>E*</t>
+  </si>
+  <si>
+    <t>ELCSPV</t>
+  </si>
+  <si>
+    <t>Discharge of batteries should lower than a level</t>
+  </si>
+  <si>
+    <t>AuxStoOUT</t>
+  </si>
+  <si>
+    <t>ELCWIN</t>
   </si>
 </sst>
 </file>
@@ -784,7 +907,6 @@
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -795,12 +917,13 @@
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -809,7 +932,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -822,12 +957,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1018,7 +1147,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1027,40 +1156,14 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFDEE2E6"/>
-      </left>
+      <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
+      <top style="thick">
+        <color rgb="FFFC8462"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
+      <bottom style="thick">
+        <color rgb="FFFC8462"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1185,7 +1288,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1197,124 +1300,127 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1322,30 +1428,34 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="49" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="49" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="53">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1879,7 +1989,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="2">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -1936,7 +2046,7 @@
       </c>
     </row>
     <row r="4" ht="16" spans="1:11">
-      <c r="A4" s="3"/>
+      <c r="A4" s="6"/>
     </row>
     <row r="7" spans="1:11">
       <c r="D7" t="s">
@@ -1993,10 +2103,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="23"/>
+      <c r="K10" s="28"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="23"/>
+      <c r="K11" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2017,12 +2127,12 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:13">
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="10"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
@@ -2037,19 +2147,19 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="11"/>
+      <c r="K6" s="18"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="19">
         <v>10</v>
       </c>
     </row>
@@ -2057,29 +2167,29 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="19">
         <v>7</v>
       </c>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
     </row>
     <row r="9" ht="16" spans="2:13">
       <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="19">
         <v>10</v>
       </c>
     </row>
@@ -2087,29 +2197,29 @@
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="19">
         <v>8</v>
       </c>
-      <c r="K10" s="13"/>
-      <c r="L10" s="14"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="21"/>
     </row>
     <row r="11" ht="16" spans="2:13">
       <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="17">
         <v>1.5</v>
       </c>
     </row>
@@ -2117,13 +2227,13 @@
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="17">
         <v>1.5</v>
       </c>
     </row>
@@ -2131,13 +2241,13 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="7">
         <v>2</v>
       </c>
     </row>
@@ -2145,13 +2255,13 @@
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2159,13 +2269,13 @@
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2173,13 +2283,13 @@
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="22">
         <v>12</v>
       </c>
     </row>
@@ -2187,561 +2297,561 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="24">
         <v>0.2</v>
       </c>
-      <c r="F17" s="10"/>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="24">
         <v>0.2</v>
       </c>
-      <c r="F18" s="10"/>
+      <c r="F18" s="7"/>
     </row>
     <row r="19" ht="16" spans="2:6">
       <c r="B19" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="24">
         <v>0.2</v>
       </c>
-      <c r="F19" s="10"/>
+      <c r="F19" s="7"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="24">
         <v>0.5</v>
       </c>
-      <c r="F20" s="10"/>
+      <c r="F20" s="7"/>
     </row>
     <row r="21" ht="16" spans="2:6">
       <c r="B21" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="24">
         <v>0.8</v>
       </c>
-      <c r="F21" s="10"/>
+      <c r="F21" s="7"/>
     </row>
     <row r="22" ht="16" spans="2:6">
       <c r="B22" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="10"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="7"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="10">
-        <v>1</v>
-      </c>
-      <c r="F23" s="10"/>
+      <c r="E23" s="7">
+        <v>1</v>
+      </c>
+      <c r="F23" s="7"/>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="10">
-        <v>1</v>
-      </c>
-      <c r="F24" s="10"/>
+      <c r="E24" s="7">
+        <v>1</v>
+      </c>
+      <c r="F24" s="7"/>
     </row>
     <row r="25" ht="16" spans="2:6">
       <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="10">
-        <v>1</v>
-      </c>
-      <c r="F25" s="10"/>
+      <c r="E25" s="7">
+        <v>1</v>
+      </c>
+      <c r="F25" s="7"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="17">
         <v>0.05</v>
       </c>
-      <c r="F26" s="10"/>
+      <c r="F26" s="7"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="20" t="s">
+      <c r="D27" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="20">
+      <c r="E27" s="25">
         <v>2020</v>
       </c>
-      <c r="F27" s="10"/>
+      <c r="F27" s="7"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="26">
         <v>2020</v>
       </c>
-      <c r="F28" s="10"/>
+      <c r="F28" s="7"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
     </row>
     <row r="38" spans="3:5">
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="22" t="s">
+      <c r="C54" s="27" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="22"/>
-      <c r="H56" s="22"/>
-      <c r="I56" s="22"/>
-      <c r="J56" s="22"/>
-      <c r="K56" s="22"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="27"/>
+      <c r="I56" s="27"/>
+      <c r="J56" s="27"/>
+      <c r="K56" s="27"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="22" t="s">
+      <c r="C57" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="22" t="s">
+      <c r="D57" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="22" t="s">
+      <c r="E57" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="F57" s="22" t="s">
+      <c r="F57" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="G57" s="22" t="s">
+      <c r="G57" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="22" t="s">
+      <c r="H57" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="22" t="s">
+      <c r="I57" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="J57" s="22" t="s">
+      <c r="J57" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="K57" s="22" t="s">
+      <c r="K57" s="27" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="22"/>
-      <c r="I58" s="22"/>
-      <c r="J58" s="22"/>
-      <c r="K58" s="22"/>
+      <c r="C58" s="27"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="27"/>
+      <c r="I58" s="27"/>
+      <c r="J58" s="27"/>
+      <c r="K58" s="27"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="22"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
-      <c r="H59" s="22"/>
-      <c r="I59" s="22"/>
-      <c r="J59" s="22"/>
-      <c r="K59" s="22"/>
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="27"/>
+      <c r="I59" s="27"/>
+      <c r="J59" s="27"/>
+      <c r="K59" s="27"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="22"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="22"/>
-      <c r="H60" s="22"/>
-      <c r="I60" s="22"/>
-      <c r="J60" s="22"/>
-      <c r="K60" s="22"/>
+      <c r="C60" s="27"/>
+      <c r="D60" s="27"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="27"/>
+      <c r="G60" s="27"/>
+      <c r="H60" s="27"/>
+      <c r="I60" s="27"/>
+      <c r="J60" s="27"/>
+      <c r="K60" s="27"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="22"/>
-      <c r="H61" s="22"/>
-      <c r="I61" s="22"/>
-      <c r="J61" s="22"/>
-      <c r="K61" s="22"/>
+      <c r="C61" s="27"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="27"/>
+      <c r="I61" s="27"/>
+      <c r="J61" s="27"/>
+      <c r="K61" s="27"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="22"/>
-      <c r="J62" s="22"/>
-      <c r="K62" s="22"/>
+      <c r="C62" s="27"/>
+      <c r="D62" s="27"/>
+      <c r="E62" s="27"/>
+      <c r="F62" s="27"/>
+      <c r="G62" s="27"/>
+      <c r="H62" s="27"/>
+      <c r="I62" s="27"/>
+      <c r="J62" s="27"/>
+      <c r="K62" s="27"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="22"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="22"/>
-      <c r="H63" s="22"/>
-      <c r="I63" s="22"/>
-      <c r="J63" s="22"/>
-      <c r="K63" s="22"/>
+      <c r="C63" s="27"/>
+      <c r="D63" s="27"/>
+      <c r="E63" s="27"/>
+      <c r="F63" s="27"/>
+      <c r="G63" s="27"/>
+      <c r="H63" s="27"/>
+      <c r="I63" s="27"/>
+      <c r="J63" s="27"/>
+      <c r="K63" s="27"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="22"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="22"/>
-      <c r="H64" s="22"/>
-      <c r="I64" s="22"/>
-      <c r="J64" s="22"/>
-      <c r="K64" s="22"/>
+      <c r="C64" s="27"/>
+      <c r="D64" s="27"/>
+      <c r="E64" s="27"/>
+      <c r="F64" s="27"/>
+      <c r="G64" s="27"/>
+      <c r="H64" s="27"/>
+      <c r="I64" s="27"/>
+      <c r="J64" s="27"/>
+      <c r="K64" s="27"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
-      <c r="H65" s="22"/>
-      <c r="I65" s="22"/>
-      <c r="J65" s="22"/>
-      <c r="K65" s="22"/>
+      <c r="C65" s="27"/>
+      <c r="D65" s="27"/>
+      <c r="E65" s="27"/>
+      <c r="F65" s="27"/>
+      <c r="G65" s="27"/>
+      <c r="H65" s="27"/>
+      <c r="I65" s="27"/>
+      <c r="J65" s="27"/>
+      <c r="K65" s="27"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="22"/>
-      <c r="D66" s="22"/>
-      <c r="E66" s="22"/>
-      <c r="F66" s="22"/>
-      <c r="G66" s="22"/>
-      <c r="H66" s="22"/>
-      <c r="I66" s="22"/>
-      <c r="J66" s="22"/>
-      <c r="K66" s="22"/>
+      <c r="C66" s="27"/>
+      <c r="D66" s="27"/>
+      <c r="E66" s="27"/>
+      <c r="F66" s="27"/>
+      <c r="G66" s="27"/>
+      <c r="H66" s="27"/>
+      <c r="I66" s="27"/>
+      <c r="J66" s="27"/>
+      <c r="K66" s="27"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="22"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
-      <c r="H67" s="22"/>
-      <c r="I67" s="22"/>
-      <c r="J67" s="22"/>
-      <c r="K67" s="22"/>
+      <c r="C67" s="27"/>
+      <c r="D67" s="27"/>
+      <c r="E67" s="27"/>
+      <c r="F67" s="27"/>
+      <c r="G67" s="27"/>
+      <c r="H67" s="27"/>
+      <c r="I67" s="27"/>
+      <c r="J67" s="27"/>
+      <c r="K67" s="27"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="22"/>
-      <c r="D68" s="22"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
-      <c r="G68" s="22"/>
-      <c r="H68" s="22"/>
-      <c r="I68" s="22"/>
-      <c r="J68" s="22"/>
-      <c r="K68" s="22"/>
+      <c r="C68" s="27"/>
+      <c r="D68" s="27"/>
+      <c r="E68" s="27"/>
+      <c r="F68" s="27"/>
+      <c r="G68" s="27"/>
+      <c r="H68" s="27"/>
+      <c r="I68" s="27"/>
+      <c r="J68" s="27"/>
+      <c r="K68" s="27"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="22"/>
-      <c r="D69" s="22"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="22"/>
-      <c r="H69" s="22"/>
-      <c r="I69" s="22"/>
-      <c r="J69" s="22"/>
-      <c r="K69" s="22"/>
+      <c r="C69" s="27"/>
+      <c r="D69" s="27"/>
+      <c r="E69" s="27"/>
+      <c r="F69" s="27"/>
+      <c r="G69" s="27"/>
+      <c r="H69" s="27"/>
+      <c r="I69" s="27"/>
+      <c r="J69" s="27"/>
+      <c r="K69" s="27"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="22"/>
-      <c r="D70" s="22"/>
-      <c r="E70" s="22"/>
-      <c r="F70" s="22"/>
-      <c r="G70" s="22"/>
-      <c r="H70" s="22"/>
-      <c r="I70" s="22"/>
-      <c r="J70" s="22"/>
-      <c r="K70" s="22"/>
+      <c r="C70" s="27"/>
+      <c r="D70" s="27"/>
+      <c r="E70" s="27"/>
+      <c r="F70" s="27"/>
+      <c r="G70" s="27"/>
+      <c r="H70" s="27"/>
+      <c r="I70" s="27"/>
+      <c r="J70" s="27"/>
+      <c r="K70" s="27"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="22"/>
-      <c r="D71" s="22"/>
-      <c r="E71" s="22"/>
-      <c r="F71" s="22"/>
-      <c r="G71" s="22"/>
-      <c r="H71" s="22"/>
-      <c r="I71" s="22"/>
-      <c r="J71" s="22"/>
-      <c r="K71" s="22"/>
+      <c r="C71" s="27"/>
+      <c r="D71" s="27"/>
+      <c r="E71" s="27"/>
+      <c r="F71" s="27"/>
+      <c r="G71" s="27"/>
+      <c r="H71" s="27"/>
+      <c r="I71" s="27"/>
+      <c r="J71" s="27"/>
+      <c r="K71" s="27"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="22"/>
-      <c r="D72" s="22"/>
-      <c r="E72" s="22"/>
-      <c r="F72" s="22"/>
-      <c r="G72" s="22"/>
-      <c r="H72" s="22"/>
-      <c r="I72" s="22"/>
-      <c r="J72" s="22"/>
-      <c r="K72" s="22"/>
+      <c r="C72" s="27"/>
+      <c r="D72" s="27"/>
+      <c r="E72" s="27"/>
+      <c r="F72" s="27"/>
+      <c r="G72" s="27"/>
+      <c r="H72" s="27"/>
+      <c r="I72" s="27"/>
+      <c r="J72" s="27"/>
+      <c r="K72" s="27"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="22"/>
-      <c r="D73" s="22"/>
-      <c r="E73" s="22"/>
-      <c r="F73" s="22"/>
-      <c r="G73" s="22"/>
-      <c r="H73" s="22"/>
-      <c r="I73" s="22"/>
-      <c r="J73" s="22"/>
-      <c r="K73" s="22"/>
+      <c r="C73" s="27"/>
+      <c r="D73" s="27"/>
+      <c r="E73" s="27"/>
+      <c r="F73" s="27"/>
+      <c r="G73" s="27"/>
+      <c r="H73" s="27"/>
+      <c r="I73" s="27"/>
+      <c r="J73" s="27"/>
+      <c r="K73" s="27"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="22"/>
-      <c r="D74" s="22"/>
-      <c r="E74" s="22"/>
-      <c r="F74" s="22"/>
-      <c r="G74" s="22"/>
-      <c r="H74" s="22"/>
-      <c r="I74" s="22"/>
-      <c r="J74" s="22"/>
-      <c r="K74" s="22"/>
+      <c r="C74" s="27"/>
+      <c r="D74" s="27"/>
+      <c r="E74" s="27"/>
+      <c r="F74" s="27"/>
+      <c r="G74" s="27"/>
+      <c r="H74" s="27"/>
+      <c r="I74" s="27"/>
+      <c r="J74" s="27"/>
+      <c r="K74" s="27"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="22"/>
-      <c r="D75" s="22"/>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
-      <c r="G75" s="22"/>
-      <c r="H75" s="22"/>
-      <c r="I75" s="22"/>
-      <c r="J75" s="22"/>
-      <c r="K75" s="22"/>
+      <c r="C75" s="27"/>
+      <c r="D75" s="27"/>
+      <c r="E75" s="27"/>
+      <c r="F75" s="27"/>
+      <c r="G75" s="27"/>
+      <c r="H75" s="27"/>
+      <c r="I75" s="27"/>
+      <c r="J75" s="27"/>
+      <c r="K75" s="27"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="22"/>
-      <c r="D76" s="22"/>
-      <c r="E76" s="22"/>
-      <c r="F76" s="22"/>
-      <c r="G76" s="22"/>
-      <c r="H76" s="22"/>
-      <c r="I76" s="22"/>
-      <c r="J76" s="22"/>
-      <c r="K76" s="22"/>
+      <c r="C76" s="27"/>
+      <c r="D76" s="27"/>
+      <c r="E76" s="27"/>
+      <c r="F76" s="27"/>
+      <c r="G76" s="27"/>
+      <c r="H76" s="27"/>
+      <c r="I76" s="27"/>
+      <c r="J76" s="27"/>
+      <c r="K76" s="27"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="22"/>
-      <c r="D77" s="22"/>
-      <c r="E77" s="22"/>
-      <c r="F77" s="22"/>
-      <c r="G77" s="22"/>
-      <c r="H77" s="22"/>
-      <c r="I77" s="22"/>
-      <c r="J77" s="22"/>
-      <c r="K77" s="22"/>
+      <c r="C77" s="27"/>
+      <c r="D77" s="27"/>
+      <c r="E77" s="27"/>
+      <c r="F77" s="27"/>
+      <c r="G77" s="27"/>
+      <c r="H77" s="27"/>
+      <c r="I77" s="27"/>
+      <c r="J77" s="27"/>
+      <c r="K77" s="27"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="22"/>
-      <c r="D78" s="22"/>
-      <c r="E78" s="22"/>
-      <c r="F78" s="22"/>
-      <c r="G78" s="22"/>
-      <c r="H78" s="22"/>
-      <c r="I78" s="22"/>
-      <c r="J78" s="22"/>
-      <c r="K78" s="22"/>
+      <c r="C78" s="27"/>
+      <c r="D78" s="27"/>
+      <c r="E78" s="27"/>
+      <c r="F78" s="27"/>
+      <c r="G78" s="27"/>
+      <c r="H78" s="27"/>
+      <c r="I78" s="27"/>
+      <c r="J78" s="27"/>
+      <c r="K78" s="27"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="22"/>
-      <c r="D79" s="22"/>
-      <c r="E79" s="22"/>
-      <c r="F79" s="22"/>
-      <c r="G79" s="22"/>
-      <c r="H79" s="22"/>
-      <c r="I79" s="22"/>
-      <c r="J79" s="22"/>
-      <c r="K79" s="22"/>
+      <c r="C79" s="27"/>
+      <c r="D79" s="27"/>
+      <c r="E79" s="27"/>
+      <c r="F79" s="27"/>
+      <c r="G79" s="27"/>
+      <c r="H79" s="27"/>
+      <c r="I79" s="27"/>
+      <c r="J79" s="27"/>
+      <c r="K79" s="27"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="22"/>
-      <c r="D80" s="22"/>
-      <c r="E80" s="22"/>
-      <c r="F80" s="22"/>
-      <c r="G80" s="22"/>
-      <c r="H80" s="22"/>
-      <c r="I80" s="22"/>
-      <c r="J80" s="22"/>
-      <c r="K80" s="22"/>
+      <c r="C80" s="27"/>
+      <c r="D80" s="27"/>
+      <c r="E80" s="27"/>
+      <c r="F80" s="27"/>
+      <c r="G80" s="27"/>
+      <c r="H80" s="27"/>
+      <c r="I80" s="27"/>
+      <c r="J80" s="27"/>
+      <c r="K80" s="27"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="22"/>
-      <c r="D81" s="22"/>
-      <c r="E81" s="22"/>
-      <c r="F81" s="22"/>
-      <c r="G81" s="22"/>
-      <c r="H81" s="22"/>
-      <c r="I81" s="22"/>
-      <c r="J81" s="22"/>
-      <c r="K81" s="22"/>
+      <c r="C81" s="27"/>
+      <c r="D81" s="27"/>
+      <c r="E81" s="27"/>
+      <c r="F81" s="27"/>
+      <c r="G81" s="27"/>
+      <c r="H81" s="27"/>
+      <c r="I81" s="27"/>
+      <c r="J81" s="27"/>
+      <c r="K81" s="27"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="22"/>
-      <c r="D82" s="22"/>
-      <c r="E82" s="22"/>
-      <c r="F82" s="22"/>
-      <c r="G82" s="22"/>
-      <c r="H82" s="22"/>
-      <c r="I82" s="22"/>
-      <c r="J82" s="22"/>
-      <c r="K82" s="22"/>
+      <c r="C82" s="27"/>
+      <c r="D82" s="27"/>
+      <c r="E82" s="27"/>
+      <c r="F82" s="27"/>
+      <c r="G82" s="27"/>
+      <c r="H82" s="27"/>
+      <c r="I82" s="27"/>
+      <c r="J82" s="27"/>
+      <c r="K82" s="27"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="22"/>
-      <c r="D83" s="22"/>
-      <c r="E83" s="22"/>
-      <c r="F83" s="22"/>
-      <c r="G83" s="22"/>
-      <c r="H83" s="22"/>
-      <c r="I83" s="22"/>
-      <c r="J83" s="22"/>
-      <c r="K83" s="22"/>
+      <c r="C83" s="27"/>
+      <c r="D83" s="27"/>
+      <c r="E83" s="27"/>
+      <c r="F83" s="27"/>
+      <c r="G83" s="27"/>
+      <c r="H83" s="27"/>
+      <c r="I83" s="27"/>
+      <c r="J83" s="27"/>
+      <c r="K83" s="27"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="22" t="s">
+      <c r="C84" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="D84" s="22">
-        <v>1</v>
-      </c>
-      <c r="E84" s="22"/>
-      <c r="F84" s="22"/>
-      <c r="G84" s="22"/>
-      <c r="H84" s="22"/>
-      <c r="I84" s="22"/>
-      <c r="J84" s="22"/>
-      <c r="K84" s="22"/>
+      <c r="D84" s="27">
+        <v>1</v>
+      </c>
+      <c r="E84" s="27"/>
+      <c r="F84" s="27"/>
+      <c r="G84" s="27"/>
+      <c r="H84" s="27"/>
+      <c r="I84" s="27"/>
+      <c r="J84" s="27"/>
+      <c r="K84" s="27"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="22"/>
-      <c r="D85" s="22"/>
-      <c r="E85" s="22"/>
-      <c r="F85" s="22"/>
-      <c r="G85" s="22"/>
-      <c r="H85" s="22"/>
-      <c r="I85" s="22"/>
-      <c r="J85" s="22"/>
-      <c r="K85" s="22"/>
+      <c r="C85" s="27"/>
+      <c r="D85" s="27"/>
+      <c r="E85" s="27"/>
+      <c r="F85" s="27"/>
+      <c r="G85" s="27"/>
+      <c r="H85" s="27"/>
+      <c r="I85" s="27"/>
+      <c r="J85" s="27"/>
+      <c r="K85" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2753,7 +2863,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:N52"/>
+  <dimension ref="B2:N54"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="4" max="4" width="27.1636363636364" customWidth="1"/>
@@ -2782,255 +2892,255 @@
       </c>
     </row>
     <row r="8" spans="2:14">
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="N8" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="9" spans="2:14">
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="5" t="s">
         <v>72</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="5">
         <v>1.25</v>
       </c>
       <c r="L9">
         <v>0.05</v>
       </c>
-      <c r="M9" s="2">
-        <v>1</v>
-      </c>
-      <c r="N9" s="2"/>
+      <c r="M9" s="5">
+        <v>1</v>
+      </c>
+      <c r="N9" s="5"/>
     </row>
     <row r="10" spans="2:14">
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="5" t="s">
         <v>72</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="5">
         <v>1.11</v>
       </c>
       <c r="L10">
         <v>0.05</v>
       </c>
-      <c r="M10" s="2">
-        <v>1</v>
-      </c>
-      <c r="N10" s="2"/>
+      <c r="M10" s="5">
+        <v>1</v>
+      </c>
+      <c r="N10" s="5"/>
     </row>
     <row r="11" spans="2:14">
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="5" t="s">
         <v>72</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11" s="5">
         <v>1.15</v>
       </c>
       <c r="L11">
         <v>0.08</v>
       </c>
-      <c r="M11" s="2">
-        <v>1</v>
-      </c>
-      <c r="N11" s="2"/>
+      <c r="M11" s="5">
+        <v>1</v>
+      </c>
+      <c r="N11" s="5"/>
     </row>
     <row r="12" ht="16" spans="2:14">
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="5" t="s">
         <v>72</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="5">
         <v>1.12</v>
       </c>
       <c r="L12">
         <v>0.03</v>
       </c>
-      <c r="M12" s="2">
-        <v>1</v>
-      </c>
-      <c r="N12" s="2"/>
+      <c r="M12" s="5">
+        <v>1</v>
+      </c>
+      <c r="N12" s="5"/>
     </row>
     <row r="13" spans="2:14">
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="5" t="s">
         <v>72</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13" s="5">
         <v>1.2</v>
       </c>
       <c r="L13">
         <v>0.1</v>
       </c>
-      <c r="M13" s="2">
-        <v>1</v>
-      </c>
-      <c r="N13" s="2"/>
+      <c r="M13" s="5">
+        <v>1</v>
+      </c>
+      <c r="N13" s="5"/>
     </row>
     <row r="14" spans="2:14">
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="5" t="s">
         <v>72</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K14" s="5">
         <v>1.06</v>
       </c>
       <c r="L14">
         <v>0.15</v>
       </c>
-      <c r="M14" s="2">
-        <v>1</v>
-      </c>
-      <c r="N14" s="2"/>
+      <c r="M14" s="5">
+        <v>1</v>
+      </c>
+      <c r="N14" s="5"/>
     </row>
     <row r="15" spans="2:14">
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="5" t="s">
         <v>72</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
-      <c r="K15" s="2">
+      <c r="K15" s="5">
         <v>1.06</v>
       </c>
       <c r="L15">
         <v>0.3</v>
       </c>
-      <c r="M15" s="2">
-        <v>1</v>
-      </c>
-      <c r="N15" s="2"/>
+      <c r="M15" s="5">
+        <v>1</v>
+      </c>
+      <c r="N15" s="5"/>
     </row>
     <row r="16" ht="16" spans="2:14">
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="6" t="s">
         <v>86</v>
       </c>
       <c r="G16" t="str">
@@ -3041,7 +3151,7 @@
         <f>H15</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I16" s="5" t="s">
         <v>72</v>
       </c>
       <c r="J16">
@@ -3062,10 +3172,10 @@
       </c>
     </row>
     <row r="17" ht="16" spans="4:14">
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="6" t="s">
         <v>88</v>
       </c>
       <c r="G17" t="str">
@@ -3076,7 +3186,7 @@
         <f t="shared" si="1"/>
         <v>2025, 2150</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="I17" s="5" t="s">
         <v>72</v>
       </c>
       <c r="J17">
@@ -3097,10 +3207,10 @@
       </c>
     </row>
     <row r="18" ht="16" spans="4:14">
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="6" t="s">
         <v>90</v>
       </c>
       <c r="G18" t="str">
@@ -3111,7 +3221,7 @@
         <f>H17</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="I18" s="5" t="s">
         <v>72</v>
       </c>
       <c r="J18">
@@ -3127,309 +3237,1015 @@
         <v>1</v>
       </c>
     </row>
+    <row r="27" spans="4:14">
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+    </row>
     <row r="28" spans="4:14">
-      <c r="H28" t="s">
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7" t="s">
         <v>59</v>
       </c>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
     </row>
     <row r="29" spans="4:14">
-      <c r="D29" t="s">
+      <c r="D29" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I29" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="J29" t="s">
+      <c r="J29" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="K29" t="s">
+      <c r="K29" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="L29" t="s">
+      <c r="L29" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="M29" t="s">
+      <c r="M29" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="N29" t="s">
+      <c r="N29" s="7" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="30" ht="16" spans="4:14">
-      <c r="D30" t="s">
+      <c r="D30" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="E30" s="7"/>
+      <c r="F30" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G30" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="J30">
-        <v>1</v>
-      </c>
-      <c r="K30">
-        <v>1</v>
-      </c>
-      <c r="L30">
+      <c r="J30" s="7">
+        <v>1</v>
+      </c>
+      <c r="K30" s="7">
+        <v>1</v>
+      </c>
+      <c r="L30" s="7">
         <v>0.01</v>
       </c>
-      <c r="M30">
-        <v>1</v>
-      </c>
+      <c r="M30" s="7">
+        <v>1</v>
+      </c>
+      <c r="N30" s="7"/>
     </row>
     <row r="31" ht="16" spans="4:14">
-      <c r="D31" t="s">
+      <c r="D31" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="E31" s="7"/>
+      <c r="F31" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G31" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H31" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="J31">
-        <v>1</v>
-      </c>
-      <c r="K31">
-        <v>1</v>
-      </c>
-      <c r="L31">
+      <c r="J31" s="7">
+        <v>1</v>
+      </c>
+      <c r="K31" s="7">
+        <v>1</v>
+      </c>
+      <c r="L31" s="7">
         <f t="shared" ref="L31:L36" si="2">L30</f>
         <v>0.01</v>
       </c>
-      <c r="M31">
-        <v>1</v>
-      </c>
+      <c r="M31" s="7">
+        <v>1</v>
+      </c>
+      <c r="N31" s="7"/>
     </row>
     <row r="32" ht="16" spans="4:14">
-      <c r="D32" t="s">
+      <c r="D32" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="E32" s="7"/>
+      <c r="F32" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="J32">
-        <v>1</v>
-      </c>
-      <c r="K32">
-        <v>1</v>
-      </c>
-      <c r="L32">
+      <c r="J32" s="7">
+        <v>1</v>
+      </c>
+      <c r="K32" s="7">
+        <v>1</v>
+      </c>
+      <c r="L32" s="7">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" ht="16" spans="4:13">
-      <c r="D33" t="s">
+      <c r="M32" s="7">
+        <v>1</v>
+      </c>
+      <c r="N32" s="7"/>
+    </row>
+    <row r="33" ht="16" spans="4:14">
+      <c r="D33" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="E33" s="7"/>
+      <c r="F33" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="J33">
-        <v>1</v>
-      </c>
-      <c r="K33">
+      <c r="J33" s="7">
+        <v>1</v>
+      </c>
+      <c r="K33" s="7">
         <f>K32</f>
         <v>1</v>
       </c>
-      <c r="L33">
+      <c r="L33" s="7">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" ht="16" spans="4:13">
-      <c r="D34" t="s">
+      <c r="M33" s="7">
+        <v>1</v>
+      </c>
+      <c r="N33" s="7"/>
+    </row>
+    <row r="34" ht="16" spans="4:14">
+      <c r="D34" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="E34" s="7"/>
+      <c r="F34" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G34" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I34" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="J34">
-        <v>1</v>
-      </c>
-      <c r="K34">
+      <c r="J34" s="7">
+        <v>1</v>
+      </c>
+      <c r="K34" s="7">
         <f>K33</f>
         <v>1</v>
       </c>
-      <c r="L34">
+      <c r="L34" s="7">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" ht="16" spans="4:13">
-      <c r="D35" t="s">
+      <c r="M34" s="7">
+        <v>1</v>
+      </c>
+      <c r="N34" s="7"/>
+    </row>
+    <row r="35" ht="16" spans="4:14">
+      <c r="D35" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="E35" s="7"/>
+      <c r="F35" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="J35">
-        <v>1</v>
-      </c>
-      <c r="K35">
-        <f>K34</f>
-        <v>1</v>
-      </c>
-      <c r="L35">
+      <c r="J35" s="7">
+        <v>1</v>
+      </c>
+      <c r="K35" s="7">
+        <f t="shared" ref="K35:K43" si="3">K34</f>
+        <v>1</v>
+      </c>
+      <c r="L35" s="7">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" ht="16" spans="4:13">
-      <c r="D36" t="s">
+      <c r="M35" s="7">
+        <v>1</v>
+      </c>
+      <c r="N35" s="7"/>
+    </row>
+    <row r="36" ht="16" spans="4:14">
+      <c r="D36" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="E36" s="7"/>
+      <c r="F36" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G36" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="J36">
-        <v>1</v>
-      </c>
-      <c r="K36">
-        <f>K35</f>
-        <v>1</v>
-      </c>
-      <c r="L36">
+      <c r="J36" s="7">
+        <v>1</v>
+      </c>
+      <c r="K36" s="7">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L36" s="7">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="4:13">
-      <c r="F37" s="5"/>
-    </row>
-    <row r="38" spans="4:13">
-      <c r="F38" s="5"/>
-    </row>
-    <row r="39" spans="4:13">
-      <c r="F39" s="5"/>
-    </row>
-    <row r="40" spans="4:13">
-      <c r="F40" s="5"/>
-    </row>
-    <row r="41" spans="4:13">
-      <c r="F41" s="5"/>
-    </row>
-    <row r="42" spans="4:13">
-      <c r="F42" s="5"/>
-    </row>
-    <row r="43" spans="4:13">
-      <c r="F43" s="5"/>
-    </row>
-    <row r="44" spans="4:13">
-      <c r="F44" s="5"/>
-    </row>
-    <row r="45" spans="4:13">
-      <c r="F45" s="5"/>
-    </row>
-    <row r="46" spans="4:13">
-      <c r="F46" s="5"/>
-    </row>
-    <row r="47" spans="4:13">
-      <c r="F47" s="5"/>
-    </row>
-    <row r="48" spans="4:13">
-      <c r="F48" s="5"/>
-    </row>
-    <row r="49" spans="6:6">
-      <c r="F49" s="5"/>
-    </row>
-    <row r="50" spans="6:6">
-      <c r="F50" s="6"/>
-    </row>
-    <row r="51" spans="6:6">
-      <c r="F51" s="7"/>
-    </row>
-    <row r="52" spans="6:6">
-      <c r="F52" s="7"/>
+      <c r="M36" s="7">
+        <v>1</v>
+      </c>
+      <c r="N36" s="7"/>
+    </row>
+    <row r="37" ht="16" spans="4:14">
+      <c r="D37" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="E37" s="10"/>
+      <c r="F37" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="J37" s="10">
+        <v>1</v>
+      </c>
+      <c r="K37" s="10">
+        <v>1</v>
+      </c>
+      <c r="L37" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="M37" s="10">
+        <v>1</v>
+      </c>
+      <c r="N37" s="7"/>
+    </row>
+    <row r="38" ht="16" spans="4:14">
+      <c r="D38" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E38" s="10"/>
+      <c r="F38" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="J38" s="10">
+        <v>1</v>
+      </c>
+      <c r="K38" s="10">
+        <v>1</v>
+      </c>
+      <c r="L38" s="10">
+        <f t="shared" ref="L38:L43" si="4">L37</f>
+        <v>0.01</v>
+      </c>
+      <c r="M38" s="10">
+        <v>1</v>
+      </c>
+      <c r="N38" s="7"/>
+    </row>
+    <row r="39" ht="16" spans="4:14">
+      <c r="D39" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="E39" s="10"/>
+      <c r="F39" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="J39" s="10">
+        <v>1</v>
+      </c>
+      <c r="K39" s="10">
+        <v>1</v>
+      </c>
+      <c r="L39" s="10">
+        <f t="shared" si="4"/>
+        <v>0.01</v>
+      </c>
+      <c r="M39" s="10">
+        <v>1</v>
+      </c>
+      <c r="N39" s="7"/>
+    </row>
+    <row r="40" ht="16" spans="4:14">
+      <c r="D40" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="E40" s="10"/>
+      <c r="F40" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="J40" s="10">
+        <v>1</v>
+      </c>
+      <c r="K40" s="10">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L40" s="10">
+        <f t="shared" si="4"/>
+        <v>0.01</v>
+      </c>
+      <c r="M40" s="10">
+        <v>1</v>
+      </c>
+      <c r="N40" s="7"/>
+    </row>
+    <row r="41" ht="16" spans="4:14">
+      <c r="D41" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E41" s="10"/>
+      <c r="F41" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="J41" s="10">
+        <v>1</v>
+      </c>
+      <c r="K41" s="10">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L41" s="10">
+        <f t="shared" si="4"/>
+        <v>0.01</v>
+      </c>
+      <c r="M41" s="10">
+        <v>1</v>
+      </c>
+      <c r="N41" s="7"/>
+    </row>
+    <row r="42" ht="16" spans="4:14">
+      <c r="D42" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="E42" s="10"/>
+      <c r="F42" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="J42" s="10">
+        <v>1</v>
+      </c>
+      <c r="K42" s="10">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L42" s="10">
+        <f t="shared" si="4"/>
+        <v>0.01</v>
+      </c>
+      <c r="M42" s="10">
+        <v>1</v>
+      </c>
+      <c r="N42" s="7"/>
+    </row>
+    <row r="43" ht="16" spans="4:14">
+      <c r="D43" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E43" s="10"/>
+      <c r="F43" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="J43" s="10">
+        <v>1</v>
+      </c>
+      <c r="K43" s="10">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L43" s="10">
+        <f t="shared" si="4"/>
+        <v>0.01</v>
+      </c>
+      <c r="M43" s="10">
+        <v>1</v>
+      </c>
+      <c r="N43" s="7"/>
+    </row>
+    <row r="44" spans="4:14">
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="7"/>
+    </row>
+    <row r="45" spans="4:14">
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="7"/>
+    </row>
+    <row r="46" spans="4:14">
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
+      <c r="M46" s="7"/>
+      <c r="N46" s="7"/>
+    </row>
+    <row r="47" spans="4:14">
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
+      <c r="M47" s="7"/>
+      <c r="N47" s="7"/>
+    </row>
+    <row r="48" spans="4:14">
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
+      <c r="M48" s="7"/>
+      <c r="N48" s="7"/>
+    </row>
+    <row r="49" spans="4:14">
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+      <c r="M49" s="7"/>
+      <c r="N49" s="7"/>
+    </row>
+    <row r="50" spans="4:14">
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
+      <c r="L50" s="7"/>
+      <c r="M50" s="7"/>
+      <c r="N50" s="7"/>
+    </row>
+    <row r="51" spans="4:14">
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7"/>
+      <c r="L51" s="7"/>
+      <c r="M51" s="7"/>
+      <c r="N51" s="7"/>
+    </row>
+    <row r="52" spans="4:14">
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="7"/>
+      <c r="J52" s="7"/>
+      <c r="K52" s="7"/>
+      <c r="L52" s="7"/>
+      <c r="M52" s="7"/>
+      <c r="N52" s="7"/>
+    </row>
+    <row r="53" spans="4:14">
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="7"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="7"/>
+      <c r="J53" s="7"/>
+      <c r="K53" s="7"/>
+      <c r="L53" s="7"/>
+      <c r="M53" s="7"/>
+      <c r="N53" s="7"/>
+    </row>
+    <row r="54" spans="4:14">
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
+      <c r="K54" s="7"/>
+      <c r="L54" s="7"/>
+      <c r="M54" s="7"/>
+      <c r="N54" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="E13:U33"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="9" max="9" width="43.7272727272727" customWidth="1"/>
+    <col min="12" max="12" width="10.2727272727273" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="13" spans="5:21">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+    </row>
+    <row r="14" spans="5:21">
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+    </row>
+    <row r="15" spans="5:21">
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+    </row>
+    <row r="16" spans="5:21">
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+    </row>
+    <row r="17" spans="5:21">
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+    </row>
+    <row r="18" spans="5:21">
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+    </row>
+    <row r="19" spans="5:21">
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+    </row>
+    <row r="20" spans="5:21">
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+    </row>
+    <row r="21" spans="5:21">
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+    </row>
+    <row r="22" spans="5:21">
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+    </row>
+    <row r="23" spans="5:21">
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+    </row>
+    <row r="24" spans="5:21">
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+    </row>
+    <row r="26" spans="5:21">
+      <c r="F26" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" spans="5:21">
+      <c r="L29" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" ht="15.25" spans="5:21">
+      <c r="F30" t="s">
+        <v>60</v>
+      </c>
+      <c r="G30" t="s">
+        <v>25</v>
+      </c>
+      <c r="H30" t="s">
+        <v>48</v>
+      </c>
+      <c r="I30" t="s">
+        <v>124</v>
+      </c>
+      <c r="J30" t="s">
+        <v>33</v>
+      </c>
+      <c r="K30" t="s">
+        <v>125</v>
+      </c>
+      <c r="L30" t="s">
+        <v>1</v>
+      </c>
+      <c r="M30" t="s">
+        <v>126</v>
+      </c>
+      <c r="N30" t="s">
+        <v>127</v>
+      </c>
+      <c r="O30" t="s">
+        <v>128</v>
+      </c>
+      <c r="P30" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" ht="16" spans="5:21">
+      <c r="F31" t="s">
+        <v>130</v>
+      </c>
+      <c r="G31" t="s">
+        <v>131</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I31" t="s">
+        <v>133</v>
+      </c>
+      <c r="J31" t="s">
+        <v>17</v>
+      </c>
+      <c r="K31" t="s">
+        <v>17</v>
+      </c>
+      <c r="M31">
+        <v>-0.25</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>3</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="32" ht="15.25" spans="5:21">
+      <c r="K32" t="s">
+        <v>135</v>
+      </c>
+      <c r="N32" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="9:13">
+      <c r="I33" t="s">
+        <v>136</v>
+      </c>
+      <c r="J33" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33" t="s">
+        <v>17</v>
+      </c>
+      <c r="M33">
+        <v>-0.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -668,7 +668,7 @@
     <t>UC_RHSRTS~0</t>
   </si>
   <si>
-    <t>UCE_Min-DispatchablePrd</t>
+    <t>UCE_MaxOutput-of-gidstorage</t>
   </si>
   <si>
     <t>ELE,CHP</t>
@@ -907,6 +907,7 @@
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -917,7 +918,6 @@
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -3909,6 +3909,7 @@
   <dimension ref="E13:U33"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
+    <col min="6" max="6" width="25.0909090909091" customWidth="1"/>
     <col min="9" max="9" width="43.7272727272727" customWidth="1"/>
     <col min="12" max="12" width="10.2727272727273" customWidth="1"/>
   </cols>
@@ -4189,7 +4190,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" ht="16" spans="5:21">
+    <row r="31" spans="5:21">
       <c r="F31" t="s">
         <v>130</v>
       </c>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="6"/>
+    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
@@ -416,7 +416,7 @@
     <t>START</t>
   </si>
   <si>
-    <t>Tra_EV_Bat*virgi*</t>
+    <t>Tra_EV_Bat*virgi*, -Tra_EV_Batt-Sodium_virgin_pack, -Tra_EV_Batt-Sodium_virgin</t>
   </si>
   <si>
     <t>~TFM_AVA</t>
@@ -907,17 +907,17 @@
       <charset val="0"/>
     </font>
     <font>
-      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
-    <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -4190,7 +4190,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="5:21">
+    <row r="31" ht="16" spans="5:21">
       <c r="F31" t="s">
         <v>130</v>
       </c>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="4"/>
+    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
@@ -901,23 +901,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
-    <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -1416,7 +1416,7 @@
     <xf numFmtId="0" fontId="27" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1440,7 +1440,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2103,10 +2102,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="28"/>
+      <c r="K10" s="27"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="28"/>
+      <c r="K11" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2127,11 +2126,11 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:13">
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
       <c r="F5" s="7"/>
     </row>
     <row r="6" spans="2:13">
@@ -2147,19 +2146,19 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="18"/>
+      <c r="K6" s="17"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="18">
         <v>10</v>
       </c>
     </row>
@@ -2167,17 +2166,17 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="18">
         <v>7</v>
       </c>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
     </row>
     <row r="9" ht="16" spans="2:13">
       <c r="B9" t="s">
@@ -2186,10 +2185,10 @@
       <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="18">
         <v>10</v>
       </c>
     </row>
@@ -2197,17 +2196,17 @@
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="18">
         <v>8</v>
       </c>
-      <c r="K10" s="20"/>
-      <c r="L10" s="21"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="20"/>
     </row>
     <row r="11" ht="16" spans="2:13">
       <c r="B11" t="s">
@@ -2216,10 +2215,10 @@
       <c r="C11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="16">
         <v>1.5</v>
       </c>
     </row>
@@ -2230,10 +2229,10 @@
       <c r="C12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="16">
         <v>1.5</v>
       </c>
     </row>
@@ -2244,7 +2243,7 @@
       <c r="C13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="16" t="s">
         <v>35</v>
       </c>
       <c r="E13" s="7">
@@ -2258,7 +2257,7 @@
       <c r="C14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="16" t="s">
         <v>35</v>
       </c>
       <c r="E14" s="7">
@@ -2272,7 +2271,7 @@
       <c r="C15" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="16" t="s">
         <v>35</v>
       </c>
       <c r="E15" s="7">
@@ -2283,13 +2282,13 @@
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="21">
         <v>12</v>
       </c>
     </row>
@@ -2297,13 +2296,13 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="23" t="s">
+      <c r="D17" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="23">
         <v>0.2</v>
       </c>
       <c r="F17" s="7"/>
@@ -2312,13 +2311,13 @@
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="D18" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="23">
         <v>0.2</v>
       </c>
       <c r="F18" s="7"/>
@@ -2330,10 +2329,10 @@
       <c r="C19" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="D19" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="23">
         <v>0.2</v>
       </c>
       <c r="F19" s="7"/>
@@ -2342,13 +2341,13 @@
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="23">
         <v>0.5</v>
       </c>
       <c r="F20" s="7"/>
@@ -2360,10 +2359,10 @@
       <c r="C21" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="23" t="s">
+      <c r="D21" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="23">
         <v>0.8</v>
       </c>
       <c r="F21" s="7"/>
@@ -2375,10 +2374,10 @@
       <c r="C22" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="D22" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="17"/>
+      <c r="E22" s="16"/>
       <c r="F22" s="7"/>
     </row>
     <row r="23" spans="2:6">
@@ -2388,7 +2387,7 @@
       <c r="C23" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="23" t="s">
+      <c r="D23" s="22" t="s">
         <v>43</v>
       </c>
       <c r="E23" s="7">
@@ -2403,7 +2402,7 @@
       <c r="C24" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="D24" s="22" t="s">
         <v>43</v>
       </c>
       <c r="E24" s="7">
@@ -2418,7 +2417,7 @@
       <c r="C25" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="23" t="s">
+      <c r="D25" s="22" t="s">
         <v>43</v>
       </c>
       <c r="E25" s="7">
@@ -2430,13 +2429,13 @@
       <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="23" t="s">
+      <c r="D26" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="16">
         <v>0.05</v>
       </c>
       <c r="F26" s="7"/>
@@ -2445,13 +2444,13 @@
       <c r="B27" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="C27" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="25" t="s">
+      <c r="D27" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="25">
+      <c r="E27" s="24">
         <v>2020</v>
       </c>
       <c r="F27" s="7"/>
@@ -2460,10 +2459,10 @@
       <c r="C28" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="25" t="s">
+      <c r="D28" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="25">
         <v>2020</v>
       </c>
       <c r="F28" s="7"/>
@@ -2498,360 +2497,360 @@
       <c r="E38" s="1"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="27" t="s">
+      <c r="C54" s="26" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="27"/>
-      <c r="E56" s="27"/>
-      <c r="F56" s="27"/>
-      <c r="G56" s="27"/>
-      <c r="H56" s="27"/>
-      <c r="I56" s="27"/>
-      <c r="J56" s="27"/>
-      <c r="K56" s="27"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="26"/>
+      <c r="J56" s="26"/>
+      <c r="K56" s="26"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="27" t="s">
+      <c r="C57" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="27" t="s">
+      <c r="D57" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="27" t="s">
+      <c r="E57" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="F57" s="27" t="s">
+      <c r="F57" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="G57" s="27" t="s">
+      <c r="G57" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="27" t="s">
+      <c r="H57" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="27" t="s">
+      <c r="I57" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="J57" s="27" t="s">
+      <c r="J57" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="K57" s="27" t="s">
+      <c r="K57" s="26" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="27"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
-      <c r="H58" s="27"/>
-      <c r="I58" s="27"/>
-      <c r="J58" s="27"/>
-      <c r="K58" s="27"/>
+      <c r="C58" s="26"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="26"/>
+      <c r="J58" s="26"/>
+      <c r="K58" s="26"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="27"/>
-      <c r="D59" s="27"/>
-      <c r="E59" s="27"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
-      <c r="H59" s="27"/>
-      <c r="I59" s="27"/>
-      <c r="J59" s="27"/>
-      <c r="K59" s="27"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
+      <c r="H59" s="26"/>
+      <c r="I59" s="26"/>
+      <c r="J59" s="26"/>
+      <c r="K59" s="26"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="27"/>
-      <c r="D60" s="27"/>
-      <c r="E60" s="27"/>
-      <c r="F60" s="27"/>
-      <c r="G60" s="27"/>
-      <c r="H60" s="27"/>
-      <c r="I60" s="27"/>
-      <c r="J60" s="27"/>
-      <c r="K60" s="27"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="26"/>
+      <c r="H60" s="26"/>
+      <c r="I60" s="26"/>
+      <c r="J60" s="26"/>
+      <c r="K60" s="26"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="27"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="27"/>
-      <c r="I61" s="27"/>
-      <c r="J61" s="27"/>
-      <c r="K61" s="27"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="26"/>
+      <c r="J61" s="26"/>
+      <c r="K61" s="26"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="27"/>
-      <c r="D62" s="27"/>
-      <c r="E62" s="27"/>
-      <c r="F62" s="27"/>
-      <c r="G62" s="27"/>
-      <c r="H62" s="27"/>
-      <c r="I62" s="27"/>
-      <c r="J62" s="27"/>
-      <c r="K62" s="27"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="26"/>
+      <c r="G62" s="26"/>
+      <c r="H62" s="26"/>
+      <c r="I62" s="26"/>
+      <c r="J62" s="26"/>
+      <c r="K62" s="26"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="27"/>
-      <c r="D63" s="27"/>
-      <c r="E63" s="27"/>
-      <c r="F63" s="27"/>
-      <c r="G63" s="27"/>
-      <c r="H63" s="27"/>
-      <c r="I63" s="27"/>
-      <c r="J63" s="27"/>
-      <c r="K63" s="27"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="26"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="26"/>
+      <c r="G63" s="26"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="26"/>
+      <c r="J63" s="26"/>
+      <c r="K63" s="26"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="27"/>
-      <c r="D64" s="27"/>
-      <c r="E64" s="27"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="27"/>
-      <c r="H64" s="27"/>
-      <c r="I64" s="27"/>
-      <c r="J64" s="27"/>
-      <c r="K64" s="27"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="26"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="26"/>
+      <c r="J64" s="26"/>
+      <c r="K64" s="26"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="27"/>
-      <c r="D65" s="27"/>
-      <c r="E65" s="27"/>
-      <c r="F65" s="27"/>
-      <c r="G65" s="27"/>
-      <c r="H65" s="27"/>
-      <c r="I65" s="27"/>
-      <c r="J65" s="27"/>
-      <c r="K65" s="27"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
+      <c r="G65" s="26"/>
+      <c r="H65" s="26"/>
+      <c r="I65" s="26"/>
+      <c r="J65" s="26"/>
+      <c r="K65" s="26"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="27"/>
-      <c r="D66" s="27"/>
-      <c r="E66" s="27"/>
-      <c r="F66" s="27"/>
-      <c r="G66" s="27"/>
-      <c r="H66" s="27"/>
-      <c r="I66" s="27"/>
-      <c r="J66" s="27"/>
-      <c r="K66" s="27"/>
+      <c r="C66" s="26"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="26"/>
+      <c r="G66" s="26"/>
+      <c r="H66" s="26"/>
+      <c r="I66" s="26"/>
+      <c r="J66" s="26"/>
+      <c r="K66" s="26"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="27"/>
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="27"/>
-      <c r="H67" s="27"/>
-      <c r="I67" s="27"/>
-      <c r="J67" s="27"/>
-      <c r="K67" s="27"/>
+      <c r="C67" s="26"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
+      <c r="G67" s="26"/>
+      <c r="H67" s="26"/>
+      <c r="I67" s="26"/>
+      <c r="J67" s="26"/>
+      <c r="K67" s="26"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="27"/>
-      <c r="D68" s="27"/>
-      <c r="E68" s="27"/>
-      <c r="F68" s="27"/>
-      <c r="G68" s="27"/>
-      <c r="H68" s="27"/>
-      <c r="I68" s="27"/>
-      <c r="J68" s="27"/>
-      <c r="K68" s="27"/>
+      <c r="C68" s="26"/>
+      <c r="D68" s="26"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="26"/>
+      <c r="G68" s="26"/>
+      <c r="H68" s="26"/>
+      <c r="I68" s="26"/>
+      <c r="J68" s="26"/>
+      <c r="K68" s="26"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="27"/>
-      <c r="D69" s="27"/>
-      <c r="E69" s="27"/>
-      <c r="F69" s="27"/>
-      <c r="G69" s="27"/>
-      <c r="H69" s="27"/>
-      <c r="I69" s="27"/>
-      <c r="J69" s="27"/>
-      <c r="K69" s="27"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="26"/>
+      <c r="G69" s="26"/>
+      <c r="H69" s="26"/>
+      <c r="I69" s="26"/>
+      <c r="J69" s="26"/>
+      <c r="K69" s="26"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="27"/>
-      <c r="D70" s="27"/>
-      <c r="E70" s="27"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="27"/>
-      <c r="H70" s="27"/>
-      <c r="I70" s="27"/>
-      <c r="J70" s="27"/>
-      <c r="K70" s="27"/>
+      <c r="C70" s="26"/>
+      <c r="D70" s="26"/>
+      <c r="E70" s="26"/>
+      <c r="F70" s="26"/>
+      <c r="G70" s="26"/>
+      <c r="H70" s="26"/>
+      <c r="I70" s="26"/>
+      <c r="J70" s="26"/>
+      <c r="K70" s="26"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="27"/>
-      <c r="D71" s="27"/>
-      <c r="E71" s="27"/>
-      <c r="F71" s="27"/>
-      <c r="G71" s="27"/>
-      <c r="H71" s="27"/>
-      <c r="I71" s="27"/>
-      <c r="J71" s="27"/>
-      <c r="K71" s="27"/>
+      <c r="C71" s="26"/>
+      <c r="D71" s="26"/>
+      <c r="E71" s="26"/>
+      <c r="F71" s="26"/>
+      <c r="G71" s="26"/>
+      <c r="H71" s="26"/>
+      <c r="I71" s="26"/>
+      <c r="J71" s="26"/>
+      <c r="K71" s="26"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="27"/>
-      <c r="D72" s="27"/>
-      <c r="E72" s="27"/>
-      <c r="F72" s="27"/>
-      <c r="G72" s="27"/>
-      <c r="H72" s="27"/>
-      <c r="I72" s="27"/>
-      <c r="J72" s="27"/>
-      <c r="K72" s="27"/>
+      <c r="C72" s="26"/>
+      <c r="D72" s="26"/>
+      <c r="E72" s="26"/>
+      <c r="F72" s="26"/>
+      <c r="G72" s="26"/>
+      <c r="H72" s="26"/>
+      <c r="I72" s="26"/>
+      <c r="J72" s="26"/>
+      <c r="K72" s="26"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="27"/>
-      <c r="D73" s="27"/>
-      <c r="E73" s="27"/>
-      <c r="F73" s="27"/>
-      <c r="G73" s="27"/>
-      <c r="H73" s="27"/>
-      <c r="I73" s="27"/>
-      <c r="J73" s="27"/>
-      <c r="K73" s="27"/>
+      <c r="C73" s="26"/>
+      <c r="D73" s="26"/>
+      <c r="E73" s="26"/>
+      <c r="F73" s="26"/>
+      <c r="G73" s="26"/>
+      <c r="H73" s="26"/>
+      <c r="I73" s="26"/>
+      <c r="J73" s="26"/>
+      <c r="K73" s="26"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="27"/>
-      <c r="D74" s="27"/>
-      <c r="E74" s="27"/>
-      <c r="F74" s="27"/>
-      <c r="G74" s="27"/>
-      <c r="H74" s="27"/>
-      <c r="I74" s="27"/>
-      <c r="J74" s="27"/>
-      <c r="K74" s="27"/>
+      <c r="C74" s="26"/>
+      <c r="D74" s="26"/>
+      <c r="E74" s="26"/>
+      <c r="F74" s="26"/>
+      <c r="G74" s="26"/>
+      <c r="H74" s="26"/>
+      <c r="I74" s="26"/>
+      <c r="J74" s="26"/>
+      <c r="K74" s="26"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="27"/>
-      <c r="D75" s="27"/>
-      <c r="E75" s="27"/>
-      <c r="F75" s="27"/>
-      <c r="G75" s="27"/>
-      <c r="H75" s="27"/>
-      <c r="I75" s="27"/>
-      <c r="J75" s="27"/>
-      <c r="K75" s="27"/>
+      <c r="C75" s="26"/>
+      <c r="D75" s="26"/>
+      <c r="E75" s="26"/>
+      <c r="F75" s="26"/>
+      <c r="G75" s="26"/>
+      <c r="H75" s="26"/>
+      <c r="I75" s="26"/>
+      <c r="J75" s="26"/>
+      <c r="K75" s="26"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="27"/>
-      <c r="D76" s="27"/>
-      <c r="E76" s="27"/>
-      <c r="F76" s="27"/>
-      <c r="G76" s="27"/>
-      <c r="H76" s="27"/>
-      <c r="I76" s="27"/>
-      <c r="J76" s="27"/>
-      <c r="K76" s="27"/>
+      <c r="C76" s="26"/>
+      <c r="D76" s="26"/>
+      <c r="E76" s="26"/>
+      <c r="F76" s="26"/>
+      <c r="G76" s="26"/>
+      <c r="H76" s="26"/>
+      <c r="I76" s="26"/>
+      <c r="J76" s="26"/>
+      <c r="K76" s="26"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="27"/>
-      <c r="D77" s="27"/>
-      <c r="E77" s="27"/>
-      <c r="F77" s="27"/>
-      <c r="G77" s="27"/>
-      <c r="H77" s="27"/>
-      <c r="I77" s="27"/>
-      <c r="J77" s="27"/>
-      <c r="K77" s="27"/>
+      <c r="C77" s="26"/>
+      <c r="D77" s="26"/>
+      <c r="E77" s="26"/>
+      <c r="F77" s="26"/>
+      <c r="G77" s="26"/>
+      <c r="H77" s="26"/>
+      <c r="I77" s="26"/>
+      <c r="J77" s="26"/>
+      <c r="K77" s="26"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="27"/>
-      <c r="D78" s="27"/>
-      <c r="E78" s="27"/>
-      <c r="F78" s="27"/>
-      <c r="G78" s="27"/>
-      <c r="H78" s="27"/>
-      <c r="I78" s="27"/>
-      <c r="J78" s="27"/>
-      <c r="K78" s="27"/>
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
+      <c r="H78" s="26"/>
+      <c r="I78" s="26"/>
+      <c r="J78" s="26"/>
+      <c r="K78" s="26"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="27"/>
-      <c r="D79" s="27"/>
-      <c r="E79" s="27"/>
-      <c r="F79" s="27"/>
-      <c r="G79" s="27"/>
-      <c r="H79" s="27"/>
-      <c r="I79" s="27"/>
-      <c r="J79" s="27"/>
-      <c r="K79" s="27"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="26"/>
+      <c r="E79" s="26"/>
+      <c r="F79" s="26"/>
+      <c r="G79" s="26"/>
+      <c r="H79" s="26"/>
+      <c r="I79" s="26"/>
+      <c r="J79" s="26"/>
+      <c r="K79" s="26"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="27"/>
-      <c r="D80" s="27"/>
-      <c r="E80" s="27"/>
-      <c r="F80" s="27"/>
-      <c r="G80" s="27"/>
-      <c r="H80" s="27"/>
-      <c r="I80" s="27"/>
-      <c r="J80" s="27"/>
-      <c r="K80" s="27"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="26"/>
+      <c r="K80" s="26"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="27"/>
-      <c r="D81" s="27"/>
-      <c r="E81" s="27"/>
-      <c r="F81" s="27"/>
-      <c r="G81" s="27"/>
-      <c r="H81" s="27"/>
-      <c r="I81" s="27"/>
-      <c r="J81" s="27"/>
-      <c r="K81" s="27"/>
+      <c r="C81" s="26"/>
+      <c r="D81" s="26"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="26"/>
+      <c r="G81" s="26"/>
+      <c r="H81" s="26"/>
+      <c r="I81" s="26"/>
+      <c r="J81" s="26"/>
+      <c r="K81" s="26"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="27"/>
-      <c r="D82" s="27"/>
-      <c r="E82" s="27"/>
-      <c r="F82" s="27"/>
-      <c r="G82" s="27"/>
-      <c r="H82" s="27"/>
-      <c r="I82" s="27"/>
-      <c r="J82" s="27"/>
-      <c r="K82" s="27"/>
+      <c r="C82" s="26"/>
+      <c r="D82" s="26"/>
+      <c r="E82" s="26"/>
+      <c r="F82" s="26"/>
+      <c r="G82" s="26"/>
+      <c r="H82" s="26"/>
+      <c r="I82" s="26"/>
+      <c r="J82" s="26"/>
+      <c r="K82" s="26"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="27"/>
-      <c r="D83" s="27"/>
-      <c r="E83" s="27"/>
-      <c r="F83" s="27"/>
-      <c r="G83" s="27"/>
-      <c r="H83" s="27"/>
-      <c r="I83" s="27"/>
-      <c r="J83" s="27"/>
-      <c r="K83" s="27"/>
+      <c r="C83" s="26"/>
+      <c r="D83" s="26"/>
+      <c r="E83" s="26"/>
+      <c r="F83" s="26"/>
+      <c r="G83" s="26"/>
+      <c r="H83" s="26"/>
+      <c r="I83" s="26"/>
+      <c r="J83" s="26"/>
+      <c r="K83" s="26"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="27" t="s">
+      <c r="C84" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D84" s="27">
-        <v>1</v>
-      </c>
-      <c r="E84" s="27"/>
-      <c r="F84" s="27"/>
-      <c r="G84" s="27"/>
-      <c r="H84" s="27"/>
-      <c r="I84" s="27"/>
-      <c r="J84" s="27"/>
-      <c r="K84" s="27"/>
+      <c r="D84" s="26">
+        <v>1</v>
+      </c>
+      <c r="E84" s="26"/>
+      <c r="F84" s="26"/>
+      <c r="G84" s="26"/>
+      <c r="H84" s="26"/>
+      <c r="I84" s="26"/>
+      <c r="J84" s="26"/>
+      <c r="K84" s="26"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="27"/>
-      <c r="D85" s="27"/>
-      <c r="E85" s="27"/>
-      <c r="F85" s="27"/>
-      <c r="G85" s="27"/>
-      <c r="H85" s="27"/>
-      <c r="I85" s="27"/>
-      <c r="J85" s="27"/>
-      <c r="K85" s="27"/>
+      <c r="C85" s="26"/>
+      <c r="D85" s="26"/>
+      <c r="E85" s="26"/>
+      <c r="F85" s="26"/>
+      <c r="G85" s="26"/>
+      <c r="H85" s="26"/>
+      <c r="I85" s="26"/>
+      <c r="J85" s="26"/>
+      <c r="K85" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3482,7 +3481,7 @@
         <v>1</v>
       </c>
       <c r="K35" s="7">
-        <f t="shared" ref="K35:K43" si="3">K34</f>
+        <f>K34</f>
         <v>1</v>
       </c>
       <c r="L35" s="7">
@@ -3515,7 +3514,7 @@
         <v>1</v>
       </c>
       <c r="K36" s="7">
-        <f t="shared" si="3"/>
+        <f>K35</f>
         <v>1</v>
       </c>
       <c r="L36" s="7">
@@ -3527,207 +3526,31 @@
       </c>
       <c r="N36" s="7"/>
     </row>
-    <row r="37" ht="16" spans="4:14">
-      <c r="D37" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="E37" s="10"/>
-      <c r="F37" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G37" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="J37" s="10">
-        <v>1</v>
-      </c>
-      <c r="K37" s="10">
-        <v>1</v>
-      </c>
-      <c r="L37" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="M37" s="10">
-        <v>1</v>
-      </c>
+    <row r="37" spans="4:14">
       <c r="N37" s="7"/>
     </row>
-    <row r="38" ht="16" spans="4:14">
-      <c r="D38" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="E38" s="10"/>
-      <c r="F38" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G38" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="J38" s="10">
-        <v>1</v>
-      </c>
-      <c r="K38" s="10">
-        <v>1</v>
-      </c>
-      <c r="L38" s="10">
-        <f t="shared" ref="L38:L43" si="4">L37</f>
-        <v>0.01</v>
-      </c>
-      <c r="M38" s="10">
-        <v>1</v>
-      </c>
+    <row r="38" spans="4:14">
       <c r="N38" s="7"/>
     </row>
-    <row r="39" ht="16" spans="4:14">
-      <c r="D39" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="E39" s="10"/>
-      <c r="F39" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="J39" s="10">
-        <v>1</v>
-      </c>
-      <c r="K39" s="10">
-        <v>1</v>
-      </c>
-      <c r="L39" s="10">
-        <f t="shared" si="4"/>
-        <v>0.01</v>
-      </c>
-      <c r="M39" s="10">
-        <v>1</v>
-      </c>
+    <row r="39" spans="4:14">
       <c r="N39" s="7"/>
     </row>
-    <row r="40" ht="16" spans="4:14">
-      <c r="D40" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E40" s="10"/>
-      <c r="F40" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="J40" s="10">
-        <v>1</v>
-      </c>
-      <c r="K40" s="10">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L40" s="10">
-        <f t="shared" si="4"/>
-        <v>0.01</v>
-      </c>
-      <c r="M40" s="10">
-        <v>1</v>
-      </c>
+    <row r="40" spans="4:14">
       <c r="N40" s="7"/>
     </row>
-    <row r="41" ht="16" spans="4:14">
-      <c r="D41" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="E41" s="10"/>
-      <c r="F41" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="I41" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="J41" s="10">
-        <v>1</v>
-      </c>
-      <c r="K41" s="10">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L41" s="10">
-        <f t="shared" si="4"/>
-        <v>0.01</v>
-      </c>
-      <c r="M41" s="10">
-        <v>1</v>
-      </c>
+    <row r="41" spans="4:14">
       <c r="N41" s="7"/>
     </row>
-    <row r="42" ht="16" spans="4:14">
-      <c r="D42" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="E42" s="10"/>
-      <c r="F42" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="I42" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="J42" s="10">
-        <v>1</v>
-      </c>
-      <c r="K42" s="10">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L42" s="10">
-        <f t="shared" si="4"/>
-        <v>0.01</v>
-      </c>
-      <c r="M42" s="10">
-        <v>1</v>
-      </c>
+    <row r="42" spans="4:14">
       <c r="N42" s="7"/>
     </row>
     <row r="43" ht="16" spans="4:14">
       <c r="D43" s="10" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="E43" s="10"/>
-      <c r="F43" s="13" t="s">
-        <v>121</v>
+      <c r="F43" s="11" t="s">
+        <v>108</v>
       </c>
       <c r="G43" s="10" t="s">
         <v>70</v>
@@ -3742,126 +3565,242 @@
         <v>1</v>
       </c>
       <c r="K43" s="10">
+        <v>1</v>
+      </c>
+      <c r="L43" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="M43" s="10">
+        <v>1</v>
+      </c>
+      <c r="N43" s="7"/>
+    </row>
+    <row r="44" ht="16" spans="4:14">
+      <c r="D44" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E44" s="10"/>
+      <c r="F44" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="J44" s="10">
+        <v>1</v>
+      </c>
+      <c r="K44" s="10">
+        <v>1</v>
+      </c>
+      <c r="L44" s="10">
+        <f t="shared" ref="L44:L49" si="3">L43</f>
+        <v>0.01</v>
+      </c>
+      <c r="M44" s="10">
+        <v>1</v>
+      </c>
+      <c r="N44" s="7"/>
+    </row>
+    <row r="45" ht="16" spans="4:14">
+      <c r="D45" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="E45" s="10"/>
+      <c r="F45" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="J45" s="10">
+        <v>1</v>
+      </c>
+      <c r="K45" s="10">
+        <v>1</v>
+      </c>
+      <c r="L45" s="10">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L43" s="10">
-        <f t="shared" si="4"/>
         <v>0.01</v>
       </c>
-      <c r="M43" s="10">
-        <v>1</v>
-      </c>
-      <c r="N43" s="7"/>
-    </row>
-    <row r="44" spans="4:14">
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="7"/>
-    </row>
-    <row r="45" spans="4:14">
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
+      <c r="M45" s="10">
+        <v>1</v>
+      </c>
       <c r="N45" s="7"/>
     </row>
-    <row r="46" spans="4:14">
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
+    <row r="46" ht="16" spans="4:14">
+      <c r="D46" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="E46" s="10"/>
+      <c r="F46" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="J46" s="10">
+        <v>1</v>
+      </c>
+      <c r="K46" s="10">
+        <f>K45</f>
+        <v>1</v>
+      </c>
+      <c r="L46" s="10">
+        <f t="shared" si="3"/>
+        <v>0.01</v>
+      </c>
+      <c r="M46" s="10">
+        <v>1</v>
+      </c>
       <c r="N46" s="7"/>
     </row>
-    <row r="47" spans="4:14">
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="7"/>
+    <row r="47" ht="16" spans="4:14">
+      <c r="D47" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E47" s="10"/>
+      <c r="F47" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="J47" s="10">
+        <v>1</v>
+      </c>
+      <c r="K47" s="10">
+        <f>K46</f>
+        <v>1</v>
+      </c>
+      <c r="L47" s="10">
+        <f t="shared" si="3"/>
+        <v>0.01</v>
+      </c>
+      <c r="M47" s="10">
+        <v>1</v>
+      </c>
       <c r="N47" s="7"/>
     </row>
-    <row r="48" spans="4:14">
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
+    <row r="48" ht="16" spans="4:14">
+      <c r="D48" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="E48" s="10"/>
+      <c r="F48" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="J48" s="10">
+        <v>1</v>
+      </c>
+      <c r="K48" s="10">
+        <f>K47</f>
+        <v>1</v>
+      </c>
+      <c r="L48" s="10">
+        <f t="shared" si="3"/>
+        <v>0.01</v>
+      </c>
+      <c r="M48" s="10">
+        <v>1</v>
+      </c>
       <c r="N48" s="7"/>
     </row>
-    <row r="49" spans="4:14">
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
+    <row r="49" ht="16" spans="4:14">
+      <c r="D49" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E49" s="10"/>
+      <c r="F49" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="I49" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="J49" s="10">
+        <v>1</v>
+      </c>
+      <c r="K49" s="10">
+        <f>K48</f>
+        <v>1</v>
+      </c>
+      <c r="L49" s="10">
+        <f t="shared" si="3"/>
+        <v>0.01</v>
+      </c>
+      <c r="M49" s="10">
+        <v>1</v>
+      </c>
       <c r="N49" s="7"/>
     </row>
     <row r="50" spans="4:14">
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="10"/>
+      <c r="J50" s="10"/>
+      <c r="K50" s="10"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
       <c r="N50" s="7"/>
     </row>
     <row r="51" spans="4:14">
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
       <c r="N51" s="7"/>
     </row>
     <row r="52" spans="4:14">
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
-      <c r="F52" s="16"/>
+      <c r="F52" s="15"/>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
       <c r="I52" s="7"/>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="5"/>
+    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
@@ -276,7 +276,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="135">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -642,12 +642,6 @@
   </si>
   <si>
     <t>EN_STG_4hBatt_NMC811</t>
-  </si>
-  <si>
-    <t>~UC_Sets: R_E: AllRegions</t>
-  </si>
-  <si>
-    <t>~UC_T: UP</t>
   </si>
   <si>
     <t>Pset_CI</t>
@@ -901,12 +895,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -4081,15 +4075,8 @@
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
     </row>
-    <row r="26" spans="5:21">
-      <c r="F26" t="s">
-        <v>122</v>
-      </c>
-    </row>
     <row r="29" spans="5:21">
-      <c r="L29" s="2" t="s">
-        <v>123</v>
-      </c>
+      <c r="L29" s="2"/>
     </row>
     <row r="30" ht="15.25" spans="5:21">
       <c r="F30" t="s">
@@ -4102,28 +4089,28 @@
         <v>48</v>
       </c>
       <c r="I30" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J30" t="s">
         <v>33</v>
       </c>
       <c r="K30" t="s">
+        <v>123</v>
+      </c>
+      <c r="L30" t="s">
+        <v>1</v>
+      </c>
+      <c r="M30" t="s">
+        <v>124</v>
+      </c>
+      <c r="N30" t="s">
         <v>125</v>
       </c>
-      <c r="L30" t="s">
-        <v>1</v>
-      </c>
-      <c r="M30" t="s">
+      <c r="O30" t="s">
         <v>126</v>
       </c>
-      <c r="N30" t="s">
+      <c r="P30" t="s">
         <v>127</v>
-      </c>
-      <c r="O30" t="s">
-        <v>128</v>
-      </c>
-      <c r="P30" t="s">
-        <v>129</v>
       </c>
       <c r="Q30" t="s">
         <v>67</v>
@@ -4131,16 +4118,16 @@
     </row>
     <row r="31" ht="16" spans="5:21">
       <c r="F31" t="s">
+        <v>128</v>
+      </c>
+      <c r="G31" t="s">
+        <v>129</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G31" t="s">
+      <c r="I31" t="s">
         <v>131</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="I31" t="s">
-        <v>133</v>
       </c>
       <c r="J31" t="s">
         <v>17</v>
@@ -4158,12 +4145,12 @@
         <v>3</v>
       </c>
       <c r="Q31" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" ht="15.25" spans="5:21">
       <c r="K32" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N32" s="2">
         <v>1</v>
@@ -4171,7 +4158,7 @@
     </row>
     <row r="33" spans="9:13">
       <c r="I33" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J33" t="s">
         <v>17</v>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -12,8 +12,9 @@
     <sheet name="Sheet9" sheetId="9" r:id="rId3"/>
     <sheet name="ROR_has_no_regulation_cap" sheetId="10" r:id="rId4"/>
     <sheet name="Ramp_rate_constraints" sheetId="11" r:id="rId5"/>
-    <sheet name="Growth_rate" sheetId="12" r:id="rId6"/>
-    <sheet name="Peak_demand_limit_battery" sheetId="13" r:id="rId7"/>
+    <sheet name="Peak_demand_limit_battery" sheetId="13" r:id="rId6"/>
+    <sheet name="Growth_rate" sheetId="12" r:id="rId7"/>
+    <sheet name="util_limit" sheetId="14" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="IQ_FWD_Q" hidden="1">501</definedName>
@@ -276,7 +277,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="148">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -449,6 +450,51 @@
     <t>ENCAN01_SMR</t>
   </si>
   <si>
+    <t>UC_N</t>
+  </si>
+  <si>
+    <t>Pset_CI</t>
+  </si>
+  <si>
+    <t>Cset_CN</t>
+  </si>
+  <si>
+    <t>UC_FLO</t>
+  </si>
+  <si>
+    <t>UC_COMPRD</t>
+  </si>
+  <si>
+    <t>UC_RHSRTS</t>
+  </si>
+  <si>
+    <t>UC_RHSRTS~0</t>
+  </si>
+  <si>
+    <t>UC_Desc</t>
+  </si>
+  <si>
+    <t>UCE_MaxOutput-of-gidstorage</t>
+  </si>
+  <si>
+    <t>ELE,CHP</t>
+  </si>
+  <si>
+    <t>E*</t>
+  </si>
+  <si>
+    <t>ELCSPV</t>
+  </si>
+  <si>
+    <t>Discharge of batteries should lower than a level</t>
+  </si>
+  <si>
+    <t>AuxStoOUT</t>
+  </si>
+  <si>
+    <t>ELCWIN</t>
+  </si>
+  <si>
     <t>~UC_Sets: R_S: AllRegions</t>
   </si>
   <si>
@@ -458,9 +504,6 @@
     <t>~UC_T</t>
   </si>
   <si>
-    <t>UC_N</t>
-  </si>
-  <si>
     <t>Pset_Set</t>
   </si>
   <si>
@@ -479,9 +522,6 @@
     <t>UC_RHSTS~0</t>
   </si>
   <si>
-    <t>UC_Desc</t>
-  </si>
-  <si>
     <t>UC_Grow_LI</t>
   </si>
   <si>
@@ -644,43 +684,43 @@
     <t>EN_STG_4hBatt_NMC811</t>
   </si>
   <si>
-    <t>Pset_CI</t>
-  </si>
-  <si>
-    <t>Cset_CN</t>
-  </si>
-  <si>
-    <t>UC_FLO</t>
-  </si>
-  <si>
-    <t>UC_COMPRD</t>
-  </si>
-  <si>
-    <t>UC_RHSRTS</t>
-  </si>
-  <si>
-    <t>UC_RHSRTS~0</t>
-  </si>
-  <si>
-    <t>UCE_MaxOutput-of-gidstorage</t>
-  </si>
-  <si>
-    <t>ELE,CHP</t>
-  </si>
-  <si>
-    <t>E*</t>
-  </si>
-  <si>
-    <t>ELCSPV</t>
-  </si>
-  <si>
-    <t>Discharge of batteries should lower than a level</t>
-  </si>
-  <si>
-    <t>AuxStoOUT</t>
-  </si>
-  <si>
-    <t>ELCWIN</t>
+    <t>~UC_Sets: R_E: AllRegions</t>
+  </si>
+  <si>
+    <t>~UC_T: LO</t>
+  </si>
+  <si>
+    <t>UC_RHSRT</t>
+  </si>
+  <si>
+    <t>UC_RHSRT~0</t>
+  </si>
+  <si>
+    <t>UCE_MaxUtility_scale</t>
+  </si>
+  <si>
+    <t>Tra_E*fromrecy, Tra_EV_Bat*virgin_pack</t>
+  </si>
+  <si>
+    <t>Util_Rep_B*</t>
+  </si>
+  <si>
+    <t>UCE_2</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-LFP_fromrecy, Tra_EV_Batt-LFP_virgin_pack</t>
+  </si>
+  <si>
+    <t>Tra_E*fromrecy, Tra_EV_Bat*virgin_pack, -Tra_EV_Batt-LFP_fromrecy, -Tra_EV_Batt-LFP_virgin_pack</t>
+  </si>
+  <si>
+    <t>UCE_3</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt, Util_Rep_Batt-LFP</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt*, Util_Rep_Bat*, -EN_STG_4hBatt, -Util_Rep_Batt-LFP</t>
   </si>
 </sst>
 </file>
@@ -702,18 +742,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10.2"/>
+      <color rgb="FF212529"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.2"/>
-      <color rgb="FF212529"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -895,6 +935,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
@@ -911,11 +956,6 @@
       <name val="Tahoma"/>
       <charset val="0"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="0"/>
-    </font>
   </fonts>
   <fills count="38">
     <fill>
@@ -926,12 +966,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -939,6 +973,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1410,43 +1450,46 @@
     <xf numFmtId="0" fontId="27" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -1982,7 +2025,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="18">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -2096,10 +2139,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="27"/>
+      <c r="K10" s="30"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="27"/>
+      <c r="K11" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2123,8 +2166,8 @@
       <c r="C5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
       <c r="F5" s="7"/>
     </row>
     <row r="6" spans="2:13">
@@ -2140,19 +2183,19 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="17"/>
+      <c r="K6" s="20"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="21">
         <v>10</v>
       </c>
     </row>
@@ -2160,17 +2203,17 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="21">
         <v>7</v>
       </c>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
     </row>
     <row r="9" ht="16" spans="2:13">
       <c r="B9" t="s">
@@ -2179,10 +2222,10 @@
       <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="21">
         <v>10</v>
       </c>
     </row>
@@ -2190,17 +2233,17 @@
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="21">
         <v>8</v>
       </c>
-      <c r="K10" s="19"/>
-      <c r="L10" s="20"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="23"/>
     </row>
     <row r="11" ht="16" spans="2:13">
       <c r="B11" t="s">
@@ -2209,10 +2252,10 @@
       <c r="C11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="19">
         <v>1.5</v>
       </c>
     </row>
@@ -2223,10 +2266,10 @@
       <c r="C12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="19">
         <v>1.5</v>
       </c>
     </row>
@@ -2237,7 +2280,7 @@
       <c r="C13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="19" t="s">
         <v>35</v>
       </c>
       <c r="E13" s="7">
@@ -2251,7 +2294,7 @@
       <c r="C14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="19" t="s">
         <v>35</v>
       </c>
       <c r="E14" s="7">
@@ -2265,7 +2308,7 @@
       <c r="C15" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="19" t="s">
         <v>35</v>
       </c>
       <c r="E15" s="7">
@@ -2276,13 +2319,13 @@
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="24">
         <v>12</v>
       </c>
     </row>
@@ -2290,13 +2333,13 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="26">
         <v>0.2</v>
       </c>
       <c r="F17" s="7"/>
@@ -2305,13 +2348,13 @@
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="26">
         <v>0.2</v>
       </c>
       <c r="F18" s="7"/>
@@ -2323,10 +2366,10 @@
       <c r="C19" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="D19" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="26">
         <v>0.2</v>
       </c>
       <c r="F19" s="7"/>
@@ -2335,13 +2378,13 @@
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="26">
         <v>0.5</v>
       </c>
       <c r="F20" s="7"/>
@@ -2353,10 +2396,10 @@
       <c r="C21" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="26">
         <v>0.8</v>
       </c>
       <c r="F21" s="7"/>
@@ -2368,10 +2411,10 @@
       <c r="C22" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="16"/>
+      <c r="E22" s="19"/>
       <c r="F22" s="7"/>
     </row>
     <row r="23" spans="2:6">
@@ -2381,7 +2424,7 @@
       <c r="C23" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="25" t="s">
         <v>43</v>
       </c>
       <c r="E23" s="7">
@@ -2396,7 +2439,7 @@
       <c r="C24" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="25" t="s">
         <v>43</v>
       </c>
       <c r="E24" s="7">
@@ -2411,7 +2454,7 @@
       <c r="C25" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="D25" s="25" t="s">
         <v>43</v>
       </c>
       <c r="E25" s="7">
@@ -2423,28 +2466,28 @@
       <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="D26" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="19">
         <v>0.05</v>
       </c>
       <c r="F26" s="7"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="24" t="s">
+      <c r="D27" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="27">
         <v>2020</v>
       </c>
       <c r="F27" s="7"/>
@@ -2453,10 +2496,10 @@
       <c r="C28" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="24" t="s">
+      <c r="D28" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="25">
+      <c r="E28" s="28">
         <v>2020</v>
       </c>
       <c r="F28" s="7"/>
@@ -2486,365 +2529,365 @@
       <c r="F32" s="7"/>
     </row>
     <row r="38" spans="3:5">
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="26" t="s">
+      <c r="C54" s="29" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="26"/>
-      <c r="E56" s="26"/>
-      <c r="F56" s="26"/>
-      <c r="G56" s="26"/>
-      <c r="H56" s="26"/>
-      <c r="I56" s="26"/>
-      <c r="J56" s="26"/>
-      <c r="K56" s="26"/>
+      <c r="D56" s="29"/>
+      <c r="E56" s="29"/>
+      <c r="F56" s="29"/>
+      <c r="G56" s="29"/>
+      <c r="H56" s="29"/>
+      <c r="I56" s="29"/>
+      <c r="J56" s="29"/>
+      <c r="K56" s="29"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="26" t="s">
+      <c r="C57" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="26" t="s">
+      <c r="D57" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="26" t="s">
+      <c r="E57" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="F57" s="26" t="s">
+      <c r="F57" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="G57" s="26" t="s">
+      <c r="G57" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="26" t="s">
+      <c r="H57" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="26" t="s">
+      <c r="I57" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="J57" s="26" t="s">
+      <c r="J57" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="K57" s="26" t="s">
+      <c r="K57" s="29" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="26"/>
-      <c r="D58" s="26"/>
-      <c r="E58" s="26"/>
-      <c r="F58" s="26"/>
-      <c r="G58" s="26"/>
-      <c r="H58" s="26"/>
-      <c r="I58" s="26"/>
-      <c r="J58" s="26"/>
-      <c r="K58" s="26"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="29"/>
+      <c r="E58" s="29"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="29"/>
+      <c r="H58" s="29"/>
+      <c r="I58" s="29"/>
+      <c r="J58" s="29"/>
+      <c r="K58" s="29"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="26"/>
-      <c r="D59" s="26"/>
-      <c r="E59" s="26"/>
-      <c r="F59" s="26"/>
-      <c r="G59" s="26"/>
-      <c r="H59" s="26"/>
-      <c r="I59" s="26"/>
-      <c r="J59" s="26"/>
-      <c r="K59" s="26"/>
+      <c r="C59" s="29"/>
+      <c r="D59" s="29"/>
+      <c r="E59" s="29"/>
+      <c r="F59" s="29"/>
+      <c r="G59" s="29"/>
+      <c r="H59" s="29"/>
+      <c r="I59" s="29"/>
+      <c r="J59" s="29"/>
+      <c r="K59" s="29"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="26"/>
-      <c r="D60" s="26"/>
-      <c r="E60" s="26"/>
-      <c r="F60" s="26"/>
-      <c r="G60" s="26"/>
-      <c r="H60" s="26"/>
-      <c r="I60" s="26"/>
-      <c r="J60" s="26"/>
-      <c r="K60" s="26"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="29"/>
+      <c r="E60" s="29"/>
+      <c r="F60" s="29"/>
+      <c r="G60" s="29"/>
+      <c r="H60" s="29"/>
+      <c r="I60" s="29"/>
+      <c r="J60" s="29"/>
+      <c r="K60" s="29"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="26"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26"/>
-      <c r="H61" s="26"/>
-      <c r="I61" s="26"/>
-      <c r="J61" s="26"/>
-      <c r="K61" s="26"/>
+      <c r="C61" s="29"/>
+      <c r="D61" s="29"/>
+      <c r="E61" s="29"/>
+      <c r="F61" s="29"/>
+      <c r="G61" s="29"/>
+      <c r="H61" s="29"/>
+      <c r="I61" s="29"/>
+      <c r="J61" s="29"/>
+      <c r="K61" s="29"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="26"/>
-      <c r="D62" s="26"/>
-      <c r="E62" s="26"/>
-      <c r="F62" s="26"/>
-      <c r="G62" s="26"/>
-      <c r="H62" s="26"/>
-      <c r="I62" s="26"/>
-      <c r="J62" s="26"/>
-      <c r="K62" s="26"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="29"/>
+      <c r="E62" s="29"/>
+      <c r="F62" s="29"/>
+      <c r="G62" s="29"/>
+      <c r="H62" s="29"/>
+      <c r="I62" s="29"/>
+      <c r="J62" s="29"/>
+      <c r="K62" s="29"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="26"/>
-      <c r="D63" s="26"/>
-      <c r="E63" s="26"/>
-      <c r="F63" s="26"/>
-      <c r="G63" s="26"/>
-      <c r="H63" s="26"/>
-      <c r="I63" s="26"/>
-      <c r="J63" s="26"/>
-      <c r="K63" s="26"/>
+      <c r="C63" s="29"/>
+      <c r="D63" s="29"/>
+      <c r="E63" s="29"/>
+      <c r="F63" s="29"/>
+      <c r="G63" s="29"/>
+      <c r="H63" s="29"/>
+      <c r="I63" s="29"/>
+      <c r="J63" s="29"/>
+      <c r="K63" s="29"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="26"/>
-      <c r="D64" s="26"/>
-      <c r="E64" s="26"/>
-      <c r="F64" s="26"/>
-      <c r="G64" s="26"/>
-      <c r="H64" s="26"/>
-      <c r="I64" s="26"/>
-      <c r="J64" s="26"/>
-      <c r="K64" s="26"/>
+      <c r="C64" s="29"/>
+      <c r="D64" s="29"/>
+      <c r="E64" s="29"/>
+      <c r="F64" s="29"/>
+      <c r="G64" s="29"/>
+      <c r="H64" s="29"/>
+      <c r="I64" s="29"/>
+      <c r="J64" s="29"/>
+      <c r="K64" s="29"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="26"/>
-      <c r="D65" s="26"/>
-      <c r="E65" s="26"/>
-      <c r="F65" s="26"/>
-      <c r="G65" s="26"/>
-      <c r="H65" s="26"/>
-      <c r="I65" s="26"/>
-      <c r="J65" s="26"/>
-      <c r="K65" s="26"/>
+      <c r="C65" s="29"/>
+      <c r="D65" s="29"/>
+      <c r="E65" s="29"/>
+      <c r="F65" s="29"/>
+      <c r="G65" s="29"/>
+      <c r="H65" s="29"/>
+      <c r="I65" s="29"/>
+      <c r="J65" s="29"/>
+      <c r="K65" s="29"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="26"/>
-      <c r="D66" s="26"/>
-      <c r="E66" s="26"/>
-      <c r="F66" s="26"/>
-      <c r="G66" s="26"/>
-      <c r="H66" s="26"/>
-      <c r="I66" s="26"/>
-      <c r="J66" s="26"/>
-      <c r="K66" s="26"/>
+      <c r="C66" s="29"/>
+      <c r="D66" s="29"/>
+      <c r="E66" s="29"/>
+      <c r="F66" s="29"/>
+      <c r="G66" s="29"/>
+      <c r="H66" s="29"/>
+      <c r="I66" s="29"/>
+      <c r="J66" s="29"/>
+      <c r="K66" s="29"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="26"/>
-      <c r="D67" s="26"/>
-      <c r="E67" s="26"/>
-      <c r="F67" s="26"/>
-      <c r="G67" s="26"/>
-      <c r="H67" s="26"/>
-      <c r="I67" s="26"/>
-      <c r="J67" s="26"/>
-      <c r="K67" s="26"/>
+      <c r="C67" s="29"/>
+      <c r="D67" s="29"/>
+      <c r="E67" s="29"/>
+      <c r="F67" s="29"/>
+      <c r="G67" s="29"/>
+      <c r="H67" s="29"/>
+      <c r="I67" s="29"/>
+      <c r="J67" s="29"/>
+      <c r="K67" s="29"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="26"/>
-      <c r="D68" s="26"/>
-      <c r="E68" s="26"/>
-      <c r="F68" s="26"/>
-      <c r="G68" s="26"/>
-      <c r="H68" s="26"/>
-      <c r="I68" s="26"/>
-      <c r="J68" s="26"/>
-      <c r="K68" s="26"/>
+      <c r="C68" s="29"/>
+      <c r="D68" s="29"/>
+      <c r="E68" s="29"/>
+      <c r="F68" s="29"/>
+      <c r="G68" s="29"/>
+      <c r="H68" s="29"/>
+      <c r="I68" s="29"/>
+      <c r="J68" s="29"/>
+      <c r="K68" s="29"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="26"/>
-      <c r="D69" s="26"/>
-      <c r="E69" s="26"/>
-      <c r="F69" s="26"/>
-      <c r="G69" s="26"/>
-      <c r="H69" s="26"/>
-      <c r="I69" s="26"/>
-      <c r="J69" s="26"/>
-      <c r="K69" s="26"/>
+      <c r="C69" s="29"/>
+      <c r="D69" s="29"/>
+      <c r="E69" s="29"/>
+      <c r="F69" s="29"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="29"/>
+      <c r="I69" s="29"/>
+      <c r="J69" s="29"/>
+      <c r="K69" s="29"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="26"/>
-      <c r="D70" s="26"/>
-      <c r="E70" s="26"/>
-      <c r="F70" s="26"/>
-      <c r="G70" s="26"/>
-      <c r="H70" s="26"/>
-      <c r="I70" s="26"/>
-      <c r="J70" s="26"/>
-      <c r="K70" s="26"/>
+      <c r="C70" s="29"/>
+      <c r="D70" s="29"/>
+      <c r="E70" s="29"/>
+      <c r="F70" s="29"/>
+      <c r="G70" s="29"/>
+      <c r="H70" s="29"/>
+      <c r="I70" s="29"/>
+      <c r="J70" s="29"/>
+      <c r="K70" s="29"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="26"/>
-      <c r="D71" s="26"/>
-      <c r="E71" s="26"/>
-      <c r="F71" s="26"/>
-      <c r="G71" s="26"/>
-      <c r="H71" s="26"/>
-      <c r="I71" s="26"/>
-      <c r="J71" s="26"/>
-      <c r="K71" s="26"/>
+      <c r="C71" s="29"/>
+      <c r="D71" s="29"/>
+      <c r="E71" s="29"/>
+      <c r="F71" s="29"/>
+      <c r="G71" s="29"/>
+      <c r="H71" s="29"/>
+      <c r="I71" s="29"/>
+      <c r="J71" s="29"/>
+      <c r="K71" s="29"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="26"/>
-      <c r="D72" s="26"/>
-      <c r="E72" s="26"/>
-      <c r="F72" s="26"/>
-      <c r="G72" s="26"/>
-      <c r="H72" s="26"/>
-      <c r="I72" s="26"/>
-      <c r="J72" s="26"/>
-      <c r="K72" s="26"/>
+      <c r="C72" s="29"/>
+      <c r="D72" s="29"/>
+      <c r="E72" s="29"/>
+      <c r="F72" s="29"/>
+      <c r="G72" s="29"/>
+      <c r="H72" s="29"/>
+      <c r="I72" s="29"/>
+      <c r="J72" s="29"/>
+      <c r="K72" s="29"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="26"/>
-      <c r="D73" s="26"/>
-      <c r="E73" s="26"/>
-      <c r="F73" s="26"/>
-      <c r="G73" s="26"/>
-      <c r="H73" s="26"/>
-      <c r="I73" s="26"/>
-      <c r="J73" s="26"/>
-      <c r="K73" s="26"/>
+      <c r="C73" s="29"/>
+      <c r="D73" s="29"/>
+      <c r="E73" s="29"/>
+      <c r="F73" s="29"/>
+      <c r="G73" s="29"/>
+      <c r="H73" s="29"/>
+      <c r="I73" s="29"/>
+      <c r="J73" s="29"/>
+      <c r="K73" s="29"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="26"/>
-      <c r="D74" s="26"/>
-      <c r="E74" s="26"/>
-      <c r="F74" s="26"/>
-      <c r="G74" s="26"/>
-      <c r="H74" s="26"/>
-      <c r="I74" s="26"/>
-      <c r="J74" s="26"/>
-      <c r="K74" s="26"/>
+      <c r="C74" s="29"/>
+      <c r="D74" s="29"/>
+      <c r="E74" s="29"/>
+      <c r="F74" s="29"/>
+      <c r="G74" s="29"/>
+      <c r="H74" s="29"/>
+      <c r="I74" s="29"/>
+      <c r="J74" s="29"/>
+      <c r="K74" s="29"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="26"/>
-      <c r="D75" s="26"/>
-      <c r="E75" s="26"/>
-      <c r="F75" s="26"/>
-      <c r="G75" s="26"/>
-      <c r="H75" s="26"/>
-      <c r="I75" s="26"/>
-      <c r="J75" s="26"/>
-      <c r="K75" s="26"/>
+      <c r="C75" s="29"/>
+      <c r="D75" s="29"/>
+      <c r="E75" s="29"/>
+      <c r="F75" s="29"/>
+      <c r="G75" s="29"/>
+      <c r="H75" s="29"/>
+      <c r="I75" s="29"/>
+      <c r="J75" s="29"/>
+      <c r="K75" s="29"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="26"/>
-      <c r="D76" s="26"/>
-      <c r="E76" s="26"/>
-      <c r="F76" s="26"/>
-      <c r="G76" s="26"/>
-      <c r="H76" s="26"/>
-      <c r="I76" s="26"/>
-      <c r="J76" s="26"/>
-      <c r="K76" s="26"/>
+      <c r="C76" s="29"/>
+      <c r="D76" s="29"/>
+      <c r="E76" s="29"/>
+      <c r="F76" s="29"/>
+      <c r="G76" s="29"/>
+      <c r="H76" s="29"/>
+      <c r="I76" s="29"/>
+      <c r="J76" s="29"/>
+      <c r="K76" s="29"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="26"/>
-      <c r="D77" s="26"/>
-      <c r="E77" s="26"/>
-      <c r="F77" s="26"/>
-      <c r="G77" s="26"/>
-      <c r="H77" s="26"/>
-      <c r="I77" s="26"/>
-      <c r="J77" s="26"/>
-      <c r="K77" s="26"/>
+      <c r="C77" s="29"/>
+      <c r="D77" s="29"/>
+      <c r="E77" s="29"/>
+      <c r="F77" s="29"/>
+      <c r="G77" s="29"/>
+      <c r="H77" s="29"/>
+      <c r="I77" s="29"/>
+      <c r="J77" s="29"/>
+      <c r="K77" s="29"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="26"/>
-      <c r="D78" s="26"/>
-      <c r="E78" s="26"/>
-      <c r="F78" s="26"/>
-      <c r="G78" s="26"/>
-      <c r="H78" s="26"/>
-      <c r="I78" s="26"/>
-      <c r="J78" s="26"/>
-      <c r="K78" s="26"/>
+      <c r="C78" s="29"/>
+      <c r="D78" s="29"/>
+      <c r="E78" s="29"/>
+      <c r="F78" s="29"/>
+      <c r="G78" s="29"/>
+      <c r="H78" s="29"/>
+      <c r="I78" s="29"/>
+      <c r="J78" s="29"/>
+      <c r="K78" s="29"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="26"/>
-      <c r="D79" s="26"/>
-      <c r="E79" s="26"/>
-      <c r="F79" s="26"/>
-      <c r="G79" s="26"/>
-      <c r="H79" s="26"/>
-      <c r="I79" s="26"/>
-      <c r="J79" s="26"/>
-      <c r="K79" s="26"/>
+      <c r="C79" s="29"/>
+      <c r="D79" s="29"/>
+      <c r="E79" s="29"/>
+      <c r="F79" s="29"/>
+      <c r="G79" s="29"/>
+      <c r="H79" s="29"/>
+      <c r="I79" s="29"/>
+      <c r="J79" s="29"/>
+      <c r="K79" s="29"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="26"/>
-      <c r="D80" s="26"/>
-      <c r="E80" s="26"/>
-      <c r="F80" s="26"/>
-      <c r="G80" s="26"/>
-      <c r="H80" s="26"/>
-      <c r="I80" s="26"/>
-      <c r="J80" s="26"/>
-      <c r="K80" s="26"/>
+      <c r="C80" s="29"/>
+      <c r="D80" s="29"/>
+      <c r="E80" s="29"/>
+      <c r="F80" s="29"/>
+      <c r="G80" s="29"/>
+      <c r="H80" s="29"/>
+      <c r="I80" s="29"/>
+      <c r="J80" s="29"/>
+      <c r="K80" s="29"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="26"/>
-      <c r="D81" s="26"/>
-      <c r="E81" s="26"/>
-      <c r="F81" s="26"/>
-      <c r="G81" s="26"/>
-      <c r="H81" s="26"/>
-      <c r="I81" s="26"/>
-      <c r="J81" s="26"/>
-      <c r="K81" s="26"/>
+      <c r="C81" s="29"/>
+      <c r="D81" s="29"/>
+      <c r="E81" s="29"/>
+      <c r="F81" s="29"/>
+      <c r="G81" s="29"/>
+      <c r="H81" s="29"/>
+      <c r="I81" s="29"/>
+      <c r="J81" s="29"/>
+      <c r="K81" s="29"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="26"/>
-      <c r="D82" s="26"/>
-      <c r="E82" s="26"/>
-      <c r="F82" s="26"/>
-      <c r="G82" s="26"/>
-      <c r="H82" s="26"/>
-      <c r="I82" s="26"/>
-      <c r="J82" s="26"/>
-      <c r="K82" s="26"/>
+      <c r="C82" s="29"/>
+      <c r="D82" s="29"/>
+      <c r="E82" s="29"/>
+      <c r="F82" s="29"/>
+      <c r="G82" s="29"/>
+      <c r="H82" s="29"/>
+      <c r="I82" s="29"/>
+      <c r="J82" s="29"/>
+      <c r="K82" s="29"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="26"/>
-      <c r="D83" s="26"/>
-      <c r="E83" s="26"/>
-      <c r="F83" s="26"/>
-      <c r="G83" s="26"/>
-      <c r="H83" s="26"/>
-      <c r="I83" s="26"/>
-      <c r="J83" s="26"/>
-      <c r="K83" s="26"/>
+      <c r="C83" s="29"/>
+      <c r="D83" s="29"/>
+      <c r="E83" s="29"/>
+      <c r="F83" s="29"/>
+      <c r="G83" s="29"/>
+      <c r="H83" s="29"/>
+      <c r="I83" s="29"/>
+      <c r="J83" s="29"/>
+      <c r="K83" s="29"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="26" t="s">
+      <c r="C84" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="D84" s="26">
-        <v>1</v>
-      </c>
-      <c r="E84" s="26"/>
-      <c r="F84" s="26"/>
-      <c r="G84" s="26"/>
-      <c r="H84" s="26"/>
-      <c r="I84" s="26"/>
-      <c r="J84" s="26"/>
-      <c r="K84" s="26"/>
+      <c r="D84" s="29">
+        <v>1</v>
+      </c>
+      <c r="E84" s="29"/>
+      <c r="F84" s="29"/>
+      <c r="G84" s="29"/>
+      <c r="H84" s="29"/>
+      <c r="I84" s="29"/>
+      <c r="J84" s="29"/>
+      <c r="K84" s="29"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="26"/>
-      <c r="D85" s="26"/>
-      <c r="E85" s="26"/>
-      <c r="F85" s="26"/>
-      <c r="G85" s="26"/>
-      <c r="H85" s="26"/>
-      <c r="I85" s="26"/>
-      <c r="J85" s="26"/>
-      <c r="K85" s="26"/>
+      <c r="C85" s="29"/>
+      <c r="D85" s="29"/>
+      <c r="E85" s="29"/>
+      <c r="F85" s="29"/>
+      <c r="G85" s="29"/>
+      <c r="H85" s="29"/>
+      <c r="I85" s="29"/>
+      <c r="J85" s="29"/>
+      <c r="K85" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2854,6 +2897,440 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="E13:W33"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="6" max="6" width="25.0909090909091" customWidth="1"/>
+    <col min="9" max="9" width="43.7272727272727" customWidth="1"/>
+    <col min="12" max="12" width="10.2727272727273" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="13" spans="5:21">
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
+      <c r="T13" s="16"/>
+      <c r="U13" s="16"/>
+    </row>
+    <row r="14" spans="5:21">
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="16"/>
+      <c r="U14" s="16"/>
+    </row>
+    <row r="15" spans="5:21">
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="16"/>
+      <c r="T15" s="16"/>
+      <c r="U15" s="16"/>
+    </row>
+    <row r="16" spans="5:21">
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
+      <c r="T16" s="16"/>
+      <c r="U16" s="16"/>
+    </row>
+    <row r="17" spans="5:23">
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+    </row>
+    <row r="18" spans="5:23">
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
+    </row>
+    <row r="19" spans="5:23">
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+    </row>
+    <row r="20" spans="5:23">
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
+    </row>
+    <row r="21" spans="5:23">
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
+    </row>
+    <row r="22" spans="5:23">
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
+    </row>
+    <row r="23" spans="5:23">
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1"/>
+      <c r="W23" s="1"/>
+    </row>
+    <row r="24" spans="5:23">
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
+    </row>
+    <row r="25" spans="5:23">
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+    </row>
+    <row r="26" spans="5:23">
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+    </row>
+    <row r="27" spans="5:23">
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+    </row>
+    <row r="28" spans="5:23">
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+    </row>
+    <row r="29" spans="5:23">
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
+    </row>
+    <row r="30" ht="15.25" spans="5:23">
+      <c r="F30" t="s">
+        <v>57</v>
+      </c>
+      <c r="G30" t="s">
+        <v>25</v>
+      </c>
+      <c r="H30" t="s">
+        <v>48</v>
+      </c>
+      <c r="I30" t="s">
+        <v>58</v>
+      </c>
+      <c r="J30" t="s">
+        <v>33</v>
+      </c>
+      <c r="K30" t="s">
+        <v>59</v>
+      </c>
+      <c r="L30" t="s">
+        <v>1</v>
+      </c>
+      <c r="M30" t="s">
+        <v>60</v>
+      </c>
+      <c r="N30" t="s">
+        <v>61</v>
+      </c>
+      <c r="O30" t="s">
+        <v>62</v>
+      </c>
+      <c r="P30" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" ht="16" spans="5:23">
+      <c r="F31" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31" t="s">
+        <v>66</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="I31" t="s">
+        <v>68</v>
+      </c>
+      <c r="J31" t="s">
+        <v>17</v>
+      </c>
+      <c r="K31" t="s">
+        <v>17</v>
+      </c>
+      <c r="M31">
+        <v>-0.25</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>3</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" ht="15.25" spans="5:23">
+      <c r="K32" t="s">
+        <v>70</v>
+      </c>
+      <c r="N32" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="9:13">
+      <c r="I33" t="s">
+        <v>71</v>
+      </c>
+      <c r="J33" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33" t="s">
+        <v>17</v>
+      </c>
+      <c r="M33">
+        <v>-0.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B2:N54"/>
@@ -2871,31 +3348,31 @@
   <sheetData>
     <row r="2" spans="2:14">
       <c r="B2" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="2:14">
       <c r="B3" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="2:14">
       <c r="H4" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="2:14">
       <c r="D8" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>4</v>
@@ -2904,36 +3381,36 @@
         <v>2</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="K8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="N8" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="9" spans="2:14">
       <c r="D9" s="5" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -2951,19 +3428,19 @@
     </row>
     <row r="10" spans="2:14">
       <c r="D10" s="5" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -2981,19 +3458,19 @@
     </row>
     <row r="11" spans="2:14">
       <c r="D11" s="5" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -3011,19 +3488,19 @@
     </row>
     <row r="12" ht="16" spans="2:14">
       <c r="D12" s="5" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -3041,19 +3518,19 @@
     </row>
     <row r="13" spans="2:14">
       <c r="D13" s="5" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -3071,19 +3548,19 @@
     </row>
     <row r="14" spans="2:14">
       <c r="D14" s="5" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -3101,19 +3578,19 @@
     </row>
     <row r="15" spans="2:14">
       <c r="D15" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="H15" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>71</v>
-      </c>
       <c r="I15" s="5" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -3131,10 +3608,10 @@
     </row>
     <row r="16" ht="16" spans="2:14">
       <c r="D16" s="5" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="G16" t="str">
         <f>G15</f>
@@ -3145,7 +3622,7 @@
         <v>2025, 2150</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J16">
         <f t="shared" ref="J16:L16" si="0">J12</f>
@@ -3166,10 +3643,10 @@
     </row>
     <row r="17" ht="16" spans="4:14">
       <c r="D17" s="5" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" ref="G17:M17" si="1">G16</f>
@@ -3180,7 +3657,7 @@
         <v>2025, 2150</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J17">
         <f t="shared" si="1"/>
@@ -3201,10 +3678,10 @@
     </row>
     <row r="18" ht="16" spans="4:14">
       <c r="D18" s="5" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G18" t="str">
         <f>G17</f>
@@ -3215,7 +3692,7 @@
         <v>2025, 2150</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -3249,7 +3726,7 @@
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
       <c r="H28" s="7" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
@@ -3260,16 +3737,16 @@
     </row>
     <row r="29" spans="4:14">
       <c r="D29" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>6</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>4</v>
@@ -3278,37 +3755,37 @@
         <v>2</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="K29" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N29" s="7" t="s">
         <v>64</v>
-      </c>
-      <c r="L29" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="M29" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="N29" s="7" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="30" ht="16" spans="4:14">
       <c r="D30" s="7" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="J30" s="7">
         <v>1</v>
@@ -3326,20 +3803,20 @@
     </row>
     <row r="31" ht="16" spans="4:14">
       <c r="D31" s="7" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="9" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="J31" s="7">
         <v>1</v>
@@ -3358,20 +3835,20 @@
     </row>
     <row r="32" ht="16" spans="4:14">
       <c r="D32" s="7" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="9" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="J32" s="7">
         <v>1</v>
@@ -3390,20 +3867,20 @@
     </row>
     <row r="33" ht="16" spans="4:14">
       <c r="D33" s="7" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="8" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="J33" s="7">
         <v>1</v>
@@ -3423,20 +3900,20 @@
     </row>
     <row r="34" ht="16" spans="4:14">
       <c r="D34" s="7" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="8" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="J34" s="7">
         <v>1</v>
@@ -3456,20 +3933,20 @@
     </row>
     <row r="35" ht="16" spans="4:14">
       <c r="D35" s="7" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="8" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="J35" s="7">
         <v>1</v>
@@ -3489,20 +3966,20 @@
     </row>
     <row r="36" ht="16" spans="4:14">
       <c r="D36" s="7" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H36" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="G36" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>93</v>
-      </c>
       <c r="I36" s="7" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="J36" s="7">
         <v>1</v>
@@ -3520,275 +3997,275 @@
       </c>
       <c r="N36" s="7"/>
     </row>
-    <row r="37" spans="4:14">
+    <row r="37" ht="16" spans="4:14">
+      <c r="D37" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E37" s="10"/>
+      <c r="F37" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J37" s="10">
+        <v>1</v>
+      </c>
+      <c r="K37" s="10">
+        <v>1</v>
+      </c>
+      <c r="L37" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="M37" s="10">
+        <v>1</v>
+      </c>
       <c r="N37" s="7"/>
     </row>
-    <row r="38" spans="4:14">
+    <row r="38" ht="16" spans="4:14">
+      <c r="D38" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E38" s="10"/>
+      <c r="F38" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J38" s="10">
+        <v>1</v>
+      </c>
+      <c r="K38" s="10">
+        <v>1</v>
+      </c>
+      <c r="L38" s="10">
+        <f t="shared" ref="L38:L43" si="3">L37</f>
+        <v>0.01</v>
+      </c>
+      <c r="M38" s="10">
+        <v>1</v>
+      </c>
       <c r="N38" s="7"/>
     </row>
-    <row r="39" spans="4:14">
+    <row r="39" ht="16" spans="4:14">
+      <c r="D39" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="E39" s="10"/>
+      <c r="F39" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J39" s="10">
+        <v>1</v>
+      </c>
+      <c r="K39" s="10">
+        <v>1</v>
+      </c>
+      <c r="L39" s="10">
+        <f t="shared" si="3"/>
+        <v>0.01</v>
+      </c>
+      <c r="M39" s="10">
+        <v>1</v>
+      </c>
       <c r="N39" s="7"/>
     </row>
-    <row r="40" spans="4:14">
+    <row r="40" ht="16" spans="4:14">
+      <c r="D40" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E40" s="10"/>
+      <c r="F40" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J40" s="10">
+        <v>1</v>
+      </c>
+      <c r="K40" s="10">
+        <f>K39</f>
+        <v>1</v>
+      </c>
+      <c r="L40" s="10">
+        <f t="shared" si="3"/>
+        <v>0.01</v>
+      </c>
+      <c r="M40" s="10">
+        <v>1</v>
+      </c>
       <c r="N40" s="7"/>
     </row>
-    <row r="41" spans="4:14">
+    <row r="41" ht="16" spans="4:14">
+      <c r="D41" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="E41" s="10"/>
+      <c r="F41" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J41" s="10">
+        <v>1</v>
+      </c>
+      <c r="K41" s="10">
+        <f>K40</f>
+        <v>1</v>
+      </c>
+      <c r="L41" s="10">
+        <f t="shared" si="3"/>
+        <v>0.01</v>
+      </c>
+      <c r="M41" s="10">
+        <v>1</v>
+      </c>
       <c r="N41" s="7"/>
     </row>
-    <row r="42" spans="4:14">
+    <row r="42" ht="16" spans="4:14">
+      <c r="D42" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="E42" s="10"/>
+      <c r="F42" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J42" s="10">
+        <v>1</v>
+      </c>
+      <c r="K42" s="10">
+        <f>K41</f>
+        <v>1</v>
+      </c>
+      <c r="L42" s="10">
+        <f t="shared" si="3"/>
+        <v>0.01</v>
+      </c>
+      <c r="M42" s="10">
+        <v>1</v>
+      </c>
       <c r="N42" s="7"/>
     </row>
     <row r="43" ht="16" spans="4:14">
       <c r="D43" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="E43" s="10"/>
+      <c r="F43" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I43" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="E43" s="10"/>
-      <c r="F43" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="I43" s="10" t="s">
-        <v>94</v>
-      </c>
       <c r="J43" s="10">
         <v>1</v>
       </c>
       <c r="K43" s="10">
+        <f>K42</f>
         <v>1</v>
       </c>
       <c r="L43" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="M43" s="10">
-        <v>1</v>
-      </c>
-      <c r="N43" s="7"/>
-    </row>
-    <row r="44" ht="16" spans="4:14">
-      <c r="D44" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="E44" s="10"/>
-      <c r="F44" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="I44" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="J44" s="10">
-        <v>1</v>
-      </c>
-      <c r="K44" s="10">
-        <v>1</v>
-      </c>
-      <c r="L44" s="10">
-        <f t="shared" ref="L44:L49" si="3">L43</f>
-        <v>0.01</v>
-      </c>
-      <c r="M44" s="10">
-        <v>1</v>
-      </c>
-      <c r="N44" s="7"/>
-    </row>
-    <row r="45" ht="16" spans="4:14">
-      <c r="D45" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="E45" s="10"/>
-      <c r="F45" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="I45" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="J45" s="10">
-        <v>1</v>
-      </c>
-      <c r="K45" s="10">
-        <v>1</v>
-      </c>
-      <c r="L45" s="10">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M45" s="10">
-        <v>1</v>
-      </c>
+      <c r="M43" s="10">
+        <v>1</v>
+      </c>
+      <c r="N43" s="7"/>
+    </row>
+    <row r="44" spans="4:14">
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="7"/>
+    </row>
+    <row r="45" spans="4:14">
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
       <c r="N45" s="7"/>
     </row>
-    <row r="46" ht="16" spans="4:14">
-      <c r="D46" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E46" s="10"/>
-      <c r="F46" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="I46" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="J46" s="10">
-        <v>1</v>
-      </c>
-      <c r="K46" s="10">
-        <f>K45</f>
-        <v>1</v>
-      </c>
-      <c r="L46" s="10">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
-      </c>
-      <c r="M46" s="10">
-        <v>1</v>
-      </c>
+    <row r="46" spans="4:14">
       <c r="N46" s="7"/>
     </row>
-    <row r="47" ht="16" spans="4:14">
-      <c r="D47" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="E47" s="10"/>
-      <c r="F47" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="I47" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="J47" s="10">
-        <v>1</v>
-      </c>
-      <c r="K47" s="10">
-        <f>K46</f>
-        <v>1</v>
-      </c>
-      <c r="L47" s="10">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
-      </c>
-      <c r="M47" s="10">
-        <v>1</v>
-      </c>
+    <row r="47" spans="4:14">
       <c r="N47" s="7"/>
     </row>
-    <row r="48" ht="16" spans="4:14">
-      <c r="D48" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="E48" s="10"/>
-      <c r="F48" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="J48" s="10">
-        <v>1</v>
-      </c>
-      <c r="K48" s="10">
-        <f>K47</f>
-        <v>1</v>
-      </c>
-      <c r="L48" s="10">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
-      </c>
-      <c r="M48" s="10">
-        <v>1</v>
-      </c>
+    <row r="48" spans="4:14">
       <c r="N48" s="7"/>
     </row>
-    <row r="49" ht="16" spans="4:14">
-      <c r="D49" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="E49" s="10"/>
-      <c r="F49" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="G49" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="I49" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="J49" s="10">
-        <v>1</v>
-      </c>
-      <c r="K49" s="10">
-        <f>K48</f>
-        <v>1</v>
-      </c>
-      <c r="L49" s="10">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
-      </c>
-      <c r="M49" s="10">
-        <v>1</v>
-      </c>
+    <row r="49" spans="4:14">
       <c r="N49" s="7"/>
     </row>
     <row r="50" spans="4:14">
-      <c r="D50" s="10"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="10"/>
-      <c r="M50" s="10"/>
       <c r="N50" s="7"/>
     </row>
     <row r="51" spans="4:14">
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
       <c r="N51" s="7"/>
     </row>
     <row r="52" spans="4:14">
@@ -3836,81 +4313,124 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="E13:U33"/>
+  <dimension ref="F9:R38"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
-    <col min="6" max="6" width="25.0909090909091" customWidth="1"/>
+    <col min="6" max="6" width="24.5454545454545" customWidth="1"/>
+    <col min="8" max="8" width="49.4545454545455" customWidth="1"/>
     <col min="9" max="9" width="43.7272727272727" customWidth="1"/>
-    <col min="12" max="12" width="10.2727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="5:21">
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
+    <row r="9" spans="6:18">
+      <c r="F9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="6:18">
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+    </row>
+    <row r="12" spans="6:18">
+      <c r="K12" s="1"/>
+      <c r="L12" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+    </row>
+    <row r="13" spans="6:18">
+      <c r="F13" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" t="s">
+        <v>58</v>
+      </c>
+      <c r="J13" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-    </row>
-    <row r="14" spans="5:21">
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
+    </row>
+    <row r="14" spans="6:18">
+      <c r="F14" t="s">
+        <v>139</v>
+      </c>
+      <c r="G14"/>
+      <c r="H14" t="s">
+        <v>140</v>
+      </c>
+      <c r="I14"/>
+      <c r="J14"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
+      <c r="M14" s="1">
+        <v>0.25</v>
+      </c>
       <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <v>5</v>
+      </c>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-    </row>
-    <row r="15" spans="5:21">
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
+    </row>
+    <row r="15" spans="6:18">
+      <c r="H15" t="s">
+        <v>141</v>
+      </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
+      <c r="M15" s="2">
+        <v>-1</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-    </row>
-    <row r="16" spans="5:21">
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
+    </row>
+    <row r="16" spans="6:18">
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -3919,17 +4439,8 @@
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-    </row>
-    <row r="17" spans="5:21">
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
+    </row>
+    <row r="17" spans="6:18">
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -3938,17 +4449,8 @@
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-    </row>
-    <row r="18" spans="5:21">
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
+    </row>
+    <row r="18" spans="6:18">
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -3957,17 +4459,8 @@
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-    </row>
-    <row r="19" spans="5:21">
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
+    </row>
+    <row r="19" spans="6:18">
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -3976,17 +4469,8 @@
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-    </row>
-    <row r="20" spans="5:21">
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
+    </row>
+    <row r="20" spans="6:18">
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -3995,17 +4479,8 @@
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-    </row>
-    <row r="21" spans="5:21">
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
+    </row>
+    <row r="21" spans="6:18">
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -4014,17 +4489,8 @@
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-    </row>
-    <row r="22" spans="5:21">
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
+    </row>
+    <row r="22" spans="6:18">
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -4033,17 +4499,8 @@
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-    </row>
-    <row r="23" spans="5:21">
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
+    </row>
+    <row r="23" spans="6:18">
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -4052,17 +4509,8 @@
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
-      <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-    </row>
-    <row r="24" spans="5:21">
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
+    </row>
+    <row r="24" spans="6:18">
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -4071,108 +4519,241 @@
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-    </row>
-    <row r="29" spans="5:21">
-      <c r="L29" s="2"/>
-    </row>
-    <row r="30" ht="15.25" spans="5:21">
-      <c r="F30" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30" t="s">
+    </row>
+    <row r="25" spans="6:18">
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+    </row>
+    <row r="26" spans="6:18">
+      <c r="K26" s="1"/>
+      <c r="L26" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+    </row>
+    <row r="27" spans="6:18">
+      <c r="F27" t="s">
+        <v>57</v>
+      </c>
+      <c r="G27" t="s">
         <v>25</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H27" t="s">
         <v>48</v>
       </c>
-      <c r="I30" t="s">
-        <v>122</v>
-      </c>
-      <c r="J30" t="s">
+      <c r="I27" t="s">
+        <v>58</v>
+      </c>
+      <c r="J27" t="s">
         <v>33</v>
       </c>
-      <c r="K30" t="s">
-        <v>123</v>
-      </c>
-      <c r="L30" t="s">
-        <v>1</v>
-      </c>
-      <c r="M30" t="s">
-        <v>124</v>
-      </c>
-      <c r="N30" t="s">
-        <v>125</v>
-      </c>
-      <c r="O30" t="s">
-        <v>126</v>
-      </c>
-      <c r="P30" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" ht="16" spans="5:21">
-      <c r="F31" t="s">
-        <v>128</v>
-      </c>
-      <c r="G31" t="s">
-        <v>129</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I31" t="s">
-        <v>131</v>
-      </c>
-      <c r="J31" t="s">
-        <v>17</v>
-      </c>
-      <c r="K31" t="s">
-        <v>17</v>
-      </c>
-      <c r="M31">
+      <c r="K27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R27" s="1"/>
+    </row>
+    <row r="28" ht="16" spans="6:18">
+      <c r="F28" t="s">
+        <v>142</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1">
         <v>-0.25</v>
       </c>
-      <c r="O31">
+      <c r="N28" s="1"/>
+      <c r="O28" s="1">
         <v>0</v>
       </c>
-      <c r="P31">
-        <v>3</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="32" ht="15.25" spans="5:21">
-      <c r="K32" t="s">
-        <v>133</v>
-      </c>
-      <c r="N32" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="9:13">
-      <c r="I33" t="s">
-        <v>134</v>
-      </c>
-      <c r="J33" t="s">
-        <v>17</v>
-      </c>
-      <c r="K33" t="s">
-        <v>17</v>
-      </c>
-      <c r="M33">
-        <v>-0.1</v>
-      </c>
+      <c r="P28" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+    </row>
+    <row r="29" spans="6:18">
+      <c r="H29" t="s">
+        <v>144</v>
+      </c>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="2">
+        <v>1</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+    </row>
+    <row r="30" spans="6:18">
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
+    </row>
+    <row r="31" spans="6:18">
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+    </row>
+    <row r="32" spans="6:18">
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+    </row>
+    <row r="33" spans="6:18">
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+    </row>
+    <row r="34" spans="6:18">
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+    </row>
+    <row r="35" spans="6:18">
+      <c r="K35" s="1"/>
+      <c r="L35" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
+    </row>
+    <row r="36" spans="6:18">
+      <c r="F36" t="s">
+        <v>57</v>
+      </c>
+      <c r="G36" t="s">
+        <v>25</v>
+      </c>
+      <c r="H36" t="s">
+        <v>48</v>
+      </c>
+      <c r="I36" t="s">
+        <v>58</v>
+      </c>
+      <c r="J36" t="s">
+        <v>33</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="6:18">
+      <c r="F37" t="s">
+        <v>145</v>
+      </c>
+      <c r="H37" t="s">
+        <v>146</v>
+      </c>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1">
+        <v>-0.25</v>
+      </c>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1">
+        <v>0</v>
+      </c>
+      <c r="P37" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q37" s="1"/>
+    </row>
+    <row r="38" spans="6:18">
+      <c r="H38" t="s">
+        <v>147</v>
+      </c>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="2">
+        <v>1</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="6"/>
+    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
@@ -244,40 +244,8 @@
 </comments>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>xli9</author>
-  </authors>
-  <commentList>
-    <comment ref="M20" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t>xli9:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Times New Roman"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">
-Bca the capacity unit is GWh</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="157">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -450,6 +418,12 @@
     <t>ENCAN01_SMR</t>
   </si>
   <si>
+    <t>~UC_Sets: R_E: AllRegions</t>
+  </si>
+  <si>
+    <t>~UC_T: UP</t>
+  </si>
+  <si>
     <t>UC_N</t>
   </si>
   <si>
@@ -489,12 +463,15 @@
     <t>Discharge of batteries should lower than a level</t>
   </si>
   <si>
+    <t>ELCWIN</t>
+  </si>
+  <si>
+    <t>E*, Uti*, Tra_BEV_Batt_VtoG</t>
+  </si>
+  <si>
     <t>AuxStoOUT</t>
   </si>
   <si>
-    <t>ELCWIN</t>
-  </si>
-  <si>
     <t>~UC_Sets: R_S: AllRegions</t>
   </si>
   <si>
@@ -684,9 +661,6 @@
     <t>EN_STG_4hBatt_NMC811</t>
   </si>
   <si>
-    <t>~UC_Sets: R_E: AllRegions</t>
-  </si>
-  <si>
     <t>~UC_T: LO</t>
   </si>
   <si>
@@ -711,7 +685,7 @@
     <t>Tra_EV_Batt-LFP_fromrecy, Tra_EV_Batt-LFP_virgin_pack</t>
   </si>
   <si>
-    <t>Tra_E*fromrecy, Tra_EV_Bat*virgin_pack, -Tra_EV_Batt-LFP_fromrecy, -Tra_EV_Batt-LFP_virgin_pack</t>
+    <t>Tra_EV_Batt-NMC*fromrecy, Tra_EV_Batt-NMC*virgin_pack</t>
   </si>
   <si>
     <t>UCE_3</t>
@@ -720,7 +694,28 @@
     <t>EN_STG_4hBatt, Util_Rep_Batt-LFP</t>
   </si>
   <si>
-    <t>EN_STG_4hBatt*, Util_Rep_Bat*, -EN_STG_4hBatt, -Util_Rep_Batt-LFP</t>
+    <t>EN_STG_4hBatt_NMC*, Util_Rep_Batt-NMC*</t>
+  </si>
+  <si>
+    <t>~UC_T: UC_CAP</t>
+  </si>
+  <si>
+    <t>limtype</t>
+  </si>
+  <si>
+    <t>Allregions</t>
+  </si>
+  <si>
+    <t>UC_ACT</t>
+  </si>
+  <si>
+    <t>UCE_4</t>
+  </si>
+  <si>
+    <t>TRDELC</t>
+  </si>
+  <si>
+    <t>Tra_EV_Bat*fromrecy, Tra_EV_Bat*virgin_pack</t>
   </si>
 </sst>
 </file>
@@ -733,7 +728,7 @@
     <numFmt numFmtId="176" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -746,6 +741,21 @@
       <color rgb="FF212529"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -928,24 +938,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="0"/>
-    </font>
-    <font>
       <b/>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -956,13 +949,29 @@
       <name val="Tahoma"/>
       <charset val="0"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -978,12 +987,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -991,6 +994,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1190,6 +1199,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thick">
@@ -1230,21 +1254,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1316,181 +1325,195 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="51" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="53">
@@ -2025,7 +2048,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="36">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -2082,7 +2105,7 @@
       </c>
     </row>
     <row r="4" ht="16" spans="1:11">
-      <c r="A4" s="6"/>
+      <c r="A4" s="2"/>
     </row>
     <row r="7" spans="1:11">
       <c r="D7" t="s">
@@ -2139,10 +2162,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="30"/>
+      <c r="K10" s="40"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="30"/>
+      <c r="K11" s="40"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2163,12 +2186,12 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:13">
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="7"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
@@ -2183,19 +2206,19 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="20"/>
+      <c r="K6" s="29"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="30">
         <v>10</v>
       </c>
     </row>
@@ -2203,29 +2226,29 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="30">
         <v>7</v>
       </c>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
     </row>
     <row r="9" ht="16" spans="2:13">
       <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="30">
         <v>10</v>
       </c>
     </row>
@@ -2233,29 +2256,29 @@
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="30">
         <v>8</v>
       </c>
-      <c r="K10" s="22"/>
-      <c r="L10" s="23"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="32"/>
     </row>
     <row r="11" ht="16" spans="2:13">
       <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="28">
         <v>1.5</v>
       </c>
     </row>
@@ -2263,13 +2286,13 @@
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="28">
         <v>1.5</v>
       </c>
     </row>
@@ -2277,13 +2300,13 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="16">
         <v>2</v>
       </c>
     </row>
@@ -2291,13 +2314,13 @@
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="16">
         <v>0</v>
       </c>
     </row>
@@ -2305,13 +2328,13 @@
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="16">
         <v>0</v>
       </c>
     </row>
@@ -2319,13 +2342,13 @@
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="33">
         <v>12</v>
       </c>
     </row>
@@ -2333,561 +2356,561 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="D17" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="35">
         <v>0.2</v>
       </c>
-      <c r="F17" s="7"/>
+      <c r="F17" s="16"/>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="25" t="s">
+      <c r="D18" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="35">
         <v>0.2</v>
       </c>
-      <c r="F18" s="7"/>
+      <c r="F18" s="16"/>
     </row>
     <row r="19" ht="16" spans="2:6">
       <c r="B19" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="25" t="s">
+      <c r="D19" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="35">
         <v>0.2</v>
       </c>
-      <c r="F19" s="7"/>
+      <c r="F19" s="16"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="25" t="s">
+      <c r="D20" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="35">
         <v>0.5</v>
       </c>
-      <c r="F20" s="7"/>
+      <c r="F20" s="16"/>
     </row>
     <row r="21" ht="16" spans="2:6">
       <c r="B21" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="35">
         <v>0.8</v>
       </c>
-      <c r="F21" s="7"/>
+      <c r="F21" s="16"/>
     </row>
     <row r="22" ht="16" spans="2:6">
       <c r="B22" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="25" t="s">
+      <c r="D22" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="19"/>
-      <c r="F22" s="7"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="16"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="25" t="s">
+      <c r="D23" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="7">
-        <v>1</v>
-      </c>
-      <c r="F23" s="7"/>
+      <c r="E23" s="16">
+        <v>1</v>
+      </c>
+      <c r="F23" s="16"/>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="25" t="s">
+      <c r="D24" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="7">
-        <v>1</v>
-      </c>
-      <c r="F24" s="7"/>
+      <c r="E24" s="16">
+        <v>1</v>
+      </c>
+      <c r="F24" s="16"/>
     </row>
     <row r="25" ht="16" spans="2:6">
       <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="25" t="s">
+      <c r="D25" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="7">
-        <v>1</v>
-      </c>
-      <c r="F25" s="7"/>
+      <c r="E25" s="16">
+        <v>1</v>
+      </c>
+      <c r="F25" s="16"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="25" t="s">
+      <c r="D26" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="28">
         <v>0.05</v>
       </c>
-      <c r="F26" s="7"/>
+      <c r="F26" s="16"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="27" t="s">
+      <c r="C27" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="27" t="s">
+      <c r="D27" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="37">
         <v>2020</v>
       </c>
-      <c r="F27" s="7"/>
+      <c r="F27" s="16"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="27" t="s">
+      <c r="D28" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="38">
         <v>2020</v>
       </c>
-      <c r="F28" s="7"/>
+      <c r="F28" s="16"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
     </row>
     <row r="38" spans="3:5">
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="29" t="s">
+      <c r="C54" s="39" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="29"/>
-      <c r="E56" s="29"/>
-      <c r="F56" s="29"/>
-      <c r="G56" s="29"/>
-      <c r="H56" s="29"/>
-      <c r="I56" s="29"/>
-      <c r="J56" s="29"/>
-      <c r="K56" s="29"/>
+      <c r="D56" s="39"/>
+      <c r="E56" s="39"/>
+      <c r="F56" s="39"/>
+      <c r="G56" s="39"/>
+      <c r="H56" s="39"/>
+      <c r="I56" s="39"/>
+      <c r="J56" s="39"/>
+      <c r="K56" s="39"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="29" t="s">
+      <c r="C57" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="29" t="s">
+      <c r="D57" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="29" t="s">
+      <c r="E57" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="F57" s="29" t="s">
+      <c r="F57" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="G57" s="29" t="s">
+      <c r="G57" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="29" t="s">
+      <c r="H57" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="29" t="s">
+      <c r="I57" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="J57" s="29" t="s">
+      <c r="J57" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="K57" s="29" t="s">
+      <c r="K57" s="39" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="29"/>
-      <c r="J58" s="29"/>
-      <c r="K58" s="29"/>
+      <c r="C58" s="39"/>
+      <c r="D58" s="39"/>
+      <c r="E58" s="39"/>
+      <c r="F58" s="39"/>
+      <c r="G58" s="39"/>
+      <c r="H58" s="39"/>
+      <c r="I58" s="39"/>
+      <c r="J58" s="39"/>
+      <c r="K58" s="39"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="29"/>
-      <c r="D59" s="29"/>
-      <c r="E59" s="29"/>
-      <c r="F59" s="29"/>
-      <c r="G59" s="29"/>
-      <c r="H59" s="29"/>
-      <c r="I59" s="29"/>
-      <c r="J59" s="29"/>
-      <c r="K59" s="29"/>
+      <c r="C59" s="39"/>
+      <c r="D59" s="39"/>
+      <c r="E59" s="39"/>
+      <c r="F59" s="39"/>
+      <c r="G59" s="39"/>
+      <c r="H59" s="39"/>
+      <c r="I59" s="39"/>
+      <c r="J59" s="39"/>
+      <c r="K59" s="39"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="29"/>
-      <c r="D60" s="29"/>
-      <c r="E60" s="29"/>
-      <c r="F60" s="29"/>
-      <c r="G60" s="29"/>
-      <c r="H60" s="29"/>
-      <c r="I60" s="29"/>
-      <c r="J60" s="29"/>
-      <c r="K60" s="29"/>
+      <c r="C60" s="39"/>
+      <c r="D60" s="39"/>
+      <c r="E60" s="39"/>
+      <c r="F60" s="39"/>
+      <c r="G60" s="39"/>
+      <c r="H60" s="39"/>
+      <c r="I60" s="39"/>
+      <c r="J60" s="39"/>
+      <c r="K60" s="39"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="29"/>
-      <c r="J61" s="29"/>
-      <c r="K61" s="29"/>
+      <c r="C61" s="39"/>
+      <c r="D61" s="39"/>
+      <c r="E61" s="39"/>
+      <c r="F61" s="39"/>
+      <c r="G61" s="39"/>
+      <c r="H61" s="39"/>
+      <c r="I61" s="39"/>
+      <c r="J61" s="39"/>
+      <c r="K61" s="39"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="29"/>
-      <c r="D62" s="29"/>
-      <c r="E62" s="29"/>
-      <c r="F62" s="29"/>
-      <c r="G62" s="29"/>
-      <c r="H62" s="29"/>
-      <c r="I62" s="29"/>
-      <c r="J62" s="29"/>
-      <c r="K62" s="29"/>
+      <c r="C62" s="39"/>
+      <c r="D62" s="39"/>
+      <c r="E62" s="39"/>
+      <c r="F62" s="39"/>
+      <c r="G62" s="39"/>
+      <c r="H62" s="39"/>
+      <c r="I62" s="39"/>
+      <c r="J62" s="39"/>
+      <c r="K62" s="39"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="29"/>
-      <c r="D63" s="29"/>
-      <c r="E63" s="29"/>
-      <c r="F63" s="29"/>
-      <c r="G63" s="29"/>
-      <c r="H63" s="29"/>
-      <c r="I63" s="29"/>
-      <c r="J63" s="29"/>
-      <c r="K63" s="29"/>
+      <c r="C63" s="39"/>
+      <c r="D63" s="39"/>
+      <c r="E63" s="39"/>
+      <c r="F63" s="39"/>
+      <c r="G63" s="39"/>
+      <c r="H63" s="39"/>
+      <c r="I63" s="39"/>
+      <c r="J63" s="39"/>
+      <c r="K63" s="39"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="29"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="29"/>
-      <c r="H64" s="29"/>
-      <c r="I64" s="29"/>
-      <c r="J64" s="29"/>
-      <c r="K64" s="29"/>
+      <c r="C64" s="39"/>
+      <c r="D64" s="39"/>
+      <c r="E64" s="39"/>
+      <c r="F64" s="39"/>
+      <c r="G64" s="39"/>
+      <c r="H64" s="39"/>
+      <c r="I64" s="39"/>
+      <c r="J64" s="39"/>
+      <c r="K64" s="39"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="29"/>
-      <c r="D65" s="29"/>
-      <c r="E65" s="29"/>
-      <c r="F65" s="29"/>
-      <c r="G65" s="29"/>
-      <c r="H65" s="29"/>
-      <c r="I65" s="29"/>
-      <c r="J65" s="29"/>
-      <c r="K65" s="29"/>
+      <c r="C65" s="39"/>
+      <c r="D65" s="39"/>
+      <c r="E65" s="39"/>
+      <c r="F65" s="39"/>
+      <c r="G65" s="39"/>
+      <c r="H65" s="39"/>
+      <c r="I65" s="39"/>
+      <c r="J65" s="39"/>
+      <c r="K65" s="39"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="29"/>
-      <c r="D66" s="29"/>
-      <c r="E66" s="29"/>
-      <c r="F66" s="29"/>
-      <c r="G66" s="29"/>
-      <c r="H66" s="29"/>
-      <c r="I66" s="29"/>
-      <c r="J66" s="29"/>
-      <c r="K66" s="29"/>
+      <c r="C66" s="39"/>
+      <c r="D66" s="39"/>
+      <c r="E66" s="39"/>
+      <c r="F66" s="39"/>
+      <c r="G66" s="39"/>
+      <c r="H66" s="39"/>
+      <c r="I66" s="39"/>
+      <c r="J66" s="39"/>
+      <c r="K66" s="39"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="29"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="29"/>
-      <c r="J67" s="29"/>
-      <c r="K67" s="29"/>
+      <c r="C67" s="39"/>
+      <c r="D67" s="39"/>
+      <c r="E67" s="39"/>
+      <c r="F67" s="39"/>
+      <c r="G67" s="39"/>
+      <c r="H67" s="39"/>
+      <c r="I67" s="39"/>
+      <c r="J67" s="39"/>
+      <c r="K67" s="39"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="29"/>
-      <c r="D68" s="29"/>
-      <c r="E68" s="29"/>
-      <c r="F68" s="29"/>
-      <c r="G68" s="29"/>
-      <c r="H68" s="29"/>
-      <c r="I68" s="29"/>
-      <c r="J68" s="29"/>
-      <c r="K68" s="29"/>
+      <c r="C68" s="39"/>
+      <c r="D68" s="39"/>
+      <c r="E68" s="39"/>
+      <c r="F68" s="39"/>
+      <c r="G68" s="39"/>
+      <c r="H68" s="39"/>
+      <c r="I68" s="39"/>
+      <c r="J68" s="39"/>
+      <c r="K68" s="39"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="29"/>
-      <c r="D69" s="29"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="29"/>
-      <c r="H69" s="29"/>
-      <c r="I69" s="29"/>
-      <c r="J69" s="29"/>
-      <c r="K69" s="29"/>
+      <c r="C69" s="39"/>
+      <c r="D69" s="39"/>
+      <c r="E69" s="39"/>
+      <c r="F69" s="39"/>
+      <c r="G69" s="39"/>
+      <c r="H69" s="39"/>
+      <c r="I69" s="39"/>
+      <c r="J69" s="39"/>
+      <c r="K69" s="39"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="29"/>
-      <c r="J70" s="29"/>
-      <c r="K70" s="29"/>
+      <c r="C70" s="39"/>
+      <c r="D70" s="39"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="39"/>
+      <c r="G70" s="39"/>
+      <c r="H70" s="39"/>
+      <c r="I70" s="39"/>
+      <c r="J70" s="39"/>
+      <c r="K70" s="39"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="29"/>
-      <c r="D71" s="29"/>
-      <c r="E71" s="29"/>
-      <c r="F71" s="29"/>
-      <c r="G71" s="29"/>
-      <c r="H71" s="29"/>
-      <c r="I71" s="29"/>
-      <c r="J71" s="29"/>
-      <c r="K71" s="29"/>
+      <c r="C71" s="39"/>
+      <c r="D71" s="39"/>
+      <c r="E71" s="39"/>
+      <c r="F71" s="39"/>
+      <c r="G71" s="39"/>
+      <c r="H71" s="39"/>
+      <c r="I71" s="39"/>
+      <c r="J71" s="39"/>
+      <c r="K71" s="39"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="29"/>
-      <c r="D72" s="29"/>
-      <c r="E72" s="29"/>
-      <c r="F72" s="29"/>
-      <c r="G72" s="29"/>
-      <c r="H72" s="29"/>
-      <c r="I72" s="29"/>
-      <c r="J72" s="29"/>
-      <c r="K72" s="29"/>
+      <c r="C72" s="39"/>
+      <c r="D72" s="39"/>
+      <c r="E72" s="39"/>
+      <c r="F72" s="39"/>
+      <c r="G72" s="39"/>
+      <c r="H72" s="39"/>
+      <c r="I72" s="39"/>
+      <c r="J72" s="39"/>
+      <c r="K72" s="39"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="29"/>
-      <c r="D73" s="29"/>
-      <c r="E73" s="29"/>
-      <c r="F73" s="29"/>
-      <c r="G73" s="29"/>
-      <c r="H73" s="29"/>
-      <c r="I73" s="29"/>
-      <c r="J73" s="29"/>
-      <c r="K73" s="29"/>
+      <c r="C73" s="39"/>
+      <c r="D73" s="39"/>
+      <c r="E73" s="39"/>
+      <c r="F73" s="39"/>
+      <c r="G73" s="39"/>
+      <c r="H73" s="39"/>
+      <c r="I73" s="39"/>
+      <c r="J73" s="39"/>
+      <c r="K73" s="39"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="29"/>
-      <c r="D74" s="29"/>
-      <c r="E74" s="29"/>
-      <c r="F74" s="29"/>
-      <c r="G74" s="29"/>
-      <c r="H74" s="29"/>
-      <c r="I74" s="29"/>
-      <c r="J74" s="29"/>
-      <c r="K74" s="29"/>
+      <c r="C74" s="39"/>
+      <c r="D74" s="39"/>
+      <c r="E74" s="39"/>
+      <c r="F74" s="39"/>
+      <c r="G74" s="39"/>
+      <c r="H74" s="39"/>
+      <c r="I74" s="39"/>
+      <c r="J74" s="39"/>
+      <c r="K74" s="39"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="29"/>
-      <c r="D75" s="29"/>
-      <c r="E75" s="29"/>
-      <c r="F75" s="29"/>
-      <c r="G75" s="29"/>
-      <c r="H75" s="29"/>
-      <c r="I75" s="29"/>
-      <c r="J75" s="29"/>
-      <c r="K75" s="29"/>
+      <c r="C75" s="39"/>
+      <c r="D75" s="39"/>
+      <c r="E75" s="39"/>
+      <c r="F75" s="39"/>
+      <c r="G75" s="39"/>
+      <c r="H75" s="39"/>
+      <c r="I75" s="39"/>
+      <c r="J75" s="39"/>
+      <c r="K75" s="39"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="29"/>
-      <c r="D76" s="29"/>
-      <c r="E76" s="29"/>
-      <c r="F76" s="29"/>
-      <c r="G76" s="29"/>
-      <c r="H76" s="29"/>
-      <c r="I76" s="29"/>
-      <c r="J76" s="29"/>
-      <c r="K76" s="29"/>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="39"/>
+      <c r="G76" s="39"/>
+      <c r="H76" s="39"/>
+      <c r="I76" s="39"/>
+      <c r="J76" s="39"/>
+      <c r="K76" s="39"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="29"/>
-      <c r="D77" s="29"/>
-      <c r="E77" s="29"/>
-      <c r="F77" s="29"/>
-      <c r="G77" s="29"/>
-      <c r="H77" s="29"/>
-      <c r="I77" s="29"/>
-      <c r="J77" s="29"/>
-      <c r="K77" s="29"/>
+      <c r="C77" s="39"/>
+      <c r="D77" s="39"/>
+      <c r="E77" s="39"/>
+      <c r="F77" s="39"/>
+      <c r="G77" s="39"/>
+      <c r="H77" s="39"/>
+      <c r="I77" s="39"/>
+      <c r="J77" s="39"/>
+      <c r="K77" s="39"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="29"/>
-      <c r="D78" s="29"/>
-      <c r="E78" s="29"/>
-      <c r="F78" s="29"/>
-      <c r="G78" s="29"/>
-      <c r="H78" s="29"/>
-      <c r="I78" s="29"/>
-      <c r="J78" s="29"/>
-      <c r="K78" s="29"/>
+      <c r="C78" s="39"/>
+      <c r="D78" s="39"/>
+      <c r="E78" s="39"/>
+      <c r="F78" s="39"/>
+      <c r="G78" s="39"/>
+      <c r="H78" s="39"/>
+      <c r="I78" s="39"/>
+      <c r="J78" s="39"/>
+      <c r="K78" s="39"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="29"/>
-      <c r="D79" s="29"/>
-      <c r="E79" s="29"/>
-      <c r="F79" s="29"/>
-      <c r="G79" s="29"/>
-      <c r="H79" s="29"/>
-      <c r="I79" s="29"/>
-      <c r="J79" s="29"/>
-      <c r="K79" s="29"/>
+      <c r="C79" s="39"/>
+      <c r="D79" s="39"/>
+      <c r="E79" s="39"/>
+      <c r="F79" s="39"/>
+      <c r="G79" s="39"/>
+      <c r="H79" s="39"/>
+      <c r="I79" s="39"/>
+      <c r="J79" s="39"/>
+      <c r="K79" s="39"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="29"/>
-      <c r="D80" s="29"/>
-      <c r="E80" s="29"/>
-      <c r="F80" s="29"/>
-      <c r="G80" s="29"/>
-      <c r="H80" s="29"/>
-      <c r="I80" s="29"/>
-      <c r="J80" s="29"/>
-      <c r="K80" s="29"/>
+      <c r="C80" s="39"/>
+      <c r="D80" s="39"/>
+      <c r="E80" s="39"/>
+      <c r="F80" s="39"/>
+      <c r="G80" s="39"/>
+      <c r="H80" s="39"/>
+      <c r="I80" s="39"/>
+      <c r="J80" s="39"/>
+      <c r="K80" s="39"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="29"/>
-      <c r="D81" s="29"/>
-      <c r="E81" s="29"/>
-      <c r="F81" s="29"/>
-      <c r="G81" s="29"/>
-      <c r="H81" s="29"/>
-      <c r="I81" s="29"/>
-      <c r="J81" s="29"/>
-      <c r="K81" s="29"/>
+      <c r="C81" s="39"/>
+      <c r="D81" s="39"/>
+      <c r="E81" s="39"/>
+      <c r="F81" s="39"/>
+      <c r="G81" s="39"/>
+      <c r="H81" s="39"/>
+      <c r="I81" s="39"/>
+      <c r="J81" s="39"/>
+      <c r="K81" s="39"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="29"/>
-      <c r="D82" s="29"/>
-      <c r="E82" s="29"/>
-      <c r="F82" s="29"/>
-      <c r="G82" s="29"/>
-      <c r="H82" s="29"/>
-      <c r="I82" s="29"/>
-      <c r="J82" s="29"/>
-      <c r="K82" s="29"/>
+      <c r="C82" s="39"/>
+      <c r="D82" s="39"/>
+      <c r="E82" s="39"/>
+      <c r="F82" s="39"/>
+      <c r="G82" s="39"/>
+      <c r="H82" s="39"/>
+      <c r="I82" s="39"/>
+      <c r="J82" s="39"/>
+      <c r="K82" s="39"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="29"/>
-      <c r="D83" s="29"/>
-      <c r="E83" s="29"/>
-      <c r="F83" s="29"/>
-      <c r="G83" s="29"/>
-      <c r="H83" s="29"/>
-      <c r="I83" s="29"/>
-      <c r="J83" s="29"/>
-      <c r="K83" s="29"/>
+      <c r="C83" s="39"/>
+      <c r="D83" s="39"/>
+      <c r="E83" s="39"/>
+      <c r="F83" s="39"/>
+      <c r="G83" s="39"/>
+      <c r="H83" s="39"/>
+      <c r="I83" s="39"/>
+      <c r="J83" s="39"/>
+      <c r="K83" s="39"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="29" t="s">
+      <c r="C84" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="D84" s="29">
-        <v>1</v>
-      </c>
-      <c r="E84" s="29"/>
-      <c r="F84" s="29"/>
-      <c r="G84" s="29"/>
-      <c r="H84" s="29"/>
-      <c r="I84" s="29"/>
-      <c r="J84" s="29"/>
-      <c r="K84" s="29"/>
+      <c r="D84" s="39">
+        <v>1</v>
+      </c>
+      <c r="E84" s="39"/>
+      <c r="F84" s="39"/>
+      <c r="G84" s="39"/>
+      <c r="H84" s="39"/>
+      <c r="I84" s="39"/>
+      <c r="J84" s="39"/>
+      <c r="K84" s="39"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="29"/>
-      <c r="D85" s="29"/>
-      <c r="E85" s="29"/>
-      <c r="F85" s="29"/>
-      <c r="G85" s="29"/>
-      <c r="H85" s="29"/>
-      <c r="I85" s="29"/>
-      <c r="J85" s="29"/>
-      <c r="K85" s="29"/>
+      <c r="C85" s="39"/>
+      <c r="D85" s="39"/>
+      <c r="E85" s="39"/>
+      <c r="F85" s="39"/>
+      <c r="G85" s="39"/>
+      <c r="H85" s="39"/>
+      <c r="I85" s="39"/>
+      <c r="J85" s="39"/>
+      <c r="K85" s="39"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2899,96 +2922,97 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="E13:W33"/>
+  <dimension ref="E13:W38"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="6" max="6" width="25.0909090909091" customWidth="1"/>
+    <col min="8" max="8" width="27" customWidth="1"/>
     <col min="9" max="9" width="43.7272727272727" customWidth="1"/>
     <col min="12" max="12" width="10.2727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="13" spans="5:21">
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="16"/>
-      <c r="U13" s="16"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
     </row>
     <row r="14" spans="5:21">
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="16"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
     </row>
     <row r="15" spans="5:21">
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="16"/>
-      <c r="S15" s="16"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="16"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
     </row>
     <row r="16" spans="5:21">
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="16"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
     </row>
     <row r="17" spans="5:23">
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -3005,11 +3029,11 @@
       <c r="W17" s="1"/>
     </row>
     <row r="18" spans="5:23">
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -3026,11 +3050,11 @@
       <c r="W18" s="1"/>
     </row>
     <row r="19" spans="5:23">
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -3047,11 +3071,11 @@
       <c r="W19" s="1"/>
     </row>
     <row r="20" spans="5:23">
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -3068,11 +3092,11 @@
       <c r="W20" s="1"/>
     </row>
     <row r="21" spans="5:23">
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -3089,11 +3113,11 @@
       <c r="W21" s="1"/>
     </row>
     <row r="22" spans="5:23">
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -3110,11 +3134,11 @@
       <c r="W22" s="1"/>
     </row>
     <row r="23" spans="5:23">
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -3131,11 +3155,11 @@
       <c r="W23" s="1"/>
     </row>
     <row r="24" spans="5:23">
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -3168,165 +3192,313 @@
       <c r="W25" s="1"/>
     </row>
     <row r="26" spans="5:23">
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
+      <c r="F26" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="25"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="25"/>
+      <c r="P26" s="25"/>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="25"/>
+      <c r="U26" s="25"/>
+      <c r="V26" s="25"/>
       <c r="W26" s="1"/>
     </row>
     <row r="27" spans="5:23">
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="25"/>
+      <c r="S27" s="25"/>
+      <c r="T27" s="25"/>
+      <c r="U27" s="25"/>
+      <c r="V27" s="25"/>
       <c r="W27" s="1"/>
     </row>
     <row r="28" spans="5:23">
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
+      <c r="M28" s="25"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="25"/>
+      <c r="P28" s="25"/>
+      <c r="Q28" s="25"/>
+      <c r="R28" s="25"/>
+      <c r="S28" s="25"/>
+      <c r="T28" s="25"/>
+      <c r="U28" s="25"/>
+      <c r="V28" s="25"/>
       <c r="W28" s="1"/>
     </row>
     <row r="29" spans="5:23">
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="M29" s="25"/>
+      <c r="N29" s="25"/>
+      <c r="O29" s="25"/>
+      <c r="P29" s="25"/>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="25"/>
+      <c r="S29" s="25"/>
+      <c r="T29" s="25"/>
+      <c r="U29" s="25"/>
+      <c r="V29" s="25"/>
       <c r="W29" s="1"/>
     </row>
     <row r="30" ht="15.25" spans="5:23">
-      <c r="F30" t="s">
-        <v>57</v>
-      </c>
-      <c r="G30" t="s">
+      <c r="F30" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="G30" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="I30" t="s">
-        <v>58</v>
-      </c>
-      <c r="J30" t="s">
+      <c r="I30" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="J30" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="K30" t="s">
-        <v>59</v>
-      </c>
-      <c r="L30" t="s">
-        <v>1</v>
-      </c>
-      <c r="M30" t="s">
-        <v>60</v>
-      </c>
-      <c r="N30" t="s">
+      <c r="K30" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="O30" t="s">
+      <c r="L30" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="M30" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="P30" t="s">
+      <c r="N30" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="O30" s="25" t="s">
         <v>64</v>
       </c>
+      <c r="P30" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q30" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="R30" s="25"/>
+      <c r="S30" s="25"/>
+      <c r="T30" s="25"/>
+      <c r="U30" s="25"/>
+      <c r="V30" s="25"/>
     </row>
     <row r="31" ht="16" spans="5:23">
-      <c r="F31" t="s">
-        <v>65</v>
-      </c>
-      <c r="G31" t="s">
-        <v>66</v>
-      </c>
-      <c r="H31" s="17" t="s">
+      <c r="F31" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="I31" t="s">
+      <c r="G31" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="J31" t="s">
-        <v>17</v>
-      </c>
-      <c r="K31" t="s">
-        <v>17</v>
-      </c>
-      <c r="M31">
+      <c r="H31" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="I31" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="25">
         <v>-0.25</v>
       </c>
-      <c r="O31">
+      <c r="N31" s="25"/>
+      <c r="O31" s="25">
         <v>0</v>
       </c>
-      <c r="P31">
+      <c r="P31" s="25">
         <v>3</v>
       </c>
-      <c r="Q31" t="s">
-        <v>69</v>
-      </c>
+      <c r="Q31" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="R31" s="25"/>
+      <c r="S31" s="25"/>
+      <c r="T31" s="25"/>
+      <c r="U31" s="25"/>
+      <c r="V31" s="25"/>
     </row>
     <row r="32" ht="15.25" spans="5:23">
-      <c r="K32" t="s">
-        <v>70</v>
-      </c>
-      <c r="N32" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="9:13">
-      <c r="I33" t="s">
-        <v>71</v>
-      </c>
-      <c r="J33" t="s">
-        <v>17</v>
-      </c>
-      <c r="K33" t="s">
-        <v>17</v>
-      </c>
-      <c r="M33">
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="25">
         <v>-0.1</v>
       </c>
+      <c r="N32" s="25"/>
+      <c r="O32" s="25"/>
+      <c r="P32" s="25"/>
+      <c r="Q32" s="25"/>
+      <c r="R32" s="25"/>
+      <c r="S32" s="25"/>
+      <c r="T32" s="25"/>
+      <c r="U32" s="25"/>
+      <c r="V32" s="25"/>
+    </row>
+    <row r="33" spans="6:22">
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
+      <c r="K33" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="26">
+        <v>1</v>
+      </c>
+      <c r="O33" s="25"/>
+      <c r="P33" s="25"/>
+      <c r="Q33" s="25"/>
+      <c r="R33" s="25"/>
+      <c r="S33" s="25"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="25"/>
+      <c r="V33" s="25"/>
+    </row>
+    <row r="34" spans="6:22">
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
+      <c r="M34" s="25"/>
+      <c r="N34" s="25"/>
+      <c r="O34" s="25"/>
+      <c r="P34" s="25"/>
+      <c r="Q34" s="25"/>
+      <c r="R34" s="25"/>
+      <c r="S34" s="25"/>
+      <c r="T34" s="25"/>
+      <c r="U34" s="25"/>
+      <c r="V34" s="25"/>
+    </row>
+    <row r="35" spans="6:22">
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
+      <c r="M35" s="25"/>
+      <c r="N35" s="25"/>
+      <c r="O35" s="25"/>
+      <c r="P35" s="25"/>
+      <c r="Q35" s="25"/>
+      <c r="R35" s="25"/>
+      <c r="S35" s="25"/>
+      <c r="T35" s="25"/>
+      <c r="U35" s="25"/>
+      <c r="V35" s="25"/>
+    </row>
+    <row r="36" spans="6:22">
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="25"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="25"/>
+      <c r="M36" s="25"/>
+      <c r="N36" s="25"/>
+      <c r="O36" s="25"/>
+      <c r="P36" s="25"/>
+      <c r="Q36" s="25"/>
+      <c r="R36" s="25"/>
+      <c r="S36" s="25"/>
+      <c r="T36" s="25"/>
+      <c r="U36" s="25"/>
+      <c r="V36" s="25"/>
+    </row>
+    <row r="37" spans="6:22">
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="25"/>
+      <c r="K37" s="25"/>
+      <c r="L37" s="25"/>
+      <c r="M37" s="25"/>
+      <c r="N37" s="25"/>
+      <c r="O37" s="25"/>
+      <c r="P37" s="25"/>
+      <c r="Q37" s="25"/>
+      <c r="R37" s="25"/>
+      <c r="S37" s="25"/>
+      <c r="T37" s="25"/>
+      <c r="U37" s="25"/>
+      <c r="V37" s="25"/>
+    </row>
+    <row r="38" spans="6:22">
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="25"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="25"/>
+      <c r="L38" s="25"/>
+      <c r="M38" s="25"/>
+      <c r="N38" s="25"/>
+      <c r="O38" s="25"/>
+      <c r="P38" s="25"/>
+      <c r="Q38" s="25"/>
+      <c r="R38" s="25"/>
+      <c r="S38" s="25"/>
+      <c r="T38" s="25"/>
+      <c r="U38" s="25"/>
+      <c r="V38" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3348,270 +3520,270 @@
   <sheetData>
     <row r="2" spans="2:14">
       <c r="B2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="2:14">
       <c r="B3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="2:14">
       <c r="H4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="2:14">
-      <c r="D8" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="4" t="s">
+      <c r="D8" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H8" s="4" t="s">
+      <c r="G8" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="M8" s="4" t="s">
+      <c r="J8" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="N8" s="4" t="s">
-        <v>64</v>
+      <c r="K8" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="M8" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="N8" s="14" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="2:14">
-      <c r="D9" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H9" s="5" t="s">
+      <c r="D9" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="F9" s="15" t="s">
         <v>85</v>
       </c>
+      <c r="G9" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>88</v>
+      </c>
       <c r="J9">
         <v>1</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="15">
         <v>1.25</v>
       </c>
       <c r="L9">
         <v>0.05</v>
       </c>
-      <c r="M9" s="5">
-        <v>1</v>
-      </c>
-      <c r="N9" s="5"/>
+      <c r="M9" s="15">
+        <v>1</v>
+      </c>
+      <c r="N9" s="15"/>
     </row>
     <row r="10" spans="2:14">
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="H10" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>85</v>
+      <c r="I10" s="15" t="s">
+        <v>88</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10" s="15">
         <v>1.11</v>
       </c>
       <c r="L10">
         <v>0.05</v>
       </c>
-      <c r="M10" s="5">
-        <v>1</v>
-      </c>
-      <c r="N10" s="5"/>
+      <c r="M10" s="15">
+        <v>1</v>
+      </c>
+      <c r="N10" s="15"/>
     </row>
     <row r="11" spans="2:14">
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="I11" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>85</v>
-      </c>
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11" s="15">
         <v>1.15</v>
       </c>
       <c r="L11">
         <v>0.08</v>
       </c>
-      <c r="M11" s="5">
-        <v>1</v>
-      </c>
-      <c r="N11" s="5"/>
+      <c r="M11" s="15">
+        <v>1</v>
+      </c>
+      <c r="N11" s="15"/>
     </row>
     <row r="12" ht="16" spans="2:14">
-      <c r="D12" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>85</v>
+      <c r="D12" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>88</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12" s="15">
         <v>1.12</v>
       </c>
       <c r="L12">
         <v>0.03</v>
       </c>
-      <c r="M12" s="5">
-        <v>1</v>
-      </c>
-      <c r="N12" s="5"/>
+      <c r="M12" s="15">
+        <v>1</v>
+      </c>
+      <c r="N12" s="15"/>
     </row>
     <row r="13" spans="2:14">
-      <c r="D13" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>85</v>
+      <c r="D13" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>88</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13" s="5">
+      <c r="K13" s="15">
         <v>1.2</v>
       </c>
       <c r="L13">
         <v>0.1</v>
       </c>
-      <c r="M13" s="5">
-        <v>1</v>
-      </c>
-      <c r="N13" s="5"/>
+      <c r="M13" s="15">
+        <v>1</v>
+      </c>
+      <c r="N13" s="15"/>
     </row>
     <row r="14" spans="2:14">
-      <c r="D14" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>85</v>
+      <c r="D14" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>88</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K14" s="15">
         <v>1.06</v>
       </c>
       <c r="L14">
         <v>0.15</v>
       </c>
-      <c r="M14" s="5">
-        <v>1</v>
-      </c>
-      <c r="N14" s="5"/>
+      <c r="M14" s="15">
+        <v>1</v>
+      </c>
+      <c r="N14" s="15"/>
     </row>
     <row r="15" spans="2:14">
-      <c r="D15" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>85</v>
+      <c r="D15" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>88</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K15" s="15">
         <v>1.06</v>
       </c>
       <c r="L15">
         <v>0.3</v>
       </c>
-      <c r="M15" s="5">
-        <v>1</v>
-      </c>
-      <c r="N15" s="5"/>
+      <c r="M15" s="15">
+        <v>1</v>
+      </c>
+      <c r="N15" s="15"/>
     </row>
     <row r="16" ht="16" spans="2:14">
-      <c r="D16" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>99</v>
+      <c r="D16" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="G16" t="str">
         <f>G15</f>
@@ -3621,8 +3793,8 @@
         <f>H15</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I16" s="5" t="s">
-        <v>85</v>
+      <c r="I16" s="15" t="s">
+        <v>88</v>
       </c>
       <c r="J16">
         <f t="shared" ref="J16:L16" si="0">J12</f>
@@ -3642,11 +3814,11 @@
       </c>
     </row>
     <row r="17" ht="16" spans="4:14">
-      <c r="D17" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>101</v>
+      <c r="D17" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" ref="G17:M17" si="1">G16</f>
@@ -3656,8 +3828,8 @@
         <f t="shared" si="1"/>
         <v>2025, 2150</v>
       </c>
-      <c r="I17" s="5" t="s">
-        <v>85</v>
+      <c r="I17" s="15" t="s">
+        <v>88</v>
       </c>
       <c r="J17">
         <f t="shared" si="1"/>
@@ -3677,11 +3849,11 @@
       </c>
     </row>
     <row r="18" ht="16" spans="4:14">
-      <c r="D18" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>103</v>
+      <c r="D18" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="G18" t="str">
         <f>G17</f>
@@ -3691,8 +3863,8 @@
         <f>H17</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I18" s="5" t="s">
-        <v>85</v>
+      <c r="I18" s="15" t="s">
+        <v>88</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -3708,604 +3880,604 @@
       </c>
     </row>
     <row r="27" spans="4:14">
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+      <c r="N27" s="16"/>
     </row>
     <row r="28" spans="4:14">
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
     </row>
     <row r="29" spans="4:14">
-      <c r="D29" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F29" s="7" t="s">
+      <c r="D29" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F29" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H29" s="7" t="s">
+      <c r="G29" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H29" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="I29" s="7" t="s">
+      <c r="I29" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="J29" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="L29" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="M29" s="7" t="s">
+      <c r="J29" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="N29" s="7" t="s">
-        <v>64</v>
+      <c r="K29" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="N29" s="16" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="30" ht="16" spans="4:14">
-      <c r="D30" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I30" s="7" t="s">
+      <c r="D30" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="J30" s="7">
-        <v>1</v>
-      </c>
-      <c r="K30" s="7">
-        <v>1</v>
-      </c>
-      <c r="L30" s="7">
+      <c r="E30" s="16"/>
+      <c r="F30" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="J30" s="16">
+        <v>1</v>
+      </c>
+      <c r="K30" s="16">
+        <v>1</v>
+      </c>
+      <c r="L30" s="16">
         <v>0.01</v>
       </c>
-      <c r="M30" s="7">
-        <v>1</v>
-      </c>
-      <c r="N30" s="7"/>
+      <c r="M30" s="16">
+        <v>1</v>
+      </c>
+      <c r="N30" s="16"/>
     </row>
     <row r="31" ht="16" spans="4:14">
-      <c r="D31" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="E31" s="7"/>
-      <c r="F31" s="9" t="s">
+      <c r="D31" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="16"/>
+      <c r="F31" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H31" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="G31" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="J31" s="7">
-        <v>1</v>
-      </c>
-      <c r="K31" s="7">
-        <v>1</v>
-      </c>
-      <c r="L31" s="7">
+      <c r="I31" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="J31" s="16">
+        <v>1</v>
+      </c>
+      <c r="K31" s="16">
+        <v>1</v>
+      </c>
+      <c r="L31" s="16">
         <f t="shared" ref="L31:L36" si="2">L30</f>
         <v>0.01</v>
       </c>
-      <c r="M31" s="7">
-        <v>1</v>
-      </c>
-      <c r="N31" s="7"/>
+      <c r="M31" s="16">
+        <v>1</v>
+      </c>
+      <c r="N31" s="16"/>
     </row>
     <row r="32" ht="16" spans="4:14">
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="E32" s="16"/>
+      <c r="F32" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="I32" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="E32" s="7"/>
-      <c r="F32" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="J32" s="7">
-        <v>1</v>
-      </c>
-      <c r="K32" s="7">
-        <v>1</v>
-      </c>
-      <c r="L32" s="7">
+      <c r="J32" s="16">
+        <v>1</v>
+      </c>
+      <c r="K32" s="16">
+        <v>1</v>
+      </c>
+      <c r="L32" s="16">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M32" s="7">
-        <v>1</v>
-      </c>
-      <c r="N32" s="7"/>
+      <c r="M32" s="16">
+        <v>1</v>
+      </c>
+      <c r="N32" s="16"/>
     </row>
     <row r="33" ht="16" spans="4:14">
-      <c r="D33" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="J33" s="7">
-        <v>1</v>
-      </c>
-      <c r="K33" s="7">
+      <c r="D33" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E33" s="16"/>
+      <c r="F33" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="J33" s="16">
+        <v>1</v>
+      </c>
+      <c r="K33" s="16">
         <f>K32</f>
         <v>1</v>
       </c>
-      <c r="L33" s="7">
+      <c r="L33" s="16">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M33" s="7">
-        <v>1</v>
-      </c>
-      <c r="N33" s="7"/>
+      <c r="M33" s="16">
+        <v>1</v>
+      </c>
+      <c r="N33" s="16"/>
     </row>
     <row r="34" ht="16" spans="4:14">
-      <c r="D34" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="J34" s="7">
-        <v>1</v>
-      </c>
-      <c r="K34" s="7">
+      <c r="D34" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="E34" s="16"/>
+      <c r="F34" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="J34" s="16">
+        <v>1</v>
+      </c>
+      <c r="K34" s="16">
         <f>K33</f>
         <v>1</v>
       </c>
-      <c r="L34" s="7">
+      <c r="L34" s="16">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M34" s="7">
-        <v>1</v>
-      </c>
-      <c r="N34" s="7"/>
+      <c r="M34" s="16">
+        <v>1</v>
+      </c>
+      <c r="N34" s="16"/>
     </row>
     <row r="35" ht="16" spans="4:14">
-      <c r="D35" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E35" s="7"/>
-      <c r="F35" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="J35" s="7">
-        <v>1</v>
-      </c>
-      <c r="K35" s="7">
+      <c r="D35" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E35" s="16"/>
+      <c r="F35" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="I35" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="J35" s="16">
+        <v>1</v>
+      </c>
+      <c r="K35" s="16">
         <f>K34</f>
         <v>1</v>
       </c>
-      <c r="L35" s="7">
+      <c r="L35" s="16">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M35" s="7">
-        <v>1</v>
-      </c>
-      <c r="N35" s="7"/>
+      <c r="M35" s="16">
+        <v>1</v>
+      </c>
+      <c r="N35" s="16"/>
     </row>
     <row r="36" ht="16" spans="4:14">
-      <c r="D36" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="E36" s="7"/>
-      <c r="F36" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="J36" s="7">
-        <v>1</v>
-      </c>
-      <c r="K36" s="7">
+      <c r="D36" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="E36" s="16"/>
+      <c r="F36" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="I36" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="J36" s="16">
+        <v>1</v>
+      </c>
+      <c r="K36" s="16">
         <f>K35</f>
         <v>1</v>
       </c>
-      <c r="L36" s="7">
+      <c r="L36" s="16">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M36" s="7">
-        <v>1</v>
-      </c>
-      <c r="N36" s="7"/>
+      <c r="M36" s="16">
+        <v>1</v>
+      </c>
+      <c r="N36" s="16"/>
     </row>
     <row r="37" ht="16" spans="4:14">
-      <c r="D37" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="E37" s="10"/>
-      <c r="F37" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="G37" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J37" s="10">
-        <v>1</v>
-      </c>
-      <c r="K37" s="10">
-        <v>1</v>
-      </c>
-      <c r="L37" s="10">
+      <c r="D37" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="E37" s="19"/>
+      <c r="F37" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="H37" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="I37" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="J37" s="19">
+        <v>1</v>
+      </c>
+      <c r="K37" s="19">
+        <v>1</v>
+      </c>
+      <c r="L37" s="19">
         <v>0.01</v>
       </c>
-      <c r="M37" s="10">
-        <v>1</v>
-      </c>
-      <c r="N37" s="7"/>
+      <c r="M37" s="19">
+        <v>1</v>
+      </c>
+      <c r="N37" s="16"/>
     </row>
     <row r="38" ht="16" spans="4:14">
-      <c r="D38" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="E38" s="10"/>
-      <c r="F38" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="G38" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J38" s="10">
-        <v>1</v>
-      </c>
-      <c r="K38" s="10">
-        <v>1</v>
-      </c>
-      <c r="L38" s="10">
+      <c r="D38" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="E38" s="19"/>
+      <c r="F38" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="I38" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="J38" s="19">
+        <v>1</v>
+      </c>
+      <c r="K38" s="19">
+        <v>1</v>
+      </c>
+      <c r="L38" s="19">
         <f t="shared" ref="L38:L43" si="3">L37</f>
         <v>0.01</v>
       </c>
-      <c r="M38" s="10">
-        <v>1</v>
-      </c>
-      <c r="N38" s="7"/>
+      <c r="M38" s="19">
+        <v>1</v>
+      </c>
+      <c r="N38" s="16"/>
     </row>
     <row r="39" ht="16" spans="4:14">
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E39" s="19"/>
+      <c r="F39" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="H39" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="E39" s="10"/>
-      <c r="F39" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J39" s="10">
-        <v>1</v>
-      </c>
-      <c r="K39" s="10">
-        <v>1</v>
-      </c>
-      <c r="L39" s="10">
+      <c r="I39" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="J39" s="19">
+        <v>1</v>
+      </c>
+      <c r="K39" s="19">
+        <v>1</v>
+      </c>
+      <c r="L39" s="19">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M39" s="10">
-        <v>1</v>
-      </c>
-      <c r="N39" s="7"/>
+      <c r="M39" s="19">
+        <v>1</v>
+      </c>
+      <c r="N39" s="16"/>
     </row>
     <row r="40" ht="16" spans="4:14">
-      <c r="D40" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="E40" s="10"/>
-      <c r="F40" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J40" s="10">
-        <v>1</v>
-      </c>
-      <c r="K40" s="10">
+      <c r="D40" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E40" s="19"/>
+      <c r="F40" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="G40" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="I40" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="J40" s="19">
+        <v>1</v>
+      </c>
+      <c r="K40" s="19">
         <f>K39</f>
         <v>1</v>
       </c>
-      <c r="L40" s="10">
+      <c r="L40" s="19">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M40" s="10">
-        <v>1</v>
-      </c>
-      <c r="N40" s="7"/>
+      <c r="M40" s="19">
+        <v>1</v>
+      </c>
+      <c r="N40" s="16"/>
     </row>
     <row r="41" ht="16" spans="4:14">
-      <c r="D41" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="E41" s="10"/>
-      <c r="F41" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="I41" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J41" s="10">
-        <v>1</v>
-      </c>
-      <c r="K41" s="10">
+      <c r="D41" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E41" s="19"/>
+      <c r="F41" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="G41" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="H41" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="I41" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="J41" s="19">
+        <v>1</v>
+      </c>
+      <c r="K41" s="19">
         <f>K40</f>
         <v>1</v>
       </c>
-      <c r="L41" s="10">
+      <c r="L41" s="19">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M41" s="10">
-        <v>1</v>
-      </c>
-      <c r="N41" s="7"/>
+      <c r="M41" s="19">
+        <v>1</v>
+      </c>
+      <c r="N41" s="16"/>
     </row>
     <row r="42" ht="16" spans="4:14">
-      <c r="D42" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="E42" s="10"/>
-      <c r="F42" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="I42" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J42" s="10">
-        <v>1</v>
-      </c>
-      <c r="K42" s="10">
+      <c r="D42" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="E42" s="19"/>
+      <c r="F42" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="G42" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="H42" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="I42" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="J42" s="19">
+        <v>1</v>
+      </c>
+      <c r="K42" s="19">
         <f>K41</f>
         <v>1</v>
       </c>
-      <c r="L42" s="10">
+      <c r="L42" s="19">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M42" s="10">
-        <v>1</v>
-      </c>
-      <c r="N42" s="7"/>
+      <c r="M42" s="19">
+        <v>1</v>
+      </c>
+      <c r="N42" s="16"/>
     </row>
     <row r="43" ht="16" spans="4:14">
-      <c r="D43" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="E43" s="10"/>
-      <c r="F43" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="I43" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J43" s="10">
-        <v>1</v>
-      </c>
-      <c r="K43" s="10">
+      <c r="D43" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="E43" s="19"/>
+      <c r="F43" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="G43" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="H43" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="I43" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="J43" s="19">
+        <v>1</v>
+      </c>
+      <c r="K43" s="19">
         <f>K42</f>
         <v>1</v>
       </c>
-      <c r="L43" s="10">
+      <c r="L43" s="19">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M43" s="10">
-        <v>1</v>
-      </c>
-      <c r="N43" s="7"/>
+      <c r="M43" s="19">
+        <v>1</v>
+      </c>
+      <c r="N43" s="16"/>
     </row>
     <row r="44" spans="4:14">
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="7"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
+      <c r="K44" s="19"/>
+      <c r="L44" s="19"/>
+      <c r="M44" s="19"/>
+      <c r="N44" s="16"/>
     </row>
     <row r="45" spans="4:14">
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="7"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="23"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="16"/>
     </row>
     <row r="46" spans="4:14">
-      <c r="N46" s="7"/>
+      <c r="N46" s="16"/>
     </row>
     <row r="47" spans="4:14">
-      <c r="N47" s="7"/>
+      <c r="N47" s="16"/>
     </row>
     <row r="48" spans="4:14">
-      <c r="N48" s="7"/>
+      <c r="N48" s="16"/>
     </row>
     <row r="49" spans="4:14">
-      <c r="N49" s="7"/>
+      <c r="N49" s="16"/>
     </row>
     <row r="50" spans="4:14">
-      <c r="N50" s="7"/>
+      <c r="N50" s="16"/>
     </row>
     <row r="51" spans="4:14">
-      <c r="N51" s="7"/>
+      <c r="N51" s="16"/>
     </row>
     <row r="52" spans="4:14">
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
-      <c r="N52" s="7"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="16"/>
+      <c r="I52" s="16"/>
+      <c r="J52" s="16"/>
+      <c r="K52" s="16"/>
+      <c r="L52" s="16"/>
+      <c r="M52" s="16"/>
+      <c r="N52" s="16"/>
     </row>
     <row r="53" spans="4:14">
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="7"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="7"/>
-      <c r="K53" s="7"/>
-      <c r="L53" s="7"/>
-      <c r="M53" s="7"/>
-      <c r="N53" s="7"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="16"/>
+      <c r="H53" s="16"/>
+      <c r="I53" s="16"/>
+      <c r="J53" s="16"/>
+      <c r="K53" s="16"/>
+      <c r="L53" s="16"/>
+      <c r="M53" s="16"/>
+      <c r="N53" s="16"/>
     </row>
     <row r="54" spans="4:14">
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
-      <c r="K54" s="7"/>
-      <c r="L54" s="7"/>
-      <c r="M54" s="7"/>
-      <c r="N54" s="7"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
+      <c r="H54" s="16"/>
+      <c r="I54" s="16"/>
+      <c r="J54" s="16"/>
+      <c r="K54" s="16"/>
+      <c r="L54" s="16"/>
+      <c r="M54" s="16"/>
+      <c r="N54" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4316,17 +4488,22 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="F9:R38"/>
+  <dimension ref="F9:AR56"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="6" max="6" width="24.5454545454545" customWidth="1"/>
-    <col min="8" max="8" width="49.4545454545455" customWidth="1"/>
+    <col min="8" max="8" width="56.3636363636364" customWidth="1"/>
     <col min="9" max="9" width="43.7272727272727" customWidth="1"/>
+    <col min="14" max="14" width="12.8181818181818" customWidth="1"/>
+    <col min="15" max="15" width="40.1818181818182" customWidth="1"/>
+    <col min="16" max="16" width="12.6363636363636" customWidth="1"/>
+    <col min="17" max="17" width="12.3636363636364" customWidth="1"/>
+    <col min="48" max="48" width="12.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="9" spans="6:18">
       <c r="F9" t="s">
-        <v>135</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="6:18">
@@ -4341,8 +4518,8 @@
     </row>
     <row r="12" spans="6:18">
       <c r="K12" s="1"/>
-      <c r="L12" s="2" t="s">
-        <v>136</v>
+      <c r="L12" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -4353,7 +4530,7 @@
     </row>
     <row r="13" spans="6:18">
       <c r="F13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G13" t="s">
         <v>25</v>
@@ -4362,44 +4539,41 @@
         <v>48</v>
       </c>
       <c r="I13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J13" t="s">
         <v>33</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>1</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R13" s="1"/>
     </row>
     <row r="14" spans="6:18">
       <c r="F14" t="s">
-        <v>139</v>
-      </c>
-      <c r="G14"/>
+        <v>141</v>
+      </c>
       <c r="H14" t="s">
-        <v>140</v>
-      </c>
-      <c r="I14"/>
-      <c r="J14"/>
+        <v>142</v>
+      </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1">
@@ -4417,14 +4591,14 @@
     </row>
     <row r="15" spans="6:18">
       <c r="H15" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
-      <c r="M15" s="2">
+      <c r="M15" s="1">
         <v>-1</v>
       </c>
-      <c r="N15" s="2"/>
+      <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
@@ -4532,8 +4706,8 @@
     </row>
     <row r="26" spans="6:18">
       <c r="K26" s="1"/>
-      <c r="L26" s="2" t="s">
-        <v>136</v>
+      <c r="L26" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -4544,7 +4718,7 @@
     </row>
     <row r="27" spans="6:18">
       <c r="F27" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G27" t="s">
         <v>25</v>
@@ -4553,40 +4727,40 @@
         <v>48</v>
       </c>
       <c r="I27" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J27" t="s">
         <v>33</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>1</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R27" s="1"/>
     </row>
     <row r="28" ht="16" spans="6:18">
       <c r="F28" t="s">
-        <v>142</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -4605,14 +4779,14 @@
     </row>
     <row r="29" spans="6:18">
       <c r="H29" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
-      <c r="M29" s="2">
-        <v>1</v>
-      </c>
-      <c r="N29" s="2"/>
+      <c r="M29" s="1">
+        <v>1</v>
+      </c>
+      <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
@@ -4670,8 +4844,8 @@
     </row>
     <row r="35" spans="6:18">
       <c r="K35" s="1"/>
-      <c r="L35" s="2" t="s">
-        <v>136</v>
+      <c r="L35" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
@@ -4681,7 +4855,7 @@
     </row>
     <row r="36" spans="6:18">
       <c r="F36" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G36" t="s">
         <v>25</v>
@@ -4690,39 +4864,39 @@
         <v>48</v>
       </c>
       <c r="I36" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J36" t="s">
         <v>33</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>1</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="6:18">
       <c r="F37" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H37" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -4740,17 +4914,211 @@
     </row>
     <row r="38" spans="6:18">
       <c r="H38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
-      <c r="M38" s="2">
-        <v>1</v>
-      </c>
-      <c r="N38" s="2"/>
+      <c r="M38" s="1">
+        <v>1</v>
+      </c>
+      <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
+    </row>
+    <row r="51" spans="6:44">
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="5"/>
+      <c r="Q51" s="5"/>
+      <c r="R51" s="6"/>
+      <c r="S51" s="6"/>
+      <c r="T51" s="6"/>
+      <c r="U51" s="6"/>
+      <c r="V51" s="6"/>
+      <c r="W51" s="6"/>
+      <c r="X51" s="6"/>
+      <c r="Y51" s="6"/>
+      <c r="Z51" s="6"/>
+      <c r="AA51" s="6"/>
+      <c r="AB51" s="6"/>
+      <c r="AC51" s="6"/>
+      <c r="AD51" s="6"/>
+      <c r="AE51" s="6"/>
+      <c r="AF51" s="6"/>
+      <c r="AG51" s="6"/>
+      <c r="AH51" s="6"/>
+      <c r="AI51" s="6"/>
+      <c r="AJ51" s="6"/>
+      <c r="AK51" s="6"/>
+      <c r="AL51" s="6"/>
+      <c r="AM51" s="6"/>
+    </row>
+    <row r="52" ht="16" spans="6:44">
+      <c r="G52" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N52" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="O52" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q52" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="S52" s="6"/>
+      <c r="T52" s="6"/>
+      <c r="U52" s="6"/>
+      <c r="V52" s="6"/>
+      <c r="W52" s="6"/>
+      <c r="X52" s="6"/>
+      <c r="Y52" s="6"/>
+      <c r="Z52" s="6"/>
+      <c r="AA52" s="6"/>
+      <c r="AB52" s="6"/>
+      <c r="AC52" s="6"/>
+      <c r="AD52" s="6"/>
+      <c r="AE52" s="6"/>
+      <c r="AF52" s="6"/>
+      <c r="AG52" s="6"/>
+      <c r="AH52" s="6"/>
+      <c r="AI52" s="6"/>
+      <c r="AJ52" s="6"/>
+      <c r="AK52" s="6"/>
+      <c r="AL52" s="6"/>
+      <c r="AM52" s="6"/>
+      <c r="AN52" s="6"/>
+      <c r="AO52" s="6"/>
+      <c r="AP52" s="6"/>
+      <c r="AQ52" s="6"/>
+      <c r="AR52" s="6"/>
+    </row>
+    <row r="53" ht="16" spans="6:44">
+      <c r="F53" s="9"/>
+      <c r="G53" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I53" s="10">
+        <v>2023</v>
+      </c>
+      <c r="J53" s="11">
+        <v>-1</v>
+      </c>
+      <c r="K53" s="12"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="N53" s="3"/>
+      <c r="O53" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="P53" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>10</v>
+      </c>
+      <c r="R53" s="6"/>
+      <c r="S53" s="6"/>
+      <c r="T53" s="6"/>
+      <c r="U53" s="6"/>
+      <c r="V53" s="6"/>
+      <c r="W53" s="6"/>
+      <c r="X53" s="6"/>
+      <c r="Y53" s="6"/>
+      <c r="Z53" s="6"/>
+      <c r="AA53" s="6"/>
+      <c r="AB53" s="6"/>
+      <c r="AC53" s="6"/>
+      <c r="AD53" s="6"/>
+      <c r="AE53" s="6"/>
+      <c r="AF53" s="6"/>
+      <c r="AG53" s="6"/>
+      <c r="AH53" s="6"/>
+      <c r="AI53" s="6"/>
+      <c r="AJ53" s="6"/>
+      <c r="AK53" s="6"/>
+      <c r="AL53" s="6"/>
+      <c r="AM53" s="6"/>
+      <c r="AN53" s="6"/>
+      <c r="AO53" s="6"/>
+      <c r="AP53" s="6"/>
+      <c r="AQ53" s="6"/>
+      <c r="AR53" s="6"/>
+    </row>
+    <row r="54" spans="6:44">
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+      <c r="O54" s="3"/>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="6:44">
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="6:44">
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -245,7 +245,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="158">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -707,6 +707,9 @@
   </si>
   <si>
     <t>UC_ACT</t>
+  </si>
+  <si>
+    <t>UC_COMNET</t>
   </si>
   <si>
     <t>UCE_4</t>
@@ -944,17 +947,17 @@
       <charset val="0"/>
     </font>
     <font>
-      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
-    <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -1190,12 +1193,21 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFE4E7EB"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1331,7 +1343,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1343,34 +1355,34 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1456,10 +1468,10 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1470,8 +1482,10 @@
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="51" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="51" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1497,9 +1511,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -2048,7 +2060,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="34">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -2162,10 +2174,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="40"/>
+      <c r="K10" s="38"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="40"/>
+      <c r="K11" s="38"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2189,8 +2201,8 @@
       <c r="C5" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
       <c r="F5" s="16"/>
     </row>
     <row r="6" spans="2:13">
@@ -2206,19 +2218,19 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="29"/>
+      <c r="K6" s="27"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="28">
         <v>10</v>
       </c>
     </row>
@@ -2226,17 +2238,17 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="28">
         <v>7</v>
       </c>
-      <c r="L8" s="28"/>
-      <c r="M8" s="28"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
     </row>
     <row r="9" ht="16" spans="2:13">
       <c r="B9" t="s">
@@ -2245,10 +2257,10 @@
       <c r="C9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="D9" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="28">
         <v>10</v>
       </c>
     </row>
@@ -2256,17 +2268,17 @@
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="28">
         <v>8</v>
       </c>
-      <c r="K10" s="31"/>
-      <c r="L10" s="32"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="30"/>
     </row>
     <row r="11" ht="16" spans="2:13">
       <c r="B11" t="s">
@@ -2275,10 +2287,10 @@
       <c r="C11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="26">
         <v>1.5</v>
       </c>
     </row>
@@ -2289,10 +2301,10 @@
       <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="26">
         <v>1.5</v>
       </c>
     </row>
@@ -2303,7 +2315,7 @@
       <c r="C13" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="26" t="s">
         <v>35</v>
       </c>
       <c r="E13" s="16">
@@ -2317,7 +2329,7 @@
       <c r="C14" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="26" t="s">
         <v>35</v>
       </c>
       <c r="E14" s="16">
@@ -2331,7 +2343,7 @@
       <c r="C15" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="26" t="s">
         <v>35</v>
       </c>
       <c r="E15" s="16">
@@ -2342,13 +2354,13 @@
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="28" t="s">
+      <c r="D16" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="31">
         <v>12</v>
       </c>
     </row>
@@ -2356,13 +2368,13 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="34" t="s">
+      <c r="D17" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="33">
         <v>0.2</v>
       </c>
       <c r="F17" s="16"/>
@@ -2371,13 +2383,13 @@
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="34" t="s">
+      <c r="D18" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="35">
+      <c r="E18" s="33">
         <v>0.2</v>
       </c>
       <c r="F18" s="16"/>
@@ -2389,10 +2401,10 @@
       <c r="C19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="34" t="s">
+      <c r="D19" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="35">
+      <c r="E19" s="33">
         <v>0.2</v>
       </c>
       <c r="F19" s="16"/>
@@ -2401,13 +2413,13 @@
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="34" t="s">
+      <c r="D20" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="35">
+      <c r="E20" s="33">
         <v>0.5</v>
       </c>
       <c r="F20" s="16"/>
@@ -2419,10 +2431,10 @@
       <c r="C21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="34" t="s">
+      <c r="D21" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="35">
+      <c r="E21" s="33">
         <v>0.8</v>
       </c>
       <c r="F21" s="16"/>
@@ -2434,10 +2446,10 @@
       <c r="C22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="34" t="s">
+      <c r="D22" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="28"/>
+      <c r="E22" s="26"/>
       <c r="F22" s="16"/>
     </row>
     <row r="23" spans="2:6">
@@ -2447,7 +2459,7 @@
       <c r="C23" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="34" t="s">
+      <c r="D23" s="32" t="s">
         <v>43</v>
       </c>
       <c r="E23" s="16">
@@ -2462,7 +2474,7 @@
       <c r="C24" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="34" t="s">
+      <c r="D24" s="32" t="s">
         <v>43</v>
       </c>
       <c r="E24" s="16">
@@ -2477,7 +2489,7 @@
       <c r="C25" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="34" t="s">
+      <c r="D25" s="32" t="s">
         <v>43</v>
       </c>
       <c r="E25" s="16">
@@ -2489,28 +2501,28 @@
       <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="34" t="s">
+      <c r="D26" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="28">
+      <c r="E26" s="26">
         <v>0.05</v>
       </c>
       <c r="F26" s="16"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="37" t="s">
+      <c r="C27" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="37" t="s">
+      <c r="D27" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="37">
+      <c r="E27" s="35">
         <v>2020</v>
       </c>
       <c r="F27" s="16"/>
@@ -2519,10 +2531,10 @@
       <c r="C28" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="37" t="s">
+      <c r="D28" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="38">
+      <c r="E28" s="36">
         <v>2020</v>
       </c>
       <c r="F28" s="16"/>
@@ -2557,360 +2569,360 @@
       <c r="E38" s="1"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="39" t="s">
+      <c r="C54" s="37" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="39"/>
-      <c r="E56" s="39"/>
-      <c r="F56" s="39"/>
-      <c r="G56" s="39"/>
-      <c r="H56" s="39"/>
-      <c r="I56" s="39"/>
-      <c r="J56" s="39"/>
-      <c r="K56" s="39"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="37"/>
+      <c r="F56" s="37"/>
+      <c r="G56" s="37"/>
+      <c r="H56" s="37"/>
+      <c r="I56" s="37"/>
+      <c r="J56" s="37"/>
+      <c r="K56" s="37"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="39" t="s">
+      <c r="C57" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="39" t="s">
+      <c r="D57" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="39" t="s">
+      <c r="E57" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="F57" s="39" t="s">
+      <c r="F57" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="G57" s="39" t="s">
+      <c r="G57" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="39" t="s">
+      <c r="H57" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="39" t="s">
+      <c r="I57" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="J57" s="39" t="s">
+      <c r="J57" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="K57" s="39" t="s">
+      <c r="K57" s="37" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="39"/>
-      <c r="D58" s="39"/>
-      <c r="E58" s="39"/>
-      <c r="F58" s="39"/>
-      <c r="G58" s="39"/>
-      <c r="H58" s="39"/>
-      <c r="I58" s="39"/>
-      <c r="J58" s="39"/>
-      <c r="K58" s="39"/>
+      <c r="C58" s="37"/>
+      <c r="D58" s="37"/>
+      <c r="E58" s="37"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="37"/>
+      <c r="H58" s="37"/>
+      <c r="I58" s="37"/>
+      <c r="J58" s="37"/>
+      <c r="K58" s="37"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="39"/>
-      <c r="D59" s="39"/>
-      <c r="E59" s="39"/>
-      <c r="F59" s="39"/>
-      <c r="G59" s="39"/>
-      <c r="H59" s="39"/>
-      <c r="I59" s="39"/>
-      <c r="J59" s="39"/>
-      <c r="K59" s="39"/>
+      <c r="C59" s="37"/>
+      <c r="D59" s="37"/>
+      <c r="E59" s="37"/>
+      <c r="F59" s="37"/>
+      <c r="G59" s="37"/>
+      <c r="H59" s="37"/>
+      <c r="I59" s="37"/>
+      <c r="J59" s="37"/>
+      <c r="K59" s="37"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="39"/>
-      <c r="D60" s="39"/>
-      <c r="E60" s="39"/>
-      <c r="F60" s="39"/>
-      <c r="G60" s="39"/>
-      <c r="H60" s="39"/>
-      <c r="I60" s="39"/>
-      <c r="J60" s="39"/>
-      <c r="K60" s="39"/>
+      <c r="C60" s="37"/>
+      <c r="D60" s="37"/>
+      <c r="E60" s="37"/>
+      <c r="F60" s="37"/>
+      <c r="G60" s="37"/>
+      <c r="H60" s="37"/>
+      <c r="I60" s="37"/>
+      <c r="J60" s="37"/>
+      <c r="K60" s="37"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="39"/>
-      <c r="D61" s="39"/>
-      <c r="E61" s="39"/>
-      <c r="F61" s="39"/>
-      <c r="G61" s="39"/>
-      <c r="H61" s="39"/>
-      <c r="I61" s="39"/>
-      <c r="J61" s="39"/>
-      <c r="K61" s="39"/>
+      <c r="C61" s="37"/>
+      <c r="D61" s="37"/>
+      <c r="E61" s="37"/>
+      <c r="F61" s="37"/>
+      <c r="G61" s="37"/>
+      <c r="H61" s="37"/>
+      <c r="I61" s="37"/>
+      <c r="J61" s="37"/>
+      <c r="K61" s="37"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="39"/>
-      <c r="D62" s="39"/>
-      <c r="E62" s="39"/>
-      <c r="F62" s="39"/>
-      <c r="G62" s="39"/>
-      <c r="H62" s="39"/>
-      <c r="I62" s="39"/>
-      <c r="J62" s="39"/>
-      <c r="K62" s="39"/>
+      <c r="C62" s="37"/>
+      <c r="D62" s="37"/>
+      <c r="E62" s="37"/>
+      <c r="F62" s="37"/>
+      <c r="G62" s="37"/>
+      <c r="H62" s="37"/>
+      <c r="I62" s="37"/>
+      <c r="J62" s="37"/>
+      <c r="K62" s="37"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="39"/>
-      <c r="D63" s="39"/>
-      <c r="E63" s="39"/>
-      <c r="F63" s="39"/>
-      <c r="G63" s="39"/>
-      <c r="H63" s="39"/>
-      <c r="I63" s="39"/>
-      <c r="J63" s="39"/>
-      <c r="K63" s="39"/>
+      <c r="C63" s="37"/>
+      <c r="D63" s="37"/>
+      <c r="E63" s="37"/>
+      <c r="F63" s="37"/>
+      <c r="G63" s="37"/>
+      <c r="H63" s="37"/>
+      <c r="I63" s="37"/>
+      <c r="J63" s="37"/>
+      <c r="K63" s="37"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="39"/>
-      <c r="D64" s="39"/>
-      <c r="E64" s="39"/>
-      <c r="F64" s="39"/>
-      <c r="G64" s="39"/>
-      <c r="H64" s="39"/>
-      <c r="I64" s="39"/>
-      <c r="J64" s="39"/>
-      <c r="K64" s="39"/>
+      <c r="C64" s="37"/>
+      <c r="D64" s="37"/>
+      <c r="E64" s="37"/>
+      <c r="F64" s="37"/>
+      <c r="G64" s="37"/>
+      <c r="H64" s="37"/>
+      <c r="I64" s="37"/>
+      <c r="J64" s="37"/>
+      <c r="K64" s="37"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="39"/>
-      <c r="D65" s="39"/>
-      <c r="E65" s="39"/>
-      <c r="F65" s="39"/>
-      <c r="G65" s="39"/>
-      <c r="H65" s="39"/>
-      <c r="I65" s="39"/>
-      <c r="J65" s="39"/>
-      <c r="K65" s="39"/>
+      <c r="C65" s="37"/>
+      <c r="D65" s="37"/>
+      <c r="E65" s="37"/>
+      <c r="F65" s="37"/>
+      <c r="G65" s="37"/>
+      <c r="H65" s="37"/>
+      <c r="I65" s="37"/>
+      <c r="J65" s="37"/>
+      <c r="K65" s="37"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="39"/>
-      <c r="D66" s="39"/>
-      <c r="E66" s="39"/>
-      <c r="F66" s="39"/>
-      <c r="G66" s="39"/>
-      <c r="H66" s="39"/>
-      <c r="I66" s="39"/>
-      <c r="J66" s="39"/>
-      <c r="K66" s="39"/>
+      <c r="C66" s="37"/>
+      <c r="D66" s="37"/>
+      <c r="E66" s="37"/>
+      <c r="F66" s="37"/>
+      <c r="G66" s="37"/>
+      <c r="H66" s="37"/>
+      <c r="I66" s="37"/>
+      <c r="J66" s="37"/>
+      <c r="K66" s="37"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="39"/>
-      <c r="D67" s="39"/>
-      <c r="E67" s="39"/>
-      <c r="F67" s="39"/>
-      <c r="G67" s="39"/>
-      <c r="H67" s="39"/>
-      <c r="I67" s="39"/>
-      <c r="J67" s="39"/>
-      <c r="K67" s="39"/>
+      <c r="C67" s="37"/>
+      <c r="D67" s="37"/>
+      <c r="E67" s="37"/>
+      <c r="F67" s="37"/>
+      <c r="G67" s="37"/>
+      <c r="H67" s="37"/>
+      <c r="I67" s="37"/>
+      <c r="J67" s="37"/>
+      <c r="K67" s="37"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="39"/>
-      <c r="D68" s="39"/>
-      <c r="E68" s="39"/>
-      <c r="F68" s="39"/>
-      <c r="G68" s="39"/>
-      <c r="H68" s="39"/>
-      <c r="I68" s="39"/>
-      <c r="J68" s="39"/>
-      <c r="K68" s="39"/>
+      <c r="C68" s="37"/>
+      <c r="D68" s="37"/>
+      <c r="E68" s="37"/>
+      <c r="F68" s="37"/>
+      <c r="G68" s="37"/>
+      <c r="H68" s="37"/>
+      <c r="I68" s="37"/>
+      <c r="J68" s="37"/>
+      <c r="K68" s="37"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="39"/>
-      <c r="D69" s="39"/>
-      <c r="E69" s="39"/>
-      <c r="F69" s="39"/>
-      <c r="G69" s="39"/>
-      <c r="H69" s="39"/>
-      <c r="I69" s="39"/>
-      <c r="J69" s="39"/>
-      <c r="K69" s="39"/>
+      <c r="C69" s="37"/>
+      <c r="D69" s="37"/>
+      <c r="E69" s="37"/>
+      <c r="F69" s="37"/>
+      <c r="G69" s="37"/>
+      <c r="H69" s="37"/>
+      <c r="I69" s="37"/>
+      <c r="J69" s="37"/>
+      <c r="K69" s="37"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="39"/>
-      <c r="D70" s="39"/>
-      <c r="E70" s="39"/>
-      <c r="F70" s="39"/>
-      <c r="G70" s="39"/>
-      <c r="H70" s="39"/>
-      <c r="I70" s="39"/>
-      <c r="J70" s="39"/>
-      <c r="K70" s="39"/>
+      <c r="C70" s="37"/>
+      <c r="D70" s="37"/>
+      <c r="E70" s="37"/>
+      <c r="F70" s="37"/>
+      <c r="G70" s="37"/>
+      <c r="H70" s="37"/>
+      <c r="I70" s="37"/>
+      <c r="J70" s="37"/>
+      <c r="K70" s="37"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="39"/>
-      <c r="D71" s="39"/>
-      <c r="E71" s="39"/>
-      <c r="F71" s="39"/>
-      <c r="G71" s="39"/>
-      <c r="H71" s="39"/>
-      <c r="I71" s="39"/>
-      <c r="J71" s="39"/>
-      <c r="K71" s="39"/>
+      <c r="C71" s="37"/>
+      <c r="D71" s="37"/>
+      <c r="E71" s="37"/>
+      <c r="F71" s="37"/>
+      <c r="G71" s="37"/>
+      <c r="H71" s="37"/>
+      <c r="I71" s="37"/>
+      <c r="J71" s="37"/>
+      <c r="K71" s="37"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="39"/>
-      <c r="D72" s="39"/>
-      <c r="E72" s="39"/>
-      <c r="F72" s="39"/>
-      <c r="G72" s="39"/>
-      <c r="H72" s="39"/>
-      <c r="I72" s="39"/>
-      <c r="J72" s="39"/>
-      <c r="K72" s="39"/>
+      <c r="C72" s="37"/>
+      <c r="D72" s="37"/>
+      <c r="E72" s="37"/>
+      <c r="F72" s="37"/>
+      <c r="G72" s="37"/>
+      <c r="H72" s="37"/>
+      <c r="I72" s="37"/>
+      <c r="J72" s="37"/>
+      <c r="K72" s="37"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="39"/>
-      <c r="D73" s="39"/>
-      <c r="E73" s="39"/>
-      <c r="F73" s="39"/>
-      <c r="G73" s="39"/>
-      <c r="H73" s="39"/>
-      <c r="I73" s="39"/>
-      <c r="J73" s="39"/>
-      <c r="K73" s="39"/>
+      <c r="C73" s="37"/>
+      <c r="D73" s="37"/>
+      <c r="E73" s="37"/>
+      <c r="F73" s="37"/>
+      <c r="G73" s="37"/>
+      <c r="H73" s="37"/>
+      <c r="I73" s="37"/>
+      <c r="J73" s="37"/>
+      <c r="K73" s="37"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="39"/>
-      <c r="D74" s="39"/>
-      <c r="E74" s="39"/>
-      <c r="F74" s="39"/>
-      <c r="G74" s="39"/>
-      <c r="H74" s="39"/>
-      <c r="I74" s="39"/>
-      <c r="J74" s="39"/>
-      <c r="K74" s="39"/>
+      <c r="C74" s="37"/>
+      <c r="D74" s="37"/>
+      <c r="E74" s="37"/>
+      <c r="F74" s="37"/>
+      <c r="G74" s="37"/>
+      <c r="H74" s="37"/>
+      <c r="I74" s="37"/>
+      <c r="J74" s="37"/>
+      <c r="K74" s="37"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="39"/>
-      <c r="D75" s="39"/>
-      <c r="E75" s="39"/>
-      <c r="F75" s="39"/>
-      <c r="G75" s="39"/>
-      <c r="H75" s="39"/>
-      <c r="I75" s="39"/>
-      <c r="J75" s="39"/>
-      <c r="K75" s="39"/>
+      <c r="C75" s="37"/>
+      <c r="D75" s="37"/>
+      <c r="E75" s="37"/>
+      <c r="F75" s="37"/>
+      <c r="G75" s="37"/>
+      <c r="H75" s="37"/>
+      <c r="I75" s="37"/>
+      <c r="J75" s="37"/>
+      <c r="K75" s="37"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="39"/>
-      <c r="D76" s="39"/>
-      <c r="E76" s="39"/>
-      <c r="F76" s="39"/>
-      <c r="G76" s="39"/>
-      <c r="H76" s="39"/>
-      <c r="I76" s="39"/>
-      <c r="J76" s="39"/>
-      <c r="K76" s="39"/>
+      <c r="C76" s="37"/>
+      <c r="D76" s="37"/>
+      <c r="E76" s="37"/>
+      <c r="F76" s="37"/>
+      <c r="G76" s="37"/>
+      <c r="H76" s="37"/>
+      <c r="I76" s="37"/>
+      <c r="J76" s="37"/>
+      <c r="K76" s="37"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="39"/>
-      <c r="D77" s="39"/>
-      <c r="E77" s="39"/>
-      <c r="F77" s="39"/>
-      <c r="G77" s="39"/>
-      <c r="H77" s="39"/>
-      <c r="I77" s="39"/>
-      <c r="J77" s="39"/>
-      <c r="K77" s="39"/>
+      <c r="C77" s="37"/>
+      <c r="D77" s="37"/>
+      <c r="E77" s="37"/>
+      <c r="F77" s="37"/>
+      <c r="G77" s="37"/>
+      <c r="H77" s="37"/>
+      <c r="I77" s="37"/>
+      <c r="J77" s="37"/>
+      <c r="K77" s="37"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="39"/>
-      <c r="D78" s="39"/>
-      <c r="E78" s="39"/>
-      <c r="F78" s="39"/>
-      <c r="G78" s="39"/>
-      <c r="H78" s="39"/>
-      <c r="I78" s="39"/>
-      <c r="J78" s="39"/>
-      <c r="K78" s="39"/>
+      <c r="C78" s="37"/>
+      <c r="D78" s="37"/>
+      <c r="E78" s="37"/>
+      <c r="F78" s="37"/>
+      <c r="G78" s="37"/>
+      <c r="H78" s="37"/>
+      <c r="I78" s="37"/>
+      <c r="J78" s="37"/>
+      <c r="K78" s="37"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="39"/>
-      <c r="D79" s="39"/>
-      <c r="E79" s="39"/>
-      <c r="F79" s="39"/>
-      <c r="G79" s="39"/>
-      <c r="H79" s="39"/>
-      <c r="I79" s="39"/>
-      <c r="J79" s="39"/>
-      <c r="K79" s="39"/>
+      <c r="C79" s="37"/>
+      <c r="D79" s="37"/>
+      <c r="E79" s="37"/>
+      <c r="F79" s="37"/>
+      <c r="G79" s="37"/>
+      <c r="H79" s="37"/>
+      <c r="I79" s="37"/>
+      <c r="J79" s="37"/>
+      <c r="K79" s="37"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="39"/>
-      <c r="D80" s="39"/>
-      <c r="E80" s="39"/>
-      <c r="F80" s="39"/>
-      <c r="G80" s="39"/>
-      <c r="H80" s="39"/>
-      <c r="I80" s="39"/>
-      <c r="J80" s="39"/>
-      <c r="K80" s="39"/>
+      <c r="C80" s="37"/>
+      <c r="D80" s="37"/>
+      <c r="E80" s="37"/>
+      <c r="F80" s="37"/>
+      <c r="G80" s="37"/>
+      <c r="H80" s="37"/>
+      <c r="I80" s="37"/>
+      <c r="J80" s="37"/>
+      <c r="K80" s="37"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="39"/>
-      <c r="D81" s="39"/>
-      <c r="E81" s="39"/>
-      <c r="F81" s="39"/>
-      <c r="G81" s="39"/>
-      <c r="H81" s="39"/>
-      <c r="I81" s="39"/>
-      <c r="J81" s="39"/>
-      <c r="K81" s="39"/>
+      <c r="C81" s="37"/>
+      <c r="D81" s="37"/>
+      <c r="E81" s="37"/>
+      <c r="F81" s="37"/>
+      <c r="G81" s="37"/>
+      <c r="H81" s="37"/>
+      <c r="I81" s="37"/>
+      <c r="J81" s="37"/>
+      <c r="K81" s="37"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="39"/>
-      <c r="D82" s="39"/>
-      <c r="E82" s="39"/>
-      <c r="F82" s="39"/>
-      <c r="G82" s="39"/>
-      <c r="H82" s="39"/>
-      <c r="I82" s="39"/>
-      <c r="J82" s="39"/>
-      <c r="K82" s="39"/>
+      <c r="C82" s="37"/>
+      <c r="D82" s="37"/>
+      <c r="E82" s="37"/>
+      <c r="F82" s="37"/>
+      <c r="G82" s="37"/>
+      <c r="H82" s="37"/>
+      <c r="I82" s="37"/>
+      <c r="J82" s="37"/>
+      <c r="K82" s="37"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="39"/>
-      <c r="D83" s="39"/>
-      <c r="E83" s="39"/>
-      <c r="F83" s="39"/>
-      <c r="G83" s="39"/>
-      <c r="H83" s="39"/>
-      <c r="I83" s="39"/>
-      <c r="J83" s="39"/>
-      <c r="K83" s="39"/>
+      <c r="C83" s="37"/>
+      <c r="D83" s="37"/>
+      <c r="E83" s="37"/>
+      <c r="F83" s="37"/>
+      <c r="G83" s="37"/>
+      <c r="H83" s="37"/>
+      <c r="I83" s="37"/>
+      <c r="J83" s="37"/>
+      <c r="K83" s="37"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="39" t="s">
+      <c r="C84" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="D84" s="39">
-        <v>1</v>
-      </c>
-      <c r="E84" s="39"/>
-      <c r="F84" s="39"/>
-      <c r="G84" s="39"/>
-      <c r="H84" s="39"/>
-      <c r="I84" s="39"/>
-      <c r="J84" s="39"/>
-      <c r="K84" s="39"/>
+      <c r="D84" s="37">
+        <v>1</v>
+      </c>
+      <c r="E84" s="37"/>
+      <c r="F84" s="37"/>
+      <c r="G84" s="37"/>
+      <c r="H84" s="37"/>
+      <c r="I84" s="37"/>
+      <c r="J84" s="37"/>
+      <c r="K84" s="37"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="39"/>
-      <c r="D85" s="39"/>
-      <c r="E85" s="39"/>
-      <c r="F85" s="39"/>
-      <c r="G85" s="39"/>
-      <c r="H85" s="39"/>
-      <c r="I85" s="39"/>
-      <c r="J85" s="39"/>
-      <c r="K85" s="39"/>
+      <c r="C85" s="37"/>
+      <c r="D85" s="37"/>
+      <c r="E85" s="37"/>
+      <c r="F85" s="37"/>
+      <c r="G85" s="37"/>
+      <c r="H85" s="37"/>
+      <c r="I85" s="37"/>
+      <c r="J85" s="37"/>
+      <c r="K85" s="37"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3192,309 +3204,309 @@
       <c r="W25" s="1"/>
     </row>
     <row r="26" spans="5:23">
-      <c r="F26" s="25" t="s">
+      <c r="F26" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
-      <c r="J26" s="25"/>
-      <c r="K26" s="25"/>
-      <c r="L26" s="25"/>
-      <c r="M26" s="25"/>
-      <c r="N26" s="25"/>
-      <c r="O26" s="25"/>
-      <c r="P26" s="25"/>
-      <c r="Q26" s="25"/>
-      <c r="R26" s="25"/>
-      <c r="S26" s="25"/>
-      <c r="T26" s="25"/>
-      <c r="U26" s="25"/>
-      <c r="V26" s="25"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
       <c r="W26" s="1"/>
     </row>
     <row r="27" spans="5:23">
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
-      <c r="J27" s="25"/>
-      <c r="K27" s="25"/>
-      <c r="L27" s="25"/>
-      <c r="M27" s="25"/>
-      <c r="N27" s="25"/>
-      <c r="O27" s="25"/>
-      <c r="P27" s="25"/>
-      <c r="Q27" s="25"/>
-      <c r="R27" s="25"/>
-      <c r="S27" s="25"/>
-      <c r="T27" s="25"/>
-      <c r="U27" s="25"/>
-      <c r="V27" s="25"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
       <c r="W27" s="1"/>
     </row>
     <row r="28" spans="5:23">
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="25"/>
-      <c r="J28" s="25"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="25"/>
-      <c r="N28" s="25"/>
-      <c r="O28" s="25"/>
-      <c r="P28" s="25"/>
-      <c r="Q28" s="25"/>
-      <c r="R28" s="25"/>
-      <c r="S28" s="25"/>
-      <c r="T28" s="25"/>
-      <c r="U28" s="25"/>
-      <c r="V28" s="25"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
       <c r="W28" s="1"/>
     </row>
     <row r="29" spans="5:23">
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="25"/>
-      <c r="J29" s="25"/>
-      <c r="K29" s="25"/>
-      <c r="L29" s="26" t="s">
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="M29" s="25"/>
-      <c r="N29" s="25"/>
-      <c r="O29" s="25"/>
-      <c r="P29" s="25"/>
-      <c r="Q29" s="25"/>
-      <c r="R29" s="25"/>
-      <c r="S29" s="25"/>
-      <c r="T29" s="25"/>
-      <c r="U29" s="25"/>
-      <c r="V29" s="25"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1"/>
       <c r="W29" s="1"/>
     </row>
     <row r="30" ht="15.25" spans="5:23">
-      <c r="F30" s="25" t="s">
+      <c r="F30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G30" s="25" t="s">
+      <c r="G30" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H30" s="25" t="s">
+      <c r="H30" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I30" s="25" t="s">
+      <c r="I30" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J30" s="25" t="s">
+      <c r="J30" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K30" s="25" t="s">
+      <c r="K30" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="L30" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="M30" s="25" t="s">
+      <c r="L30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M30" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="N30" s="25" t="s">
+      <c r="N30" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="O30" s="25" t="s">
+      <c r="O30" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="P30" s="25" t="s">
+      <c r="P30" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="Q30" s="25" t="s">
+      <c r="Q30" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="R30" s="25"/>
-      <c r="S30" s="25"/>
-      <c r="T30" s="25"/>
-      <c r="U30" s="25"/>
-      <c r="V30" s="25"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+      <c r="V30" s="1"/>
     </row>
     <row r="31" ht="16" spans="5:23">
-      <c r="F31" s="25" t="s">
+      <c r="F31" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G31" s="25" t="s">
+      <c r="G31" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H31" s="27" t="s">
+      <c r="H31" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="I31" s="25" t="s">
+      <c r="I31" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="J31" s="25"/>
-      <c r="K31" s="25"/>
-      <c r="L31" s="25"/>
-      <c r="M31" s="25">
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1">
         <v>-0.25</v>
       </c>
-      <c r="N31" s="25"/>
-      <c r="O31" s="25">
+      <c r="N31" s="1"/>
+      <c r="O31" s="1">
         <v>0</v>
       </c>
-      <c r="P31" s="25">
+      <c r="P31" s="1">
         <v>3</v>
       </c>
-      <c r="Q31" s="25" t="s">
+      <c r="Q31" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="R31" s="25"/>
-      <c r="S31" s="25"/>
-      <c r="T31" s="25"/>
-      <c r="U31" s="25"/>
-      <c r="V31" s="25"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
     </row>
     <row r="32" ht="15.25" spans="5:23">
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="25" t="s">
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="J32" s="25"/>
-      <c r="K32" s="25"/>
-      <c r="L32" s="25"/>
-      <c r="M32" s="25">
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1">
         <v>-0.1</v>
       </c>
-      <c r="N32" s="25"/>
-      <c r="O32" s="25"/>
-      <c r="P32" s="25"/>
-      <c r="Q32" s="25"/>
-      <c r="R32" s="25"/>
-      <c r="S32" s="25"/>
-      <c r="T32" s="25"/>
-      <c r="U32" s="25"/>
-      <c r="V32" s="25"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
     </row>
     <row r="33" spans="6:22">
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25" t="s">
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I33" s="25"/>
-      <c r="J33" s="25"/>
-      <c r="K33" s="25" t="s">
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="L33" s="25"/>
-      <c r="M33" s="25"/>
-      <c r="N33" s="26">
-        <v>1</v>
-      </c>
-      <c r="O33" s="25"/>
-      <c r="P33" s="25"/>
-      <c r="Q33" s="25"/>
-      <c r="R33" s="25"/>
-      <c r="S33" s="25"/>
-      <c r="T33" s="25"/>
-      <c r="U33" s="25"/>
-      <c r="V33" s="25"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1">
+        <v>1</v>
+      </c>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
     </row>
     <row r="34" spans="6:22">
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
-      <c r="O34" s="25"/>
-      <c r="P34" s="25"/>
-      <c r="Q34" s="25"/>
-      <c r="R34" s="25"/>
-      <c r="S34" s="25"/>
-      <c r="T34" s="25"/>
-      <c r="U34" s="25"/>
-      <c r="V34" s="25"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
     </row>
     <row r="35" spans="6:22">
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="25"/>
-      <c r="K35" s="25"/>
-      <c r="L35" s="25"/>
-      <c r="M35" s="25"/>
-      <c r="N35" s="25"/>
-      <c r="O35" s="25"/>
-      <c r="P35" s="25"/>
-      <c r="Q35" s="25"/>
-      <c r="R35" s="25"/>
-      <c r="S35" s="25"/>
-      <c r="T35" s="25"/>
-      <c r="U35" s="25"/>
-      <c r="V35" s="25"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1"/>
     </row>
     <row r="36" spans="6:22">
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="25"/>
-      <c r="J36" s="25"/>
-      <c r="K36" s="25"/>
-      <c r="L36" s="25"/>
-      <c r="M36" s="25"/>
-      <c r="N36" s="25"/>
-      <c r="O36" s="25"/>
-      <c r="P36" s="25"/>
-      <c r="Q36" s="25"/>
-      <c r="R36" s="25"/>
-      <c r="S36" s="25"/>
-      <c r="T36" s="25"/>
-      <c r="U36" s="25"/>
-      <c r="V36" s="25"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
     </row>
     <row r="37" spans="6:22">
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="25"/>
-      <c r="J37" s="25"/>
-      <c r="K37" s="25"/>
-      <c r="L37" s="25"/>
-      <c r="M37" s="25"/>
-      <c r="N37" s="25"/>
-      <c r="O37" s="25"/>
-      <c r="P37" s="25"/>
-      <c r="Q37" s="25"/>
-      <c r="R37" s="25"/>
-      <c r="S37" s="25"/>
-      <c r="T37" s="25"/>
-      <c r="U37" s="25"/>
-      <c r="V37" s="25"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1"/>
     </row>
     <row r="38" spans="6:22">
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="25"/>
-      <c r="I38" s="25"/>
-      <c r="J38" s="25"/>
-      <c r="K38" s="25"/>
-      <c r="L38" s="25"/>
-      <c r="M38" s="25"/>
-      <c r="N38" s="25"/>
-      <c r="O38" s="25"/>
-      <c r="P38" s="25"/>
-      <c r="Q38" s="25"/>
-      <c r="R38" s="25"/>
-      <c r="S38" s="25"/>
-      <c r="T38" s="25"/>
-      <c r="U38" s="25"/>
-      <c r="V38" s="25"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4963,7 +4975,7 @@
       <c r="AL51" s="6"/>
       <c r="AM51" s="6"/>
     </row>
-    <row r="52" ht="16" spans="6:44">
+    <row r="52" ht="16.75" spans="6:44">
       <c r="G52" s="3" t="s">
         <v>59</v>
       </c>
@@ -4995,7 +5007,7 @@
         <v>61</v>
       </c>
       <c r="Q52" s="8" t="s">
-        <v>63</v>
+        <v>154</v>
       </c>
       <c r="S52" s="6"/>
       <c r="T52" s="6"/>
@@ -5027,7 +5039,7 @@
     <row r="53" ht="16" spans="6:44">
       <c r="F53" s="9"/>
       <c r="G53" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>110</v>
@@ -5041,14 +5053,14 @@
       <c r="K53" s="12"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N53" s="3"/>
       <c r="O53" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="P53" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="P53" s="3" t="s">
-        <v>155</v>
       </c>
       <c r="Q53" s="3">
         <v>10</v>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -715,7 +715,7 @@
     <t>UCE_4</t>
   </si>
   <si>
-    <t>TRDELC</t>
+    <t>AuxStoIN</t>
   </si>
   <si>
     <t>Tra_EV_Bat*fromrecy, Tra_EV_Bat*virgin_pack</t>
@@ -943,6 +943,12 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
@@ -952,12 +958,6 @@
       <charset val="0"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -1471,7 +1471,7 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1491,6 +1491,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2060,7 +2061,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="35">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -2174,10 +2175,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="38"/>
+      <c r="K10" s="39"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="38"/>
+      <c r="K11" s="39"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2198,12 +2199,12 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:13">
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="16"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="17"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
@@ -2218,19 +2219,19 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="27"/>
+      <c r="K6" s="28"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="29">
         <v>10</v>
       </c>
     </row>
@@ -2238,17 +2239,17 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <v>7</v>
       </c>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
     </row>
     <row r="9" ht="16" spans="2:13">
       <c r="B9" t="s">
@@ -2257,10 +2258,10 @@
       <c r="C9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <v>10</v>
       </c>
     </row>
@@ -2268,17 +2269,17 @@
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <v>8</v>
       </c>
-      <c r="K10" s="29"/>
-      <c r="L10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="31"/>
     </row>
     <row r="11" ht="16" spans="2:13">
       <c r="B11" t="s">
@@ -2287,10 +2288,10 @@
       <c r="C11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <v>1.5</v>
       </c>
     </row>
@@ -2301,10 +2302,10 @@
       <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <v>1.5</v>
       </c>
     </row>
@@ -2312,13 +2313,13 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="D13" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="17">
         <v>2</v>
       </c>
     </row>
@@ -2326,13 +2327,13 @@
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2340,13 +2341,13 @@
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2354,13 +2355,13 @@
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="32">
         <v>12</v>
       </c>
     </row>
@@ -2368,31 +2369,31 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="34">
         <v>0.2</v>
       </c>
-      <c r="F17" s="16"/>
+      <c r="F17" s="17"/>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="34">
         <v>0.2</v>
       </c>
-      <c r="F18" s="16"/>
+      <c r="F18" s="17"/>
     </row>
     <row r="19" ht="16" spans="2:6">
       <c r="B19" t="s">
@@ -2401,28 +2402,28 @@
       <c r="C19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="33">
+      <c r="E19" s="34">
         <v>0.2</v>
       </c>
-      <c r="F19" s="16"/>
+      <c r="F19" s="17"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="34">
         <v>0.5</v>
       </c>
-      <c r="F20" s="16"/>
+      <c r="F20" s="17"/>
     </row>
     <row r="21" ht="16" spans="2:6">
       <c r="B21" t="s">
@@ -2431,13 +2432,13 @@
       <c r="C21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="34">
         <v>0.8</v>
       </c>
-      <c r="F21" s="16"/>
+      <c r="F21" s="17"/>
     </row>
     <row r="22" ht="16" spans="2:6">
       <c r="B22" t="s">
@@ -2446,122 +2447,122 @@
       <c r="C22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="26"/>
-      <c r="F22" s="16"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="17"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D23" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="16">
-        <v>1</v>
-      </c>
-      <c r="F23" s="16"/>
+      <c r="E23" s="17">
+        <v>1</v>
+      </c>
+      <c r="F23" s="17"/>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="16">
-        <v>1</v>
-      </c>
-      <c r="F24" s="16"/>
+      <c r="E24" s="17">
+        <v>1</v>
+      </c>
+      <c r="F24" s="17"/>
     </row>
     <row r="25" ht="16" spans="2:6">
       <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="16">
-        <v>1</v>
-      </c>
-      <c r="F25" s="16"/>
+      <c r="E25" s="17">
+        <v>1</v>
+      </c>
+      <c r="F25" s="17"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C26" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="27">
         <v>0.05</v>
       </c>
-      <c r="F26" s="16"/>
+      <c r="F26" s="17"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="34" t="s">
+      <c r="B27" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="35" t="s">
+      <c r="C27" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="35" t="s">
+      <c r="D27" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="35">
+      <c r="E27" s="36">
         <v>2020</v>
       </c>
-      <c r="F27" s="16"/>
+      <c r="F27" s="17"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="35" t="s">
+      <c r="D28" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="36">
+      <c r="E28" s="37">
         <v>2020</v>
       </c>
-      <c r="F28" s="16"/>
+      <c r="F28" s="17"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
     </row>
     <row r="38" spans="3:5">
       <c r="C38" s="1"/>
@@ -2569,360 +2570,360 @@
       <c r="E38" s="1"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="37" t="s">
+      <c r="C54" s="38" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="37"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="37"/>
-      <c r="G56" s="37"/>
-      <c r="H56" s="37"/>
-      <c r="I56" s="37"/>
-      <c r="J56" s="37"/>
-      <c r="K56" s="37"/>
+      <c r="D56" s="38"/>
+      <c r="E56" s="38"/>
+      <c r="F56" s="38"/>
+      <c r="G56" s="38"/>
+      <c r="H56" s="38"/>
+      <c r="I56" s="38"/>
+      <c r="J56" s="38"/>
+      <c r="K56" s="38"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="37" t="s">
+      <c r="C57" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="37" t="s">
+      <c r="D57" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="37" t="s">
+      <c r="E57" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="F57" s="37" t="s">
+      <c r="F57" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="G57" s="37" t="s">
+      <c r="G57" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="37" t="s">
+      <c r="H57" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="37" t="s">
+      <c r="I57" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="J57" s="37" t="s">
+      <c r="J57" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="K57" s="37" t="s">
+      <c r="K57" s="38" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="37"/>
-      <c r="H58" s="37"/>
-      <c r="I58" s="37"/>
-      <c r="J58" s="37"/>
-      <c r="K58" s="37"/>
+      <c r="C58" s="38"/>
+      <c r="D58" s="38"/>
+      <c r="E58" s="38"/>
+      <c r="F58" s="38"/>
+      <c r="G58" s="38"/>
+      <c r="H58" s="38"/>
+      <c r="I58" s="38"/>
+      <c r="J58" s="38"/>
+      <c r="K58" s="38"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="37"/>
-      <c r="D59" s="37"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="37"/>
-      <c r="G59" s="37"/>
-      <c r="H59" s="37"/>
-      <c r="I59" s="37"/>
-      <c r="J59" s="37"/>
-      <c r="K59" s="37"/>
+      <c r="C59" s="38"/>
+      <c r="D59" s="38"/>
+      <c r="E59" s="38"/>
+      <c r="F59" s="38"/>
+      <c r="G59" s="38"/>
+      <c r="H59" s="38"/>
+      <c r="I59" s="38"/>
+      <c r="J59" s="38"/>
+      <c r="K59" s="38"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="37"/>
-      <c r="D60" s="37"/>
-      <c r="E60" s="37"/>
-      <c r="F60" s="37"/>
-      <c r="G60" s="37"/>
-      <c r="H60" s="37"/>
-      <c r="I60" s="37"/>
-      <c r="J60" s="37"/>
-      <c r="K60" s="37"/>
+      <c r="C60" s="38"/>
+      <c r="D60" s="38"/>
+      <c r="E60" s="38"/>
+      <c r="F60" s="38"/>
+      <c r="G60" s="38"/>
+      <c r="H60" s="38"/>
+      <c r="I60" s="38"/>
+      <c r="J60" s="38"/>
+      <c r="K60" s="38"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="37"/>
-      <c r="D61" s="37"/>
-      <c r="E61" s="37"/>
-      <c r="F61" s="37"/>
-      <c r="G61" s="37"/>
-      <c r="H61" s="37"/>
-      <c r="I61" s="37"/>
-      <c r="J61" s="37"/>
-      <c r="K61" s="37"/>
+      <c r="C61" s="38"/>
+      <c r="D61" s="38"/>
+      <c r="E61" s="38"/>
+      <c r="F61" s="38"/>
+      <c r="G61" s="38"/>
+      <c r="H61" s="38"/>
+      <c r="I61" s="38"/>
+      <c r="J61" s="38"/>
+      <c r="K61" s="38"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="37"/>
-      <c r="D62" s="37"/>
-      <c r="E62" s="37"/>
-      <c r="F62" s="37"/>
-      <c r="G62" s="37"/>
-      <c r="H62" s="37"/>
-      <c r="I62" s="37"/>
-      <c r="J62" s="37"/>
-      <c r="K62" s="37"/>
+      <c r="C62" s="38"/>
+      <c r="D62" s="38"/>
+      <c r="E62" s="38"/>
+      <c r="F62" s="38"/>
+      <c r="G62" s="38"/>
+      <c r="H62" s="38"/>
+      <c r="I62" s="38"/>
+      <c r="J62" s="38"/>
+      <c r="K62" s="38"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="37"/>
-      <c r="D63" s="37"/>
-      <c r="E63" s="37"/>
-      <c r="F63" s="37"/>
-      <c r="G63" s="37"/>
-      <c r="H63" s="37"/>
-      <c r="I63" s="37"/>
-      <c r="J63" s="37"/>
-      <c r="K63" s="37"/>
+      <c r="C63" s="38"/>
+      <c r="D63" s="38"/>
+      <c r="E63" s="38"/>
+      <c r="F63" s="38"/>
+      <c r="G63" s="38"/>
+      <c r="H63" s="38"/>
+      <c r="I63" s="38"/>
+      <c r="J63" s="38"/>
+      <c r="K63" s="38"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="37"/>
-      <c r="D64" s="37"/>
-      <c r="E64" s="37"/>
-      <c r="F64" s="37"/>
-      <c r="G64" s="37"/>
-      <c r="H64" s="37"/>
-      <c r="I64" s="37"/>
-      <c r="J64" s="37"/>
-      <c r="K64" s="37"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="38"/>
+      <c r="E64" s="38"/>
+      <c r="F64" s="38"/>
+      <c r="G64" s="38"/>
+      <c r="H64" s="38"/>
+      <c r="I64" s="38"/>
+      <c r="J64" s="38"/>
+      <c r="K64" s="38"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="37"/>
-      <c r="D65" s="37"/>
-      <c r="E65" s="37"/>
-      <c r="F65" s="37"/>
-      <c r="G65" s="37"/>
-      <c r="H65" s="37"/>
-      <c r="I65" s="37"/>
-      <c r="J65" s="37"/>
-      <c r="K65" s="37"/>
+      <c r="C65" s="38"/>
+      <c r="D65" s="38"/>
+      <c r="E65" s="38"/>
+      <c r="F65" s="38"/>
+      <c r="G65" s="38"/>
+      <c r="H65" s="38"/>
+      <c r="I65" s="38"/>
+      <c r="J65" s="38"/>
+      <c r="K65" s="38"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="37"/>
-      <c r="D66" s="37"/>
-      <c r="E66" s="37"/>
-      <c r="F66" s="37"/>
-      <c r="G66" s="37"/>
-      <c r="H66" s="37"/>
-      <c r="I66" s="37"/>
-      <c r="J66" s="37"/>
-      <c r="K66" s="37"/>
+      <c r="C66" s="38"/>
+      <c r="D66" s="38"/>
+      <c r="E66" s="38"/>
+      <c r="F66" s="38"/>
+      <c r="G66" s="38"/>
+      <c r="H66" s="38"/>
+      <c r="I66" s="38"/>
+      <c r="J66" s="38"/>
+      <c r="K66" s="38"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="37"/>
-      <c r="D67" s="37"/>
-      <c r="E67" s="37"/>
-      <c r="F67" s="37"/>
-      <c r="G67" s="37"/>
-      <c r="H67" s="37"/>
-      <c r="I67" s="37"/>
-      <c r="J67" s="37"/>
-      <c r="K67" s="37"/>
+      <c r="C67" s="38"/>
+      <c r="D67" s="38"/>
+      <c r="E67" s="38"/>
+      <c r="F67" s="38"/>
+      <c r="G67" s="38"/>
+      <c r="H67" s="38"/>
+      <c r="I67" s="38"/>
+      <c r="J67" s="38"/>
+      <c r="K67" s="38"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="37"/>
-      <c r="D68" s="37"/>
-      <c r="E68" s="37"/>
-      <c r="F68" s="37"/>
-      <c r="G68" s="37"/>
-      <c r="H68" s="37"/>
-      <c r="I68" s="37"/>
-      <c r="J68" s="37"/>
-      <c r="K68" s="37"/>
+      <c r="C68" s="38"/>
+      <c r="D68" s="38"/>
+      <c r="E68" s="38"/>
+      <c r="F68" s="38"/>
+      <c r="G68" s="38"/>
+      <c r="H68" s="38"/>
+      <c r="I68" s="38"/>
+      <c r="J68" s="38"/>
+      <c r="K68" s="38"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="37"/>
-      <c r="D69" s="37"/>
-      <c r="E69" s="37"/>
-      <c r="F69" s="37"/>
-      <c r="G69" s="37"/>
-      <c r="H69" s="37"/>
-      <c r="I69" s="37"/>
-      <c r="J69" s="37"/>
-      <c r="K69" s="37"/>
+      <c r="C69" s="38"/>
+      <c r="D69" s="38"/>
+      <c r="E69" s="38"/>
+      <c r="F69" s="38"/>
+      <c r="G69" s="38"/>
+      <c r="H69" s="38"/>
+      <c r="I69" s="38"/>
+      <c r="J69" s="38"/>
+      <c r="K69" s="38"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="37"/>
-      <c r="D70" s="37"/>
-      <c r="E70" s="37"/>
-      <c r="F70" s="37"/>
-      <c r="G70" s="37"/>
-      <c r="H70" s="37"/>
-      <c r="I70" s="37"/>
-      <c r="J70" s="37"/>
-      <c r="K70" s="37"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="38"/>
+      <c r="H70" s="38"/>
+      <c r="I70" s="38"/>
+      <c r="J70" s="38"/>
+      <c r="K70" s="38"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="37"/>
-      <c r="D71" s="37"/>
-      <c r="E71" s="37"/>
-      <c r="F71" s="37"/>
-      <c r="G71" s="37"/>
-      <c r="H71" s="37"/>
-      <c r="I71" s="37"/>
-      <c r="J71" s="37"/>
-      <c r="K71" s="37"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="38"/>
+      <c r="E71" s="38"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="38"/>
+      <c r="H71" s="38"/>
+      <c r="I71" s="38"/>
+      <c r="J71" s="38"/>
+      <c r="K71" s="38"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="37"/>
-      <c r="D72" s="37"/>
-      <c r="E72" s="37"/>
-      <c r="F72" s="37"/>
-      <c r="G72" s="37"/>
-      <c r="H72" s="37"/>
-      <c r="I72" s="37"/>
-      <c r="J72" s="37"/>
-      <c r="K72" s="37"/>
+      <c r="C72" s="38"/>
+      <c r="D72" s="38"/>
+      <c r="E72" s="38"/>
+      <c r="F72" s="38"/>
+      <c r="G72" s="38"/>
+      <c r="H72" s="38"/>
+      <c r="I72" s="38"/>
+      <c r="J72" s="38"/>
+      <c r="K72" s="38"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="37"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="37"/>
-      <c r="I73" s="37"/>
-      <c r="J73" s="37"/>
-      <c r="K73" s="37"/>
+      <c r="C73" s="38"/>
+      <c r="D73" s="38"/>
+      <c r="E73" s="38"/>
+      <c r="F73" s="38"/>
+      <c r="G73" s="38"/>
+      <c r="H73" s="38"/>
+      <c r="I73" s="38"/>
+      <c r="J73" s="38"/>
+      <c r="K73" s="38"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="37"/>
-      <c r="D74" s="37"/>
-      <c r="E74" s="37"/>
-      <c r="F74" s="37"/>
-      <c r="G74" s="37"/>
-      <c r="H74" s="37"/>
-      <c r="I74" s="37"/>
-      <c r="J74" s="37"/>
-      <c r="K74" s="37"/>
+      <c r="C74" s="38"/>
+      <c r="D74" s="38"/>
+      <c r="E74" s="38"/>
+      <c r="F74" s="38"/>
+      <c r="G74" s="38"/>
+      <c r="H74" s="38"/>
+      <c r="I74" s="38"/>
+      <c r="J74" s="38"/>
+      <c r="K74" s="38"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="37"/>
-      <c r="D75" s="37"/>
-      <c r="E75" s="37"/>
-      <c r="F75" s="37"/>
-      <c r="G75" s="37"/>
-      <c r="H75" s="37"/>
-      <c r="I75" s="37"/>
-      <c r="J75" s="37"/>
-      <c r="K75" s="37"/>
+      <c r="C75" s="38"/>
+      <c r="D75" s="38"/>
+      <c r="E75" s="38"/>
+      <c r="F75" s="38"/>
+      <c r="G75" s="38"/>
+      <c r="H75" s="38"/>
+      <c r="I75" s="38"/>
+      <c r="J75" s="38"/>
+      <c r="K75" s="38"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="37"/>
-      <c r="D76" s="37"/>
-      <c r="E76" s="37"/>
-      <c r="F76" s="37"/>
-      <c r="G76" s="37"/>
-      <c r="H76" s="37"/>
-      <c r="I76" s="37"/>
-      <c r="J76" s="37"/>
-      <c r="K76" s="37"/>
+      <c r="C76" s="38"/>
+      <c r="D76" s="38"/>
+      <c r="E76" s="38"/>
+      <c r="F76" s="38"/>
+      <c r="G76" s="38"/>
+      <c r="H76" s="38"/>
+      <c r="I76" s="38"/>
+      <c r="J76" s="38"/>
+      <c r="K76" s="38"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="37"/>
-      <c r="D77" s="37"/>
-      <c r="E77" s="37"/>
-      <c r="F77" s="37"/>
-      <c r="G77" s="37"/>
-      <c r="H77" s="37"/>
-      <c r="I77" s="37"/>
-      <c r="J77" s="37"/>
-      <c r="K77" s="37"/>
+      <c r="C77" s="38"/>
+      <c r="D77" s="38"/>
+      <c r="E77" s="38"/>
+      <c r="F77" s="38"/>
+      <c r="G77" s="38"/>
+      <c r="H77" s="38"/>
+      <c r="I77" s="38"/>
+      <c r="J77" s="38"/>
+      <c r="K77" s="38"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="37"/>
-      <c r="D78" s="37"/>
-      <c r="E78" s="37"/>
-      <c r="F78" s="37"/>
-      <c r="G78" s="37"/>
-      <c r="H78" s="37"/>
-      <c r="I78" s="37"/>
-      <c r="J78" s="37"/>
-      <c r="K78" s="37"/>
+      <c r="C78" s="38"/>
+      <c r="D78" s="38"/>
+      <c r="E78" s="38"/>
+      <c r="F78" s="38"/>
+      <c r="G78" s="38"/>
+      <c r="H78" s="38"/>
+      <c r="I78" s="38"/>
+      <c r="J78" s="38"/>
+      <c r="K78" s="38"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="37"/>
-      <c r="D79" s="37"/>
-      <c r="E79" s="37"/>
-      <c r="F79" s="37"/>
-      <c r="G79" s="37"/>
-      <c r="H79" s="37"/>
-      <c r="I79" s="37"/>
-      <c r="J79" s="37"/>
-      <c r="K79" s="37"/>
+      <c r="C79" s="38"/>
+      <c r="D79" s="38"/>
+      <c r="E79" s="38"/>
+      <c r="F79" s="38"/>
+      <c r="G79" s="38"/>
+      <c r="H79" s="38"/>
+      <c r="I79" s="38"/>
+      <c r="J79" s="38"/>
+      <c r="K79" s="38"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="37"/>
-      <c r="D80" s="37"/>
-      <c r="E80" s="37"/>
-      <c r="F80" s="37"/>
-      <c r="G80" s="37"/>
-      <c r="H80" s="37"/>
-      <c r="I80" s="37"/>
-      <c r="J80" s="37"/>
-      <c r="K80" s="37"/>
+      <c r="C80" s="38"/>
+      <c r="D80" s="38"/>
+      <c r="E80" s="38"/>
+      <c r="F80" s="38"/>
+      <c r="G80" s="38"/>
+      <c r="H80" s="38"/>
+      <c r="I80" s="38"/>
+      <c r="J80" s="38"/>
+      <c r="K80" s="38"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="37"/>
-      <c r="D81" s="37"/>
-      <c r="E81" s="37"/>
-      <c r="F81" s="37"/>
-      <c r="G81" s="37"/>
-      <c r="H81" s="37"/>
-      <c r="I81" s="37"/>
-      <c r="J81" s="37"/>
-      <c r="K81" s="37"/>
+      <c r="C81" s="38"/>
+      <c r="D81" s="38"/>
+      <c r="E81" s="38"/>
+      <c r="F81" s="38"/>
+      <c r="G81" s="38"/>
+      <c r="H81" s="38"/>
+      <c r="I81" s="38"/>
+      <c r="J81" s="38"/>
+      <c r="K81" s="38"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="37"/>
-      <c r="D82" s="37"/>
-      <c r="E82" s="37"/>
-      <c r="F82" s="37"/>
-      <c r="G82" s="37"/>
-      <c r="H82" s="37"/>
-      <c r="I82" s="37"/>
-      <c r="J82" s="37"/>
-      <c r="K82" s="37"/>
+      <c r="C82" s="38"/>
+      <c r="D82" s="38"/>
+      <c r="E82" s="38"/>
+      <c r="F82" s="38"/>
+      <c r="G82" s="38"/>
+      <c r="H82" s="38"/>
+      <c r="I82" s="38"/>
+      <c r="J82" s="38"/>
+      <c r="K82" s="38"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="37"/>
-      <c r="D83" s="37"/>
-      <c r="E83" s="37"/>
-      <c r="F83" s="37"/>
-      <c r="G83" s="37"/>
-      <c r="H83" s="37"/>
-      <c r="I83" s="37"/>
-      <c r="J83" s="37"/>
-      <c r="K83" s="37"/>
+      <c r="C83" s="38"/>
+      <c r="D83" s="38"/>
+      <c r="E83" s="38"/>
+      <c r="F83" s="38"/>
+      <c r="G83" s="38"/>
+      <c r="H83" s="38"/>
+      <c r="I83" s="38"/>
+      <c r="J83" s="38"/>
+      <c r="K83" s="38"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="37" t="s">
+      <c r="C84" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="D84" s="37">
-        <v>1</v>
-      </c>
-      <c r="E84" s="37"/>
-      <c r="F84" s="37"/>
-      <c r="G84" s="37"/>
-      <c r="H84" s="37"/>
-      <c r="I84" s="37"/>
-      <c r="J84" s="37"/>
-      <c r="K84" s="37"/>
+      <c r="D84" s="38">
+        <v>1</v>
+      </c>
+      <c r="E84" s="38"/>
+      <c r="F84" s="38"/>
+      <c r="G84" s="38"/>
+      <c r="H84" s="38"/>
+      <c r="I84" s="38"/>
+      <c r="J84" s="38"/>
+      <c r="K84" s="38"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="37"/>
-      <c r="D85" s="37"/>
-      <c r="E85" s="37"/>
-      <c r="F85" s="37"/>
-      <c r="G85" s="37"/>
-      <c r="H85" s="37"/>
-      <c r="I85" s="37"/>
-      <c r="J85" s="37"/>
-      <c r="K85" s="37"/>
+      <c r="C85" s="38"/>
+      <c r="D85" s="38"/>
+      <c r="E85" s="38"/>
+      <c r="F85" s="38"/>
+      <c r="G85" s="38"/>
+      <c r="H85" s="38"/>
+      <c r="I85" s="38"/>
+      <c r="J85" s="38"/>
+      <c r="K85" s="38"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3337,7 +3338,7 @@
       <c r="G31" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H31" s="25" t="s">
+      <c r="H31" s="26" t="s">
         <v>69</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -3546,252 +3547,252 @@
       </c>
     </row>
     <row r="8" spans="2:14">
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="J8" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="K8" s="14" t="s">
+      <c r="K8" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="L8" s="14" t="s">
+      <c r="L8" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="M8" s="14" t="s">
+      <c r="M8" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="N8" s="14" t="s">
+      <c r="N8" s="15" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="9" spans="2:14">
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="16" t="s">
         <v>88</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="16">
         <v>1.25</v>
       </c>
       <c r="L9">
         <v>0.05</v>
       </c>
-      <c r="M9" s="15">
-        <v>1</v>
-      </c>
-      <c r="N9" s="15"/>
+      <c r="M9" s="16">
+        <v>1</v>
+      </c>
+      <c r="N9" s="16"/>
     </row>
     <row r="10" spans="2:14">
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="16" t="s">
         <v>88</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="16">
         <v>1.11</v>
       </c>
       <c r="L10">
         <v>0.05</v>
       </c>
-      <c r="M10" s="15">
-        <v>1</v>
-      </c>
-      <c r="N10" s="15"/>
+      <c r="M10" s="16">
+        <v>1</v>
+      </c>
+      <c r="N10" s="16"/>
     </row>
     <row r="11" spans="2:14">
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" s="16" t="s">
         <v>88</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="16">
         <v>1.15</v>
       </c>
       <c r="L11">
         <v>0.08</v>
       </c>
-      <c r="M11" s="15">
-        <v>1</v>
-      </c>
-      <c r="N11" s="15"/>
+      <c r="M11" s="16">
+        <v>1</v>
+      </c>
+      <c r="N11" s="16"/>
     </row>
     <row r="12" ht="16" spans="2:14">
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="16" t="s">
         <v>93</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="16" t="s">
         <v>88</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
-      <c r="K12" s="15">
+      <c r="K12" s="16">
         <v>1.12</v>
       </c>
       <c r="L12">
         <v>0.03</v>
       </c>
-      <c r="M12" s="15">
-        <v>1</v>
-      </c>
-      <c r="N12" s="15"/>
+      <c r="M12" s="16">
+        <v>1</v>
+      </c>
+      <c r="N12" s="16"/>
     </row>
     <row r="13" spans="2:14">
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="H13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" s="16" t="s">
         <v>88</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="16">
         <v>1.2</v>
       </c>
       <c r="L13">
         <v>0.1</v>
       </c>
-      <c r="M13" s="15">
-        <v>1</v>
-      </c>
-      <c r="N13" s="15"/>
+      <c r="M13" s="16">
+        <v>1</v>
+      </c>
+      <c r="N13" s="16"/>
     </row>
     <row r="14" spans="2:14">
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H14" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I14" s="16" t="s">
         <v>88</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="16">
         <v>1.06</v>
       </c>
       <c r="L14">
         <v>0.15</v>
       </c>
-      <c r="M14" s="15">
-        <v>1</v>
-      </c>
-      <c r="N14" s="15"/>
+      <c r="M14" s="16">
+        <v>1</v>
+      </c>
+      <c r="N14" s="16"/>
     </row>
     <row r="15" spans="2:14">
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="16" t="s">
         <v>88</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="16">
         <v>1.06</v>
       </c>
       <c r="L15">
         <v>0.3</v>
       </c>
-      <c r="M15" s="15">
-        <v>1</v>
-      </c>
-      <c r="N15" s="15"/>
+      <c r="M15" s="16">
+        <v>1</v>
+      </c>
+      <c r="N15" s="16"/>
     </row>
     <row r="16" ht="16" spans="2:14">
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="16" t="s">
         <v>101</v>
       </c>
       <c r="F16" s="2" t="s">
@@ -3805,7 +3806,7 @@
         <f>H15</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="I16" s="16" t="s">
         <v>88</v>
       </c>
       <c r="J16">
@@ -3826,7 +3827,7 @@
       </c>
     </row>
     <row r="17" ht="16" spans="4:14">
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="16" t="s">
         <v>103</v>
       </c>
       <c r="F17" s="2" t="s">
@@ -3840,7 +3841,7 @@
         <f t="shared" si="1"/>
         <v>2025, 2150</v>
       </c>
-      <c r="I17" s="15" t="s">
+      <c r="I17" s="16" t="s">
         <v>88</v>
       </c>
       <c r="J17">
@@ -3861,7 +3862,7 @@
       </c>
     </row>
     <row r="18" ht="16" spans="4:14">
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="16" t="s">
         <v>105</v>
       </c>
       <c r="F18" s="2" t="s">
@@ -3875,7 +3876,7 @@
         <f>H17</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I18" s="15" t="s">
+      <c r="I18" s="16" t="s">
         <v>88</v>
       </c>
       <c r="J18">
@@ -3892,604 +3893,604 @@
       </c>
     </row>
     <row r="27" spans="4:14">
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
     </row>
     <row r="28" spans="4:14">
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16" t="s">
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
     </row>
     <row r="29" spans="4:14">
-      <c r="D29" s="16" t="s">
+      <c r="D29" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="E29" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="F29" s="16" t="s">
+      <c r="F29" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="16" t="s">
+      <c r="G29" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="H29" s="16" t="s">
+      <c r="H29" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="I29" s="16" t="s">
+      <c r="I29" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="J29" s="16" t="s">
+      <c r="J29" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="K29" s="16" t="s">
+      <c r="K29" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="L29" s="16" t="s">
+      <c r="L29" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="M29" s="16" t="s">
+      <c r="M29" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="N29" s="16" t="s">
+      <c r="N29" s="17" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="30" ht="16" spans="4:14">
-      <c r="D30" s="16" t="s">
+      <c r="D30" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="16"/>
-      <c r="F30" s="17" t="s">
+      <c r="E30" s="17"/>
+      <c r="F30" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="G30" s="16" t="s">
+      <c r="G30" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H30" s="16" t="s">
+      <c r="H30" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="I30" s="16" t="s">
+      <c r="I30" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="16">
-        <v>1</v>
-      </c>
-      <c r="K30" s="16">
-        <v>1</v>
-      </c>
-      <c r="L30" s="16">
+      <c r="J30" s="17">
+        <v>1</v>
+      </c>
+      <c r="K30" s="17">
+        <v>1</v>
+      </c>
+      <c r="L30" s="17">
         <v>0.01</v>
       </c>
-      <c r="M30" s="16">
-        <v>1</v>
-      </c>
-      <c r="N30" s="16"/>
+      <c r="M30" s="17">
+        <v>1</v>
+      </c>
+      <c r="N30" s="17"/>
     </row>
     <row r="31" ht="16" spans="4:14">
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="16"/>
-      <c r="F31" s="18" t="s">
+      <c r="E31" s="17"/>
+      <c r="F31" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="G31" s="16" t="s">
+      <c r="G31" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H31" s="16" t="s">
+      <c r="H31" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="I31" s="16" t="s">
+      <c r="I31" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="J31" s="16">
-        <v>1</v>
-      </c>
-      <c r="K31" s="16">
-        <v>1</v>
-      </c>
-      <c r="L31" s="16">
+      <c r="J31" s="17">
+        <v>1</v>
+      </c>
+      <c r="K31" s="17">
+        <v>1</v>
+      </c>
+      <c r="L31" s="17">
         <f t="shared" ref="L31:L36" si="2">L30</f>
         <v>0.01</v>
       </c>
-      <c r="M31" s="16">
-        <v>1</v>
-      </c>
-      <c r="N31" s="16"/>
+      <c r="M31" s="17">
+        <v>1</v>
+      </c>
+      <c r="N31" s="17"/>
     </row>
     <row r="32" ht="16" spans="4:14">
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="E32" s="16"/>
-      <c r="F32" s="18" t="s">
+      <c r="E32" s="17"/>
+      <c r="F32" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="G32" s="16" t="s">
+      <c r="G32" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H32" s="16" t="s">
+      <c r="H32" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="I32" s="16" t="s">
+      <c r="I32" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="J32" s="16">
-        <v>1</v>
-      </c>
-      <c r="K32" s="16">
-        <v>1</v>
-      </c>
-      <c r="L32" s="16">
+      <c r="J32" s="17">
+        <v>1</v>
+      </c>
+      <c r="K32" s="17">
+        <v>1</v>
+      </c>
+      <c r="L32" s="17">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M32" s="16">
-        <v>1</v>
-      </c>
-      <c r="N32" s="16"/>
+      <c r="M32" s="17">
+        <v>1</v>
+      </c>
+      <c r="N32" s="17"/>
     </row>
     <row r="33" ht="16" spans="4:14">
-      <c r="D33" s="16" t="s">
+      <c r="D33" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="16"/>
-      <c r="F33" s="17" t="s">
+      <c r="E33" s="17"/>
+      <c r="F33" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G33" s="16" t="s">
+      <c r="G33" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H33" s="16" t="s">
+      <c r="H33" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="I33" s="16" t="s">
+      <c r="I33" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="J33" s="16">
-        <v>1</v>
-      </c>
-      <c r="K33" s="16">
+      <c r="J33" s="17">
+        <v>1</v>
+      </c>
+      <c r="K33" s="17">
         <f>K32</f>
         <v>1</v>
       </c>
-      <c r="L33" s="16">
+      <c r="L33" s="17">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M33" s="16">
-        <v>1</v>
-      </c>
-      <c r="N33" s="16"/>
+      <c r="M33" s="17">
+        <v>1</v>
+      </c>
+      <c r="N33" s="17"/>
     </row>
     <row r="34" ht="16" spans="4:14">
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="E34" s="16"/>
-      <c r="F34" s="17" t="s">
+      <c r="E34" s="17"/>
+      <c r="F34" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="G34" s="16" t="s">
+      <c r="G34" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H34" s="16" t="s">
+      <c r="H34" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="I34" s="16" t="s">
+      <c r="I34" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="J34" s="16">
-        <v>1</v>
-      </c>
-      <c r="K34" s="16">
+      <c r="J34" s="17">
+        <v>1</v>
+      </c>
+      <c r="K34" s="17">
         <f>K33</f>
         <v>1</v>
       </c>
-      <c r="L34" s="16">
+      <c r="L34" s="17">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M34" s="16">
-        <v>1</v>
-      </c>
-      <c r="N34" s="16"/>
+      <c r="M34" s="17">
+        <v>1</v>
+      </c>
+      <c r="N34" s="17"/>
     </row>
     <row r="35" ht="16" spans="4:14">
-      <c r="D35" s="16" t="s">
+      <c r="D35" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E35" s="16"/>
-      <c r="F35" s="17" t="s">
+      <c r="E35" s="17"/>
+      <c r="F35" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="16" t="s">
+      <c r="G35" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H35" s="16" t="s">
+      <c r="H35" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="I35" s="16" t="s">
+      <c r="I35" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="J35" s="16">
-        <v>1</v>
-      </c>
-      <c r="K35" s="16">
+      <c r="J35" s="17">
+        <v>1</v>
+      </c>
+      <c r="K35" s="17">
         <f>K34</f>
         <v>1</v>
       </c>
-      <c r="L35" s="16">
+      <c r="L35" s="17">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M35" s="16">
-        <v>1</v>
-      </c>
-      <c r="N35" s="16"/>
+      <c r="M35" s="17">
+        <v>1</v>
+      </c>
+      <c r="N35" s="17"/>
     </row>
     <row r="36" ht="16" spans="4:14">
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="E36" s="16"/>
-      <c r="F36" s="17" t="s">
+      <c r="E36" s="17"/>
+      <c r="F36" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="G36" s="16" t="s">
+      <c r="G36" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H36" s="16" t="s">
+      <c r="H36" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="I36" s="16" t="s">
+      <c r="I36" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="J36" s="16">
-        <v>1</v>
-      </c>
-      <c r="K36" s="16">
+      <c r="J36" s="17">
+        <v>1</v>
+      </c>
+      <c r="K36" s="17">
         <f>K35</f>
         <v>1</v>
       </c>
-      <c r="L36" s="16">
+      <c r="L36" s="17">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M36" s="16">
-        <v>1</v>
-      </c>
-      <c r="N36" s="16"/>
+      <c r="M36" s="17">
+        <v>1</v>
+      </c>
+      <c r="N36" s="17"/>
     </row>
     <row r="37" ht="16" spans="4:14">
-      <c r="D37" s="19" t="s">
+      <c r="D37" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="E37" s="19"/>
-      <c r="F37" s="20" t="s">
+      <c r="E37" s="20"/>
+      <c r="F37" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="G37" s="19" t="s">
+      <c r="G37" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="H37" s="19" t="s">
+      <c r="H37" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="I37" s="19" t="s">
+      <c r="I37" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="J37" s="19">
-        <v>1</v>
-      </c>
-      <c r="K37" s="19">
-        <v>1</v>
-      </c>
-      <c r="L37" s="19">
+      <c r="J37" s="20">
+        <v>1</v>
+      </c>
+      <c r="K37" s="20">
+        <v>1</v>
+      </c>
+      <c r="L37" s="20">
         <v>0.01</v>
       </c>
-      <c r="M37" s="19">
-        <v>1</v>
-      </c>
-      <c r="N37" s="16"/>
+      <c r="M37" s="20">
+        <v>1</v>
+      </c>
+      <c r="N37" s="17"/>
     </row>
     <row r="38" ht="16" spans="4:14">
-      <c r="D38" s="19" t="s">
+      <c r="D38" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="E38" s="19"/>
-      <c r="F38" s="21" t="s">
+      <c r="E38" s="20"/>
+      <c r="F38" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="G38" s="19" t="s">
+      <c r="G38" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="H38" s="19" t="s">
+      <c r="H38" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="I38" s="19" t="s">
+      <c r="I38" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="J38" s="19">
-        <v>1</v>
-      </c>
-      <c r="K38" s="19">
-        <v>1</v>
-      </c>
-      <c r="L38" s="19">
+      <c r="J38" s="20">
+        <v>1</v>
+      </c>
+      <c r="K38" s="20">
+        <v>1</v>
+      </c>
+      <c r="L38" s="20">
         <f t="shared" ref="L38:L43" si="3">L37</f>
         <v>0.01</v>
       </c>
-      <c r="M38" s="19">
-        <v>1</v>
-      </c>
-      <c r="N38" s="16"/>
+      <c r="M38" s="20">
+        <v>1</v>
+      </c>
+      <c r="N38" s="17"/>
     </row>
     <row r="39" ht="16" spans="4:14">
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="E39" s="19"/>
-      <c r="F39" s="21" t="s">
+      <c r="E39" s="20"/>
+      <c r="F39" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="G39" s="19" t="s">
+      <c r="G39" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="H39" s="19" t="s">
+      <c r="H39" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="I39" s="19" t="s">
+      <c r="I39" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="J39" s="19">
-        <v>1</v>
-      </c>
-      <c r="K39" s="19">
-        <v>1</v>
-      </c>
-      <c r="L39" s="19">
+      <c r="J39" s="20">
+        <v>1</v>
+      </c>
+      <c r="K39" s="20">
+        <v>1</v>
+      </c>
+      <c r="L39" s="20">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M39" s="19">
-        <v>1</v>
-      </c>
-      <c r="N39" s="16"/>
+      <c r="M39" s="20">
+        <v>1</v>
+      </c>
+      <c r="N39" s="17"/>
     </row>
     <row r="40" ht="16" spans="4:14">
-      <c r="D40" s="19" t="s">
+      <c r="D40" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="E40" s="19"/>
-      <c r="F40" s="22" t="s">
+      <c r="E40" s="20"/>
+      <c r="F40" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="G40" s="19" t="s">
+      <c r="G40" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="H40" s="19" t="s">
+      <c r="H40" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="I40" s="19" t="s">
+      <c r="I40" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="J40" s="19">
-        <v>1</v>
-      </c>
-      <c r="K40" s="19">
+      <c r="J40" s="20">
+        <v>1</v>
+      </c>
+      <c r="K40" s="20">
         <f>K39</f>
         <v>1</v>
       </c>
-      <c r="L40" s="19">
+      <c r="L40" s="20">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M40" s="19">
-        <v>1</v>
-      </c>
-      <c r="N40" s="16"/>
+      <c r="M40" s="20">
+        <v>1</v>
+      </c>
+      <c r="N40" s="17"/>
     </row>
     <row r="41" ht="16" spans="4:14">
-      <c r="D41" s="19" t="s">
+      <c r="D41" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="E41" s="19"/>
-      <c r="F41" s="22" t="s">
+      <c r="E41" s="20"/>
+      <c r="F41" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="G41" s="19" t="s">
+      <c r="G41" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="H41" s="19" t="s">
+      <c r="H41" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="I41" s="19" t="s">
+      <c r="I41" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="J41" s="19">
-        <v>1</v>
-      </c>
-      <c r="K41" s="19">
+      <c r="J41" s="20">
+        <v>1</v>
+      </c>
+      <c r="K41" s="20">
         <f>K40</f>
         <v>1</v>
       </c>
-      <c r="L41" s="19">
+      <c r="L41" s="20">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M41" s="19">
-        <v>1</v>
-      </c>
-      <c r="N41" s="16"/>
+      <c r="M41" s="20">
+        <v>1</v>
+      </c>
+      <c r="N41" s="17"/>
     </row>
     <row r="42" ht="16" spans="4:14">
-      <c r="D42" s="19" t="s">
+      <c r="D42" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="E42" s="19"/>
-      <c r="F42" s="22" t="s">
+      <c r="E42" s="20"/>
+      <c r="F42" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="G42" s="19" t="s">
+      <c r="G42" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="H42" s="19" t="s">
+      <c r="H42" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="I42" s="19" t="s">
+      <c r="I42" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="J42" s="19">
-        <v>1</v>
-      </c>
-      <c r="K42" s="19">
+      <c r="J42" s="20">
+        <v>1</v>
+      </c>
+      <c r="K42" s="20">
         <f>K41</f>
         <v>1</v>
       </c>
-      <c r="L42" s="19">
+      <c r="L42" s="20">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M42" s="19">
-        <v>1</v>
-      </c>
-      <c r="N42" s="16"/>
+      <c r="M42" s="20">
+        <v>1</v>
+      </c>
+      <c r="N42" s="17"/>
     </row>
     <row r="43" ht="16" spans="4:14">
-      <c r="D43" s="19" t="s">
+      <c r="D43" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="E43" s="19"/>
-      <c r="F43" s="22" t="s">
+      <c r="E43" s="20"/>
+      <c r="F43" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="G43" s="19" t="s">
+      <c r="G43" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="H43" s="19" t="s">
+      <c r="H43" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="I43" s="19" t="s">
+      <c r="I43" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="J43" s="19">
-        <v>1</v>
-      </c>
-      <c r="K43" s="19">
+      <c r="J43" s="20">
+        <v>1</v>
+      </c>
+      <c r="K43" s="20">
         <f>K42</f>
         <v>1</v>
       </c>
-      <c r="L43" s="19">
+      <c r="L43" s="20">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M43" s="19">
-        <v>1</v>
-      </c>
-      <c r="N43" s="16"/>
+      <c r="M43" s="20">
+        <v>1</v>
+      </c>
+      <c r="N43" s="17"/>
     </row>
     <row r="44" spans="4:14">
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="19"/>
-      <c r="J44" s="19"/>
-      <c r="K44" s="19"/>
-      <c r="L44" s="19"/>
-      <c r="M44" s="19"/>
-      <c r="N44" s="16"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="20"/>
+      <c r="N44" s="17"/>
     </row>
     <row r="45" spans="4:14">
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19"/>
-      <c r="K45" s="19"/>
-      <c r="L45" s="19"/>
-      <c r="M45" s="19"/>
-      <c r="N45" s="16"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="20"/>
+      <c r="M45" s="20"/>
+      <c r="N45" s="17"/>
     </row>
     <row r="46" spans="4:14">
-      <c r="N46" s="16"/>
+      <c r="N46" s="17"/>
     </row>
     <row r="47" spans="4:14">
-      <c r="N47" s="16"/>
+      <c r="N47" s="17"/>
     </row>
     <row r="48" spans="4:14">
-      <c r="N48" s="16"/>
+      <c r="N48" s="17"/>
     </row>
     <row r="49" spans="4:14">
-      <c r="N49" s="16"/>
+      <c r="N49" s="17"/>
     </row>
     <row r="50" spans="4:14">
-      <c r="N50" s="16"/>
+      <c r="N50" s="17"/>
     </row>
     <row r="51" spans="4:14">
-      <c r="N51" s="16"/>
+      <c r="N51" s="17"/>
     </row>
     <row r="52" spans="4:14">
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="24"/>
-      <c r="G52" s="16"/>
-      <c r="H52" s="16"/>
-      <c r="I52" s="16"/>
-      <c r="J52" s="16"/>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="16"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="25"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
+      <c r="M52" s="17"/>
+      <c r="N52" s="17"/>
     </row>
     <row r="53" spans="4:14">
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="16"/>
-      <c r="H53" s="16"/>
-      <c r="I53" s="16"/>
-      <c r="J53" s="16"/>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="16"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="17"/>
+      <c r="I53" s="17"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="17"/>
+      <c r="L53" s="17"/>
+      <c r="M53" s="17"/>
+      <c r="N53" s="17"/>
     </row>
     <row r="54" spans="4:14">
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
-      <c r="H54" s="16"/>
-      <c r="I54" s="16"/>
-      <c r="J54" s="16"/>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="16"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5052,14 +5053,14 @@
       </c>
       <c r="K53" s="12"/>
       <c r="L53" s="3"/>
-      <c r="M53" s="3" t="s">
+      <c r="M53" s="13" t="s">
         <v>156</v>
       </c>
       <c r="N53" s="3"/>
-      <c r="O53" s="13" t="s">
+      <c r="O53" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="P53" s="3" t="s">
+      <c r="P53" s="13" t="s">
         <v>156</v>
       </c>
       <c r="Q53" s="3">

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -245,7 +245,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="157">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -709,16 +709,13 @@
     <t>UC_ACT</t>
   </si>
   <si>
-    <t>UC_COMNET</t>
-  </si>
-  <si>
     <t>UCE_4</t>
   </si>
   <si>
+    <t>Tra_EV_Bat*fromrecy, Tra_EV_Bat*virgin_pack</t>
+  </si>
+  <si>
     <t>AuxStoIN</t>
-  </si>
-  <si>
-    <t>Tra_EV_Bat*fromrecy, Tra_EV_Bat*virgin_pack</t>
   </si>
 </sst>
 </file>
@@ -941,7 +938,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -953,13 +949,14 @@
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <name val="Times New Roman"/>
+      <name val="Tahoma"/>
       <charset val="0"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
   </fonts>
@@ -1193,21 +1190,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFE4E7EB"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1343,7 +1331,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1355,34 +1343,34 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1468,10 +1456,10 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1482,17 +1470,14 @@
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="51" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="51" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1512,7 +1497,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -2061,7 +2045,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="35">
+      <c r="F21" s="33">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -2175,10 +2159,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="39"/>
+      <c r="K10" s="37"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="39"/>
+      <c r="K11" s="37"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2199,12 +2183,12 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:13">
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="17"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
@@ -2219,19 +2203,19 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="28"/>
+      <c r="K6" s="26"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="27">
         <v>10</v>
       </c>
     </row>
@@ -2239,17 +2223,17 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="27">
         <v>7</v>
       </c>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
     </row>
     <row r="9" ht="16" spans="2:13">
       <c r="B9" t="s">
@@ -2258,10 +2242,10 @@
       <c r="C9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="27">
         <v>10</v>
       </c>
     </row>
@@ -2269,17 +2253,17 @@
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="27">
         <v>8</v>
       </c>
-      <c r="K10" s="30"/>
-      <c r="L10" s="31"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="29"/>
     </row>
     <row r="11" ht="16" spans="2:13">
       <c r="B11" t="s">
@@ -2288,10 +2272,10 @@
       <c r="C11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="25">
         <v>1.5</v>
       </c>
     </row>
@@ -2302,10 +2286,10 @@
       <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="25">
         <v>1.5</v>
       </c>
     </row>
@@ -2313,13 +2297,13 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="16">
         <v>2</v>
       </c>
     </row>
@@ -2327,13 +2311,13 @@
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="16">
         <v>0</v>
       </c>
     </row>
@@ -2341,13 +2325,13 @@
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="16">
         <v>0</v>
       </c>
     </row>
@@ -2355,13 +2339,13 @@
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="32">
+      <c r="E16" s="30">
         <v>12</v>
       </c>
     </row>
@@ -2369,31 +2353,31 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="33" t="s">
+      <c r="D17" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="32">
         <v>0.2</v>
       </c>
-      <c r="F17" s="17"/>
+      <c r="F17" s="16"/>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="32">
         <v>0.2</v>
       </c>
-      <c r="F18" s="17"/>
+      <c r="F18" s="16"/>
     </row>
     <row r="19" ht="16" spans="2:6">
       <c r="B19" t="s">
@@ -2402,28 +2386,28 @@
       <c r="C19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="D19" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="32">
         <v>0.2</v>
       </c>
-      <c r="F19" s="17"/>
+      <c r="F19" s="16"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="33" t="s">
+      <c r="D20" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="34">
+      <c r="E20" s="32">
         <v>0.5</v>
       </c>
-      <c r="F20" s="17"/>
+      <c r="F20" s="16"/>
     </row>
     <row r="21" ht="16" spans="2:6">
       <c r="B21" t="s">
@@ -2432,13 +2416,13 @@
       <c r="C21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="33" t="s">
+      <c r="D21" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="34">
+      <c r="E21" s="32">
         <v>0.8</v>
       </c>
-      <c r="F21" s="17"/>
+      <c r="F21" s="16"/>
     </row>
     <row r="22" ht="16" spans="2:6">
       <c r="B22" t="s">
@@ -2447,122 +2431,122 @@
       <c r="C22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="33" t="s">
+      <c r="D22" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="27"/>
-      <c r="F22" s="17"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="16"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="33" t="s">
+      <c r="D23" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="17">
-        <v>1</v>
-      </c>
-      <c r="F23" s="17"/>
+      <c r="E23" s="16">
+        <v>1</v>
+      </c>
+      <c r="F23" s="16"/>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="33" t="s">
+      <c r="D24" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="17">
-        <v>1</v>
-      </c>
-      <c r="F24" s="17"/>
+      <c r="E24" s="16">
+        <v>1</v>
+      </c>
+      <c r="F24" s="16"/>
     </row>
     <row r="25" ht="16" spans="2:6">
       <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="33" t="s">
+      <c r="D25" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="17">
-        <v>1</v>
-      </c>
-      <c r="F25" s="17"/>
+      <c r="E25" s="16">
+        <v>1</v>
+      </c>
+      <c r="F25" s="16"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="27" t="s">
+      <c r="C26" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="33" t="s">
+      <c r="D26" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="25">
         <v>0.05</v>
       </c>
-      <c r="F26" s="17"/>
+      <c r="F26" s="16"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="35" t="s">
+      <c r="B27" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="36" t="s">
+      <c r="C27" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="36" t="s">
+      <c r="D27" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="36">
+      <c r="E27" s="34">
         <v>2020</v>
       </c>
-      <c r="F27" s="17"/>
+      <c r="F27" s="16"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="36" t="s">
+      <c r="D28" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="37">
+      <c r="E28" s="35">
         <v>2020</v>
       </c>
-      <c r="F28" s="17"/>
+      <c r="F28" s="16"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
     </row>
     <row r="38" spans="3:5">
       <c r="C38" s="1"/>
@@ -2570,360 +2554,360 @@
       <c r="E38" s="1"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="38" t="s">
+      <c r="C54" s="36" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="38"/>
-      <c r="E56" s="38"/>
-      <c r="F56" s="38"/>
-      <c r="G56" s="38"/>
-      <c r="H56" s="38"/>
-      <c r="I56" s="38"/>
-      <c r="J56" s="38"/>
-      <c r="K56" s="38"/>
+      <c r="D56" s="36"/>
+      <c r="E56" s="36"/>
+      <c r="F56" s="36"/>
+      <c r="G56" s="36"/>
+      <c r="H56" s="36"/>
+      <c r="I56" s="36"/>
+      <c r="J56" s="36"/>
+      <c r="K56" s="36"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="38" t="s">
+      <c r="C57" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="38" t="s">
+      <c r="D57" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="38" t="s">
+      <c r="E57" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="F57" s="38" t="s">
+      <c r="F57" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="G57" s="38" t="s">
+      <c r="G57" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="38" t="s">
+      <c r="H57" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="38" t="s">
+      <c r="I57" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="J57" s="38" t="s">
+      <c r="J57" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="K57" s="38" t="s">
+      <c r="K57" s="36" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="38"/>
-      <c r="D58" s="38"/>
-      <c r="E58" s="38"/>
-      <c r="F58" s="38"/>
-      <c r="G58" s="38"/>
-      <c r="H58" s="38"/>
-      <c r="I58" s="38"/>
-      <c r="J58" s="38"/>
-      <c r="K58" s="38"/>
+      <c r="C58" s="36"/>
+      <c r="D58" s="36"/>
+      <c r="E58" s="36"/>
+      <c r="F58" s="36"/>
+      <c r="G58" s="36"/>
+      <c r="H58" s="36"/>
+      <c r="I58" s="36"/>
+      <c r="J58" s="36"/>
+      <c r="K58" s="36"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="38"/>
-      <c r="D59" s="38"/>
-      <c r="E59" s="38"/>
-      <c r="F59" s="38"/>
-      <c r="G59" s="38"/>
-      <c r="H59" s="38"/>
-      <c r="I59" s="38"/>
-      <c r="J59" s="38"/>
-      <c r="K59" s="38"/>
+      <c r="C59" s="36"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="36"/>
+      <c r="F59" s="36"/>
+      <c r="G59" s="36"/>
+      <c r="H59" s="36"/>
+      <c r="I59" s="36"/>
+      <c r="J59" s="36"/>
+      <c r="K59" s="36"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="38"/>
-      <c r="D60" s="38"/>
-      <c r="E60" s="38"/>
-      <c r="F60" s="38"/>
-      <c r="G60" s="38"/>
-      <c r="H60" s="38"/>
-      <c r="I60" s="38"/>
-      <c r="J60" s="38"/>
-      <c r="K60" s="38"/>
+      <c r="C60" s="36"/>
+      <c r="D60" s="36"/>
+      <c r="E60" s="36"/>
+      <c r="F60" s="36"/>
+      <c r="G60" s="36"/>
+      <c r="H60" s="36"/>
+      <c r="I60" s="36"/>
+      <c r="J60" s="36"/>
+      <c r="K60" s="36"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="38"/>
-      <c r="D61" s="38"/>
-      <c r="E61" s="38"/>
-      <c r="F61" s="38"/>
-      <c r="G61" s="38"/>
-      <c r="H61" s="38"/>
-      <c r="I61" s="38"/>
-      <c r="J61" s="38"/>
-      <c r="K61" s="38"/>
+      <c r="C61" s="36"/>
+      <c r="D61" s="36"/>
+      <c r="E61" s="36"/>
+      <c r="F61" s="36"/>
+      <c r="G61" s="36"/>
+      <c r="H61" s="36"/>
+      <c r="I61" s="36"/>
+      <c r="J61" s="36"/>
+      <c r="K61" s="36"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="38"/>
-      <c r="D62" s="38"/>
-      <c r="E62" s="38"/>
-      <c r="F62" s="38"/>
-      <c r="G62" s="38"/>
-      <c r="H62" s="38"/>
-      <c r="I62" s="38"/>
-      <c r="J62" s="38"/>
-      <c r="K62" s="38"/>
+      <c r="C62" s="36"/>
+      <c r="D62" s="36"/>
+      <c r="E62" s="36"/>
+      <c r="F62" s="36"/>
+      <c r="G62" s="36"/>
+      <c r="H62" s="36"/>
+      <c r="I62" s="36"/>
+      <c r="J62" s="36"/>
+      <c r="K62" s="36"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="38"/>
-      <c r="D63" s="38"/>
-      <c r="E63" s="38"/>
-      <c r="F63" s="38"/>
-      <c r="G63" s="38"/>
-      <c r="H63" s="38"/>
-      <c r="I63" s="38"/>
-      <c r="J63" s="38"/>
-      <c r="K63" s="38"/>
+      <c r="C63" s="36"/>
+      <c r="D63" s="36"/>
+      <c r="E63" s="36"/>
+      <c r="F63" s="36"/>
+      <c r="G63" s="36"/>
+      <c r="H63" s="36"/>
+      <c r="I63" s="36"/>
+      <c r="J63" s="36"/>
+      <c r="K63" s="36"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="38"/>
-      <c r="D64" s="38"/>
-      <c r="E64" s="38"/>
-      <c r="F64" s="38"/>
-      <c r="G64" s="38"/>
-      <c r="H64" s="38"/>
-      <c r="I64" s="38"/>
-      <c r="J64" s="38"/>
-      <c r="K64" s="38"/>
+      <c r="C64" s="36"/>
+      <c r="D64" s="36"/>
+      <c r="E64" s="36"/>
+      <c r="F64" s="36"/>
+      <c r="G64" s="36"/>
+      <c r="H64" s="36"/>
+      <c r="I64" s="36"/>
+      <c r="J64" s="36"/>
+      <c r="K64" s="36"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="38"/>
-      <c r="D65" s="38"/>
-      <c r="E65" s="38"/>
-      <c r="F65" s="38"/>
-      <c r="G65" s="38"/>
-      <c r="H65" s="38"/>
-      <c r="I65" s="38"/>
-      <c r="J65" s="38"/>
-      <c r="K65" s="38"/>
+      <c r="C65" s="36"/>
+      <c r="D65" s="36"/>
+      <c r="E65" s="36"/>
+      <c r="F65" s="36"/>
+      <c r="G65" s="36"/>
+      <c r="H65" s="36"/>
+      <c r="I65" s="36"/>
+      <c r="J65" s="36"/>
+      <c r="K65" s="36"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="38"/>
-      <c r="D66" s="38"/>
-      <c r="E66" s="38"/>
-      <c r="F66" s="38"/>
-      <c r="G66" s="38"/>
-      <c r="H66" s="38"/>
-      <c r="I66" s="38"/>
-      <c r="J66" s="38"/>
-      <c r="K66" s="38"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+      <c r="G66" s="36"/>
+      <c r="H66" s="36"/>
+      <c r="I66" s="36"/>
+      <c r="J66" s="36"/>
+      <c r="K66" s="36"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="38"/>
-      <c r="D67" s="38"/>
-      <c r="E67" s="38"/>
-      <c r="F67" s="38"/>
-      <c r="G67" s="38"/>
-      <c r="H67" s="38"/>
-      <c r="I67" s="38"/>
-      <c r="J67" s="38"/>
-      <c r="K67" s="38"/>
+      <c r="C67" s="36"/>
+      <c r="D67" s="36"/>
+      <c r="E67" s="36"/>
+      <c r="F67" s="36"/>
+      <c r="G67" s="36"/>
+      <c r="H67" s="36"/>
+      <c r="I67" s="36"/>
+      <c r="J67" s="36"/>
+      <c r="K67" s="36"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="38"/>
-      <c r="D68" s="38"/>
-      <c r="E68" s="38"/>
-      <c r="F68" s="38"/>
-      <c r="G68" s="38"/>
-      <c r="H68" s="38"/>
-      <c r="I68" s="38"/>
-      <c r="J68" s="38"/>
-      <c r="K68" s="38"/>
+      <c r="C68" s="36"/>
+      <c r="D68" s="36"/>
+      <c r="E68" s="36"/>
+      <c r="F68" s="36"/>
+      <c r="G68" s="36"/>
+      <c r="H68" s="36"/>
+      <c r="I68" s="36"/>
+      <c r="J68" s="36"/>
+      <c r="K68" s="36"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="38"/>
-      <c r="D69" s="38"/>
-      <c r="E69" s="38"/>
-      <c r="F69" s="38"/>
-      <c r="G69" s="38"/>
-      <c r="H69" s="38"/>
-      <c r="I69" s="38"/>
-      <c r="J69" s="38"/>
-      <c r="K69" s="38"/>
+      <c r="C69" s="36"/>
+      <c r="D69" s="36"/>
+      <c r="E69" s="36"/>
+      <c r="F69" s="36"/>
+      <c r="G69" s="36"/>
+      <c r="H69" s="36"/>
+      <c r="I69" s="36"/>
+      <c r="J69" s="36"/>
+      <c r="K69" s="36"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="38"/>
-      <c r="D70" s="38"/>
-      <c r="E70" s="38"/>
-      <c r="F70" s="38"/>
-      <c r="G70" s="38"/>
-      <c r="H70" s="38"/>
-      <c r="I70" s="38"/>
-      <c r="J70" s="38"/>
-      <c r="K70" s="38"/>
+      <c r="C70" s="36"/>
+      <c r="D70" s="36"/>
+      <c r="E70" s="36"/>
+      <c r="F70" s="36"/>
+      <c r="G70" s="36"/>
+      <c r="H70" s="36"/>
+      <c r="I70" s="36"/>
+      <c r="J70" s="36"/>
+      <c r="K70" s="36"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="38"/>
-      <c r="D71" s="38"/>
-      <c r="E71" s="38"/>
-      <c r="F71" s="38"/>
-      <c r="G71" s="38"/>
-      <c r="H71" s="38"/>
-      <c r="I71" s="38"/>
-      <c r="J71" s="38"/>
-      <c r="K71" s="38"/>
+      <c r="C71" s="36"/>
+      <c r="D71" s="36"/>
+      <c r="E71" s="36"/>
+      <c r="F71" s="36"/>
+      <c r="G71" s="36"/>
+      <c r="H71" s="36"/>
+      <c r="I71" s="36"/>
+      <c r="J71" s="36"/>
+      <c r="K71" s="36"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="38"/>
-      <c r="D72" s="38"/>
-      <c r="E72" s="38"/>
-      <c r="F72" s="38"/>
-      <c r="G72" s="38"/>
-      <c r="H72" s="38"/>
-      <c r="I72" s="38"/>
-      <c r="J72" s="38"/>
-      <c r="K72" s="38"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+      <c r="G72" s="36"/>
+      <c r="H72" s="36"/>
+      <c r="I72" s="36"/>
+      <c r="J72" s="36"/>
+      <c r="K72" s="36"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="38"/>
-      <c r="D73" s="38"/>
-      <c r="E73" s="38"/>
-      <c r="F73" s="38"/>
-      <c r="G73" s="38"/>
-      <c r="H73" s="38"/>
-      <c r="I73" s="38"/>
-      <c r="J73" s="38"/>
-      <c r="K73" s="38"/>
+      <c r="C73" s="36"/>
+      <c r="D73" s="36"/>
+      <c r="E73" s="36"/>
+      <c r="F73" s="36"/>
+      <c r="G73" s="36"/>
+      <c r="H73" s="36"/>
+      <c r="I73" s="36"/>
+      <c r="J73" s="36"/>
+      <c r="K73" s="36"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="38"/>
-      <c r="D74" s="38"/>
-      <c r="E74" s="38"/>
-      <c r="F74" s="38"/>
-      <c r="G74" s="38"/>
-      <c r="H74" s="38"/>
-      <c r="I74" s="38"/>
-      <c r="J74" s="38"/>
-      <c r="K74" s="38"/>
+      <c r="C74" s="36"/>
+      <c r="D74" s="36"/>
+      <c r="E74" s="36"/>
+      <c r="F74" s="36"/>
+      <c r="G74" s="36"/>
+      <c r="H74" s="36"/>
+      <c r="I74" s="36"/>
+      <c r="J74" s="36"/>
+      <c r="K74" s="36"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="38"/>
-      <c r="D75" s="38"/>
-      <c r="E75" s="38"/>
-      <c r="F75" s="38"/>
-      <c r="G75" s="38"/>
-      <c r="H75" s="38"/>
-      <c r="I75" s="38"/>
-      <c r="J75" s="38"/>
-      <c r="K75" s="38"/>
+      <c r="C75" s="36"/>
+      <c r="D75" s="36"/>
+      <c r="E75" s="36"/>
+      <c r="F75" s="36"/>
+      <c r="G75" s="36"/>
+      <c r="H75" s="36"/>
+      <c r="I75" s="36"/>
+      <c r="J75" s="36"/>
+      <c r="K75" s="36"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="38"/>
-      <c r="D76" s="38"/>
-      <c r="E76" s="38"/>
-      <c r="F76" s="38"/>
-      <c r="G76" s="38"/>
-      <c r="H76" s="38"/>
-      <c r="I76" s="38"/>
-      <c r="J76" s="38"/>
-      <c r="K76" s="38"/>
+      <c r="C76" s="36"/>
+      <c r="D76" s="36"/>
+      <c r="E76" s="36"/>
+      <c r="F76" s="36"/>
+      <c r="G76" s="36"/>
+      <c r="H76" s="36"/>
+      <c r="I76" s="36"/>
+      <c r="J76" s="36"/>
+      <c r="K76" s="36"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="38"/>
-      <c r="D77" s="38"/>
-      <c r="E77" s="38"/>
-      <c r="F77" s="38"/>
-      <c r="G77" s="38"/>
-      <c r="H77" s="38"/>
-      <c r="I77" s="38"/>
-      <c r="J77" s="38"/>
-      <c r="K77" s="38"/>
+      <c r="C77" s="36"/>
+      <c r="D77" s="36"/>
+      <c r="E77" s="36"/>
+      <c r="F77" s="36"/>
+      <c r="G77" s="36"/>
+      <c r="H77" s="36"/>
+      <c r="I77" s="36"/>
+      <c r="J77" s="36"/>
+      <c r="K77" s="36"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="38"/>
-      <c r="D78" s="38"/>
-      <c r="E78" s="38"/>
-      <c r="F78" s="38"/>
-      <c r="G78" s="38"/>
-      <c r="H78" s="38"/>
-      <c r="I78" s="38"/>
-      <c r="J78" s="38"/>
-      <c r="K78" s="38"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+      <c r="G78" s="36"/>
+      <c r="H78" s="36"/>
+      <c r="I78" s="36"/>
+      <c r="J78" s="36"/>
+      <c r="K78" s="36"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="38"/>
-      <c r="D79" s="38"/>
-      <c r="E79" s="38"/>
-      <c r="F79" s="38"/>
-      <c r="G79" s="38"/>
-      <c r="H79" s="38"/>
-      <c r="I79" s="38"/>
-      <c r="J79" s="38"/>
-      <c r="K79" s="38"/>
+      <c r="C79" s="36"/>
+      <c r="D79" s="36"/>
+      <c r="E79" s="36"/>
+      <c r="F79" s="36"/>
+      <c r="G79" s="36"/>
+      <c r="H79" s="36"/>
+      <c r="I79" s="36"/>
+      <c r="J79" s="36"/>
+      <c r="K79" s="36"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="38"/>
-      <c r="D80" s="38"/>
-      <c r="E80" s="38"/>
-      <c r="F80" s="38"/>
-      <c r="G80" s="38"/>
-      <c r="H80" s="38"/>
-      <c r="I80" s="38"/>
-      <c r="J80" s="38"/>
-      <c r="K80" s="38"/>
+      <c r="C80" s="36"/>
+      <c r="D80" s="36"/>
+      <c r="E80" s="36"/>
+      <c r="F80" s="36"/>
+      <c r="G80" s="36"/>
+      <c r="H80" s="36"/>
+      <c r="I80" s="36"/>
+      <c r="J80" s="36"/>
+      <c r="K80" s="36"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="38"/>
-      <c r="D81" s="38"/>
-      <c r="E81" s="38"/>
-      <c r="F81" s="38"/>
-      <c r="G81" s="38"/>
-      <c r="H81" s="38"/>
-      <c r="I81" s="38"/>
-      <c r="J81" s="38"/>
-      <c r="K81" s="38"/>
+      <c r="C81" s="36"/>
+      <c r="D81" s="36"/>
+      <c r="E81" s="36"/>
+      <c r="F81" s="36"/>
+      <c r="G81" s="36"/>
+      <c r="H81" s="36"/>
+      <c r="I81" s="36"/>
+      <c r="J81" s="36"/>
+      <c r="K81" s="36"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="38"/>
-      <c r="D82" s="38"/>
-      <c r="E82" s="38"/>
-      <c r="F82" s="38"/>
-      <c r="G82" s="38"/>
-      <c r="H82" s="38"/>
-      <c r="I82" s="38"/>
-      <c r="J82" s="38"/>
-      <c r="K82" s="38"/>
+      <c r="C82" s="36"/>
+      <c r="D82" s="36"/>
+      <c r="E82" s="36"/>
+      <c r="F82" s="36"/>
+      <c r="G82" s="36"/>
+      <c r="H82" s="36"/>
+      <c r="I82" s="36"/>
+      <c r="J82" s="36"/>
+      <c r="K82" s="36"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="38"/>
-      <c r="D83" s="38"/>
-      <c r="E83" s="38"/>
-      <c r="F83" s="38"/>
-      <c r="G83" s="38"/>
-      <c r="H83" s="38"/>
-      <c r="I83" s="38"/>
-      <c r="J83" s="38"/>
-      <c r="K83" s="38"/>
+      <c r="C83" s="36"/>
+      <c r="D83" s="36"/>
+      <c r="E83" s="36"/>
+      <c r="F83" s="36"/>
+      <c r="G83" s="36"/>
+      <c r="H83" s="36"/>
+      <c r="I83" s="36"/>
+      <c r="J83" s="36"/>
+      <c r="K83" s="36"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="38" t="s">
+      <c r="C84" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="D84" s="38">
-        <v>1</v>
-      </c>
-      <c r="E84" s="38"/>
-      <c r="F84" s="38"/>
-      <c r="G84" s="38"/>
-      <c r="H84" s="38"/>
-      <c r="I84" s="38"/>
-      <c r="J84" s="38"/>
-      <c r="K84" s="38"/>
+      <c r="D84" s="36">
+        <v>1</v>
+      </c>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
+      <c r="G84" s="36"/>
+      <c r="H84" s="36"/>
+      <c r="I84" s="36"/>
+      <c r="J84" s="36"/>
+      <c r="K84" s="36"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="38"/>
-      <c r="D85" s="38"/>
-      <c r="E85" s="38"/>
-      <c r="F85" s="38"/>
-      <c r="G85" s="38"/>
-      <c r="H85" s="38"/>
-      <c r="I85" s="38"/>
-      <c r="J85" s="38"/>
-      <c r="K85" s="38"/>
+      <c r="C85" s="36"/>
+      <c r="D85" s="36"/>
+      <c r="E85" s="36"/>
+      <c r="F85" s="36"/>
+      <c r="G85" s="36"/>
+      <c r="H85" s="36"/>
+      <c r="I85" s="36"/>
+      <c r="J85" s="36"/>
+      <c r="K85" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2942,6 +2926,7 @@
     <col min="8" max="8" width="27" customWidth="1"/>
     <col min="9" max="9" width="43.7272727272727" customWidth="1"/>
     <col min="12" max="12" width="10.2727272727273" customWidth="1"/>
+    <col min="14" max="14" width="12.8181818181818" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="13" spans="5:21">
@@ -3338,7 +3323,7 @@
       <c r="G31" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H31" s="26" t="s">
+      <c r="H31" s="13" t="s">
         <v>69</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -3547,252 +3532,252 @@
       </c>
     </row>
     <row r="8" spans="2:14">
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="K8" s="15" t="s">
+      <c r="K8" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="L8" s="15" t="s">
+      <c r="L8" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="M8" s="15" t="s">
+      <c r="M8" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="N8" s="15" t="s">
+      <c r="N8" s="14" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="9" spans="2:14">
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="I9" s="15" t="s">
         <v>88</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="15">
         <v>1.25</v>
       </c>
       <c r="L9">
         <v>0.05</v>
       </c>
-      <c r="M9" s="16">
-        <v>1</v>
-      </c>
-      <c r="N9" s="16"/>
+      <c r="M9" s="15">
+        <v>1</v>
+      </c>
+      <c r="N9" s="15"/>
     </row>
     <row r="10" spans="2:14">
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="I10" s="16" t="s">
+      <c r="I10" s="15" t="s">
         <v>88</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="15">
         <v>1.11</v>
       </c>
       <c r="L10">
         <v>0.05</v>
       </c>
-      <c r="M10" s="16">
-        <v>1</v>
-      </c>
-      <c r="N10" s="16"/>
+      <c r="M10" s="15">
+        <v>1</v>
+      </c>
+      <c r="N10" s="15"/>
     </row>
     <row r="11" spans="2:14">
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="15" t="s">
         <v>88</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="15">
         <v>1.15</v>
       </c>
       <c r="L11">
         <v>0.08</v>
       </c>
-      <c r="M11" s="16">
-        <v>1</v>
-      </c>
-      <c r="N11" s="16"/>
+      <c r="M11" s="15">
+        <v>1</v>
+      </c>
+      <c r="N11" s="15"/>
     </row>
     <row r="12" ht="16" spans="2:14">
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="15" t="s">
         <v>93</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="I12" s="16" t="s">
+      <c r="I12" s="15" t="s">
         <v>88</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="15">
         <v>1.12</v>
       </c>
       <c r="L12">
         <v>0.03</v>
       </c>
-      <c r="M12" s="16">
-        <v>1</v>
-      </c>
-      <c r="N12" s="16"/>
+      <c r="M12" s="15">
+        <v>1</v>
+      </c>
+      <c r="N12" s="15"/>
     </row>
     <row r="13" spans="2:14">
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="H13" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="I13" s="16" t="s">
+      <c r="I13" s="15" t="s">
         <v>88</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="15">
         <v>1.2</v>
       </c>
       <c r="L13">
         <v>0.1</v>
       </c>
-      <c r="M13" s="16">
-        <v>1</v>
-      </c>
-      <c r="N13" s="16"/>
+      <c r="M13" s="15">
+        <v>1</v>
+      </c>
+      <c r="N13" s="15"/>
     </row>
     <row r="14" spans="2:14">
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="H14" s="16" t="s">
+      <c r="H14" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="16" t="s">
+      <c r="I14" s="15" t="s">
         <v>88</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="15">
         <v>1.06</v>
       </c>
       <c r="L14">
         <v>0.15</v>
       </c>
-      <c r="M14" s="16">
-        <v>1</v>
-      </c>
-      <c r="N14" s="16"/>
+      <c r="M14" s="15">
+        <v>1</v>
+      </c>
+      <c r="N14" s="15"/>
     </row>
     <row r="15" spans="2:14">
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="H15" s="16" t="s">
+      <c r="H15" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="I15" s="16" t="s">
+      <c r="I15" s="15" t="s">
         <v>88</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="15">
         <v>1.06</v>
       </c>
       <c r="L15">
         <v>0.3</v>
       </c>
-      <c r="M15" s="16">
-        <v>1</v>
-      </c>
-      <c r="N15" s="16"/>
+      <c r="M15" s="15">
+        <v>1</v>
+      </c>
+      <c r="N15" s="15"/>
     </row>
     <row r="16" ht="16" spans="2:14">
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="15" t="s">
         <v>101</v>
       </c>
       <c r="F16" s="2" t="s">
@@ -3806,7 +3791,7 @@
         <f>H15</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I16" s="16" t="s">
+      <c r="I16" s="15" t="s">
         <v>88</v>
       </c>
       <c r="J16">
@@ -3827,7 +3812,7 @@
       </c>
     </row>
     <row r="17" ht="16" spans="4:14">
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="15" t="s">
         <v>103</v>
       </c>
       <c r="F17" s="2" t="s">
@@ -3841,7 +3826,7 @@
         <f t="shared" si="1"/>
         <v>2025, 2150</v>
       </c>
-      <c r="I17" s="16" t="s">
+      <c r="I17" s="15" t="s">
         <v>88</v>
       </c>
       <c r="J17">
@@ -3862,7 +3847,7 @@
       </c>
     </row>
     <row r="18" ht="16" spans="4:14">
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="15" t="s">
         <v>105</v>
       </c>
       <c r="F18" s="2" t="s">
@@ -3876,7 +3861,7 @@
         <f>H17</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I18" s="16" t="s">
+      <c r="I18" s="15" t="s">
         <v>88</v>
       </c>
       <c r="J18">
@@ -3893,604 +3878,604 @@
       </c>
     </row>
     <row r="27" spans="4:14">
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+      <c r="N27" s="16"/>
     </row>
     <row r="28" spans="4:14">
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17" t="s">
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
     </row>
     <row r="29" spans="4:14">
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="F29" s="17" t="s">
+      <c r="F29" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="17" t="s">
+      <c r="G29" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="H29" s="17" t="s">
+      <c r="H29" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="I29" s="17" t="s">
+      <c r="I29" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="J29" s="17" t="s">
+      <c r="J29" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="K29" s="17" t="s">
+      <c r="K29" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="L29" s="17" t="s">
+      <c r="L29" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="M29" s="17" t="s">
+      <c r="M29" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="N29" s="17" t="s">
+      <c r="N29" s="16" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="30" ht="16" spans="4:14">
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="17"/>
-      <c r="F30" s="18" t="s">
+      <c r="E30" s="16"/>
+      <c r="F30" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="G30" s="17" t="s">
+      <c r="G30" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H30" s="17" t="s">
+      <c r="H30" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="I30" s="17" t="s">
+      <c r="I30" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="17">
-        <v>1</v>
-      </c>
-      <c r="K30" s="17">
-        <v>1</v>
-      </c>
-      <c r="L30" s="17">
+      <c r="J30" s="16">
+        <v>1</v>
+      </c>
+      <c r="K30" s="16">
+        <v>1</v>
+      </c>
+      <c r="L30" s="16">
         <v>0.01</v>
       </c>
-      <c r="M30" s="17">
-        <v>1</v>
-      </c>
-      <c r="N30" s="17"/>
+      <c r="M30" s="16">
+        <v>1</v>
+      </c>
+      <c r="N30" s="16"/>
     </row>
     <row r="31" ht="16" spans="4:14">
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="17"/>
-      <c r="F31" s="19" t="s">
+      <c r="E31" s="16"/>
+      <c r="F31" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="G31" s="17" t="s">
+      <c r="G31" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H31" s="17" t="s">
+      <c r="H31" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="I31" s="17" t="s">
+      <c r="I31" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="J31" s="17">
-        <v>1</v>
-      </c>
-      <c r="K31" s="17">
-        <v>1</v>
-      </c>
-      <c r="L31" s="17">
+      <c r="J31" s="16">
+        <v>1</v>
+      </c>
+      <c r="K31" s="16">
+        <v>1</v>
+      </c>
+      <c r="L31" s="16">
         <f t="shared" ref="L31:L36" si="2">L30</f>
         <v>0.01</v>
       </c>
-      <c r="M31" s="17">
-        <v>1</v>
-      </c>
-      <c r="N31" s="17"/>
+      <c r="M31" s="16">
+        <v>1</v>
+      </c>
+      <c r="N31" s="16"/>
     </row>
     <row r="32" ht="16" spans="4:14">
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="E32" s="17"/>
-      <c r="F32" s="19" t="s">
+      <c r="E32" s="16"/>
+      <c r="F32" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="G32" s="17" t="s">
+      <c r="G32" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H32" s="17" t="s">
+      <c r="H32" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="I32" s="17" t="s">
+      <c r="I32" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="J32" s="17">
-        <v>1</v>
-      </c>
-      <c r="K32" s="17">
-        <v>1</v>
-      </c>
-      <c r="L32" s="17">
+      <c r="J32" s="16">
+        <v>1</v>
+      </c>
+      <c r="K32" s="16">
+        <v>1</v>
+      </c>
+      <c r="L32" s="16">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M32" s="17">
-        <v>1</v>
-      </c>
-      <c r="N32" s="17"/>
+      <c r="M32" s="16">
+        <v>1</v>
+      </c>
+      <c r="N32" s="16"/>
     </row>
     <row r="33" ht="16" spans="4:14">
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="17"/>
-      <c r="F33" s="18" t="s">
+      <c r="E33" s="16"/>
+      <c r="F33" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="G33" s="17" t="s">
+      <c r="G33" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H33" s="17" t="s">
+      <c r="H33" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="I33" s="17" t="s">
+      <c r="I33" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="J33" s="17">
-        <v>1</v>
-      </c>
-      <c r="K33" s="17">
+      <c r="J33" s="16">
+        <v>1</v>
+      </c>
+      <c r="K33" s="16">
         <f>K32</f>
         <v>1</v>
       </c>
-      <c r="L33" s="17">
+      <c r="L33" s="16">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M33" s="17">
-        <v>1</v>
-      </c>
-      <c r="N33" s="17"/>
+      <c r="M33" s="16">
+        <v>1</v>
+      </c>
+      <c r="N33" s="16"/>
     </row>
     <row r="34" ht="16" spans="4:14">
-      <c r="D34" s="17" t="s">
+      <c r="D34" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="E34" s="17"/>
-      <c r="F34" s="18" t="s">
+      <c r="E34" s="16"/>
+      <c r="F34" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="G34" s="17" t="s">
+      <c r="G34" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H34" s="17" t="s">
+      <c r="H34" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="I34" s="17" t="s">
+      <c r="I34" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="J34" s="17">
-        <v>1</v>
-      </c>
-      <c r="K34" s="17">
+      <c r="J34" s="16">
+        <v>1</v>
+      </c>
+      <c r="K34" s="16">
         <f>K33</f>
         <v>1</v>
       </c>
-      <c r="L34" s="17">
+      <c r="L34" s="16">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M34" s="17">
-        <v>1</v>
-      </c>
-      <c r="N34" s="17"/>
+      <c r="M34" s="16">
+        <v>1</v>
+      </c>
+      <c r="N34" s="16"/>
     </row>
     <row r="35" ht="16" spans="4:14">
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="E35" s="17"/>
-      <c r="F35" s="18" t="s">
+      <c r="E35" s="16"/>
+      <c r="F35" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="17" t="s">
+      <c r="G35" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H35" s="17" t="s">
+      <c r="H35" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="I35" s="17" t="s">
+      <c r="I35" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="J35" s="17">
-        <v>1</v>
-      </c>
-      <c r="K35" s="17">
+      <c r="J35" s="16">
+        <v>1</v>
+      </c>
+      <c r="K35" s="16">
         <f>K34</f>
         <v>1</v>
       </c>
-      <c r="L35" s="17">
+      <c r="L35" s="16">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M35" s="17">
-        <v>1</v>
-      </c>
-      <c r="N35" s="17"/>
+      <c r="M35" s="16">
+        <v>1</v>
+      </c>
+      <c r="N35" s="16"/>
     </row>
     <row r="36" ht="16" spans="4:14">
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="E36" s="17"/>
-      <c r="F36" s="18" t="s">
+      <c r="E36" s="16"/>
+      <c r="F36" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="G36" s="17" t="s">
+      <c r="G36" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H36" s="17" t="s">
+      <c r="H36" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="I36" s="17" t="s">
+      <c r="I36" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="J36" s="17">
-        <v>1</v>
-      </c>
-      <c r="K36" s="17">
+      <c r="J36" s="16">
+        <v>1</v>
+      </c>
+      <c r="K36" s="16">
         <f>K35</f>
         <v>1</v>
       </c>
-      <c r="L36" s="17">
+      <c r="L36" s="16">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M36" s="17">
-        <v>1</v>
-      </c>
-      <c r="N36" s="17"/>
+      <c r="M36" s="16">
+        <v>1</v>
+      </c>
+      <c r="N36" s="16"/>
     </row>
     <row r="37" ht="16" spans="4:14">
-      <c r="D37" s="20" t="s">
+      <c r="D37" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="E37" s="20"/>
-      <c r="F37" s="21" t="s">
+      <c r="E37" s="19"/>
+      <c r="F37" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="G37" s="20" t="s">
+      <c r="G37" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="H37" s="20" t="s">
+      <c r="H37" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="I37" s="20" t="s">
+      <c r="I37" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="J37" s="20">
-        <v>1</v>
-      </c>
-      <c r="K37" s="20">
-        <v>1</v>
-      </c>
-      <c r="L37" s="20">
+      <c r="J37" s="19">
+        <v>1</v>
+      </c>
+      <c r="K37" s="19">
+        <v>1</v>
+      </c>
+      <c r="L37" s="19">
         <v>0.01</v>
       </c>
-      <c r="M37" s="20">
-        <v>1</v>
-      </c>
-      <c r="N37" s="17"/>
+      <c r="M37" s="19">
+        <v>1</v>
+      </c>
+      <c r="N37" s="16"/>
     </row>
     <row r="38" ht="16" spans="4:14">
-      <c r="D38" s="20" t="s">
+      <c r="D38" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E38" s="20"/>
-      <c r="F38" s="22" t="s">
+      <c r="E38" s="19"/>
+      <c r="F38" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="G38" s="20" t="s">
+      <c r="G38" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="H38" s="20" t="s">
+      <c r="H38" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="I38" s="20" t="s">
+      <c r="I38" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="J38" s="20">
-        <v>1</v>
-      </c>
-      <c r="K38" s="20">
-        <v>1</v>
-      </c>
-      <c r="L38" s="20">
+      <c r="J38" s="19">
+        <v>1</v>
+      </c>
+      <c r="K38" s="19">
+        <v>1</v>
+      </c>
+      <c r="L38" s="19">
         <f t="shared" ref="L38:L43" si="3">L37</f>
         <v>0.01</v>
       </c>
-      <c r="M38" s="20">
-        <v>1</v>
-      </c>
-      <c r="N38" s="17"/>
+      <c r="M38" s="19">
+        <v>1</v>
+      </c>
+      <c r="N38" s="16"/>
     </row>
     <row r="39" ht="16" spans="4:14">
-      <c r="D39" s="20" t="s">
+      <c r="D39" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E39" s="20"/>
-      <c r="F39" s="22" t="s">
+      <c r="E39" s="19"/>
+      <c r="F39" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="G39" s="20" t="s">
+      <c r="G39" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="H39" s="20" t="s">
+      <c r="H39" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="I39" s="20" t="s">
+      <c r="I39" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="J39" s="20">
-        <v>1</v>
-      </c>
-      <c r="K39" s="20">
-        <v>1</v>
-      </c>
-      <c r="L39" s="20">
+      <c r="J39" s="19">
+        <v>1</v>
+      </c>
+      <c r="K39" s="19">
+        <v>1</v>
+      </c>
+      <c r="L39" s="19">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M39" s="20">
-        <v>1</v>
-      </c>
-      <c r="N39" s="17"/>
+      <c r="M39" s="19">
+        <v>1</v>
+      </c>
+      <c r="N39" s="16"/>
     </row>
     <row r="40" ht="16" spans="4:14">
-      <c r="D40" s="20" t="s">
+      <c r="D40" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="E40" s="20"/>
-      <c r="F40" s="23" t="s">
+      <c r="E40" s="19"/>
+      <c r="F40" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="G40" s="20" t="s">
+      <c r="G40" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="H40" s="20" t="s">
+      <c r="H40" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="I40" s="20" t="s">
+      <c r="I40" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="J40" s="20">
-        <v>1</v>
-      </c>
-      <c r="K40" s="20">
+      <c r="J40" s="19">
+        <v>1</v>
+      </c>
+      <c r="K40" s="19">
         <f>K39</f>
         <v>1</v>
       </c>
-      <c r="L40" s="20">
+      <c r="L40" s="19">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M40" s="20">
-        <v>1</v>
-      </c>
-      <c r="N40" s="17"/>
+      <c r="M40" s="19">
+        <v>1</v>
+      </c>
+      <c r="N40" s="16"/>
     </row>
     <row r="41" ht="16" spans="4:14">
-      <c r="D41" s="20" t="s">
+      <c r="D41" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="E41" s="20"/>
-      <c r="F41" s="23" t="s">
+      <c r="E41" s="19"/>
+      <c r="F41" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="G41" s="20" t="s">
+      <c r="G41" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="H41" s="20" t="s">
+      <c r="H41" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="I41" s="20" t="s">
+      <c r="I41" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="J41" s="20">
-        <v>1</v>
-      </c>
-      <c r="K41" s="20">
+      <c r="J41" s="19">
+        <v>1</v>
+      </c>
+      <c r="K41" s="19">
         <f>K40</f>
         <v>1</v>
       </c>
-      <c r="L41" s="20">
+      <c r="L41" s="19">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M41" s="20">
-        <v>1</v>
-      </c>
-      <c r="N41" s="17"/>
+      <c r="M41" s="19">
+        <v>1</v>
+      </c>
+      <c r="N41" s="16"/>
     </row>
     <row r="42" ht="16" spans="4:14">
-      <c r="D42" s="20" t="s">
+      <c r="D42" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="E42" s="20"/>
-      <c r="F42" s="23" t="s">
+      <c r="E42" s="19"/>
+      <c r="F42" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="G42" s="20" t="s">
+      <c r="G42" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="H42" s="20" t="s">
+      <c r="H42" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="I42" s="20" t="s">
+      <c r="I42" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="J42" s="20">
-        <v>1</v>
-      </c>
-      <c r="K42" s="20">
+      <c r="J42" s="19">
+        <v>1</v>
+      </c>
+      <c r="K42" s="19">
         <f>K41</f>
         <v>1</v>
       </c>
-      <c r="L42" s="20">
+      <c r="L42" s="19">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M42" s="20">
-        <v>1</v>
-      </c>
-      <c r="N42" s="17"/>
+      <c r="M42" s="19">
+        <v>1</v>
+      </c>
+      <c r="N42" s="16"/>
     </row>
     <row r="43" ht="16" spans="4:14">
-      <c r="D43" s="20" t="s">
+      <c r="D43" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="E43" s="20"/>
-      <c r="F43" s="23" t="s">
+      <c r="E43" s="19"/>
+      <c r="F43" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="G43" s="20" t="s">
+      <c r="G43" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="H43" s="20" t="s">
+      <c r="H43" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="I43" s="20" t="s">
+      <c r="I43" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="J43" s="20">
-        <v>1</v>
-      </c>
-      <c r="K43" s="20">
+      <c r="J43" s="19">
+        <v>1</v>
+      </c>
+      <c r="K43" s="19">
         <f>K42</f>
         <v>1</v>
       </c>
-      <c r="L43" s="20">
+      <c r="L43" s="19">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M43" s="20">
-        <v>1</v>
-      </c>
-      <c r="N43" s="17"/>
+      <c r="M43" s="19">
+        <v>1</v>
+      </c>
+      <c r="N43" s="16"/>
     </row>
     <row r="44" spans="4:14">
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
-      <c r="K44" s="20"/>
-      <c r="L44" s="20"/>
-      <c r="M44" s="20"/>
-      <c r="N44" s="17"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
+      <c r="K44" s="19"/>
+      <c r="L44" s="19"/>
+      <c r="M44" s="19"/>
+      <c r="N44" s="16"/>
     </row>
     <row r="45" spans="4:14">
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="24"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="20"/>
-      <c r="K45" s="20"/>
-      <c r="L45" s="20"/>
-      <c r="M45" s="20"/>
-      <c r="N45" s="17"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="23"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="16"/>
     </row>
     <row r="46" spans="4:14">
-      <c r="N46" s="17"/>
+      <c r="N46" s="16"/>
     </row>
     <row r="47" spans="4:14">
-      <c r="N47" s="17"/>
+      <c r="N47" s="16"/>
     </row>
     <row r="48" spans="4:14">
-      <c r="N48" s="17"/>
+      <c r="N48" s="16"/>
     </row>
     <row r="49" spans="4:14">
-      <c r="N49" s="17"/>
+      <c r="N49" s="16"/>
     </row>
     <row r="50" spans="4:14">
-      <c r="N50" s="17"/>
+      <c r="N50" s="16"/>
     </row>
     <row r="51" spans="4:14">
-      <c r="N51" s="17"/>
+      <c r="N51" s="16"/>
     </row>
     <row r="52" spans="4:14">
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="17"/>
-      <c r="M52" s="17"/>
-      <c r="N52" s="17"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="16"/>
+      <c r="I52" s="16"/>
+      <c r="J52" s="16"/>
+      <c r="K52" s="16"/>
+      <c r="L52" s="16"/>
+      <c r="M52" s="16"/>
+      <c r="N52" s="16"/>
     </row>
     <row r="53" spans="4:14">
-      <c r="D53" s="17"/>
-      <c r="E53" s="17"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="17"/>
-      <c r="H53" s="17"/>
-      <c r="I53" s="17"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="17"/>
-      <c r="L53" s="17"/>
-      <c r="M53" s="17"/>
-      <c r="N53" s="17"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="16"/>
+      <c r="H53" s="16"/>
+      <c r="I53" s="16"/>
+      <c r="J53" s="16"/>
+      <c r="K53" s="16"/>
+      <c r="L53" s="16"/>
+      <c r="M53" s="16"/>
+      <c r="N53" s="16"/>
     </row>
     <row r="54" spans="4:14">
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="17"/>
-      <c r="G54" s="17"/>
-      <c r="H54" s="17"/>
-      <c r="I54" s="17"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="17"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
+      <c r="H54" s="16"/>
+      <c r="I54" s="16"/>
+      <c r="J54" s="16"/>
+      <c r="K54" s="16"/>
+      <c r="L54" s="16"/>
+      <c r="M54" s="16"/>
+      <c r="N54" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4501,7 +4486,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="F9:AR56"/>
+  <dimension ref="F9:AR70"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="6" max="6" width="24.5454545454545" customWidth="1"/>
@@ -4976,7 +4961,7 @@
       <c r="AL51" s="6"/>
       <c r="AM51" s="6"/>
     </row>
-    <row r="52" ht="16.75" spans="6:44">
+    <row r="52" spans="6:44">
       <c r="G52" s="3" t="s">
         <v>59</v>
       </c>
@@ -5007,8 +4992,11 @@
       <c r="P52" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q52" s="8" t="s">
-        <v>154</v>
+      <c r="Q52" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R52" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="S52" s="6"/>
       <c r="T52" s="6"/>
@@ -5038,35 +5026,28 @@
       <c r="AR52" s="6"/>
     </row>
     <row r="53" ht="16" spans="6:44">
-      <c r="F53" s="9"/>
+      <c r="F53" s="8"/>
       <c r="G53" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="I53" s="10">
+      <c r="I53" s="9">
         <v>2023</v>
       </c>
-      <c r="J53" s="11">
+      <c r="J53" s="10">
         <v>-1</v>
       </c>
-      <c r="K53" s="12"/>
+      <c r="K53" s="11"/>
       <c r="L53" s="3"/>
-      <c r="M53" s="13" t="s">
-        <v>156</v>
-      </c>
       <c r="N53" s="3"/>
-      <c r="O53" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="P53" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q53" s="3">
-        <v>10</v>
-      </c>
-      <c r="R53" s="6"/>
+      <c r="O53" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="R53" s="1">
+        <v>0</v>
+      </c>
       <c r="S53" s="6"/>
       <c r="T53" s="6"/>
       <c r="U53" s="6"/>
@@ -5094,18 +5075,26 @@
       <c r="AQ53" s="6"/>
       <c r="AR53" s="6"/>
     </row>
-    <row r="54" spans="6:44">
+    <row r="54" ht="16" spans="6:44">
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
-      <c r="M54" s="3"/>
+      <c r="M54" s="2" t="s">
+        <v>156</v>
+      </c>
       <c r="N54" s="3"/>
-      <c r="O54" s="3"/>
-      <c r="P54" s="3"/>
-      <c r="Q54" s="3"/>
+      <c r="O54" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>10</v>
+      </c>
     </row>
     <row r="55" spans="6:44">
       <c r="G55" s="3"/>
@@ -5133,6 +5122,85 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
     </row>
+    <row r="66" ht="15.25" spans="7:20">
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
+      <c r="P66" s="1"/>
+      <c r="Q66" s="1"/>
+      <c r="R66" s="1"/>
+      <c r="S66" s="1"/>
+      <c r="T66" s="1"/>
+    </row>
+    <row r="67" ht="16" spans="7:20">
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="13"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="N67" s="1"/>
+      <c r="O67" s="1"/>
+      <c r="Q67" s="1"/>
+      <c r="R67" s="1"/>
+      <c r="S67" s="1"/>
+      <c r="T67" s="1"/>
+    </row>
+    <row r="68" ht="15.25" spans="7:20">
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+      <c r="N68" s="1"/>
+      <c r="O68" s="1"/>
+      <c r="P68" s="1"/>
+      <c r="Q68" s="1"/>
+      <c r="R68" s="1"/>
+      <c r="S68" s="1"/>
+      <c r="T68" s="1"/>
+    </row>
+    <row r="69" spans="7:20">
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1"/>
+      <c r="O69" s="1"/>
+      <c r="P69" s="1"/>
+      <c r="Q69" s="1"/>
+      <c r="R69" s="1"/>
+      <c r="S69" s="1"/>
+      <c r="T69" s="1"/>
+    </row>
+    <row r="70" spans="7:20">
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+      <c r="O70" s="1"/>
+      <c r="P70" s="1"/>
+      <c r="Q70" s="1"/>
+      <c r="R70" s="1"/>
+      <c r="S70" s="1"/>
+      <c r="T70" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -245,7 +245,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="155">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -439,10 +439,10 @@
     <t>UC_COMPRD</t>
   </si>
   <si>
-    <t>UC_RHSRTS</t>
-  </si>
-  <si>
-    <t>UC_RHSRTS~0</t>
+    <t>UC_RHSRT</t>
+  </si>
+  <si>
+    <t>UC_RHSRT~0</t>
   </si>
   <si>
     <t>UC_Desc</t>
@@ -664,12 +664,6 @@
     <t>~UC_T: LO</t>
   </si>
   <si>
-    <t>UC_RHSRT</t>
-  </si>
-  <si>
-    <t>UC_RHSRT~0</t>
-  </si>
-  <si>
     <t>UCE_MaxUtility_scale</t>
   </si>
   <si>
@@ -709,7 +703,7 @@
     <t>UC_ACT</t>
   </si>
   <si>
-    <t>UCE_4</t>
+    <t>UCE_MinAct_of_EVBattery</t>
   </si>
   <si>
     <t>Tra_EV_Bat*fromrecy, Tra_EV_Bat*virgin_pack</t>
@@ -938,12 +932,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -956,7 +950,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Times New Roman"/>
+      <name val="Tahoma"/>
       <charset val="0"/>
     </font>
   </fonts>
@@ -2927,6 +2921,7 @@
     <col min="9" max="9" width="43.7272727272727" customWidth="1"/>
     <col min="12" max="12" width="10.2727272727273" customWidth="1"/>
     <col min="14" max="14" width="12.8181818181818" customWidth="1"/>
+    <col min="15" max="15" width="11.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="13" spans="5:21">
@@ -3179,7 +3174,6 @@
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
@@ -3304,7 +3298,7 @@
       <c r="O30" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="P30" s="1" t="s">
+      <c r="P30" t="s">
         <v>65</v>
       </c>
       <c r="Q30" s="1" t="s">
@@ -3316,7 +3310,7 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
     </row>
-    <row r="31" ht="16" spans="5:23">
+    <row r="31" spans="5:23">
       <c r="F31" s="1" t="s">
         <v>67</v>
       </c>
@@ -4555,10 +4549,10 @@
         <v>63</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>139</v>
+        <v>64</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="Q13" s="1" t="s">
         <v>66</v>
@@ -4567,10 +4561,10 @@
     </row>
     <row r="14" spans="6:18">
       <c r="F14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -4589,7 +4583,7 @@
     </row>
     <row r="15" spans="6:18">
       <c r="H15" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -4743,10 +4737,10 @@
         <v>63</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>139</v>
+        <v>64</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="Q27" s="1" t="s">
         <v>66</v>
@@ -4755,10 +4749,10 @@
     </row>
     <row r="28" ht="16" spans="6:18">
       <c r="F28" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -4777,7 +4771,7 @@
     </row>
     <row r="29" spans="6:18">
       <c r="H29" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -4880,10 +4874,10 @@
         <v>63</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>139</v>
+        <v>64</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="Q36" s="1" t="s">
         <v>66</v>
@@ -4891,10 +4885,10 @@
     </row>
     <row r="37" spans="6:18">
       <c r="F37" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H37" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -4912,7 +4906,7 @@
     </row>
     <row r="38" spans="6:18">
       <c r="H38" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -4928,7 +4922,7 @@
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
@@ -4966,16 +4960,16 @@
         <v>59</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>4</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>25</v>
@@ -4984,7 +4978,7 @@
         <v>33</v>
       </c>
       <c r="N52" s="5" t="s">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="O52" s="5" t="s">
         <v>27</v>
@@ -5028,7 +5022,7 @@
     <row r="53" ht="16" spans="6:44">
       <c r="F53" s="8"/>
       <c r="G53" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>110</v>
@@ -5043,7 +5037,7 @@
       <c r="L53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R53" s="1">
         <v>0</v>
@@ -5083,14 +5077,14 @@
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q54" s="3">
         <v>10</v>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -245,7 +245,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="160">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -710,6 +710,21 @@
   </si>
   <si>
     <t>AuxStoIN</t>
+  </si>
+  <si>
+    <t>UCE_MinAct_of_GRIDBattery</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt*, Util_Rep_Bat*</t>
+  </si>
+  <si>
+    <t>UCE_MinAct_of_HPS</t>
+  </si>
+  <si>
+    <t>UCE_MinAct_of_vtog</t>
+  </si>
+  <si>
+    <t>Tra_BEV_Batt_VtoG</t>
   </si>
 </sst>
 </file>
@@ -1453,7 +1468,7 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1471,6 +1486,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2039,7 +2055,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="34">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -2153,10 +2169,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="37"/>
+      <c r="K10" s="38"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="37"/>
+      <c r="K11" s="38"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2177,12 +2193,12 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:13">
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="16"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="17"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
@@ -2197,19 +2213,19 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="26"/>
+      <c r="K6" s="27"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="28">
         <v>10</v>
       </c>
     </row>
@@ -2217,17 +2233,17 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="28">
         <v>7</v>
       </c>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
     </row>
     <row r="9" ht="16" spans="2:13">
       <c r="B9" t="s">
@@ -2236,10 +2252,10 @@
       <c r="C9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="28">
         <v>10</v>
       </c>
     </row>
@@ -2247,17 +2263,17 @@
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="28">
         <v>8</v>
       </c>
-      <c r="K10" s="28"/>
-      <c r="L10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="30"/>
     </row>
     <row r="11" ht="16" spans="2:13">
       <c r="B11" t="s">
@@ -2266,10 +2282,10 @@
       <c r="C11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <v>1.5</v>
       </c>
     </row>
@@ -2280,10 +2296,10 @@
       <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D12" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="26">
         <v>1.5</v>
       </c>
     </row>
@@ -2291,13 +2307,13 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="17">
         <v>2</v>
       </c>
     </row>
@@ -2305,13 +2321,13 @@
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2319,13 +2335,13 @@
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="17">
         <v>0</v>
       </c>
     </row>
@@ -2333,13 +2349,13 @@
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>12</v>
       </c>
     </row>
@@ -2347,31 +2363,31 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D17" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="33">
         <v>0.2</v>
       </c>
-      <c r="F17" s="16"/>
+      <c r="F17" s="17"/>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="33">
         <v>0.2</v>
       </c>
-      <c r="F18" s="16"/>
+      <c r="F18" s="17"/>
     </row>
     <row r="19" ht="16" spans="2:6">
       <c r="B19" t="s">
@@ -2380,28 +2396,28 @@
       <c r="C19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="D19" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="32">
+      <c r="E19" s="33">
         <v>0.2</v>
       </c>
-      <c r="F19" s="16"/>
+      <c r="F19" s="17"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="D20" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="32">
+      <c r="E20" s="33">
         <v>0.5</v>
       </c>
-      <c r="F20" s="16"/>
+      <c r="F20" s="17"/>
     </row>
     <row r="21" ht="16" spans="2:6">
       <c r="B21" t="s">
@@ -2410,13 +2426,13 @@
       <c r="C21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="31" t="s">
+      <c r="D21" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="33">
         <v>0.8</v>
       </c>
-      <c r="F21" s="16"/>
+      <c r="F21" s="17"/>
     </row>
     <row r="22" ht="16" spans="2:6">
       <c r="B22" t="s">
@@ -2425,122 +2441,122 @@
       <c r="C22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="31" t="s">
+      <c r="D22" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="25"/>
-      <c r="F22" s="16"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="17"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="31" t="s">
+      <c r="D23" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="16">
-        <v>1</v>
-      </c>
-      <c r="F23" s="16"/>
+      <c r="E23" s="17">
+        <v>1</v>
+      </c>
+      <c r="F23" s="17"/>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="31" t="s">
+      <c r="D24" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="16">
-        <v>1</v>
-      </c>
-      <c r="F24" s="16"/>
+      <c r="E24" s="17">
+        <v>1</v>
+      </c>
+      <c r="F24" s="17"/>
     </row>
     <row r="25" ht="16" spans="2:6">
       <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="31" t="s">
+      <c r="D25" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="16">
-        <v>1</v>
-      </c>
-      <c r="F25" s="16"/>
+      <c r="E25" s="17">
+        <v>1</v>
+      </c>
+      <c r="F25" s="17"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="25" t="s">
+      <c r="C26" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="31" t="s">
+      <c r="D26" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="25">
+      <c r="E26" s="26">
         <v>0.05</v>
       </c>
-      <c r="F26" s="16"/>
+      <c r="F26" s="17"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="33" t="s">
+      <c r="B27" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="34" t="s">
+      <c r="C27" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="34" t="s">
+      <c r="D27" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="34">
+      <c r="E27" s="35">
         <v>2020</v>
       </c>
-      <c r="F27" s="16"/>
+      <c r="F27" s="17"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="34" t="s">
+      <c r="D28" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="35">
+      <c r="E28" s="36">
         <v>2020</v>
       </c>
-      <c r="F28" s="16"/>
+      <c r="F28" s="17"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
     </row>
     <row r="38" spans="3:5">
       <c r="C38" s="1"/>
@@ -2548,360 +2564,360 @@
       <c r="E38" s="1"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="36" t="s">
+      <c r="C54" s="37" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="36"/>
-      <c r="E56" s="36"/>
-      <c r="F56" s="36"/>
-      <c r="G56" s="36"/>
-      <c r="H56" s="36"/>
-      <c r="I56" s="36"/>
-      <c r="J56" s="36"/>
-      <c r="K56" s="36"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="37"/>
+      <c r="F56" s="37"/>
+      <c r="G56" s="37"/>
+      <c r="H56" s="37"/>
+      <c r="I56" s="37"/>
+      <c r="J56" s="37"/>
+      <c r="K56" s="37"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="36" t="s">
+      <c r="C57" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="36" t="s">
+      <c r="D57" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="36" t="s">
+      <c r="E57" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="F57" s="36" t="s">
+      <c r="F57" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="G57" s="36" t="s">
+      <c r="G57" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="36" t="s">
+      <c r="H57" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="36" t="s">
+      <c r="I57" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="J57" s="36" t="s">
+      <c r="J57" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="K57" s="36" t="s">
+      <c r="K57" s="37" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="36"/>
-      <c r="D58" s="36"/>
-      <c r="E58" s="36"/>
-      <c r="F58" s="36"/>
-      <c r="G58" s="36"/>
-      <c r="H58" s="36"/>
-      <c r="I58" s="36"/>
-      <c r="J58" s="36"/>
-      <c r="K58" s="36"/>
+      <c r="C58" s="37"/>
+      <c r="D58" s="37"/>
+      <c r="E58" s="37"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="37"/>
+      <c r="H58" s="37"/>
+      <c r="I58" s="37"/>
+      <c r="J58" s="37"/>
+      <c r="K58" s="37"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="36"/>
-      <c r="D59" s="36"/>
-      <c r="E59" s="36"/>
-      <c r="F59" s="36"/>
-      <c r="G59" s="36"/>
-      <c r="H59" s="36"/>
-      <c r="I59" s="36"/>
-      <c r="J59" s="36"/>
-      <c r="K59" s="36"/>
+      <c r="C59" s="37"/>
+      <c r="D59" s="37"/>
+      <c r="E59" s="37"/>
+      <c r="F59" s="37"/>
+      <c r="G59" s="37"/>
+      <c r="H59" s="37"/>
+      <c r="I59" s="37"/>
+      <c r="J59" s="37"/>
+      <c r="K59" s="37"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="36"/>
-      <c r="D60" s="36"/>
-      <c r="E60" s="36"/>
-      <c r="F60" s="36"/>
-      <c r="G60" s="36"/>
-      <c r="H60" s="36"/>
-      <c r="I60" s="36"/>
-      <c r="J60" s="36"/>
-      <c r="K60" s="36"/>
+      <c r="C60" s="37"/>
+      <c r="D60" s="37"/>
+      <c r="E60" s="37"/>
+      <c r="F60" s="37"/>
+      <c r="G60" s="37"/>
+      <c r="H60" s="37"/>
+      <c r="I60" s="37"/>
+      <c r="J60" s="37"/>
+      <c r="K60" s="37"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-      <c r="G61" s="36"/>
-      <c r="H61" s="36"/>
-      <c r="I61" s="36"/>
-      <c r="J61" s="36"/>
-      <c r="K61" s="36"/>
+      <c r="C61" s="37"/>
+      <c r="D61" s="37"/>
+      <c r="E61" s="37"/>
+      <c r="F61" s="37"/>
+      <c r="G61" s="37"/>
+      <c r="H61" s="37"/>
+      <c r="I61" s="37"/>
+      <c r="J61" s="37"/>
+      <c r="K61" s="37"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="36"/>
-      <c r="D62" s="36"/>
-      <c r="E62" s="36"/>
-      <c r="F62" s="36"/>
-      <c r="G62" s="36"/>
-      <c r="H62" s="36"/>
-      <c r="I62" s="36"/>
-      <c r="J62" s="36"/>
-      <c r="K62" s="36"/>
+      <c r="C62" s="37"/>
+      <c r="D62" s="37"/>
+      <c r="E62" s="37"/>
+      <c r="F62" s="37"/>
+      <c r="G62" s="37"/>
+      <c r="H62" s="37"/>
+      <c r="I62" s="37"/>
+      <c r="J62" s="37"/>
+      <c r="K62" s="37"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="36"/>
-      <c r="D63" s="36"/>
-      <c r="E63" s="36"/>
-      <c r="F63" s="36"/>
-      <c r="G63" s="36"/>
-      <c r="H63" s="36"/>
-      <c r="I63" s="36"/>
-      <c r="J63" s="36"/>
-      <c r="K63" s="36"/>
+      <c r="C63" s="37"/>
+      <c r="D63" s="37"/>
+      <c r="E63" s="37"/>
+      <c r="F63" s="37"/>
+      <c r="G63" s="37"/>
+      <c r="H63" s="37"/>
+      <c r="I63" s="37"/>
+      <c r="J63" s="37"/>
+      <c r="K63" s="37"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="36"/>
-      <c r="D64" s="36"/>
-      <c r="E64" s="36"/>
-      <c r="F64" s="36"/>
-      <c r="G64" s="36"/>
-      <c r="H64" s="36"/>
-      <c r="I64" s="36"/>
-      <c r="J64" s="36"/>
-      <c r="K64" s="36"/>
+      <c r="C64" s="37"/>
+      <c r="D64" s="37"/>
+      <c r="E64" s="37"/>
+      <c r="F64" s="37"/>
+      <c r="G64" s="37"/>
+      <c r="H64" s="37"/>
+      <c r="I64" s="37"/>
+      <c r="J64" s="37"/>
+      <c r="K64" s="37"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="36"/>
-      <c r="D65" s="36"/>
-      <c r="E65" s="36"/>
-      <c r="F65" s="36"/>
-      <c r="G65" s="36"/>
-      <c r="H65" s="36"/>
-      <c r="I65" s="36"/>
-      <c r="J65" s="36"/>
-      <c r="K65" s="36"/>
+      <c r="C65" s="37"/>
+      <c r="D65" s="37"/>
+      <c r="E65" s="37"/>
+      <c r="F65" s="37"/>
+      <c r="G65" s="37"/>
+      <c r="H65" s="37"/>
+      <c r="I65" s="37"/>
+      <c r="J65" s="37"/>
+      <c r="K65" s="37"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="36"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="36"/>
-      <c r="F66" s="36"/>
-      <c r="G66" s="36"/>
-      <c r="H66" s="36"/>
-      <c r="I66" s="36"/>
-      <c r="J66" s="36"/>
-      <c r="K66" s="36"/>
+      <c r="C66" s="37"/>
+      <c r="D66" s="37"/>
+      <c r="E66" s="37"/>
+      <c r="F66" s="37"/>
+      <c r="G66" s="37"/>
+      <c r="H66" s="37"/>
+      <c r="I66" s="37"/>
+      <c r="J66" s="37"/>
+      <c r="K66" s="37"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="36"/>
-      <c r="D67" s="36"/>
-      <c r="E67" s="36"/>
-      <c r="F67" s="36"/>
-      <c r="G67" s="36"/>
-      <c r="H67" s="36"/>
-      <c r="I67" s="36"/>
-      <c r="J67" s="36"/>
-      <c r="K67" s="36"/>
+      <c r="C67" s="37"/>
+      <c r="D67" s="37"/>
+      <c r="E67" s="37"/>
+      <c r="F67" s="37"/>
+      <c r="G67" s="37"/>
+      <c r="H67" s="37"/>
+      <c r="I67" s="37"/>
+      <c r="J67" s="37"/>
+      <c r="K67" s="37"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="36"/>
-      <c r="D68" s="36"/>
-      <c r="E68" s="36"/>
-      <c r="F68" s="36"/>
-      <c r="G68" s="36"/>
-      <c r="H68" s="36"/>
-      <c r="I68" s="36"/>
-      <c r="J68" s="36"/>
-      <c r="K68" s="36"/>
+      <c r="C68" s="37"/>
+      <c r="D68" s="37"/>
+      <c r="E68" s="37"/>
+      <c r="F68" s="37"/>
+      <c r="G68" s="37"/>
+      <c r="H68" s="37"/>
+      <c r="I68" s="37"/>
+      <c r="J68" s="37"/>
+      <c r="K68" s="37"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="36"/>
-      <c r="D69" s="36"/>
-      <c r="E69" s="36"/>
-      <c r="F69" s="36"/>
-      <c r="G69" s="36"/>
-      <c r="H69" s="36"/>
-      <c r="I69" s="36"/>
-      <c r="J69" s="36"/>
-      <c r="K69" s="36"/>
+      <c r="C69" s="37"/>
+      <c r="D69" s="37"/>
+      <c r="E69" s="37"/>
+      <c r="F69" s="37"/>
+      <c r="G69" s="37"/>
+      <c r="H69" s="37"/>
+      <c r="I69" s="37"/>
+      <c r="J69" s="37"/>
+      <c r="K69" s="37"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="36"/>
-      <c r="D70" s="36"/>
-      <c r="E70" s="36"/>
-      <c r="F70" s="36"/>
-      <c r="G70" s="36"/>
-      <c r="H70" s="36"/>
-      <c r="I70" s="36"/>
-      <c r="J70" s="36"/>
-      <c r="K70" s="36"/>
+      <c r="C70" s="37"/>
+      <c r="D70" s="37"/>
+      <c r="E70" s="37"/>
+      <c r="F70" s="37"/>
+      <c r="G70" s="37"/>
+      <c r="H70" s="37"/>
+      <c r="I70" s="37"/>
+      <c r="J70" s="37"/>
+      <c r="K70" s="37"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="36"/>
-      <c r="D71" s="36"/>
-      <c r="E71" s="36"/>
-      <c r="F71" s="36"/>
-      <c r="G71" s="36"/>
-      <c r="H71" s="36"/>
-      <c r="I71" s="36"/>
-      <c r="J71" s="36"/>
-      <c r="K71" s="36"/>
+      <c r="C71" s="37"/>
+      <c r="D71" s="37"/>
+      <c r="E71" s="37"/>
+      <c r="F71" s="37"/>
+      <c r="G71" s="37"/>
+      <c r="H71" s="37"/>
+      <c r="I71" s="37"/>
+      <c r="J71" s="37"/>
+      <c r="K71" s="37"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="36"/>
-      <c r="D72" s="36"/>
-      <c r="E72" s="36"/>
-      <c r="F72" s="36"/>
-      <c r="G72" s="36"/>
-      <c r="H72" s="36"/>
-      <c r="I72" s="36"/>
-      <c r="J72" s="36"/>
-      <c r="K72" s="36"/>
+      <c r="C72" s="37"/>
+      <c r="D72" s="37"/>
+      <c r="E72" s="37"/>
+      <c r="F72" s="37"/>
+      <c r="G72" s="37"/>
+      <c r="H72" s="37"/>
+      <c r="I72" s="37"/>
+      <c r="J72" s="37"/>
+      <c r="K72" s="37"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="36"/>
-      <c r="D73" s="36"/>
-      <c r="E73" s="36"/>
-      <c r="F73" s="36"/>
-      <c r="G73" s="36"/>
-      <c r="H73" s="36"/>
-      <c r="I73" s="36"/>
-      <c r="J73" s="36"/>
-      <c r="K73" s="36"/>
+      <c r="C73" s="37"/>
+      <c r="D73" s="37"/>
+      <c r="E73" s="37"/>
+      <c r="F73" s="37"/>
+      <c r="G73" s="37"/>
+      <c r="H73" s="37"/>
+      <c r="I73" s="37"/>
+      <c r="J73" s="37"/>
+      <c r="K73" s="37"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="36"/>
-      <c r="D74" s="36"/>
-      <c r="E74" s="36"/>
-      <c r="F74" s="36"/>
-      <c r="G74" s="36"/>
-      <c r="H74" s="36"/>
-      <c r="I74" s="36"/>
-      <c r="J74" s="36"/>
-      <c r="K74" s="36"/>
+      <c r="C74" s="37"/>
+      <c r="D74" s="37"/>
+      <c r="E74" s="37"/>
+      <c r="F74" s="37"/>
+      <c r="G74" s="37"/>
+      <c r="H74" s="37"/>
+      <c r="I74" s="37"/>
+      <c r="J74" s="37"/>
+      <c r="K74" s="37"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="36"/>
-      <c r="D75" s="36"/>
-      <c r="E75" s="36"/>
-      <c r="F75" s="36"/>
-      <c r="G75" s="36"/>
-      <c r="H75" s="36"/>
-      <c r="I75" s="36"/>
-      <c r="J75" s="36"/>
-      <c r="K75" s="36"/>
+      <c r="C75" s="37"/>
+      <c r="D75" s="37"/>
+      <c r="E75" s="37"/>
+      <c r="F75" s="37"/>
+      <c r="G75" s="37"/>
+      <c r="H75" s="37"/>
+      <c r="I75" s="37"/>
+      <c r="J75" s="37"/>
+      <c r="K75" s="37"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="36"/>
-      <c r="D76" s="36"/>
-      <c r="E76" s="36"/>
-      <c r="F76" s="36"/>
-      <c r="G76" s="36"/>
-      <c r="H76" s="36"/>
-      <c r="I76" s="36"/>
-      <c r="J76" s="36"/>
-      <c r="K76" s="36"/>
+      <c r="C76" s="37"/>
+      <c r="D76" s="37"/>
+      <c r="E76" s="37"/>
+      <c r="F76" s="37"/>
+      <c r="G76" s="37"/>
+      <c r="H76" s="37"/>
+      <c r="I76" s="37"/>
+      <c r="J76" s="37"/>
+      <c r="K76" s="37"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="36"/>
-      <c r="D77" s="36"/>
-      <c r="E77" s="36"/>
-      <c r="F77" s="36"/>
-      <c r="G77" s="36"/>
-      <c r="H77" s="36"/>
-      <c r="I77" s="36"/>
-      <c r="J77" s="36"/>
-      <c r="K77" s="36"/>
+      <c r="C77" s="37"/>
+      <c r="D77" s="37"/>
+      <c r="E77" s="37"/>
+      <c r="F77" s="37"/>
+      <c r="G77" s="37"/>
+      <c r="H77" s="37"/>
+      <c r="I77" s="37"/>
+      <c r="J77" s="37"/>
+      <c r="K77" s="37"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="36"/>
-      <c r="D78" s="36"/>
-      <c r="E78" s="36"/>
-      <c r="F78" s="36"/>
-      <c r="G78" s="36"/>
-      <c r="H78" s="36"/>
-      <c r="I78" s="36"/>
-      <c r="J78" s="36"/>
-      <c r="K78" s="36"/>
+      <c r="C78" s="37"/>
+      <c r="D78" s="37"/>
+      <c r="E78" s="37"/>
+      <c r="F78" s="37"/>
+      <c r="G78" s="37"/>
+      <c r="H78" s="37"/>
+      <c r="I78" s="37"/>
+      <c r="J78" s="37"/>
+      <c r="K78" s="37"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-      <c r="G79" s="36"/>
-      <c r="H79" s="36"/>
-      <c r="I79" s="36"/>
-      <c r="J79" s="36"/>
-      <c r="K79" s="36"/>
+      <c r="C79" s="37"/>
+      <c r="D79" s="37"/>
+      <c r="E79" s="37"/>
+      <c r="F79" s="37"/>
+      <c r="G79" s="37"/>
+      <c r="H79" s="37"/>
+      <c r="I79" s="37"/>
+      <c r="J79" s="37"/>
+      <c r="K79" s="37"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="36"/>
-      <c r="D80" s="36"/>
-      <c r="E80" s="36"/>
-      <c r="F80" s="36"/>
-      <c r="G80" s="36"/>
-      <c r="H80" s="36"/>
-      <c r="I80" s="36"/>
-      <c r="J80" s="36"/>
-      <c r="K80" s="36"/>
+      <c r="C80" s="37"/>
+      <c r="D80" s="37"/>
+      <c r="E80" s="37"/>
+      <c r="F80" s="37"/>
+      <c r="G80" s="37"/>
+      <c r="H80" s="37"/>
+      <c r="I80" s="37"/>
+      <c r="J80" s="37"/>
+      <c r="K80" s="37"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="36"/>
-      <c r="D81" s="36"/>
-      <c r="E81" s="36"/>
-      <c r="F81" s="36"/>
-      <c r="G81" s="36"/>
-      <c r="H81" s="36"/>
-      <c r="I81" s="36"/>
-      <c r="J81" s="36"/>
-      <c r="K81" s="36"/>
+      <c r="C81" s="37"/>
+      <c r="D81" s="37"/>
+      <c r="E81" s="37"/>
+      <c r="F81" s="37"/>
+      <c r="G81" s="37"/>
+      <c r="H81" s="37"/>
+      <c r="I81" s="37"/>
+      <c r="J81" s="37"/>
+      <c r="K81" s="37"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="36"/>
-      <c r="D82" s="36"/>
-      <c r="E82" s="36"/>
-      <c r="F82" s="36"/>
-      <c r="G82" s="36"/>
-      <c r="H82" s="36"/>
-      <c r="I82" s="36"/>
-      <c r="J82" s="36"/>
-      <c r="K82" s="36"/>
+      <c r="C82" s="37"/>
+      <c r="D82" s="37"/>
+      <c r="E82" s="37"/>
+      <c r="F82" s="37"/>
+      <c r="G82" s="37"/>
+      <c r="H82" s="37"/>
+      <c r="I82" s="37"/>
+      <c r="J82" s="37"/>
+      <c r="K82" s="37"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="36"/>
-      <c r="D83" s="36"/>
-      <c r="E83" s="36"/>
-      <c r="F83" s="36"/>
-      <c r="G83" s="36"/>
-      <c r="H83" s="36"/>
-      <c r="I83" s="36"/>
-      <c r="J83" s="36"/>
-      <c r="K83" s="36"/>
+      <c r="C83" s="37"/>
+      <c r="D83" s="37"/>
+      <c r="E83" s="37"/>
+      <c r="F83" s="37"/>
+      <c r="G83" s="37"/>
+      <c r="H83" s="37"/>
+      <c r="I83" s="37"/>
+      <c r="J83" s="37"/>
+      <c r="K83" s="37"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="36" t="s">
+      <c r="C84" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="D84" s="36">
-        <v>1</v>
-      </c>
-      <c r="E84" s="36"/>
-      <c r="F84" s="36"/>
-      <c r="G84" s="36"/>
-      <c r="H84" s="36"/>
-      <c r="I84" s="36"/>
-      <c r="J84" s="36"/>
-      <c r="K84" s="36"/>
+      <c r="D84" s="37">
+        <v>1</v>
+      </c>
+      <c r="E84" s="37"/>
+      <c r="F84" s="37"/>
+      <c r="G84" s="37"/>
+      <c r="H84" s="37"/>
+      <c r="I84" s="37"/>
+      <c r="J84" s="37"/>
+      <c r="K84" s="37"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="36"/>
-      <c r="D85" s="36"/>
-      <c r="E85" s="36"/>
-      <c r="F85" s="36"/>
-      <c r="G85" s="36"/>
-      <c r="H85" s="36"/>
-      <c r="I85" s="36"/>
-      <c r="J85" s="36"/>
-      <c r="K85" s="36"/>
+      <c r="C85" s="37"/>
+      <c r="D85" s="37"/>
+      <c r="E85" s="37"/>
+      <c r="F85" s="37"/>
+      <c r="G85" s="37"/>
+      <c r="H85" s="37"/>
+      <c r="I85" s="37"/>
+      <c r="J85" s="37"/>
+      <c r="K85" s="37"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3310,14 +3326,14 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
     </row>
-    <row r="31" spans="5:23">
+    <row r="31" ht="16" spans="5:23">
       <c r="F31" s="1" t="s">
         <v>67</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H31" s="13" t="s">
+      <c r="H31" s="14" t="s">
         <v>69</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -3526,252 +3542,252 @@
       </c>
     </row>
     <row r="8" spans="2:14">
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="J8" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="K8" s="14" t="s">
+      <c r="K8" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="L8" s="14" t="s">
+      <c r="L8" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="M8" s="14" t="s">
+      <c r="M8" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="N8" s="14" t="s">
+      <c r="N8" s="15" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="9" spans="2:14">
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="16" t="s">
         <v>88</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="16">
         <v>1.25</v>
       </c>
       <c r="L9">
         <v>0.05</v>
       </c>
-      <c r="M9" s="15">
-        <v>1</v>
-      </c>
-      <c r="N9" s="15"/>
+      <c r="M9" s="16">
+        <v>1</v>
+      </c>
+      <c r="N9" s="16"/>
     </row>
     <row r="10" spans="2:14">
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="16" t="s">
         <v>88</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="16">
         <v>1.11</v>
       </c>
       <c r="L10">
         <v>0.05</v>
       </c>
-      <c r="M10" s="15">
-        <v>1</v>
-      </c>
-      <c r="N10" s="15"/>
+      <c r="M10" s="16">
+        <v>1</v>
+      </c>
+      <c r="N10" s="16"/>
     </row>
     <row r="11" spans="2:14">
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" s="16" t="s">
         <v>88</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="16">
         <v>1.15</v>
       </c>
       <c r="L11">
         <v>0.08</v>
       </c>
-      <c r="M11" s="15">
-        <v>1</v>
-      </c>
-      <c r="N11" s="15"/>
+      <c r="M11" s="16">
+        <v>1</v>
+      </c>
+      <c r="N11" s="16"/>
     </row>
     <row r="12" ht="16" spans="2:14">
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="16" t="s">
         <v>93</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="16" t="s">
         <v>88</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
-      <c r="K12" s="15">
+      <c r="K12" s="16">
         <v>1.12</v>
       </c>
       <c r="L12">
         <v>0.03</v>
       </c>
-      <c r="M12" s="15">
-        <v>1</v>
-      </c>
-      <c r="N12" s="15"/>
+      <c r="M12" s="16">
+        <v>1</v>
+      </c>
+      <c r="N12" s="16"/>
     </row>
     <row r="13" spans="2:14">
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="H13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" s="16" t="s">
         <v>88</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="16">
         <v>1.2</v>
       </c>
       <c r="L13">
         <v>0.1</v>
       </c>
-      <c r="M13" s="15">
-        <v>1</v>
-      </c>
-      <c r="N13" s="15"/>
+      <c r="M13" s="16">
+        <v>1</v>
+      </c>
+      <c r="N13" s="16"/>
     </row>
     <row r="14" spans="2:14">
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H14" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I14" s="16" t="s">
         <v>88</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="16">
         <v>1.06</v>
       </c>
       <c r="L14">
         <v>0.15</v>
       </c>
-      <c r="M14" s="15">
-        <v>1</v>
-      </c>
-      <c r="N14" s="15"/>
+      <c r="M14" s="16">
+        <v>1</v>
+      </c>
+      <c r="N14" s="16"/>
     </row>
     <row r="15" spans="2:14">
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="16" t="s">
         <v>88</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="16">
         <v>1.06</v>
       </c>
       <c r="L15">
         <v>0.3</v>
       </c>
-      <c r="M15" s="15">
-        <v>1</v>
-      </c>
-      <c r="N15" s="15"/>
+      <c r="M15" s="16">
+        <v>1</v>
+      </c>
+      <c r="N15" s="16"/>
     </row>
     <row r="16" ht="16" spans="2:14">
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="16" t="s">
         <v>101</v>
       </c>
       <c r="F16" s="2" t="s">
@@ -3785,7 +3801,7 @@
         <f>H15</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="I16" s="16" t="s">
         <v>88</v>
       </c>
       <c r="J16">
@@ -3806,7 +3822,7 @@
       </c>
     </row>
     <row r="17" ht="16" spans="4:14">
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="16" t="s">
         <v>103</v>
       </c>
       <c r="F17" s="2" t="s">
@@ -3820,7 +3836,7 @@
         <f t="shared" si="1"/>
         <v>2025, 2150</v>
       </c>
-      <c r="I17" s="15" t="s">
+      <c r="I17" s="16" t="s">
         <v>88</v>
       </c>
       <c r="J17">
@@ -3841,7 +3857,7 @@
       </c>
     </row>
     <row r="18" ht="16" spans="4:14">
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="16" t="s">
         <v>105</v>
       </c>
       <c r="F18" s="2" t="s">
@@ -3855,7 +3871,7 @@
         <f>H17</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I18" s="15" t="s">
+      <c r="I18" s="16" t="s">
         <v>88</v>
       </c>
       <c r="J18">
@@ -3872,604 +3888,604 @@
       </c>
     </row>
     <row r="27" spans="4:14">
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
     </row>
     <row r="28" spans="4:14">
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16" t="s">
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
     </row>
     <row r="29" spans="4:14">
-      <c r="D29" s="16" t="s">
+      <c r="D29" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="E29" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="F29" s="16" t="s">
+      <c r="F29" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="16" t="s">
+      <c r="G29" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="H29" s="16" t="s">
+      <c r="H29" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="I29" s="16" t="s">
+      <c r="I29" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="J29" s="16" t="s">
+      <c r="J29" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="K29" s="16" t="s">
+      <c r="K29" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="L29" s="16" t="s">
+      <c r="L29" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="M29" s="16" t="s">
+      <c r="M29" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="N29" s="16" t="s">
+      <c r="N29" s="17" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="30" ht="16" spans="4:14">
-      <c r="D30" s="16" t="s">
+      <c r="D30" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="16"/>
-      <c r="F30" s="17" t="s">
+      <c r="E30" s="17"/>
+      <c r="F30" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="G30" s="16" t="s">
+      <c r="G30" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H30" s="16" t="s">
+      <c r="H30" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="I30" s="16" t="s">
+      <c r="I30" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="16">
-        <v>1</v>
-      </c>
-      <c r="K30" s="16">
-        <v>1</v>
-      </c>
-      <c r="L30" s="16">
+      <c r="J30" s="17">
+        <v>1</v>
+      </c>
+      <c r="K30" s="17">
+        <v>1</v>
+      </c>
+      <c r="L30" s="17">
         <v>0.01</v>
       </c>
-      <c r="M30" s="16">
-        <v>1</v>
-      </c>
-      <c r="N30" s="16"/>
+      <c r="M30" s="17">
+        <v>1</v>
+      </c>
+      <c r="N30" s="17"/>
     </row>
     <row r="31" ht="16" spans="4:14">
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="16"/>
-      <c r="F31" s="18" t="s">
+      <c r="E31" s="17"/>
+      <c r="F31" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="G31" s="16" t="s">
+      <c r="G31" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H31" s="16" t="s">
+      <c r="H31" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="I31" s="16" t="s">
+      <c r="I31" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="J31" s="16">
-        <v>1</v>
-      </c>
-      <c r="K31" s="16">
-        <v>1</v>
-      </c>
-      <c r="L31" s="16">
+      <c r="J31" s="17">
+        <v>1</v>
+      </c>
+      <c r="K31" s="17">
+        <v>1</v>
+      </c>
+      <c r="L31" s="17">
         <f t="shared" ref="L31:L36" si="2">L30</f>
         <v>0.01</v>
       </c>
-      <c r="M31" s="16">
-        <v>1</v>
-      </c>
-      <c r="N31" s="16"/>
+      <c r="M31" s="17">
+        <v>1</v>
+      </c>
+      <c r="N31" s="17"/>
     </row>
     <row r="32" ht="16" spans="4:14">
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="E32" s="16"/>
-      <c r="F32" s="18" t="s">
+      <c r="E32" s="17"/>
+      <c r="F32" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="G32" s="16" t="s">
+      <c r="G32" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H32" s="16" t="s">
+      <c r="H32" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="I32" s="16" t="s">
+      <c r="I32" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="J32" s="16">
-        <v>1</v>
-      </c>
-      <c r="K32" s="16">
-        <v>1</v>
-      </c>
-      <c r="L32" s="16">
+      <c r="J32" s="17">
+        <v>1</v>
+      </c>
+      <c r="K32" s="17">
+        <v>1</v>
+      </c>
+      <c r="L32" s="17">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M32" s="16">
-        <v>1</v>
-      </c>
-      <c r="N32" s="16"/>
+      <c r="M32" s="17">
+        <v>1</v>
+      </c>
+      <c r="N32" s="17"/>
     </row>
     <row r="33" ht="16" spans="4:14">
-      <c r="D33" s="16" t="s">
+      <c r="D33" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="16"/>
-      <c r="F33" s="17" t="s">
+      <c r="E33" s="17"/>
+      <c r="F33" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G33" s="16" t="s">
+      <c r="G33" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H33" s="16" t="s">
+      <c r="H33" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="I33" s="16" t="s">
+      <c r="I33" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="J33" s="16">
-        <v>1</v>
-      </c>
-      <c r="K33" s="16">
+      <c r="J33" s="17">
+        <v>1</v>
+      </c>
+      <c r="K33" s="17">
         <f>K32</f>
         <v>1</v>
       </c>
-      <c r="L33" s="16">
+      <c r="L33" s="17">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M33" s="16">
-        <v>1</v>
-      </c>
-      <c r="N33" s="16"/>
+      <c r="M33" s="17">
+        <v>1</v>
+      </c>
+      <c r="N33" s="17"/>
     </row>
     <row r="34" ht="16" spans="4:14">
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="E34" s="16"/>
-      <c r="F34" s="17" t="s">
+      <c r="E34" s="17"/>
+      <c r="F34" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="G34" s="16" t="s">
+      <c r="G34" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H34" s="16" t="s">
+      <c r="H34" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="I34" s="16" t="s">
+      <c r="I34" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="J34" s="16">
-        <v>1</v>
-      </c>
-      <c r="K34" s="16">
+      <c r="J34" s="17">
+        <v>1</v>
+      </c>
+      <c r="K34" s="17">
         <f>K33</f>
         <v>1</v>
       </c>
-      <c r="L34" s="16">
+      <c r="L34" s="17">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M34" s="16">
-        <v>1</v>
-      </c>
-      <c r="N34" s="16"/>
+      <c r="M34" s="17">
+        <v>1</v>
+      </c>
+      <c r="N34" s="17"/>
     </row>
     <row r="35" ht="16" spans="4:14">
-      <c r="D35" s="16" t="s">
+      <c r="D35" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E35" s="16"/>
-      <c r="F35" s="17" t="s">
+      <c r="E35" s="17"/>
+      <c r="F35" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="16" t="s">
+      <c r="G35" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H35" s="16" t="s">
+      <c r="H35" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="I35" s="16" t="s">
+      <c r="I35" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="J35" s="16">
-        <v>1</v>
-      </c>
-      <c r="K35" s="16">
+      <c r="J35" s="17">
+        <v>1</v>
+      </c>
+      <c r="K35" s="17">
         <f>K34</f>
         <v>1</v>
       </c>
-      <c r="L35" s="16">
+      <c r="L35" s="17">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M35" s="16">
-        <v>1</v>
-      </c>
-      <c r="N35" s="16"/>
+      <c r="M35" s="17">
+        <v>1</v>
+      </c>
+      <c r="N35" s="17"/>
     </row>
     <row r="36" ht="16" spans="4:14">
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="E36" s="16"/>
-      <c r="F36" s="17" t="s">
+      <c r="E36" s="17"/>
+      <c r="F36" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="G36" s="16" t="s">
+      <c r="G36" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H36" s="16" t="s">
+      <c r="H36" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="I36" s="16" t="s">
+      <c r="I36" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="J36" s="16">
-        <v>1</v>
-      </c>
-      <c r="K36" s="16">
+      <c r="J36" s="17">
+        <v>1</v>
+      </c>
+      <c r="K36" s="17">
         <f>K35</f>
         <v>1</v>
       </c>
-      <c r="L36" s="16">
+      <c r="L36" s="17">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M36" s="16">
-        <v>1</v>
-      </c>
-      <c r="N36" s="16"/>
+      <c r="M36" s="17">
+        <v>1</v>
+      </c>
+      <c r="N36" s="17"/>
     </row>
     <row r="37" ht="16" spans="4:14">
-      <c r="D37" s="19" t="s">
+      <c r="D37" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="E37" s="19"/>
-      <c r="F37" s="20" t="s">
+      <c r="E37" s="20"/>
+      <c r="F37" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="G37" s="19" t="s">
+      <c r="G37" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="H37" s="19" t="s">
+      <c r="H37" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="I37" s="19" t="s">
+      <c r="I37" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="J37" s="19">
-        <v>1</v>
-      </c>
-      <c r="K37" s="19">
-        <v>1</v>
-      </c>
-      <c r="L37" s="19">
+      <c r="J37" s="20">
+        <v>1</v>
+      </c>
+      <c r="K37" s="20">
+        <v>1</v>
+      </c>
+      <c r="L37" s="20">
         <v>0.01</v>
       </c>
-      <c r="M37" s="19">
-        <v>1</v>
-      </c>
-      <c r="N37" s="16"/>
+      <c r="M37" s="20">
+        <v>1</v>
+      </c>
+      <c r="N37" s="17"/>
     </row>
     <row r="38" ht="16" spans="4:14">
-      <c r="D38" s="19" t="s">
+      <c r="D38" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="E38" s="19"/>
-      <c r="F38" s="21" t="s">
+      <c r="E38" s="20"/>
+      <c r="F38" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="G38" s="19" t="s">
+      <c r="G38" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="H38" s="19" t="s">
+      <c r="H38" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="I38" s="19" t="s">
+      <c r="I38" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="J38" s="19">
-        <v>1</v>
-      </c>
-      <c r="K38" s="19">
-        <v>1</v>
-      </c>
-      <c r="L38" s="19">
+      <c r="J38" s="20">
+        <v>1</v>
+      </c>
+      <c r="K38" s="20">
+        <v>1</v>
+      </c>
+      <c r="L38" s="20">
         <f t="shared" ref="L38:L43" si="3">L37</f>
         <v>0.01</v>
       </c>
-      <c r="M38" s="19">
-        <v>1</v>
-      </c>
-      <c r="N38" s="16"/>
+      <c r="M38" s="20">
+        <v>1</v>
+      </c>
+      <c r="N38" s="17"/>
     </row>
     <row r="39" ht="16" spans="4:14">
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="E39" s="19"/>
-      <c r="F39" s="21" t="s">
+      <c r="E39" s="20"/>
+      <c r="F39" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="G39" s="19" t="s">
+      <c r="G39" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="H39" s="19" t="s">
+      <c r="H39" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="I39" s="19" t="s">
+      <c r="I39" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="J39" s="19">
-        <v>1</v>
-      </c>
-      <c r="K39" s="19">
-        <v>1</v>
-      </c>
-      <c r="L39" s="19">
+      <c r="J39" s="20">
+        <v>1</v>
+      </c>
+      <c r="K39" s="20">
+        <v>1</v>
+      </c>
+      <c r="L39" s="20">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M39" s="19">
-        <v>1</v>
-      </c>
-      <c r="N39" s="16"/>
+      <c r="M39" s="20">
+        <v>1</v>
+      </c>
+      <c r="N39" s="17"/>
     </row>
     <row r="40" ht="16" spans="4:14">
-      <c r="D40" s="19" t="s">
+      <c r="D40" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="E40" s="19"/>
-      <c r="F40" s="22" t="s">
+      <c r="E40" s="20"/>
+      <c r="F40" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="G40" s="19" t="s">
+      <c r="G40" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="H40" s="19" t="s">
+      <c r="H40" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="I40" s="19" t="s">
+      <c r="I40" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="J40" s="19">
-        <v>1</v>
-      </c>
-      <c r="K40" s="19">
+      <c r="J40" s="20">
+        <v>1</v>
+      </c>
+      <c r="K40" s="20">
         <f>K39</f>
         <v>1</v>
       </c>
-      <c r="L40" s="19">
+      <c r="L40" s="20">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M40" s="19">
-        <v>1</v>
-      </c>
-      <c r="N40" s="16"/>
+      <c r="M40" s="20">
+        <v>1</v>
+      </c>
+      <c r="N40" s="17"/>
     </row>
     <row r="41" ht="16" spans="4:14">
-      <c r="D41" s="19" t="s">
+      <c r="D41" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="E41" s="19"/>
-      <c r="F41" s="22" t="s">
+      <c r="E41" s="20"/>
+      <c r="F41" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="G41" s="19" t="s">
+      <c r="G41" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="H41" s="19" t="s">
+      <c r="H41" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="I41" s="19" t="s">
+      <c r="I41" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="J41" s="19">
-        <v>1</v>
-      </c>
-      <c r="K41" s="19">
+      <c r="J41" s="20">
+        <v>1</v>
+      </c>
+      <c r="K41" s="20">
         <f>K40</f>
         <v>1</v>
       </c>
-      <c r="L41" s="19">
+      <c r="L41" s="20">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M41" s="19">
-        <v>1</v>
-      </c>
-      <c r="N41" s="16"/>
+      <c r="M41" s="20">
+        <v>1</v>
+      </c>
+      <c r="N41" s="17"/>
     </row>
     <row r="42" ht="16" spans="4:14">
-      <c r="D42" s="19" t="s">
+      <c r="D42" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="E42" s="19"/>
-      <c r="F42" s="22" t="s">
+      <c r="E42" s="20"/>
+      <c r="F42" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="G42" s="19" t="s">
+      <c r="G42" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="H42" s="19" t="s">
+      <c r="H42" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="I42" s="19" t="s">
+      <c r="I42" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="J42" s="19">
-        <v>1</v>
-      </c>
-      <c r="K42" s="19">
+      <c r="J42" s="20">
+        <v>1</v>
+      </c>
+      <c r="K42" s="20">
         <f>K41</f>
         <v>1</v>
       </c>
-      <c r="L42" s="19">
+      <c r="L42" s="20">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M42" s="19">
-        <v>1</v>
-      </c>
-      <c r="N42" s="16"/>
+      <c r="M42" s="20">
+        <v>1</v>
+      </c>
+      <c r="N42" s="17"/>
     </row>
     <row r="43" ht="16" spans="4:14">
-      <c r="D43" s="19" t="s">
+      <c r="D43" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="E43" s="19"/>
-      <c r="F43" s="22" t="s">
+      <c r="E43" s="20"/>
+      <c r="F43" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="G43" s="19" t="s">
+      <c r="G43" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="H43" s="19" t="s">
+      <c r="H43" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="I43" s="19" t="s">
+      <c r="I43" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="J43" s="19">
-        <v>1</v>
-      </c>
-      <c r="K43" s="19">
+      <c r="J43" s="20">
+        <v>1</v>
+      </c>
+      <c r="K43" s="20">
         <f>K42</f>
         <v>1</v>
       </c>
-      <c r="L43" s="19">
+      <c r="L43" s="20">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M43" s="19">
-        <v>1</v>
-      </c>
-      <c r="N43" s="16"/>
+      <c r="M43" s="20">
+        <v>1</v>
+      </c>
+      <c r="N43" s="17"/>
     </row>
     <row r="44" spans="4:14">
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="19"/>
-      <c r="J44" s="19"/>
-      <c r="K44" s="19"/>
-      <c r="L44" s="19"/>
-      <c r="M44" s="19"/>
-      <c r="N44" s="16"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="20"/>
+      <c r="N44" s="17"/>
     </row>
     <row r="45" spans="4:14">
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19"/>
-      <c r="K45" s="19"/>
-      <c r="L45" s="19"/>
-      <c r="M45" s="19"/>
-      <c r="N45" s="16"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="20"/>
+      <c r="M45" s="20"/>
+      <c r="N45" s="17"/>
     </row>
     <row r="46" spans="4:14">
-      <c r="N46" s="16"/>
+      <c r="N46" s="17"/>
     </row>
     <row r="47" spans="4:14">
-      <c r="N47" s="16"/>
+      <c r="N47" s="17"/>
     </row>
     <row r="48" spans="4:14">
-      <c r="N48" s="16"/>
+      <c r="N48" s="17"/>
     </row>
     <row r="49" spans="4:14">
-      <c r="N49" s="16"/>
+      <c r="N49" s="17"/>
     </row>
     <row r="50" spans="4:14">
-      <c r="N50" s="16"/>
+      <c r="N50" s="17"/>
     </row>
     <row r="51" spans="4:14">
-      <c r="N51" s="16"/>
+      <c r="N51" s="17"/>
     </row>
     <row r="52" spans="4:14">
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="24"/>
-      <c r="G52" s="16"/>
-      <c r="H52" s="16"/>
-      <c r="I52" s="16"/>
-      <c r="J52" s="16"/>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="16"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="25"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
+      <c r="M52" s="17"/>
+      <c r="N52" s="17"/>
     </row>
     <row r="53" spans="4:14">
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="16"/>
-      <c r="H53" s="16"/>
-      <c r="I53" s="16"/>
-      <c r="J53" s="16"/>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="16"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="17"/>
+      <c r="I53" s="17"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="17"/>
+      <c r="L53" s="17"/>
+      <c r="M53" s="17"/>
+      <c r="N53" s="17"/>
     </row>
     <row r="54" spans="4:14">
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
-      <c r="H54" s="16"/>
-      <c r="I54" s="16"/>
-      <c r="J54" s="16"/>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="16"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4480,16 +4496,18 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="F9:AR70"/>
+  <dimension ref="F9:AR83"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="6" max="6" width="24.5454545454545" customWidth="1"/>
+    <col min="7" max="7" width="25.3636363636364" customWidth="1"/>
     <col min="8" max="8" width="56.3636363636364" customWidth="1"/>
     <col min="9" max="9" width="43.7272727272727" customWidth="1"/>
     <col min="14" max="14" width="12.8181818181818" customWidth="1"/>
     <col min="15" max="15" width="40.1818181818182" customWidth="1"/>
     <col min="16" max="16" width="12.6363636363636" customWidth="1"/>
     <col min="17" max="17" width="12.3636363636364" customWidth="1"/>
+    <col min="18" max="18" width="10.3636363636364" customWidth="1"/>
     <col min="48" max="48" width="12.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4978,21 +4996,20 @@
         <v>33</v>
       </c>
       <c r="N52" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q52" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R52" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="O52" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q52" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="R52" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="S52" s="6"/>
       <c r="T52" s="6"/>
       <c r="U52" s="6"/>
       <c r="V52" s="6"/>
@@ -5035,14 +5052,15 @@
       </c>
       <c r="K53" s="11"/>
       <c r="L53" s="3"/>
-      <c r="N53" s="3"/>
-      <c r="O53" s="12" t="s">
+      <c r="N53" s="12" t="s">
         <v>153</v>
       </c>
+      <c r="Q53" s="1">
+        <v>0</v>
+      </c>
       <c r="R53" s="1">
-        <v>0</v>
-      </c>
-      <c r="S53" s="6"/>
+        <v>3</v>
+      </c>
       <c r="T53" s="6"/>
       <c r="U53" s="6"/>
       <c r="V53" s="6"/>
@@ -5079,14 +5097,13 @@
       <c r="M54" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="N54" s="3"/>
-      <c r="O54" s="12" t="s">
+      <c r="N54" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="P54" s="2" t="s">
+      <c r="O54" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="P54" s="3">
         <v>10</v>
       </c>
     </row>
@@ -5101,7 +5118,6 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-      <c r="Q55" s="3"/>
     </row>
     <row r="56" spans="6:44">
       <c r="G56" s="3"/>
@@ -5114,7 +5130,106 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-      <c r="Q56" s="3"/>
+    </row>
+    <row r="61" spans="6:44">
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J61" s="5"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="5"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="5"/>
+      <c r="Q61" s="6"/>
+      <c r="R61" s="6"/>
+    </row>
+    <row r="62" spans="6:44">
+      <c r="G62" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K62" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N62" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q62" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R62" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="63" ht="16" spans="6:44">
+      <c r="G63" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I63" s="9">
+        <v>2023</v>
+      </c>
+      <c r="J63" s="10">
+        <v>-1</v>
+      </c>
+      <c r="K63" s="11"/>
+      <c r="L63" s="3"/>
+      <c r="N63" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q63" s="1">
+        <v>0</v>
+      </c>
+      <c r="R63" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" ht="16" spans="6:44">
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="N64" s="12" t="str">
+        <f>N63</f>
+        <v>EN_STG_4hBatt*, Util_Rep_Bat*</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="P64" s="3">
+        <v>10</v>
+      </c>
     </row>
     <row r="66" ht="15.25" spans="7:20">
       <c r="G66" s="1"/>
@@ -5129,22 +5244,20 @@
       <c r="P66" s="1"/>
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
-      <c r="S66" s="1"/>
       <c r="T66" s="1"/>
     </row>
     <row r="67" ht="16" spans="7:20">
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
-      <c r="I67" s="13"/>
+      <c r="I67" s="14"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
       <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
+      <c r="P67" s="1"/>
       <c r="Q67" s="1"/>
       <c r="R67" s="1"/>
-      <c r="S67" s="1"/>
       <c r="T67" s="1"/>
     </row>
     <row r="68" ht="15.25" spans="7:20">
@@ -5160,7 +5273,6 @@
       <c r="P68" s="1"/>
       <c r="Q68" s="1"/>
       <c r="R68" s="1"/>
-      <c r="S68" s="1"/>
       <c r="T68" s="1"/>
     </row>
     <row r="69" spans="7:20">
@@ -5176,24 +5288,208 @@
       <c r="P69" s="1"/>
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
-      <c r="S69" s="1"/>
       <c r="T69" s="1"/>
     </row>
     <row r="70" spans="7:20">
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
-      <c r="M70" s="1"/>
-      <c r="N70" s="1"/>
-      <c r="O70" s="1"/>
-      <c r="P70" s="1"/>
-      <c r="Q70" s="1"/>
-      <c r="R70" s="1"/>
-      <c r="S70" s="1"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="5"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="5"/>
+      <c r="Q70" s="6"/>
+      <c r="R70" s="6"/>
       <c r="T70" s="1"/>
+    </row>
+    <row r="71" spans="7:20">
+      <c r="G71" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="J71" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K71" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="L71" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M71" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N71" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O71" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P71" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q71" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R71" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="72" ht="16" spans="7:20">
+      <c r="G72" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I72" s="9">
+        <v>2023</v>
+      </c>
+      <c r="J72" s="10">
+        <v>-1</v>
+      </c>
+      <c r="K72" s="11"/>
+      <c r="L72" s="3"/>
+      <c r="N72" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q72" s="1">
+        <v>0</v>
+      </c>
+      <c r="R72" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" ht="16" spans="7:20">
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="3"/>
+      <c r="L73" s="3"/>
+      <c r="M73" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="N73" s="12" t="str">
+        <f>N72</f>
+        <v>*HPS*</v>
+      </c>
+      <c r="O73" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="P73" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="7:20">
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J80" s="5"/>
+      <c r="K80" s="5"/>
+      <c r="L80" s="5"/>
+      <c r="M80" s="5"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="5"/>
+      <c r="P80" s="5"/>
+      <c r="Q80" s="6"/>
+      <c r="R80" s="6"/>
+    </row>
+    <row r="81" spans="7:18">
+      <c r="G81" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I81" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="J81" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K81" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N81" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P81" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q81" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R81" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="82" ht="16" spans="7:18">
+      <c r="G82" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I82" s="9">
+        <v>2023</v>
+      </c>
+      <c r="J82" s="10">
+        <v>-1</v>
+      </c>
+      <c r="K82" s="11"/>
+      <c r="L82" s="3"/>
+      <c r="N82" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q82" s="1">
+        <v>0</v>
+      </c>
+      <c r="R82" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" ht="16" spans="7:18">
+      <c r="G83" s="3"/>
+      <c r="H83" s="3"/>
+      <c r="I83" s="3"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="3"/>
+      <c r="L83" s="3"/>
+      <c r="M83" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="N83" s="12" t="str">
+        <f>N82</f>
+        <v>Tra_BEV_Batt_VtoG</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="P83" s="3">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -245,7 +245,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="159">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -700,16 +700,13 @@
     <t>Allregions</t>
   </si>
   <si>
-    <t>UC_ACT</t>
-  </si>
-  <si>
     <t>UCE_MinAct_of_EVBattery</t>
   </si>
   <si>
+    <t>AuxStoIN</t>
+  </si>
+  <si>
     <t>Tra_EV_Bat*fromrecy, Tra_EV_Bat*virgin_pack</t>
-  </si>
-  <si>
-    <t>AuxStoIN</t>
   </si>
   <si>
     <t>UCE_MinAct_of_GRIDBattery</t>
@@ -958,12 +955,12 @@
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -1468,7 +1465,7 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1484,9 +1481,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2055,7 +2050,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="32">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -2169,10 +2164,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="38"/>
+      <c r="K10" s="36"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="38"/>
+      <c r="K11" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2193,12 +2188,12 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:13">
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="17"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="15"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
@@ -2213,19 +2208,19 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="27"/>
+      <c r="K6" s="25"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="26">
         <v>10</v>
       </c>
     </row>
@@ -2233,17 +2228,17 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="26">
         <v>7</v>
       </c>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
     </row>
     <row r="9" ht="16" spans="2:13">
       <c r="B9" t="s">
@@ -2252,10 +2247,10 @@
       <c r="C9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="26">
         <v>10</v>
       </c>
     </row>
@@ -2263,17 +2258,17 @@
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="26">
         <v>8</v>
       </c>
-      <c r="K10" s="29"/>
-      <c r="L10" s="30"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="28"/>
     </row>
     <row r="11" ht="16" spans="2:13">
       <c r="B11" t="s">
@@ -2282,10 +2277,10 @@
       <c r="C11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="24">
         <v>1.5</v>
       </c>
     </row>
@@ -2296,10 +2291,10 @@
       <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="24">
         <v>1.5</v>
       </c>
     </row>
@@ -2307,13 +2302,13 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="D13" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="15">
         <v>2</v>
       </c>
     </row>
@@ -2321,13 +2316,13 @@
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2335,13 +2330,13 @@
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="15">
         <v>0</v>
       </c>
     </row>
@@ -2349,13 +2344,13 @@
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="29">
         <v>12</v>
       </c>
     </row>
@@ -2363,31 +2358,31 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="31">
         <v>0.2</v>
       </c>
-      <c r="F17" s="17"/>
+      <c r="F17" s="15"/>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="31">
         <v>0.2</v>
       </c>
-      <c r="F18" s="17"/>
+      <c r="F18" s="15"/>
     </row>
     <row r="19" ht="16" spans="2:6">
       <c r="B19" t="s">
@@ -2396,28 +2391,28 @@
       <c r="C19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="33">
+      <c r="E19" s="31">
         <v>0.2</v>
       </c>
-      <c r="F19" s="17"/>
+      <c r="F19" s="15"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="31">
         <v>0.5</v>
       </c>
-      <c r="F20" s="17"/>
+      <c r="F20" s="15"/>
     </row>
     <row r="21" ht="16" spans="2:6">
       <c r="B21" t="s">
@@ -2426,13 +2421,13 @@
       <c r="C21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="31">
         <v>0.8</v>
       </c>
-      <c r="F21" s="17"/>
+      <c r="F21" s="15"/>
     </row>
     <row r="22" ht="16" spans="2:6">
       <c r="B22" t="s">
@@ -2441,122 +2436,122 @@
       <c r="C22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="26"/>
-      <c r="F22" s="17"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="15"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D23" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="17">
-        <v>1</v>
-      </c>
-      <c r="F23" s="17"/>
+      <c r="E23" s="15">
+        <v>1</v>
+      </c>
+      <c r="F23" s="15"/>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="17">
-        <v>1</v>
-      </c>
-      <c r="F24" s="17"/>
+      <c r="E24" s="15">
+        <v>1</v>
+      </c>
+      <c r="F24" s="15"/>
     </row>
     <row r="25" ht="16" spans="2:6">
       <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="17">
-        <v>1</v>
-      </c>
-      <c r="F25" s="17"/>
+      <c r="E25" s="15">
+        <v>1</v>
+      </c>
+      <c r="F25" s="15"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C26" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="24">
         <v>0.05</v>
       </c>
-      <c r="F26" s="17"/>
+      <c r="F26" s="15"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="34" t="s">
+      <c r="B27" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="35" t="s">
+      <c r="C27" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="35" t="s">
+      <c r="D27" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="35">
+      <c r="E27" s="33">
         <v>2020</v>
       </c>
-      <c r="F27" s="17"/>
+      <c r="F27" s="15"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="35" t="s">
+      <c r="D28" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="36">
+      <c r="E28" s="34">
         <v>2020</v>
       </c>
-      <c r="F28" s="17"/>
+      <c r="F28" s="15"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
     </row>
     <row r="38" spans="3:5">
       <c r="C38" s="1"/>
@@ -2564,360 +2559,360 @@
       <c r="E38" s="1"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="37" t="s">
+      <c r="C54" s="35" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="37"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="37"/>
-      <c r="G56" s="37"/>
-      <c r="H56" s="37"/>
-      <c r="I56" s="37"/>
-      <c r="J56" s="37"/>
-      <c r="K56" s="37"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="35"/>
+      <c r="G56" s="35"/>
+      <c r="H56" s="35"/>
+      <c r="I56" s="35"/>
+      <c r="J56" s="35"/>
+      <c r="K56" s="35"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="37" t="s">
+      <c r="C57" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="37" t="s">
+      <c r="D57" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="37" t="s">
+      <c r="E57" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="F57" s="37" t="s">
+      <c r="F57" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="G57" s="37" t="s">
+      <c r="G57" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="37" t="s">
+      <c r="H57" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="37" t="s">
+      <c r="I57" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="J57" s="37" t="s">
+      <c r="J57" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="K57" s="37" t="s">
+      <c r="K57" s="35" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="37"/>
-      <c r="H58" s="37"/>
-      <c r="I58" s="37"/>
-      <c r="J58" s="37"/>
-      <c r="K58" s="37"/>
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="35"/>
+      <c r="I58" s="35"/>
+      <c r="J58" s="35"/>
+      <c r="K58" s="35"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="37"/>
-      <c r="D59" s="37"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="37"/>
-      <c r="G59" s="37"/>
-      <c r="H59" s="37"/>
-      <c r="I59" s="37"/>
-      <c r="J59" s="37"/>
-      <c r="K59" s="37"/>
+      <c r="C59" s="35"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="35"/>
+      <c r="H59" s="35"/>
+      <c r="I59" s="35"/>
+      <c r="J59" s="35"/>
+      <c r="K59" s="35"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="37"/>
-      <c r="D60" s="37"/>
-      <c r="E60" s="37"/>
-      <c r="F60" s="37"/>
-      <c r="G60" s="37"/>
-      <c r="H60" s="37"/>
-      <c r="I60" s="37"/>
-      <c r="J60" s="37"/>
-      <c r="K60" s="37"/>
+      <c r="C60" s="35"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="35"/>
+      <c r="F60" s="35"/>
+      <c r="G60" s="35"/>
+      <c r="H60" s="35"/>
+      <c r="I60" s="35"/>
+      <c r="J60" s="35"/>
+      <c r="K60" s="35"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="37"/>
-      <c r="D61" s="37"/>
-      <c r="E61" s="37"/>
-      <c r="F61" s="37"/>
-      <c r="G61" s="37"/>
-      <c r="H61" s="37"/>
-      <c r="I61" s="37"/>
-      <c r="J61" s="37"/>
-      <c r="K61" s="37"/>
+      <c r="C61" s="35"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="35"/>
+      <c r="F61" s="35"/>
+      <c r="G61" s="35"/>
+      <c r="H61" s="35"/>
+      <c r="I61" s="35"/>
+      <c r="J61" s="35"/>
+      <c r="K61" s="35"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="37"/>
-      <c r="D62" s="37"/>
-      <c r="E62" s="37"/>
-      <c r="F62" s="37"/>
-      <c r="G62" s="37"/>
-      <c r="H62" s="37"/>
-      <c r="I62" s="37"/>
-      <c r="J62" s="37"/>
-      <c r="K62" s="37"/>
+      <c r="C62" s="35"/>
+      <c r="D62" s="35"/>
+      <c r="E62" s="35"/>
+      <c r="F62" s="35"/>
+      <c r="G62" s="35"/>
+      <c r="H62" s="35"/>
+      <c r="I62" s="35"/>
+      <c r="J62" s="35"/>
+      <c r="K62" s="35"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="37"/>
-      <c r="D63" s="37"/>
-      <c r="E63" s="37"/>
-      <c r="F63" s="37"/>
-      <c r="G63" s="37"/>
-      <c r="H63" s="37"/>
-      <c r="I63" s="37"/>
-      <c r="J63" s="37"/>
-      <c r="K63" s="37"/>
+      <c r="C63" s="35"/>
+      <c r="D63" s="35"/>
+      <c r="E63" s="35"/>
+      <c r="F63" s="35"/>
+      <c r="G63" s="35"/>
+      <c r="H63" s="35"/>
+      <c r="I63" s="35"/>
+      <c r="J63" s="35"/>
+      <c r="K63" s="35"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="37"/>
-      <c r="D64" s="37"/>
-      <c r="E64" s="37"/>
-      <c r="F64" s="37"/>
-      <c r="G64" s="37"/>
-      <c r="H64" s="37"/>
-      <c r="I64" s="37"/>
-      <c r="J64" s="37"/>
-      <c r="K64" s="37"/>
+      <c r="C64" s="35"/>
+      <c r="D64" s="35"/>
+      <c r="E64" s="35"/>
+      <c r="F64" s="35"/>
+      <c r="G64" s="35"/>
+      <c r="H64" s="35"/>
+      <c r="I64" s="35"/>
+      <c r="J64" s="35"/>
+      <c r="K64" s="35"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="37"/>
-      <c r="D65" s="37"/>
-      <c r="E65" s="37"/>
-      <c r="F65" s="37"/>
-      <c r="G65" s="37"/>
-      <c r="H65" s="37"/>
-      <c r="I65" s="37"/>
-      <c r="J65" s="37"/>
-      <c r="K65" s="37"/>
+      <c r="C65" s="35"/>
+      <c r="D65" s="35"/>
+      <c r="E65" s="35"/>
+      <c r="F65" s="35"/>
+      <c r="G65" s="35"/>
+      <c r="H65" s="35"/>
+      <c r="I65" s="35"/>
+      <c r="J65" s="35"/>
+      <c r="K65" s="35"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="37"/>
-      <c r="D66" s="37"/>
-      <c r="E66" s="37"/>
-      <c r="F66" s="37"/>
-      <c r="G66" s="37"/>
-      <c r="H66" s="37"/>
-      <c r="I66" s="37"/>
-      <c r="J66" s="37"/>
-      <c r="K66" s="37"/>
+      <c r="C66" s="35"/>
+      <c r="D66" s="35"/>
+      <c r="E66" s="35"/>
+      <c r="F66" s="35"/>
+      <c r="G66" s="35"/>
+      <c r="H66" s="35"/>
+      <c r="I66" s="35"/>
+      <c r="J66" s="35"/>
+      <c r="K66" s="35"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="37"/>
-      <c r="D67" s="37"/>
-      <c r="E67" s="37"/>
-      <c r="F67" s="37"/>
-      <c r="G67" s="37"/>
-      <c r="H67" s="37"/>
-      <c r="I67" s="37"/>
-      <c r="J67" s="37"/>
-      <c r="K67" s="37"/>
+      <c r="C67" s="35"/>
+      <c r="D67" s="35"/>
+      <c r="E67" s="35"/>
+      <c r="F67" s="35"/>
+      <c r="G67" s="35"/>
+      <c r="H67" s="35"/>
+      <c r="I67" s="35"/>
+      <c r="J67" s="35"/>
+      <c r="K67" s="35"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="37"/>
-      <c r="D68" s="37"/>
-      <c r="E68" s="37"/>
-      <c r="F68" s="37"/>
-      <c r="G68" s="37"/>
-      <c r="H68" s="37"/>
-      <c r="I68" s="37"/>
-      <c r="J68" s="37"/>
-      <c r="K68" s="37"/>
+      <c r="C68" s="35"/>
+      <c r="D68" s="35"/>
+      <c r="E68" s="35"/>
+      <c r="F68" s="35"/>
+      <c r="G68" s="35"/>
+      <c r="H68" s="35"/>
+      <c r="I68" s="35"/>
+      <c r="J68" s="35"/>
+      <c r="K68" s="35"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="37"/>
-      <c r="D69" s="37"/>
-      <c r="E69" s="37"/>
-      <c r="F69" s="37"/>
-      <c r="G69" s="37"/>
-      <c r="H69" s="37"/>
-      <c r="I69" s="37"/>
-      <c r="J69" s="37"/>
-      <c r="K69" s="37"/>
+      <c r="C69" s="35"/>
+      <c r="D69" s="35"/>
+      <c r="E69" s="35"/>
+      <c r="F69" s="35"/>
+      <c r="G69" s="35"/>
+      <c r="H69" s="35"/>
+      <c r="I69" s="35"/>
+      <c r="J69" s="35"/>
+      <c r="K69" s="35"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="37"/>
-      <c r="D70" s="37"/>
-      <c r="E70" s="37"/>
-      <c r="F70" s="37"/>
-      <c r="G70" s="37"/>
-      <c r="H70" s="37"/>
-      <c r="I70" s="37"/>
-      <c r="J70" s="37"/>
-      <c r="K70" s="37"/>
+      <c r="C70" s="35"/>
+      <c r="D70" s="35"/>
+      <c r="E70" s="35"/>
+      <c r="F70" s="35"/>
+      <c r="G70" s="35"/>
+      <c r="H70" s="35"/>
+      <c r="I70" s="35"/>
+      <c r="J70" s="35"/>
+      <c r="K70" s="35"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="37"/>
-      <c r="D71" s="37"/>
-      <c r="E71" s="37"/>
-      <c r="F71" s="37"/>
-      <c r="G71" s="37"/>
-      <c r="H71" s="37"/>
-      <c r="I71" s="37"/>
-      <c r="J71" s="37"/>
-      <c r="K71" s="37"/>
+      <c r="C71" s="35"/>
+      <c r="D71" s="35"/>
+      <c r="E71" s="35"/>
+      <c r="F71" s="35"/>
+      <c r="G71" s="35"/>
+      <c r="H71" s="35"/>
+      <c r="I71" s="35"/>
+      <c r="J71" s="35"/>
+      <c r="K71" s="35"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="37"/>
-      <c r="D72" s="37"/>
-      <c r="E72" s="37"/>
-      <c r="F72" s="37"/>
-      <c r="G72" s="37"/>
-      <c r="H72" s="37"/>
-      <c r="I72" s="37"/>
-      <c r="J72" s="37"/>
-      <c r="K72" s="37"/>
+      <c r="C72" s="35"/>
+      <c r="D72" s="35"/>
+      <c r="E72" s="35"/>
+      <c r="F72" s="35"/>
+      <c r="G72" s="35"/>
+      <c r="H72" s="35"/>
+      <c r="I72" s="35"/>
+      <c r="J72" s="35"/>
+      <c r="K72" s="35"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="37"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="37"/>
-      <c r="I73" s="37"/>
-      <c r="J73" s="37"/>
-      <c r="K73" s="37"/>
+      <c r="C73" s="35"/>
+      <c r="D73" s="35"/>
+      <c r="E73" s="35"/>
+      <c r="F73" s="35"/>
+      <c r="G73" s="35"/>
+      <c r="H73" s="35"/>
+      <c r="I73" s="35"/>
+      <c r="J73" s="35"/>
+      <c r="K73" s="35"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="37"/>
-      <c r="D74" s="37"/>
-      <c r="E74" s="37"/>
-      <c r="F74" s="37"/>
-      <c r="G74" s="37"/>
-      <c r="H74" s="37"/>
-      <c r="I74" s="37"/>
-      <c r="J74" s="37"/>
-      <c r="K74" s="37"/>
+      <c r="C74" s="35"/>
+      <c r="D74" s="35"/>
+      <c r="E74" s="35"/>
+      <c r="F74" s="35"/>
+      <c r="G74" s="35"/>
+      <c r="H74" s="35"/>
+      <c r="I74" s="35"/>
+      <c r="J74" s="35"/>
+      <c r="K74" s="35"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="37"/>
-      <c r="D75" s="37"/>
-      <c r="E75" s="37"/>
-      <c r="F75" s="37"/>
-      <c r="G75" s="37"/>
-      <c r="H75" s="37"/>
-      <c r="I75" s="37"/>
-      <c r="J75" s="37"/>
-      <c r="K75" s="37"/>
+      <c r="C75" s="35"/>
+      <c r="D75" s="35"/>
+      <c r="E75" s="35"/>
+      <c r="F75" s="35"/>
+      <c r="G75" s="35"/>
+      <c r="H75" s="35"/>
+      <c r="I75" s="35"/>
+      <c r="J75" s="35"/>
+      <c r="K75" s="35"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="37"/>
-      <c r="D76" s="37"/>
-      <c r="E76" s="37"/>
-      <c r="F76" s="37"/>
-      <c r="G76" s="37"/>
-      <c r="H76" s="37"/>
-      <c r="I76" s="37"/>
-      <c r="J76" s="37"/>
-      <c r="K76" s="37"/>
+      <c r="C76" s="35"/>
+      <c r="D76" s="35"/>
+      <c r="E76" s="35"/>
+      <c r="F76" s="35"/>
+      <c r="G76" s="35"/>
+      <c r="H76" s="35"/>
+      <c r="I76" s="35"/>
+      <c r="J76" s="35"/>
+      <c r="K76" s="35"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="37"/>
-      <c r="D77" s="37"/>
-      <c r="E77" s="37"/>
-      <c r="F77" s="37"/>
-      <c r="G77" s="37"/>
-      <c r="H77" s="37"/>
-      <c r="I77" s="37"/>
-      <c r="J77" s="37"/>
-      <c r="K77" s="37"/>
+      <c r="C77" s="35"/>
+      <c r="D77" s="35"/>
+      <c r="E77" s="35"/>
+      <c r="F77" s="35"/>
+      <c r="G77" s="35"/>
+      <c r="H77" s="35"/>
+      <c r="I77" s="35"/>
+      <c r="J77" s="35"/>
+      <c r="K77" s="35"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="37"/>
-      <c r="D78" s="37"/>
-      <c r="E78" s="37"/>
-      <c r="F78" s="37"/>
-      <c r="G78" s="37"/>
-      <c r="H78" s="37"/>
-      <c r="I78" s="37"/>
-      <c r="J78" s="37"/>
-      <c r="K78" s="37"/>
+      <c r="C78" s="35"/>
+      <c r="D78" s="35"/>
+      <c r="E78" s="35"/>
+      <c r="F78" s="35"/>
+      <c r="G78" s="35"/>
+      <c r="H78" s="35"/>
+      <c r="I78" s="35"/>
+      <c r="J78" s="35"/>
+      <c r="K78" s="35"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="37"/>
-      <c r="D79" s="37"/>
-      <c r="E79" s="37"/>
-      <c r="F79" s="37"/>
-      <c r="G79" s="37"/>
-      <c r="H79" s="37"/>
-      <c r="I79" s="37"/>
-      <c r="J79" s="37"/>
-      <c r="K79" s="37"/>
+      <c r="C79" s="35"/>
+      <c r="D79" s="35"/>
+      <c r="E79" s="35"/>
+      <c r="F79" s="35"/>
+      <c r="G79" s="35"/>
+      <c r="H79" s="35"/>
+      <c r="I79" s="35"/>
+      <c r="J79" s="35"/>
+      <c r="K79" s="35"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="37"/>
-      <c r="D80" s="37"/>
-      <c r="E80" s="37"/>
-      <c r="F80" s="37"/>
-      <c r="G80" s="37"/>
-      <c r="H80" s="37"/>
-      <c r="I80" s="37"/>
-      <c r="J80" s="37"/>
-      <c r="K80" s="37"/>
+      <c r="C80" s="35"/>
+      <c r="D80" s="35"/>
+      <c r="E80" s="35"/>
+      <c r="F80" s="35"/>
+      <c r="G80" s="35"/>
+      <c r="H80" s="35"/>
+      <c r="I80" s="35"/>
+      <c r="J80" s="35"/>
+      <c r="K80" s="35"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="37"/>
-      <c r="D81" s="37"/>
-      <c r="E81" s="37"/>
-      <c r="F81" s="37"/>
-      <c r="G81" s="37"/>
-      <c r="H81" s="37"/>
-      <c r="I81" s="37"/>
-      <c r="J81" s="37"/>
-      <c r="K81" s="37"/>
+      <c r="C81" s="35"/>
+      <c r="D81" s="35"/>
+      <c r="E81" s="35"/>
+      <c r="F81" s="35"/>
+      <c r="G81" s="35"/>
+      <c r="H81" s="35"/>
+      <c r="I81" s="35"/>
+      <c r="J81" s="35"/>
+      <c r="K81" s="35"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="37"/>
-      <c r="D82" s="37"/>
-      <c r="E82" s="37"/>
-      <c r="F82" s="37"/>
-      <c r="G82" s="37"/>
-      <c r="H82" s="37"/>
-      <c r="I82" s="37"/>
-      <c r="J82" s="37"/>
-      <c r="K82" s="37"/>
+      <c r="C82" s="35"/>
+      <c r="D82" s="35"/>
+      <c r="E82" s="35"/>
+      <c r="F82" s="35"/>
+      <c r="G82" s="35"/>
+      <c r="H82" s="35"/>
+      <c r="I82" s="35"/>
+      <c r="J82" s="35"/>
+      <c r="K82" s="35"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="37"/>
-      <c r="D83" s="37"/>
-      <c r="E83" s="37"/>
-      <c r="F83" s="37"/>
-      <c r="G83" s="37"/>
-      <c r="H83" s="37"/>
-      <c r="I83" s="37"/>
-      <c r="J83" s="37"/>
-      <c r="K83" s="37"/>
+      <c r="C83" s="35"/>
+      <c r="D83" s="35"/>
+      <c r="E83" s="35"/>
+      <c r="F83" s="35"/>
+      <c r="G83" s="35"/>
+      <c r="H83" s="35"/>
+      <c r="I83" s="35"/>
+      <c r="J83" s="35"/>
+      <c r="K83" s="35"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="37" t="s">
+      <c r="C84" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="D84" s="37">
-        <v>1</v>
-      </c>
-      <c r="E84" s="37"/>
-      <c r="F84" s="37"/>
-      <c r="G84" s="37"/>
-      <c r="H84" s="37"/>
-      <c r="I84" s="37"/>
-      <c r="J84" s="37"/>
-      <c r="K84" s="37"/>
+      <c r="D84" s="35">
+        <v>1</v>
+      </c>
+      <c r="E84" s="35"/>
+      <c r="F84" s="35"/>
+      <c r="G84" s="35"/>
+      <c r="H84" s="35"/>
+      <c r="I84" s="35"/>
+      <c r="J84" s="35"/>
+      <c r="K84" s="35"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="37"/>
-      <c r="D85" s="37"/>
-      <c r="E85" s="37"/>
-      <c r="F85" s="37"/>
-      <c r="G85" s="37"/>
-      <c r="H85" s="37"/>
-      <c r="I85" s="37"/>
-      <c r="J85" s="37"/>
-      <c r="K85" s="37"/>
+      <c r="C85" s="35"/>
+      <c r="D85" s="35"/>
+      <c r="E85" s="35"/>
+      <c r="F85" s="35"/>
+      <c r="G85" s="35"/>
+      <c r="H85" s="35"/>
+      <c r="I85" s="35"/>
+      <c r="J85" s="35"/>
+      <c r="K85" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3333,7 +3328,7 @@
       <c r="G31" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H31" s="14" t="s">
+      <c r="H31" s="12" t="s">
         <v>69</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -3542,252 +3537,252 @@
       </c>
     </row>
     <row r="8" spans="2:14">
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="K8" s="15" t="s">
+      <c r="K8" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="L8" s="15" t="s">
+      <c r="L8" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="M8" s="15" t="s">
+      <c r="M8" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="N8" s="15" t="s">
+      <c r="N8" s="13" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="9" spans="2:14">
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="I9" s="14" t="s">
         <v>88</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="14">
         <v>1.25</v>
       </c>
       <c r="L9">
         <v>0.05</v>
       </c>
-      <c r="M9" s="16">
-        <v>1</v>
-      </c>
-      <c r="N9" s="16"/>
+      <c r="M9" s="14">
+        <v>1</v>
+      </c>
+      <c r="N9" s="14"/>
     </row>
     <row r="10" spans="2:14">
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="I10" s="16" t="s">
+      <c r="I10" s="14" t="s">
         <v>88</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="14">
         <v>1.11</v>
       </c>
       <c r="L10">
         <v>0.05</v>
       </c>
-      <c r="M10" s="16">
-        <v>1</v>
-      </c>
-      <c r="N10" s="16"/>
+      <c r="M10" s="14">
+        <v>1</v>
+      </c>
+      <c r="N10" s="14"/>
     </row>
     <row r="11" spans="2:14">
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="14" t="s">
         <v>88</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="14">
         <v>1.15</v>
       </c>
       <c r="L11">
         <v>0.08</v>
       </c>
-      <c r="M11" s="16">
-        <v>1</v>
-      </c>
-      <c r="N11" s="16"/>
+      <c r="M11" s="14">
+        <v>1</v>
+      </c>
+      <c r="N11" s="14"/>
     </row>
     <row r="12" ht="16" spans="2:14">
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="14" t="s">
         <v>93</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="I12" s="16" t="s">
+      <c r="I12" s="14" t="s">
         <v>88</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="14">
         <v>1.12</v>
       </c>
       <c r="L12">
         <v>0.03</v>
       </c>
-      <c r="M12" s="16">
-        <v>1</v>
-      </c>
-      <c r="N12" s="16"/>
+      <c r="M12" s="14">
+        <v>1</v>
+      </c>
+      <c r="N12" s="14"/>
     </row>
     <row r="13" spans="2:14">
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="H13" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="I13" s="16" t="s">
+      <c r="I13" s="14" t="s">
         <v>88</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="14">
         <v>1.2</v>
       </c>
       <c r="L13">
         <v>0.1</v>
       </c>
-      <c r="M13" s="16">
-        <v>1</v>
-      </c>
-      <c r="N13" s="16"/>
+      <c r="M13" s="14">
+        <v>1</v>
+      </c>
+      <c r="N13" s="14"/>
     </row>
     <row r="14" spans="2:14">
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H14" s="16" t="s">
+      <c r="H14" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="16" t="s">
+      <c r="I14" s="14" t="s">
         <v>88</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="14">
         <v>1.06</v>
       </c>
       <c r="L14">
         <v>0.15</v>
       </c>
-      <c r="M14" s="16">
-        <v>1</v>
-      </c>
-      <c r="N14" s="16"/>
+      <c r="M14" s="14">
+        <v>1</v>
+      </c>
+      <c r="N14" s="14"/>
     </row>
     <row r="15" spans="2:14">
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H15" s="16" t="s">
+      <c r="H15" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="I15" s="16" t="s">
+      <c r="I15" s="14" t="s">
         <v>88</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="14">
         <v>1.06</v>
       </c>
       <c r="L15">
         <v>0.3</v>
       </c>
-      <c r="M15" s="16">
-        <v>1</v>
-      </c>
-      <c r="N15" s="16"/>
+      <c r="M15" s="14">
+        <v>1</v>
+      </c>
+      <c r="N15" s="14"/>
     </row>
     <row r="16" ht="16" spans="2:14">
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="14" t="s">
         <v>101</v>
       </c>
       <c r="F16" s="2" t="s">
@@ -3801,7 +3796,7 @@
         <f>H15</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I16" s="16" t="s">
+      <c r="I16" s="14" t="s">
         <v>88</v>
       </c>
       <c r="J16">
@@ -3822,7 +3817,7 @@
       </c>
     </row>
     <row r="17" ht="16" spans="4:14">
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="14" t="s">
         <v>103</v>
       </c>
       <c r="F17" s="2" t="s">
@@ -3836,7 +3831,7 @@
         <f t="shared" si="1"/>
         <v>2025, 2150</v>
       </c>
-      <c r="I17" s="16" t="s">
+      <c r="I17" s="14" t="s">
         <v>88</v>
       </c>
       <c r="J17">
@@ -3857,7 +3852,7 @@
       </c>
     </row>
     <row r="18" ht="16" spans="4:14">
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="14" t="s">
         <v>105</v>
       </c>
       <c r="F18" s="2" t="s">
@@ -3871,7 +3866,7 @@
         <f>H17</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I18" s="16" t="s">
+      <c r="I18" s="14" t="s">
         <v>88</v>
       </c>
       <c r="J18">
@@ -3888,604 +3883,604 @@
       </c>
     </row>
     <row r="27" spans="4:14">
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
     </row>
     <row r="28" spans="4:14">
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17" t="s">
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
     </row>
     <row r="29" spans="4:14">
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="F29" s="17" t="s">
+      <c r="F29" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="17" t="s">
+      <c r="G29" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="H29" s="17" t="s">
+      <c r="H29" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="I29" s="17" t="s">
+      <c r="I29" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="J29" s="17" t="s">
+      <c r="J29" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="K29" s="17" t="s">
+      <c r="K29" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="L29" s="17" t="s">
+      <c r="L29" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="M29" s="17" t="s">
+      <c r="M29" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="N29" s="17" t="s">
+      <c r="N29" s="15" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="30" ht="16" spans="4:14">
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="17"/>
-      <c r="F30" s="18" t="s">
+      <c r="E30" s="15"/>
+      <c r="F30" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="G30" s="17" t="s">
+      <c r="G30" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="H30" s="17" t="s">
+      <c r="H30" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="I30" s="17" t="s">
+      <c r="I30" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="17">
-        <v>1</v>
-      </c>
-      <c r="K30" s="17">
-        <v>1</v>
-      </c>
-      <c r="L30" s="17">
+      <c r="J30" s="15">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15">
+        <v>1</v>
+      </c>
+      <c r="L30" s="15">
         <v>0.01</v>
       </c>
-      <c r="M30" s="17">
-        <v>1</v>
-      </c>
-      <c r="N30" s="17"/>
+      <c r="M30" s="15">
+        <v>1</v>
+      </c>
+      <c r="N30" s="15"/>
     </row>
     <row r="31" ht="16" spans="4:14">
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="17"/>
-      <c r="F31" s="19" t="s">
+      <c r="E31" s="15"/>
+      <c r="F31" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="G31" s="17" t="s">
+      <c r="G31" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="H31" s="17" t="s">
+      <c r="H31" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="I31" s="17" t="s">
+      <c r="I31" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="J31" s="17">
-        <v>1</v>
-      </c>
-      <c r="K31" s="17">
-        <v>1</v>
-      </c>
-      <c r="L31" s="17">
+      <c r="J31" s="15">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>1</v>
+      </c>
+      <c r="L31" s="15">
         <f t="shared" ref="L31:L36" si="2">L30</f>
         <v>0.01</v>
       </c>
-      <c r="M31" s="17">
-        <v>1</v>
-      </c>
-      <c r="N31" s="17"/>
+      <c r="M31" s="15">
+        <v>1</v>
+      </c>
+      <c r="N31" s="15"/>
     </row>
     <row r="32" ht="16" spans="4:14">
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="E32" s="17"/>
-      <c r="F32" s="19" t="s">
+      <c r="E32" s="15"/>
+      <c r="F32" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="G32" s="17" t="s">
+      <c r="G32" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="H32" s="17" t="s">
+      <c r="H32" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="I32" s="17" t="s">
+      <c r="I32" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="J32" s="17">
-        <v>1</v>
-      </c>
-      <c r="K32" s="17">
-        <v>1</v>
-      </c>
-      <c r="L32" s="17">
+      <c r="J32" s="15">
+        <v>1</v>
+      </c>
+      <c r="K32" s="15">
+        <v>1</v>
+      </c>
+      <c r="L32" s="15">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M32" s="17">
-        <v>1</v>
-      </c>
-      <c r="N32" s="17"/>
+      <c r="M32" s="15">
+        <v>1</v>
+      </c>
+      <c r="N32" s="15"/>
     </row>
     <row r="33" ht="16" spans="4:14">
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="17"/>
-      <c r="F33" s="18" t="s">
+      <c r="E33" s="15"/>
+      <c r="F33" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G33" s="17" t="s">
+      <c r="G33" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="H33" s="17" t="s">
+      <c r="H33" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="I33" s="17" t="s">
+      <c r="I33" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="J33" s="17">
-        <v>1</v>
-      </c>
-      <c r="K33" s="17">
+      <c r="J33" s="15">
+        <v>1</v>
+      </c>
+      <c r="K33" s="15">
         <f>K32</f>
         <v>1</v>
       </c>
-      <c r="L33" s="17">
+      <c r="L33" s="15">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M33" s="17">
-        <v>1</v>
-      </c>
-      <c r="N33" s="17"/>
+      <c r="M33" s="15">
+        <v>1</v>
+      </c>
+      <c r="N33" s="15"/>
     </row>
     <row r="34" ht="16" spans="4:14">
-      <c r="D34" s="17" t="s">
+      <c r="D34" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E34" s="17"/>
-      <c r="F34" s="18" t="s">
+      <c r="E34" s="15"/>
+      <c r="F34" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="G34" s="17" t="s">
+      <c r="G34" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="H34" s="17" t="s">
+      <c r="H34" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="I34" s="17" t="s">
+      <c r="I34" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="J34" s="17">
-        <v>1</v>
-      </c>
-      <c r="K34" s="17">
+      <c r="J34" s="15">
+        <v>1</v>
+      </c>
+      <c r="K34" s="15">
         <f>K33</f>
         <v>1</v>
       </c>
-      <c r="L34" s="17">
+      <c r="L34" s="15">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M34" s="17">
-        <v>1</v>
-      </c>
-      <c r="N34" s="17"/>
+      <c r="M34" s="15">
+        <v>1</v>
+      </c>
+      <c r="N34" s="15"/>
     </row>
     <row r="35" ht="16" spans="4:14">
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E35" s="17"/>
-      <c r="F35" s="18" t="s">
+      <c r="E35" s="15"/>
+      <c r="F35" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="17" t="s">
+      <c r="G35" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="H35" s="17" t="s">
+      <c r="H35" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="I35" s="17" t="s">
+      <c r="I35" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="J35" s="17">
-        <v>1</v>
-      </c>
-      <c r="K35" s="17">
+      <c r="J35" s="15">
+        <v>1</v>
+      </c>
+      <c r="K35" s="15">
         <f>K34</f>
         <v>1</v>
       </c>
-      <c r="L35" s="17">
+      <c r="L35" s="15">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M35" s="17">
-        <v>1</v>
-      </c>
-      <c r="N35" s="17"/>
+      <c r="M35" s="15">
+        <v>1</v>
+      </c>
+      <c r="N35" s="15"/>
     </row>
     <row r="36" ht="16" spans="4:14">
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E36" s="17"/>
-      <c r="F36" s="18" t="s">
+      <c r="E36" s="15"/>
+      <c r="F36" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G36" s="17" t="s">
+      <c r="G36" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="H36" s="17" t="s">
+      <c r="H36" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="I36" s="17" t="s">
+      <c r="I36" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="J36" s="17">
-        <v>1</v>
-      </c>
-      <c r="K36" s="17">
+      <c r="J36" s="15">
+        <v>1</v>
+      </c>
+      <c r="K36" s="15">
         <f>K35</f>
         <v>1</v>
       </c>
-      <c r="L36" s="17">
+      <c r="L36" s="15">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M36" s="17">
-        <v>1</v>
-      </c>
-      <c r="N36" s="17"/>
+      <c r="M36" s="15">
+        <v>1</v>
+      </c>
+      <c r="N36" s="15"/>
     </row>
     <row r="37" ht="16" spans="4:14">
-      <c r="D37" s="20" t="s">
+      <c r="D37" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="E37" s="20"/>
-      <c r="F37" s="21" t="s">
+      <c r="E37" s="18"/>
+      <c r="F37" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="G37" s="20" t="s">
+      <c r="G37" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="H37" s="20" t="s">
+      <c r="H37" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="I37" s="20" t="s">
+      <c r="I37" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="J37" s="20">
-        <v>1</v>
-      </c>
-      <c r="K37" s="20">
-        <v>1</v>
-      </c>
-      <c r="L37" s="20">
+      <c r="J37" s="18">
+        <v>1</v>
+      </c>
+      <c r="K37" s="18">
+        <v>1</v>
+      </c>
+      <c r="L37" s="18">
         <v>0.01</v>
       </c>
-      <c r="M37" s="20">
-        <v>1</v>
-      </c>
-      <c r="N37" s="17"/>
+      <c r="M37" s="18">
+        <v>1</v>
+      </c>
+      <c r="N37" s="15"/>
     </row>
     <row r="38" ht="16" spans="4:14">
-      <c r="D38" s="20" t="s">
+      <c r="D38" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="E38" s="20"/>
-      <c r="F38" s="22" t="s">
+      <c r="E38" s="18"/>
+      <c r="F38" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="G38" s="20" t="s">
+      <c r="G38" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="H38" s="20" t="s">
+      <c r="H38" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="I38" s="20" t="s">
+      <c r="I38" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="J38" s="20">
-        <v>1</v>
-      </c>
-      <c r="K38" s="20">
-        <v>1</v>
-      </c>
-      <c r="L38" s="20">
+      <c r="J38" s="18">
+        <v>1</v>
+      </c>
+      <c r="K38" s="18">
+        <v>1</v>
+      </c>
+      <c r="L38" s="18">
         <f t="shared" ref="L38:L43" si="3">L37</f>
         <v>0.01</v>
       </c>
-      <c r="M38" s="20">
-        <v>1</v>
-      </c>
-      <c r="N38" s="17"/>
+      <c r="M38" s="18">
+        <v>1</v>
+      </c>
+      <c r="N38" s="15"/>
     </row>
     <row r="39" ht="16" spans="4:14">
-      <c r="D39" s="20" t="s">
+      <c r="D39" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="E39" s="20"/>
-      <c r="F39" s="22" t="s">
+      <c r="E39" s="18"/>
+      <c r="F39" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="G39" s="20" t="s">
+      <c r="G39" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="H39" s="20" t="s">
+      <c r="H39" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="I39" s="20" t="s">
+      <c r="I39" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="J39" s="20">
-        <v>1</v>
-      </c>
-      <c r="K39" s="20">
-        <v>1</v>
-      </c>
-      <c r="L39" s="20">
+      <c r="J39" s="18">
+        <v>1</v>
+      </c>
+      <c r="K39" s="18">
+        <v>1</v>
+      </c>
+      <c r="L39" s="18">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M39" s="20">
-        <v>1</v>
-      </c>
-      <c r="N39" s="17"/>
+      <c r="M39" s="18">
+        <v>1</v>
+      </c>
+      <c r="N39" s="15"/>
     </row>
     <row r="40" ht="16" spans="4:14">
-      <c r="D40" s="20" t="s">
+      <c r="D40" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E40" s="20"/>
-      <c r="F40" s="23" t="s">
+      <c r="E40" s="18"/>
+      <c r="F40" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="G40" s="20" t="s">
+      <c r="G40" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="H40" s="20" t="s">
+      <c r="H40" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="I40" s="20" t="s">
+      <c r="I40" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="J40" s="20">
-        <v>1</v>
-      </c>
-      <c r="K40" s="20">
+      <c r="J40" s="18">
+        <v>1</v>
+      </c>
+      <c r="K40" s="18">
         <f>K39</f>
         <v>1</v>
       </c>
-      <c r="L40" s="20">
+      <c r="L40" s="18">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M40" s="20">
-        <v>1</v>
-      </c>
-      <c r="N40" s="17"/>
+      <c r="M40" s="18">
+        <v>1</v>
+      </c>
+      <c r="N40" s="15"/>
     </row>
     <row r="41" ht="16" spans="4:14">
-      <c r="D41" s="20" t="s">
+      <c r="D41" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="E41" s="20"/>
-      <c r="F41" s="23" t="s">
+      <c r="E41" s="18"/>
+      <c r="F41" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="G41" s="20" t="s">
+      <c r="G41" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="H41" s="20" t="s">
+      <c r="H41" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="I41" s="20" t="s">
+      <c r="I41" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="J41" s="20">
-        <v>1</v>
-      </c>
-      <c r="K41" s="20">
+      <c r="J41" s="18">
+        <v>1</v>
+      </c>
+      <c r="K41" s="18">
         <f>K40</f>
         <v>1</v>
       </c>
-      <c r="L41" s="20">
+      <c r="L41" s="18">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M41" s="20">
-        <v>1</v>
-      </c>
-      <c r="N41" s="17"/>
+      <c r="M41" s="18">
+        <v>1</v>
+      </c>
+      <c r="N41" s="15"/>
     </row>
     <row r="42" ht="16" spans="4:14">
-      <c r="D42" s="20" t="s">
+      <c r="D42" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="E42" s="20"/>
-      <c r="F42" s="23" t="s">
+      <c r="E42" s="18"/>
+      <c r="F42" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="G42" s="20" t="s">
+      <c r="G42" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="H42" s="20" t="s">
+      <c r="H42" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="I42" s="20" t="s">
+      <c r="I42" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="J42" s="20">
-        <v>1</v>
-      </c>
-      <c r="K42" s="20">
+      <c r="J42" s="18">
+        <v>1</v>
+      </c>
+      <c r="K42" s="18">
         <f>K41</f>
         <v>1</v>
       </c>
-      <c r="L42" s="20">
+      <c r="L42" s="18">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M42" s="20">
-        <v>1</v>
-      </c>
-      <c r="N42" s="17"/>
+      <c r="M42" s="18">
+        <v>1</v>
+      </c>
+      <c r="N42" s="15"/>
     </row>
     <row r="43" ht="16" spans="4:14">
-      <c r="D43" s="20" t="s">
+      <c r="D43" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="E43" s="20"/>
-      <c r="F43" s="23" t="s">
+      <c r="E43" s="18"/>
+      <c r="F43" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="G43" s="20" t="s">
+      <c r="G43" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="H43" s="20" t="s">
+      <c r="H43" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="I43" s="20" t="s">
+      <c r="I43" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="J43" s="20">
-        <v>1</v>
-      </c>
-      <c r="K43" s="20">
+      <c r="J43" s="18">
+        <v>1</v>
+      </c>
+      <c r="K43" s="18">
         <f>K42</f>
         <v>1</v>
       </c>
-      <c r="L43" s="20">
+      <c r="L43" s="18">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="M43" s="20">
-        <v>1</v>
-      </c>
-      <c r="N43" s="17"/>
+      <c r="M43" s="18">
+        <v>1</v>
+      </c>
+      <c r="N43" s="15"/>
     </row>
     <row r="44" spans="4:14">
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
-      <c r="K44" s="20"/>
-      <c r="L44" s="20"/>
-      <c r="M44" s="20"/>
-      <c r="N44" s="17"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="18"/>
+      <c r="M44" s="18"/>
+      <c r="N44" s="15"/>
     </row>
     <row r="45" spans="4:14">
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="24"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="20"/>
-      <c r="K45" s="20"/>
-      <c r="L45" s="20"/>
-      <c r="M45" s="20"/>
-      <c r="N45" s="17"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18"/>
+      <c r="L45" s="18"/>
+      <c r="M45" s="18"/>
+      <c r="N45" s="15"/>
     </row>
     <row r="46" spans="4:14">
-      <c r="N46" s="17"/>
+      <c r="N46" s="15"/>
     </row>
     <row r="47" spans="4:14">
-      <c r="N47" s="17"/>
+      <c r="N47" s="15"/>
     </row>
     <row r="48" spans="4:14">
-      <c r="N48" s="17"/>
+      <c r="N48" s="15"/>
     </row>
     <row r="49" spans="4:14">
-      <c r="N49" s="17"/>
+      <c r="N49" s="15"/>
     </row>
     <row r="50" spans="4:14">
-      <c r="N50" s="17"/>
+      <c r="N50" s="15"/>
     </row>
     <row r="51" spans="4:14">
-      <c r="N51" s="17"/>
+      <c r="N51" s="15"/>
     </row>
     <row r="52" spans="4:14">
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="17"/>
-      <c r="M52" s="17"/>
-      <c r="N52" s="17"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="15"/>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="15"/>
+      <c r="K52" s="15"/>
+      <c r="L52" s="15"/>
+      <c r="M52" s="15"/>
+      <c r="N52" s="15"/>
     </row>
     <row r="53" spans="4:14">
-      <c r="D53" s="17"/>
-      <c r="E53" s="17"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="17"/>
-      <c r="H53" s="17"/>
-      <c r="I53" s="17"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="17"/>
-      <c r="L53" s="17"/>
-      <c r="M53" s="17"/>
-      <c r="N53" s="17"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="15"/>
+      <c r="H53" s="15"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="15"/>
+      <c r="K53" s="15"/>
+      <c r="L53" s="15"/>
+      <c r="M53" s="15"/>
+      <c r="N53" s="15"/>
     </row>
     <row r="54" spans="4:14">
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="17"/>
-      <c r="G54" s="17"/>
-      <c r="H54" s="17"/>
-      <c r="I54" s="17"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="17"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="15"/>
+      <c r="H54" s="15"/>
+      <c r="I54" s="15"/>
+      <c r="J54" s="15"/>
+      <c r="K54" s="15"/>
+      <c r="L54" s="15"/>
+      <c r="M54" s="15"/>
+      <c r="N54" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4503,6 +4498,7 @@
     <col min="7" max="7" width="25.3636363636364" customWidth="1"/>
     <col min="8" max="8" width="56.3636363636364" customWidth="1"/>
     <col min="9" max="9" width="43.7272727272727" customWidth="1"/>
+    <col min="13" max="13" width="40.1818181818182" customWidth="1"/>
     <col min="14" max="14" width="12.8181818181818" customWidth="1"/>
     <col min="15" max="15" width="40.1818181818182" customWidth="1"/>
     <col min="16" max="16" width="12.6363636363636" customWidth="1"/>
@@ -4986,28 +4982,25 @@
       <c r="J52" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="K52" s="5" t="s">
-        <v>151</v>
+      <c r="K52" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M52" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N52" s="5" t="s">
+      <c r="M52" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="O52" s="3" t="s">
+      <c r="N52" s="3" t="s">
         <v>61</v>
       </c>
+      <c r="O52" t="s">
+        <v>62</v>
+      </c>
       <c r="P52" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R52" s="1" t="s">
         <v>65</v>
       </c>
       <c r="T52" s="6"/>
@@ -5039,26 +5032,34 @@
     <row r="53" ht="16" spans="6:44">
       <c r="F53" s="8"/>
       <c r="G53" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>110</v>
       </c>
       <c r="I53" s="9">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="J53" s="10">
         <v>-1</v>
       </c>
-      <c r="K53" s="11"/>
-      <c r="L53" s="3"/>
-      <c r="N53" s="12" t="s">
+      <c r="K53" s="3"/>
+      <c r="L53" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="M53" s="11" t="s">
         <v>153</v>
       </c>
+      <c r="N53" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="O53" s="3">
+        <v>10</v>
+      </c>
+      <c r="P53" s="1">
+        <v>0</v>
+      </c>
       <c r="Q53" s="1">
-        <v>0</v>
-      </c>
-      <c r="R53" s="1">
         <v>3</v>
       </c>
       <c r="T53" s="6"/>
@@ -5087,25 +5088,12 @@
       <c r="AQ53" s="6"/>
       <c r="AR53" s="6"/>
     </row>
-    <row r="54" ht="16" spans="6:44">
+    <row r="54" spans="6:44">
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
-      <c r="L54" s="3"/>
-      <c r="M54" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="N54" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="O54" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="P54" s="3">
-        <v>10</v>
-      </c>
     </row>
     <row r="55" spans="6:44">
       <c r="G55" s="3"/>
@@ -5117,7 +5105,6 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-      <c r="P55" s="3"/>
     </row>
     <row r="56" spans="6:44">
       <c r="G56" s="3"/>
@@ -5129,7 +5116,6 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-      <c r="P56" s="3"/>
     </row>
     <row r="61" spans="6:44">
       <c r="G61" s="3"/>
@@ -5143,9 +5129,8 @@
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
       <c r="O61" s="5"/>
-      <c r="P61" s="5"/>
+      <c r="P61" s="6"/>
       <c r="Q61" s="6"/>
-      <c r="R61" s="6"/>
     </row>
     <row r="62" spans="6:44">
       <c r="G62" s="3" t="s">
@@ -5160,76 +5145,67 @@
       <c r="J62" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="K62" s="5" t="s">
-        <v>151</v>
+      <c r="K62" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M62" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N62" s="5" t="s">
+      <c r="M62" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="O62" s="3" t="s">
+      <c r="N62" s="3" t="s">
         <v>61</v>
       </c>
+      <c r="O62" t="s">
+        <v>62</v>
+      </c>
       <c r="P62" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R62" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="63" ht="16" spans="6:44">
       <c r="G63" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>110</v>
       </c>
       <c r="I63" s="9">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="J63" s="10">
         <v>-1</v>
       </c>
-      <c r="K63" s="11"/>
-      <c r="L63" s="3"/>
-      <c r="N63" s="13" t="s">
-        <v>156</v>
+      <c r="K63" s="3"/>
+      <c r="L63" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="M63" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="O63" s="3">
+        <v>10</v>
+      </c>
+      <c r="P63" s="1">
+        <v>0</v>
       </c>
       <c r="Q63" s="1">
-        <v>0</v>
-      </c>
-      <c r="R63" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="64" ht="16" spans="6:44">
+    <row r="64" spans="6:44">
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
-      <c r="L64" s="3"/>
-      <c r="M64" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="N64" s="12" t="str">
-        <f>N63</f>
-        <v>EN_STG_4hBatt*, Util_Rep_Bat*</v>
-      </c>
-      <c r="O64" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="P64" s="3">
-        <v>10</v>
-      </c>
     </row>
     <row r="66" ht="15.25" spans="7:20">
       <c r="G66" s="1"/>
@@ -5243,21 +5219,19 @@
       <c r="O66" s="1"/>
       <c r="P66" s="1"/>
       <c r="Q66" s="1"/>
-      <c r="R66" s="1"/>
       <c r="T66" s="1"/>
     </row>
     <row r="67" ht="16" spans="7:20">
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
-      <c r="I67" s="14"/>
+      <c r="I67" s="12"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
-      <c r="N67" s="1"/>
+      <c r="O67" s="1"/>
       <c r="P67" s="1"/>
       <c r="Q67" s="1"/>
-      <c r="R67" s="1"/>
       <c r="T67" s="1"/>
     </row>
     <row r="68" ht="15.25" spans="7:20">
@@ -5272,7 +5246,6 @@
       <c r="O68" s="1"/>
       <c r="P68" s="1"/>
       <c r="Q68" s="1"/>
-      <c r="R68" s="1"/>
       <c r="T68" s="1"/>
     </row>
     <row r="69" spans="7:20">
@@ -5287,7 +5260,6 @@
       <c r="O69" s="1"/>
       <c r="P69" s="1"/>
       <c r="Q69" s="1"/>
-      <c r="R69" s="1"/>
       <c r="T69" s="1"/>
     </row>
     <row r="70" spans="7:20">
@@ -5302,9 +5274,8 @@
       <c r="M70" s="5"/>
       <c r="N70" s="5"/>
       <c r="O70" s="5"/>
-      <c r="P70" s="5"/>
+      <c r="P70" s="6"/>
       <c r="Q70" s="6"/>
-      <c r="R70" s="6"/>
       <c r="T70" s="1"/>
     </row>
     <row r="71" spans="7:20">
@@ -5320,76 +5291,67 @@
       <c r="J71" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="K71" s="5" t="s">
-        <v>151</v>
+      <c r="K71" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M71" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N71" s="5" t="s">
+      <c r="M71" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="O71" s="3" t="s">
+      <c r="N71" s="3" t="s">
         <v>61</v>
       </c>
+      <c r="O71" t="s">
+        <v>62</v>
+      </c>
       <c r="P71" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R71" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="72" ht="16" spans="7:20">
       <c r="G72" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>110</v>
       </c>
       <c r="I72" s="9">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="J72" s="10">
         <v>-1</v>
       </c>
-      <c r="K72" s="11"/>
-      <c r="L72" s="3"/>
-      <c r="N72" s="13" t="s">
+      <c r="K72" s="3"/>
+      <c r="L72" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="M72" s="11" t="s">
         <v>39</v>
       </c>
+      <c r="N72" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="O72" s="3">
+        <v>10</v>
+      </c>
+      <c r="P72" s="1">
+        <v>0</v>
+      </c>
       <c r="Q72" s="1">
-        <v>0</v>
-      </c>
-      <c r="R72" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="73" ht="16" spans="7:20">
+    <row r="73" spans="7:20">
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
       <c r="J73" s="3"/>
       <c r="K73" s="3"/>
-      <c r="L73" s="3"/>
-      <c r="M73" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="N73" s="12" t="str">
-        <f>N72</f>
-        <v>*HPS*</v>
-      </c>
-      <c r="O73" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="P73" s="3">
-        <v>10</v>
-      </c>
     </row>
     <row r="80" spans="7:20">
       <c r="G80" s="3"/>
@@ -5403,11 +5365,10 @@
       <c r="M80" s="5"/>
       <c r="N80" s="5"/>
       <c r="O80" s="5"/>
-      <c r="P80" s="5"/>
+      <c r="P80" s="6"/>
       <c r="Q80" s="6"/>
-      <c r="R80" s="6"/>
-    </row>
-    <row r="81" spans="7:18">
+    </row>
+    <row r="81" spans="7:17">
       <c r="G81" s="3" t="s">
         <v>59</v>
       </c>
@@ -5420,76 +5381,67 @@
       <c r="J81" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="K81" s="5" t="s">
-        <v>151</v>
+      <c r="K81" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M81" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N81" s="5" t="s">
+      <c r="M81" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="O81" s="3" t="s">
+      <c r="N81" s="3" t="s">
         <v>61</v>
       </c>
+      <c r="O81" t="s">
+        <v>62</v>
+      </c>
       <c r="P81" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R81" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="82" ht="16" spans="7:18">
+    <row r="82" ht="16" spans="7:17">
       <c r="G82" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>110</v>
       </c>
       <c r="I82" s="9">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="J82" s="10">
         <v>-1</v>
       </c>
-      <c r="K82" s="11"/>
-      <c r="L82" s="3"/>
-      <c r="N82" s="13" t="s">
-        <v>159</v>
+      <c r="K82" s="3"/>
+      <c r="L82" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="M82" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="O82" s="3">
+        <v>10</v>
+      </c>
+      <c r="P82" s="1">
+        <v>0</v>
       </c>
       <c r="Q82" s="1">
-        <v>0</v>
-      </c>
-      <c r="R82" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="83" ht="16" spans="7:18">
+    <row r="83" spans="7:17">
       <c r="G83" s="3"/>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
-      <c r="L83" s="3"/>
-      <c r="M83" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="N83" s="12" t="str">
-        <f>N82</f>
-        <v>Tra_BEV_Batt_VtoG</v>
-      </c>
-      <c r="O83" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="P83" s="3">
-        <v>10</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="7"/>
+    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
@@ -245,7 +245,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="149">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -622,37 +622,7 @@
     <t>EN_STG_4hBatt</t>
   </si>
   <si>
-    <t>2020, 2150</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy9</t>
-  </si>
-  <si>
-    <t>EN_STG_4hBatt_LMO</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy10</t>
-  </si>
-  <si>
-    <t>EN_STG_4hBatt_NCA</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy11</t>
-  </si>
-  <si>
-    <t>EN_STG_4hBatt_NMC111</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy12</t>
-  </si>
-  <si>
-    <t>EN_STG_4hBatt_NMC532</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy13</t>
-  </si>
-  <si>
-    <t>EN_STG_4hBatt_NMC622</t>
+    <t>2019, 2150</t>
   </si>
   <si>
     <t>UC_Grow_Recy14</t>
@@ -955,18 +925,18 @@
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -987,7 +957,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.6"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1000,12 +970,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1337,7 +1301,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1361,16 +1325,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1379,93 +1343,93 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1496,11 +1460,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1512,9 +1480,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -2050,7 +2017,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="36">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -2164,10 +2131,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="36"/>
+      <c r="K10" s="39"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="36"/>
+      <c r="K11" s="39"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2188,11 +2155,11 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:13">
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
       <c r="F5" s="15"/>
     </row>
     <row r="6" spans="2:13">
@@ -2208,19 +2175,19 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="25"/>
+      <c r="K6" s="29"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="30">
         <v>10</v>
       </c>
     </row>
@@ -2228,17 +2195,17 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="30">
         <v>7</v>
       </c>
-      <c r="L8" s="24"/>
-      <c r="M8" s="24"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
     </row>
     <row r="9" ht="16" spans="2:13">
       <c r="B9" t="s">
@@ -2247,10 +2214,10 @@
       <c r="C9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="30">
         <v>10</v>
       </c>
     </row>
@@ -2258,17 +2225,17 @@
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="30">
         <v>8</v>
       </c>
-      <c r="K10" s="27"/>
-      <c r="L10" s="28"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="32"/>
     </row>
     <row r="11" ht="16" spans="2:13">
       <c r="B11" t="s">
@@ -2277,10 +2244,10 @@
       <c r="C11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="28">
         <v>1.5</v>
       </c>
     </row>
@@ -2291,10 +2258,10 @@
       <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="24" t="s">
+      <c r="D12" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="28">
         <v>1.5</v>
       </c>
     </row>
@@ -2305,7 +2272,7 @@
       <c r="C13" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D13" s="28" t="s">
         <v>35</v>
       </c>
       <c r="E13" s="15">
@@ -2319,7 +2286,7 @@
       <c r="C14" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="28" t="s">
         <v>35</v>
       </c>
       <c r="E14" s="15">
@@ -2333,7 +2300,7 @@
       <c r="C15" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="28" t="s">
         <v>35</v>
       </c>
       <c r="E15" s="15">
@@ -2344,13 +2311,13 @@
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="33">
         <v>12</v>
       </c>
     </row>
@@ -2358,13 +2325,13 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="30" t="s">
+      <c r="D17" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="35">
         <v>0.2</v>
       </c>
       <c r="F17" s="15"/>
@@ -2373,13 +2340,13 @@
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="35">
         <v>0.2</v>
       </c>
       <c r="F18" s="15"/>
@@ -2391,10 +2358,10 @@
       <c r="C19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="30" t="s">
+      <c r="D19" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="35">
         <v>0.2</v>
       </c>
       <c r="F19" s="15"/>
@@ -2403,13 +2370,13 @@
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="35">
         <v>0.5</v>
       </c>
       <c r="F20" s="15"/>
@@ -2421,10 +2388,10 @@
       <c r="C21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="35">
         <v>0.8</v>
       </c>
       <c r="F21" s="15"/>
@@ -2436,10 +2403,10 @@
       <c r="C22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="30" t="s">
+      <c r="D22" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="24"/>
+      <c r="E22" s="28"/>
       <c r="F22" s="15"/>
     </row>
     <row r="23" spans="2:6">
@@ -2449,7 +2416,7 @@
       <c r="C23" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="30" t="s">
+      <c r="D23" s="34" t="s">
         <v>43</v>
       </c>
       <c r="E23" s="15">
@@ -2464,7 +2431,7 @@
       <c r="C24" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="30" t="s">
+      <c r="D24" s="34" t="s">
         <v>43</v>
       </c>
       <c r="E24" s="15">
@@ -2479,7 +2446,7 @@
       <c r="C25" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="30" t="s">
+      <c r="D25" s="34" t="s">
         <v>43</v>
       </c>
       <c r="E25" s="15">
@@ -2491,28 +2458,28 @@
       <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="30" t="s">
+      <c r="D26" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="28">
         <v>0.05</v>
       </c>
       <c r="F26" s="15"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="32" t="s">
+      <c r="B27" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="33" t="s">
+      <c r="C27" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="33" t="s">
+      <c r="D27" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="37">
         <v>2020</v>
       </c>
       <c r="F27" s="15"/>
@@ -2521,10 +2488,10 @@
       <c r="C28" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="33" t="s">
+      <c r="D28" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="34">
+      <c r="E28" s="18">
         <v>2020</v>
       </c>
       <c r="F28" s="15"/>
@@ -2559,360 +2526,360 @@
       <c r="E38" s="1"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="35" t="s">
+      <c r="C54" s="38" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="35"/>
-      <c r="E56" s="35"/>
-      <c r="F56" s="35"/>
-      <c r="G56" s="35"/>
-      <c r="H56" s="35"/>
-      <c r="I56" s="35"/>
-      <c r="J56" s="35"/>
-      <c r="K56" s="35"/>
+      <c r="D56" s="38"/>
+      <c r="E56" s="38"/>
+      <c r="F56" s="38"/>
+      <c r="G56" s="38"/>
+      <c r="H56" s="38"/>
+      <c r="I56" s="38"/>
+      <c r="J56" s="38"/>
+      <c r="K56" s="38"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="35" t="s">
+      <c r="C57" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="35" t="s">
+      <c r="D57" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="35" t="s">
+      <c r="E57" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="F57" s="35" t="s">
+      <c r="F57" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="G57" s="35" t="s">
+      <c r="G57" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="35" t="s">
+      <c r="H57" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="35" t="s">
+      <c r="I57" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="J57" s="35" t="s">
+      <c r="J57" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="K57" s="35" t="s">
+      <c r="K57" s="38" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="35"/>
-      <c r="D58" s="35"/>
-      <c r="E58" s="35"/>
-      <c r="F58" s="35"/>
-      <c r="G58" s="35"/>
-      <c r="H58" s="35"/>
-      <c r="I58" s="35"/>
-      <c r="J58" s="35"/>
-      <c r="K58" s="35"/>
+      <c r="C58" s="38"/>
+      <c r="D58" s="38"/>
+      <c r="E58" s="38"/>
+      <c r="F58" s="38"/>
+      <c r="G58" s="38"/>
+      <c r="H58" s="38"/>
+      <c r="I58" s="38"/>
+      <c r="J58" s="38"/>
+      <c r="K58" s="38"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="35"/>
-      <c r="D59" s="35"/>
-      <c r="E59" s="35"/>
-      <c r="F59" s="35"/>
-      <c r="G59" s="35"/>
-      <c r="H59" s="35"/>
-      <c r="I59" s="35"/>
-      <c r="J59" s="35"/>
-      <c r="K59" s="35"/>
+      <c r="C59" s="38"/>
+      <c r="D59" s="38"/>
+      <c r="E59" s="38"/>
+      <c r="F59" s="38"/>
+      <c r="G59" s="38"/>
+      <c r="H59" s="38"/>
+      <c r="I59" s="38"/>
+      <c r="J59" s="38"/>
+      <c r="K59" s="38"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="35"/>
-      <c r="D60" s="35"/>
-      <c r="E60" s="35"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="35"/>
-      <c r="H60" s="35"/>
-      <c r="I60" s="35"/>
-      <c r="J60" s="35"/>
-      <c r="K60" s="35"/>
+      <c r="C60" s="38"/>
+      <c r="D60" s="38"/>
+      <c r="E60" s="38"/>
+      <c r="F60" s="38"/>
+      <c r="G60" s="38"/>
+      <c r="H60" s="38"/>
+      <c r="I60" s="38"/>
+      <c r="J60" s="38"/>
+      <c r="K60" s="38"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="35"/>
-      <c r="D61" s="35"/>
-      <c r="E61" s="35"/>
-      <c r="F61" s="35"/>
-      <c r="G61" s="35"/>
-      <c r="H61" s="35"/>
-      <c r="I61" s="35"/>
-      <c r="J61" s="35"/>
-      <c r="K61" s="35"/>
+      <c r="C61" s="38"/>
+      <c r="D61" s="38"/>
+      <c r="E61" s="38"/>
+      <c r="F61" s="38"/>
+      <c r="G61" s="38"/>
+      <c r="H61" s="38"/>
+      <c r="I61" s="38"/>
+      <c r="J61" s="38"/>
+      <c r="K61" s="38"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="35"/>
-      <c r="D62" s="35"/>
-      <c r="E62" s="35"/>
-      <c r="F62" s="35"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="35"/>
-      <c r="I62" s="35"/>
-      <c r="J62" s="35"/>
-      <c r="K62" s="35"/>
+      <c r="C62" s="38"/>
+      <c r="D62" s="38"/>
+      <c r="E62" s="38"/>
+      <c r="F62" s="38"/>
+      <c r="G62" s="38"/>
+      <c r="H62" s="38"/>
+      <c r="I62" s="38"/>
+      <c r="J62" s="38"/>
+      <c r="K62" s="38"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="35"/>
-      <c r="D63" s="35"/>
-      <c r="E63" s="35"/>
-      <c r="F63" s="35"/>
-      <c r="G63" s="35"/>
-      <c r="H63" s="35"/>
-      <c r="I63" s="35"/>
-      <c r="J63" s="35"/>
-      <c r="K63" s="35"/>
+      <c r="C63" s="38"/>
+      <c r="D63" s="38"/>
+      <c r="E63" s="38"/>
+      <c r="F63" s="38"/>
+      <c r="G63" s="38"/>
+      <c r="H63" s="38"/>
+      <c r="I63" s="38"/>
+      <c r="J63" s="38"/>
+      <c r="K63" s="38"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="35"/>
-      <c r="D64" s="35"/>
-      <c r="E64" s="35"/>
-      <c r="F64" s="35"/>
-      <c r="G64" s="35"/>
-      <c r="H64" s="35"/>
-      <c r="I64" s="35"/>
-      <c r="J64" s="35"/>
-      <c r="K64" s="35"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="38"/>
+      <c r="E64" s="38"/>
+      <c r="F64" s="38"/>
+      <c r="G64" s="38"/>
+      <c r="H64" s="38"/>
+      <c r="I64" s="38"/>
+      <c r="J64" s="38"/>
+      <c r="K64" s="38"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="35"/>
-      <c r="D65" s="35"/>
-      <c r="E65" s="35"/>
-      <c r="F65" s="35"/>
-      <c r="G65" s="35"/>
-      <c r="H65" s="35"/>
-      <c r="I65" s="35"/>
-      <c r="J65" s="35"/>
-      <c r="K65" s="35"/>
+      <c r="C65" s="38"/>
+      <c r="D65" s="38"/>
+      <c r="E65" s="38"/>
+      <c r="F65" s="38"/>
+      <c r="G65" s="38"/>
+      <c r="H65" s="38"/>
+      <c r="I65" s="38"/>
+      <c r="J65" s="38"/>
+      <c r="K65" s="38"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="35"/>
-      <c r="D66" s="35"/>
-      <c r="E66" s="35"/>
-      <c r="F66" s="35"/>
-      <c r="G66" s="35"/>
-      <c r="H66" s="35"/>
-      <c r="I66" s="35"/>
-      <c r="J66" s="35"/>
-      <c r="K66" s="35"/>
+      <c r="C66" s="38"/>
+      <c r="D66" s="38"/>
+      <c r="E66" s="38"/>
+      <c r="F66" s="38"/>
+      <c r="G66" s="38"/>
+      <c r="H66" s="38"/>
+      <c r="I66" s="38"/>
+      <c r="J66" s="38"/>
+      <c r="K66" s="38"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="35"/>
-      <c r="D67" s="35"/>
-      <c r="E67" s="35"/>
-      <c r="F67" s="35"/>
-      <c r="G67" s="35"/>
-      <c r="H67" s="35"/>
-      <c r="I67" s="35"/>
-      <c r="J67" s="35"/>
-      <c r="K67" s="35"/>
+      <c r="C67" s="38"/>
+      <c r="D67" s="38"/>
+      <c r="E67" s="38"/>
+      <c r="F67" s="38"/>
+      <c r="G67" s="38"/>
+      <c r="H67" s="38"/>
+      <c r="I67" s="38"/>
+      <c r="J67" s="38"/>
+      <c r="K67" s="38"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="35"/>
-      <c r="D68" s="35"/>
-      <c r="E68" s="35"/>
-      <c r="F68" s="35"/>
-      <c r="G68" s="35"/>
-      <c r="H68" s="35"/>
-      <c r="I68" s="35"/>
-      <c r="J68" s="35"/>
-      <c r="K68" s="35"/>
+      <c r="C68" s="38"/>
+      <c r="D68" s="38"/>
+      <c r="E68" s="38"/>
+      <c r="F68" s="38"/>
+      <c r="G68" s="38"/>
+      <c r="H68" s="38"/>
+      <c r="I68" s="38"/>
+      <c r="J68" s="38"/>
+      <c r="K68" s="38"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="35"/>
-      <c r="D69" s="35"/>
-      <c r="E69" s="35"/>
-      <c r="F69" s="35"/>
-      <c r="G69" s="35"/>
-      <c r="H69" s="35"/>
-      <c r="I69" s="35"/>
-      <c r="J69" s="35"/>
-      <c r="K69" s="35"/>
+      <c r="C69" s="38"/>
+      <c r="D69" s="38"/>
+      <c r="E69" s="38"/>
+      <c r="F69" s="38"/>
+      <c r="G69" s="38"/>
+      <c r="H69" s="38"/>
+      <c r="I69" s="38"/>
+      <c r="J69" s="38"/>
+      <c r="K69" s="38"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="35"/>
-      <c r="D70" s="35"/>
-      <c r="E70" s="35"/>
-      <c r="F70" s="35"/>
-      <c r="G70" s="35"/>
-      <c r="H70" s="35"/>
-      <c r="I70" s="35"/>
-      <c r="J70" s="35"/>
-      <c r="K70" s="35"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="38"/>
+      <c r="H70" s="38"/>
+      <c r="I70" s="38"/>
+      <c r="J70" s="38"/>
+      <c r="K70" s="38"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="35"/>
-      <c r="D71" s="35"/>
-      <c r="E71" s="35"/>
-      <c r="F71" s="35"/>
-      <c r="G71" s="35"/>
-      <c r="H71" s="35"/>
-      <c r="I71" s="35"/>
-      <c r="J71" s="35"/>
-      <c r="K71" s="35"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="38"/>
+      <c r="E71" s="38"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="38"/>
+      <c r="H71" s="38"/>
+      <c r="I71" s="38"/>
+      <c r="J71" s="38"/>
+      <c r="K71" s="38"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="35"/>
-      <c r="D72" s="35"/>
-      <c r="E72" s="35"/>
-      <c r="F72" s="35"/>
-      <c r="G72" s="35"/>
-      <c r="H72" s="35"/>
-      <c r="I72" s="35"/>
-      <c r="J72" s="35"/>
-      <c r="K72" s="35"/>
+      <c r="C72" s="38"/>
+      <c r="D72" s="38"/>
+      <c r="E72" s="38"/>
+      <c r="F72" s="38"/>
+      <c r="G72" s="38"/>
+      <c r="H72" s="38"/>
+      <c r="I72" s="38"/>
+      <c r="J72" s="38"/>
+      <c r="K72" s="38"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="35"/>
-      <c r="D73" s="35"/>
-      <c r="E73" s="35"/>
-      <c r="F73" s="35"/>
-      <c r="G73" s="35"/>
-      <c r="H73" s="35"/>
-      <c r="I73" s="35"/>
-      <c r="J73" s="35"/>
-      <c r="K73" s="35"/>
+      <c r="C73" s="38"/>
+      <c r="D73" s="38"/>
+      <c r="E73" s="38"/>
+      <c r="F73" s="38"/>
+      <c r="G73" s="38"/>
+      <c r="H73" s="38"/>
+      <c r="I73" s="38"/>
+      <c r="J73" s="38"/>
+      <c r="K73" s="38"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="35"/>
-      <c r="D74" s="35"/>
-      <c r="E74" s="35"/>
-      <c r="F74" s="35"/>
-      <c r="G74" s="35"/>
-      <c r="H74" s="35"/>
-      <c r="I74" s="35"/>
-      <c r="J74" s="35"/>
-      <c r="K74" s="35"/>
+      <c r="C74" s="38"/>
+      <c r="D74" s="38"/>
+      <c r="E74" s="38"/>
+      <c r="F74" s="38"/>
+      <c r="G74" s="38"/>
+      <c r="H74" s="38"/>
+      <c r="I74" s="38"/>
+      <c r="J74" s="38"/>
+      <c r="K74" s="38"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="35"/>
-      <c r="D75" s="35"/>
-      <c r="E75" s="35"/>
-      <c r="F75" s="35"/>
-      <c r="G75" s="35"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
-      <c r="J75" s="35"/>
-      <c r="K75" s="35"/>
+      <c r="C75" s="38"/>
+      <c r="D75" s="38"/>
+      <c r="E75" s="38"/>
+      <c r="F75" s="38"/>
+      <c r="G75" s="38"/>
+      <c r="H75" s="38"/>
+      <c r="I75" s="38"/>
+      <c r="J75" s="38"/>
+      <c r="K75" s="38"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="35"/>
-      <c r="D76" s="35"/>
-      <c r="E76" s="35"/>
-      <c r="F76" s="35"/>
-      <c r="G76" s="35"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
-      <c r="J76" s="35"/>
-      <c r="K76" s="35"/>
+      <c r="C76" s="38"/>
+      <c r="D76" s="38"/>
+      <c r="E76" s="38"/>
+      <c r="F76" s="38"/>
+      <c r="G76" s="38"/>
+      <c r="H76" s="38"/>
+      <c r="I76" s="38"/>
+      <c r="J76" s="38"/>
+      <c r="K76" s="38"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="35"/>
-      <c r="D77" s="35"/>
-      <c r="E77" s="35"/>
-      <c r="F77" s="35"/>
-      <c r="G77" s="35"/>
-      <c r="H77" s="35"/>
-      <c r="I77" s="35"/>
-      <c r="J77" s="35"/>
-      <c r="K77" s="35"/>
+      <c r="C77" s="38"/>
+      <c r="D77" s="38"/>
+      <c r="E77" s="38"/>
+      <c r="F77" s="38"/>
+      <c r="G77" s="38"/>
+      <c r="H77" s="38"/>
+      <c r="I77" s="38"/>
+      <c r="J77" s="38"/>
+      <c r="K77" s="38"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="35"/>
-      <c r="D78" s="35"/>
-      <c r="E78" s="35"/>
-      <c r="F78" s="35"/>
-      <c r="G78" s="35"/>
-      <c r="H78" s="35"/>
-      <c r="I78" s="35"/>
-      <c r="J78" s="35"/>
-      <c r="K78" s="35"/>
+      <c r="C78" s="38"/>
+      <c r="D78" s="38"/>
+      <c r="E78" s="38"/>
+      <c r="F78" s="38"/>
+      <c r="G78" s="38"/>
+      <c r="H78" s="38"/>
+      <c r="I78" s="38"/>
+      <c r="J78" s="38"/>
+      <c r="K78" s="38"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="35"/>
-      <c r="D79" s="35"/>
-      <c r="E79" s="35"/>
-      <c r="F79" s="35"/>
-      <c r="G79" s="35"/>
-      <c r="H79" s="35"/>
-      <c r="I79" s="35"/>
-      <c r="J79" s="35"/>
-      <c r="K79" s="35"/>
+      <c r="C79" s="38"/>
+      <c r="D79" s="38"/>
+      <c r="E79" s="38"/>
+      <c r="F79" s="38"/>
+      <c r="G79" s="38"/>
+      <c r="H79" s="38"/>
+      <c r="I79" s="38"/>
+      <c r="J79" s="38"/>
+      <c r="K79" s="38"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="35"/>
-      <c r="D80" s="35"/>
-      <c r="E80" s="35"/>
-      <c r="F80" s="35"/>
-      <c r="G80" s="35"/>
-      <c r="H80" s="35"/>
-      <c r="I80" s="35"/>
-      <c r="J80" s="35"/>
-      <c r="K80" s="35"/>
+      <c r="C80" s="38"/>
+      <c r="D80" s="38"/>
+      <c r="E80" s="38"/>
+      <c r="F80" s="38"/>
+      <c r="G80" s="38"/>
+      <c r="H80" s="38"/>
+      <c r="I80" s="38"/>
+      <c r="J80" s="38"/>
+      <c r="K80" s="38"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="35"/>
-      <c r="D81" s="35"/>
-      <c r="E81" s="35"/>
-      <c r="F81" s="35"/>
-      <c r="G81" s="35"/>
-      <c r="H81" s="35"/>
-      <c r="I81" s="35"/>
-      <c r="J81" s="35"/>
-      <c r="K81" s="35"/>
+      <c r="C81" s="38"/>
+      <c r="D81" s="38"/>
+      <c r="E81" s="38"/>
+      <c r="F81" s="38"/>
+      <c r="G81" s="38"/>
+      <c r="H81" s="38"/>
+      <c r="I81" s="38"/>
+      <c r="J81" s="38"/>
+      <c r="K81" s="38"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="35"/>
-      <c r="D82" s="35"/>
-      <c r="E82" s="35"/>
-      <c r="F82" s="35"/>
-      <c r="G82" s="35"/>
-      <c r="H82" s="35"/>
-      <c r="I82" s="35"/>
-      <c r="J82" s="35"/>
-      <c r="K82" s="35"/>
+      <c r="C82" s="38"/>
+      <c r="D82" s="38"/>
+      <c r="E82" s="38"/>
+      <c r="F82" s="38"/>
+      <c r="G82" s="38"/>
+      <c r="H82" s="38"/>
+      <c r="I82" s="38"/>
+      <c r="J82" s="38"/>
+      <c r="K82" s="38"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="35"/>
-      <c r="D83" s="35"/>
-      <c r="E83" s="35"/>
-      <c r="F83" s="35"/>
-      <c r="G83" s="35"/>
-      <c r="H83" s="35"/>
-      <c r="I83" s="35"/>
-      <c r="J83" s="35"/>
-      <c r="K83" s="35"/>
+      <c r="C83" s="38"/>
+      <c r="D83" s="38"/>
+      <c r="E83" s="38"/>
+      <c r="F83" s="38"/>
+      <c r="G83" s="38"/>
+      <c r="H83" s="38"/>
+      <c r="I83" s="38"/>
+      <c r="J83" s="38"/>
+      <c r="K83" s="38"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="35" t="s">
+      <c r="C84" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="D84" s="35">
-        <v>1</v>
-      </c>
-      <c r="E84" s="35"/>
-      <c r="F84" s="35"/>
-      <c r="G84" s="35"/>
-      <c r="H84" s="35"/>
-      <c r="I84" s="35"/>
-      <c r="J84" s="35"/>
-      <c r="K84" s="35"/>
+      <c r="D84" s="38">
+        <v>1</v>
+      </c>
+      <c r="E84" s="38"/>
+      <c r="F84" s="38"/>
+      <c r="G84" s="38"/>
+      <c r="H84" s="38"/>
+      <c r="I84" s="38"/>
+      <c r="J84" s="38"/>
+      <c r="K84" s="38"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="35"/>
-      <c r="D85" s="35"/>
-      <c r="E85" s="35"/>
-      <c r="F85" s="35"/>
-      <c r="G85" s="35"/>
-      <c r="H85" s="35"/>
-      <c r="I85" s="35"/>
-      <c r="J85" s="35"/>
-      <c r="K85" s="35"/>
+      <c r="C85" s="38"/>
+      <c r="D85" s="38"/>
+      <c r="E85" s="38"/>
+      <c r="F85" s="38"/>
+      <c r="G85" s="38"/>
+      <c r="H85" s="38"/>
+      <c r="I85" s="38"/>
+      <c r="J85" s="38"/>
+      <c r="K85" s="38"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4193,17 +4160,17 @@
         <v>1</v>
       </c>
       <c r="K37" s="18">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="L37" s="18">
         <v>0.01</v>
       </c>
       <c r="M37" s="18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N37" s="15"/>
     </row>
-    <row r="38" ht="16" spans="4:14">
+    <row r="38" spans="4:14">
       <c r="D38" s="18" t="s">
         <v>126</v>
       </c>
@@ -4224,215 +4191,145 @@
         <v>1</v>
       </c>
       <c r="K38" s="18">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="L38" s="18">
-        <f t="shared" ref="L38:L43" si="3">L37</f>
         <v>0.01</v>
       </c>
       <c r="M38" s="18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N38" s="15"/>
     </row>
     <row r="39" ht="16" spans="4:14">
-      <c r="D39" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="E39" s="18"/>
-      <c r="F39" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="G39" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="H39" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="I39" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="J39" s="18">
-        <v>1</v>
-      </c>
-      <c r="K39" s="18">
-        <v>1</v>
-      </c>
-      <c r="L39" s="18">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
-      </c>
-      <c r="M39" s="18">
-        <v>1</v>
-      </c>
-      <c r="N39" s="15"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="21"/>
+      <c r="K39" s="21"/>
+      <c r="L39" s="21"/>
+      <c r="M39" s="21"/>
+      <c r="N39" s="23"/>
     </row>
     <row r="40" ht="16" spans="4:14">
-      <c r="D40" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="E40" s="18"/>
-      <c r="F40" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="H40" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="I40" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="J40" s="18">
-        <v>1</v>
-      </c>
-      <c r="K40" s="18">
-        <f>K39</f>
-        <v>1</v>
-      </c>
-      <c r="L40" s="18">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
-      </c>
-      <c r="M40" s="18">
-        <v>1</v>
-      </c>
-      <c r="N40" s="15"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="21"/>
+      <c r="K40" s="21"/>
+      <c r="L40" s="21"/>
+      <c r="M40" s="21"/>
+      <c r="N40" s="23"/>
     </row>
     <row r="41" ht="16" spans="4:14">
-      <c r="D41" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="E41" s="18"/>
-      <c r="F41" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="G41" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="H41" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="I41" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="J41" s="18">
-        <v>1</v>
-      </c>
-      <c r="K41" s="18">
-        <f>K40</f>
-        <v>1</v>
-      </c>
-      <c r="L41" s="18">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
-      </c>
-      <c r="M41" s="18">
-        <v>1</v>
-      </c>
-      <c r="N41" s="15"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="21"/>
+      <c r="K41" s="21"/>
+      <c r="L41" s="21"/>
+      <c r="M41" s="21"/>
+      <c r="N41" s="23"/>
     </row>
     <row r="42" ht="16" spans="4:14">
-      <c r="D42" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="E42" s="18"/>
-      <c r="F42" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="G42" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="H42" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="I42" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="J42" s="18">
-        <v>1</v>
-      </c>
-      <c r="K42" s="18">
-        <f>K41</f>
-        <v>1</v>
-      </c>
-      <c r="L42" s="18">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
-      </c>
-      <c r="M42" s="18">
-        <v>1</v>
-      </c>
-      <c r="N42" s="15"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="21"/>
+      <c r="K42" s="21"/>
+      <c r="L42" s="21"/>
+      <c r="M42" s="21"/>
+      <c r="N42" s="23"/>
     </row>
     <row r="43" ht="16" spans="4:14">
-      <c r="D43" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="E43" s="18"/>
-      <c r="F43" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="G43" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="H43" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="I43" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="J43" s="18">
-        <v>1</v>
-      </c>
-      <c r="K43" s="18">
-        <f>K42</f>
-        <v>1</v>
-      </c>
-      <c r="L43" s="18">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
-      </c>
-      <c r="M43" s="18">
-        <v>1</v>
-      </c>
-      <c r="N43" s="15"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="21"/>
+      <c r="K43" s="21"/>
+      <c r="L43" s="21"/>
+      <c r="M43" s="21"/>
+      <c r="N43" s="23"/>
     </row>
     <row r="44" spans="4:14">
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="18"/>
-      <c r="K44" s="18"/>
-      <c r="L44" s="18"/>
-      <c r="M44" s="18"/>
-      <c r="N44" s="15"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="25"/>
+      <c r="H44" s="25"/>
+      <c r="I44" s="25"/>
+      <c r="J44" s="25"/>
+      <c r="K44" s="25"/>
+      <c r="L44" s="25"/>
+      <c r="M44" s="25"/>
+      <c r="N44" s="23"/>
     </row>
     <row r="45" spans="4:14">
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="22"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="18"/>
-      <c r="J45" s="18"/>
-      <c r="K45" s="18"/>
-      <c r="L45" s="18"/>
-      <c r="M45" s="18"/>
-      <c r="N45" s="15"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="21"/>
+      <c r="K45" s="21"/>
+      <c r="L45" s="21"/>
+      <c r="M45" s="21"/>
+      <c r="N45" s="23"/>
     </row>
     <row r="46" spans="4:14">
-      <c r="N46" s="15"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
+      <c r="H46" s="25"/>
+      <c r="I46" s="25"/>
+      <c r="J46" s="25"/>
+      <c r="K46" s="25"/>
+      <c r="L46" s="25"/>
+      <c r="M46" s="25"/>
+      <c r="N46" s="23"/>
     </row>
     <row r="47" spans="4:14">
-      <c r="N47" s="15"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="25"/>
+      <c r="J47" s="25"/>
+      <c r="K47" s="25"/>
+      <c r="L47" s="25"/>
+      <c r="M47" s="25"/>
+      <c r="N47" s="23"/>
     </row>
     <row r="48" spans="4:14">
-      <c r="N48" s="15"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="25"/>
+      <c r="I48" s="25"/>
+      <c r="J48" s="25"/>
+      <c r="K48" s="25"/>
+      <c r="L48" s="25"/>
+      <c r="M48" s="25"/>
+      <c r="N48" s="23"/>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" s="15"/>
@@ -4446,7 +4343,7 @@
     <row r="52" spans="4:14">
       <c r="D52" s="15"/>
       <c r="E52" s="15"/>
-      <c r="F52" s="23"/>
+      <c r="F52" s="27"/>
       <c r="G52" s="15"/>
       <c r="H52" s="15"/>
       <c r="I52" s="15"/>
@@ -4525,7 +4422,7 @@
     <row r="12" spans="6:18">
       <c r="K12" s="1"/>
       <c r="L12" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -4575,10 +4472,10 @@
     </row>
     <row r="14" spans="6:18">
       <c r="F14" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="H14" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -4597,7 +4494,7 @@
     </row>
     <row r="15" spans="6:18">
       <c r="H15" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -4713,7 +4610,7 @@
     <row r="26" spans="6:18">
       <c r="K26" s="1"/>
       <c r="L26" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -4763,10 +4660,10 @@
     </row>
     <row r="28" ht="16" spans="6:18">
       <c r="F28" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -4785,7 +4682,7 @@
     </row>
     <row r="29" spans="6:18">
       <c r="H29" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -4851,7 +4748,7 @@
     <row r="35" spans="6:18">
       <c r="K35" s="1"/>
       <c r="L35" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
@@ -4899,10 +4796,10 @@
     </row>
     <row r="37" spans="6:18">
       <c r="F37" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="H37" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -4920,7 +4817,7 @@
     </row>
     <row r="38" spans="6:18">
       <c r="H38" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -4936,7 +4833,7 @@
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="4" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
@@ -4974,13 +4871,13 @@
         <v>59</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>4</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>25</v>
@@ -5032,7 +4929,7 @@
     <row r="53" ht="16" spans="6:44">
       <c r="F53" s="8"/>
       <c r="G53" s="3" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>110</v>
@@ -5045,13 +4942,13 @@
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="M53" s="11" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="O53" s="3">
         <v>10</v>
@@ -5121,7 +5018,7 @@
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="4" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
@@ -5137,13 +5034,13 @@
         <v>59</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="I62" s="7" t="s">
         <v>4</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>25</v>
@@ -5169,7 +5066,7 @@
     </row>
     <row r="63" ht="16" spans="6:44">
       <c r="G63" s="3" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>110</v>
@@ -5182,13 +5079,13 @@
       </c>
       <c r="K63" s="3"/>
       <c r="L63" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="M63" s="11" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="O63" s="3">
         <v>10</v>
@@ -5266,7 +5163,7 @@
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
       <c r="I70" s="4" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="J70" s="5"/>
       <c r="K70" s="5"/>
@@ -5283,13 +5180,13 @@
         <v>59</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="I71" s="7" t="s">
         <v>4</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="K71" s="3" t="s">
         <v>25</v>
@@ -5315,7 +5212,7 @@
     </row>
     <row r="72" ht="16" spans="7:20">
       <c r="G72" s="3" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>110</v>
@@ -5328,13 +5225,13 @@
       </c>
       <c r="K72" s="3"/>
       <c r="L72" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="M72" s="11" t="s">
         <v>39</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="O72" s="3">
         <v>10</v>
@@ -5357,7 +5254,7 @@
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
       <c r="I80" s="4" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="J80" s="5"/>
       <c r="K80" s="5"/>
@@ -5373,13 +5270,13 @@
         <v>59</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="I81" s="7" t="s">
         <v>4</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>25</v>
@@ -5405,7 +5302,7 @@
     </row>
     <row r="82" ht="16" spans="7:17">
       <c r="G82" s="3" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>110</v>
@@ -5418,13 +5315,13 @@
       </c>
       <c r="K82" s="3"/>
       <c r="L82" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="M82" s="11" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="O82" s="3">
         <v>10</v>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="6"/>
+    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
@@ -936,7 +936,7 @@
       <charset val="0"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -951,6 +951,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -958,12 +970,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1301,7 +1307,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1325,16 +1331,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1343,93 +1349,93 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1447,6 +1453,21 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1455,35 +1476,31 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="53">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2017,7 +2034,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="44">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -2131,10 +2148,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="39"/>
+      <c r="K10" s="13"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="39"/>
+      <c r="K11" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2155,12 +2172,12 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:13">
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="15"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="26"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
@@ -2175,19 +2192,19 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="29"/>
+      <c r="K6" s="37"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="38">
         <v>10</v>
       </c>
     </row>
@@ -2195,17 +2212,17 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="38">
         <v>7</v>
       </c>
-      <c r="L8" s="28"/>
-      <c r="M8" s="28"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="36"/>
     </row>
     <row r="9" ht="16" spans="2:13">
       <c r="B9" t="s">
@@ -2214,10 +2231,10 @@
       <c r="C9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="D9" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="38">
         <v>10</v>
       </c>
     </row>
@@ -2225,17 +2242,17 @@
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="38">
         <v>8</v>
       </c>
-      <c r="K10" s="31"/>
-      <c r="L10" s="32"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="40"/>
     </row>
     <row r="11" ht="16" spans="2:13">
       <c r="B11" t="s">
@@ -2244,10 +2261,10 @@
       <c r="C11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="36">
         <v>1.5</v>
       </c>
     </row>
@@ -2258,10 +2275,10 @@
       <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="36">
         <v>1.5</v>
       </c>
     </row>
@@ -2269,13 +2286,13 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="26">
         <v>2</v>
       </c>
     </row>
@@ -2283,13 +2300,13 @@
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2297,13 +2314,13 @@
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2311,13 +2328,13 @@
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="28" t="s">
+      <c r="D16" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="41">
         <v>12</v>
       </c>
     </row>
@@ -2325,31 +2342,31 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="34" t="s">
+      <c r="D17" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="43">
         <v>0.2</v>
       </c>
-      <c r="F17" s="15"/>
+      <c r="F17" s="26"/>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="34" t="s">
+      <c r="D18" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="35">
+      <c r="E18" s="43">
         <v>0.2</v>
       </c>
-      <c r="F18" s="15"/>
+      <c r="F18" s="26"/>
     </row>
     <row r="19" ht="16" spans="2:6">
       <c r="B19" t="s">
@@ -2358,28 +2375,28 @@
       <c r="C19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="34" t="s">
+      <c r="D19" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="35">
+      <c r="E19" s="43">
         <v>0.2</v>
       </c>
-      <c r="F19" s="15"/>
+      <c r="F19" s="26"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="34" t="s">
+      <c r="D20" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="35">
+      <c r="E20" s="43">
         <v>0.5</v>
       </c>
-      <c r="F20" s="15"/>
+      <c r="F20" s="26"/>
     </row>
     <row r="21" ht="16" spans="2:6">
       <c r="B21" t="s">
@@ -2388,13 +2405,13 @@
       <c r="C21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="34" t="s">
+      <c r="D21" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="35">
+      <c r="E21" s="43">
         <v>0.8</v>
       </c>
-      <c r="F21" s="15"/>
+      <c r="F21" s="26"/>
     </row>
     <row r="22" ht="16" spans="2:6">
       <c r="B22" t="s">
@@ -2403,122 +2420,122 @@
       <c r="C22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="34" t="s">
+      <c r="D22" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="28"/>
-      <c r="F22" s="15"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="26"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="34" t="s">
+      <c r="D23" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="15">
-        <v>1</v>
-      </c>
-      <c r="F23" s="15"/>
+      <c r="E23" s="26">
+        <v>1</v>
+      </c>
+      <c r="F23" s="26"/>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="34" t="s">
+      <c r="D24" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="15">
-        <v>1</v>
-      </c>
-      <c r="F24" s="15"/>
+      <c r="E24" s="26">
+        <v>1</v>
+      </c>
+      <c r="F24" s="26"/>
     </row>
     <row r="25" ht="16" spans="2:6">
       <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="34" t="s">
+      <c r="D25" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="15">
-        <v>1</v>
-      </c>
-      <c r="F25" s="15"/>
+      <c r="E25" s="26">
+        <v>1</v>
+      </c>
+      <c r="F25" s="26"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="34" t="s">
+      <c r="D26" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="28">
+      <c r="E26" s="36">
         <v>0.05</v>
       </c>
-      <c r="F26" s="15"/>
+      <c r="F26" s="26"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="37" t="s">
+      <c r="C27" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="37" t="s">
+      <c r="D27" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="37">
+      <c r="E27" s="45">
         <v>2020</v>
       </c>
-      <c r="F27" s="15"/>
+      <c r="F27" s="26"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="37" t="s">
+      <c r="D28" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="29">
         <v>2020</v>
       </c>
-      <c r="F28" s="15"/>
+      <c r="F28" s="26"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
     </row>
     <row r="38" spans="3:5">
       <c r="C38" s="1"/>
@@ -2526,360 +2543,360 @@
       <c r="E38" s="1"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="38" t="s">
+      <c r="C54" s="46" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="38"/>
-      <c r="E56" s="38"/>
-      <c r="F56" s="38"/>
-      <c r="G56" s="38"/>
-      <c r="H56" s="38"/>
-      <c r="I56" s="38"/>
-      <c r="J56" s="38"/>
-      <c r="K56" s="38"/>
+      <c r="D56" s="46"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="46"/>
+      <c r="G56" s="46"/>
+      <c r="H56" s="46"/>
+      <c r="I56" s="46"/>
+      <c r="J56" s="46"/>
+      <c r="K56" s="46"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="38" t="s">
+      <c r="C57" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="38" t="s">
+      <c r="D57" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="38" t="s">
+      <c r="E57" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="F57" s="38" t="s">
+      <c r="F57" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="G57" s="38" t="s">
+      <c r="G57" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="38" t="s">
+      <c r="H57" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="38" t="s">
+      <c r="I57" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="J57" s="38" t="s">
+      <c r="J57" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="K57" s="38" t="s">
+      <c r="K57" s="46" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="38"/>
-      <c r="D58" s="38"/>
-      <c r="E58" s="38"/>
-      <c r="F58" s="38"/>
-      <c r="G58" s="38"/>
-      <c r="H58" s="38"/>
-      <c r="I58" s="38"/>
-      <c r="J58" s="38"/>
-      <c r="K58" s="38"/>
+      <c r="C58" s="46"/>
+      <c r="D58" s="46"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="46"/>
+      <c r="G58" s="46"/>
+      <c r="H58" s="46"/>
+      <c r="I58" s="46"/>
+      <c r="J58" s="46"/>
+      <c r="K58" s="46"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="38"/>
-      <c r="D59" s="38"/>
-      <c r="E59" s="38"/>
-      <c r="F59" s="38"/>
-      <c r="G59" s="38"/>
-      <c r="H59" s="38"/>
-      <c r="I59" s="38"/>
-      <c r="J59" s="38"/>
-      <c r="K59" s="38"/>
+      <c r="C59" s="46"/>
+      <c r="D59" s="46"/>
+      <c r="E59" s="46"/>
+      <c r="F59" s="46"/>
+      <c r="G59" s="46"/>
+      <c r="H59" s="46"/>
+      <c r="I59" s="46"/>
+      <c r="J59" s="46"/>
+      <c r="K59" s="46"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="38"/>
-      <c r="D60" s="38"/>
-      <c r="E60" s="38"/>
-      <c r="F60" s="38"/>
-      <c r="G60" s="38"/>
-      <c r="H60" s="38"/>
-      <c r="I60" s="38"/>
-      <c r="J60" s="38"/>
-      <c r="K60" s="38"/>
+      <c r="C60" s="46"/>
+      <c r="D60" s="46"/>
+      <c r="E60" s="46"/>
+      <c r="F60" s="46"/>
+      <c r="G60" s="46"/>
+      <c r="H60" s="46"/>
+      <c r="I60" s="46"/>
+      <c r="J60" s="46"/>
+      <c r="K60" s="46"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="38"/>
-      <c r="D61" s="38"/>
-      <c r="E61" s="38"/>
-      <c r="F61" s="38"/>
-      <c r="G61" s="38"/>
-      <c r="H61" s="38"/>
-      <c r="I61" s="38"/>
-      <c r="J61" s="38"/>
-      <c r="K61" s="38"/>
+      <c r="C61" s="46"/>
+      <c r="D61" s="46"/>
+      <c r="E61" s="46"/>
+      <c r="F61" s="46"/>
+      <c r="G61" s="46"/>
+      <c r="H61" s="46"/>
+      <c r="I61" s="46"/>
+      <c r="J61" s="46"/>
+      <c r="K61" s="46"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="38"/>
-      <c r="D62" s="38"/>
-      <c r="E62" s="38"/>
-      <c r="F62" s="38"/>
-      <c r="G62" s="38"/>
-      <c r="H62" s="38"/>
-      <c r="I62" s="38"/>
-      <c r="J62" s="38"/>
-      <c r="K62" s="38"/>
+      <c r="C62" s="46"/>
+      <c r="D62" s="46"/>
+      <c r="E62" s="46"/>
+      <c r="F62" s="46"/>
+      <c r="G62" s="46"/>
+      <c r="H62" s="46"/>
+      <c r="I62" s="46"/>
+      <c r="J62" s="46"/>
+      <c r="K62" s="46"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="38"/>
-      <c r="D63" s="38"/>
-      <c r="E63" s="38"/>
-      <c r="F63" s="38"/>
-      <c r="G63" s="38"/>
-      <c r="H63" s="38"/>
-      <c r="I63" s="38"/>
-      <c r="J63" s="38"/>
-      <c r="K63" s="38"/>
+      <c r="C63" s="46"/>
+      <c r="D63" s="46"/>
+      <c r="E63" s="46"/>
+      <c r="F63" s="46"/>
+      <c r="G63" s="46"/>
+      <c r="H63" s="46"/>
+      <c r="I63" s="46"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="46"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="38"/>
-      <c r="D64" s="38"/>
-      <c r="E64" s="38"/>
-      <c r="F64" s="38"/>
-      <c r="G64" s="38"/>
-      <c r="H64" s="38"/>
-      <c r="I64" s="38"/>
-      <c r="J64" s="38"/>
-      <c r="K64" s="38"/>
+      <c r="C64" s="46"/>
+      <c r="D64" s="46"/>
+      <c r="E64" s="46"/>
+      <c r="F64" s="46"/>
+      <c r="G64" s="46"/>
+      <c r="H64" s="46"/>
+      <c r="I64" s="46"/>
+      <c r="J64" s="46"/>
+      <c r="K64" s="46"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="38"/>
-      <c r="D65" s="38"/>
-      <c r="E65" s="38"/>
-      <c r="F65" s="38"/>
-      <c r="G65" s="38"/>
-      <c r="H65" s="38"/>
-      <c r="I65" s="38"/>
-      <c r="J65" s="38"/>
-      <c r="K65" s="38"/>
+      <c r="C65" s="46"/>
+      <c r="D65" s="46"/>
+      <c r="E65" s="46"/>
+      <c r="F65" s="46"/>
+      <c r="G65" s="46"/>
+      <c r="H65" s="46"/>
+      <c r="I65" s="46"/>
+      <c r="J65" s="46"/>
+      <c r="K65" s="46"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="38"/>
-      <c r="D66" s="38"/>
-      <c r="E66" s="38"/>
-      <c r="F66" s="38"/>
-      <c r="G66" s="38"/>
-      <c r="H66" s="38"/>
-      <c r="I66" s="38"/>
-      <c r="J66" s="38"/>
-      <c r="K66" s="38"/>
+      <c r="C66" s="46"/>
+      <c r="D66" s="46"/>
+      <c r="E66" s="46"/>
+      <c r="F66" s="46"/>
+      <c r="G66" s="46"/>
+      <c r="H66" s="46"/>
+      <c r="I66" s="46"/>
+      <c r="J66" s="46"/>
+      <c r="K66" s="46"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="38"/>
-      <c r="D67" s="38"/>
-      <c r="E67" s="38"/>
-      <c r="F67" s="38"/>
-      <c r="G67" s="38"/>
-      <c r="H67" s="38"/>
-      <c r="I67" s="38"/>
-      <c r="J67" s="38"/>
-      <c r="K67" s="38"/>
+      <c r="C67" s="46"/>
+      <c r="D67" s="46"/>
+      <c r="E67" s="46"/>
+      <c r="F67" s="46"/>
+      <c r="G67" s="46"/>
+      <c r="H67" s="46"/>
+      <c r="I67" s="46"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="46"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="38"/>
-      <c r="D68" s="38"/>
-      <c r="E68" s="38"/>
-      <c r="F68" s="38"/>
-      <c r="G68" s="38"/>
-      <c r="H68" s="38"/>
-      <c r="I68" s="38"/>
-      <c r="J68" s="38"/>
-      <c r="K68" s="38"/>
+      <c r="C68" s="46"/>
+      <c r="D68" s="46"/>
+      <c r="E68" s="46"/>
+      <c r="F68" s="46"/>
+      <c r="G68" s="46"/>
+      <c r="H68" s="46"/>
+      <c r="I68" s="46"/>
+      <c r="J68" s="46"/>
+      <c r="K68" s="46"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="38"/>
-      <c r="D69" s="38"/>
-      <c r="E69" s="38"/>
-      <c r="F69" s="38"/>
-      <c r="G69" s="38"/>
-      <c r="H69" s="38"/>
-      <c r="I69" s="38"/>
-      <c r="J69" s="38"/>
-      <c r="K69" s="38"/>
+      <c r="C69" s="46"/>
+      <c r="D69" s="46"/>
+      <c r="E69" s="46"/>
+      <c r="F69" s="46"/>
+      <c r="G69" s="46"/>
+      <c r="H69" s="46"/>
+      <c r="I69" s="46"/>
+      <c r="J69" s="46"/>
+      <c r="K69" s="46"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="38"/>
-      <c r="D70" s="38"/>
-      <c r="E70" s="38"/>
-      <c r="F70" s="38"/>
-      <c r="G70" s="38"/>
-      <c r="H70" s="38"/>
-      <c r="I70" s="38"/>
-      <c r="J70" s="38"/>
-      <c r="K70" s="38"/>
+      <c r="C70" s="46"/>
+      <c r="D70" s="46"/>
+      <c r="E70" s="46"/>
+      <c r="F70" s="46"/>
+      <c r="G70" s="46"/>
+      <c r="H70" s="46"/>
+      <c r="I70" s="46"/>
+      <c r="J70" s="46"/>
+      <c r="K70" s="46"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="38"/>
-      <c r="D71" s="38"/>
-      <c r="E71" s="38"/>
-      <c r="F71" s="38"/>
-      <c r="G71" s="38"/>
-      <c r="H71" s="38"/>
-      <c r="I71" s="38"/>
-      <c r="J71" s="38"/>
-      <c r="K71" s="38"/>
+      <c r="C71" s="46"/>
+      <c r="D71" s="46"/>
+      <c r="E71" s="46"/>
+      <c r="F71" s="46"/>
+      <c r="G71" s="46"/>
+      <c r="H71" s="46"/>
+      <c r="I71" s="46"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="46"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="38"/>
-      <c r="D72" s="38"/>
-      <c r="E72" s="38"/>
-      <c r="F72" s="38"/>
-      <c r="G72" s="38"/>
-      <c r="H72" s="38"/>
-      <c r="I72" s="38"/>
-      <c r="J72" s="38"/>
-      <c r="K72" s="38"/>
+      <c r="C72" s="46"/>
+      <c r="D72" s="46"/>
+      <c r="E72" s="46"/>
+      <c r="F72" s="46"/>
+      <c r="G72" s="46"/>
+      <c r="H72" s="46"/>
+      <c r="I72" s="46"/>
+      <c r="J72" s="46"/>
+      <c r="K72" s="46"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="38"/>
-      <c r="D73" s="38"/>
-      <c r="E73" s="38"/>
-      <c r="F73" s="38"/>
-      <c r="G73" s="38"/>
-      <c r="H73" s="38"/>
-      <c r="I73" s="38"/>
-      <c r="J73" s="38"/>
-      <c r="K73" s="38"/>
+      <c r="C73" s="46"/>
+      <c r="D73" s="46"/>
+      <c r="E73" s="46"/>
+      <c r="F73" s="46"/>
+      <c r="G73" s="46"/>
+      <c r="H73" s="46"/>
+      <c r="I73" s="46"/>
+      <c r="J73" s="46"/>
+      <c r="K73" s="46"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="38"/>
-      <c r="D74" s="38"/>
-      <c r="E74" s="38"/>
-      <c r="F74" s="38"/>
-      <c r="G74" s="38"/>
-      <c r="H74" s="38"/>
-      <c r="I74" s="38"/>
-      <c r="J74" s="38"/>
-      <c r="K74" s="38"/>
+      <c r="C74" s="46"/>
+      <c r="D74" s="46"/>
+      <c r="E74" s="46"/>
+      <c r="F74" s="46"/>
+      <c r="G74" s="46"/>
+      <c r="H74" s="46"/>
+      <c r="I74" s="46"/>
+      <c r="J74" s="46"/>
+      <c r="K74" s="46"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="38"/>
-      <c r="D75" s="38"/>
-      <c r="E75" s="38"/>
-      <c r="F75" s="38"/>
-      <c r="G75" s="38"/>
-      <c r="H75" s="38"/>
-      <c r="I75" s="38"/>
-      <c r="J75" s="38"/>
-      <c r="K75" s="38"/>
+      <c r="C75" s="46"/>
+      <c r="D75" s="46"/>
+      <c r="E75" s="46"/>
+      <c r="F75" s="46"/>
+      <c r="G75" s="46"/>
+      <c r="H75" s="46"/>
+      <c r="I75" s="46"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="46"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="38"/>
-      <c r="D76" s="38"/>
-      <c r="E76" s="38"/>
-      <c r="F76" s="38"/>
-      <c r="G76" s="38"/>
-      <c r="H76" s="38"/>
-      <c r="I76" s="38"/>
-      <c r="J76" s="38"/>
-      <c r="K76" s="38"/>
+      <c r="C76" s="46"/>
+      <c r="D76" s="46"/>
+      <c r="E76" s="46"/>
+      <c r="F76" s="46"/>
+      <c r="G76" s="46"/>
+      <c r="H76" s="46"/>
+      <c r="I76" s="46"/>
+      <c r="J76" s="46"/>
+      <c r="K76" s="46"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="38"/>
-      <c r="D77" s="38"/>
-      <c r="E77" s="38"/>
-      <c r="F77" s="38"/>
-      <c r="G77" s="38"/>
-      <c r="H77" s="38"/>
-      <c r="I77" s="38"/>
-      <c r="J77" s="38"/>
-      <c r="K77" s="38"/>
+      <c r="C77" s="46"/>
+      <c r="D77" s="46"/>
+      <c r="E77" s="46"/>
+      <c r="F77" s="46"/>
+      <c r="G77" s="46"/>
+      <c r="H77" s="46"/>
+      <c r="I77" s="46"/>
+      <c r="J77" s="46"/>
+      <c r="K77" s="46"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="38"/>
-      <c r="D78" s="38"/>
-      <c r="E78" s="38"/>
-      <c r="F78" s="38"/>
-      <c r="G78" s="38"/>
-      <c r="H78" s="38"/>
-      <c r="I78" s="38"/>
-      <c r="J78" s="38"/>
-      <c r="K78" s="38"/>
+      <c r="C78" s="46"/>
+      <c r="D78" s="46"/>
+      <c r="E78" s="46"/>
+      <c r="F78" s="46"/>
+      <c r="G78" s="46"/>
+      <c r="H78" s="46"/>
+      <c r="I78" s="46"/>
+      <c r="J78" s="46"/>
+      <c r="K78" s="46"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="38"/>
-      <c r="D79" s="38"/>
-      <c r="E79" s="38"/>
-      <c r="F79" s="38"/>
-      <c r="G79" s="38"/>
-      <c r="H79" s="38"/>
-      <c r="I79" s="38"/>
-      <c r="J79" s="38"/>
-      <c r="K79" s="38"/>
+      <c r="C79" s="46"/>
+      <c r="D79" s="46"/>
+      <c r="E79" s="46"/>
+      <c r="F79" s="46"/>
+      <c r="G79" s="46"/>
+      <c r="H79" s="46"/>
+      <c r="I79" s="46"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="46"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="38"/>
-      <c r="D80" s="38"/>
-      <c r="E80" s="38"/>
-      <c r="F80" s="38"/>
-      <c r="G80" s="38"/>
-      <c r="H80" s="38"/>
-      <c r="I80" s="38"/>
-      <c r="J80" s="38"/>
-      <c r="K80" s="38"/>
+      <c r="C80" s="46"/>
+      <c r="D80" s="46"/>
+      <c r="E80" s="46"/>
+      <c r="F80" s="46"/>
+      <c r="G80" s="46"/>
+      <c r="H80" s="46"/>
+      <c r="I80" s="46"/>
+      <c r="J80" s="46"/>
+      <c r="K80" s="46"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="38"/>
-      <c r="D81" s="38"/>
-      <c r="E81" s="38"/>
-      <c r="F81" s="38"/>
-      <c r="G81" s="38"/>
-      <c r="H81" s="38"/>
-      <c r="I81" s="38"/>
-      <c r="J81" s="38"/>
-      <c r="K81" s="38"/>
+      <c r="C81" s="46"/>
+      <c r="D81" s="46"/>
+      <c r="E81" s="46"/>
+      <c r="F81" s="46"/>
+      <c r="G81" s="46"/>
+      <c r="H81" s="46"/>
+      <c r="I81" s="46"/>
+      <c r="J81" s="46"/>
+      <c r="K81" s="46"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="38"/>
-      <c r="D82" s="38"/>
-      <c r="E82" s="38"/>
-      <c r="F82" s="38"/>
-      <c r="G82" s="38"/>
-      <c r="H82" s="38"/>
-      <c r="I82" s="38"/>
-      <c r="J82" s="38"/>
-      <c r="K82" s="38"/>
+      <c r="C82" s="46"/>
+      <c r="D82" s="46"/>
+      <c r="E82" s="46"/>
+      <c r="F82" s="46"/>
+      <c r="G82" s="46"/>
+      <c r="H82" s="46"/>
+      <c r="I82" s="46"/>
+      <c r="J82" s="46"/>
+      <c r="K82" s="46"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="38"/>
-      <c r="D83" s="38"/>
-      <c r="E83" s="38"/>
-      <c r="F83" s="38"/>
-      <c r="G83" s="38"/>
-      <c r="H83" s="38"/>
-      <c r="I83" s="38"/>
-      <c r="J83" s="38"/>
-      <c r="K83" s="38"/>
+      <c r="C83" s="46"/>
+      <c r="D83" s="46"/>
+      <c r="E83" s="46"/>
+      <c r="F83" s="46"/>
+      <c r="G83" s="46"/>
+      <c r="H83" s="46"/>
+      <c r="I83" s="46"/>
+      <c r="J83" s="46"/>
+      <c r="K83" s="46"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="38" t="s">
+      <c r="C84" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="D84" s="38">
-        <v>1</v>
-      </c>
-      <c r="E84" s="38"/>
-      <c r="F84" s="38"/>
-      <c r="G84" s="38"/>
-      <c r="H84" s="38"/>
-      <c r="I84" s="38"/>
-      <c r="J84" s="38"/>
-      <c r="K84" s="38"/>
+      <c r="D84" s="46">
+        <v>1</v>
+      </c>
+      <c r="E84" s="46"/>
+      <c r="F84" s="46"/>
+      <c r="G84" s="46"/>
+      <c r="H84" s="46"/>
+      <c r="I84" s="46"/>
+      <c r="J84" s="46"/>
+      <c r="K84" s="46"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="38"/>
-      <c r="D85" s="38"/>
-      <c r="E85" s="38"/>
-      <c r="F85" s="38"/>
-      <c r="G85" s="38"/>
-      <c r="H85" s="38"/>
-      <c r="I85" s="38"/>
-      <c r="J85" s="38"/>
-      <c r="K85" s="38"/>
+      <c r="C85" s="46"/>
+      <c r="D85" s="46"/>
+      <c r="E85" s="46"/>
+      <c r="F85" s="46"/>
+      <c r="G85" s="46"/>
+      <c r="H85" s="46"/>
+      <c r="I85" s="46"/>
+      <c r="J85" s="46"/>
+      <c r="K85" s="46"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3504,252 +3521,252 @@
       </c>
     </row>
     <row r="8" spans="2:14">
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="H8" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="K8" s="13" t="s">
+      <c r="K8" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="L8" s="13" t="s">
+      <c r="L8" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="M8" s="13" t="s">
+      <c r="M8" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="N8" s="13" t="s">
+      <c r="N8" s="24" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="9" spans="2:14">
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="25" t="s">
         <v>88</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="25">
         <v>1.25</v>
       </c>
       <c r="L9">
         <v>0.05</v>
       </c>
-      <c r="M9" s="14">
-        <v>1</v>
-      </c>
-      <c r="N9" s="14"/>
+      <c r="M9" s="25">
+        <v>1</v>
+      </c>
+      <c r="N9" s="25"/>
     </row>
     <row r="10" spans="2:14">
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="25" t="s">
         <v>88</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="25">
         <v>1.11</v>
       </c>
       <c r="L10">
         <v>0.05</v>
       </c>
-      <c r="M10" s="14">
-        <v>1</v>
-      </c>
-      <c r="N10" s="14"/>
+      <c r="M10" s="25">
+        <v>1</v>
+      </c>
+      <c r="N10" s="25"/>
     </row>
     <row r="11" spans="2:14">
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="25" t="s">
         <v>88</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="25">
         <v>1.15</v>
       </c>
       <c r="L11">
         <v>0.08</v>
       </c>
-      <c r="M11" s="14">
-        <v>1</v>
-      </c>
-      <c r="N11" s="14"/>
+      <c r="M11" s="25">
+        <v>1</v>
+      </c>
+      <c r="N11" s="25"/>
     </row>
     <row r="12" ht="16" spans="2:14">
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="25" t="s">
         <v>93</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="25" t="s">
         <v>88</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="25">
         <v>1.12</v>
       </c>
       <c r="L12">
         <v>0.03</v>
       </c>
-      <c r="M12" s="14">
-        <v>1</v>
-      </c>
-      <c r="N12" s="14"/>
+      <c r="M12" s="25">
+        <v>1</v>
+      </c>
+      <c r="N12" s="25"/>
     </row>
     <row r="13" spans="2:14">
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="H13" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="25" t="s">
         <v>88</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="25">
         <v>1.2</v>
       </c>
       <c r="L13">
         <v>0.1</v>
       </c>
-      <c r="M13" s="14">
-        <v>1</v>
-      </c>
-      <c r="N13" s="14"/>
+      <c r="M13" s="25">
+        <v>1</v>
+      </c>
+      <c r="N13" s="25"/>
     </row>
     <row r="14" spans="2:14">
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="H14" s="14" t="s">
+      <c r="H14" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="25" t="s">
         <v>88</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="25">
         <v>1.06</v>
       </c>
       <c r="L14">
         <v>0.15</v>
       </c>
-      <c r="M14" s="14">
-        <v>1</v>
-      </c>
-      <c r="N14" s="14"/>
+      <c r="M14" s="25">
+        <v>1</v>
+      </c>
+      <c r="N14" s="25"/>
     </row>
     <row r="15" spans="2:14">
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="H15" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="25" t="s">
         <v>88</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="25">
         <v>1.06</v>
       </c>
       <c r="L15">
         <v>0.3</v>
       </c>
-      <c r="M15" s="14">
-        <v>1</v>
-      </c>
-      <c r="N15" s="14"/>
+      <c r="M15" s="25">
+        <v>1</v>
+      </c>
+      <c r="N15" s="25"/>
     </row>
     <row r="16" ht="16" spans="2:14">
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="25" t="s">
         <v>101</v>
       </c>
       <c r="F16" s="2" t="s">
@@ -3763,7 +3780,7 @@
         <f>H15</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="25" t="s">
         <v>88</v>
       </c>
       <c r="J16">
@@ -3784,7 +3801,7 @@
       </c>
     </row>
     <row r="17" ht="16" spans="4:14">
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="25" t="s">
         <v>103</v>
       </c>
       <c r="F17" s="2" t="s">
@@ -3798,7 +3815,7 @@
         <f t="shared" si="1"/>
         <v>2025, 2150</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I17" s="25" t="s">
         <v>88</v>
       </c>
       <c r="J17">
@@ -3819,7 +3836,7 @@
       </c>
     </row>
     <row r="18" ht="16" spans="4:14">
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="25" t="s">
         <v>105</v>
       </c>
       <c r="F18" s="2" t="s">
@@ -3833,7 +3850,7 @@
         <f>H17</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I18" s="14" t="s">
+      <c r="I18" s="25" t="s">
         <v>88</v>
       </c>
       <c r="J18">
@@ -3850,534 +3867,534 @@
       </c>
     </row>
     <row r="27" spans="4:14">
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="26"/>
     </row>
     <row r="28" spans="4:14">
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15" t="s">
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
     </row>
     <row r="29" spans="4:14">
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="F29" s="15" t="s">
+      <c r="F29" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="15" t="s">
+      <c r="G29" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="H29" s="15" t="s">
+      <c r="H29" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="I29" s="15" t="s">
+      <c r="I29" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="J29" s="15" t="s">
+      <c r="J29" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="K29" s="15" t="s">
+      <c r="K29" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="L29" s="15" t="s">
+      <c r="L29" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="M29" s="15" t="s">
+      <c r="M29" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="N29" s="15" t="s">
+      <c r="N29" s="26" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="30" ht="16" spans="4:14">
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="15"/>
-      <c r="F30" s="16" t="s">
+      <c r="E30" s="26"/>
+      <c r="F30" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="G30" s="15" t="s">
+      <c r="G30" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="H30" s="15" t="s">
+      <c r="H30" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="I30" s="15" t="s">
+      <c r="I30" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="15">
-        <v>1</v>
-      </c>
-      <c r="K30" s="15">
-        <v>1</v>
-      </c>
-      <c r="L30" s="15">
+      <c r="J30" s="26">
+        <v>1</v>
+      </c>
+      <c r="K30" s="26">
+        <v>1</v>
+      </c>
+      <c r="L30" s="26">
         <v>0.01</v>
       </c>
-      <c r="M30" s="15">
-        <v>1</v>
-      </c>
-      <c r="N30" s="15"/>
+      <c r="M30" s="26">
+        <v>1</v>
+      </c>
+      <c r="N30" s="26"/>
     </row>
     <row r="31" ht="16" spans="4:14">
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="15"/>
-      <c r="F31" s="17" t="s">
+      <c r="E31" s="26"/>
+      <c r="F31" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="G31" s="15" t="s">
+      <c r="G31" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="H31" s="15" t="s">
+      <c r="H31" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="I31" s="15" t="s">
+      <c r="I31" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="J31" s="15">
-        <v>1</v>
-      </c>
-      <c r="K31" s="15">
-        <v>1</v>
-      </c>
-      <c r="L31" s="15">
+      <c r="J31" s="26">
+        <v>1</v>
+      </c>
+      <c r="K31" s="26">
+        <v>1</v>
+      </c>
+      <c r="L31" s="26">
         <f t="shared" ref="L31:L36" si="2">L30</f>
         <v>0.01</v>
       </c>
-      <c r="M31" s="15">
-        <v>1</v>
-      </c>
-      <c r="N31" s="15"/>
+      <c r="M31" s="26">
+        <v>1</v>
+      </c>
+      <c r="N31" s="26"/>
     </row>
     <row r="32" ht="16" spans="4:14">
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="E32" s="15"/>
-      <c r="F32" s="17" t="s">
+      <c r="E32" s="26"/>
+      <c r="F32" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="H32" s="15" t="s">
+      <c r="H32" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="I32" s="15" t="s">
+      <c r="I32" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="J32" s="15">
-        <v>1</v>
-      </c>
-      <c r="K32" s="15">
-        <v>1</v>
-      </c>
-      <c r="L32" s="15">
+      <c r="J32" s="26">
+        <v>1</v>
+      </c>
+      <c r="K32" s="26">
+        <v>1</v>
+      </c>
+      <c r="L32" s="26">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M32" s="15">
-        <v>1</v>
-      </c>
-      <c r="N32" s="15"/>
+      <c r="M32" s="26">
+        <v>1</v>
+      </c>
+      <c r="N32" s="26"/>
     </row>
     <row r="33" ht="16" spans="4:14">
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="15"/>
-      <c r="F33" s="16" t="s">
+      <c r="E33" s="26"/>
+      <c r="F33" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="G33" s="15" t="s">
+      <c r="G33" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="H33" s="15" t="s">
+      <c r="H33" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="I33" s="15" t="s">
+      <c r="I33" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="J33" s="15">
-        <v>1</v>
-      </c>
-      <c r="K33" s="15">
+      <c r="J33" s="26">
+        <v>1</v>
+      </c>
+      <c r="K33" s="26">
         <f>K32</f>
         <v>1</v>
       </c>
-      <c r="L33" s="15">
+      <c r="L33" s="26">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M33" s="15">
-        <v>1</v>
-      </c>
-      <c r="N33" s="15"/>
+      <c r="M33" s="26">
+        <v>1</v>
+      </c>
+      <c r="N33" s="26"/>
     </row>
     <row r="34" ht="16" spans="4:14">
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="E34" s="15"/>
-      <c r="F34" s="16" t="s">
+      <c r="E34" s="26"/>
+      <c r="F34" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="G34" s="15" t="s">
+      <c r="G34" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="H34" s="15" t="s">
+      <c r="H34" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="I34" s="15" t="s">
+      <c r="I34" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="J34" s="15">
-        <v>1</v>
-      </c>
-      <c r="K34" s="15">
+      <c r="J34" s="26">
+        <v>1</v>
+      </c>
+      <c r="K34" s="26">
         <f>K33</f>
         <v>1</v>
       </c>
-      <c r="L34" s="15">
+      <c r="L34" s="26">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M34" s="15">
-        <v>1</v>
-      </c>
-      <c r="N34" s="15"/>
+      <c r="M34" s="26">
+        <v>1</v>
+      </c>
+      <c r="N34" s="26"/>
     </row>
     <row r="35" ht="16" spans="4:14">
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="E35" s="15"/>
-      <c r="F35" s="16" t="s">
+      <c r="E35" s="26"/>
+      <c r="F35" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="15" t="s">
+      <c r="G35" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="H35" s="15" t="s">
+      <c r="H35" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="I35" s="15" t="s">
+      <c r="I35" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="J35" s="15">
-        <v>1</v>
-      </c>
-      <c r="K35" s="15">
+      <c r="J35" s="26">
+        <v>1</v>
+      </c>
+      <c r="K35" s="26">
         <f>K34</f>
         <v>1</v>
       </c>
-      <c r="L35" s="15">
+      <c r="L35" s="26">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M35" s="15">
-        <v>1</v>
-      </c>
-      <c r="N35" s="15"/>
+      <c r="M35" s="26">
+        <v>1</v>
+      </c>
+      <c r="N35" s="26"/>
     </row>
     <row r="36" ht="16" spans="4:14">
-      <c r="D36" s="15" t="s">
+      <c r="D36" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="E36" s="15"/>
-      <c r="F36" s="16" t="s">
+      <c r="E36" s="26"/>
+      <c r="F36" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="G36" s="15" t="s">
+      <c r="G36" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="H36" s="15" t="s">
+      <c r="H36" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="I36" s="15" t="s">
+      <c r="I36" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="J36" s="15">
-        <v>1</v>
-      </c>
-      <c r="K36" s="15">
+      <c r="J36" s="26">
+        <v>1</v>
+      </c>
+      <c r="K36" s="26">
         <f>K35</f>
         <v>1</v>
       </c>
-      <c r="L36" s="15">
+      <c r="L36" s="26">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M36" s="15">
-        <v>1</v>
-      </c>
-      <c r="N36" s="15"/>
+      <c r="M36" s="26">
+        <v>1</v>
+      </c>
+      <c r="N36" s="26"/>
     </row>
     <row r="37" ht="16" spans="4:14">
-      <c r="D37" s="18" t="s">
+      <c r="D37" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="E37" s="18"/>
-      <c r="F37" s="19" t="s">
+      <c r="E37" s="29"/>
+      <c r="F37" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="G37" s="18" t="s">
+      <c r="G37" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="H37" s="18" t="s">
+      <c r="H37" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="I37" s="18" t="s">
+      <c r="I37" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="J37" s="18">
-        <v>1</v>
-      </c>
-      <c r="K37" s="18">
+      <c r="J37" s="29">
+        <v>1</v>
+      </c>
+      <c r="K37" s="29">
         <v>1.1</v>
       </c>
-      <c r="L37" s="18">
+      <c r="L37" s="29">
         <v>0.01</v>
       </c>
-      <c r="M37" s="18">
+      <c r="M37" s="29">
         <v>3</v>
       </c>
-      <c r="N37" s="15"/>
+      <c r="N37" s="26"/>
     </row>
     <row r="38" spans="4:14">
-      <c r="D38" s="18" t="s">
+      <c r="D38" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="E38" s="18"/>
-      <c r="F38" s="20" t="s">
+      <c r="E38" s="29"/>
+      <c r="F38" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="G38" s="18" t="s">
+      <c r="G38" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="H38" s="18" t="s">
+      <c r="H38" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="I38" s="18" t="s">
+      <c r="I38" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="J38" s="18">
-        <v>1</v>
-      </c>
-      <c r="K38" s="18">
+      <c r="J38" s="29">
+        <v>1</v>
+      </c>
+      <c r="K38" s="29">
         <v>1.1</v>
       </c>
-      <c r="L38" s="18">
+      <c r="L38" s="29">
         <v>0.01</v>
       </c>
-      <c r="M38" s="18">
+      <c r="M38" s="29">
         <v>3</v>
       </c>
-      <c r="N38" s="15"/>
+      <c r="N38" s="26"/>
     </row>
     <row r="39" ht="16" spans="4:14">
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="21"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
-      <c r="M39" s="21"/>
-      <c r="N39" s="23"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="32"/>
+      <c r="L39" s="32"/>
+      <c r="M39" s="32"/>
+      <c r="N39" s="32"/>
     </row>
     <row r="40" ht="16" spans="4:14">
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="21"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
-      <c r="M40" s="21"/>
-      <c r="N40" s="23"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="32"/>
+      <c r="M40" s="32"/>
+      <c r="N40" s="32"/>
     </row>
     <row r="41" ht="16" spans="4:14">
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="21"/>
-      <c r="K41" s="21"/>
-      <c r="L41" s="21"/>
-      <c r="M41" s="21"/>
-      <c r="N41" s="23"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="32"/>
+      <c r="J41" s="32"/>
+      <c r="K41" s="32"/>
+      <c r="L41" s="32"/>
+      <c r="M41" s="32"/>
+      <c r="N41" s="32"/>
     </row>
     <row r="42" ht="16" spans="4:14">
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="21"/>
-      <c r="J42" s="21"/>
-      <c r="K42" s="21"/>
-      <c r="L42" s="21"/>
-      <c r="M42" s="21"/>
-      <c r="N42" s="23"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+      <c r="N42" s="32"/>
     </row>
     <row r="43" ht="16" spans="4:14">
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="21"/>
-      <c r="J43" s="21"/>
-      <c r="K43" s="21"/>
-      <c r="L43" s="21"/>
-      <c r="M43" s="21"/>
-      <c r="N43" s="23"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="32"/>
+      <c r="L43" s="32"/>
+      <c r="M43" s="32"/>
+      <c r="N43" s="32"/>
     </row>
     <row r="44" spans="4:14">
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="25"/>
-      <c r="I44" s="25"/>
-      <c r="J44" s="25"/>
-      <c r="K44" s="25"/>
-      <c r="L44" s="25"/>
-      <c r="M44" s="25"/>
-      <c r="N44" s="23"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="32"/>
     </row>
     <row r="45" spans="4:14">
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="26"/>
-      <c r="G45" s="21"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="21"/>
-      <c r="J45" s="21"/>
-      <c r="K45" s="21"/>
-      <c r="L45" s="21"/>
-      <c r="M45" s="21"/>
-      <c r="N45" s="23"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="35"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
+      <c r="J45" s="32"/>
+      <c r="K45" s="32"/>
+      <c r="L45" s="32"/>
+      <c r="M45" s="32"/>
+      <c r="N45" s="32"/>
     </row>
     <row r="46" spans="4:14">
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
-      <c r="H46" s="25"/>
-      <c r="I46" s="25"/>
-      <c r="J46" s="25"/>
-      <c r="K46" s="25"/>
-      <c r="L46" s="25"/>
-      <c r="M46" s="25"/>
-      <c r="N46" s="23"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="32"/>
     </row>
     <row r="47" spans="4:14">
-      <c r="D47" s="25"/>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25"/>
-      <c r="H47" s="25"/>
-      <c r="I47" s="25"/>
-      <c r="J47" s="25"/>
-      <c r="K47" s="25"/>
-      <c r="L47" s="25"/>
-      <c r="M47" s="25"/>
-      <c r="N47" s="23"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="32"/>
     </row>
     <row r="48" spans="4:14">
-      <c r="D48" s="25"/>
-      <c r="E48" s="25"/>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25"/>
-      <c r="H48" s="25"/>
-      <c r="I48" s="25"/>
-      <c r="J48" s="25"/>
-      <c r="K48" s="25"/>
-      <c r="L48" s="25"/>
-      <c r="M48" s="25"/>
-      <c r="N48" s="23"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="32"/>
     </row>
     <row r="49" spans="4:14">
-      <c r="N49" s="15"/>
+      <c r="N49" s="26"/>
     </row>
     <row r="50" spans="4:14">
-      <c r="N50" s="15"/>
+      <c r="N50" s="26"/>
     </row>
     <row r="51" spans="4:14">
-      <c r="N51" s="15"/>
+      <c r="N51" s="26"/>
     </row>
     <row r="52" spans="4:14">
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="15"/>
-      <c r="I52" s="15"/>
-      <c r="J52" s="15"/>
-      <c r="K52" s="15"/>
-      <c r="L52" s="15"/>
-      <c r="M52" s="15"/>
-      <c r="N52" s="15"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="26"/>
+      <c r="H52" s="26"/>
+      <c r="I52" s="26"/>
+      <c r="J52" s="26"/>
+      <c r="K52" s="26"/>
+      <c r="L52" s="26"/>
+      <c r="M52" s="26"/>
+      <c r="N52" s="26"/>
     </row>
     <row r="53" spans="4:14">
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="15"/>
-      <c r="I53" s="15"/>
-      <c r="J53" s="15"/>
-      <c r="K53" s="15"/>
-      <c r="L53" s="15"/>
-      <c r="M53" s="15"/>
-      <c r="N53" s="15"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="26"/>
+      <c r="I53" s="26"/>
+      <c r="J53" s="26"/>
+      <c r="K53" s="26"/>
+      <c r="L53" s="26"/>
+      <c r="M53" s="26"/>
+      <c r="N53" s="26"/>
     </row>
     <row r="54" spans="4:14">
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="15"/>
-      <c r="H54" s="15"/>
-      <c r="I54" s="15"/>
-      <c r="J54" s="15"/>
-      <c r="K54" s="15"/>
-      <c r="L54" s="15"/>
-      <c r="M54" s="15"/>
-      <c r="N54" s="15"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="26"/>
+      <c r="I54" s="26"/>
+      <c r="J54" s="26"/>
+      <c r="K54" s="26"/>
+      <c r="L54" s="26"/>
+      <c r="M54" s="26"/>
+      <c r="N54" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5160,95 +5177,101 @@
       <c r="T69" s="1"/>
     </row>
     <row r="70" spans="7:20">
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="4" t="s">
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="J70" s="5"/>
-      <c r="K70" s="5"/>
-      <c r="L70" s="5"/>
-      <c r="M70" s="5"/>
-      <c r="N70" s="5"/>
-      <c r="O70" s="5"/>
-      <c r="P70" s="6"/>
-      <c r="Q70" s="6"/>
+      <c r="J70" s="15"/>
+      <c r="K70" s="15"/>
+      <c r="L70" s="15"/>
+      <c r="M70" s="15"/>
+      <c r="N70" s="15"/>
+      <c r="O70" s="15"/>
+      <c r="P70" s="16"/>
+      <c r="Q70" s="16"/>
       <c r="T70" s="1"/>
     </row>
     <row r="71" spans="7:20">
-      <c r="G71" s="3" t="s">
+      <c r="G71" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="H71" s="3" t="s">
+      <c r="H71" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="I71" s="7" t="s">
+      <c r="I71" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="J71" s="5" t="s">
+      <c r="J71" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="K71" s="3" t="s">
+      <c r="K71" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="L71" s="3" t="s">
+      <c r="L71" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="M71" s="5" t="s">
+      <c r="M71" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N71" s="3" t="s">
+      <c r="N71" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="O71" t="s">
+      <c r="O71" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="P71" s="1" t="s">
+      <c r="P71" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="Q71" s="1" t="s">
+      <c r="Q71" s="19" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="72" ht="16" spans="7:20">
-      <c r="G72" s="3" t="s">
+      <c r="G72" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="H72" s="3" t="s">
+      <c r="H72" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="I72" s="9">
+      <c r="I72" s="20">
         <v>2019</v>
       </c>
-      <c r="J72" s="10">
+      <c r="J72" s="21">
         <v>-1</v>
       </c>
-      <c r="K72" s="3"/>
-      <c r="L72" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="M72" s="11" t="s">
+      <c r="K72" s="13"/>
+      <c r="L72" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="M72" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="N72" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="N72" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="O72" s="13">
         <v>10</v>
       </c>
-      <c r="P72" s="1">
+      <c r="P72" s="19">
         <v>0</v>
       </c>
-      <c r="Q72" s="1">
+      <c r="Q72" s="19">
         <v>3</v>
       </c>
     </row>
     <row r="73" spans="7:20">
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
+      <c r="G73" s="13"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
+      <c r="J73" s="13"/>
+      <c r="K73" s="13"/>
+      <c r="L73" s="18"/>
+      <c r="M73" s="18"/>
+      <c r="N73" s="18"/>
+      <c r="O73" s="18"/>
+      <c r="P73" s="18"/>
+      <c r="Q73" s="18"/>
     </row>
     <row r="80" spans="7:20">
       <c r="G80" s="3"/>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -649,7 +649,7 @@
     <t>Tra_EV_Batt-LFP_fromrecy, Tra_EV_Batt-LFP_virgin_pack</t>
   </si>
   <si>
-    <t>Tra_EV_Batt-NMC*fromrecy, Tra_EV_Batt-NMC*virgin_pack</t>
+    <t>Tra_E*fromrecy, Tra_EV_Bat*virgin_pack, -Tra_EV_Batt-LFP_fromrecy, -Tra_EV_Batt-LFP_virgin_pack</t>
   </si>
   <si>
     <t>UCE_3</t>
@@ -658,7 +658,7 @@
     <t>EN_STG_4hBatt, Util_Rep_Batt-LFP</t>
   </si>
   <si>
-    <t>EN_STG_4hBatt_NMC*, Util_Rep_Batt-NMC*</t>
+    <t>EN_STG_4hBatt*, Util_Rep_Bat*, -EN_STG_4hBatt, -Util_Rep_Batt-LFP</t>
   </si>
   <si>
     <t>~UC_T: UC_CAP</t>
@@ -914,12 +914,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -936,7 +936,7 @@
       <charset val="0"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -946,12 +946,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1307,7 +1301,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1331,16 +1325,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1349,93 +1343,93 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1456,17 +1450,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1476,12 +1466,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1491,15 +1481,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="53">
@@ -2034,7 +2024,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="44">
+      <c r="F21" s="40">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -2172,12 +2162,12 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:13">
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="26"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="22"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
@@ -2192,19 +2182,19 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="37"/>
+      <c r="K6" s="33"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="34">
         <v>10</v>
       </c>
     </row>
@@ -2212,17 +2202,17 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="34">
         <v>7</v>
       </c>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
     </row>
     <row r="9" ht="16" spans="2:13">
       <c r="B9" t="s">
@@ -2231,10 +2221,10 @@
       <c r="C9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="34">
         <v>10</v>
       </c>
     </row>
@@ -2242,17 +2232,17 @@
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="34">
         <v>8</v>
       </c>
-      <c r="K10" s="39"/>
-      <c r="L10" s="40"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="36"/>
     </row>
     <row r="11" ht="16" spans="2:13">
       <c r="B11" t="s">
@@ -2261,10 +2251,10 @@
       <c r="C11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="32">
         <v>1.5</v>
       </c>
     </row>
@@ -2275,10 +2265,10 @@
       <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="36">
+      <c r="E12" s="32">
         <v>1.5</v>
       </c>
     </row>
@@ -2286,13 +2276,13 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="22">
         <v>2</v>
       </c>
     </row>
@@ -2300,13 +2290,13 @@
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="36" t="s">
+      <c r="D14" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="22">
         <v>0</v>
       </c>
     </row>
@@ -2314,13 +2304,13 @@
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="36" t="s">
+      <c r="D15" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="22">
         <v>0</v>
       </c>
     </row>
@@ -2328,13 +2318,13 @@
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="36" t="s">
+      <c r="C16" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="36" t="s">
+      <c r="D16" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="37">
         <v>12</v>
       </c>
     </row>
@@ -2342,31 +2332,31 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="42" t="s">
+      <c r="D17" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="43">
+      <c r="E17" s="39">
         <v>0.2</v>
       </c>
-      <c r="F17" s="26"/>
+      <c r="F17" s="22"/>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="42" t="s">
+      <c r="D18" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="43">
+      <c r="E18" s="39">
         <v>0.2</v>
       </c>
-      <c r="F18" s="26"/>
+      <c r="F18" s="22"/>
     </row>
     <row r="19" ht="16" spans="2:6">
       <c r="B19" t="s">
@@ -2375,28 +2365,28 @@
       <c r="C19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="42" t="s">
+      <c r="D19" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="43">
+      <c r="E19" s="39">
         <v>0.2</v>
       </c>
-      <c r="F19" s="26"/>
+      <c r="F19" s="22"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="42" t="s">
+      <c r="D20" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="43">
+      <c r="E20" s="39">
         <v>0.5</v>
       </c>
-      <c r="F20" s="26"/>
+      <c r="F20" s="22"/>
     </row>
     <row r="21" ht="16" spans="2:6">
       <c r="B21" t="s">
@@ -2405,13 +2395,13 @@
       <c r="C21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="42" t="s">
+      <c r="D21" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="43">
+      <c r="E21" s="39">
         <v>0.8</v>
       </c>
-      <c r="F21" s="26"/>
+      <c r="F21" s="22"/>
     </row>
     <row r="22" ht="16" spans="2:6">
       <c r="B22" t="s">
@@ -2420,122 +2410,122 @@
       <c r="C22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="42" t="s">
+      <c r="D22" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="36"/>
-      <c r="F22" s="26"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="22"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="42" t="s">
+      <c r="D23" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="26">
-        <v>1</v>
-      </c>
-      <c r="F23" s="26"/>
+      <c r="E23" s="22">
+        <v>1</v>
+      </c>
+      <c r="F23" s="22"/>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C24" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="42" t="s">
+      <c r="D24" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="26">
-        <v>1</v>
-      </c>
-      <c r="F24" s="26"/>
+      <c r="E24" s="22">
+        <v>1</v>
+      </c>
+      <c r="F24" s="22"/>
     </row>
     <row r="25" ht="16" spans="2:6">
       <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="27" t="s">
+      <c r="C25" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="42" t="s">
+      <c r="D25" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="26">
-        <v>1</v>
-      </c>
-      <c r="F25" s="26"/>
+      <c r="E25" s="22">
+        <v>1</v>
+      </c>
+      <c r="F25" s="22"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="36" t="s">
+      <c r="C26" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="42" t="s">
+      <c r="D26" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="36">
+      <c r="E26" s="32">
         <v>0.05</v>
       </c>
-      <c r="F26" s="26"/>
+      <c r="F26" s="22"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="44" t="s">
+      <c r="B27" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="45" t="s">
+      <c r="C27" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="45" t="s">
+      <c r="D27" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="45">
+      <c r="E27" s="41">
         <v>2020</v>
       </c>
-      <c r="F27" s="26"/>
+      <c r="F27" s="22"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="45" t="s">
+      <c r="D28" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="29">
+      <c r="E28" s="25">
         <v>2020</v>
       </c>
-      <c r="F28" s="26"/>
+      <c r="F28" s="22"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
     </row>
     <row r="38" spans="3:5">
       <c r="C38" s="1"/>
@@ -2543,360 +2533,360 @@
       <c r="E38" s="1"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="46" t="s">
+      <c r="C54" s="42" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="46"/>
-      <c r="E56" s="46"/>
-      <c r="F56" s="46"/>
-      <c r="G56" s="46"/>
-      <c r="H56" s="46"/>
-      <c r="I56" s="46"/>
-      <c r="J56" s="46"/>
-      <c r="K56" s="46"/>
+      <c r="D56" s="42"/>
+      <c r="E56" s="42"/>
+      <c r="F56" s="42"/>
+      <c r="G56" s="42"/>
+      <c r="H56" s="42"/>
+      <c r="I56" s="42"/>
+      <c r="J56" s="42"/>
+      <c r="K56" s="42"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="46" t="s">
+      <c r="C57" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="46" t="s">
+      <c r="D57" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="46" t="s">
+      <c r="E57" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="F57" s="46" t="s">
+      <c r="F57" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="G57" s="46" t="s">
+      <c r="G57" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="46" t="s">
+      <c r="H57" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="46" t="s">
+      <c r="I57" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="J57" s="46" t="s">
+      <c r="J57" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="K57" s="46" t="s">
+      <c r="K57" s="42" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="46"/>
-      <c r="D58" s="46"/>
-      <c r="E58" s="46"/>
-      <c r="F58" s="46"/>
-      <c r="G58" s="46"/>
-      <c r="H58" s="46"/>
-      <c r="I58" s="46"/>
-      <c r="J58" s="46"/>
-      <c r="K58" s="46"/>
+      <c r="C58" s="42"/>
+      <c r="D58" s="42"/>
+      <c r="E58" s="42"/>
+      <c r="F58" s="42"/>
+      <c r="G58" s="42"/>
+      <c r="H58" s="42"/>
+      <c r="I58" s="42"/>
+      <c r="J58" s="42"/>
+      <c r="K58" s="42"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="46"/>
-      <c r="D59" s="46"/>
-      <c r="E59" s="46"/>
-      <c r="F59" s="46"/>
-      <c r="G59" s="46"/>
-      <c r="H59" s="46"/>
-      <c r="I59" s="46"/>
-      <c r="J59" s="46"/>
-      <c r="K59" s="46"/>
+      <c r="C59" s="42"/>
+      <c r="D59" s="42"/>
+      <c r="E59" s="42"/>
+      <c r="F59" s="42"/>
+      <c r="G59" s="42"/>
+      <c r="H59" s="42"/>
+      <c r="I59" s="42"/>
+      <c r="J59" s="42"/>
+      <c r="K59" s="42"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="46"/>
-      <c r="D60" s="46"/>
-      <c r="E60" s="46"/>
-      <c r="F60" s="46"/>
-      <c r="G60" s="46"/>
-      <c r="H60" s="46"/>
-      <c r="I60" s="46"/>
-      <c r="J60" s="46"/>
-      <c r="K60" s="46"/>
+      <c r="C60" s="42"/>
+      <c r="D60" s="42"/>
+      <c r="E60" s="42"/>
+      <c r="F60" s="42"/>
+      <c r="G60" s="42"/>
+      <c r="H60" s="42"/>
+      <c r="I60" s="42"/>
+      <c r="J60" s="42"/>
+      <c r="K60" s="42"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="46"/>
-      <c r="D61" s="46"/>
-      <c r="E61" s="46"/>
-      <c r="F61" s="46"/>
-      <c r="G61" s="46"/>
-      <c r="H61" s="46"/>
-      <c r="I61" s="46"/>
-      <c r="J61" s="46"/>
-      <c r="K61" s="46"/>
+      <c r="C61" s="42"/>
+      <c r="D61" s="42"/>
+      <c r="E61" s="42"/>
+      <c r="F61" s="42"/>
+      <c r="G61" s="42"/>
+      <c r="H61" s="42"/>
+      <c r="I61" s="42"/>
+      <c r="J61" s="42"/>
+      <c r="K61" s="42"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="46"/>
-      <c r="D62" s="46"/>
-      <c r="E62" s="46"/>
-      <c r="F62" s="46"/>
-      <c r="G62" s="46"/>
-      <c r="H62" s="46"/>
-      <c r="I62" s="46"/>
-      <c r="J62" s="46"/>
-      <c r="K62" s="46"/>
+      <c r="C62" s="42"/>
+      <c r="D62" s="42"/>
+      <c r="E62" s="42"/>
+      <c r="F62" s="42"/>
+      <c r="G62" s="42"/>
+      <c r="H62" s="42"/>
+      <c r="I62" s="42"/>
+      <c r="J62" s="42"/>
+      <c r="K62" s="42"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="46"/>
-      <c r="D63" s="46"/>
-      <c r="E63" s="46"/>
-      <c r="F63" s="46"/>
-      <c r="G63" s="46"/>
-      <c r="H63" s="46"/>
-      <c r="I63" s="46"/>
-      <c r="J63" s="46"/>
-      <c r="K63" s="46"/>
+      <c r="C63" s="42"/>
+      <c r="D63" s="42"/>
+      <c r="E63" s="42"/>
+      <c r="F63" s="42"/>
+      <c r="G63" s="42"/>
+      <c r="H63" s="42"/>
+      <c r="I63" s="42"/>
+      <c r="J63" s="42"/>
+      <c r="K63" s="42"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="46"/>
-      <c r="D64" s="46"/>
-      <c r="E64" s="46"/>
-      <c r="F64" s="46"/>
-      <c r="G64" s="46"/>
-      <c r="H64" s="46"/>
-      <c r="I64" s="46"/>
-      <c r="J64" s="46"/>
-      <c r="K64" s="46"/>
+      <c r="C64" s="42"/>
+      <c r="D64" s="42"/>
+      <c r="E64" s="42"/>
+      <c r="F64" s="42"/>
+      <c r="G64" s="42"/>
+      <c r="H64" s="42"/>
+      <c r="I64" s="42"/>
+      <c r="J64" s="42"/>
+      <c r="K64" s="42"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="46"/>
-      <c r="D65" s="46"/>
-      <c r="E65" s="46"/>
-      <c r="F65" s="46"/>
-      <c r="G65" s="46"/>
-      <c r="H65" s="46"/>
-      <c r="I65" s="46"/>
-      <c r="J65" s="46"/>
-      <c r="K65" s="46"/>
+      <c r="C65" s="42"/>
+      <c r="D65" s="42"/>
+      <c r="E65" s="42"/>
+      <c r="F65" s="42"/>
+      <c r="G65" s="42"/>
+      <c r="H65" s="42"/>
+      <c r="I65" s="42"/>
+      <c r="J65" s="42"/>
+      <c r="K65" s="42"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="46"/>
-      <c r="D66" s="46"/>
-      <c r="E66" s="46"/>
-      <c r="F66" s="46"/>
-      <c r="G66" s="46"/>
-      <c r="H66" s="46"/>
-      <c r="I66" s="46"/>
-      <c r="J66" s="46"/>
-      <c r="K66" s="46"/>
+      <c r="C66" s="42"/>
+      <c r="D66" s="42"/>
+      <c r="E66" s="42"/>
+      <c r="F66" s="42"/>
+      <c r="G66" s="42"/>
+      <c r="H66" s="42"/>
+      <c r="I66" s="42"/>
+      <c r="J66" s="42"/>
+      <c r="K66" s="42"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="46"/>
-      <c r="D67" s="46"/>
-      <c r="E67" s="46"/>
-      <c r="F67" s="46"/>
-      <c r="G67" s="46"/>
-      <c r="H67" s="46"/>
-      <c r="I67" s="46"/>
-      <c r="J67" s="46"/>
-      <c r="K67" s="46"/>
+      <c r="C67" s="42"/>
+      <c r="D67" s="42"/>
+      <c r="E67" s="42"/>
+      <c r="F67" s="42"/>
+      <c r="G67" s="42"/>
+      <c r="H67" s="42"/>
+      <c r="I67" s="42"/>
+      <c r="J67" s="42"/>
+      <c r="K67" s="42"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="46"/>
-      <c r="D68" s="46"/>
-      <c r="E68" s="46"/>
-      <c r="F68" s="46"/>
-      <c r="G68" s="46"/>
-      <c r="H68" s="46"/>
-      <c r="I68" s="46"/>
-      <c r="J68" s="46"/>
-      <c r="K68" s="46"/>
+      <c r="C68" s="42"/>
+      <c r="D68" s="42"/>
+      <c r="E68" s="42"/>
+      <c r="F68" s="42"/>
+      <c r="G68" s="42"/>
+      <c r="H68" s="42"/>
+      <c r="I68" s="42"/>
+      <c r="J68" s="42"/>
+      <c r="K68" s="42"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="46"/>
-      <c r="D69" s="46"/>
-      <c r="E69" s="46"/>
-      <c r="F69" s="46"/>
-      <c r="G69" s="46"/>
-      <c r="H69" s="46"/>
-      <c r="I69" s="46"/>
-      <c r="J69" s="46"/>
-      <c r="K69" s="46"/>
+      <c r="C69" s="42"/>
+      <c r="D69" s="42"/>
+      <c r="E69" s="42"/>
+      <c r="F69" s="42"/>
+      <c r="G69" s="42"/>
+      <c r="H69" s="42"/>
+      <c r="I69" s="42"/>
+      <c r="J69" s="42"/>
+      <c r="K69" s="42"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="46"/>
-      <c r="D70" s="46"/>
-      <c r="E70" s="46"/>
-      <c r="F70" s="46"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="46"/>
-      <c r="I70" s="46"/>
-      <c r="J70" s="46"/>
-      <c r="K70" s="46"/>
+      <c r="C70" s="42"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="42"/>
+      <c r="G70" s="42"/>
+      <c r="H70" s="42"/>
+      <c r="I70" s="42"/>
+      <c r="J70" s="42"/>
+      <c r="K70" s="42"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="46"/>
-      <c r="D71" s="46"/>
-      <c r="E71" s="46"/>
-      <c r="F71" s="46"/>
-      <c r="G71" s="46"/>
-      <c r="H71" s="46"/>
-      <c r="I71" s="46"/>
-      <c r="J71" s="46"/>
-      <c r="K71" s="46"/>
+      <c r="C71" s="42"/>
+      <c r="D71" s="42"/>
+      <c r="E71" s="42"/>
+      <c r="F71" s="42"/>
+      <c r="G71" s="42"/>
+      <c r="H71" s="42"/>
+      <c r="I71" s="42"/>
+      <c r="J71" s="42"/>
+      <c r="K71" s="42"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="46"/>
-      <c r="D72" s="46"/>
-      <c r="E72" s="46"/>
-      <c r="F72" s="46"/>
-      <c r="G72" s="46"/>
-      <c r="H72" s="46"/>
-      <c r="I72" s="46"/>
-      <c r="J72" s="46"/>
-      <c r="K72" s="46"/>
+      <c r="C72" s="42"/>
+      <c r="D72" s="42"/>
+      <c r="E72" s="42"/>
+      <c r="F72" s="42"/>
+      <c r="G72" s="42"/>
+      <c r="H72" s="42"/>
+      <c r="I72" s="42"/>
+      <c r="J72" s="42"/>
+      <c r="K72" s="42"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="46"/>
-      <c r="D73" s="46"/>
-      <c r="E73" s="46"/>
-      <c r="F73" s="46"/>
-      <c r="G73" s="46"/>
-      <c r="H73" s="46"/>
-      <c r="I73" s="46"/>
-      <c r="J73" s="46"/>
-      <c r="K73" s="46"/>
+      <c r="C73" s="42"/>
+      <c r="D73" s="42"/>
+      <c r="E73" s="42"/>
+      <c r="F73" s="42"/>
+      <c r="G73" s="42"/>
+      <c r="H73" s="42"/>
+      <c r="I73" s="42"/>
+      <c r="J73" s="42"/>
+      <c r="K73" s="42"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="46"/>
-      <c r="D74" s="46"/>
-      <c r="E74" s="46"/>
-      <c r="F74" s="46"/>
-      <c r="G74" s="46"/>
-      <c r="H74" s="46"/>
-      <c r="I74" s="46"/>
-      <c r="J74" s="46"/>
-      <c r="K74" s="46"/>
+      <c r="C74" s="42"/>
+      <c r="D74" s="42"/>
+      <c r="E74" s="42"/>
+      <c r="F74" s="42"/>
+      <c r="G74" s="42"/>
+      <c r="H74" s="42"/>
+      <c r="I74" s="42"/>
+      <c r="J74" s="42"/>
+      <c r="K74" s="42"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="46"/>
-      <c r="D75" s="46"/>
-      <c r="E75" s="46"/>
-      <c r="F75" s="46"/>
-      <c r="G75" s="46"/>
-      <c r="H75" s="46"/>
-      <c r="I75" s="46"/>
-      <c r="J75" s="46"/>
-      <c r="K75" s="46"/>
+      <c r="C75" s="42"/>
+      <c r="D75" s="42"/>
+      <c r="E75" s="42"/>
+      <c r="F75" s="42"/>
+      <c r="G75" s="42"/>
+      <c r="H75" s="42"/>
+      <c r="I75" s="42"/>
+      <c r="J75" s="42"/>
+      <c r="K75" s="42"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="46"/>
-      <c r="D76" s="46"/>
-      <c r="E76" s="46"/>
-      <c r="F76" s="46"/>
-      <c r="G76" s="46"/>
-      <c r="H76" s="46"/>
-      <c r="I76" s="46"/>
-      <c r="J76" s="46"/>
-      <c r="K76" s="46"/>
+      <c r="C76" s="42"/>
+      <c r="D76" s="42"/>
+      <c r="E76" s="42"/>
+      <c r="F76" s="42"/>
+      <c r="G76" s="42"/>
+      <c r="H76" s="42"/>
+      <c r="I76" s="42"/>
+      <c r="J76" s="42"/>
+      <c r="K76" s="42"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="46"/>
-      <c r="D77" s="46"/>
-      <c r="E77" s="46"/>
-      <c r="F77" s="46"/>
-      <c r="G77" s="46"/>
-      <c r="H77" s="46"/>
-      <c r="I77" s="46"/>
-      <c r="J77" s="46"/>
-      <c r="K77" s="46"/>
+      <c r="C77" s="42"/>
+      <c r="D77" s="42"/>
+      <c r="E77" s="42"/>
+      <c r="F77" s="42"/>
+      <c r="G77" s="42"/>
+      <c r="H77" s="42"/>
+      <c r="I77" s="42"/>
+      <c r="J77" s="42"/>
+      <c r="K77" s="42"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="46"/>
-      <c r="D78" s="46"/>
-      <c r="E78" s="46"/>
-      <c r="F78" s="46"/>
-      <c r="G78" s="46"/>
-      <c r="H78" s="46"/>
-      <c r="I78" s="46"/>
-      <c r="J78" s="46"/>
-      <c r="K78" s="46"/>
+      <c r="C78" s="42"/>
+      <c r="D78" s="42"/>
+      <c r="E78" s="42"/>
+      <c r="F78" s="42"/>
+      <c r="G78" s="42"/>
+      <c r="H78" s="42"/>
+      <c r="I78" s="42"/>
+      <c r="J78" s="42"/>
+      <c r="K78" s="42"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="46"/>
-      <c r="D79" s="46"/>
-      <c r="E79" s="46"/>
-      <c r="F79" s="46"/>
-      <c r="G79" s="46"/>
-      <c r="H79" s="46"/>
-      <c r="I79" s="46"/>
-      <c r="J79" s="46"/>
-      <c r="K79" s="46"/>
+      <c r="C79" s="42"/>
+      <c r="D79" s="42"/>
+      <c r="E79" s="42"/>
+      <c r="F79" s="42"/>
+      <c r="G79" s="42"/>
+      <c r="H79" s="42"/>
+      <c r="I79" s="42"/>
+      <c r="J79" s="42"/>
+      <c r="K79" s="42"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="46"/>
-      <c r="D80" s="46"/>
-      <c r="E80" s="46"/>
-      <c r="F80" s="46"/>
-      <c r="G80" s="46"/>
-      <c r="H80" s="46"/>
-      <c r="I80" s="46"/>
-      <c r="J80" s="46"/>
-      <c r="K80" s="46"/>
+      <c r="C80" s="42"/>
+      <c r="D80" s="42"/>
+      <c r="E80" s="42"/>
+      <c r="F80" s="42"/>
+      <c r="G80" s="42"/>
+      <c r="H80" s="42"/>
+      <c r="I80" s="42"/>
+      <c r="J80" s="42"/>
+      <c r="K80" s="42"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="46"/>
-      <c r="D81" s="46"/>
-      <c r="E81" s="46"/>
-      <c r="F81" s="46"/>
-      <c r="G81" s="46"/>
-      <c r="H81" s="46"/>
-      <c r="I81" s="46"/>
-      <c r="J81" s="46"/>
-      <c r="K81" s="46"/>
+      <c r="C81" s="42"/>
+      <c r="D81" s="42"/>
+      <c r="E81" s="42"/>
+      <c r="F81" s="42"/>
+      <c r="G81" s="42"/>
+      <c r="H81" s="42"/>
+      <c r="I81" s="42"/>
+      <c r="J81" s="42"/>
+      <c r="K81" s="42"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="46"/>
-      <c r="D82" s="46"/>
-      <c r="E82" s="46"/>
-      <c r="F82" s="46"/>
-      <c r="G82" s="46"/>
-      <c r="H82" s="46"/>
-      <c r="I82" s="46"/>
-      <c r="J82" s="46"/>
-      <c r="K82" s="46"/>
+      <c r="C82" s="42"/>
+      <c r="D82" s="42"/>
+      <c r="E82" s="42"/>
+      <c r="F82" s="42"/>
+      <c r="G82" s="42"/>
+      <c r="H82" s="42"/>
+      <c r="I82" s="42"/>
+      <c r="J82" s="42"/>
+      <c r="K82" s="42"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="46"/>
-      <c r="D83" s="46"/>
-      <c r="E83" s="46"/>
-      <c r="F83" s="46"/>
-      <c r="G83" s="46"/>
-      <c r="H83" s="46"/>
-      <c r="I83" s="46"/>
-      <c r="J83" s="46"/>
-      <c r="K83" s="46"/>
+      <c r="C83" s="42"/>
+      <c r="D83" s="42"/>
+      <c r="E83" s="42"/>
+      <c r="F83" s="42"/>
+      <c r="G83" s="42"/>
+      <c r="H83" s="42"/>
+      <c r="I83" s="42"/>
+      <c r="J83" s="42"/>
+      <c r="K83" s="42"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="46" t="s">
+      <c r="C84" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="D84" s="46">
-        <v>1</v>
-      </c>
-      <c r="E84" s="46"/>
-      <c r="F84" s="46"/>
-      <c r="G84" s="46"/>
-      <c r="H84" s="46"/>
-      <c r="I84" s="46"/>
-      <c r="J84" s="46"/>
-      <c r="K84" s="46"/>
+      <c r="D84" s="42">
+        <v>1</v>
+      </c>
+      <c r="E84" s="42"/>
+      <c r="F84" s="42"/>
+      <c r="G84" s="42"/>
+      <c r="H84" s="42"/>
+      <c r="I84" s="42"/>
+      <c r="J84" s="42"/>
+      <c r="K84" s="42"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="46"/>
-      <c r="D85" s="46"/>
-      <c r="E85" s="46"/>
-      <c r="F85" s="46"/>
-      <c r="G85" s="46"/>
-      <c r="H85" s="46"/>
-      <c r="I85" s="46"/>
-      <c r="J85" s="46"/>
-      <c r="K85" s="46"/>
+      <c r="C85" s="42"/>
+      <c r="D85" s="42"/>
+      <c r="E85" s="42"/>
+      <c r="F85" s="42"/>
+      <c r="G85" s="42"/>
+      <c r="H85" s="42"/>
+      <c r="I85" s="42"/>
+      <c r="J85" s="42"/>
+      <c r="K85" s="42"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3521,252 +3511,252 @@
       </c>
     </row>
     <row r="8" spans="2:14">
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="24" t="s">
+      <c r="I8" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="J8" s="24" t="s">
+      <c r="J8" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="K8" s="24" t="s">
+      <c r="K8" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="L8" s="24" t="s">
+      <c r="L8" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="M8" s="24" t="s">
+      <c r="M8" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="N8" s="24" t="s">
+      <c r="N8" s="20" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="9" spans="2:14">
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="25" t="s">
+      <c r="H9" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="I9" s="25" t="s">
+      <c r="I9" s="21" t="s">
         <v>88</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
-      <c r="K9" s="25">
+      <c r="K9" s="21">
         <v>1.25</v>
       </c>
       <c r="L9">
         <v>0.05</v>
       </c>
-      <c r="M9" s="25">
-        <v>1</v>
-      </c>
-      <c r="N9" s="25"/>
+      <c r="M9" s="21">
+        <v>1</v>
+      </c>
+      <c r="N9" s="21"/>
     </row>
     <row r="10" spans="2:14">
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="H10" s="25" t="s">
+      <c r="H10" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="I10" s="25" t="s">
+      <c r="I10" s="21" t="s">
         <v>88</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10" s="25">
+      <c r="K10" s="21">
         <v>1.11</v>
       </c>
       <c r="L10">
         <v>0.05</v>
       </c>
-      <c r="M10" s="25">
-        <v>1</v>
-      </c>
-      <c r="N10" s="25"/>
+      <c r="M10" s="21">
+        <v>1</v>
+      </c>
+      <c r="N10" s="21"/>
     </row>
     <row r="11" spans="2:14">
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="H11" s="25" t="s">
+      <c r="H11" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="I11" s="25" t="s">
+      <c r="I11" s="21" t="s">
         <v>88</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11" s="25">
+      <c r="K11" s="21">
         <v>1.15</v>
       </c>
       <c r="L11">
         <v>0.08</v>
       </c>
-      <c r="M11" s="25">
-        <v>1</v>
-      </c>
-      <c r="N11" s="25"/>
+      <c r="M11" s="21">
+        <v>1</v>
+      </c>
+      <c r="N11" s="21"/>
     </row>
     <row r="12" ht="16" spans="2:14">
-      <c r="D12" s="25" t="s">
+      <c r="D12" s="21" t="s">
         <v>93</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="H12" s="25" t="s">
+      <c r="H12" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="I12" s="25" t="s">
+      <c r="I12" s="21" t="s">
         <v>88</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
-      <c r="K12" s="25">
+      <c r="K12" s="21">
         <v>1.12</v>
       </c>
       <c r="L12">
         <v>0.03</v>
       </c>
-      <c r="M12" s="25">
-        <v>1</v>
-      </c>
-      <c r="N12" s="25"/>
+      <c r="M12" s="21">
+        <v>1</v>
+      </c>
+      <c r="N12" s="21"/>
     </row>
     <row r="13" spans="2:14">
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="F13" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="H13" s="25" t="s">
+      <c r="H13" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="I13" s="25" t="s">
+      <c r="I13" s="21" t="s">
         <v>88</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="21">
         <v>1.2</v>
       </c>
       <c r="L13">
         <v>0.1</v>
       </c>
-      <c r="M13" s="25">
-        <v>1</v>
-      </c>
-      <c r="N13" s="25"/>
+      <c r="M13" s="21">
+        <v>1</v>
+      </c>
+      <c r="N13" s="21"/>
     </row>
     <row r="14" spans="2:14">
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="F14" s="25" t="s">
+      <c r="F14" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="H14" s="25" t="s">
+      <c r="H14" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="25" t="s">
+      <c r="I14" s="21" t="s">
         <v>88</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
-      <c r="K14" s="25">
+      <c r="K14" s="21">
         <v>1.06</v>
       </c>
       <c r="L14">
         <v>0.15</v>
       </c>
-      <c r="M14" s="25">
-        <v>1</v>
-      </c>
-      <c r="N14" s="25"/>
+      <c r="M14" s="21">
+        <v>1</v>
+      </c>
+      <c r="N14" s="21"/>
     </row>
     <row r="15" spans="2:14">
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="F15" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="H15" s="25" t="s">
+      <c r="H15" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="I15" s="25" t="s">
+      <c r="I15" s="21" t="s">
         <v>88</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
-      <c r="K15" s="25">
+      <c r="K15" s="21">
         <v>1.06</v>
       </c>
       <c r="L15">
         <v>0.3</v>
       </c>
-      <c r="M15" s="25">
-        <v>1</v>
-      </c>
-      <c r="N15" s="25"/>
+      <c r="M15" s="21">
+        <v>1</v>
+      </c>
+      <c r="N15" s="21"/>
     </row>
     <row r="16" ht="16" spans="2:14">
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="21" t="s">
         <v>101</v>
       </c>
       <c r="F16" s="2" t="s">
@@ -3780,7 +3770,7 @@
         <f>H15</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I16" s="25" t="s">
+      <c r="I16" s="21" t="s">
         <v>88</v>
       </c>
       <c r="J16">
@@ -3801,7 +3791,7 @@
       </c>
     </row>
     <row r="17" ht="16" spans="4:14">
-      <c r="D17" s="25" t="s">
+      <c r="D17" s="21" t="s">
         <v>103</v>
       </c>
       <c r="F17" s="2" t="s">
@@ -3815,7 +3805,7 @@
         <f t="shared" si="1"/>
         <v>2025, 2150</v>
       </c>
-      <c r="I17" s="25" t="s">
+      <c r="I17" s="21" t="s">
         <v>88</v>
       </c>
       <c r="J17">
@@ -3836,7 +3826,7 @@
       </c>
     </row>
     <row r="18" ht="16" spans="4:14">
-      <c r="D18" s="25" t="s">
+      <c r="D18" s="21" t="s">
         <v>105</v>
       </c>
       <c r="F18" s="2" t="s">
@@ -3850,7 +3840,7 @@
         <f>H17</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I18" s="25" t="s">
+      <c r="I18" s="21" t="s">
         <v>88</v>
       </c>
       <c r="J18">
@@ -3867,421 +3857,421 @@
       </c>
     </row>
     <row r="27" spans="4:14">
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="26"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
     </row>
     <row r="28" spans="4:14">
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26" t="s">
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="26"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="26"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
     </row>
     <row r="29" spans="4:14">
-      <c r="D29" s="26" t="s">
+      <c r="D29" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="E29" s="26" t="s">
+      <c r="E29" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="F29" s="26" t="s">
+      <c r="F29" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="26" t="s">
+      <c r="G29" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="H29" s="26" t="s">
+      <c r="H29" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="I29" s="26" t="s">
+      <c r="I29" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="J29" s="26" t="s">
+      <c r="J29" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="K29" s="26" t="s">
+      <c r="K29" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="L29" s="26" t="s">
+      <c r="L29" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="M29" s="26" t="s">
+      <c r="M29" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="N29" s="26" t="s">
+      <c r="N29" s="22" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="30" ht="16" spans="4:14">
-      <c r="D30" s="26" t="s">
+      <c r="D30" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="26"/>
-      <c r="F30" s="27" t="s">
+      <c r="E30" s="22"/>
+      <c r="F30" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="G30" s="26" t="s">
+      <c r="G30" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="H30" s="26" t="s">
+      <c r="H30" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="I30" s="26" t="s">
+      <c r="I30" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="26">
-        <v>1</v>
-      </c>
-      <c r="K30" s="26">
-        <v>1</v>
-      </c>
-      <c r="L30" s="26">
+      <c r="J30" s="22">
+        <v>1</v>
+      </c>
+      <c r="K30" s="22">
+        <v>1</v>
+      </c>
+      <c r="L30" s="22">
         <v>0.01</v>
       </c>
-      <c r="M30" s="26">
-        <v>1</v>
-      </c>
-      <c r="N30" s="26"/>
+      <c r="M30" s="22">
+        <v>1</v>
+      </c>
+      <c r="N30" s="22"/>
     </row>
     <row r="31" ht="16" spans="4:14">
-      <c r="D31" s="26" t="s">
+      <c r="D31" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="26"/>
-      <c r="F31" s="28" t="s">
+      <c r="E31" s="22"/>
+      <c r="F31" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="G31" s="26" t="s">
+      <c r="G31" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="H31" s="26" t="s">
+      <c r="H31" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="I31" s="26" t="s">
+      <c r="I31" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="J31" s="26">
-        <v>1</v>
-      </c>
-      <c r="K31" s="26">
-        <v>1</v>
-      </c>
-      <c r="L31" s="26">
+      <c r="J31" s="22">
+        <v>1</v>
+      </c>
+      <c r="K31" s="22">
+        <v>1</v>
+      </c>
+      <c r="L31" s="22">
         <f t="shared" ref="L31:L36" si="2">L30</f>
         <v>0.01</v>
       </c>
-      <c r="M31" s="26">
-        <v>1</v>
-      </c>
-      <c r="N31" s="26"/>
+      <c r="M31" s="22">
+        <v>1</v>
+      </c>
+      <c r="N31" s="22"/>
     </row>
     <row r="32" ht="16" spans="4:14">
-      <c r="D32" s="26" t="s">
+      <c r="D32" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="E32" s="26"/>
-      <c r="F32" s="28" t="s">
+      <c r="E32" s="22"/>
+      <c r="F32" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="G32" s="26" t="s">
+      <c r="G32" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="H32" s="26" t="s">
+      <c r="H32" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="I32" s="26" t="s">
+      <c r="I32" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="J32" s="26">
-        <v>1</v>
-      </c>
-      <c r="K32" s="26">
-        <v>1</v>
-      </c>
-      <c r="L32" s="26">
+      <c r="J32" s="22">
+        <v>1</v>
+      </c>
+      <c r="K32" s="22">
+        <v>1</v>
+      </c>
+      <c r="L32" s="22">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M32" s="26">
-        <v>1</v>
-      </c>
-      <c r="N32" s="26"/>
+      <c r="M32" s="22">
+        <v>1</v>
+      </c>
+      <c r="N32" s="22"/>
     </row>
     <row r="33" ht="16" spans="4:14">
-      <c r="D33" s="26" t="s">
+      <c r="D33" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="26"/>
-      <c r="F33" s="27" t="s">
+      <c r="E33" s="22"/>
+      <c r="F33" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="G33" s="26" t="s">
+      <c r="G33" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="H33" s="26" t="s">
+      <c r="H33" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="I33" s="26" t="s">
+      <c r="I33" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="J33" s="26">
-        <v>1</v>
-      </c>
-      <c r="K33" s="26">
+      <c r="J33" s="22">
+        <v>1</v>
+      </c>
+      <c r="K33" s="22">
         <f>K32</f>
         <v>1</v>
       </c>
-      <c r="L33" s="26">
+      <c r="L33" s="22">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M33" s="26">
-        <v>1</v>
-      </c>
-      <c r="N33" s="26"/>
+      <c r="M33" s="22">
+        <v>1</v>
+      </c>
+      <c r="N33" s="22"/>
     </row>
     <row r="34" ht="16" spans="4:14">
-      <c r="D34" s="26" t="s">
+      <c r="D34" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="E34" s="26"/>
-      <c r="F34" s="27" t="s">
+      <c r="E34" s="22"/>
+      <c r="F34" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="G34" s="26" t="s">
+      <c r="G34" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="H34" s="26" t="s">
+      <c r="H34" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="I34" s="26" t="s">
+      <c r="I34" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="J34" s="26">
-        <v>1</v>
-      </c>
-      <c r="K34" s="26">
+      <c r="J34" s="22">
+        <v>1</v>
+      </c>
+      <c r="K34" s="22">
         <f>K33</f>
         <v>1</v>
       </c>
-      <c r="L34" s="26">
+      <c r="L34" s="22">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M34" s="26">
-        <v>1</v>
-      </c>
-      <c r="N34" s="26"/>
+      <c r="M34" s="22">
+        <v>1</v>
+      </c>
+      <c r="N34" s="22"/>
     </row>
     <row r="35" ht="16" spans="4:14">
-      <c r="D35" s="26" t="s">
+      <c r="D35" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="E35" s="26"/>
-      <c r="F35" s="27" t="s">
+      <c r="E35" s="22"/>
+      <c r="F35" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="26" t="s">
+      <c r="G35" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="H35" s="26" t="s">
+      <c r="H35" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="I35" s="26" t="s">
+      <c r="I35" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="J35" s="26">
-        <v>1</v>
-      </c>
-      <c r="K35" s="26">
+      <c r="J35" s="22">
+        <v>1</v>
+      </c>
+      <c r="K35" s="22">
         <f>K34</f>
         <v>1</v>
       </c>
-      <c r="L35" s="26">
+      <c r="L35" s="22">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M35" s="26">
-        <v>1</v>
-      </c>
-      <c r="N35" s="26"/>
+      <c r="M35" s="22">
+        <v>1</v>
+      </c>
+      <c r="N35" s="22"/>
     </row>
     <row r="36" ht="16" spans="4:14">
-      <c r="D36" s="26" t="s">
+      <c r="D36" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="E36" s="26"/>
-      <c r="F36" s="27" t="s">
+      <c r="E36" s="22"/>
+      <c r="F36" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="G36" s="26" t="s">
+      <c r="G36" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="H36" s="26" t="s">
+      <c r="H36" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="I36" s="26" t="s">
+      <c r="I36" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="J36" s="26">
-        <v>1</v>
-      </c>
-      <c r="K36" s="26">
+      <c r="J36" s="22">
+        <v>1</v>
+      </c>
+      <c r="K36" s="22">
         <f>K35</f>
         <v>1</v>
       </c>
-      <c r="L36" s="26">
+      <c r="L36" s="22">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M36" s="26">
-        <v>1</v>
-      </c>
-      <c r="N36" s="26"/>
+      <c r="M36" s="22">
+        <v>1</v>
+      </c>
+      <c r="N36" s="22"/>
     </row>
     <row r="37" ht="16" spans="4:14">
-      <c r="D37" s="29" t="s">
+      <c r="D37" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="E37" s="29"/>
-      <c r="F37" s="30" t="s">
+      <c r="E37" s="25"/>
+      <c r="F37" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="G37" s="29" t="s">
+      <c r="G37" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="H37" s="29" t="s">
+      <c r="H37" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="I37" s="29" t="s">
+      <c r="I37" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="J37" s="29">
-        <v>1</v>
-      </c>
-      <c r="K37" s="29">
+      <c r="J37" s="25">
+        <v>1</v>
+      </c>
+      <c r="K37" s="25">
         <v>1.1</v>
       </c>
-      <c r="L37" s="29">
+      <c r="L37" s="25">
         <v>0.01</v>
       </c>
-      <c r="M37" s="29">
+      <c r="M37" s="25">
         <v>3</v>
       </c>
-      <c r="N37" s="26"/>
+      <c r="N37" s="22"/>
     </row>
     <row r="38" spans="4:14">
-      <c r="D38" s="29" t="s">
+      <c r="D38" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="E38" s="29"/>
-      <c r="F38" s="31" t="s">
+      <c r="E38" s="25"/>
+      <c r="F38" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="G38" s="29" t="s">
+      <c r="G38" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="H38" s="29" t="s">
+      <c r="H38" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="I38" s="29" t="s">
+      <c r="I38" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="J38" s="29">
-        <v>1</v>
-      </c>
-      <c r="K38" s="29">
+      <c r="J38" s="25">
+        <v>1</v>
+      </c>
+      <c r="K38" s="25">
         <v>1.1</v>
       </c>
-      <c r="L38" s="29">
+      <c r="L38" s="25">
         <v>0.01</v>
       </c>
-      <c r="M38" s="29">
+      <c r="M38" s="25">
         <v>3</v>
       </c>
-      <c r="N38" s="26"/>
+      <c r="N38" s="22"/>
     </row>
     <row r="39" ht="16" spans="4:14">
-      <c r="D39" s="32"/>
-      <c r="E39" s="32"/>
-      <c r="F39" s="33"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="32"/>
-      <c r="I39" s="32"/>
-      <c r="J39" s="32"/>
-      <c r="K39" s="32"/>
-      <c r="L39" s="32"/>
-      <c r="M39" s="32"/>
-      <c r="N39" s="32"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="28"/>
+      <c r="N39" s="28"/>
     </row>
     <row r="40" ht="16" spans="4:14">
-      <c r="D40" s="32"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="32"/>
-      <c r="J40" s="32"/>
-      <c r="K40" s="32"/>
-      <c r="L40" s="32"/>
-      <c r="M40" s="32"/>
-      <c r="N40" s="32"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="28"/>
     </row>
     <row r="41" ht="16" spans="4:14">
-      <c r="D41" s="32"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="32"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="32"/>
-      <c r="L41" s="32"/>
-      <c r="M41" s="32"/>
-      <c r="N41" s="32"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="28"/>
+      <c r="J41" s="28"/>
+      <c r="K41" s="28"/>
+      <c r="L41" s="28"/>
+      <c r="M41" s="28"/>
+      <c r="N41" s="28"/>
     </row>
     <row r="42" ht="16" spans="4:14">
-      <c r="D42" s="32"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
-      <c r="I42" s="32"/>
-      <c r="J42" s="32"/>
-      <c r="K42" s="32"/>
-      <c r="L42" s="32"/>
-      <c r="M42" s="32"/>
-      <c r="N42" s="32"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="28"/>
+      <c r="N42" s="28"/>
     </row>
     <row r="43" ht="16" spans="4:14">
-      <c r="D43" s="32"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="34"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="32"/>
-      <c r="J43" s="32"/>
-      <c r="K43" s="32"/>
-      <c r="L43" s="32"/>
-      <c r="M43" s="32"/>
-      <c r="N43" s="32"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="28"/>
+      <c r="N43" s="28"/>
     </row>
     <row r="44" spans="4:14">
       <c r="D44" s="1"/>
@@ -4294,20 +4284,20 @@
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
-      <c r="N44" s="32"/>
+      <c r="N44" s="28"/>
     </row>
     <row r="45" spans="4:14">
-      <c r="D45" s="32"/>
-      <c r="E45" s="32"/>
-      <c r="F45" s="35"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32"/>
-      <c r="I45" s="32"/>
-      <c r="J45" s="32"/>
-      <c r="K45" s="32"/>
-      <c r="L45" s="32"/>
-      <c r="M45" s="32"/>
-      <c r="N45" s="32"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="28"/>
+      <c r="J45" s="28"/>
+      <c r="K45" s="28"/>
+      <c r="L45" s="28"/>
+      <c r="M45" s="28"/>
+      <c r="N45" s="28"/>
     </row>
     <row r="46" spans="4:14">
       <c r="D46" s="1"/>
@@ -4320,7 +4310,7 @@
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
-      <c r="N46" s="32"/>
+      <c r="N46" s="28"/>
     </row>
     <row r="47" spans="4:14">
       <c r="D47" s="1"/>
@@ -4333,7 +4323,7 @@
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
-      <c r="N47" s="32"/>
+      <c r="N47" s="28"/>
     </row>
     <row r="48" spans="4:14">
       <c r="D48" s="1"/>
@@ -4346,55 +4336,55 @@
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
-      <c r="N48" s="32"/>
+      <c r="N48" s="28"/>
     </row>
     <row r="49" spans="4:14">
-      <c r="N49" s="26"/>
+      <c r="N49" s="22"/>
     </row>
     <row r="50" spans="4:14">
-      <c r="N50" s="26"/>
+      <c r="N50" s="22"/>
     </row>
     <row r="51" spans="4:14">
-      <c r="N51" s="26"/>
+      <c r="N51" s="22"/>
     </row>
     <row r="52" spans="4:14">
-      <c r="D52" s="26"/>
-      <c r="E52" s="26"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="26"/>
-      <c r="H52" s="26"/>
-      <c r="I52" s="26"/>
-      <c r="J52" s="26"/>
-      <c r="K52" s="26"/>
-      <c r="L52" s="26"/>
-      <c r="M52" s="26"/>
-      <c r="N52" s="26"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="22"/>
+      <c r="J52" s="22"/>
+      <c r="K52" s="22"/>
+      <c r="L52" s="22"/>
+      <c r="M52" s="22"/>
+      <c r="N52" s="22"/>
     </row>
     <row r="53" spans="4:14">
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
-      <c r="G53" s="26"/>
-      <c r="H53" s="26"/>
-      <c r="I53" s="26"/>
-      <c r="J53" s="26"/>
-      <c r="K53" s="26"/>
-      <c r="L53" s="26"/>
-      <c r="M53" s="26"/>
-      <c r="N53" s="26"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="22"/>
+      <c r="I53" s="22"/>
+      <c r="J53" s="22"/>
+      <c r="K53" s="22"/>
+      <c r="L53" s="22"/>
+      <c r="M53" s="22"/>
+      <c r="N53" s="22"/>
     </row>
     <row r="54" spans="4:14">
-      <c r="D54" s="26"/>
-      <c r="E54" s="26"/>
-      <c r="F54" s="26"/>
-      <c r="G54" s="26"/>
-      <c r="H54" s="26"/>
-      <c r="I54" s="26"/>
-      <c r="J54" s="26"/>
-      <c r="K54" s="26"/>
-      <c r="L54" s="26"/>
-      <c r="M54" s="26"/>
-      <c r="N54" s="26"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="22"/>
+      <c r="H54" s="22"/>
+      <c r="I54" s="22"/>
+      <c r="J54" s="22"/>
+      <c r="K54" s="22"/>
+      <c r="L54" s="22"/>
+      <c r="M54" s="22"/>
+      <c r="N54" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4685,7 +4675,7 @@
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1">
-        <v>-0.25</v>
+        <v>-0.1</v>
       </c>
       <c r="N28" s="1"/>
       <c r="O28" s="1">
@@ -4821,7 +4811,7 @@
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1">
-        <v>-0.25</v>
+        <v>-0.1</v>
       </c>
       <c r="N37" s="1"/>
       <c r="O37" s="1">
@@ -5188,8 +5178,8 @@
       <c r="M70" s="15"/>
       <c r="N70" s="15"/>
       <c r="O70" s="15"/>
-      <c r="P70" s="16"/>
-      <c r="Q70" s="16"/>
+      <c r="P70" s="15"/>
+      <c r="Q70" s="15"/>
       <c r="T70" s="1"/>
     </row>
     <row r="71" spans="7:20">
@@ -5199,7 +5189,7 @@
       <c r="H71" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="I71" s="17" t="s">
+      <c r="I71" s="16" t="s">
         <v>4</v>
       </c>
       <c r="J71" s="15" t="s">
@@ -5217,13 +5207,13 @@
       <c r="N71" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="O71" s="18" t="s">
+      <c r="O71" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="P71" s="19" t="s">
+      <c r="P71" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="Q71" s="19" t="s">
+      <c r="Q71" s="13" t="s">
         <v>65</v>
       </c>
     </row>
@@ -5234,29 +5224,29 @@
       <c r="H72" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="I72" s="20">
+      <c r="I72" s="17">
         <v>2019</v>
       </c>
-      <c r="J72" s="21">
+      <c r="J72" s="18">
         <v>-1</v>
       </c>
       <c r="K72" s="13"/>
-      <c r="L72" s="22" t="s">
+      <c r="L72" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="M72" s="23" t="s">
+      <c r="M72" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="N72" s="22" t="s">
+      <c r="N72" s="19" t="s">
         <v>74</v>
       </c>
       <c r="O72" s="13">
         <v>10</v>
       </c>
-      <c r="P72" s="19">
+      <c r="P72" s="13">
         <v>0</v>
       </c>
-      <c r="Q72" s="19">
+      <c r="Q72" s="13">
         <v>3</v>
       </c>
     </row>
@@ -5266,12 +5256,12 @@
       <c r="I73" s="13"/>
       <c r="J73" s="13"/>
       <c r="K73" s="13"/>
-      <c r="L73" s="18"/>
-      <c r="M73" s="18"/>
-      <c r="N73" s="18"/>
-      <c r="O73" s="18"/>
-      <c r="P73" s="18"/>
-      <c r="Q73" s="18"/>
+      <c r="L73" s="13"/>
+      <c r="M73" s="13"/>
+      <c r="N73" s="13"/>
+      <c r="O73" s="13"/>
+      <c r="P73" s="13"/>
+      <c r="Q73" s="13"/>
     </row>
     <row r="80" spans="7:20">
       <c r="G80" s="3"/>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="7"/>
+    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
@@ -245,7 +245,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="149">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -493,12 +493,6 @@
     <t>UC_CAP~RHS</t>
   </si>
   <si>
-    <t>UC_RHSTS</t>
-  </si>
-  <si>
-    <t>UC_RHSTS~0</t>
-  </si>
-  <si>
     <t>UC_Grow_LI</t>
   </si>
   <si>
@@ -566,6 +560,12 @@
   </si>
   <si>
     <t>MINBatMaterials_COB_direct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original : </t>
+  </si>
+  <si>
+    <t>RHSTS</t>
   </si>
   <si>
     <t>UC_Grow_Recy1</t>
@@ -914,23 +914,23 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
-      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -1461,10 +1461,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1965,7 +1965,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="str">
-        <f>G11</f>
+        <f xml:space="preserve">G11</f>
         <v>en*hbatt*, Util_Rep_Batt*</v>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
         <v>3</v>
       </c>
       <c r="G13" t="str">
-        <f>G21</f>
+        <f xml:space="preserve">G21</f>
         <v>en*hbatt*, Util_Rep_Batt*</v>
       </c>
       <c r="H13">
@@ -1986,14 +1986,14 @@
     </row>
     <row r="14" spans="2:8">
       <c r="D14" t="str">
-        <f>D13</f>
+        <f xml:space="preserve">D13</f>
         <v>FIXOM</v>
       </c>
       <c r="F14">
         <v>2</v>
       </c>
       <c r="G14" t="str">
-        <f>G13</f>
+        <f xml:space="preserve">G13</f>
         <v>en*hbatt*, Util_Rep_Batt*</v>
       </c>
       <c r="H14">
@@ -2028,7 +2028,7 @@
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
-        <f>G12</f>
+        <f xml:space="preserve">G12</f>
         <v>en*hbatt*, Util_Rep_Batt*</v>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="D5" s="32"/>
       <c r="E5" s="32"/>
-      <c r="F5" s="22"/>
+      <c r="F5" s="21"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
@@ -2276,13 +2276,13 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="21" t="s">
         <v>39</v>
       </c>
       <c r="D13" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="21">
         <v>2</v>
       </c>
     </row>
@@ -2290,13 +2290,13 @@
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="21" t="s">
         <v>40</v>
       </c>
       <c r="D14" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="21">
         <v>0</v>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       <c r="D15" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="21">
         <v>0</v>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       <c r="E17" s="39">
         <v>0.2</v>
       </c>
-      <c r="F17" s="22"/>
+      <c r="F17" s="21"/>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
@@ -2356,7 +2356,7 @@
       <c r="E18" s="39">
         <v>0.2</v>
       </c>
-      <c r="F18" s="22"/>
+      <c r="F18" s="21"/>
     </row>
     <row r="19" ht="16" spans="2:6">
       <c r="B19" t="s">
@@ -2371,7 +2371,7 @@
       <c r="E19" s="39">
         <v>0.2</v>
       </c>
-      <c r="F19" s="22"/>
+      <c r="F19" s="21"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
@@ -2386,7 +2386,7 @@
       <c r="E20" s="39">
         <v>0.5</v>
       </c>
-      <c r="F20" s="22"/>
+      <c r="F20" s="21"/>
     </row>
     <row r="21" ht="16" spans="2:6">
       <c r="B21" t="s">
@@ -2401,7 +2401,7 @@
       <c r="E21" s="39">
         <v>0.8</v>
       </c>
-      <c r="F21" s="22"/>
+      <c r="F21" s="21"/>
     </row>
     <row r="22" ht="16" spans="2:6">
       <c r="B22" t="s">
@@ -2414,37 +2414,37 @@
         <v>43</v>
       </c>
       <c r="E22" s="32"/>
-      <c r="F22" s="22"/>
+      <c r="F22" s="21"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="21" t="s">
         <v>39</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="22">
-        <v>1</v>
-      </c>
-      <c r="F23" s="22"/>
+      <c r="E23" s="21">
+        <v>1</v>
+      </c>
+      <c r="F23" s="21"/>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="21" t="s">
         <v>44</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="22">
-        <v>1</v>
-      </c>
-      <c r="F24" s="22"/>
+      <c r="E24" s="21">
+        <v>1</v>
+      </c>
+      <c r="F24" s="21"/>
     </row>
     <row r="25" ht="16" spans="2:6">
       <c r="B25" t="s">
@@ -2456,10 +2456,10 @@
       <c r="D25" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="22">
-        <v>1</v>
-      </c>
-      <c r="F25" s="22"/>
+      <c r="E25" s="21">
+        <v>1</v>
+      </c>
+      <c r="F25" s="21"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
@@ -2474,7 +2474,7 @@
       <c r="E26" s="32">
         <v>0.05</v>
       </c>
-      <c r="F26" s="22"/>
+      <c r="F26" s="21"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="40" t="s">
@@ -2489,10 +2489,10 @@
       <c r="E27" s="41">
         <v>2020</v>
       </c>
-      <c r="F27" s="22"/>
+      <c r="F27" s="21"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="21" t="s">
         <v>46</v>
       </c>
       <c r="D28" s="41" t="s">
@@ -2501,31 +2501,31 @@
       <c r="E28" s="25">
         <v>2020</v>
       </c>
-      <c r="F28" s="22"/>
+      <c r="F28" s="21"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
     </row>
     <row r="38" spans="3:5">
       <c r="C38" s="1"/>
@@ -3535,246 +3535,246 @@
       <c r="K8" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="L8" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="M8" s="20" t="s">
-        <v>83</v>
+      <c r="L8" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="M8" s="21" t="s">
+        <v>65</v>
       </c>
       <c r="N8" s="20" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="9" spans="2:14">
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="H9" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="I9" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="I9" s="21" t="s">
-        <v>88</v>
-      </c>
       <c r="J9">
         <v>1</v>
       </c>
-      <c r="K9" s="21">
+      <c r="K9" s="22">
         <v>1.25</v>
       </c>
       <c r="L9">
         <v>0.05</v>
       </c>
-      <c r="M9" s="21">
-        <v>1</v>
-      </c>
-      <c r="N9" s="21"/>
+      <c r="M9" s="22">
+        <v>1</v>
+      </c>
+      <c r="N9" s="22"/>
     </row>
     <row r="10" spans="2:14">
-      <c r="D10" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="21" t="s">
+      <c r="D10" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="H10" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="I10" s="21" t="s">
-        <v>88</v>
-      </c>
       <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10" s="21">
+      <c r="K10" s="22">
         <v>1.11</v>
       </c>
       <c r="L10">
         <v>0.05</v>
       </c>
-      <c r="M10" s="21">
-        <v>1</v>
-      </c>
-      <c r="N10" s="21"/>
+      <c r="M10" s="22">
+        <v>1</v>
+      </c>
+      <c r="N10" s="22"/>
     </row>
     <row r="11" spans="2:14">
-      <c r="D11" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="G11" s="21" t="s">
+      <c r="D11" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="H11" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="I11" s="21" t="s">
-        <v>88</v>
-      </c>
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11" s="21">
+      <c r="K11" s="22">
         <v>1.15</v>
       </c>
       <c r="L11">
         <v>0.08</v>
       </c>
-      <c r="M11" s="21">
-        <v>1</v>
-      </c>
-      <c r="N11" s="21"/>
+      <c r="M11" s="22">
+        <v>1</v>
+      </c>
+      <c r="N11" s="22"/>
     </row>
     <row r="12" ht="16" spans="2:14">
-      <c r="D12" s="21" t="s">
-        <v>93</v>
+      <c r="D12" s="22" t="s">
+        <v>91</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G12" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="H12" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="I12" s="21" t="s">
-        <v>88</v>
-      </c>
       <c r="J12">
         <v>1</v>
       </c>
-      <c r="K12" s="21">
+      <c r="K12" s="22">
         <v>1.12</v>
       </c>
       <c r="L12">
         <v>0.03</v>
       </c>
-      <c r="M12" s="21">
-        <v>1</v>
-      </c>
-      <c r="N12" s="21"/>
+      <c r="M12" s="22">
+        <v>1</v>
+      </c>
+      <c r="N12" s="22"/>
     </row>
     <row r="13" spans="2:14">
-      <c r="D13" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="G13" s="21" t="s">
+      <c r="D13" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="H13" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="I13" s="21" t="s">
-        <v>88</v>
-      </c>
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13" s="21">
+      <c r="K13" s="22">
         <v>1.2</v>
       </c>
       <c r="L13">
         <v>0.1</v>
       </c>
-      <c r="M13" s="21">
-        <v>1</v>
-      </c>
-      <c r="N13" s="21"/>
+      <c r="M13" s="22">
+        <v>1</v>
+      </c>
+      <c r="N13" s="22"/>
     </row>
     <row r="14" spans="2:14">
-      <c r="D14" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="G14" s="21" t="s">
+      <c r="D14" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="I14" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="H14" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="I14" s="21" t="s">
-        <v>88</v>
-      </c>
       <c r="J14">
         <v>1</v>
       </c>
-      <c r="K14" s="21">
+      <c r="K14" s="22">
         <v>1.06</v>
       </c>
       <c r="L14">
         <v>0.15</v>
       </c>
-      <c r="M14" s="21">
-        <v>1</v>
-      </c>
-      <c r="N14" s="21"/>
+      <c r="M14" s="22">
+        <v>1</v>
+      </c>
+      <c r="N14" s="22"/>
     </row>
     <row r="15" spans="2:14">
-      <c r="D15" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="G15" s="21" t="s">
+      <c r="D15" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="I15" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="H15" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="I15" s="21" t="s">
-        <v>88</v>
-      </c>
       <c r="J15">
         <v>1</v>
       </c>
-      <c r="K15" s="21">
+      <c r="K15" s="22">
         <v>1.06</v>
       </c>
       <c r="L15">
         <v>0.3</v>
       </c>
-      <c r="M15" s="21">
-        <v>1</v>
-      </c>
-      <c r="N15" s="21"/>
+      <c r="M15" s="22">
+        <v>1</v>
+      </c>
+      <c r="N15" s="22"/>
     </row>
     <row r="16" ht="16" spans="2:14">
-      <c r="D16" s="21" t="s">
-        <v>101</v>
+      <c r="D16" s="22" t="s">
+        <v>99</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G16" t="str">
-        <f>G15</f>
+        <f xml:space="preserve">G15</f>
         <v>CAP,GROWTH</v>
       </c>
       <c r="H16" t="str">
-        <f>H15</f>
+        <f xml:space="preserve">H15</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I16" s="21" t="s">
-        <v>88</v>
+      <c r="I16" s="22" t="s">
+        <v>86</v>
       </c>
       <c r="J16">
-        <f t="shared" ref="J16:L16" si="0">J12</f>
+        <f t="shared" ref="J16:L16" si="0" xml:space="preserve">J12</f>
         <v>1</v>
       </c>
       <c r="K16">
@@ -3786,27 +3786,27 @@
         <v>0.03</v>
       </c>
       <c r="M16">
-        <f>M15</f>
+        <f xml:space="preserve">M15</f>
         <v>1</v>
       </c>
     </row>
     <row r="17" ht="16" spans="4:14">
-      <c r="D17" s="21" t="s">
-        <v>103</v>
+      <c r="D17" s="22" t="s">
+        <v>101</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G17" t="str">
-        <f t="shared" ref="G17:M17" si="1">G16</f>
+        <f t="shared" ref="G17:M17" si="1" xml:space="preserve">G16</f>
         <v>CAP,GROWTH</v>
       </c>
       <c r="H17" t="str">
         <f t="shared" si="1"/>
         <v>2025, 2150</v>
       </c>
-      <c r="I17" s="21" t="s">
-        <v>88</v>
+      <c r="I17" s="22" t="s">
+        <v>86</v>
       </c>
       <c r="J17">
         <f t="shared" si="1"/>
@@ -3826,22 +3826,22 @@
       </c>
     </row>
     <row r="18" ht="16" spans="4:14">
-      <c r="D18" s="21" t="s">
-        <v>105</v>
+      <c r="D18" s="22" t="s">
+        <v>103</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G18" t="str">
-        <f>G17</f>
+        <f xml:space="preserve">G17</f>
         <v>CAP,GROWTH</v>
       </c>
       <c r="H18" t="str">
-        <f>H17</f>
+        <f xml:space="preserve">H17</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I18" s="21" t="s">
-        <v>88</v>
+      <c r="I18" s="22" t="s">
+        <v>86</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -3856,295 +3856,303 @@
         <v>1</v>
       </c>
     </row>
+    <row r="25" spans="4:14">
+      <c r="K25" t="s">
+        <v>105</v>
+      </c>
+      <c r="L25" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
     <row r="27" spans="4:14">
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="22"/>
-      <c r="N27" s="22"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="21"/>
+      <c r="M27" s="21"/>
+      <c r="N27" s="21"/>
     </row>
     <row r="28" spans="4:14">
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22" t="s">
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="22"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="21"/>
     </row>
     <row r="29" spans="4:14">
-      <c r="D29" s="22" t="s">
+      <c r="D29" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E29" s="22" t="s">
+      <c r="E29" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="F29" s="22" t="s">
+      <c r="F29" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="22" t="s">
+      <c r="G29" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="H29" s="22" t="s">
+      <c r="H29" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="I29" s="22" t="s">
+      <c r="I29" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="J29" s="22" t="s">
+      <c r="J29" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="K29" s="22" t="s">
+      <c r="K29" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="L29" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="M29" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="N29" s="22" t="s">
+      <c r="L29" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="M29" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N29" s="21" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="30" ht="16" spans="4:14">
-      <c r="D30" s="22" t="s">
+      <c r="D30" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="22"/>
+      <c r="E30" s="21"/>
       <c r="F30" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="G30" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="H30" s="22" t="s">
+      <c r="G30" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="H30" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="I30" s="22" t="s">
+      <c r="I30" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="22">
-        <v>1</v>
-      </c>
-      <c r="K30" s="22">
-        <v>1</v>
-      </c>
-      <c r="L30" s="22">
+      <c r="J30" s="21">
+        <v>1</v>
+      </c>
+      <c r="K30" s="21">
+        <v>1</v>
+      </c>
+      <c r="L30" s="21">
         <v>0.01</v>
       </c>
-      <c r="M30" s="22">
-        <v>1</v>
-      </c>
-      <c r="N30" s="22"/>
+      <c r="M30" s="21">
+        <v>1</v>
+      </c>
+      <c r="N30" s="21"/>
     </row>
     <row r="31" ht="16" spans="4:14">
-      <c r="D31" s="22" t="s">
+      <c r="D31" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="22"/>
+      <c r="E31" s="21"/>
       <c r="F31" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="G31" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="H31" s="22" t="s">
+      <c r="G31" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="H31" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="I31" s="22" t="s">
+      <c r="I31" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="J31" s="22">
-        <v>1</v>
-      </c>
-      <c r="K31" s="22">
-        <v>1</v>
-      </c>
-      <c r="L31" s="22">
-        <f t="shared" ref="L31:L36" si="2">L30</f>
+      <c r="J31" s="21">
+        <v>1</v>
+      </c>
+      <c r="K31" s="21">
+        <v>1</v>
+      </c>
+      <c r="L31" s="21">
+        <f t="shared" ref="L31:L36" si="2" xml:space="preserve">L30</f>
         <v>0.01</v>
       </c>
-      <c r="M31" s="22">
-        <v>1</v>
-      </c>
-      <c r="N31" s="22"/>
+      <c r="M31" s="21">
+        <v>1</v>
+      </c>
+      <c r="N31" s="21"/>
     </row>
     <row r="32" ht="16" spans="4:14">
-      <c r="D32" s="22" t="s">
+      <c r="D32" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="E32" s="22"/>
+      <c r="E32" s="21"/>
       <c r="F32" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="G32" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="H32" s="22" t="s">
+      <c r="G32" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="H32" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="I32" s="22" t="s">
+      <c r="I32" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="J32" s="22">
-        <v>1</v>
-      </c>
-      <c r="K32" s="22">
-        <v>1</v>
-      </c>
-      <c r="L32" s="22">
+      <c r="J32" s="21">
+        <v>1</v>
+      </c>
+      <c r="K32" s="21">
+        <v>1</v>
+      </c>
+      <c r="L32" s="21">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M32" s="22">
-        <v>1</v>
-      </c>
-      <c r="N32" s="22"/>
+      <c r="M32" s="21">
+        <v>1</v>
+      </c>
+      <c r="N32" s="21"/>
     </row>
     <row r="33" ht="16" spans="4:14">
-      <c r="D33" s="22" t="s">
+      <c r="D33" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="22"/>
+      <c r="E33" s="21"/>
       <c r="F33" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="G33" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="H33" s="22" t="s">
+      <c r="G33" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="H33" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="I33" s="22" t="s">
+      <c r="I33" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="J33" s="22">
-        <v>1</v>
-      </c>
-      <c r="K33" s="22">
-        <f>K32</f>
-        <v>1</v>
-      </c>
-      <c r="L33" s="22">
+      <c r="J33" s="21">
+        <v>1</v>
+      </c>
+      <c r="K33" s="21">
+        <f xml:space="preserve">K32</f>
+        <v>1</v>
+      </c>
+      <c r="L33" s="21">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M33" s="22">
-        <v>1</v>
-      </c>
-      <c r="N33" s="22"/>
+      <c r="M33" s="21">
+        <v>1</v>
+      </c>
+      <c r="N33" s="21"/>
     </row>
     <row r="34" ht="16" spans="4:14">
-      <c r="D34" s="22" t="s">
+      <c r="D34" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="E34" s="22"/>
+      <c r="E34" s="21"/>
       <c r="F34" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="G34" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="H34" s="22" t="s">
+      <c r="G34" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="H34" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="I34" s="22" t="s">
+      <c r="I34" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="J34" s="22">
-        <v>1</v>
-      </c>
-      <c r="K34" s="22">
-        <f>K33</f>
-        <v>1</v>
-      </c>
-      <c r="L34" s="22">
+      <c r="J34" s="21">
+        <v>1</v>
+      </c>
+      <c r="K34" s="21">
+        <f xml:space="preserve">K33</f>
+        <v>1</v>
+      </c>
+      <c r="L34" s="21">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M34" s="22">
-        <v>1</v>
-      </c>
-      <c r="N34" s="22"/>
+      <c r="M34" s="21">
+        <v>1</v>
+      </c>
+      <c r="N34" s="21"/>
     </row>
     <row r="35" ht="16" spans="4:14">
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="E35" s="22"/>
+      <c r="E35" s="21"/>
       <c r="F35" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="H35" s="22" t="s">
+      <c r="G35" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="H35" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="I35" s="22" t="s">
+      <c r="I35" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="J35" s="22">
-        <v>1</v>
-      </c>
-      <c r="K35" s="22">
-        <f>K34</f>
-        <v>1</v>
-      </c>
-      <c r="L35" s="22">
+      <c r="J35" s="21">
+        <v>1</v>
+      </c>
+      <c r="K35" s="21">
+        <f xml:space="preserve">K34</f>
+        <v>1</v>
+      </c>
+      <c r="L35" s="21">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M35" s="22">
-        <v>1</v>
-      </c>
-      <c r="N35" s="22"/>
+      <c r="M35" s="21">
+        <v>1</v>
+      </c>
+      <c r="N35" s="21"/>
     </row>
     <row r="36" ht="16" spans="4:14">
-      <c r="D36" s="22" t="s">
+      <c r="D36" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="E36" s="22"/>
+      <c r="E36" s="21"/>
       <c r="F36" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="G36" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="H36" s="22" t="s">
+      <c r="G36" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="H36" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="I36" s="22" t="s">
+      <c r="I36" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="J36" s="22">
-        <v>1</v>
-      </c>
-      <c r="K36" s="22">
-        <f>K35</f>
-        <v>1</v>
-      </c>
-      <c r="L36" s="22">
+      <c r="J36" s="21">
+        <v>1</v>
+      </c>
+      <c r="K36" s="21">
+        <f xml:space="preserve">K35</f>
+        <v>1</v>
+      </c>
+      <c r="L36" s="21">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M36" s="22">
-        <v>1</v>
-      </c>
-      <c r="N36" s="22"/>
+      <c r="M36" s="21">
+        <v>1</v>
+      </c>
+      <c r="N36" s="21"/>
     </row>
     <row r="37" ht="16" spans="4:14">
       <c r="D37" s="25" t="s">
@@ -4155,7 +4163,7 @@
         <v>124</v>
       </c>
       <c r="G37" s="25" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H37" s="25" t="s">
         <v>125</v>
@@ -4167,7 +4175,7 @@
         <v>1</v>
       </c>
       <c r="K37" s="25">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="L37" s="25">
         <v>0.01</v>
@@ -4175,7 +4183,7 @@
       <c r="M37" s="25">
         <v>3</v>
       </c>
-      <c r="N37" s="22"/>
+      <c r="N37" s="21"/>
     </row>
     <row r="38" spans="4:14">
       <c r="D38" s="25" t="s">
@@ -4186,7 +4194,7 @@
         <v>127</v>
       </c>
       <c r="G38" s="25" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H38" s="25" t="s">
         <v>125</v>
@@ -4198,7 +4206,7 @@
         <v>1</v>
       </c>
       <c r="K38" s="25">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="L38" s="25">
         <v>0.01</v>
@@ -4206,7 +4214,7 @@
       <c r="M38" s="25">
         <v>3</v>
       </c>
-      <c r="N38" s="22"/>
+      <c r="N38" s="21"/>
     </row>
     <row r="39" ht="16" spans="4:14">
       <c r="D39" s="28"/>
@@ -4339,52 +4347,52 @@
       <c r="N48" s="28"/>
     </row>
     <row r="49" spans="4:14">
-      <c r="N49" s="22"/>
+      <c r="N49" s="21"/>
     </row>
     <row r="50" spans="4:14">
-      <c r="N50" s="22"/>
+      <c r="N50" s="21"/>
     </row>
     <row r="51" spans="4:14">
-      <c r="N51" s="22"/>
+      <c r="N51" s="21"/>
     </row>
     <row r="52" spans="4:14">
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="21"/>
       <c r="F52" s="28"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="22"/>
-      <c r="I52" s="22"/>
-      <c r="J52" s="22"/>
-      <c r="K52" s="22"/>
-      <c r="L52" s="22"/>
-      <c r="M52" s="22"/>
-      <c r="N52" s="22"/>
+      <c r="G52" s="21"/>
+      <c r="H52" s="21"/>
+      <c r="I52" s="21"/>
+      <c r="J52" s="21"/>
+      <c r="K52" s="21"/>
+      <c r="L52" s="21"/>
+      <c r="M52" s="21"/>
+      <c r="N52" s="21"/>
     </row>
     <row r="53" spans="4:14">
-      <c r="D53" s="22"/>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="22"/>
-      <c r="H53" s="22"/>
-      <c r="I53" s="22"/>
-      <c r="J53" s="22"/>
-      <c r="K53" s="22"/>
-      <c r="L53" s="22"/>
-      <c r="M53" s="22"/>
-      <c r="N53" s="22"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="21"/>
+      <c r="I53" s="21"/>
+      <c r="J53" s="21"/>
+      <c r="K53" s="21"/>
+      <c r="L53" s="21"/>
+      <c r="M53" s="21"/>
+      <c r="N53" s="21"/>
     </row>
     <row r="54" spans="4:14">
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="22"/>
-      <c r="I54" s="22"/>
-      <c r="J54" s="22"/>
-      <c r="K54" s="22"/>
-      <c r="L54" s="22"/>
-      <c r="M54" s="22"/>
-      <c r="N54" s="22"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="21"/>
+      <c r="H54" s="21"/>
+      <c r="I54" s="21"/>
+      <c r="J54" s="21"/>
+      <c r="K54" s="21"/>
+      <c r="L54" s="21"/>
+      <c r="M54" s="21"/>
+      <c r="N54" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4402,6 +4410,7 @@
     <col min="7" max="7" width="25.3636363636364" customWidth="1"/>
     <col min="8" max="8" width="56.3636363636364" customWidth="1"/>
     <col min="9" max="9" width="43.7272727272727" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
     <col min="13" max="13" width="40.1818181818182" customWidth="1"/>
     <col min="14" max="14" width="12.8181818181818" customWidth="1"/>
     <col min="15" max="15" width="40.1818181818182" customWidth="1"/>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -245,7 +245,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="159">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -623,6 +623,36 @@
   </si>
   <si>
     <t>2019, 2150</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy9</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_LMO</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy10</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_NCA</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy11</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_NMC111</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy12</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_NMC532</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy13</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_NMC622</t>
   </si>
   <si>
     <t>UC_Grow_Recy14</t>
@@ -916,6 +946,12 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
@@ -929,14 +965,8 @@
       <name val="Tahoma"/>
       <charset val="0"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="0"/>
-    </font>
   </fonts>
-  <fills count="38">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -957,6 +987,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.35"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -964,6 +1000,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1301,7 +1343,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1325,16 +1367,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1343,90 +1385,90 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="43">
@@ -1458,6 +1500,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1466,30 +1509,27 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="53">
@@ -2162,12 +2202,12 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:13">
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="29" t="s">
         <v>23</v>
       </c>
       <c r="D5" s="32"/>
       <c r="E5" s="32"/>
-      <c r="F5" s="21"/>
+      <c r="F5" s="22"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
@@ -2276,13 +2316,13 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="22" t="s">
         <v>39</v>
       </c>
       <c r="D13" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="22">
         <v>2</v>
       </c>
     </row>
@@ -2290,13 +2330,13 @@
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="22" t="s">
         <v>40</v>
       </c>
       <c r="D14" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="22">
         <v>0</v>
       </c>
     </row>
@@ -2304,13 +2344,13 @@
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="24" t="s">
         <v>41</v>
       </c>
       <c r="D15" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="22">
         <v>0</v>
       </c>
     </row>
@@ -2341,7 +2381,7 @@
       <c r="E17" s="39">
         <v>0.2</v>
       </c>
-      <c r="F17" s="21"/>
+      <c r="F17" s="22"/>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
@@ -2356,7 +2396,7 @@
       <c r="E18" s="39">
         <v>0.2</v>
       </c>
-      <c r="F18" s="21"/>
+      <c r="F18" s="22"/>
     </row>
     <row r="19" ht="16" spans="2:6">
       <c r="B19" t="s">
@@ -2371,7 +2411,7 @@
       <c r="E19" s="39">
         <v>0.2</v>
       </c>
-      <c r="F19" s="21"/>
+      <c r="F19" s="22"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
@@ -2386,7 +2426,7 @@
       <c r="E20" s="39">
         <v>0.5</v>
       </c>
-      <c r="F20" s="21"/>
+      <c r="F20" s="22"/>
     </row>
     <row r="21" ht="16" spans="2:6">
       <c r="B21" t="s">
@@ -2401,7 +2441,7 @@
       <c r="E21" s="39">
         <v>0.8</v>
       </c>
-      <c r="F21" s="21"/>
+      <c r="F21" s="22"/>
     </row>
     <row r="22" ht="16" spans="2:6">
       <c r="B22" t="s">
@@ -2414,52 +2454,52 @@
         <v>43</v>
       </c>
       <c r="E22" s="32"/>
-      <c r="F22" s="21"/>
+      <c r="F22" s="22"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="22" t="s">
         <v>39</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="21">
-        <v>1</v>
-      </c>
-      <c r="F23" s="21"/>
+      <c r="E23" s="22">
+        <v>1</v>
+      </c>
+      <c r="F23" s="22"/>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="22" t="s">
         <v>44</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="21">
-        <v>1</v>
-      </c>
-      <c r="F24" s="21"/>
+      <c r="E24" s="22">
+        <v>1</v>
+      </c>
+      <c r="F24" s="22"/>
     </row>
     <row r="25" ht="16" spans="2:6">
       <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="24" t="s">
         <v>41</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="21">
-        <v>1</v>
-      </c>
-      <c r="F25" s="21"/>
+      <c r="E25" s="22">
+        <v>1</v>
+      </c>
+      <c r="F25" s="22"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
@@ -2474,7 +2514,7 @@
       <c r="E26" s="32">
         <v>0.05</v>
       </c>
-      <c r="F26" s="21"/>
+      <c r="F26" s="22"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="40" t="s">
@@ -2489,43 +2529,43 @@
       <c r="E27" s="41">
         <v>2020</v>
       </c>
-      <c r="F27" s="21"/>
+      <c r="F27" s="22"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="C28" s="21" t="s">
+      <c r="C28" s="22" t="s">
         <v>46</v>
       </c>
       <c r="D28" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="25">
+      <c r="E28" s="26">
         <v>2020</v>
       </c>
-      <c r="F28" s="21"/>
+      <c r="F28" s="22"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
     </row>
     <row r="38" spans="3:5">
       <c r="C38" s="1"/>
@@ -3506,257 +3546,257 @@
       </c>
     </row>
     <row r="4" spans="2:14">
-      <c r="H4" t="s">
+      <c r="H4" s="20" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="8" spans="2:14">
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="J8" s="20" t="s">
+      <c r="J8" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="K8" s="20" t="s">
+      <c r="K8" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="L8" s="21" t="s">
+      <c r="L8" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="M8" s="21" t="s">
+      <c r="M8" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="N8" s="20" t="s">
+      <c r="N8" s="21" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="9" spans="2:14">
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="G9" s="22" t="s">
+      <c r="G9" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="H9" s="22" t="s">
+      <c r="H9" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="I9" s="22" t="s">
+      <c r="I9" s="23" t="s">
         <v>86</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
-      <c r="K9" s="22">
+      <c r="K9" s="23">
         <v>1.25</v>
       </c>
       <c r="L9">
         <v>0.05</v>
       </c>
-      <c r="M9" s="22">
-        <v>1</v>
-      </c>
-      <c r="N9" s="22"/>
+      <c r="M9" s="23">
+        <v>1</v>
+      </c>
+      <c r="N9" s="23"/>
     </row>
     <row r="10" spans="2:14">
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="I10" s="22" t="s">
+      <c r="I10" s="23" t="s">
         <v>86</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10" s="22">
+      <c r="K10" s="23">
         <v>1.11</v>
       </c>
       <c r="L10">
         <v>0.05</v>
       </c>
-      <c r="M10" s="22">
-        <v>1</v>
-      </c>
-      <c r="N10" s="22"/>
+      <c r="M10" s="23">
+        <v>1</v>
+      </c>
+      <c r="N10" s="23"/>
     </row>
     <row r="11" spans="2:14">
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="H11" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="I11" s="22" t="s">
+      <c r="I11" s="23" t="s">
         <v>86</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11" s="22">
+      <c r="K11" s="23">
         <v>1.15</v>
       </c>
       <c r="L11">
         <v>0.08</v>
       </c>
-      <c r="M11" s="22">
-        <v>1</v>
-      </c>
-      <c r="N11" s="22"/>
+      <c r="M11" s="23">
+        <v>1</v>
+      </c>
+      <c r="N11" s="23"/>
     </row>
     <row r="12" ht="16" spans="2:14">
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="23" t="s">
         <v>91</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="23" t="s">
         <v>86</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
-      <c r="K12" s="22">
+      <c r="K12" s="23">
         <v>1.12</v>
       </c>
       <c r="L12">
         <v>0.03</v>
       </c>
-      <c r="M12" s="22">
-        <v>1</v>
-      </c>
-      <c r="N12" s="22"/>
+      <c r="M12" s="23">
+        <v>1</v>
+      </c>
+      <c r="N12" s="23"/>
     </row>
     <row r="13" spans="2:14">
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="I13" s="22" t="s">
+      <c r="I13" s="23" t="s">
         <v>86</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13" s="22">
+      <c r="K13" s="23">
         <v>1.2</v>
       </c>
       <c r="L13">
         <v>0.1</v>
       </c>
-      <c r="M13" s="22">
-        <v>1</v>
-      </c>
-      <c r="N13" s="22"/>
+      <c r="M13" s="23">
+        <v>1</v>
+      </c>
+      <c r="N13" s="23"/>
     </row>
     <row r="14" spans="2:14">
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="I14" s="22" t="s">
+      <c r="I14" s="23" t="s">
         <v>86</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
-      <c r="K14" s="22">
+      <c r="K14" s="23">
         <v>1.06</v>
       </c>
       <c r="L14">
         <v>0.15</v>
       </c>
-      <c r="M14" s="22">
-        <v>1</v>
-      </c>
-      <c r="N14" s="22"/>
+      <c r="M14" s="23">
+        <v>1</v>
+      </c>
+      <c r="N14" s="23"/>
     </row>
     <row r="15" spans="2:14">
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="G15" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="H15" s="22" t="s">
+      <c r="H15" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="I15" s="22" t="s">
+      <c r="I15" s="23" t="s">
         <v>86</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
-      <c r="K15" s="22">
+      <c r="K15" s="23">
         <v>1.06</v>
       </c>
       <c r="L15">
         <v>0.3</v>
       </c>
-      <c r="M15" s="22">
-        <v>1</v>
-      </c>
-      <c r="N15" s="22"/>
+      <c r="M15" s="23">
+        <v>1</v>
+      </c>
+      <c r="N15" s="23"/>
     </row>
     <row r="16" ht="16" spans="2:14">
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="23" t="s">
         <v>99</v>
       </c>
       <c r="F16" s="2" t="s">
@@ -3770,7 +3810,7 @@
         <f xml:space="preserve">H15</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I16" s="22" t="s">
+      <c r="I16" s="23" t="s">
         <v>86</v>
       </c>
       <c r="J16">
@@ -3791,7 +3831,7 @@
       </c>
     </row>
     <row r="17" ht="16" spans="4:14">
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="23" t="s">
         <v>101</v>
       </c>
       <c r="F17" s="2" t="s">
@@ -3805,7 +3845,7 @@
         <f t="shared" si="1"/>
         <v>2025, 2150</v>
       </c>
-      <c r="I17" s="22" t="s">
+      <c r="I17" s="23" t="s">
         <v>86</v>
       </c>
       <c r="J17">
@@ -3826,7 +3866,7 @@
       </c>
     </row>
     <row r="18" ht="16" spans="4:14">
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="23" t="s">
         <v>103</v>
       </c>
       <c r="F18" s="2" t="s">
@@ -3840,7 +3880,7 @@
         <f xml:space="preserve">H17</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I18" s="22" t="s">
+      <c r="I18" s="23" t="s">
         <v>86</v>
       </c>
       <c r="J18">
@@ -3865,421 +3905,534 @@
       </c>
     </row>
     <row r="27" spans="4:14">
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="21"/>
-      <c r="K27" s="21"/>
-      <c r="L27" s="21"/>
-      <c r="M27" s="21"/>
-      <c r="N27" s="21"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
     </row>
     <row r="28" spans="4:14">
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21" t="s">
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
     </row>
     <row r="29" spans="4:14">
-      <c r="D29" s="21" t="s">
+      <c r="D29" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="E29" s="21" t="s">
+      <c r="E29" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="F29" s="21" t="s">
+      <c r="F29" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="21" t="s">
+      <c r="G29" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="H29" s="21" t="s">
+      <c r="H29" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="I29" s="21" t="s">
+      <c r="I29" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="J29" s="21" t="s">
+      <c r="J29" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="K29" s="21" t="s">
+      <c r="K29" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="L29" s="21" t="s">
+      <c r="L29" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="M29" s="21" t="s">
+      <c r="M29" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="N29" s="21" t="s">
+      <c r="N29" s="22" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="30" ht="16" spans="4:14">
-      <c r="D30" s="21" t="s">
+      <c r="D30" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="21"/>
-      <c r="F30" s="23" t="s">
+      <c r="E30" s="22"/>
+      <c r="F30" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="G30" s="21" t="s">
+      <c r="G30" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="H30" s="21" t="s">
+      <c r="H30" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="I30" s="21" t="s">
+      <c r="I30" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="21">
-        <v>1</v>
-      </c>
-      <c r="K30" s="21">
-        <v>1</v>
-      </c>
-      <c r="L30" s="21">
+      <c r="J30" s="22">
+        <v>1</v>
+      </c>
+      <c r="K30" s="22">
+        <v>1</v>
+      </c>
+      <c r="L30" s="22">
         <v>0.01</v>
       </c>
-      <c r="M30" s="21">
-        <v>1</v>
-      </c>
-      <c r="N30" s="21"/>
+      <c r="M30" s="22">
+        <v>1</v>
+      </c>
+      <c r="N30" s="22"/>
     </row>
     <row r="31" ht="16" spans="4:14">
-      <c r="D31" s="21" t="s">
+      <c r="D31" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="21"/>
-      <c r="F31" s="24" t="s">
+      <c r="E31" s="22"/>
+      <c r="F31" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="G31" s="21" t="s">
+      <c r="G31" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="H31" s="21" t="s">
+      <c r="H31" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="I31" s="21" t="s">
+      <c r="I31" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="J31" s="21">
-        <v>1</v>
-      </c>
-      <c r="K31" s="21">
-        <v>1</v>
-      </c>
-      <c r="L31" s="21">
+      <c r="J31" s="22">
+        <v>1</v>
+      </c>
+      <c r="K31" s="22">
+        <v>1</v>
+      </c>
+      <c r="L31" s="22">
         <f t="shared" ref="L31:L36" si="2" xml:space="preserve">L30</f>
         <v>0.01</v>
       </c>
-      <c r="M31" s="21">
-        <v>1</v>
-      </c>
-      <c r="N31" s="21"/>
+      <c r="M31" s="22">
+        <v>1</v>
+      </c>
+      <c r="N31" s="22"/>
     </row>
     <row r="32" ht="16" spans="4:14">
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="E32" s="21"/>
-      <c r="F32" s="24" t="s">
+      <c r="E32" s="22"/>
+      <c r="F32" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="G32" s="21" t="s">
+      <c r="G32" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="H32" s="21" t="s">
+      <c r="H32" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="I32" s="21" t="s">
+      <c r="I32" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="J32" s="21">
-        <v>1</v>
-      </c>
-      <c r="K32" s="21">
-        <v>1</v>
-      </c>
-      <c r="L32" s="21">
+      <c r="J32" s="22">
+        <v>1</v>
+      </c>
+      <c r="K32" s="22">
+        <v>1</v>
+      </c>
+      <c r="L32" s="22">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M32" s="21">
-        <v>1</v>
-      </c>
-      <c r="N32" s="21"/>
+      <c r="M32" s="22">
+        <v>1</v>
+      </c>
+      <c r="N32" s="22"/>
     </row>
     <row r="33" ht="16" spans="4:14">
-      <c r="D33" s="21" t="s">
+      <c r="D33" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="21"/>
-      <c r="F33" s="23" t="s">
+      <c r="E33" s="22"/>
+      <c r="F33" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="G33" s="21" t="s">
+      <c r="G33" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="H33" s="21" t="s">
+      <c r="H33" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="I33" s="21" t="s">
+      <c r="I33" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="J33" s="21">
-        <v>1</v>
-      </c>
-      <c r="K33" s="21">
+      <c r="J33" s="22">
+        <v>1</v>
+      </c>
+      <c r="K33" s="22">
         <f xml:space="preserve">K32</f>
         <v>1</v>
       </c>
-      <c r="L33" s="21">
+      <c r="L33" s="22">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M33" s="21">
-        <v>1</v>
-      </c>
-      <c r="N33" s="21"/>
+      <c r="M33" s="22">
+        <v>1</v>
+      </c>
+      <c r="N33" s="22"/>
     </row>
     <row r="34" ht="16" spans="4:14">
-      <c r="D34" s="21" t="s">
+      <c r="D34" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="E34" s="21"/>
-      <c r="F34" s="23" t="s">
+      <c r="E34" s="22"/>
+      <c r="F34" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="G34" s="21" t="s">
+      <c r="G34" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="H34" s="21" t="s">
+      <c r="H34" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="I34" s="21" t="s">
+      <c r="I34" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="J34" s="21">
-        <v>1</v>
-      </c>
-      <c r="K34" s="21">
+      <c r="J34" s="22">
+        <v>1</v>
+      </c>
+      <c r="K34" s="22">
         <f xml:space="preserve">K33</f>
         <v>1</v>
       </c>
-      <c r="L34" s="21">
+      <c r="L34" s="22">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M34" s="21">
-        <v>1</v>
-      </c>
-      <c r="N34" s="21"/>
+      <c r="M34" s="22">
+        <v>1</v>
+      </c>
+      <c r="N34" s="22"/>
     </row>
     <row r="35" ht="16" spans="4:14">
-      <c r="D35" s="21" t="s">
+      <c r="D35" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="E35" s="21"/>
-      <c r="F35" s="23" t="s">
+      <c r="E35" s="22"/>
+      <c r="F35" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="21" t="s">
+      <c r="G35" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="H35" s="21" t="s">
+      <c r="H35" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="I35" s="21" t="s">
+      <c r="I35" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="J35" s="21">
-        <v>1</v>
-      </c>
-      <c r="K35" s="21">
+      <c r="J35" s="22">
+        <v>1</v>
+      </c>
+      <c r="K35" s="22">
         <f xml:space="preserve">K34</f>
         <v>1</v>
       </c>
-      <c r="L35" s="21">
+      <c r="L35" s="22">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M35" s="21">
-        <v>1</v>
-      </c>
-      <c r="N35" s="21"/>
+      <c r="M35" s="22">
+        <v>1</v>
+      </c>
+      <c r="N35" s="22"/>
     </row>
     <row r="36" ht="16" spans="4:14">
-      <c r="D36" s="21" t="s">
+      <c r="D36" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="E36" s="21"/>
-      <c r="F36" s="23" t="s">
+      <c r="E36" s="22"/>
+      <c r="F36" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="G36" s="21" t="s">
+      <c r="G36" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="H36" s="21" t="s">
+      <c r="H36" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="I36" s="21" t="s">
+      <c r="I36" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="J36" s="21">
-        <v>1</v>
-      </c>
-      <c r="K36" s="21">
+      <c r="J36" s="22">
+        <v>1</v>
+      </c>
+      <c r="K36" s="22">
         <f xml:space="preserve">K35</f>
         <v>1</v>
       </c>
-      <c r="L36" s="21">
+      <c r="L36" s="22">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M36" s="21">
-        <v>1</v>
-      </c>
-      <c r="N36" s="21"/>
+      <c r="M36" s="22">
+        <v>1</v>
+      </c>
+      <c r="N36" s="22"/>
     </row>
     <row r="37" ht="16" spans="4:14">
-      <c r="D37" s="25" t="s">
+      <c r="D37" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="E37" s="25"/>
-      <c r="F37" s="26" t="s">
+      <c r="E37" s="26"/>
+      <c r="F37" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="G37" s="25" t="s">
+      <c r="G37" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="H37" s="25" t="s">
+      <c r="H37" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="I37" s="25" t="s">
+      <c r="I37" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="J37" s="25">
-        <v>1</v>
-      </c>
-      <c r="K37" s="25">
-        <v>1</v>
-      </c>
-      <c r="L37" s="25">
-        <v>0.01</v>
-      </c>
-      <c r="M37" s="25">
+      <c r="J37" s="26">
+        <v>1</v>
+      </c>
+      <c r="K37" s="26">
+        <v>1</v>
+      </c>
+      <c r="L37" s="26">
+        <v>0</v>
+      </c>
+      <c r="M37" s="26">
         <v>3</v>
       </c>
-      <c r="N37" s="21"/>
-    </row>
-    <row r="38" spans="4:14">
-      <c r="D38" s="25" t="s">
+      <c r="N37" s="22"/>
+    </row>
+    <row r="38" ht="16" spans="4:14">
+      <c r="D38" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E38" s="25"/>
       <c r="F38" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="G38" s="25" t="s">
+      <c r="G38" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="H38" s="25" t="s">
+      <c r="H38" t="str">
+        <f xml:space="preserve">H37</f>
+        <v>2019, 2150</v>
+      </c>
+      <c r="I38" t="s">
+        <v>86</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="K38">
+        <v>1.1</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>3</v>
+      </c>
+      <c r="N38" s="22"/>
+    </row>
+    <row r="39" ht="16" spans="4:14">
+      <c r="D39" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="E39" s="29"/>
+      <c r="F39" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="G39" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="H39" t="str">
+        <f xml:space="preserve">H38</f>
+        <v>2019, 2150</v>
+      </c>
+      <c r="I39" s="29" t="str">
+        <f xml:space="preserve">I38</f>
+        <v>UP</v>
+      </c>
+      <c r="J39" s="29">
+        <f xml:space="preserve">J38</f>
+        <v>1</v>
+      </c>
+      <c r="K39" s="29">
+        <f xml:space="preserve">K38</f>
+        <v>1.1</v>
+      </c>
+      <c r="L39" s="29">
+        <f xml:space="preserve">L38</f>
+        <v>0</v>
+      </c>
+      <c r="M39" s="29">
+        <f xml:space="preserve">M38</f>
+        <v>3</v>
+      </c>
+      <c r="N39" s="29"/>
+    </row>
+    <row r="40" ht="16" spans="4:14">
+      <c r="D40" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="E40" s="29"/>
+      <c r="F40" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="G40" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="H40" t="str">
+        <f xml:space="preserve">H39</f>
+        <v>2019, 2150</v>
+      </c>
+      <c r="I40" s="29" t="str">
+        <f xml:space="preserve">I39</f>
+        <v>UP</v>
+      </c>
+      <c r="J40" s="29">
+        <f xml:space="preserve">J39</f>
+        <v>1</v>
+      </c>
+      <c r="K40" s="29">
+        <f xml:space="preserve">K39</f>
+        <v>1.1</v>
+      </c>
+      <c r="L40" s="29">
+        <f xml:space="preserve">L39</f>
+        <v>0</v>
+      </c>
+      <c r="M40" s="29">
+        <f xml:space="preserve">M39</f>
+        <v>3</v>
+      </c>
+      <c r="N40" s="29"/>
+    </row>
+    <row r="41" ht="16" spans="4:14">
+      <c r="D41" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E41" s="29"/>
+      <c r="F41" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G41" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="H41" t="str">
+        <f xml:space="preserve">H40</f>
+        <v>2019, 2150</v>
+      </c>
+      <c r="I41" s="29" t="str">
+        <f xml:space="preserve">I40</f>
+        <v>UP</v>
+      </c>
+      <c r="J41" s="29">
+        <f xml:space="preserve">J40</f>
+        <v>1</v>
+      </c>
+      <c r="K41" s="29">
+        <f xml:space="preserve">K40</f>
+        <v>1.1</v>
+      </c>
+      <c r="L41" s="29">
+        <f xml:space="preserve">L40</f>
+        <v>0</v>
+      </c>
+      <c r="M41" s="29">
+        <f xml:space="preserve">M40</f>
+        <v>3</v>
+      </c>
+      <c r="N41" s="29"/>
+    </row>
+    <row r="42" ht="16" spans="4:14">
+      <c r="D42" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F42" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="G42" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="H42" t="str">
+        <f xml:space="preserve">H41</f>
+        <v>2019, 2150</v>
+      </c>
+      <c r="I42" s="29" t="str">
+        <f xml:space="preserve">I41</f>
+        <v>UP</v>
+      </c>
+      <c r="J42" s="29">
+        <f xml:space="preserve">J41</f>
+        <v>1</v>
+      </c>
+      <c r="K42" s="29">
+        <f xml:space="preserve">K41</f>
+        <v>1.1</v>
+      </c>
+      <c r="L42" s="29">
+        <f xml:space="preserve">L41</f>
+        <v>0</v>
+      </c>
+      <c r="M42" s="29">
+        <f xml:space="preserve">M41</f>
+        <v>3</v>
+      </c>
+      <c r="N42" s="29"/>
+    </row>
+    <row r="43" spans="4:14">
+      <c r="D43" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="E43" s="26"/>
+      <c r="F43" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="G43" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="H43" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="I38" s="25" t="s">
+      <c r="I43" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="J38" s="25">
-        <v>1</v>
-      </c>
-      <c r="K38" s="25">
-        <v>1</v>
-      </c>
-      <c r="L38" s="25">
-        <v>0.01</v>
-      </c>
-      <c r="M38" s="25">
+      <c r="J43" s="26">
+        <v>1</v>
+      </c>
+      <c r="K43" s="26">
+        <v>1</v>
+      </c>
+      <c r="L43" s="26">
+        <v>0</v>
+      </c>
+      <c r="M43" s="26">
         <v>3</v>
       </c>
-      <c r="N38" s="21"/>
-    </row>
-    <row r="39" ht="16" spans="4:14">
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="29"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="28"/>
-      <c r="L39" s="28"/>
-      <c r="M39" s="28"/>
-      <c r="N39" s="28"/>
-    </row>
-    <row r="40" ht="16" spans="4:14">
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="28"/>
-      <c r="M40" s="28"/>
-      <c r="N40" s="28"/>
-    </row>
-    <row r="41" ht="16" spans="4:14">
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="28"/>
-      <c r="J41" s="28"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="28"/>
-      <c r="M41" s="28"/>
-      <c r="N41" s="28"/>
-    </row>
-    <row r="42" ht="16" spans="4:14">
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="28"/>
-      <c r="J42" s="28"/>
-      <c r="K42" s="28"/>
-      <c r="L42" s="28"/>
-      <c r="M42" s="28"/>
-      <c r="N42" s="28"/>
-    </row>
-    <row r="43" ht="16" spans="4:14">
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="28"/>
-      <c r="M43" s="28"/>
-      <c r="N43" s="28"/>
+      <c r="N43" s="29"/>
     </row>
     <row r="44" spans="4:14">
       <c r="D44" s="1"/>
@@ -4292,20 +4445,20 @@
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
-      <c r="N44" s="28"/>
+      <c r="N44" s="29"/>
     </row>
     <row r="45" spans="4:14">
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="29"/>
       <c r="F45" s="31"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="28"/>
-      <c r="J45" s="28"/>
-      <c r="K45" s="28"/>
-      <c r="L45" s="28"/>
-      <c r="M45" s="28"/>
-      <c r="N45" s="28"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29"/>
+      <c r="I45" s="29"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="29"/>
+      <c r="L45" s="29"/>
+      <c r="M45" s="29"/>
+      <c r="N45" s="29"/>
     </row>
     <row r="46" spans="4:14">
       <c r="D46" s="1"/>
@@ -4318,7 +4471,7 @@
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
-      <c r="N46" s="28"/>
+      <c r="N46" s="29"/>
     </row>
     <row r="47" spans="4:14">
       <c r="D47" s="1"/>
@@ -4331,7 +4484,7 @@
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
-      <c r="N47" s="28"/>
+      <c r="N47" s="29"/>
     </row>
     <row r="48" spans="4:14">
       <c r="D48" s="1"/>
@@ -4344,55 +4497,55 @@
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
-      <c r="N48" s="28"/>
+      <c r="N48" s="29"/>
     </row>
     <row r="49" spans="4:14">
-      <c r="N49" s="21"/>
+      <c r="N49" s="22"/>
     </row>
     <row r="50" spans="4:14">
-      <c r="N50" s="21"/>
+      <c r="N50" s="22"/>
     </row>
     <row r="51" spans="4:14">
-      <c r="N51" s="21"/>
+      <c r="N51" s="22"/>
     </row>
     <row r="52" spans="4:14">
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="21"/>
-      <c r="H52" s="21"/>
-      <c r="I52" s="21"/>
-      <c r="J52" s="21"/>
-      <c r="K52" s="21"/>
-      <c r="L52" s="21"/>
-      <c r="M52" s="21"/>
-      <c r="N52" s="21"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="22"/>
+      <c r="J52" s="22"/>
+      <c r="K52" s="22"/>
+      <c r="L52" s="22"/>
+      <c r="M52" s="22"/>
+      <c r="N52" s="22"/>
     </row>
     <row r="53" spans="4:14">
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="21"/>
-      <c r="H53" s="21"/>
-      <c r="I53" s="21"/>
-      <c r="J53" s="21"/>
-      <c r="K53" s="21"/>
-      <c r="L53" s="21"/>
-      <c r="M53" s="21"/>
-      <c r="N53" s="21"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="22"/>
+      <c r="I53" s="22"/>
+      <c r="J53" s="22"/>
+      <c r="K53" s="22"/>
+      <c r="L53" s="22"/>
+      <c r="M53" s="22"/>
+      <c r="N53" s="22"/>
     </row>
     <row r="54" spans="4:14">
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="21"/>
-      <c r="H54" s="21"/>
-      <c r="I54" s="21"/>
-      <c r="J54" s="21"/>
-      <c r="K54" s="21"/>
-      <c r="L54" s="21"/>
-      <c r="M54" s="21"/>
-      <c r="N54" s="21"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="22"/>
+      <c r="H54" s="22"/>
+      <c r="I54" s="22"/>
+      <c r="J54" s="22"/>
+      <c r="K54" s="22"/>
+      <c r="L54" s="22"/>
+      <c r="M54" s="22"/>
+      <c r="N54" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4438,7 +4591,7 @@
     <row r="12" spans="6:18">
       <c r="K12" s="1"/>
       <c r="L12" s="1" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -4488,10 +4641,10 @@
     </row>
     <row r="14" spans="6:18">
       <c r="F14" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="H14" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -4510,7 +4663,7 @@
     </row>
     <row r="15" spans="6:18">
       <c r="H15" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -4626,7 +4779,7 @@
     <row r="26" spans="6:18">
       <c r="K26" s="1"/>
       <c r="L26" s="1" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -4676,10 +4829,10 @@
     </row>
     <row r="28" ht="16" spans="6:18">
       <c r="F28" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -4698,7 +4851,7 @@
     </row>
     <row r="29" spans="6:18">
       <c r="H29" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -4764,7 +4917,7 @@
     <row r="35" spans="6:18">
       <c r="K35" s="1"/>
       <c r="L35" s="1" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
@@ -4812,10 +4965,10 @@
     </row>
     <row r="37" spans="6:18">
       <c r="F37" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="H37" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -4833,7 +4986,7 @@
     </row>
     <row r="38" spans="6:18">
       <c r="H38" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -4849,7 +5002,7 @@
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="4" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
@@ -4887,13 +5040,13 @@
         <v>59</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>4</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>25</v>
@@ -4945,7 +5098,7 @@
     <row r="53" ht="16" spans="6:44">
       <c r="F53" s="8"/>
       <c r="G53" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>110</v>
@@ -4958,13 +5111,13 @@
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="M53" s="11" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="O53" s="3">
         <v>10</v>
@@ -5034,7 +5187,7 @@
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="4" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
@@ -5050,13 +5203,13 @@
         <v>59</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="I62" s="7" t="s">
         <v>4</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>25</v>
@@ -5082,7 +5235,7 @@
     </row>
     <row r="63" ht="16" spans="6:44">
       <c r="G63" s="3" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>110</v>
@@ -5095,13 +5248,13 @@
       </c>
       <c r="K63" s="3"/>
       <c r="L63" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="M63" s="11" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="O63" s="3">
         <v>10</v>
@@ -5179,7 +5332,7 @@
       <c r="G70" s="13"/>
       <c r="H70" s="13"/>
       <c r="I70" s="14" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="J70" s="15"/>
       <c r="K70" s="15"/>
@@ -5196,13 +5349,13 @@
         <v>59</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="I71" s="16" t="s">
         <v>4</v>
       </c>
       <c r="J71" s="15" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="K71" s="13" t="s">
         <v>25</v>
@@ -5228,7 +5381,7 @@
     </row>
     <row r="72" ht="16" spans="7:20">
       <c r="G72" s="13" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="H72" s="13" t="s">
         <v>110</v>
@@ -5276,7 +5429,7 @@
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
       <c r="I80" s="4" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="J80" s="5"/>
       <c r="K80" s="5"/>
@@ -5292,13 +5445,13 @@
         <v>59</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="I81" s="7" t="s">
         <v>4</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>25</v>
@@ -5324,7 +5477,7 @@
     </row>
     <row r="82" ht="16" spans="7:17">
       <c r="G82" s="3" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>110</v>
@@ -5337,13 +5490,13 @@
       </c>
       <c r="K82" s="3"/>
       <c r="L82" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="M82" s="11" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="O82" s="3">
         <v>10</v>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -245,7 +245,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="171">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -659,6 +659,42 @@
   </si>
   <si>
     <t>EN_STG_4hBatt_NMC811</t>
+  </si>
+  <si>
+    <t>Cset_Set</t>
+  </si>
+  <si>
+    <t>UC_COMNET</t>
+  </si>
+  <si>
+    <t>UC_COMNET~RHS</t>
+  </si>
+  <si>
+    <t>UC_coalEmi1</t>
+  </si>
+  <si>
+    <t>ELCCO2Nc</t>
+  </si>
+  <si>
+    <t>COMNET,GROWTH</t>
+  </si>
+  <si>
+    <t>2040, 2150</t>
+  </si>
+  <si>
+    <t>UC_OilEmi2</t>
+  </si>
+  <si>
+    <t>ELCCO2No</t>
+  </si>
+  <si>
+    <t>UC_gasEmi3</t>
+  </si>
+  <si>
+    <t>ELCCO2Ng</t>
+  </si>
+  <si>
+    <t>2050, 2150</t>
   </si>
   <si>
     <t>~UC_T: LO</t>
@@ -944,7 +980,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -961,6 +996,7 @@
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -1471,7 +1507,7 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1501,13 +1537,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1518,6 +1556,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -2064,7 +2107,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="40">
+      <c r="F21" s="47">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -2202,12 +2245,12 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:13">
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="22"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="25"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
@@ -2222,19 +2265,19 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="33"/>
+      <c r="K6" s="40"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="34">
+      <c r="E7" s="41">
         <v>10</v>
       </c>
     </row>
@@ -2242,17 +2285,17 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="41">
         <v>7</v>
       </c>
-      <c r="L8" s="32"/>
-      <c r="M8" s="32"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="39"/>
     </row>
     <row r="9" ht="16" spans="2:13">
       <c r="B9" t="s">
@@ -2261,10 +2304,10 @@
       <c r="C9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="41">
         <v>10</v>
       </c>
     </row>
@@ -2272,17 +2315,17 @@
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="41">
         <v>8</v>
       </c>
-      <c r="K10" s="35"/>
-      <c r="L10" s="36"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="43"/>
     </row>
     <row r="11" ht="16" spans="2:13">
       <c r="B11" t="s">
@@ -2291,10 +2334,10 @@
       <c r="C11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="39">
         <v>1.5</v>
       </c>
     </row>
@@ -2305,10 +2348,10 @@
       <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="39">
         <v>1.5</v>
       </c>
     </row>
@@ -2316,13 +2359,13 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="25">
         <v>2</v>
       </c>
     </row>
@@ -2330,13 +2373,13 @@
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="25">
         <v>0</v>
       </c>
     </row>
@@ -2344,13 +2387,13 @@
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="25">
         <v>0</v>
       </c>
     </row>
@@ -2358,13 +2401,13 @@
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="37">
+      <c r="E16" s="44">
         <v>12</v>
       </c>
     </row>
@@ -2372,31 +2415,31 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="D17" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="46">
         <v>0.2</v>
       </c>
-      <c r="F17" s="22"/>
+      <c r="F17" s="25"/>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="D18" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="39">
+      <c r="E18" s="46">
         <v>0.2</v>
       </c>
-      <c r="F18" s="22"/>
+      <c r="F18" s="25"/>
     </row>
     <row r="19" ht="16" spans="2:6">
       <c r="B19" t="s">
@@ -2405,28 +2448,28 @@
       <c r="C19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="38" t="s">
+      <c r="D19" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="39">
+      <c r="E19" s="46">
         <v>0.2</v>
       </c>
-      <c r="F19" s="22"/>
+      <c r="F19" s="25"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="39">
+      <c r="E20" s="46">
         <v>0.5</v>
       </c>
-      <c r="F20" s="22"/>
+      <c r="F20" s="25"/>
     </row>
     <row r="21" ht="16" spans="2:6">
       <c r="B21" t="s">
@@ -2435,13 +2478,13 @@
       <c r="C21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="38" t="s">
+      <c r="D21" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="39">
+      <c r="E21" s="46">
         <v>0.8</v>
       </c>
-      <c r="F21" s="22"/>
+      <c r="F21" s="25"/>
     </row>
     <row r="22" ht="16" spans="2:6">
       <c r="B22" t="s">
@@ -2450,122 +2493,122 @@
       <c r="C22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="D22" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="32"/>
-      <c r="F22" s="22"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="25"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="38" t="s">
+      <c r="D23" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="22">
-        <v>1</v>
-      </c>
-      <c r="F23" s="22"/>
+      <c r="E23" s="25">
+        <v>1</v>
+      </c>
+      <c r="F23" s="25"/>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="D24" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="22">
-        <v>1</v>
-      </c>
-      <c r="F24" s="22"/>
+      <c r="E24" s="25">
+        <v>1</v>
+      </c>
+      <c r="F24" s="25"/>
     </row>
     <row r="25" ht="16" spans="2:6">
       <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C25" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="38" t="s">
+      <c r="D25" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="22">
-        <v>1</v>
-      </c>
-      <c r="F25" s="22"/>
+      <c r="E25" s="25">
+        <v>1</v>
+      </c>
+      <c r="F25" s="25"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="38" t="s">
+      <c r="D26" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="32">
+      <c r="E26" s="39">
         <v>0.05</v>
       </c>
-      <c r="F26" s="22"/>
+      <c r="F26" s="25"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C27" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="41" t="s">
+      <c r="D27" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="41">
+      <c r="E27" s="48">
         <v>2020</v>
       </c>
-      <c r="F27" s="22"/>
+      <c r="F27" s="25"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="41" t="s">
+      <c r="D28" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="28">
         <v>2020</v>
       </c>
-      <c r="F28" s="22"/>
+      <c r="F28" s="25"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
     </row>
     <row r="38" spans="3:5">
       <c r="C38" s="1"/>
@@ -2573,360 +2616,360 @@
       <c r="E38" s="1"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="42" t="s">
+      <c r="C54" s="49" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="42"/>
-      <c r="E56" s="42"/>
-      <c r="F56" s="42"/>
-      <c r="G56" s="42"/>
-      <c r="H56" s="42"/>
-      <c r="I56" s="42"/>
-      <c r="J56" s="42"/>
-      <c r="K56" s="42"/>
+      <c r="D56" s="49"/>
+      <c r="E56" s="49"/>
+      <c r="F56" s="49"/>
+      <c r="G56" s="49"/>
+      <c r="H56" s="49"/>
+      <c r="I56" s="49"/>
+      <c r="J56" s="49"/>
+      <c r="K56" s="49"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="42" t="s">
+      <c r="C57" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="42" t="s">
+      <c r="D57" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="42" t="s">
+      <c r="E57" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="F57" s="42" t="s">
+      <c r="F57" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="G57" s="42" t="s">
+      <c r="G57" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="42" t="s">
+      <c r="H57" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="42" t="s">
+      <c r="I57" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="J57" s="42" t="s">
+      <c r="J57" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="K57" s="42" t="s">
+      <c r="K57" s="49" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="42"/>
-      <c r="D58" s="42"/>
-      <c r="E58" s="42"/>
-      <c r="F58" s="42"/>
-      <c r="G58" s="42"/>
-      <c r="H58" s="42"/>
-      <c r="I58" s="42"/>
-      <c r="J58" s="42"/>
-      <c r="K58" s="42"/>
+      <c r="C58" s="49"/>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49"/>
+      <c r="G58" s="49"/>
+      <c r="H58" s="49"/>
+      <c r="I58" s="49"/>
+      <c r="J58" s="49"/>
+      <c r="K58" s="49"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="42"/>
-      <c r="D59" s="42"/>
-      <c r="E59" s="42"/>
-      <c r="F59" s="42"/>
-      <c r="G59" s="42"/>
-      <c r="H59" s="42"/>
-      <c r="I59" s="42"/>
-      <c r="J59" s="42"/>
-      <c r="K59" s="42"/>
+      <c r="C59" s="49"/>
+      <c r="D59" s="49"/>
+      <c r="E59" s="49"/>
+      <c r="F59" s="49"/>
+      <c r="G59" s="49"/>
+      <c r="H59" s="49"/>
+      <c r="I59" s="49"/>
+      <c r="J59" s="49"/>
+      <c r="K59" s="49"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="42"/>
-      <c r="D60" s="42"/>
-      <c r="E60" s="42"/>
-      <c r="F60" s="42"/>
-      <c r="G60" s="42"/>
-      <c r="H60" s="42"/>
-      <c r="I60" s="42"/>
-      <c r="J60" s="42"/>
-      <c r="K60" s="42"/>
+      <c r="C60" s="49"/>
+      <c r="D60" s="49"/>
+      <c r="E60" s="49"/>
+      <c r="F60" s="49"/>
+      <c r="G60" s="49"/>
+      <c r="H60" s="49"/>
+      <c r="I60" s="49"/>
+      <c r="J60" s="49"/>
+      <c r="K60" s="49"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="42"/>
-      <c r="D61" s="42"/>
-      <c r="E61" s="42"/>
-      <c r="F61" s="42"/>
-      <c r="G61" s="42"/>
-      <c r="H61" s="42"/>
-      <c r="I61" s="42"/>
-      <c r="J61" s="42"/>
-      <c r="K61" s="42"/>
+      <c r="C61" s="49"/>
+      <c r="D61" s="49"/>
+      <c r="E61" s="49"/>
+      <c r="F61" s="49"/>
+      <c r="G61" s="49"/>
+      <c r="H61" s="49"/>
+      <c r="I61" s="49"/>
+      <c r="J61" s="49"/>
+      <c r="K61" s="49"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="42"/>
-      <c r="D62" s="42"/>
-      <c r="E62" s="42"/>
-      <c r="F62" s="42"/>
-      <c r="G62" s="42"/>
-      <c r="H62" s="42"/>
-      <c r="I62" s="42"/>
-      <c r="J62" s="42"/>
-      <c r="K62" s="42"/>
+      <c r="C62" s="49"/>
+      <c r="D62" s="49"/>
+      <c r="E62" s="49"/>
+      <c r="F62" s="49"/>
+      <c r="G62" s="49"/>
+      <c r="H62" s="49"/>
+      <c r="I62" s="49"/>
+      <c r="J62" s="49"/>
+      <c r="K62" s="49"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="42"/>
-      <c r="D63" s="42"/>
-      <c r="E63" s="42"/>
-      <c r="F63" s="42"/>
-      <c r="G63" s="42"/>
-      <c r="H63" s="42"/>
-      <c r="I63" s="42"/>
-      <c r="J63" s="42"/>
-      <c r="K63" s="42"/>
+      <c r="C63" s="49"/>
+      <c r="D63" s="49"/>
+      <c r="E63" s="49"/>
+      <c r="F63" s="49"/>
+      <c r="G63" s="49"/>
+      <c r="H63" s="49"/>
+      <c r="I63" s="49"/>
+      <c r="J63" s="49"/>
+      <c r="K63" s="49"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="42"/>
-      <c r="D64" s="42"/>
-      <c r="E64" s="42"/>
-      <c r="F64" s="42"/>
-      <c r="G64" s="42"/>
-      <c r="H64" s="42"/>
-      <c r="I64" s="42"/>
-      <c r="J64" s="42"/>
-      <c r="K64" s="42"/>
+      <c r="C64" s="49"/>
+      <c r="D64" s="49"/>
+      <c r="E64" s="49"/>
+      <c r="F64" s="49"/>
+      <c r="G64" s="49"/>
+      <c r="H64" s="49"/>
+      <c r="I64" s="49"/>
+      <c r="J64" s="49"/>
+      <c r="K64" s="49"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="42"/>
-      <c r="D65" s="42"/>
-      <c r="E65" s="42"/>
-      <c r="F65" s="42"/>
-      <c r="G65" s="42"/>
-      <c r="H65" s="42"/>
-      <c r="I65" s="42"/>
-      <c r="J65" s="42"/>
-      <c r="K65" s="42"/>
+      <c r="C65" s="49"/>
+      <c r="D65" s="49"/>
+      <c r="E65" s="49"/>
+      <c r="F65" s="49"/>
+      <c r="G65" s="49"/>
+      <c r="H65" s="49"/>
+      <c r="I65" s="49"/>
+      <c r="J65" s="49"/>
+      <c r="K65" s="49"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="42"/>
-      <c r="D66" s="42"/>
-      <c r="E66" s="42"/>
-      <c r="F66" s="42"/>
-      <c r="G66" s="42"/>
-      <c r="H66" s="42"/>
-      <c r="I66" s="42"/>
-      <c r="J66" s="42"/>
-      <c r="K66" s="42"/>
+      <c r="C66" s="49"/>
+      <c r="D66" s="49"/>
+      <c r="E66" s="49"/>
+      <c r="F66" s="49"/>
+      <c r="G66" s="49"/>
+      <c r="H66" s="49"/>
+      <c r="I66" s="49"/>
+      <c r="J66" s="49"/>
+      <c r="K66" s="49"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="42"/>
-      <c r="D67" s="42"/>
-      <c r="E67" s="42"/>
-      <c r="F67" s="42"/>
-      <c r="G67" s="42"/>
-      <c r="H67" s="42"/>
-      <c r="I67" s="42"/>
-      <c r="J67" s="42"/>
-      <c r="K67" s="42"/>
+      <c r="C67" s="49"/>
+      <c r="D67" s="49"/>
+      <c r="E67" s="49"/>
+      <c r="F67" s="49"/>
+      <c r="G67" s="49"/>
+      <c r="H67" s="49"/>
+      <c r="I67" s="49"/>
+      <c r="J67" s="49"/>
+      <c r="K67" s="49"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="42"/>
-      <c r="D68" s="42"/>
-      <c r="E68" s="42"/>
-      <c r="F68" s="42"/>
-      <c r="G68" s="42"/>
-      <c r="H68" s="42"/>
-      <c r="I68" s="42"/>
-      <c r="J68" s="42"/>
-      <c r="K68" s="42"/>
+      <c r="C68" s="49"/>
+      <c r="D68" s="49"/>
+      <c r="E68" s="49"/>
+      <c r="F68" s="49"/>
+      <c r="G68" s="49"/>
+      <c r="H68" s="49"/>
+      <c r="I68" s="49"/>
+      <c r="J68" s="49"/>
+      <c r="K68" s="49"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="42"/>
-      <c r="D69" s="42"/>
-      <c r="E69" s="42"/>
-      <c r="F69" s="42"/>
-      <c r="G69" s="42"/>
-      <c r="H69" s="42"/>
-      <c r="I69" s="42"/>
-      <c r="J69" s="42"/>
-      <c r="K69" s="42"/>
+      <c r="C69" s="49"/>
+      <c r="D69" s="49"/>
+      <c r="E69" s="49"/>
+      <c r="F69" s="49"/>
+      <c r="G69" s="49"/>
+      <c r="H69" s="49"/>
+      <c r="I69" s="49"/>
+      <c r="J69" s="49"/>
+      <c r="K69" s="49"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="42"/>
-      <c r="D70" s="42"/>
-      <c r="E70" s="42"/>
-      <c r="F70" s="42"/>
-      <c r="G70" s="42"/>
-      <c r="H70" s="42"/>
-      <c r="I70" s="42"/>
-      <c r="J70" s="42"/>
-      <c r="K70" s="42"/>
+      <c r="C70" s="49"/>
+      <c r="D70" s="49"/>
+      <c r="E70" s="49"/>
+      <c r="F70" s="49"/>
+      <c r="G70" s="49"/>
+      <c r="H70" s="49"/>
+      <c r="I70" s="49"/>
+      <c r="J70" s="49"/>
+      <c r="K70" s="49"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="42"/>
-      <c r="D71" s="42"/>
-      <c r="E71" s="42"/>
-      <c r="F71" s="42"/>
-      <c r="G71" s="42"/>
-      <c r="H71" s="42"/>
-      <c r="I71" s="42"/>
-      <c r="J71" s="42"/>
-      <c r="K71" s="42"/>
+      <c r="C71" s="49"/>
+      <c r="D71" s="49"/>
+      <c r="E71" s="49"/>
+      <c r="F71" s="49"/>
+      <c r="G71" s="49"/>
+      <c r="H71" s="49"/>
+      <c r="I71" s="49"/>
+      <c r="J71" s="49"/>
+      <c r="K71" s="49"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="42"/>
-      <c r="D72" s="42"/>
-      <c r="E72" s="42"/>
-      <c r="F72" s="42"/>
-      <c r="G72" s="42"/>
-      <c r="H72" s="42"/>
-      <c r="I72" s="42"/>
-      <c r="J72" s="42"/>
-      <c r="K72" s="42"/>
+      <c r="C72" s="49"/>
+      <c r="D72" s="49"/>
+      <c r="E72" s="49"/>
+      <c r="F72" s="49"/>
+      <c r="G72" s="49"/>
+      <c r="H72" s="49"/>
+      <c r="I72" s="49"/>
+      <c r="J72" s="49"/>
+      <c r="K72" s="49"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="42"/>
-      <c r="D73" s="42"/>
-      <c r="E73" s="42"/>
-      <c r="F73" s="42"/>
-      <c r="G73" s="42"/>
-      <c r="H73" s="42"/>
-      <c r="I73" s="42"/>
-      <c r="J73" s="42"/>
-      <c r="K73" s="42"/>
+      <c r="C73" s="49"/>
+      <c r="D73" s="49"/>
+      <c r="E73" s="49"/>
+      <c r="F73" s="49"/>
+      <c r="G73" s="49"/>
+      <c r="H73" s="49"/>
+      <c r="I73" s="49"/>
+      <c r="J73" s="49"/>
+      <c r="K73" s="49"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="42"/>
-      <c r="D74" s="42"/>
-      <c r="E74" s="42"/>
-      <c r="F74" s="42"/>
-      <c r="G74" s="42"/>
-      <c r="H74" s="42"/>
-      <c r="I74" s="42"/>
-      <c r="J74" s="42"/>
-      <c r="K74" s="42"/>
+      <c r="C74" s="49"/>
+      <c r="D74" s="49"/>
+      <c r="E74" s="49"/>
+      <c r="F74" s="49"/>
+      <c r="G74" s="49"/>
+      <c r="H74" s="49"/>
+      <c r="I74" s="49"/>
+      <c r="J74" s="49"/>
+      <c r="K74" s="49"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="42"/>
-      <c r="D75" s="42"/>
-      <c r="E75" s="42"/>
-      <c r="F75" s="42"/>
-      <c r="G75" s="42"/>
-      <c r="H75" s="42"/>
-      <c r="I75" s="42"/>
-      <c r="J75" s="42"/>
-      <c r="K75" s="42"/>
+      <c r="C75" s="49"/>
+      <c r="D75" s="49"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="49"/>
+      <c r="G75" s="49"/>
+      <c r="H75" s="49"/>
+      <c r="I75" s="49"/>
+      <c r="J75" s="49"/>
+      <c r="K75" s="49"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="42"/>
-      <c r="D76" s="42"/>
-      <c r="E76" s="42"/>
-      <c r="F76" s="42"/>
-      <c r="G76" s="42"/>
-      <c r="H76" s="42"/>
-      <c r="I76" s="42"/>
-      <c r="J76" s="42"/>
-      <c r="K76" s="42"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="49"/>
+      <c r="E76" s="49"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="49"/>
+      <c r="H76" s="49"/>
+      <c r="I76" s="49"/>
+      <c r="J76" s="49"/>
+      <c r="K76" s="49"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="42"/>
-      <c r="D77" s="42"/>
-      <c r="E77" s="42"/>
-      <c r="F77" s="42"/>
-      <c r="G77" s="42"/>
-      <c r="H77" s="42"/>
-      <c r="I77" s="42"/>
-      <c r="J77" s="42"/>
-      <c r="K77" s="42"/>
+      <c r="C77" s="49"/>
+      <c r="D77" s="49"/>
+      <c r="E77" s="49"/>
+      <c r="F77" s="49"/>
+      <c r="G77" s="49"/>
+      <c r="H77" s="49"/>
+      <c r="I77" s="49"/>
+      <c r="J77" s="49"/>
+      <c r="K77" s="49"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="42"/>
-      <c r="D78" s="42"/>
-      <c r="E78" s="42"/>
-      <c r="F78" s="42"/>
-      <c r="G78" s="42"/>
-      <c r="H78" s="42"/>
-      <c r="I78" s="42"/>
-      <c r="J78" s="42"/>
-      <c r="K78" s="42"/>
+      <c r="C78" s="49"/>
+      <c r="D78" s="49"/>
+      <c r="E78" s="49"/>
+      <c r="F78" s="49"/>
+      <c r="G78" s="49"/>
+      <c r="H78" s="49"/>
+      <c r="I78" s="49"/>
+      <c r="J78" s="49"/>
+      <c r="K78" s="49"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="42"/>
-      <c r="D79" s="42"/>
-      <c r="E79" s="42"/>
-      <c r="F79" s="42"/>
-      <c r="G79" s="42"/>
-      <c r="H79" s="42"/>
-      <c r="I79" s="42"/>
-      <c r="J79" s="42"/>
-      <c r="K79" s="42"/>
+      <c r="C79" s="49"/>
+      <c r="D79" s="49"/>
+      <c r="E79" s="49"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="49"/>
+      <c r="H79" s="49"/>
+      <c r="I79" s="49"/>
+      <c r="J79" s="49"/>
+      <c r="K79" s="49"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="42"/>
-      <c r="D80" s="42"/>
-      <c r="E80" s="42"/>
-      <c r="F80" s="42"/>
-      <c r="G80" s="42"/>
-      <c r="H80" s="42"/>
-      <c r="I80" s="42"/>
-      <c r="J80" s="42"/>
-      <c r="K80" s="42"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="49"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49"/>
+      <c r="J80" s="49"/>
+      <c r="K80" s="49"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="42"/>
-      <c r="D81" s="42"/>
-      <c r="E81" s="42"/>
-      <c r="F81" s="42"/>
-      <c r="G81" s="42"/>
-      <c r="H81" s="42"/>
-      <c r="I81" s="42"/>
-      <c r="J81" s="42"/>
-      <c r="K81" s="42"/>
+      <c r="C81" s="49"/>
+      <c r="D81" s="49"/>
+      <c r="E81" s="49"/>
+      <c r="F81" s="49"/>
+      <c r="G81" s="49"/>
+      <c r="H81" s="49"/>
+      <c r="I81" s="49"/>
+      <c r="J81" s="49"/>
+      <c r="K81" s="49"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="42"/>
-      <c r="D82" s="42"/>
-      <c r="E82" s="42"/>
-      <c r="F82" s="42"/>
-      <c r="G82" s="42"/>
-      <c r="H82" s="42"/>
-      <c r="I82" s="42"/>
-      <c r="J82" s="42"/>
-      <c r="K82" s="42"/>
+      <c r="C82" s="49"/>
+      <c r="D82" s="49"/>
+      <c r="E82" s="49"/>
+      <c r="F82" s="49"/>
+      <c r="G82" s="49"/>
+      <c r="H82" s="49"/>
+      <c r="I82" s="49"/>
+      <c r="J82" s="49"/>
+      <c r="K82" s="49"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="42"/>
-      <c r="D83" s="42"/>
-      <c r="E83" s="42"/>
-      <c r="F83" s="42"/>
-      <c r="G83" s="42"/>
-      <c r="H83" s="42"/>
-      <c r="I83" s="42"/>
-      <c r="J83" s="42"/>
-      <c r="K83" s="42"/>
+      <c r="C83" s="49"/>
+      <c r="D83" s="49"/>
+      <c r="E83" s="49"/>
+      <c r="F83" s="49"/>
+      <c r="G83" s="49"/>
+      <c r="H83" s="49"/>
+      <c r="I83" s="49"/>
+      <c r="J83" s="49"/>
+      <c r="K83" s="49"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="42" t="s">
+      <c r="C84" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="D84" s="42">
-        <v>1</v>
-      </c>
-      <c r="E84" s="42"/>
-      <c r="F84" s="42"/>
-      <c r="G84" s="42"/>
-      <c r="H84" s="42"/>
-      <c r="I84" s="42"/>
-      <c r="J84" s="42"/>
-      <c r="K84" s="42"/>
+      <c r="D84" s="49">
+        <v>1</v>
+      </c>
+      <c r="E84" s="49"/>
+      <c r="F84" s="49"/>
+      <c r="G84" s="49"/>
+      <c r="H84" s="49"/>
+      <c r="I84" s="49"/>
+      <c r="J84" s="49"/>
+      <c r="K84" s="49"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="42"/>
-      <c r="D85" s="42"/>
-      <c r="E85" s="42"/>
-      <c r="F85" s="42"/>
-      <c r="G85" s="42"/>
-      <c r="H85" s="42"/>
-      <c r="I85" s="42"/>
-      <c r="J85" s="42"/>
-      <c r="K85" s="42"/>
+      <c r="C85" s="49"/>
+      <c r="D85" s="49"/>
+      <c r="E85" s="49"/>
+      <c r="F85" s="49"/>
+      <c r="G85" s="49"/>
+      <c r="H85" s="49"/>
+      <c r="I85" s="49"/>
+      <c r="J85" s="49"/>
+      <c r="K85" s="49"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3522,15 +3565,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:N54"/>
+  <dimension ref="B2:N58"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="4" max="4" width="27.1636363636364" customWidth="1"/>
     <col min="6" max="6" width="31.9090909090909" customWidth="1"/>
     <col min="7" max="7" width="19.5272727272727" customWidth="1"/>
     <col min="8" max="8" width="16.7545454545455" customWidth="1"/>
-    <col min="9" max="10" width="8.72727272727273" customWidth="1"/>
-    <col min="11" max="11" width="12.8181818181818" customWidth="1"/>
+    <col min="9" max="9" width="8.72727272727273" customWidth="1"/>
+    <col min="10" max="10" width="12.1818181818182" customWidth="1"/>
+    <col min="11" max="11" width="17.5454545454545" customWidth="1"/>
     <col min="12" max="12" width="10.1818181818182" customWidth="1"/>
     <col min="13" max="13" width="12.3636363636364" customWidth="1"/>
   </cols>
@@ -3546,9 +3590,58 @@
       </c>
     </row>
     <row r="4" spans="2:14">
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
       <c r="H4" s="20" t="s">
         <v>77</v>
       </c>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+    </row>
+    <row r="5" spans="2:14">
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+    </row>
+    <row r="6" spans="2:14">
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+    </row>
+    <row r="7" spans="2:14">
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
     </row>
     <row r="8" spans="2:14">
       <c r="D8" s="21" t="s">
@@ -3589,6 +3682,7 @@
       <c r="D9" s="23" t="s">
         <v>82</v>
       </c>
+      <c r="E9" s="20"/>
       <c r="F9" s="23" t="s">
         <v>83</v>
       </c>
@@ -3601,13 +3695,13 @@
       <c r="I9" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="20">
         <v>1</v>
       </c>
       <c r="K9" s="23">
         <v>1.25</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="20">
         <v>0.05</v>
       </c>
       <c r="M9" s="23">
@@ -3619,6 +3713,7 @@
       <c r="D10" s="23" t="s">
         <v>87</v>
       </c>
+      <c r="E10" s="20"/>
       <c r="F10" s="23" t="s">
         <v>88</v>
       </c>
@@ -3631,13 +3726,13 @@
       <c r="I10" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="20">
         <v>1</v>
       </c>
       <c r="K10" s="23">
         <v>1.11</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="20">
         <v>0.05</v>
       </c>
       <c r="M10" s="23">
@@ -3649,6 +3744,7 @@
       <c r="D11" s="23" t="s">
         <v>89</v>
       </c>
+      <c r="E11" s="20"/>
       <c r="F11" s="23" t="s">
         <v>90</v>
       </c>
@@ -3661,13 +3757,13 @@
       <c r="I11" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="20">
         <v>1</v>
       </c>
       <c r="K11" s="23">
         <v>1.15</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="20">
         <v>0.08</v>
       </c>
       <c r="M11" s="23">
@@ -3679,7 +3775,8 @@
       <c r="D12" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="E12" s="20"/>
+      <c r="F12" s="24" t="s">
         <v>92</v>
       </c>
       <c r="G12" s="23" t="s">
@@ -3691,13 +3788,13 @@
       <c r="I12" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="20">
         <v>1</v>
       </c>
       <c r="K12" s="23">
         <v>1.12</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="20">
         <v>0.03</v>
       </c>
       <c r="M12" s="23">
@@ -3709,6 +3806,7 @@
       <c r="D13" s="23" t="s">
         <v>93</v>
       </c>
+      <c r="E13" s="20"/>
       <c r="F13" s="23" t="s">
         <v>94</v>
       </c>
@@ -3721,13 +3819,13 @@
       <c r="I13" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="20">
         <v>1</v>
       </c>
       <c r="K13" s="23">
         <v>1.2</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="20">
         <v>0.1</v>
       </c>
       <c r="M13" s="23">
@@ -3739,6 +3837,7 @@
       <c r="D14" s="23" t="s">
         <v>95</v>
       </c>
+      <c r="E14" s="20"/>
       <c r="F14" s="23" t="s">
         <v>96</v>
       </c>
@@ -3751,13 +3850,13 @@
       <c r="I14" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="20">
         <v>1</v>
       </c>
       <c r="K14" s="23">
         <v>1.06</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="20">
         <v>0.15</v>
       </c>
       <c r="M14" s="23">
@@ -3769,6 +3868,7 @@
       <c r="D15" s="23" t="s">
         <v>97</v>
       </c>
+      <c r="E15" s="20"/>
       <c r="F15" s="23" t="s">
         <v>98</v>
       </c>
@@ -3781,13 +3881,13 @@
       <c r="I15" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="20">
         <v>1</v>
       </c>
       <c r="K15" s="23">
         <v>1.06</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="20">
         <v>0.3</v>
       </c>
       <c r="M15" s="23">
@@ -3799,102 +3899,108 @@
       <c r="D16" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="E16" s="20"/>
+      <c r="F16" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="G16" t="str">
+      <c r="G16" s="20" t="str">
         <f xml:space="preserve">G15</f>
         <v>CAP,GROWTH</v>
       </c>
-      <c r="H16" t="str">
+      <c r="H16" s="20" t="str">
         <f xml:space="preserve">H15</f>
         <v>2025, 2150</v>
       </c>
       <c r="I16" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="20">
         <f t="shared" ref="J16:L16" si="0" xml:space="preserve">J12</f>
         <v>1</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="20">
         <f t="shared" si="0"/>
         <v>1.12</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="20">
         <f t="shared" si="0"/>
         <v>0.03</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="20">
         <f xml:space="preserve">M15</f>
         <v>1</v>
       </c>
+      <c r="N16" s="20"/>
     </row>
     <row r="17" ht="16" spans="4:14">
       <c r="D17" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="E17" s="20"/>
+      <c r="F17" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="G17" t="str">
+      <c r="G17" s="20" t="str">
         <f t="shared" ref="G17:M17" si="1" xml:space="preserve">G16</f>
         <v>CAP,GROWTH</v>
       </c>
-      <c r="H17" t="str">
+      <c r="H17" s="20" t="str">
         <f t="shared" si="1"/>
         <v>2025, 2150</v>
       </c>
       <c r="I17" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="20">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="20">
         <f t="shared" si="1"/>
         <v>1.12</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="20">
         <f t="shared" si="1"/>
         <v>0.03</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="20">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
+      <c r="N17" s="20"/>
     </row>
     <row r="18" ht="16" spans="4:14">
       <c r="D18" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="E18" s="20"/>
+      <c r="F18" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="G18" t="str">
+      <c r="G18" s="20" t="str">
         <f xml:space="preserve">G17</f>
         <v>CAP,GROWTH</v>
       </c>
-      <c r="H18" t="str">
+      <c r="H18" s="20" t="str">
         <f xml:space="preserve">H17</f>
         <v>2025, 2150</v>
       </c>
       <c r="I18" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
-      <c r="L18">
+      <c r="J18" s="20">
+        <v>1</v>
+      </c>
+      <c r="K18" s="20">
+        <v>1</v>
+      </c>
+      <c r="L18" s="20">
         <v>0</v>
       </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
+      <c r="M18" s="20">
+        <v>1</v>
+      </c>
+      <c r="N18" s="20"/>
     </row>
     <row r="25" spans="4:14">
       <c r="K25" t="s">
@@ -3905,334 +4011,334 @@
       </c>
     </row>
     <row r="27" spans="4:14">
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="22"/>
-      <c r="N27" s="22"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="25"/>
     </row>
     <row r="28" spans="4:14">
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22" t="s">
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="22"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
+      <c r="M28" s="25"/>
+      <c r="N28" s="25"/>
     </row>
     <row r="29" spans="4:14">
-      <c r="D29" s="22" t="s">
+      <c r="D29" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="E29" s="22" t="s">
+      <c r="E29" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="F29" s="22" t="s">
+      <c r="F29" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="22" t="s">
+      <c r="G29" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="H29" s="22" t="s">
+      <c r="H29" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="I29" s="22" t="s">
+      <c r="I29" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="J29" s="22" t="s">
+      <c r="J29" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="K29" s="22" t="s">
+      <c r="K29" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="L29" s="22" t="s">
+      <c r="L29" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="M29" s="22" t="s">
+      <c r="M29" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="N29" s="22" t="s">
+      <c r="N29" s="25" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="30" ht="16" spans="4:14">
-      <c r="D30" s="22" t="s">
+      <c r="D30" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="22"/>
-      <c r="F30" s="24" t="s">
+      <c r="E30" s="25"/>
+      <c r="F30" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="G30" s="22" t="s">
+      <c r="G30" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="H30" s="22" t="s">
+      <c r="H30" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="I30" s="22" t="s">
+      <c r="I30" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="22">
-        <v>1</v>
-      </c>
-      <c r="K30" s="22">
-        <v>1</v>
-      </c>
-      <c r="L30" s="22">
+      <c r="J30" s="25">
+        <v>1</v>
+      </c>
+      <c r="K30" s="25">
+        <v>1</v>
+      </c>
+      <c r="L30" s="25">
         <v>0.01</v>
       </c>
-      <c r="M30" s="22">
-        <v>1</v>
-      </c>
-      <c r="N30" s="22"/>
+      <c r="M30" s="25">
+        <v>1</v>
+      </c>
+      <c r="N30" s="25"/>
     </row>
     <row r="31" ht="16" spans="4:14">
-      <c r="D31" s="22" t="s">
+      <c r="D31" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="22"/>
-      <c r="F31" s="25" t="s">
+      <c r="E31" s="25"/>
+      <c r="F31" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="G31" s="22" t="s">
+      <c r="G31" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="H31" s="22" t="s">
+      <c r="H31" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="I31" s="22" t="s">
+      <c r="I31" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="J31" s="22">
-        <v>1</v>
-      </c>
-      <c r="K31" s="22">
-        <v>1</v>
-      </c>
-      <c r="L31" s="22">
+      <c r="J31" s="25">
+        <v>1</v>
+      </c>
+      <c r="K31" s="25">
+        <v>1</v>
+      </c>
+      <c r="L31" s="25">
         <f t="shared" ref="L31:L36" si="2" xml:space="preserve">L30</f>
         <v>0.01</v>
       </c>
-      <c r="M31" s="22">
-        <v>1</v>
-      </c>
-      <c r="N31" s="22"/>
+      <c r="M31" s="25">
+        <v>1</v>
+      </c>
+      <c r="N31" s="25"/>
     </row>
     <row r="32" ht="16" spans="4:14">
-      <c r="D32" s="22" t="s">
+      <c r="D32" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="E32" s="22"/>
-      <c r="F32" s="25" t="s">
+      <c r="E32" s="25"/>
+      <c r="F32" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="G32" s="22" t="s">
+      <c r="G32" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="H32" s="22" t="s">
+      <c r="H32" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="I32" s="22" t="s">
+      <c r="I32" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="J32" s="22">
-        <v>1</v>
-      </c>
-      <c r="K32" s="22">
-        <v>1</v>
-      </c>
-      <c r="L32" s="22">
+      <c r="J32" s="25">
+        <v>1</v>
+      </c>
+      <c r="K32" s="25">
+        <v>1</v>
+      </c>
+      <c r="L32" s="25">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M32" s="22">
-        <v>1</v>
-      </c>
-      <c r="N32" s="22"/>
+      <c r="M32" s="25">
+        <v>1</v>
+      </c>
+      <c r="N32" s="25"/>
     </row>
     <row r="33" ht="16" spans="4:14">
-      <c r="D33" s="22" t="s">
+      <c r="D33" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="22"/>
-      <c r="F33" s="24" t="s">
+      <c r="E33" s="25"/>
+      <c r="F33" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="G33" s="22" t="s">
+      <c r="G33" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="H33" s="22" t="s">
+      <c r="H33" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="I33" s="22" t="s">
+      <c r="I33" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="J33" s="22">
-        <v>1</v>
-      </c>
-      <c r="K33" s="22">
+      <c r="J33" s="25">
+        <v>1</v>
+      </c>
+      <c r="K33" s="25">
         <f xml:space="preserve">K32</f>
         <v>1</v>
       </c>
-      <c r="L33" s="22">
+      <c r="L33" s="25">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M33" s="22">
-        <v>1</v>
-      </c>
-      <c r="N33" s="22"/>
+      <c r="M33" s="25">
+        <v>1</v>
+      </c>
+      <c r="N33" s="25"/>
     </row>
     <row r="34" ht="16" spans="4:14">
-      <c r="D34" s="22" t="s">
+      <c r="D34" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="E34" s="22"/>
-      <c r="F34" s="24" t="s">
+      <c r="E34" s="25"/>
+      <c r="F34" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="G34" s="22" t="s">
+      <c r="G34" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="H34" s="22" t="s">
+      <c r="H34" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="I34" s="22" t="s">
+      <c r="I34" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="J34" s="22">
-        <v>1</v>
-      </c>
-      <c r="K34" s="22">
+      <c r="J34" s="25">
+        <v>1</v>
+      </c>
+      <c r="K34" s="25">
         <f xml:space="preserve">K33</f>
         <v>1</v>
       </c>
-      <c r="L34" s="22">
+      <c r="L34" s="25">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M34" s="22">
-        <v>1</v>
-      </c>
-      <c r="N34" s="22"/>
+      <c r="M34" s="25">
+        <v>1</v>
+      </c>
+      <c r="N34" s="25"/>
     </row>
     <row r="35" ht="16" spans="4:14">
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="E35" s="22"/>
-      <c r="F35" s="24" t="s">
+      <c r="E35" s="25"/>
+      <c r="F35" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="22" t="s">
+      <c r="G35" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="H35" s="22" t="s">
+      <c r="H35" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="I35" s="22" t="s">
+      <c r="I35" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="J35" s="22">
-        <v>1</v>
-      </c>
-      <c r="K35" s="22">
+      <c r="J35" s="25">
+        <v>1</v>
+      </c>
+      <c r="K35" s="25">
         <f xml:space="preserve">K34</f>
         <v>1</v>
       </c>
-      <c r="L35" s="22">
+      <c r="L35" s="25">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M35" s="22">
-        <v>1</v>
-      </c>
-      <c r="N35" s="22"/>
+      <c r="M35" s="25">
+        <v>1</v>
+      </c>
+      <c r="N35" s="25"/>
     </row>
     <row r="36" ht="16" spans="4:14">
-      <c r="D36" s="22" t="s">
+      <c r="D36" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="E36" s="22"/>
-      <c r="F36" s="24" t="s">
+      <c r="E36" s="25"/>
+      <c r="F36" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="G36" s="22" t="s">
+      <c r="G36" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="H36" s="22" t="s">
+      <c r="H36" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="I36" s="22" t="s">
+      <c r="I36" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="J36" s="22">
-        <v>1</v>
-      </c>
-      <c r="K36" s="22">
+      <c r="J36" s="25">
+        <v>1</v>
+      </c>
+      <c r="K36" s="25">
         <f xml:space="preserve">K35</f>
         <v>1</v>
       </c>
-      <c r="L36" s="22">
+      <c r="L36" s="25">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M36" s="22">
-        <v>1</v>
-      </c>
-      <c r="N36" s="22"/>
+      <c r="M36" s="25">
+        <v>1</v>
+      </c>
+      <c r="N36" s="25"/>
     </row>
     <row r="37" ht="16" spans="4:14">
-      <c r="D37" s="26" t="s">
+      <c r="D37" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="E37" s="26"/>
-      <c r="F37" s="27" t="s">
+      <c r="E37" s="28"/>
+      <c r="F37" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="G37" s="26" t="s">
+      <c r="G37" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="H37" s="26" t="s">
+      <c r="H37" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="I37" s="26" t="s">
+      <c r="I37" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="J37" s="26">
-        <v>1</v>
-      </c>
-      <c r="K37" s="26">
-        <v>1</v>
-      </c>
-      <c r="L37" s="26">
+      <c r="J37" s="28">
+        <v>1</v>
+      </c>
+      <c r="K37" s="28">
+        <v>1</v>
+      </c>
+      <c r="L37" s="28">
         <v>0</v>
       </c>
-      <c r="M37" s="26">
+      <c r="M37" s="28">
         <v>3</v>
       </c>
-      <c r="N37" s="22"/>
+      <c r="N37" s="25"/>
     </row>
     <row r="38" ht="16" spans="4:14">
-      <c r="D38" s="28" t="s">
+      <c r="D38" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="F38" s="27" t="s">
+      <c r="F38" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="G38" s="26" t="s">
+      <c r="G38" s="28" t="s">
         <v>84</v>
       </c>
       <c r="H38" t="str">
@@ -4254,185 +4360,185 @@
       <c r="M38">
         <v>3</v>
       </c>
-      <c r="N38" s="22"/>
+      <c r="N38" s="25"/>
     </row>
     <row r="39" ht="16" spans="4:14">
-      <c r="D39" s="28" t="s">
+      <c r="D39" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="E39" s="29"/>
-      <c r="F39" s="27" t="s">
+      <c r="E39" s="31"/>
+      <c r="F39" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="G39" s="26" t="s">
+      <c r="G39" s="28" t="s">
         <v>84</v>
       </c>
       <c r="H39" t="str">
-        <f xml:space="preserve">H38</f>
+        <f t="shared" ref="H39:M39" si="3" xml:space="preserve">H38</f>
         <v>2019, 2150</v>
       </c>
-      <c r="I39" s="29" t="str">
-        <f xml:space="preserve">I38</f>
+      <c r="I39" s="31" t="str">
+        <f t="shared" si="3"/>
         <v>UP</v>
       </c>
-      <c r="J39" s="29">
-        <f xml:space="preserve">J38</f>
-        <v>1</v>
-      </c>
-      <c r="K39" s="29">
-        <f xml:space="preserve">K38</f>
+      <c r="J39" s="31">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="K39" s="31">
+        <f t="shared" si="3"/>
         <v>1.1</v>
       </c>
-      <c r="L39" s="29">
-        <f xml:space="preserve">L38</f>
+      <c r="L39" s="31">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M39" s="29">
-        <f xml:space="preserve">M38</f>
+      <c r="M39" s="31">
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="N39" s="29"/>
+      <c r="N39" s="31"/>
     </row>
     <row r="40" ht="16" spans="4:14">
-      <c r="D40" s="28" t="s">
+      <c r="D40" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="E40" s="29"/>
-      <c r="F40" s="27" t="s">
+      <c r="E40" s="31"/>
+      <c r="F40" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="G40" s="26" t="s">
+      <c r="G40" s="28" t="s">
         <v>84</v>
       </c>
       <c r="H40" t="str">
-        <f xml:space="preserve">H39</f>
+        <f t="shared" ref="H40:M40" si="4" xml:space="preserve">H39</f>
         <v>2019, 2150</v>
       </c>
-      <c r="I40" s="29" t="str">
-        <f xml:space="preserve">I39</f>
+      <c r="I40" s="31" t="str">
+        <f t="shared" si="4"/>
         <v>UP</v>
       </c>
-      <c r="J40" s="29">
-        <f xml:space="preserve">J39</f>
-        <v>1</v>
-      </c>
-      <c r="K40" s="29">
-        <f xml:space="preserve">K39</f>
+      <c r="J40" s="31">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K40" s="31">
+        <f t="shared" si="4"/>
         <v>1.1</v>
       </c>
-      <c r="L40" s="29">
-        <f xml:space="preserve">L39</f>
+      <c r="L40" s="31">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M40" s="29">
-        <f xml:space="preserve">M39</f>
+      <c r="M40" s="31">
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="N40" s="29"/>
+      <c r="N40" s="31"/>
     </row>
     <row r="41" ht="16" spans="4:14">
-      <c r="D41" s="28" t="s">
+      <c r="D41" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="E41" s="29"/>
-      <c r="F41" s="27" t="s">
+      <c r="E41" s="31"/>
+      <c r="F41" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="G41" s="26" t="s">
+      <c r="G41" s="28" t="s">
         <v>84</v>
       </c>
       <c r="H41" t="str">
-        <f xml:space="preserve">H40</f>
+        <f t="shared" ref="H41:M41" si="5" xml:space="preserve">H40</f>
         <v>2019, 2150</v>
       </c>
-      <c r="I41" s="29" t="str">
-        <f xml:space="preserve">I40</f>
+      <c r="I41" s="31" t="str">
+        <f t="shared" si="5"/>
         <v>UP</v>
       </c>
-      <c r="J41" s="29">
-        <f xml:space="preserve">J40</f>
-        <v>1</v>
-      </c>
-      <c r="K41" s="29">
-        <f xml:space="preserve">K40</f>
+      <c r="J41" s="31">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="K41" s="31">
+        <f t="shared" si="5"/>
         <v>1.1</v>
       </c>
-      <c r="L41" s="29">
-        <f xml:space="preserve">L40</f>
+      <c r="L41" s="31">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M41" s="29">
-        <f xml:space="preserve">M40</f>
+      <c r="M41" s="31">
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="N41" s="29"/>
+      <c r="N41" s="31"/>
     </row>
     <row r="42" ht="16" spans="4:14">
-      <c r="D42" s="28" t="s">
+      <c r="D42" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="F42" s="27" t="s">
+      <c r="F42" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="G42" s="26" t="s">
+      <c r="G42" s="28" t="s">
         <v>84</v>
       </c>
       <c r="H42" t="str">
-        <f xml:space="preserve">H41</f>
+        <f t="shared" ref="H42:M42" si="6" xml:space="preserve">H41</f>
         <v>2019, 2150</v>
       </c>
-      <c r="I42" s="29" t="str">
-        <f xml:space="preserve">I41</f>
+      <c r="I42" s="31" t="str">
+        <f t="shared" si="6"/>
         <v>UP</v>
       </c>
-      <c r="J42" s="29">
-        <f xml:space="preserve">J41</f>
-        <v>1</v>
-      </c>
-      <c r="K42" s="29">
-        <f xml:space="preserve">K41</f>
+      <c r="J42" s="31">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="K42" s="31">
+        <f t="shared" si="6"/>
         <v>1.1</v>
       </c>
-      <c r="L42" s="29">
-        <f xml:space="preserve">L41</f>
+      <c r="L42" s="31">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M42" s="29">
-        <f xml:space="preserve">M41</f>
+      <c r="M42" s="31">
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="N42" s="29"/>
+      <c r="N42" s="31"/>
     </row>
     <row r="43" spans="4:14">
-      <c r="D43" s="26" t="s">
+      <c r="D43" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="E43" s="26"/>
-      <c r="F43" s="30" t="s">
+      <c r="E43" s="28"/>
+      <c r="F43" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="G43" s="26" t="s">
+      <c r="G43" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="H43" s="26" t="s">
+      <c r="H43" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="I43" s="26" t="s">
+      <c r="I43" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="J43" s="26">
-        <v>1</v>
-      </c>
-      <c r="K43" s="26">
-        <v>1</v>
-      </c>
-      <c r="L43" s="26">
+      <c r="J43" s="28">
+        <v>1</v>
+      </c>
+      <c r="K43" s="28">
+        <v>1</v>
+      </c>
+      <c r="L43" s="28">
         <v>0</v>
       </c>
-      <c r="M43" s="26">
+      <c r="M43" s="28">
         <v>3</v>
       </c>
-      <c r="N43" s="29"/>
+      <c r="N43" s="31"/>
     </row>
     <row r="44" spans="4:14">
       <c r="D44" s="1"/>
@@ -4445,20 +4551,20 @@
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
-      <c r="N44" s="29"/>
+      <c r="N44" s="31"/>
     </row>
     <row r="45" spans="4:14">
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="29"/>
-      <c r="H45" s="29"/>
-      <c r="I45" s="29"/>
-      <c r="J45" s="29"/>
-      <c r="K45" s="29"/>
-      <c r="L45" s="29"/>
-      <c r="M45" s="29"/>
-      <c r="N45" s="29"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="33"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="31"/>
+      <c r="I45" s="31"/>
+      <c r="J45" s="31"/>
+      <c r="K45" s="31"/>
+      <c r="L45" s="31"/>
+      <c r="M45" s="31"/>
+      <c r="N45" s="31"/>
     </row>
     <row r="46" spans="4:14">
       <c r="D46" s="1"/>
@@ -4471,7 +4577,7 @@
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
-      <c r="N46" s="29"/>
+      <c r="N46" s="31"/>
     </row>
     <row r="47" spans="4:14">
       <c r="D47" s="1"/>
@@ -4484,7 +4590,7 @@
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
-      <c r="N47" s="29"/>
+      <c r="N47" s="31"/>
     </row>
     <row r="48" spans="4:14">
       <c r="D48" s="1"/>
@@ -4497,55 +4603,207 @@
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
-      <c r="N48" s="29"/>
+      <c r="N48" s="31"/>
     </row>
     <row r="49" spans="4:14">
-      <c r="N49" s="22"/>
+      <c r="N49" s="25"/>
     </row>
     <row r="50" spans="4:14">
-      <c r="N50" s="22"/>
-    </row>
-    <row r="51" spans="4:14">
-      <c r="N51" s="22"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="25"/>
+      <c r="G50" s="25"/>
+      <c r="H50" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="I50" s="25"/>
+      <c r="J50" s="25"/>
+      <c r="K50" s="25"/>
+      <c r="L50" s="25"/>
+      <c r="M50" s="25"/>
+      <c r="N50" s="25"/>
+    </row>
+    <row r="51" ht="16" spans="4:14">
+      <c r="D51" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="E51" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="F51" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="G51" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="H51" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="I51" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="J51" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="K51" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="L51" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="M51" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="N51" s="25" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="52" spans="4:14">
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="22"/>
-      <c r="I52" s="22"/>
-      <c r="J52" s="22"/>
-      <c r="K52" s="22"/>
-      <c r="L52" s="22"/>
-      <c r="M52" s="22"/>
-      <c r="N52" s="22"/>
+      <c r="D52" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="E52" s="25"/>
+      <c r="F52" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="G52" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="H52" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="I52" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="J52" s="25">
+        <v>1</v>
+      </c>
+      <c r="K52" s="25">
+        <v>1</v>
+      </c>
+      <c r="L52" s="25">
+        <v>0</v>
+      </c>
+      <c r="M52" s="25">
+        <v>5</v>
+      </c>
+      <c r="N52" s="25"/>
     </row>
     <row r="53" spans="4:14">
-      <c r="D53" s="22"/>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="22"/>
-      <c r="H53" s="22"/>
-      <c r="I53" s="22"/>
-      <c r="J53" s="22"/>
-      <c r="K53" s="22"/>
-      <c r="L53" s="22"/>
-      <c r="M53" s="22"/>
-      <c r="N53" s="22"/>
+      <c r="D53" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="E53" s="25"/>
+      <c r="F53" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="G53" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="H53" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="I53" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="J53" s="25">
+        <v>1</v>
+      </c>
+      <c r="K53" s="25">
+        <v>1</v>
+      </c>
+      <c r="L53" s="25">
+        <f xml:space="preserve">L52</f>
+        <v>0</v>
+      </c>
+      <c r="M53" s="25">
+        <v>5</v>
+      </c>
+      <c r="N53" s="25"/>
     </row>
     <row r="54" spans="4:14">
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="22"/>
-      <c r="I54" s="22"/>
-      <c r="J54" s="22"/>
-      <c r="K54" s="22"/>
-      <c r="L54" s="22"/>
-      <c r="M54" s="22"/>
-      <c r="N54" s="22"/>
+      <c r="D54" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="E54" s="25"/>
+      <c r="F54" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="G54" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="H54" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="I54" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="J54" s="25">
+        <v>1</v>
+      </c>
+      <c r="K54" s="25">
+        <v>1</v>
+      </c>
+      <c r="L54" s="25">
+        <f xml:space="preserve">L53</f>
+        <v>0</v>
+      </c>
+      <c r="M54" s="25">
+        <v>5</v>
+      </c>
+      <c r="N54" s="25"/>
+    </row>
+    <row r="55" ht="16" spans="4:14">
+      <c r="D55" s="25"/>
+      <c r="E55" s="25"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="25"/>
+      <c r="H55" s="34"/>
+      <c r="I55" s="25"/>
+      <c r="J55" s="25"/>
+      <c r="K55" s="25"/>
+      <c r="L55" s="25"/>
+      <c r="M55" s="25"/>
+      <c r="N55" s="25"/>
+    </row>
+    <row r="56" ht="16" spans="4:14">
+      <c r="D56" s="25"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="25"/>
+      <c r="H56" s="34"/>
+      <c r="I56" s="25"/>
+      <c r="J56" s="25"/>
+      <c r="K56" s="25"/>
+      <c r="L56" s="25"/>
+      <c r="M56" s="25"/>
+      <c r="N56" s="25"/>
+    </row>
+    <row r="57" ht="16" spans="4:14">
+      <c r="D57" s="25"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="25"/>
+      <c r="H57" s="25"/>
+      <c r="I57" s="25"/>
+      <c r="J57" s="25"/>
+      <c r="K57" s="25"/>
+      <c r="L57" s="25"/>
+      <c r="M57" s="25"/>
+      <c r="N57" s="25"/>
+    </row>
+    <row r="58" ht="16" spans="4:14">
+      <c r="D58" s="25"/>
+      <c r="E58" s="25"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="25"/>
+      <c r="H58" s="25"/>
+      <c r="I58" s="25"/>
+      <c r="J58" s="25"/>
+      <c r="K58" s="25"/>
+      <c r="L58" s="25"/>
+      <c r="M58" s="25"/>
+      <c r="N58" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4591,7 +4849,7 @@
     <row r="12" spans="6:18">
       <c r="K12" s="1"/>
       <c r="L12" s="1" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -4641,10 +4899,10 @@
     </row>
     <row r="14" spans="6:18">
       <c r="F14" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="H14" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -4663,7 +4921,7 @@
     </row>
     <row r="15" spans="6:18">
       <c r="H15" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -4779,7 +5037,7 @@
     <row r="26" spans="6:18">
       <c r="K26" s="1"/>
       <c r="L26" s="1" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -4829,10 +5087,10 @@
     </row>
     <row r="28" ht="16" spans="6:18">
       <c r="F28" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -4851,7 +5109,7 @@
     </row>
     <row r="29" spans="6:18">
       <c r="H29" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -4917,7 +5175,7 @@
     <row r="35" spans="6:18">
       <c r="K35" s="1"/>
       <c r="L35" s="1" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
@@ -4965,10 +5223,10 @@
     </row>
     <row r="37" spans="6:18">
       <c r="F37" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="H37" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -4986,7 +5244,7 @@
     </row>
     <row r="38" spans="6:18">
       <c r="H38" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -5002,7 +5260,7 @@
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
@@ -5040,13 +5298,13 @@
         <v>59</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>4</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>25</v>
@@ -5098,7 +5356,7 @@
     <row r="53" ht="16" spans="6:44">
       <c r="F53" s="8"/>
       <c r="G53" s="3" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>110</v>
@@ -5111,13 +5369,13 @@
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="M53" s="11" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="O53" s="3">
         <v>10</v>
@@ -5187,7 +5445,7 @@
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
@@ -5203,13 +5461,13 @@
         <v>59</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="I62" s="7" t="s">
         <v>4</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>25</v>
@@ -5235,7 +5493,7 @@
     </row>
     <row r="63" ht="16" spans="6:44">
       <c r="G63" s="3" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>110</v>
@@ -5248,13 +5506,13 @@
       </c>
       <c r="K63" s="3"/>
       <c r="L63" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="M63" s="11" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="O63" s="3">
         <v>10</v>
@@ -5332,7 +5590,7 @@
       <c r="G70" s="13"/>
       <c r="H70" s="13"/>
       <c r="I70" s="14" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="J70" s="15"/>
       <c r="K70" s="15"/>
@@ -5349,13 +5607,13 @@
         <v>59</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="I71" s="16" t="s">
         <v>4</v>
       </c>
       <c r="J71" s="15" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="K71" s="13" t="s">
         <v>25</v>
@@ -5381,7 +5639,7 @@
     </row>
     <row r="72" ht="16" spans="7:20">
       <c r="G72" s="13" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="H72" s="13" t="s">
         <v>110</v>
@@ -5429,7 +5687,7 @@
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
       <c r="I80" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="J80" s="5"/>
       <c r="K80" s="5"/>
@@ -5445,13 +5703,13 @@
         <v>59</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="I81" s="7" t="s">
         <v>4</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>25</v>
@@ -5477,7 +5735,7 @@
     </row>
     <row r="82" ht="16" spans="7:17">
       <c r="G82" s="3" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>110</v>
@@ -5490,13 +5748,13 @@
       </c>
       <c r="K82" s="3"/>
       <c r="L82" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="M82" s="11" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="O82" s="3">
         <v>10</v>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -245,7 +245,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="173">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -695,6 +695,12 @@
   </si>
   <si>
     <t>2050, 2150</t>
+  </si>
+  <si>
+    <t>UC_totco2Emi4</t>
+  </si>
+  <si>
+    <t>TOTCO2</t>
   </si>
   <si>
     <t>~UC_T: LO</t>
@@ -980,14 +986,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <name val="Times New Roman"/>
+      <name val="Tahoma"/>
       <charset val="0"/>
     </font>
     <font>
@@ -1507,7 +1513,7 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1556,10 +1562,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1567,7 +1570,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
@@ -2107,7 +2109,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="47">
+      <c r="F21" s="43">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -2248,8 +2250,8 @@
       <c r="C5" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
       <c r="F5" s="25"/>
     </row>
     <row r="6" spans="2:13">
@@ -2265,19 +2267,19 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="40"/>
+      <c r="K6" s="37"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="38">
         <v>10</v>
       </c>
     </row>
@@ -2285,17 +2287,17 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="38">
         <v>7</v>
       </c>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="36"/>
     </row>
     <row r="9" ht="16" spans="2:13">
       <c r="B9" t="s">
@@ -2304,10 +2306,10 @@
       <c r="C9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="38">
         <v>10</v>
       </c>
     </row>
@@ -2315,17 +2317,17 @@
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="38">
         <v>8</v>
       </c>
-      <c r="K10" s="42"/>
-      <c r="L10" s="43"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="34"/>
     </row>
     <row r="11" ht="16" spans="2:13">
       <c r="B11" t="s">
@@ -2334,10 +2336,10 @@
       <c r="C11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="36">
         <v>1.5</v>
       </c>
     </row>
@@ -2348,10 +2350,10 @@
       <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="D12" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="39">
+      <c r="E12" s="36">
         <v>1.5</v>
       </c>
     </row>
@@ -2362,7 +2364,7 @@
       <c r="C13" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="36" t="s">
         <v>35</v>
       </c>
       <c r="E13" s="25">
@@ -2376,7 +2378,7 @@
       <c r="C14" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="36" t="s">
         <v>35</v>
       </c>
       <c r="E14" s="25">
@@ -2390,7 +2392,7 @@
       <c r="C15" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="36" t="s">
         <v>35</v>
       </c>
       <c r="E15" s="25">
@@ -2401,13 +2403,13 @@
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="44">
+      <c r="E16" s="40">
         <v>12</v>
       </c>
     </row>
@@ -2415,13 +2417,13 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="45" t="s">
+      <c r="D17" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="46">
+      <c r="E17" s="42">
         <v>0.2</v>
       </c>
       <c r="F17" s="25"/>
@@ -2430,13 +2432,13 @@
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="45" t="s">
+      <c r="D18" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="46">
+      <c r="E18" s="42">
         <v>0.2</v>
       </c>
       <c r="F18" s="25"/>
@@ -2448,10 +2450,10 @@
       <c r="C19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="45" t="s">
+      <c r="D19" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="46">
+      <c r="E19" s="42">
         <v>0.2</v>
       </c>
       <c r="F19" s="25"/>
@@ -2460,13 +2462,13 @@
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="39" t="s">
+      <c r="C20" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="45" t="s">
+      <c r="D20" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="46">
+      <c r="E20" s="42">
         <v>0.5</v>
       </c>
       <c r="F20" s="25"/>
@@ -2478,10 +2480,10 @@
       <c r="C21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="45" t="s">
+      <c r="D21" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="46">
+      <c r="E21" s="42">
         <v>0.8</v>
       </c>
       <c r="F21" s="25"/>
@@ -2493,10 +2495,10 @@
       <c r="C22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="45" t="s">
+      <c r="D22" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="39"/>
+      <c r="E22" s="36"/>
       <c r="F22" s="25"/>
     </row>
     <row r="23" spans="2:6">
@@ -2506,7 +2508,7 @@
       <c r="C23" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="45" t="s">
+      <c r="D23" s="41" t="s">
         <v>43</v>
       </c>
       <c r="E23" s="25">
@@ -2521,7 +2523,7 @@
       <c r="C24" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="45" t="s">
+      <c r="D24" s="41" t="s">
         <v>43</v>
       </c>
       <c r="E24" s="25">
@@ -2536,7 +2538,7 @@
       <c r="C25" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="45" t="s">
+      <c r="D25" s="41" t="s">
         <v>43</v>
       </c>
       <c r="E25" s="25">
@@ -2548,28 +2550,28 @@
       <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="45" t="s">
+      <c r="D26" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="39">
+      <c r="E26" s="36">
         <v>0.05</v>
       </c>
       <c r="F26" s="25"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="47" t="s">
+      <c r="B27" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="48" t="s">
+      <c r="C27" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="48" t="s">
+      <c r="D27" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="48">
+      <c r="E27" s="44">
         <v>2020</v>
       </c>
       <c r="F27" s="25"/>
@@ -2578,7 +2580,7 @@
       <c r="C28" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="48" t="s">
+      <c r="D28" s="44" t="s">
         <v>45</v>
       </c>
       <c r="E28" s="28">
@@ -2616,360 +2618,360 @@
       <c r="E38" s="1"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="49" t="s">
+      <c r="C54" s="45" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="49"/>
-      <c r="E56" s="49"/>
-      <c r="F56" s="49"/>
-      <c r="G56" s="49"/>
-      <c r="H56" s="49"/>
-      <c r="I56" s="49"/>
-      <c r="J56" s="49"/>
-      <c r="K56" s="49"/>
+      <c r="D56" s="45"/>
+      <c r="E56" s="45"/>
+      <c r="F56" s="45"/>
+      <c r="G56" s="45"/>
+      <c r="H56" s="45"/>
+      <c r="I56" s="45"/>
+      <c r="J56" s="45"/>
+      <c r="K56" s="45"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="49" t="s">
+      <c r="C57" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="49" t="s">
+      <c r="D57" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="49" t="s">
+      <c r="E57" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="F57" s="49" t="s">
+      <c r="F57" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="G57" s="49" t="s">
+      <c r="G57" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="49" t="s">
+      <c r="H57" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="49" t="s">
+      <c r="I57" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="J57" s="49" t="s">
+      <c r="J57" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="K57" s="49" t="s">
+      <c r="K57" s="45" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="49"/>
-      <c r="D58" s="49"/>
-      <c r="E58" s="49"/>
-      <c r="F58" s="49"/>
-      <c r="G58" s="49"/>
-      <c r="H58" s="49"/>
-      <c r="I58" s="49"/>
-      <c r="J58" s="49"/>
-      <c r="K58" s="49"/>
+      <c r="C58" s="45"/>
+      <c r="D58" s="45"/>
+      <c r="E58" s="45"/>
+      <c r="F58" s="45"/>
+      <c r="G58" s="45"/>
+      <c r="H58" s="45"/>
+      <c r="I58" s="45"/>
+      <c r="J58" s="45"/>
+      <c r="K58" s="45"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="49"/>
-      <c r="D59" s="49"/>
-      <c r="E59" s="49"/>
-      <c r="F59" s="49"/>
-      <c r="G59" s="49"/>
-      <c r="H59" s="49"/>
-      <c r="I59" s="49"/>
-      <c r="J59" s="49"/>
-      <c r="K59" s="49"/>
+      <c r="C59" s="45"/>
+      <c r="D59" s="45"/>
+      <c r="E59" s="45"/>
+      <c r="F59" s="45"/>
+      <c r="G59" s="45"/>
+      <c r="H59" s="45"/>
+      <c r="I59" s="45"/>
+      <c r="J59" s="45"/>
+      <c r="K59" s="45"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="49"/>
-      <c r="D60" s="49"/>
-      <c r="E60" s="49"/>
-      <c r="F60" s="49"/>
-      <c r="G60" s="49"/>
-      <c r="H60" s="49"/>
-      <c r="I60" s="49"/>
-      <c r="J60" s="49"/>
-      <c r="K60" s="49"/>
+      <c r="C60" s="45"/>
+      <c r="D60" s="45"/>
+      <c r="E60" s="45"/>
+      <c r="F60" s="45"/>
+      <c r="G60" s="45"/>
+      <c r="H60" s="45"/>
+      <c r="I60" s="45"/>
+      <c r="J60" s="45"/>
+      <c r="K60" s="45"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="49"/>
-      <c r="D61" s="49"/>
-      <c r="E61" s="49"/>
-      <c r="F61" s="49"/>
-      <c r="G61" s="49"/>
-      <c r="H61" s="49"/>
-      <c r="I61" s="49"/>
-      <c r="J61" s="49"/>
-      <c r="K61" s="49"/>
+      <c r="C61" s="45"/>
+      <c r="D61" s="45"/>
+      <c r="E61" s="45"/>
+      <c r="F61" s="45"/>
+      <c r="G61" s="45"/>
+      <c r="H61" s="45"/>
+      <c r="I61" s="45"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="45"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="49"/>
-      <c r="D62" s="49"/>
-      <c r="E62" s="49"/>
-      <c r="F62" s="49"/>
-      <c r="G62" s="49"/>
-      <c r="H62" s="49"/>
-      <c r="I62" s="49"/>
-      <c r="J62" s="49"/>
-      <c r="K62" s="49"/>
+      <c r="C62" s="45"/>
+      <c r="D62" s="45"/>
+      <c r="E62" s="45"/>
+      <c r="F62" s="45"/>
+      <c r="G62" s="45"/>
+      <c r="H62" s="45"/>
+      <c r="I62" s="45"/>
+      <c r="J62" s="45"/>
+      <c r="K62" s="45"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="49"/>
-      <c r="D63" s="49"/>
-      <c r="E63" s="49"/>
-      <c r="F63" s="49"/>
-      <c r="G63" s="49"/>
-      <c r="H63" s="49"/>
-      <c r="I63" s="49"/>
-      <c r="J63" s="49"/>
-      <c r="K63" s="49"/>
+      <c r="C63" s="45"/>
+      <c r="D63" s="45"/>
+      <c r="E63" s="45"/>
+      <c r="F63" s="45"/>
+      <c r="G63" s="45"/>
+      <c r="H63" s="45"/>
+      <c r="I63" s="45"/>
+      <c r="J63" s="45"/>
+      <c r="K63" s="45"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="49"/>
-      <c r="D64" s="49"/>
-      <c r="E64" s="49"/>
-      <c r="F64" s="49"/>
-      <c r="G64" s="49"/>
-      <c r="H64" s="49"/>
-      <c r="I64" s="49"/>
-      <c r="J64" s="49"/>
-      <c r="K64" s="49"/>
+      <c r="C64" s="45"/>
+      <c r="D64" s="45"/>
+      <c r="E64" s="45"/>
+      <c r="F64" s="45"/>
+      <c r="G64" s="45"/>
+      <c r="H64" s="45"/>
+      <c r="I64" s="45"/>
+      <c r="J64" s="45"/>
+      <c r="K64" s="45"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="49"/>
-      <c r="D65" s="49"/>
-      <c r="E65" s="49"/>
-      <c r="F65" s="49"/>
-      <c r="G65" s="49"/>
-      <c r="H65" s="49"/>
-      <c r="I65" s="49"/>
-      <c r="J65" s="49"/>
-      <c r="K65" s="49"/>
+      <c r="C65" s="45"/>
+      <c r="D65" s="45"/>
+      <c r="E65" s="45"/>
+      <c r="F65" s="45"/>
+      <c r="G65" s="45"/>
+      <c r="H65" s="45"/>
+      <c r="I65" s="45"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="45"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="49"/>
-      <c r="D66" s="49"/>
-      <c r="E66" s="49"/>
-      <c r="F66" s="49"/>
-      <c r="G66" s="49"/>
-      <c r="H66" s="49"/>
-      <c r="I66" s="49"/>
-      <c r="J66" s="49"/>
-      <c r="K66" s="49"/>
+      <c r="C66" s="45"/>
+      <c r="D66" s="45"/>
+      <c r="E66" s="45"/>
+      <c r="F66" s="45"/>
+      <c r="G66" s="45"/>
+      <c r="H66" s="45"/>
+      <c r="I66" s="45"/>
+      <c r="J66" s="45"/>
+      <c r="K66" s="45"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="49"/>
-      <c r="D67" s="49"/>
-      <c r="E67" s="49"/>
-      <c r="F67" s="49"/>
-      <c r="G67" s="49"/>
-      <c r="H67" s="49"/>
-      <c r="I67" s="49"/>
-      <c r="J67" s="49"/>
-      <c r="K67" s="49"/>
+      <c r="C67" s="45"/>
+      <c r="D67" s="45"/>
+      <c r="E67" s="45"/>
+      <c r="F67" s="45"/>
+      <c r="G67" s="45"/>
+      <c r="H67" s="45"/>
+      <c r="I67" s="45"/>
+      <c r="J67" s="45"/>
+      <c r="K67" s="45"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="49"/>
-      <c r="D68" s="49"/>
-      <c r="E68" s="49"/>
-      <c r="F68" s="49"/>
-      <c r="G68" s="49"/>
-      <c r="H68" s="49"/>
-      <c r="I68" s="49"/>
-      <c r="J68" s="49"/>
-      <c r="K68" s="49"/>
+      <c r="C68" s="45"/>
+      <c r="D68" s="45"/>
+      <c r="E68" s="45"/>
+      <c r="F68" s="45"/>
+      <c r="G68" s="45"/>
+      <c r="H68" s="45"/>
+      <c r="I68" s="45"/>
+      <c r="J68" s="45"/>
+      <c r="K68" s="45"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="49"/>
-      <c r="D69" s="49"/>
-      <c r="E69" s="49"/>
-      <c r="F69" s="49"/>
-      <c r="G69" s="49"/>
-      <c r="H69" s="49"/>
-      <c r="I69" s="49"/>
-      <c r="J69" s="49"/>
-      <c r="K69" s="49"/>
+      <c r="C69" s="45"/>
+      <c r="D69" s="45"/>
+      <c r="E69" s="45"/>
+      <c r="F69" s="45"/>
+      <c r="G69" s="45"/>
+      <c r="H69" s="45"/>
+      <c r="I69" s="45"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="45"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="49"/>
-      <c r="D70" s="49"/>
-      <c r="E70" s="49"/>
-      <c r="F70" s="49"/>
-      <c r="G70" s="49"/>
-      <c r="H70" s="49"/>
-      <c r="I70" s="49"/>
-      <c r="J70" s="49"/>
-      <c r="K70" s="49"/>
+      <c r="C70" s="45"/>
+      <c r="D70" s="45"/>
+      <c r="E70" s="45"/>
+      <c r="F70" s="45"/>
+      <c r="G70" s="45"/>
+      <c r="H70" s="45"/>
+      <c r="I70" s="45"/>
+      <c r="J70" s="45"/>
+      <c r="K70" s="45"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="49"/>
-      <c r="D71" s="49"/>
-      <c r="E71" s="49"/>
-      <c r="F71" s="49"/>
-      <c r="G71" s="49"/>
-      <c r="H71" s="49"/>
-      <c r="I71" s="49"/>
-      <c r="J71" s="49"/>
-      <c r="K71" s="49"/>
+      <c r="C71" s="45"/>
+      <c r="D71" s="45"/>
+      <c r="E71" s="45"/>
+      <c r="F71" s="45"/>
+      <c r="G71" s="45"/>
+      <c r="H71" s="45"/>
+      <c r="I71" s="45"/>
+      <c r="J71" s="45"/>
+      <c r="K71" s="45"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="49"/>
-      <c r="D72" s="49"/>
-      <c r="E72" s="49"/>
-      <c r="F72" s="49"/>
-      <c r="G72" s="49"/>
-      <c r="H72" s="49"/>
-      <c r="I72" s="49"/>
-      <c r="J72" s="49"/>
-      <c r="K72" s="49"/>
+      <c r="C72" s="45"/>
+      <c r="D72" s="45"/>
+      <c r="E72" s="45"/>
+      <c r="F72" s="45"/>
+      <c r="G72" s="45"/>
+      <c r="H72" s="45"/>
+      <c r="I72" s="45"/>
+      <c r="J72" s="45"/>
+      <c r="K72" s="45"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="49"/>
-      <c r="D73" s="49"/>
-      <c r="E73" s="49"/>
-      <c r="F73" s="49"/>
-      <c r="G73" s="49"/>
-      <c r="H73" s="49"/>
-      <c r="I73" s="49"/>
-      <c r="J73" s="49"/>
-      <c r="K73" s="49"/>
+      <c r="C73" s="45"/>
+      <c r="D73" s="45"/>
+      <c r="E73" s="45"/>
+      <c r="F73" s="45"/>
+      <c r="G73" s="45"/>
+      <c r="H73" s="45"/>
+      <c r="I73" s="45"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="45"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="49"/>
-      <c r="D74" s="49"/>
-      <c r="E74" s="49"/>
-      <c r="F74" s="49"/>
-      <c r="G74" s="49"/>
-      <c r="H74" s="49"/>
-      <c r="I74" s="49"/>
-      <c r="J74" s="49"/>
-      <c r="K74" s="49"/>
+      <c r="C74" s="45"/>
+      <c r="D74" s="45"/>
+      <c r="E74" s="45"/>
+      <c r="F74" s="45"/>
+      <c r="G74" s="45"/>
+      <c r="H74" s="45"/>
+      <c r="I74" s="45"/>
+      <c r="J74" s="45"/>
+      <c r="K74" s="45"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="49"/>
-      <c r="D75" s="49"/>
-      <c r="E75" s="49"/>
-      <c r="F75" s="49"/>
-      <c r="G75" s="49"/>
-      <c r="H75" s="49"/>
-      <c r="I75" s="49"/>
-      <c r="J75" s="49"/>
-      <c r="K75" s="49"/>
+      <c r="C75" s="45"/>
+      <c r="D75" s="45"/>
+      <c r="E75" s="45"/>
+      <c r="F75" s="45"/>
+      <c r="G75" s="45"/>
+      <c r="H75" s="45"/>
+      <c r="I75" s="45"/>
+      <c r="J75" s="45"/>
+      <c r="K75" s="45"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="49"/>
-      <c r="D76" s="49"/>
-      <c r="E76" s="49"/>
-      <c r="F76" s="49"/>
-      <c r="G76" s="49"/>
-      <c r="H76" s="49"/>
-      <c r="I76" s="49"/>
-      <c r="J76" s="49"/>
-      <c r="K76" s="49"/>
+      <c r="C76" s="45"/>
+      <c r="D76" s="45"/>
+      <c r="E76" s="45"/>
+      <c r="F76" s="45"/>
+      <c r="G76" s="45"/>
+      <c r="H76" s="45"/>
+      <c r="I76" s="45"/>
+      <c r="J76" s="45"/>
+      <c r="K76" s="45"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="49"/>
-      <c r="D77" s="49"/>
-      <c r="E77" s="49"/>
-      <c r="F77" s="49"/>
-      <c r="G77" s="49"/>
-      <c r="H77" s="49"/>
-      <c r="I77" s="49"/>
-      <c r="J77" s="49"/>
-      <c r="K77" s="49"/>
+      <c r="C77" s="45"/>
+      <c r="D77" s="45"/>
+      <c r="E77" s="45"/>
+      <c r="F77" s="45"/>
+      <c r="G77" s="45"/>
+      <c r="H77" s="45"/>
+      <c r="I77" s="45"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="45"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="49"/>
-      <c r="D78" s="49"/>
-      <c r="E78" s="49"/>
-      <c r="F78" s="49"/>
-      <c r="G78" s="49"/>
-      <c r="H78" s="49"/>
-      <c r="I78" s="49"/>
-      <c r="J78" s="49"/>
-      <c r="K78" s="49"/>
+      <c r="C78" s="45"/>
+      <c r="D78" s="45"/>
+      <c r="E78" s="45"/>
+      <c r="F78" s="45"/>
+      <c r="G78" s="45"/>
+      <c r="H78" s="45"/>
+      <c r="I78" s="45"/>
+      <c r="J78" s="45"/>
+      <c r="K78" s="45"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="49"/>
-      <c r="D79" s="49"/>
-      <c r="E79" s="49"/>
-      <c r="F79" s="49"/>
-      <c r="G79" s="49"/>
-      <c r="H79" s="49"/>
-      <c r="I79" s="49"/>
-      <c r="J79" s="49"/>
-      <c r="K79" s="49"/>
+      <c r="C79" s="45"/>
+      <c r="D79" s="45"/>
+      <c r="E79" s="45"/>
+      <c r="F79" s="45"/>
+      <c r="G79" s="45"/>
+      <c r="H79" s="45"/>
+      <c r="I79" s="45"/>
+      <c r="J79" s="45"/>
+      <c r="K79" s="45"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="49"/>
-      <c r="D80" s="49"/>
-      <c r="E80" s="49"/>
-      <c r="F80" s="49"/>
-      <c r="G80" s="49"/>
-      <c r="H80" s="49"/>
-      <c r="I80" s="49"/>
-      <c r="J80" s="49"/>
-      <c r="K80" s="49"/>
+      <c r="C80" s="45"/>
+      <c r="D80" s="45"/>
+      <c r="E80" s="45"/>
+      <c r="F80" s="45"/>
+      <c r="G80" s="45"/>
+      <c r="H80" s="45"/>
+      <c r="I80" s="45"/>
+      <c r="J80" s="45"/>
+      <c r="K80" s="45"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="49"/>
-      <c r="D81" s="49"/>
-      <c r="E81" s="49"/>
-      <c r="F81" s="49"/>
-      <c r="G81" s="49"/>
-      <c r="H81" s="49"/>
-      <c r="I81" s="49"/>
-      <c r="J81" s="49"/>
-      <c r="K81" s="49"/>
+      <c r="C81" s="45"/>
+      <c r="D81" s="45"/>
+      <c r="E81" s="45"/>
+      <c r="F81" s="45"/>
+      <c r="G81" s="45"/>
+      <c r="H81" s="45"/>
+      <c r="I81" s="45"/>
+      <c r="J81" s="45"/>
+      <c r="K81" s="45"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="49"/>
-      <c r="D82" s="49"/>
-      <c r="E82" s="49"/>
-      <c r="F82" s="49"/>
-      <c r="G82" s="49"/>
-      <c r="H82" s="49"/>
-      <c r="I82" s="49"/>
-      <c r="J82" s="49"/>
-      <c r="K82" s="49"/>
+      <c r="C82" s="45"/>
+      <c r="D82" s="45"/>
+      <c r="E82" s="45"/>
+      <c r="F82" s="45"/>
+      <c r="G82" s="45"/>
+      <c r="H82" s="45"/>
+      <c r="I82" s="45"/>
+      <c r="J82" s="45"/>
+      <c r="K82" s="45"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="49"/>
-      <c r="D83" s="49"/>
-      <c r="E83" s="49"/>
-      <c r="F83" s="49"/>
-      <c r="G83" s="49"/>
-      <c r="H83" s="49"/>
-      <c r="I83" s="49"/>
-      <c r="J83" s="49"/>
-      <c r="K83" s="49"/>
+      <c r="C83" s="45"/>
+      <c r="D83" s="45"/>
+      <c r="E83" s="45"/>
+      <c r="F83" s="45"/>
+      <c r="G83" s="45"/>
+      <c r="H83" s="45"/>
+      <c r="I83" s="45"/>
+      <c r="J83" s="45"/>
+      <c r="K83" s="45"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="49" t="s">
+      <c r="C84" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="D84" s="49">
-        <v>1</v>
-      </c>
-      <c r="E84" s="49"/>
-      <c r="F84" s="49"/>
-      <c r="G84" s="49"/>
-      <c r="H84" s="49"/>
-      <c r="I84" s="49"/>
-      <c r="J84" s="49"/>
-      <c r="K84" s="49"/>
+      <c r="D84" s="45">
+        <v>1</v>
+      </c>
+      <c r="E84" s="45"/>
+      <c r="F84" s="45"/>
+      <c r="G84" s="45"/>
+      <c r="H84" s="45"/>
+      <c r="I84" s="45"/>
+      <c r="J84" s="45"/>
+      <c r="K84" s="45"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="49"/>
-      <c r="D85" s="49"/>
-      <c r="E85" s="49"/>
-      <c r="F85" s="49"/>
-      <c r="G85" s="49"/>
-      <c r="H85" s="49"/>
-      <c r="I85" s="49"/>
-      <c r="J85" s="49"/>
-      <c r="K85" s="49"/>
+      <c r="C85" s="45"/>
+      <c r="D85" s="45"/>
+      <c r="E85" s="45"/>
+      <c r="F85" s="45"/>
+      <c r="G85" s="45"/>
+      <c r="H85" s="45"/>
+      <c r="I85" s="45"/>
+      <c r="J85" s="45"/>
+      <c r="K85" s="45"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4636,13 +4638,13 @@
       <c r="G51" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="H51" s="34" t="s">
+      <c r="H51" s="31" t="s">
         <v>4</v>
       </c>
       <c r="I51" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="J51" s="35" t="s">
+      <c r="J51" s="2" t="s">
         <v>139</v>
       </c>
       <c r="K51" s="25" t="s">
@@ -4663,13 +4665,13 @@
         <v>141</v>
       </c>
       <c r="E52" s="25"/>
-      <c r="F52" s="36" t="s">
+      <c r="F52" s="34" t="s">
         <v>142</v>
       </c>
       <c r="G52" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="H52" s="37" t="s">
+      <c r="H52" s="31" t="s">
         <v>144</v>
       </c>
       <c r="I52" s="25" t="s">
@@ -4694,13 +4696,13 @@
         <v>145</v>
       </c>
       <c r="E53" s="25"/>
-      <c r="F53" s="36" t="s">
+      <c r="F53" s="34" t="s">
         <v>146</v>
       </c>
       <c r="G53" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="H53" s="38" t="s">
+      <c r="H53" s="35" t="s">
         <v>125</v>
       </c>
       <c r="I53" s="25" t="s">
@@ -4713,7 +4715,7 @@
         <v>1</v>
       </c>
       <c r="L53" s="25">
-        <f xml:space="preserve">L52</f>
+        <f t="shared" ref="L53:L55" si="7" xml:space="preserve">L52</f>
         <v>0</v>
       </c>
       <c r="M53" s="25">
@@ -4726,13 +4728,13 @@
         <v>147</v>
       </c>
       <c r="E54" s="25"/>
-      <c r="F54" s="36" t="s">
+      <c r="F54" s="34" t="s">
         <v>148</v>
       </c>
       <c r="G54" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="H54" s="34" t="s">
+      <c r="H54" s="31" t="s">
         <v>149</v>
       </c>
       <c r="I54" s="25" t="s">
@@ -4745,7 +4747,7 @@
         <v>1</v>
       </c>
       <c r="L54" s="25">
-        <f xml:space="preserve">L53</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M54" s="25">
@@ -4754,16 +4756,35 @@
       <c r="N54" s="25"/>
     </row>
     <row r="55" ht="16" spans="4:14">
-      <c r="D55" s="25"/>
+      <c r="D55" s="25" t="s">
+        <v>150</v>
+      </c>
       <c r="E55" s="25"/>
-      <c r="F55" s="26"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="34"/>
-      <c r="I55" s="25"/>
-      <c r="J55" s="25"/>
-      <c r="K55" s="25"/>
-      <c r="L55" s="25"/>
-      <c r="M55" s="25"/>
+      <c r="F55" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="G55" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="H55" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="I55" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="J55" s="25">
+        <v>1</v>
+      </c>
+      <c r="K55" s="25">
+        <v>1</v>
+      </c>
+      <c r="L55" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="M55" s="25">
+        <v>5</v>
+      </c>
       <c r="N55" s="25"/>
     </row>
     <row r="56" ht="16" spans="4:14">
@@ -4771,7 +4792,7 @@
       <c r="E56" s="25"/>
       <c r="F56" s="26"/>
       <c r="G56" s="25"/>
-      <c r="H56" s="34"/>
+      <c r="H56" s="31"/>
       <c r="I56" s="25"/>
       <c r="J56" s="25"/>
       <c r="K56" s="25"/>
@@ -4849,7 +4870,7 @@
     <row r="12" spans="6:18">
       <c r="K12" s="1"/>
       <c r="L12" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -4899,10 +4920,10 @@
     </row>
     <row r="14" spans="6:18">
       <c r="F14" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H14" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -4921,7 +4942,7 @@
     </row>
     <row r="15" spans="6:18">
       <c r="H15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -5037,7 +5058,7 @@
     <row r="26" spans="6:18">
       <c r="K26" s="1"/>
       <c r="L26" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -5087,10 +5108,10 @@
     </row>
     <row r="28" ht="16" spans="6:18">
       <c r="F28" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -5109,7 +5130,7 @@
     </row>
     <row r="29" spans="6:18">
       <c r="H29" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -5175,7 +5196,7 @@
     <row r="35" spans="6:18">
       <c r="K35" s="1"/>
       <c r="L35" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
@@ -5223,10 +5244,10 @@
     </row>
     <row r="37" spans="6:18">
       <c r="F37" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H37" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -5244,7 +5265,7 @@
     </row>
     <row r="38" spans="6:18">
       <c r="H38" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -5260,7 +5281,7 @@
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
@@ -5298,13 +5319,13 @@
         <v>59</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>4</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>25</v>
@@ -5356,7 +5377,7 @@
     <row r="53" ht="16" spans="6:44">
       <c r="F53" s="8"/>
       <c r="G53" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>110</v>
@@ -5369,13 +5390,13 @@
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M53" s="11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O53" s="3">
         <v>10</v>
@@ -5445,7 +5466,7 @@
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
@@ -5461,13 +5482,13 @@
         <v>59</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I62" s="7" t="s">
         <v>4</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>25</v>
@@ -5493,7 +5514,7 @@
     </row>
     <row r="63" ht="16" spans="6:44">
       <c r="G63" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>110</v>
@@ -5506,13 +5527,13 @@
       </c>
       <c r="K63" s="3"/>
       <c r="L63" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M63" s="11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O63" s="3">
         <v>10</v>
@@ -5590,7 +5611,7 @@
       <c r="G70" s="13"/>
       <c r="H70" s="13"/>
       <c r="I70" s="14" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J70" s="15"/>
       <c r="K70" s="15"/>
@@ -5607,13 +5628,13 @@
         <v>59</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I71" s="16" t="s">
         <v>4</v>
       </c>
       <c r="J71" s="15" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K71" s="13" t="s">
         <v>25</v>
@@ -5639,7 +5660,7 @@
     </row>
     <row r="72" ht="16" spans="7:20">
       <c r="G72" s="13" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H72" s="13" t="s">
         <v>110</v>
@@ -5687,7 +5708,7 @@
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
       <c r="I80" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J80" s="5"/>
       <c r="K80" s="5"/>
@@ -5703,13 +5724,13 @@
         <v>59</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I81" s="7" t="s">
         <v>4</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>25</v>
@@ -5735,7 +5756,7 @@
     </row>
     <row r="82" ht="16" spans="7:17">
       <c r="G82" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>110</v>
@@ -5748,13 +5769,13 @@
       </c>
       <c r="K82" s="3"/>
       <c r="L82" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M82" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O82" s="3">
         <v>10</v>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="6"/>
+    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
@@ -15,6 +15,7 @@
     <sheet name="Peak_demand_limit_battery" sheetId="13" r:id="rId6"/>
     <sheet name="Growth_rate" sheetId="12" r:id="rId7"/>
     <sheet name="util_limit" sheetId="14" r:id="rId8"/>
+    <sheet name="Elc_limit" sheetId="15" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="IQ_FWD_Q" hidden="1">501</definedName>
@@ -244,8 +245,40 @@
 </comments>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>xli9</author>
+  </authors>
+  <commentList>
+    <comment ref="D7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t>xli9:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">
+Should remove ,Tra_bev* bcz it’s already contained in AuxStoOut</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="180">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -764,6 +797,27 @@
   </si>
   <si>
     <t>Tra_BEV_Batt_VtoG</t>
+  </si>
+  <si>
+    <t>UC_RHSRTS</t>
+  </si>
+  <si>
+    <t>UC_RHSRTS~0</t>
+  </si>
+  <si>
+    <t>UCE_ElcBalance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELc curtailment not beyond 5% of demand </t>
+  </si>
+  <si>
+    <t>FT_TRAELC, FT_INDELC, ElecDemand</t>
+  </si>
+  <si>
+    <t>*Need to test if ElcDemand's UC_FLO can be captured or not</t>
+  </si>
+  <si>
+    <t>DEF_E</t>
   </si>
 </sst>
 </file>
@@ -993,12 +1047,12 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Times New Roman"/>
+      <name val="Tahoma"/>
       <charset val="0"/>
     </font>
     <font>
@@ -1014,6 +1068,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1096,12 +1156,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1253,6 +1307,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color rgb="FFFC8462"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFFC8462"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1264,17 +1329,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thick">
-        <color rgb="FFFC8462"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FFFC8462"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1385,7 +1439,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1409,16 +1463,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1427,16 +1481,16 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1510,71 +1564,74 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="51" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="51" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="53">
@@ -2109,7 +2166,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="43">
+      <c r="F21" s="46">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -2166,7 +2223,7 @@
       </c>
     </row>
     <row r="4" ht="16" spans="1:11">
-      <c r="A4" s="2"/>
+      <c r="A4" s="6"/>
     </row>
     <row r="7" spans="1:11">
       <c r="D7" t="s">
@@ -2223,10 +2280,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="13"/>
+      <c r="K10" s="16"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="13"/>
+      <c r="K11" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2247,12 +2304,12 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:13">
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="25"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="28"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
@@ -2267,19 +2324,19 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="37"/>
+      <c r="K6" s="40"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="41">
         <v>10</v>
       </c>
     </row>
@@ -2287,29 +2344,29 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="41">
         <v>7</v>
       </c>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="39"/>
     </row>
     <row r="9" ht="16" spans="2:13">
       <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="41">
         <v>10</v>
       </c>
     </row>
@@ -2317,29 +2374,29 @@
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="41">
         <v>8</v>
       </c>
-      <c r="K10" s="39"/>
-      <c r="L10" s="34"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="37"/>
     </row>
     <row r="11" ht="16" spans="2:13">
       <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="39">
         <v>1.5</v>
       </c>
     </row>
@@ -2347,13 +2404,13 @@
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="36">
+      <c r="E12" s="39">
         <v>1.5</v>
       </c>
     </row>
@@ -2361,13 +2418,13 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="28">
         <v>2</v>
       </c>
     </row>
@@ -2375,13 +2432,13 @@
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="36" t="s">
+      <c r="D14" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="28">
         <v>0</v>
       </c>
     </row>
@@ -2389,13 +2446,13 @@
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="36" t="s">
+      <c r="D15" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="28">
         <v>0</v>
       </c>
     </row>
@@ -2403,13 +2460,13 @@
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="36" t="s">
+      <c r="C16" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="36" t="s">
+      <c r="D16" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="40">
+      <c r="E16" s="43">
         <v>12</v>
       </c>
     </row>
@@ -2417,561 +2474,561 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="41" t="s">
+      <c r="D17" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="42">
+      <c r="E17" s="45">
         <v>0.2</v>
       </c>
-      <c r="F17" s="25"/>
+      <c r="F17" s="28"/>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="41" t="s">
+      <c r="D18" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="42">
+      <c r="E18" s="45">
         <v>0.2</v>
       </c>
-      <c r="F18" s="25"/>
+      <c r="F18" s="28"/>
     </row>
     <row r="19" ht="16" spans="2:6">
       <c r="B19" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="41" t="s">
+      <c r="D19" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="42">
+      <c r="E19" s="45">
         <v>0.2</v>
       </c>
-      <c r="F19" s="25"/>
+      <c r="F19" s="28"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="41" t="s">
+      <c r="D20" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="42">
+      <c r="E20" s="45">
         <v>0.5</v>
       </c>
-      <c r="F20" s="25"/>
+      <c r="F20" s="28"/>
     </row>
     <row r="21" ht="16" spans="2:6">
       <c r="B21" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="41" t="s">
+      <c r="D21" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="42">
+      <c r="E21" s="45">
         <v>0.8</v>
       </c>
-      <c r="F21" s="25"/>
+      <c r="F21" s="28"/>
     </row>
     <row r="22" ht="16" spans="2:6">
       <c r="B22" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="41" t="s">
+      <c r="D22" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="36"/>
-      <c r="F22" s="25"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="28"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="41" t="s">
+      <c r="D23" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="25">
-        <v>1</v>
-      </c>
-      <c r="F23" s="25"/>
+      <c r="E23" s="28">
+        <v>1</v>
+      </c>
+      <c r="F23" s="28"/>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="41" t="s">
+      <c r="D24" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="25">
-        <v>1</v>
-      </c>
-      <c r="F24" s="25"/>
+      <c r="E24" s="28">
+        <v>1</v>
+      </c>
+      <c r="F24" s="28"/>
     </row>
     <row r="25" ht="16" spans="2:6">
       <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="41" t="s">
+      <c r="D25" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="25">
-        <v>1</v>
-      </c>
-      <c r="F25" s="25"/>
+      <c r="E25" s="28">
+        <v>1</v>
+      </c>
+      <c r="F25" s="28"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="36" t="s">
+      <c r="C26" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="41" t="s">
+      <c r="D26" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="36">
+      <c r="E26" s="39">
         <v>0.05</v>
       </c>
-      <c r="F26" s="25"/>
+      <c r="F26" s="28"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="43" t="s">
+      <c r="B27" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="44" t="s">
+      <c r="C27" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="44" t="s">
+      <c r="D27" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="44">
+      <c r="E27" s="47">
         <v>2020</v>
       </c>
-      <c r="F27" s="25"/>
+      <c r="F27" s="28"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="C28" s="25" t="s">
+      <c r="C28" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="44" t="s">
+      <c r="D28" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="31">
         <v>2020</v>
       </c>
-      <c r="F28" s="25"/>
+      <c r="F28" s="28"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
     </row>
     <row r="38" spans="3:5">
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="45" t="s">
+      <c r="C54" s="48" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="45"/>
-      <c r="E56" s="45"/>
-      <c r="F56" s="45"/>
-      <c r="G56" s="45"/>
-      <c r="H56" s="45"/>
-      <c r="I56" s="45"/>
-      <c r="J56" s="45"/>
-      <c r="K56" s="45"/>
+      <c r="D56" s="48"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="48"/>
+      <c r="H56" s="48"/>
+      <c r="I56" s="48"/>
+      <c r="J56" s="48"/>
+      <c r="K56" s="48"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="45" t="s">
+      <c r="C57" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="45" t="s">
+      <c r="D57" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="45" t="s">
+      <c r="E57" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="F57" s="45" t="s">
+      <c r="F57" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="G57" s="45" t="s">
+      <c r="G57" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="45" t="s">
+      <c r="H57" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="45" t="s">
+      <c r="I57" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="J57" s="45" t="s">
+      <c r="J57" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="K57" s="45" t="s">
+      <c r="K57" s="48" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="45"/>
-      <c r="D58" s="45"/>
-      <c r="E58" s="45"/>
-      <c r="F58" s="45"/>
-      <c r="G58" s="45"/>
-      <c r="H58" s="45"/>
-      <c r="I58" s="45"/>
-      <c r="J58" s="45"/>
-      <c r="K58" s="45"/>
+      <c r="C58" s="48"/>
+      <c r="D58" s="48"/>
+      <c r="E58" s="48"/>
+      <c r="F58" s="48"/>
+      <c r="G58" s="48"/>
+      <c r="H58" s="48"/>
+      <c r="I58" s="48"/>
+      <c r="J58" s="48"/>
+      <c r="K58" s="48"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="45"/>
-      <c r="D59" s="45"/>
-      <c r="E59" s="45"/>
-      <c r="F59" s="45"/>
-      <c r="G59" s="45"/>
-      <c r="H59" s="45"/>
-      <c r="I59" s="45"/>
-      <c r="J59" s="45"/>
-      <c r="K59" s="45"/>
+      <c r="C59" s="48"/>
+      <c r="D59" s="48"/>
+      <c r="E59" s="48"/>
+      <c r="F59" s="48"/>
+      <c r="G59" s="48"/>
+      <c r="H59" s="48"/>
+      <c r="I59" s="48"/>
+      <c r="J59" s="48"/>
+      <c r="K59" s="48"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="45"/>
-      <c r="D60" s="45"/>
-      <c r="E60" s="45"/>
-      <c r="F60" s="45"/>
-      <c r="G60" s="45"/>
-      <c r="H60" s="45"/>
-      <c r="I60" s="45"/>
-      <c r="J60" s="45"/>
-      <c r="K60" s="45"/>
+      <c r="C60" s="48"/>
+      <c r="D60" s="48"/>
+      <c r="E60" s="48"/>
+      <c r="F60" s="48"/>
+      <c r="G60" s="48"/>
+      <c r="H60" s="48"/>
+      <c r="I60" s="48"/>
+      <c r="J60" s="48"/>
+      <c r="K60" s="48"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="45"/>
-      <c r="D61" s="45"/>
-      <c r="E61" s="45"/>
-      <c r="F61" s="45"/>
-      <c r="G61" s="45"/>
-      <c r="H61" s="45"/>
-      <c r="I61" s="45"/>
-      <c r="J61" s="45"/>
-      <c r="K61" s="45"/>
+      <c r="C61" s="48"/>
+      <c r="D61" s="48"/>
+      <c r="E61" s="48"/>
+      <c r="F61" s="48"/>
+      <c r="G61" s="48"/>
+      <c r="H61" s="48"/>
+      <c r="I61" s="48"/>
+      <c r="J61" s="48"/>
+      <c r="K61" s="48"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="45"/>
-      <c r="D62" s="45"/>
-      <c r="E62" s="45"/>
-      <c r="F62" s="45"/>
-      <c r="G62" s="45"/>
-      <c r="H62" s="45"/>
-      <c r="I62" s="45"/>
-      <c r="J62" s="45"/>
-      <c r="K62" s="45"/>
+      <c r="C62" s="48"/>
+      <c r="D62" s="48"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48"/>
+      <c r="J62" s="48"/>
+      <c r="K62" s="48"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="45"/>
-      <c r="D63" s="45"/>
-      <c r="E63" s="45"/>
-      <c r="F63" s="45"/>
-      <c r="G63" s="45"/>
-      <c r="H63" s="45"/>
-      <c r="I63" s="45"/>
-      <c r="J63" s="45"/>
-      <c r="K63" s="45"/>
+      <c r="C63" s="48"/>
+      <c r="D63" s="48"/>
+      <c r="E63" s="48"/>
+      <c r="F63" s="48"/>
+      <c r="G63" s="48"/>
+      <c r="H63" s="48"/>
+      <c r="I63" s="48"/>
+      <c r="J63" s="48"/>
+      <c r="K63" s="48"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="45"/>
-      <c r="D64" s="45"/>
-      <c r="E64" s="45"/>
-      <c r="F64" s="45"/>
-      <c r="G64" s="45"/>
-      <c r="H64" s="45"/>
-      <c r="I64" s="45"/>
-      <c r="J64" s="45"/>
-      <c r="K64" s="45"/>
+      <c r="C64" s="48"/>
+      <c r="D64" s="48"/>
+      <c r="E64" s="48"/>
+      <c r="F64" s="48"/>
+      <c r="G64" s="48"/>
+      <c r="H64" s="48"/>
+      <c r="I64" s="48"/>
+      <c r="J64" s="48"/>
+      <c r="K64" s="48"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="45"/>
-      <c r="D65" s="45"/>
-      <c r="E65" s="45"/>
-      <c r="F65" s="45"/>
-      <c r="G65" s="45"/>
-      <c r="H65" s="45"/>
-      <c r="I65" s="45"/>
-      <c r="J65" s="45"/>
-      <c r="K65" s="45"/>
+      <c r="C65" s="48"/>
+      <c r="D65" s="48"/>
+      <c r="E65" s="48"/>
+      <c r="F65" s="48"/>
+      <c r="G65" s="48"/>
+      <c r="H65" s="48"/>
+      <c r="I65" s="48"/>
+      <c r="J65" s="48"/>
+      <c r="K65" s="48"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="45"/>
-      <c r="D66" s="45"/>
-      <c r="E66" s="45"/>
-      <c r="F66" s="45"/>
-      <c r="G66" s="45"/>
-      <c r="H66" s="45"/>
-      <c r="I66" s="45"/>
-      <c r="J66" s="45"/>
-      <c r="K66" s="45"/>
+      <c r="C66" s="48"/>
+      <c r="D66" s="48"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="J66" s="48"/>
+      <c r="K66" s="48"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="45"/>
-      <c r="D67" s="45"/>
-      <c r="E67" s="45"/>
-      <c r="F67" s="45"/>
-      <c r="G67" s="45"/>
-      <c r="H67" s="45"/>
-      <c r="I67" s="45"/>
-      <c r="J67" s="45"/>
-      <c r="K67" s="45"/>
+      <c r="C67" s="48"/>
+      <c r="D67" s="48"/>
+      <c r="E67" s="48"/>
+      <c r="F67" s="48"/>
+      <c r="G67" s="48"/>
+      <c r="H67" s="48"/>
+      <c r="I67" s="48"/>
+      <c r="J67" s="48"/>
+      <c r="K67" s="48"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="45"/>
-      <c r="D68" s="45"/>
-      <c r="E68" s="45"/>
-      <c r="F68" s="45"/>
-      <c r="G68" s="45"/>
-      <c r="H68" s="45"/>
-      <c r="I68" s="45"/>
-      <c r="J68" s="45"/>
-      <c r="K68" s="45"/>
+      <c r="C68" s="48"/>
+      <c r="D68" s="48"/>
+      <c r="E68" s="48"/>
+      <c r="F68" s="48"/>
+      <c r="G68" s="48"/>
+      <c r="H68" s="48"/>
+      <c r="I68" s="48"/>
+      <c r="J68" s="48"/>
+      <c r="K68" s="48"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="45"/>
-      <c r="D69" s="45"/>
-      <c r="E69" s="45"/>
-      <c r="F69" s="45"/>
-      <c r="G69" s="45"/>
-      <c r="H69" s="45"/>
-      <c r="I69" s="45"/>
-      <c r="J69" s="45"/>
-      <c r="K69" s="45"/>
+      <c r="C69" s="48"/>
+      <c r="D69" s="48"/>
+      <c r="E69" s="48"/>
+      <c r="F69" s="48"/>
+      <c r="G69" s="48"/>
+      <c r="H69" s="48"/>
+      <c r="I69" s="48"/>
+      <c r="J69" s="48"/>
+      <c r="K69" s="48"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="45"/>
-      <c r="D70" s="45"/>
-      <c r="E70" s="45"/>
-      <c r="F70" s="45"/>
-      <c r="G70" s="45"/>
-      <c r="H70" s="45"/>
-      <c r="I70" s="45"/>
-      <c r="J70" s="45"/>
-      <c r="K70" s="45"/>
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="48"/>
+      <c r="K70" s="48"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="45"/>
-      <c r="D71" s="45"/>
-      <c r="E71" s="45"/>
-      <c r="F71" s="45"/>
-      <c r="G71" s="45"/>
-      <c r="H71" s="45"/>
-      <c r="I71" s="45"/>
-      <c r="J71" s="45"/>
-      <c r="K71" s="45"/>
+      <c r="C71" s="48"/>
+      <c r="D71" s="48"/>
+      <c r="E71" s="48"/>
+      <c r="F71" s="48"/>
+      <c r="G71" s="48"/>
+      <c r="H71" s="48"/>
+      <c r="I71" s="48"/>
+      <c r="J71" s="48"/>
+      <c r="K71" s="48"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="45"/>
-      <c r="D72" s="45"/>
-      <c r="E72" s="45"/>
-      <c r="F72" s="45"/>
-      <c r="G72" s="45"/>
-      <c r="H72" s="45"/>
-      <c r="I72" s="45"/>
-      <c r="J72" s="45"/>
-      <c r="K72" s="45"/>
+      <c r="C72" s="48"/>
+      <c r="D72" s="48"/>
+      <c r="E72" s="48"/>
+      <c r="F72" s="48"/>
+      <c r="G72" s="48"/>
+      <c r="H72" s="48"/>
+      <c r="I72" s="48"/>
+      <c r="J72" s="48"/>
+      <c r="K72" s="48"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="45"/>
-      <c r="D73" s="45"/>
-      <c r="E73" s="45"/>
-      <c r="F73" s="45"/>
-      <c r="G73" s="45"/>
-      <c r="H73" s="45"/>
-      <c r="I73" s="45"/>
-      <c r="J73" s="45"/>
-      <c r="K73" s="45"/>
+      <c r="C73" s="48"/>
+      <c r="D73" s="48"/>
+      <c r="E73" s="48"/>
+      <c r="F73" s="48"/>
+      <c r="G73" s="48"/>
+      <c r="H73" s="48"/>
+      <c r="I73" s="48"/>
+      <c r="J73" s="48"/>
+      <c r="K73" s="48"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="45"/>
-      <c r="D74" s="45"/>
-      <c r="E74" s="45"/>
-      <c r="F74" s="45"/>
-      <c r="G74" s="45"/>
-      <c r="H74" s="45"/>
-      <c r="I74" s="45"/>
-      <c r="J74" s="45"/>
-      <c r="K74" s="45"/>
+      <c r="C74" s="48"/>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
+      <c r="J74" s="48"/>
+      <c r="K74" s="48"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="45"/>
-      <c r="D75" s="45"/>
-      <c r="E75" s="45"/>
-      <c r="F75" s="45"/>
-      <c r="G75" s="45"/>
-      <c r="H75" s="45"/>
-      <c r="I75" s="45"/>
-      <c r="J75" s="45"/>
-      <c r="K75" s="45"/>
+      <c r="C75" s="48"/>
+      <c r="D75" s="48"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="48"/>
+      <c r="H75" s="48"/>
+      <c r="I75" s="48"/>
+      <c r="J75" s="48"/>
+      <c r="K75" s="48"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="45"/>
-      <c r="D76" s="45"/>
-      <c r="E76" s="45"/>
-      <c r="F76" s="45"/>
-      <c r="G76" s="45"/>
-      <c r="H76" s="45"/>
-      <c r="I76" s="45"/>
-      <c r="J76" s="45"/>
-      <c r="K76" s="45"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
+      <c r="J76" s="48"/>
+      <c r="K76" s="48"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="45"/>
-      <c r="D77" s="45"/>
-      <c r="E77" s="45"/>
-      <c r="F77" s="45"/>
-      <c r="G77" s="45"/>
-      <c r="H77" s="45"/>
-      <c r="I77" s="45"/>
-      <c r="J77" s="45"/>
-      <c r="K77" s="45"/>
+      <c r="C77" s="48"/>
+      <c r="D77" s="48"/>
+      <c r="E77" s="48"/>
+      <c r="F77" s="48"/>
+      <c r="G77" s="48"/>
+      <c r="H77" s="48"/>
+      <c r="I77" s="48"/>
+      <c r="J77" s="48"/>
+      <c r="K77" s="48"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="45"/>
-      <c r="D78" s="45"/>
-      <c r="E78" s="45"/>
-      <c r="F78" s="45"/>
-      <c r="G78" s="45"/>
-      <c r="H78" s="45"/>
-      <c r="I78" s="45"/>
-      <c r="J78" s="45"/>
-      <c r="K78" s="45"/>
+      <c r="C78" s="48"/>
+      <c r="D78" s="48"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="48"/>
+      <c r="G78" s="48"/>
+      <c r="H78" s="48"/>
+      <c r="I78" s="48"/>
+      <c r="J78" s="48"/>
+      <c r="K78" s="48"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="45"/>
-      <c r="D79" s="45"/>
-      <c r="E79" s="45"/>
-      <c r="F79" s="45"/>
-      <c r="G79" s="45"/>
-      <c r="H79" s="45"/>
-      <c r="I79" s="45"/>
-      <c r="J79" s="45"/>
-      <c r="K79" s="45"/>
+      <c r="C79" s="48"/>
+      <c r="D79" s="48"/>
+      <c r="E79" s="48"/>
+      <c r="F79" s="48"/>
+      <c r="G79" s="48"/>
+      <c r="H79" s="48"/>
+      <c r="I79" s="48"/>
+      <c r="J79" s="48"/>
+      <c r="K79" s="48"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="45"/>
-      <c r="D80" s="45"/>
-      <c r="E80" s="45"/>
-      <c r="F80" s="45"/>
-      <c r="G80" s="45"/>
-      <c r="H80" s="45"/>
-      <c r="I80" s="45"/>
-      <c r="J80" s="45"/>
-      <c r="K80" s="45"/>
+      <c r="C80" s="48"/>
+      <c r="D80" s="48"/>
+      <c r="E80" s="48"/>
+      <c r="F80" s="48"/>
+      <c r="G80" s="48"/>
+      <c r="H80" s="48"/>
+      <c r="I80" s="48"/>
+      <c r="J80" s="48"/>
+      <c r="K80" s="48"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="45"/>
-      <c r="D81" s="45"/>
-      <c r="E81" s="45"/>
-      <c r="F81" s="45"/>
-      <c r="G81" s="45"/>
-      <c r="H81" s="45"/>
-      <c r="I81" s="45"/>
-      <c r="J81" s="45"/>
-      <c r="K81" s="45"/>
+      <c r="C81" s="48"/>
+      <c r="D81" s="48"/>
+      <c r="E81" s="48"/>
+      <c r="F81" s="48"/>
+      <c r="G81" s="48"/>
+      <c r="H81" s="48"/>
+      <c r="I81" s="48"/>
+      <c r="J81" s="48"/>
+      <c r="K81" s="48"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="45"/>
-      <c r="D82" s="45"/>
-      <c r="E82" s="45"/>
-      <c r="F82" s="45"/>
-      <c r="G82" s="45"/>
-      <c r="H82" s="45"/>
-      <c r="I82" s="45"/>
-      <c r="J82" s="45"/>
-      <c r="K82" s="45"/>
+      <c r="C82" s="48"/>
+      <c r="D82" s="48"/>
+      <c r="E82" s="48"/>
+      <c r="F82" s="48"/>
+      <c r="G82" s="48"/>
+      <c r="H82" s="48"/>
+      <c r="I82" s="48"/>
+      <c r="J82" s="48"/>
+      <c r="K82" s="48"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="45"/>
-      <c r="D83" s="45"/>
-      <c r="E83" s="45"/>
-      <c r="F83" s="45"/>
-      <c r="G83" s="45"/>
-      <c r="H83" s="45"/>
-      <c r="I83" s="45"/>
-      <c r="J83" s="45"/>
-      <c r="K83" s="45"/>
+      <c r="C83" s="48"/>
+      <c r="D83" s="48"/>
+      <c r="E83" s="48"/>
+      <c r="F83" s="48"/>
+      <c r="G83" s="48"/>
+      <c r="H83" s="48"/>
+      <c r="I83" s="48"/>
+      <c r="J83" s="48"/>
+      <c r="K83" s="48"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="45" t="s">
+      <c r="C84" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="D84" s="45">
-        <v>1</v>
-      </c>
-      <c r="E84" s="45"/>
-      <c r="F84" s="45"/>
-      <c r="G84" s="45"/>
-      <c r="H84" s="45"/>
-      <c r="I84" s="45"/>
-      <c r="J84" s="45"/>
-      <c r="K84" s="45"/>
+      <c r="D84" s="48">
+        <v>1</v>
+      </c>
+      <c r="E84" s="48"/>
+      <c r="F84" s="48"/>
+      <c r="G84" s="48"/>
+      <c r="H84" s="48"/>
+      <c r="I84" s="48"/>
+      <c r="J84" s="48"/>
+      <c r="K84" s="48"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="45"/>
-      <c r="D85" s="45"/>
-      <c r="E85" s="45"/>
-      <c r="F85" s="45"/>
-      <c r="G85" s="45"/>
-      <c r="H85" s="45"/>
-      <c r="I85" s="45"/>
-      <c r="J85" s="45"/>
-      <c r="K85" s="45"/>
+      <c r="C85" s="48"/>
+      <c r="D85" s="48"/>
+      <c r="E85" s="48"/>
+      <c r="F85" s="48"/>
+      <c r="G85" s="48"/>
+      <c r="H85" s="48"/>
+      <c r="I85" s="48"/>
+      <c r="J85" s="48"/>
+      <c r="K85" s="48"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2995,568 +3052,568 @@
   </cols>
   <sheetData>
     <row r="13" spans="5:21">
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
     </row>
     <row r="14" spans="5:21">
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
     </row>
     <row r="15" spans="5:21">
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
     </row>
     <row r="16" spans="5:21">
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
     </row>
     <row r="17" spans="5:23">
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1"/>
-      <c r="W17" s="1"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+      <c r="W17" s="5"/>
     </row>
     <row r="18" spans="5:23">
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="1"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
     </row>
     <row r="19" spans="5:23">
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
-      <c r="W19" s="1"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
     </row>
     <row r="20" spans="5:23">
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
     </row>
     <row r="21" spans="5:23">
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="1"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
     </row>
     <row r="22" spans="5:23">
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
-      <c r="W22" s="1"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
     </row>
     <row r="23" spans="5:23">
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
-      <c r="W23" s="1"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
+      <c r="V23" s="5"/>
+      <c r="W23" s="5"/>
     </row>
     <row r="24" spans="5:23">
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-      <c r="W24" s="1"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="5"/>
+      <c r="T24" s="5"/>
+      <c r="U24" s="5"/>
+      <c r="V24" s="5"/>
+      <c r="W24" s="5"/>
     </row>
     <row r="25" spans="5:23">
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="1"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="5"/>
+      <c r="U25" s="5"/>
+      <c r="V25" s="5"/>
+      <c r="W25" s="5"/>
     </row>
     <row r="26" spans="5:23">
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="1"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5"/>
+      <c r="S26" s="5"/>
+      <c r="T26" s="5"/>
+      <c r="U26" s="5"/>
+      <c r="V26" s="5"/>
+      <c r="W26" s="5"/>
     </row>
     <row r="27" spans="5:23">
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="1"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="5"/>
+      <c r="U27" s="5"/>
+      <c r="V27" s="5"/>
+      <c r="W27" s="5"/>
     </row>
     <row r="28" spans="5:23">
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="5"/>
+      <c r="T28" s="5"/>
+      <c r="U28" s="5"/>
+      <c r="V28" s="5"/>
+      <c r="W28" s="5"/>
     </row>
     <row r="29" spans="5:23">
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1" t="s">
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
+      <c r="T29" s="5"/>
+      <c r="U29" s="5"/>
+      <c r="V29" s="5"/>
+      <c r="W29" s="5"/>
     </row>
     <row r="30" ht="15.25" spans="5:23">
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="I30" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="J30" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="K30" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="L30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="M30" s="1" t="s">
+      <c r="L30" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M30" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="N30" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="O30" s="1" t="s">
+      <c r="O30" s="5" t="s">
         <v>64</v>
       </c>
       <c r="P30" t="s">
         <v>65</v>
       </c>
-      <c r="Q30" s="1" t="s">
+      <c r="Q30" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="5"/>
+      <c r="U30" s="5"/>
+      <c r="V30" s="5"/>
     </row>
     <row r="31" ht="16" spans="5:23">
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="H31" s="12" t="s">
+      <c r="H31" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="I31" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1">
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5">
         <v>-0.25</v>
       </c>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1">
+      <c r="N31" s="5"/>
+      <c r="O31" s="5">
         <v>0</v>
       </c>
-      <c r="P31" s="1">
+      <c r="P31" s="5">
         <v>3</v>
       </c>
-      <c r="Q31" s="1" t="s">
+      <c r="Q31" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="5"/>
+      <c r="U31" s="5"/>
+      <c r="V31" s="5"/>
     </row>
     <row r="32" ht="15.25" spans="5:23">
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1" t="s">
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1">
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5">
         <v>-0.1</v>
       </c>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+      <c r="T32" s="5"/>
+      <c r="U32" s="5"/>
+      <c r="V32" s="5"/>
     </row>
     <row r="33" spans="6:22">
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1" t="s">
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1" t="s">
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1">
-        <v>1</v>
-      </c>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-      <c r="R33" s="1"/>
-      <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
-      <c r="U33" s="1"/>
-      <c r="V33" s="1"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5">
+        <v>1</v>
+      </c>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5"/>
+      <c r="U33" s="5"/>
+      <c r="V33" s="5"/>
     </row>
     <row r="34" spans="6:22">
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
-      <c r="R34" s="1"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
+      <c r="R34" s="5"/>
+      <c r="S34" s="5"/>
+      <c r="T34" s="5"/>
+      <c r="U34" s="5"/>
+      <c r="V34" s="5"/>
     </row>
     <row r="35" spans="6:22">
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+      <c r="U35" s="5"/>
+      <c r="V35" s="5"/>
     </row>
     <row r="36" spans="6:22">
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
-      <c r="R36" s="1"/>
-      <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
-      <c r="U36" s="1"/>
-      <c r="V36" s="1"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+      <c r="U36" s="5"/>
+      <c r="V36" s="5"/>
     </row>
     <row r="37" spans="6:22">
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
-      <c r="R37" s="1"/>
-      <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5"/>
+      <c r="S37" s="5"/>
+      <c r="T37" s="5"/>
+      <c r="U37" s="5"/>
+      <c r="V37" s="5"/>
     </row>
     <row r="38" spans="6:22">
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-      <c r="R38" s="1"/>
-      <c r="S38" s="1"/>
-      <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
+      <c r="T38" s="5"/>
+      <c r="U38" s="5"/>
+      <c r="V38" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3592,755 +3649,755 @@
       </c>
     </row>
     <row r="4" spans="2:14">
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20" t="s">
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
     </row>
     <row r="5" spans="2:14">
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="20"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="K8" s="21" t="s">
+      <c r="K8" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="L8" s="22" t="s">
+      <c r="L8" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="M8" s="22" t="s">
+      <c r="M8" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="N8" s="21" t="s">
+      <c r="N8" s="24" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="9" spans="2:14">
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="23" t="s">
+      <c r="E9" s="23"/>
+      <c r="F9" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="G9" s="23" t="s">
+      <c r="G9" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="I9" s="23" t="s">
+      <c r="I9" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="J9" s="20">
-        <v>1</v>
-      </c>
-      <c r="K9" s="23">
+      <c r="J9" s="23">
+        <v>1</v>
+      </c>
+      <c r="K9" s="26">
         <v>1.25</v>
       </c>
-      <c r="L9" s="20">
+      <c r="L9" s="23">
         <v>0.05</v>
       </c>
-      <c r="M9" s="23">
-        <v>1</v>
-      </c>
-      <c r="N9" s="23"/>
+      <c r="M9" s="26">
+        <v>1</v>
+      </c>
+      <c r="N9" s="26"/>
     </row>
     <row r="10" spans="2:14">
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="23" t="s">
+      <c r="E10" s="23"/>
+      <c r="F10" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="G10" s="23" t="s">
+      <c r="G10" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="I10" s="23" t="s">
+      <c r="I10" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="J10" s="20">
-        <v>1</v>
-      </c>
-      <c r="K10" s="23">
+      <c r="J10" s="23">
+        <v>1</v>
+      </c>
+      <c r="K10" s="26">
         <v>1.11</v>
       </c>
-      <c r="L10" s="20">
+      <c r="L10" s="23">
         <v>0.05</v>
       </c>
-      <c r="M10" s="23">
-        <v>1</v>
-      </c>
-      <c r="N10" s="23"/>
+      <c r="M10" s="26">
+        <v>1</v>
+      </c>
+      <c r="N10" s="26"/>
     </row>
     <row r="11" spans="2:14">
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="23" t="s">
+      <c r="E11" s="23"/>
+      <c r="F11" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="G11" s="23" t="s">
+      <c r="G11" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="H11" s="23" t="s">
+      <c r="H11" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="I11" s="23" t="s">
+      <c r="I11" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="J11" s="20">
-        <v>1</v>
-      </c>
-      <c r="K11" s="23">
+      <c r="J11" s="23">
+        <v>1</v>
+      </c>
+      <c r="K11" s="26">
         <v>1.15</v>
       </c>
-      <c r="L11" s="20">
+      <c r="L11" s="23">
         <v>0.08</v>
       </c>
-      <c r="M11" s="23">
-        <v>1</v>
-      </c>
-      <c r="N11" s="23"/>
+      <c r="M11" s="26">
+        <v>1</v>
+      </c>
+      <c r="N11" s="26"/>
     </row>
     <row r="12" ht="16" spans="2:14">
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="24" t="s">
+      <c r="E12" s="23"/>
+      <c r="F12" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="23" t="s">
+      <c r="G12" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="H12" s="23" t="s">
+      <c r="H12" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="I12" s="23" t="s">
+      <c r="I12" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="J12" s="20">
-        <v>1</v>
-      </c>
-      <c r="K12" s="23">
+      <c r="J12" s="23">
+        <v>1</v>
+      </c>
+      <c r="K12" s="26">
         <v>1.12</v>
       </c>
-      <c r="L12" s="20">
+      <c r="L12" s="23">
         <v>0.03</v>
       </c>
-      <c r="M12" s="23">
-        <v>1</v>
-      </c>
-      <c r="N12" s="23"/>
+      <c r="M12" s="26">
+        <v>1</v>
+      </c>
+      <c r="N12" s="26"/>
     </row>
     <row r="13" spans="2:14">
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E13" s="20"/>
-      <c r="F13" s="23" t="s">
+      <c r="E13" s="23"/>
+      <c r="F13" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="G13" s="23" t="s">
+      <c r="G13" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="H13" s="23" t="s">
+      <c r="H13" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="I13" s="23" t="s">
+      <c r="I13" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="J13" s="20">
-        <v>1</v>
-      </c>
-      <c r="K13" s="23">
+      <c r="J13" s="23">
+        <v>1</v>
+      </c>
+      <c r="K13" s="26">
         <v>1.2</v>
       </c>
-      <c r="L13" s="20">
+      <c r="L13" s="23">
         <v>0.1</v>
       </c>
-      <c r="M13" s="23">
-        <v>1</v>
-      </c>
-      <c r="N13" s="23"/>
+      <c r="M13" s="26">
+        <v>1</v>
+      </c>
+      <c r="N13" s="26"/>
     </row>
     <row r="14" spans="2:14">
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="E14" s="20"/>
-      <c r="F14" s="23" t="s">
+      <c r="E14" s="23"/>
+      <c r="F14" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="G14" s="23" t="s">
+      <c r="G14" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="H14" s="23" t="s">
+      <c r="H14" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="I14" s="23" t="s">
+      <c r="I14" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="J14" s="20">
-        <v>1</v>
-      </c>
-      <c r="K14" s="23">
+      <c r="J14" s="23">
+        <v>1</v>
+      </c>
+      <c r="K14" s="26">
         <v>1.06</v>
       </c>
-      <c r="L14" s="20">
+      <c r="L14" s="23">
         <v>0.15</v>
       </c>
-      <c r="M14" s="23">
-        <v>1</v>
-      </c>
-      <c r="N14" s="23"/>
+      <c r="M14" s="26">
+        <v>1</v>
+      </c>
+      <c r="N14" s="26"/>
     </row>
     <row r="15" spans="2:14">
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="23" t="s">
+      <c r="E15" s="23"/>
+      <c r="F15" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="G15" s="23" t="s">
+      <c r="G15" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="H15" s="23" t="s">
+      <c r="H15" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="I15" s="23" t="s">
+      <c r="I15" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="J15" s="20">
-        <v>1</v>
-      </c>
-      <c r="K15" s="23">
+      <c r="J15" s="23">
+        <v>1</v>
+      </c>
+      <c r="K15" s="26">
         <v>1.06</v>
       </c>
-      <c r="L15" s="20">
+      <c r="L15" s="23">
         <v>0.3</v>
       </c>
-      <c r="M15" s="23">
-        <v>1</v>
-      </c>
-      <c r="N15" s="23"/>
+      <c r="M15" s="26">
+        <v>1</v>
+      </c>
+      <c r="N15" s="26"/>
     </row>
     <row r="16" ht="16" spans="2:14">
-      <c r="D16" s="23" t="s">
+      <c r="D16" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="24" t="s">
+      <c r="E16" s="23"/>
+      <c r="F16" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="20" t="str">
+      <c r="G16" s="23" t="str">
         <f xml:space="preserve">G15</f>
         <v>CAP,GROWTH</v>
       </c>
-      <c r="H16" s="20" t="str">
+      <c r="H16" s="23" t="str">
         <f xml:space="preserve">H15</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I16" s="23" t="s">
+      <c r="I16" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="J16" s="20">
+      <c r="J16" s="23">
         <f t="shared" ref="J16:L16" si="0" xml:space="preserve">J12</f>
         <v>1</v>
       </c>
-      <c r="K16" s="20">
+      <c r="K16" s="23">
         <f t="shared" si="0"/>
         <v>1.12</v>
       </c>
-      <c r="L16" s="20">
+      <c r="L16" s="23">
         <f t="shared" si="0"/>
         <v>0.03</v>
       </c>
-      <c r="M16" s="20">
+      <c r="M16" s="23">
         <f xml:space="preserve">M15</f>
         <v>1</v>
       </c>
-      <c r="N16" s="20"/>
+      <c r="N16" s="23"/>
     </row>
     <row r="17" ht="16" spans="4:14">
-      <c r="D17" s="23" t="s">
+      <c r="D17" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="E17" s="20"/>
-      <c r="F17" s="24" t="s">
+      <c r="E17" s="23"/>
+      <c r="F17" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="G17" s="20" t="str">
+      <c r="G17" s="23" t="str">
         <f t="shared" ref="G17:M17" si="1" xml:space="preserve">G16</f>
         <v>CAP,GROWTH</v>
       </c>
-      <c r="H17" s="20" t="str">
+      <c r="H17" s="23" t="str">
         <f t="shared" si="1"/>
         <v>2025, 2150</v>
       </c>
-      <c r="I17" s="23" t="s">
+      <c r="I17" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="J17" s="20">
+      <c r="J17" s="23">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K17" s="20">
+      <c r="K17" s="23">
         <f t="shared" si="1"/>
         <v>1.12</v>
       </c>
-      <c r="L17" s="20">
+      <c r="L17" s="23">
         <f t="shared" si="1"/>
         <v>0.03</v>
       </c>
-      <c r="M17" s="20">
+      <c r="M17" s="23">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N17" s="20"/>
+      <c r="N17" s="23"/>
     </row>
     <row r="18" ht="16" spans="4:14">
-      <c r="D18" s="23" t="s">
+      <c r="D18" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="E18" s="20"/>
-      <c r="F18" s="24" t="s">
+      <c r="E18" s="23"/>
+      <c r="F18" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="G18" s="20" t="str">
+      <c r="G18" s="23" t="str">
         <f xml:space="preserve">G17</f>
         <v>CAP,GROWTH</v>
       </c>
-      <c r="H18" s="20" t="str">
+      <c r="H18" s="23" t="str">
         <f xml:space="preserve">H17</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I18" s="23" t="s">
+      <c r="I18" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="J18" s="20">
-        <v>1</v>
-      </c>
-      <c r="K18" s="20">
-        <v>1</v>
-      </c>
-      <c r="L18" s="20">
+      <c r="J18" s="23">
+        <v>1</v>
+      </c>
+      <c r="K18" s="23">
+        <v>1</v>
+      </c>
+      <c r="L18" s="23">
         <v>0</v>
       </c>
-      <c r="M18" s="20">
-        <v>1</v>
-      </c>
-      <c r="N18" s="20"/>
+      <c r="M18" s="23">
+        <v>1</v>
+      </c>
+      <c r="N18" s="23"/>
     </row>
     <row r="25" spans="4:14">
       <c r="K25" t="s">
         <v>105</v>
       </c>
-      <c r="L25" s="13" t="s">
+      <c r="L25" s="16" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="27" spans="4:14">
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
-      <c r="J27" s="25"/>
-      <c r="K27" s="25"/>
-      <c r="L27" s="25"/>
-      <c r="M27" s="25"/>
-      <c r="N27" s="25"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="28"/>
+      <c r="N27" s="28"/>
     </row>
     <row r="28" spans="4:14">
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25" t="s">
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="25"/>
-      <c r="J28" s="25"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="25"/>
-      <c r="N28" s="25"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="28"/>
     </row>
     <row r="29" spans="4:14">
-      <c r="D29" s="25" t="s">
+      <c r="D29" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="E29" s="25" t="s">
+      <c r="E29" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="F29" s="25" t="s">
+      <c r="F29" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="25" t="s">
+      <c r="G29" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="H29" s="25" t="s">
+      <c r="H29" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="I29" s="25" t="s">
+      <c r="I29" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="J29" s="25" t="s">
+      <c r="J29" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="K29" s="25" t="s">
+      <c r="K29" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="L29" s="25" t="s">
+      <c r="L29" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="M29" s="25" t="s">
+      <c r="M29" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="N29" s="25" t="s">
+      <c r="N29" s="28" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="30" ht="16" spans="4:14">
-      <c r="D30" s="25" t="s">
+      <c r="D30" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="25"/>
-      <c r="F30" s="26" t="s">
+      <c r="E30" s="28"/>
+      <c r="F30" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="G30" s="25" t="s">
+      <c r="G30" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="H30" s="25" t="s">
+      <c r="H30" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I30" s="25" t="s">
+      <c r="I30" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="25">
-        <v>1</v>
-      </c>
-      <c r="K30" s="25">
-        <v>1</v>
-      </c>
-      <c r="L30" s="25">
+      <c r="J30" s="28">
+        <v>1</v>
+      </c>
+      <c r="K30" s="28">
+        <v>1</v>
+      </c>
+      <c r="L30" s="28">
         <v>0.01</v>
       </c>
-      <c r="M30" s="25">
-        <v>1</v>
-      </c>
-      <c r="N30" s="25"/>
+      <c r="M30" s="28">
+        <v>1</v>
+      </c>
+      <c r="N30" s="28"/>
     </row>
     <row r="31" ht="16" spans="4:14">
-      <c r="D31" s="25" t="s">
+      <c r="D31" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="25"/>
-      <c r="F31" s="27" t="s">
+      <c r="E31" s="28"/>
+      <c r="F31" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="G31" s="25" t="s">
+      <c r="G31" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="H31" s="25" t="s">
+      <c r="H31" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I31" s="25" t="s">
+      <c r="I31" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="J31" s="25">
-        <v>1</v>
-      </c>
-      <c r="K31" s="25">
-        <v>1</v>
-      </c>
-      <c r="L31" s="25">
+      <c r="J31" s="28">
+        <v>1</v>
+      </c>
+      <c r="K31" s="28">
+        <v>1</v>
+      </c>
+      <c r="L31" s="28">
         <f t="shared" ref="L31:L36" si="2" xml:space="preserve">L30</f>
         <v>0.01</v>
       </c>
-      <c r="M31" s="25">
-        <v>1</v>
-      </c>
-      <c r="N31" s="25"/>
+      <c r="M31" s="28">
+        <v>1</v>
+      </c>
+      <c r="N31" s="28"/>
     </row>
     <row r="32" ht="16" spans="4:14">
-      <c r="D32" s="25" t="s">
+      <c r="D32" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="E32" s="25"/>
-      <c r="F32" s="27" t="s">
+      <c r="E32" s="28"/>
+      <c r="F32" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="G32" s="25" t="s">
+      <c r="G32" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="H32" s="25" t="s">
+      <c r="H32" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I32" s="25" t="s">
+      <c r="I32" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="J32" s="25">
-        <v>1</v>
-      </c>
-      <c r="K32" s="25">
-        <v>1</v>
-      </c>
-      <c r="L32" s="25">
+      <c r="J32" s="28">
+        <v>1</v>
+      </c>
+      <c r="K32" s="28">
+        <v>1</v>
+      </c>
+      <c r="L32" s="28">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M32" s="25">
-        <v>1</v>
-      </c>
-      <c r="N32" s="25"/>
+      <c r="M32" s="28">
+        <v>1</v>
+      </c>
+      <c r="N32" s="28"/>
     </row>
     <row r="33" ht="16" spans="4:14">
-      <c r="D33" s="25" t="s">
+      <c r="D33" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="25"/>
-      <c r="F33" s="26" t="s">
+      <c r="E33" s="28"/>
+      <c r="F33" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="G33" s="25" t="s">
+      <c r="G33" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="H33" s="25" t="s">
+      <c r="H33" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I33" s="25" t="s">
+      <c r="I33" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="J33" s="25">
-        <v>1</v>
-      </c>
-      <c r="K33" s="25">
+      <c r="J33" s="28">
+        <v>1</v>
+      </c>
+      <c r="K33" s="28">
         <f xml:space="preserve">K32</f>
         <v>1</v>
       </c>
-      <c r="L33" s="25">
+      <c r="L33" s="28">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M33" s="25">
-        <v>1</v>
-      </c>
-      <c r="N33" s="25"/>
+      <c r="M33" s="28">
+        <v>1</v>
+      </c>
+      <c r="N33" s="28"/>
     </row>
     <row r="34" ht="16" spans="4:14">
-      <c r="D34" s="25" t="s">
+      <c r="D34" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="E34" s="25"/>
-      <c r="F34" s="26" t="s">
+      <c r="E34" s="28"/>
+      <c r="F34" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="G34" s="25" t="s">
+      <c r="G34" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="H34" s="25" t="s">
+      <c r="H34" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I34" s="25" t="s">
+      <c r="I34" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="J34" s="25">
-        <v>1</v>
-      </c>
-      <c r="K34" s="25">
+      <c r="J34" s="28">
+        <v>1</v>
+      </c>
+      <c r="K34" s="28">
         <f xml:space="preserve">K33</f>
         <v>1</v>
       </c>
-      <c r="L34" s="25">
+      <c r="L34" s="28">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M34" s="25">
-        <v>1</v>
-      </c>
-      <c r="N34" s="25"/>
+      <c r="M34" s="28">
+        <v>1</v>
+      </c>
+      <c r="N34" s="28"/>
     </row>
     <row r="35" ht="16" spans="4:14">
-      <c r="D35" s="25" t="s">
+      <c r="D35" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="E35" s="25"/>
-      <c r="F35" s="26" t="s">
+      <c r="E35" s="28"/>
+      <c r="F35" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="25" t="s">
+      <c r="G35" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="H35" s="25" t="s">
+      <c r="H35" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I35" s="25" t="s">
+      <c r="I35" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="J35" s="25">
-        <v>1</v>
-      </c>
-      <c r="K35" s="25">
+      <c r="J35" s="28">
+        <v>1</v>
+      </c>
+      <c r="K35" s="28">
         <f xml:space="preserve">K34</f>
         <v>1</v>
       </c>
-      <c r="L35" s="25">
+      <c r="L35" s="28">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M35" s="25">
-        <v>1</v>
-      </c>
-      <c r="N35" s="25"/>
+      <c r="M35" s="28">
+        <v>1</v>
+      </c>
+      <c r="N35" s="28"/>
     </row>
     <row r="36" ht="16" spans="4:14">
-      <c r="D36" s="25" t="s">
+      <c r="D36" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="E36" s="25"/>
-      <c r="F36" s="26" t="s">
+      <c r="E36" s="28"/>
+      <c r="F36" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="G36" s="25" t="s">
+      <c r="G36" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="H36" s="25" t="s">
+      <c r="H36" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I36" s="25" t="s">
+      <c r="I36" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="J36" s="25">
-        <v>1</v>
-      </c>
-      <c r="K36" s="25">
+      <c r="J36" s="28">
+        <v>1</v>
+      </c>
+      <c r="K36" s="28">
         <f xml:space="preserve">K35</f>
         <v>1</v>
       </c>
-      <c r="L36" s="25">
+      <c r="L36" s="28">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M36" s="25">
-        <v>1</v>
-      </c>
-      <c r="N36" s="25"/>
+      <c r="M36" s="28">
+        <v>1</v>
+      </c>
+      <c r="N36" s="28"/>
     </row>
     <row r="37" ht="16" spans="4:14">
-      <c r="D37" s="28" t="s">
+      <c r="D37" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="E37" s="28"/>
-      <c r="F37" s="29" t="s">
+      <c r="E37" s="31"/>
+      <c r="F37" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="G37" s="28" t="s">
+      <c r="G37" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="H37" s="28" t="s">
+      <c r="H37" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="I37" s="28" t="s">
+      <c r="I37" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="J37" s="28">
-        <v>1</v>
-      </c>
-      <c r="K37" s="28">
-        <v>1</v>
-      </c>
-      <c r="L37" s="28">
+      <c r="J37" s="31">
+        <v>1</v>
+      </c>
+      <c r="K37" s="31">
+        <v>1</v>
+      </c>
+      <c r="L37" s="31">
         <v>0</v>
       </c>
-      <c r="M37" s="28">
+      <c r="M37" s="31">
         <v>3</v>
       </c>
-      <c r="N37" s="25"/>
+      <c r="N37" s="28"/>
     </row>
     <row r="38" ht="16" spans="4:14">
-      <c r="D38" s="30" t="s">
+      <c r="D38" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="F38" s="29" t="s">
+      <c r="F38" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="G38" s="28" t="s">
+      <c r="G38" s="31" t="s">
         <v>84</v>
       </c>
       <c r="H38" t="str">
@@ -4362,469 +4419,469 @@
       <c r="M38">
         <v>3</v>
       </c>
-      <c r="N38" s="25"/>
+      <c r="N38" s="28"/>
     </row>
     <row r="39" ht="16" spans="4:14">
-      <c r="D39" s="30" t="s">
+      <c r="D39" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="E39" s="31"/>
-      <c r="F39" s="29" t="s">
+      <c r="E39" s="34"/>
+      <c r="F39" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="G39" s="28" t="s">
+      <c r="G39" s="31" t="s">
         <v>84</v>
       </c>
       <c r="H39" t="str">
         <f t="shared" ref="H39:M39" si="3" xml:space="preserve">H38</f>
         <v>2019, 2150</v>
       </c>
-      <c r="I39" s="31" t="str">
+      <c r="I39" s="34" t="str">
         <f t="shared" si="3"/>
         <v>UP</v>
       </c>
-      <c r="J39" s="31">
+      <c r="J39" s="34">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K39" s="31">
+      <c r="K39" s="34">
         <f t="shared" si="3"/>
         <v>1.1</v>
       </c>
-      <c r="L39" s="31">
+      <c r="L39" s="34">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M39" s="31">
+      <c r="M39" s="34">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="N39" s="31"/>
+      <c r="N39" s="34"/>
     </row>
     <row r="40" ht="16" spans="4:14">
-      <c r="D40" s="30" t="s">
+      <c r="D40" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="E40" s="31"/>
-      <c r="F40" s="29" t="s">
+      <c r="E40" s="34"/>
+      <c r="F40" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="G40" s="28" t="s">
+      <c r="G40" s="31" t="s">
         <v>84</v>
       </c>
       <c r="H40" t="str">
         <f t="shared" ref="H40:M40" si="4" xml:space="preserve">H39</f>
         <v>2019, 2150</v>
       </c>
-      <c r="I40" s="31" t="str">
+      <c r="I40" s="34" t="str">
         <f t="shared" si="4"/>
         <v>UP</v>
       </c>
-      <c r="J40" s="31">
+      <c r="J40" s="34">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="K40" s="31">
+      <c r="K40" s="34">
         <f t="shared" si="4"/>
         <v>1.1</v>
       </c>
-      <c r="L40" s="31">
+      <c r="L40" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M40" s="31">
+      <c r="M40" s="34">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="N40" s="31"/>
+      <c r="N40" s="34"/>
     </row>
     <row r="41" ht="16" spans="4:14">
-      <c r="D41" s="30" t="s">
+      <c r="D41" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="E41" s="31"/>
-      <c r="F41" s="29" t="s">
+      <c r="E41" s="34"/>
+      <c r="F41" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="G41" s="28" t="s">
+      <c r="G41" s="31" t="s">
         <v>84</v>
       </c>
       <c r="H41" t="str">
         <f t="shared" ref="H41:M41" si="5" xml:space="preserve">H40</f>
         <v>2019, 2150</v>
       </c>
-      <c r="I41" s="31" t="str">
+      <c r="I41" s="34" t="str">
         <f t="shared" si="5"/>
         <v>UP</v>
       </c>
-      <c r="J41" s="31">
+      <c r="J41" s="34">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="K41" s="31">
+      <c r="K41" s="34">
         <f t="shared" si="5"/>
         <v>1.1</v>
       </c>
-      <c r="L41" s="31">
+      <c r="L41" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M41" s="31">
+      <c r="M41" s="34">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="N41" s="31"/>
+      <c r="N41" s="34"/>
     </row>
     <row r="42" ht="16" spans="4:14">
-      <c r="D42" s="30" t="s">
+      <c r="D42" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="F42" s="29" t="s">
+      <c r="F42" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="G42" s="28" t="s">
+      <c r="G42" s="31" t="s">
         <v>84</v>
       </c>
       <c r="H42" t="str">
         <f t="shared" ref="H42:M42" si="6" xml:space="preserve">H41</f>
         <v>2019, 2150</v>
       </c>
-      <c r="I42" s="31" t="str">
+      <c r="I42" s="34" t="str">
         <f t="shared" si="6"/>
         <v>UP</v>
       </c>
-      <c r="J42" s="31">
+      <c r="J42" s="34">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="K42" s="31">
+      <c r="K42" s="34">
         <f t="shared" si="6"/>
         <v>1.1</v>
       </c>
-      <c r="L42" s="31">
+      <c r="L42" s="34">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M42" s="31">
+      <c r="M42" s="34">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="N42" s="31"/>
+      <c r="N42" s="34"/>
     </row>
     <row r="43" spans="4:14">
-      <c r="D43" s="28" t="s">
+      <c r="D43" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="E43" s="28"/>
-      <c r="F43" s="32" t="s">
+      <c r="E43" s="31"/>
+      <c r="F43" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="G43" s="28" t="s">
+      <c r="G43" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="H43" s="28" t="s">
+      <c r="H43" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="I43" s="28" t="s">
+      <c r="I43" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="J43" s="28">
-        <v>1</v>
-      </c>
-      <c r="K43" s="28">
-        <v>1</v>
-      </c>
-      <c r="L43" s="28">
+      <c r="J43" s="31">
+        <v>1</v>
+      </c>
+      <c r="K43" s="31">
+        <v>1</v>
+      </c>
+      <c r="L43" s="31">
         <v>0</v>
       </c>
-      <c r="M43" s="28">
+      <c r="M43" s="31">
         <v>3</v>
       </c>
-      <c r="N43" s="31"/>
+      <c r="N43" s="34"/>
     </row>
     <row r="44" spans="4:14">
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="31"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="34"/>
     </row>
     <row r="45" spans="4:14">
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="33"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="31"/>
-      <c r="I45" s="31"/>
-      <c r="J45" s="31"/>
-      <c r="K45" s="31"/>
-      <c r="L45" s="31"/>
-      <c r="M45" s="31"/>
-      <c r="N45" s="31"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="36"/>
+      <c r="G45" s="34"/>
+      <c r="H45" s="34"/>
+      <c r="I45" s="34"/>
+      <c r="J45" s="34"/>
+      <c r="K45" s="34"/>
+      <c r="L45" s="34"/>
+      <c r="M45" s="34"/>
+      <c r="N45" s="34"/>
     </row>
     <row r="46" spans="4:14">
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="31"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="34"/>
     </row>
     <row r="47" spans="4:14">
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="31"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="34"/>
     </row>
     <row r="48" spans="4:14">
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="31"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="34"/>
     </row>
     <row r="49" spans="4:14">
-      <c r="N49" s="25"/>
+      <c r="N49" s="28"/>
     </row>
     <row r="50" spans="4:14">
-      <c r="D50" s="25"/>
-      <c r="E50" s="25"/>
-      <c r="F50" s="25"/>
-      <c r="G50" s="25"/>
-      <c r="H50" s="25" t="s">
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="I50" s="25"/>
-      <c r="J50" s="25"/>
-      <c r="K50" s="25"/>
-      <c r="L50" s="25"/>
-      <c r="M50" s="25"/>
-      <c r="N50" s="25"/>
+      <c r="I50" s="28"/>
+      <c r="J50" s="28"/>
+      <c r="K50" s="28"/>
+      <c r="L50" s="28"/>
+      <c r="M50" s="28"/>
+      <c r="N50" s="28"/>
     </row>
     <row r="51" ht="16" spans="4:14">
-      <c r="D51" s="25" t="s">
+      <c r="D51" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="E51" s="25" t="s">
+      <c r="E51" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="F51" s="25" t="s">
+      <c r="F51" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="G51" s="25" t="s">
+      <c r="G51" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="H51" s="31" t="s">
+      <c r="H51" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="I51" s="25" t="s">
+      <c r="I51" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="J51" s="2" t="s">
+      <c r="J51" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="K51" s="25" t="s">
+      <c r="K51" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="L51" s="25" t="s">
+      <c r="L51" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="M51" s="25" t="s">
+      <c r="M51" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="N51" s="25" t="s">
+      <c r="N51" s="28" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="52" spans="4:14">
-      <c r="D52" s="25" t="s">
+      <c r="D52" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="E52" s="25"/>
-      <c r="F52" s="34" t="s">
+      <c r="E52" s="28"/>
+      <c r="F52" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="G52" s="25" t="s">
+      <c r="G52" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="H52" s="31" t="s">
+      <c r="H52" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="I52" s="25" t="s">
+      <c r="I52" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="J52" s="25">
-        <v>1</v>
-      </c>
-      <c r="K52" s="25">
-        <v>1</v>
-      </c>
-      <c r="L52" s="25">
+      <c r="J52" s="28">
+        <v>1</v>
+      </c>
+      <c r="K52" s="28">
+        <v>1</v>
+      </c>
+      <c r="L52" s="28">
         <v>0</v>
       </c>
-      <c r="M52" s="25">
+      <c r="M52" s="28">
         <v>5</v>
       </c>
-      <c r="N52" s="25"/>
+      <c r="N52" s="28"/>
     </row>
     <row r="53" spans="4:14">
-      <c r="D53" s="25" t="s">
+      <c r="D53" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="E53" s="25"/>
-      <c r="F53" s="34" t="s">
+      <c r="E53" s="28"/>
+      <c r="F53" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="G53" s="25" t="s">
+      <c r="G53" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="H53" s="35" t="s">
+      <c r="H53" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="I53" s="25" t="s">
+      <c r="I53" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="J53" s="25">
-        <v>1</v>
-      </c>
-      <c r="K53" s="25">
-        <v>1</v>
-      </c>
-      <c r="L53" s="25">
+      <c r="J53" s="28">
+        <v>1</v>
+      </c>
+      <c r="K53" s="28">
+        <v>1</v>
+      </c>
+      <c r="L53" s="28">
         <f t="shared" ref="L53:L55" si="7" xml:space="preserve">L52</f>
         <v>0</v>
       </c>
-      <c r="M53" s="25">
+      <c r="M53" s="28">
         <v>5</v>
       </c>
-      <c r="N53" s="25"/>
+      <c r="N53" s="28"/>
     </row>
     <row r="54" spans="4:14">
-      <c r="D54" s="25" t="s">
+      <c r="D54" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="E54" s="25"/>
-      <c r="F54" s="34" t="s">
+      <c r="E54" s="28"/>
+      <c r="F54" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="G54" s="25" t="s">
+      <c r="G54" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="H54" s="31" t="s">
+      <c r="H54" s="34" t="s">
         <v>149</v>
       </c>
-      <c r="I54" s="25" t="s">
+      <c r="I54" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="J54" s="25">
-        <v>1</v>
-      </c>
-      <c r="K54" s="25">
-        <v>1</v>
-      </c>
-      <c r="L54" s="25">
+      <c r="J54" s="28">
+        <v>1</v>
+      </c>
+      <c r="K54" s="28">
+        <v>1</v>
+      </c>
+      <c r="L54" s="28">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M54" s="25">
+      <c r="M54" s="28">
         <v>5</v>
       </c>
-      <c r="N54" s="25"/>
+      <c r="N54" s="28"/>
     </row>
     <row r="55" ht="16" spans="4:14">
-      <c r="D55" s="25" t="s">
+      <c r="D55" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="E55" s="25"/>
-      <c r="F55" s="26" t="s">
+      <c r="E55" s="28"/>
+      <c r="F55" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="G55" s="25" t="s">
+      <c r="G55" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="H55" s="31" t="s">
+      <c r="H55" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="I55" s="25" t="s">
+      <c r="I55" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="J55" s="25">
-        <v>1</v>
-      </c>
-      <c r="K55" s="25">
-        <v>1</v>
-      </c>
-      <c r="L55" s="25">
+      <c r="J55" s="28">
+        <v>1</v>
+      </c>
+      <c r="K55" s="28">
+        <v>1</v>
+      </c>
+      <c r="L55" s="28">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M55" s="25">
+      <c r="M55" s="28">
         <v>5</v>
       </c>
-      <c r="N55" s="25"/>
+      <c r="N55" s="28"/>
     </row>
     <row r="56" ht="16" spans="4:14">
-      <c r="D56" s="25"/>
-      <c r="E56" s="25"/>
-      <c r="F56" s="26"/>
-      <c r="G56" s="25"/>
-      <c r="H56" s="31"/>
-      <c r="I56" s="25"/>
-      <c r="J56" s="25"/>
-      <c r="K56" s="25"/>
-      <c r="L56" s="25"/>
-      <c r="M56" s="25"/>
-      <c r="N56" s="25"/>
+      <c r="D56" s="28"/>
+      <c r="E56" s="28"/>
+      <c r="F56" s="29"/>
+      <c r="G56" s="28"/>
+      <c r="H56" s="34"/>
+      <c r="I56" s="28"/>
+      <c r="J56" s="28"/>
+      <c r="K56" s="28"/>
+      <c r="L56" s="28"/>
+      <c r="M56" s="28"/>
+      <c r="N56" s="28"/>
     </row>
     <row r="57" ht="16" spans="4:14">
-      <c r="D57" s="25"/>
-      <c r="E57" s="25"/>
-      <c r="F57" s="26"/>
-      <c r="G57" s="25"/>
-      <c r="H57" s="25"/>
-      <c r="I57" s="25"/>
-      <c r="J57" s="25"/>
-      <c r="K57" s="25"/>
-      <c r="L57" s="25"/>
-      <c r="M57" s="25"/>
-      <c r="N57" s="25"/>
+      <c r="D57" s="28"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="29"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="28"/>
+      <c r="I57" s="28"/>
+      <c r="J57" s="28"/>
+      <c r="K57" s="28"/>
+      <c r="L57" s="28"/>
+      <c r="M57" s="28"/>
+      <c r="N57" s="28"/>
     </row>
     <row r="58" ht="16" spans="4:14">
-      <c r="D58" s="25"/>
-      <c r="E58" s="25"/>
-      <c r="F58" s="26"/>
-      <c r="G58" s="25"/>
-      <c r="H58" s="25"/>
-      <c r="I58" s="25"/>
-      <c r="J58" s="25"/>
-      <c r="K58" s="25"/>
-      <c r="L58" s="25"/>
-      <c r="M58" s="25"/>
-      <c r="N58" s="25"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="28"/>
+      <c r="I58" s="28"/>
+      <c r="J58" s="28"/>
+      <c r="K58" s="28"/>
+      <c r="L58" s="28"/>
+      <c r="M58" s="28"/>
+      <c r="N58" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4858,26 +4915,26 @@
       </c>
     </row>
     <row r="11" spans="6:18">
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
     </row>
     <row r="12" spans="6:18">
-      <c r="K12" s="1"/>
-      <c r="L12" s="1" t="s">
+      <c r="K12" s="5"/>
+      <c r="L12" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
     </row>
     <row r="13" spans="6:18">
       <c r="F13" t="s">
@@ -4895,28 +4952,28 @@
       <c r="J13" t="s">
         <v>33</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="L13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="M13" s="1" t="s">
+      <c r="L13" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="N13" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="O13" s="1" t="s">
+      <c r="O13" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="P13" s="1" t="s">
+      <c r="P13" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="Q13" s="1" t="s">
+      <c r="Q13" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="R13" s="1"/>
+      <c r="R13" s="5"/>
     </row>
     <row r="14" spans="6:18">
       <c r="F14" t="s">
@@ -4925,147 +4982,147 @@
       <c r="H14" t="s">
         <v>154</v>
       </c>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1">
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5">
         <v>0.25</v>
       </c>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1">
+      <c r="N14" s="5"/>
+      <c r="O14" s="5">
         <v>0</v>
       </c>
-      <c r="P14" s="1">
+      <c r="P14" s="5">
         <v>5</v>
       </c>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
     </row>
     <row r="15" spans="6:18">
       <c r="H15" t="s">
         <v>155</v>
       </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1">
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5">
         <v>-1</v>
       </c>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
     </row>
     <row r="16" spans="6:18">
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
     </row>
     <row r="17" spans="6:18">
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
     </row>
     <row r="18" spans="6:18">
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
     </row>
     <row r="19" spans="6:18">
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
     </row>
     <row r="20" spans="6:18">
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
     </row>
     <row r="21" spans="6:18">
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
     </row>
     <row r="22" spans="6:18">
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
     </row>
     <row r="23" spans="6:18">
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
     </row>
     <row r="24" spans="6:18">
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
     </row>
     <row r="25" spans="6:18">
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
     </row>
     <row r="26" spans="6:18">
-      <c r="K26" s="1"/>
-      <c r="L26" s="1" t="s">
+      <c r="K26" s="5"/>
+      <c r="L26" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5"/>
     </row>
     <row r="27" spans="6:18">
       <c r="F27" t="s">
@@ -5083,126 +5140,126 @@
       <c r="J27" t="s">
         <v>33</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="K27" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="L27" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="M27" s="1" t="s">
+      <c r="L27" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M27" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="N27" s="1" t="s">
+      <c r="N27" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="O27" s="1" t="s">
+      <c r="O27" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="P27" s="1" t="s">
+      <c r="P27" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="Q27" s="1" t="s">
+      <c r="Q27" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="R27" s="1"/>
+      <c r="R27" s="5"/>
     </row>
     <row r="28" ht="16" spans="6:18">
       <c r="F28" t="s">
         <v>156</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1">
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5">
         <v>-0.1</v>
       </c>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1">
+      <c r="N28" s="5"/>
+      <c r="O28" s="5">
         <v>0</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P28" s="5">
         <v>5</v>
       </c>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
     </row>
     <row r="29" spans="6:18">
       <c r="H29" t="s">
         <v>158</v>
       </c>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1">
-        <v>1</v>
-      </c>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5">
+        <v>1</v>
+      </c>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="5"/>
     </row>
     <row r="30" spans="6:18">
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
     </row>
     <row r="31" spans="6:18">
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
     </row>
     <row r="32" spans="6:18">
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
     </row>
     <row r="33" spans="6:18">
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-      <c r="R33" s="1"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5"/>
     </row>
     <row r="34" spans="6:18">
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
-      <c r="R34" s="1"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
+      <c r="R34" s="5"/>
     </row>
     <row r="35" spans="6:18">
-      <c r="K35" s="1"/>
-      <c r="L35" s="1" t="s">
+      <c r="K35" s="5"/>
+      <c r="L35" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
     </row>
     <row r="36" spans="6:18">
       <c r="F36" t="s">
@@ -5220,25 +5277,25 @@
       <c r="J36" t="s">
         <v>33</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="K36" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="M36" s="1" t="s">
+      <c r="L36" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M36" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="N36" s="1" t="s">
+      <c r="N36" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="O36" s="1" t="s">
+      <c r="O36" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="P36" s="1" t="s">
+      <c r="P36" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="Q36" s="1" t="s">
+      <c r="Q36" s="5" t="s">
         <v>66</v>
       </c>
     </row>
@@ -5249,553 +5306,858 @@
       <c r="H37" t="s">
         <v>160</v>
       </c>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1">
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5">
         <v>-0.1</v>
       </c>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1">
+      <c r="N37" s="5"/>
+      <c r="O37" s="5">
         <v>0</v>
       </c>
-      <c r="P37" s="1">
+      <c r="P37" s="5">
         <v>5</v>
       </c>
-      <c r="Q37" s="1"/>
+      <c r="Q37" s="5"/>
     </row>
     <row r="38" spans="6:18">
       <c r="H38" t="s">
         <v>161</v>
       </c>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1">
-        <v>1</v>
-      </c>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5">
+        <v>1</v>
+      </c>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
     </row>
     <row r="51" spans="6:44">
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="4" t="s">
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="J51" s="5"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="5"/>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="5"/>
-      <c r="R51" s="6"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="6"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="6"/>
-      <c r="AB51" s="6"/>
-      <c r="AC51" s="6"/>
-      <c r="AD51" s="6"/>
-      <c r="AE51" s="6"/>
-      <c r="AF51" s="6"/>
-      <c r="AG51" s="6"/>
-      <c r="AH51" s="6"/>
-      <c r="AI51" s="6"/>
-      <c r="AJ51" s="6"/>
-      <c r="AK51" s="6"/>
-      <c r="AL51" s="6"/>
-      <c r="AM51" s="6"/>
+      <c r="J51" s="9"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="9"/>
+      <c r="O51" s="9"/>
+      <c r="P51" s="9"/>
+      <c r="Q51" s="9"/>
+      <c r="R51" s="10"/>
+      <c r="S51" s="10"/>
+      <c r="T51" s="10"/>
+      <c r="U51" s="10"/>
+      <c r="V51" s="10"/>
+      <c r="W51" s="10"/>
+      <c r="X51" s="10"/>
+      <c r="Y51" s="10"/>
+      <c r="Z51" s="10"/>
+      <c r="AA51" s="10"/>
+      <c r="AB51" s="10"/>
+      <c r="AC51" s="10"/>
+      <c r="AD51" s="10"/>
+      <c r="AE51" s="10"/>
+      <c r="AF51" s="10"/>
+      <c r="AG51" s="10"/>
+      <c r="AH51" s="10"/>
+      <c r="AI51" s="10"/>
+      <c r="AJ51" s="10"/>
+      <c r="AK51" s="10"/>
+      <c r="AL51" s="10"/>
+      <c r="AM51" s="10"/>
     </row>
     <row r="52" spans="6:44">
-      <c r="G52" s="3" t="s">
+      <c r="G52" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="H52" s="3" t="s">
+      <c r="H52" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="I52" s="7" t="s">
+      <c r="I52" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="J52" s="5" t="s">
+      <c r="J52" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="K52" s="3" t="s">
+      <c r="K52" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="L52" s="3" t="s">
+      <c r="L52" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="M52" s="5" t="s">
+      <c r="M52" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="N52" s="3" t="s">
+      <c r="N52" s="7" t="s">
         <v>61</v>
       </c>
       <c r="O52" t="s">
         <v>62</v>
       </c>
-      <c r="P52" s="1" t="s">
+      <c r="P52" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="Q52" s="1" t="s">
+      <c r="Q52" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="T52" s="6"/>
-      <c r="U52" s="6"/>
-      <c r="V52" s="6"/>
-      <c r="W52" s="6"/>
-      <c r="X52" s="6"/>
-      <c r="Y52" s="6"/>
-      <c r="Z52" s="6"/>
-      <c r="AA52" s="6"/>
-      <c r="AB52" s="6"/>
-      <c r="AC52" s="6"/>
-      <c r="AD52" s="6"/>
-      <c r="AE52" s="6"/>
-      <c r="AF52" s="6"/>
-      <c r="AG52" s="6"/>
-      <c r="AH52" s="6"/>
-      <c r="AI52" s="6"/>
-      <c r="AJ52" s="6"/>
-      <c r="AK52" s="6"/>
-      <c r="AL52" s="6"/>
-      <c r="AM52" s="6"/>
-      <c r="AN52" s="6"/>
-      <c r="AO52" s="6"/>
-      <c r="AP52" s="6"/>
-      <c r="AQ52" s="6"/>
-      <c r="AR52" s="6"/>
+      <c r="T52" s="10"/>
+      <c r="U52" s="10"/>
+      <c r="V52" s="10"/>
+      <c r="W52" s="10"/>
+      <c r="X52" s="10"/>
+      <c r="Y52" s="10"/>
+      <c r="Z52" s="10"/>
+      <c r="AA52" s="10"/>
+      <c r="AB52" s="10"/>
+      <c r="AC52" s="10"/>
+      <c r="AD52" s="10"/>
+      <c r="AE52" s="10"/>
+      <c r="AF52" s="10"/>
+      <c r="AG52" s="10"/>
+      <c r="AH52" s="10"/>
+      <c r="AI52" s="10"/>
+      <c r="AJ52" s="10"/>
+      <c r="AK52" s="10"/>
+      <c r="AL52" s="10"/>
+      <c r="AM52" s="10"/>
+      <c r="AN52" s="10"/>
+      <c r="AO52" s="10"/>
+      <c r="AP52" s="10"/>
+      <c r="AQ52" s="10"/>
+      <c r="AR52" s="10"/>
     </row>
     <row r="53" ht="16" spans="6:44">
-      <c r="F53" s="8"/>
-      <c r="G53" s="3" t="s">
+      <c r="F53" s="12"/>
+      <c r="G53" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="H53" s="3" t="s">
+      <c r="H53" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="I53" s="9">
+      <c r="I53" s="13">
         <v>2019</v>
       </c>
-      <c r="J53" s="10">
+      <c r="J53" s="14">
         <v>-1</v>
       </c>
-      <c r="K53" s="3"/>
-      <c r="L53" s="2" t="s">
+      <c r="K53" s="7"/>
+      <c r="L53" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="M53" s="11" t="s">
+      <c r="M53" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="N53" s="2" t="s">
+      <c r="N53" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="O53" s="3">
+      <c r="O53" s="7">
         <v>10</v>
       </c>
-      <c r="P53" s="1">
+      <c r="P53" s="5">
         <v>0</v>
       </c>
-      <c r="Q53" s="1">
+      <c r="Q53" s="5">
         <v>3</v>
       </c>
-      <c r="T53" s="6"/>
-      <c r="U53" s="6"/>
-      <c r="V53" s="6"/>
-      <c r="W53" s="6"/>
-      <c r="X53" s="6"/>
-      <c r="Y53" s="6"/>
-      <c r="Z53" s="6"/>
-      <c r="AA53" s="6"/>
-      <c r="AB53" s="6"/>
-      <c r="AC53" s="6"/>
-      <c r="AD53" s="6"/>
-      <c r="AE53" s="6"/>
-      <c r="AF53" s="6"/>
-      <c r="AG53" s="6"/>
-      <c r="AH53" s="6"/>
-      <c r="AI53" s="6"/>
-      <c r="AJ53" s="6"/>
-      <c r="AK53" s="6"/>
-      <c r="AL53" s="6"/>
-      <c r="AM53" s="6"/>
-      <c r="AN53" s="6"/>
-      <c r="AO53" s="6"/>
-      <c r="AP53" s="6"/>
-      <c r="AQ53" s="6"/>
-      <c r="AR53" s="6"/>
+      <c r="T53" s="10"/>
+      <c r="U53" s="10"/>
+      <c r="V53" s="10"/>
+      <c r="W53" s="10"/>
+      <c r="X53" s="10"/>
+      <c r="Y53" s="10"/>
+      <c r="Z53" s="10"/>
+      <c r="AA53" s="10"/>
+      <c r="AB53" s="10"/>
+      <c r="AC53" s="10"/>
+      <c r="AD53" s="10"/>
+      <c r="AE53" s="10"/>
+      <c r="AF53" s="10"/>
+      <c r="AG53" s="10"/>
+      <c r="AH53" s="10"/>
+      <c r="AI53" s="10"/>
+      <c r="AJ53" s="10"/>
+      <c r="AK53" s="10"/>
+      <c r="AL53" s="10"/>
+      <c r="AM53" s="10"/>
+      <c r="AN53" s="10"/>
+      <c r="AO53" s="10"/>
+      <c r="AP53" s="10"/>
+      <c r="AQ53" s="10"/>
+      <c r="AR53" s="10"/>
     </row>
     <row r="54" spans="6:44">
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-      <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
+      <c r="K54" s="7"/>
     </row>
     <row r="55" spans="6:44">
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3"/>
-      <c r="O55" s="3"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+      <c r="K55" s="7"/>
+      <c r="L55" s="7"/>
+      <c r="M55" s="7"/>
+      <c r="N55" s="7"/>
+      <c r="O55" s="7"/>
     </row>
     <row r="56" spans="6:44">
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-      <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
-      <c r="L56" s="3"/>
-      <c r="M56" s="3"/>
-      <c r="N56" s="3"/>
-      <c r="O56" s="3"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+      <c r="K56" s="7"/>
+      <c r="L56" s="7"/>
+      <c r="M56" s="7"/>
+      <c r="N56" s="7"/>
+      <c r="O56" s="7"/>
     </row>
     <row r="61" spans="6:44">
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="4" t="s">
+      <c r="G61" s="7"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="J61" s="5"/>
-      <c r="K61" s="5"/>
-      <c r="L61" s="5"/>
-      <c r="M61" s="5"/>
-      <c r="N61" s="5"/>
-      <c r="O61" s="5"/>
-      <c r="P61" s="6"/>
-      <c r="Q61" s="6"/>
+      <c r="J61" s="9"/>
+      <c r="K61" s="9"/>
+      <c r="L61" s="9"/>
+      <c r="M61" s="9"/>
+      <c r="N61" s="9"/>
+      <c r="O61" s="9"/>
+      <c r="P61" s="10"/>
+      <c r="Q61" s="10"/>
     </row>
     <row r="62" spans="6:44">
-      <c r="G62" s="3" t="s">
+      <c r="G62" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="H62" s="3" t="s">
+      <c r="H62" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="I62" s="7" t="s">
+      <c r="I62" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="J62" s="5" t="s">
+      <c r="J62" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="K62" s="3" t="s">
+      <c r="K62" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="L62" s="3" t="s">
+      <c r="L62" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="M62" s="5" t="s">
+      <c r="M62" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="N62" s="3" t="s">
+      <c r="N62" s="7" t="s">
         <v>61</v>
       </c>
       <c r="O62" t="s">
         <v>62</v>
       </c>
-      <c r="P62" s="1" t="s">
+      <c r="P62" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="Q62" s="1" t="s">
+      <c r="Q62" s="5" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="63" ht="16" spans="6:44">
-      <c r="G63" s="3" t="s">
+      <c r="G63" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="H63" s="3" t="s">
+      <c r="H63" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="I63" s="9">
+      <c r="I63" s="13">
         <v>2019</v>
       </c>
-      <c r="J63" s="10">
+      <c r="J63" s="14">
         <v>-1</v>
       </c>
-      <c r="K63" s="3"/>
-      <c r="L63" s="2" t="s">
+      <c r="K63" s="7"/>
+      <c r="L63" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="M63" s="11" t="s">
+      <c r="M63" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="N63" s="2" t="s">
+      <c r="N63" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="O63" s="3">
+      <c r="O63" s="7">
         <v>10</v>
       </c>
-      <c r="P63" s="1">
+      <c r="P63" s="5">
         <v>0</v>
       </c>
-      <c r="Q63" s="1">
+      <c r="Q63" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="64" spans="6:44">
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="7"/>
+      <c r="K64" s="7"/>
     </row>
     <row r="66" ht="15.25" spans="7:20">
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
-      <c r="M66" s="1"/>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
-      <c r="P66" s="1"/>
-      <c r="Q66" s="1"/>
-      <c r="T66" s="1"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="5"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="5"/>
+      <c r="Q66" s="5"/>
+      <c r="T66" s="5"/>
     </row>
     <row r="67" ht="16" spans="7:20">
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="12"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
-      <c r="M67" s="1"/>
-      <c r="O67" s="1"/>
-      <c r="P67" s="1"/>
-      <c r="Q67" s="1"/>
-      <c r="T67" s="1"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="5"/>
+      <c r="K67" s="5"/>
+      <c r="L67" s="5"/>
+      <c r="M67" s="5"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="5"/>
+      <c r="Q67" s="5"/>
+      <c r="T67" s="5"/>
     </row>
     <row r="68" ht="15.25" spans="7:20">
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-      <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
-      <c r="P68" s="1"/>
-      <c r="Q68" s="1"/>
-      <c r="T68" s="1"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="5"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="5"/>
+      <c r="Q68" s="5"/>
+      <c r="T68" s="5"/>
     </row>
     <row r="69" spans="7:20">
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
-      <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
-      <c r="P69" s="1"/>
-      <c r="Q69" s="1"/>
-      <c r="T69" s="1"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="5"/>
+      <c r="L69" s="5"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="5"/>
+      <c r="Q69" s="5"/>
+      <c r="T69" s="5"/>
     </row>
     <row r="70" spans="7:20">
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="14" t="s">
+      <c r="G70" s="16"/>
+      <c r="H70" s="16"/>
+      <c r="I70" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="J70" s="15"/>
-      <c r="K70" s="15"/>
-      <c r="L70" s="15"/>
-      <c r="M70" s="15"/>
-      <c r="N70" s="15"/>
-      <c r="O70" s="15"/>
-      <c r="P70" s="15"/>
-      <c r="Q70" s="15"/>
-      <c r="T70" s="1"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="18"/>
+      <c r="L70" s="18"/>
+      <c r="M70" s="18"/>
+      <c r="N70" s="18"/>
+      <c r="O70" s="18"/>
+      <c r="P70" s="18"/>
+      <c r="Q70" s="18"/>
+      <c r="T70" s="5"/>
     </row>
     <row r="71" spans="7:20">
-      <c r="G71" s="13" t="s">
+      <c r="G71" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="H71" s="13" t="s">
+      <c r="H71" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="I71" s="16" t="s">
+      <c r="I71" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="J71" s="15" t="s">
+      <c r="J71" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="K71" s="13" t="s">
+      <c r="K71" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="L71" s="13" t="s">
+      <c r="L71" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="M71" s="15" t="s">
+      <c r="M71" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="N71" s="13" t="s">
+      <c r="N71" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="O71" s="13" t="s">
+      <c r="O71" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="P71" s="13" t="s">
+      <c r="P71" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="Q71" s="13" t="s">
+      <c r="Q71" s="16" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="72" ht="16" spans="7:20">
-      <c r="G72" s="13" t="s">
+      <c r="G72" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="H72" s="13" t="s">
+      <c r="H72" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="I72" s="17">
+      <c r="I72" s="20">
         <v>2019</v>
       </c>
-      <c r="J72" s="18">
+      <c r="J72" s="21">
         <v>-1</v>
       </c>
-      <c r="K72" s="13"/>
-      <c r="L72" s="19" t="s">
+      <c r="K72" s="16"/>
+      <c r="L72" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="M72" s="19" t="s">
+      <c r="M72" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="N72" s="19" t="s">
+      <c r="N72" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="O72" s="13">
+      <c r="O72" s="16">
         <v>10</v>
       </c>
-      <c r="P72" s="13">
+      <c r="P72" s="16">
         <v>0</v>
       </c>
-      <c r="Q72" s="13">
+      <c r="Q72" s="16">
         <v>3</v>
       </c>
     </row>
     <row r="73" spans="7:20">
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
-      <c r="J73" s="13"/>
-      <c r="K73" s="13"/>
-      <c r="L73" s="13"/>
-      <c r="M73" s="13"/>
-      <c r="N73" s="13"/>
-      <c r="O73" s="13"/>
-      <c r="P73" s="13"/>
-      <c r="Q73" s="13"/>
+      <c r="G73" s="16"/>
+      <c r="H73" s="16"/>
+      <c r="I73" s="16"/>
+      <c r="J73" s="16"/>
+      <c r="K73" s="16"/>
+      <c r="L73" s="16"/>
+      <c r="M73" s="16"/>
+      <c r="N73" s="16"/>
+      <c r="O73" s="16"/>
+      <c r="P73" s="16"/>
+      <c r="Q73" s="16"/>
     </row>
     <row r="80" spans="7:20">
-      <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
-      <c r="I80" s="4" t="s">
+      <c r="G80" s="7"/>
+      <c r="H80" s="7"/>
+      <c r="I80" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="J80" s="5"/>
-      <c r="K80" s="5"/>
-      <c r="L80" s="5"/>
-      <c r="M80" s="5"/>
-      <c r="N80" s="5"/>
-      <c r="O80" s="5"/>
-      <c r="P80" s="6"/>
-      <c r="Q80" s="6"/>
+      <c r="J80" s="9"/>
+      <c r="K80" s="9"/>
+      <c r="L80" s="9"/>
+      <c r="M80" s="9"/>
+      <c r="N80" s="9"/>
+      <c r="O80" s="9"/>
+      <c r="P80" s="10"/>
+      <c r="Q80" s="10"/>
     </row>
     <row r="81" spans="7:17">
-      <c r="G81" s="3" t="s">
+      <c r="G81" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="H81" s="3" t="s">
+      <c r="H81" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="I81" s="7" t="s">
+      <c r="I81" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="J81" s="5" t="s">
+      <c r="J81" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="K81" s="3" t="s">
+      <c r="K81" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="L81" s="3" t="s">
+      <c r="L81" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="M81" s="5" t="s">
+      <c r="M81" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="N81" s="3" t="s">
+      <c r="N81" s="7" t="s">
         <v>61</v>
       </c>
       <c r="O81" t="s">
         <v>62</v>
       </c>
-      <c r="P81" s="1" t="s">
+      <c r="P81" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="Q81" s="1" t="s">
+      <c r="Q81" s="5" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="82" ht="16" spans="7:17">
-      <c r="G82" s="3" t="s">
+      <c r="G82" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="H82" s="3" t="s">
+      <c r="H82" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="I82" s="9">
+      <c r="I82" s="13">
         <v>2019</v>
       </c>
-      <c r="J82" s="10">
+      <c r="J82" s="14">
         <v>-1</v>
       </c>
-      <c r="K82" s="3"/>
-      <c r="L82" s="2" t="s">
+      <c r="K82" s="7"/>
+      <c r="L82" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="M82" s="11" t="s">
+      <c r="M82" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="N82" s="2" t="s">
+      <c r="N82" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="O82" s="3">
+      <c r="O82" s="7">
         <v>10</v>
       </c>
-      <c r="P82" s="1">
+      <c r="P82" s="5">
         <v>0</v>
       </c>
-      <c r="Q82" s="1">
+      <c r="Q82" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="83" spans="7:17">
-      <c r="G83" s="3"/>
-      <c r="H83" s="3"/>
-      <c r="I83" s="3"/>
-      <c r="J83" s="3"/>
-      <c r="K83" s="3"/>
+      <c r="G83" s="7"/>
+      <c r="H83" s="7"/>
+      <c r="I83" s="7"/>
+      <c r="J83" s="7"/>
+      <c r="K83" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B2:M26"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="25.0909090909091" customWidth="1"/>
+    <col min="4" max="4" width="34.4545454545455" customWidth="1"/>
+    <col min="5" max="5" width="43.7272727272727" customWidth="1"/>
+    <col min="7" max="7" width="11.1818181818182" customWidth="1"/>
+    <col min="8" max="8" width="10.1818181818182" customWidth="1"/>
+    <col min="10" max="10" width="12.8181818181818" customWidth="1"/>
+    <col min="11" max="11" width="11.3636363636364" customWidth="1"/>
+    <col min="12" max="12" width="13.6363636363636" customWidth="1"/>
+    <col min="13" max="13" width="56.8181818181818" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:13">
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="2:13">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" ht="15.25" spans="2:13">
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" ht="16" spans="2:13">
+      <c r="B7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>3</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" ht="15.25" spans="2:13">
+      <c r="D8" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="1">
+        <v>-1.05</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+    </row>
+    <row r="9" spans="2:13">
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+    </row>
+    <row r="10" spans="2:13">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+    </row>
+    <row r="11" spans="2:13">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+    </row>
+    <row r="12" spans="2:13">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+    </row>
+    <row r="13" spans="2:13">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+    </row>
+    <row r="14" spans="2:13">
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+    </row>
+    <row r="15" spans="2:13">
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13">
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+    </row>
+    <row r="17" spans="5:13">
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+    </row>
+    <row r="18" spans="5:13">
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+    </row>
+    <row r="19" spans="5:13">
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+    </row>
+    <row r="23" spans="5:13">
+      <c r="G23" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" spans="5:13">
+      <c r="G24" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="1"/>
+      <c r="J24" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" spans="5:13">
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+    </row>
+    <row r="26" spans="5:13">
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -278,7 +278,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="186">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -811,13 +811,31 @@
     <t xml:space="preserve">ELc curtailment not beyond 5% of demand </t>
   </si>
   <si>
-    <t>FT_TRAELC, FT_INDELC, ElecDemand</t>
+    <t>FT_TRAELC, FT_INDELC, ElecDemand, H2prd*, H2Conv*</t>
+  </si>
+  <si>
+    <t>STG</t>
   </si>
   <si>
     <t>*Need to test if ElcDemand's UC_FLO can be captured or not</t>
   </si>
   <si>
     <t>DEF_E</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>VAR_FIn</t>
+  </si>
+  <si>
+    <t>VAR_FOut</t>
+  </si>
+  <si>
+    <t>NorthAm</t>
   </si>
 </sst>
 </file>
@@ -830,10 +848,43 @@
     <numFmt numFmtId="176" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF3974D2"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF3974D2"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -870,12 +921,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF3974D2"/>
-      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1040,19 +1085,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
       <charset val="0"/>
     </font>
     <font>
@@ -1061,8 +1101,13 @@
       <name val="Tahoma"/>
       <charset val="0"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+    </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1072,6 +1117,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8E7FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1090,12 +1147,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.35"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1298,7 +1349,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1314,6 +1365,21 @@
       </top>
       <bottom style="thick">
         <color rgb="FFFC8462"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFF5F5F5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF5F5F5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF5F5F5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF5F5F5"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1433,206 +1499,226 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="51" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="51" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="53">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2166,7 +2252,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="46">
+      <c r="F21" s="52">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -2223,7 +2309,7 @@
       </c>
     </row>
     <row r="4" ht="16" spans="1:11">
-      <c r="A4" s="6"/>
+      <c r="A4" s="12"/>
     </row>
     <row r="7" spans="1:11">
       <c r="D7" t="s">
@@ -2280,10 +2366,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="16"/>
+      <c r="K10" s="22"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="16"/>
+      <c r="K11" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2304,12 +2390,12 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:13">
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="28"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="34"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
@@ -2324,19 +2410,19 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="40"/>
+      <c r="K6" s="46"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="47">
         <v>10</v>
       </c>
     </row>
@@ -2344,29 +2430,29 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="47">
         <v>7</v>
       </c>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
+      <c r="L8" s="45"/>
+      <c r="M8" s="45"/>
     </row>
     <row r="9" ht="16" spans="2:13">
       <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="47">
         <v>10</v>
       </c>
     </row>
@@ -2374,29 +2460,29 @@
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="47">
         <v>8</v>
       </c>
-      <c r="K10" s="42"/>
-      <c r="L10" s="37"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="43"/>
     </row>
     <row r="11" ht="16" spans="2:13">
       <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="45">
         <v>1.5</v>
       </c>
     </row>
@@ -2404,13 +2490,13 @@
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="D12" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="39">
+      <c r="E12" s="45">
         <v>1.5</v>
       </c>
     </row>
@@ -2418,13 +2504,13 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="34">
         <v>2</v>
       </c>
     </row>
@@ -2432,13 +2518,13 @@
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="34">
         <v>0</v>
       </c>
     </row>
@@ -2446,13 +2532,13 @@
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="34">
         <v>0</v>
       </c>
     </row>
@@ -2460,13 +2546,13 @@
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="43">
+      <c r="E16" s="49">
         <v>12</v>
       </c>
     </row>
@@ -2474,561 +2560,561 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="44" t="s">
+      <c r="D17" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="51">
         <v>0.2</v>
       </c>
-      <c r="F17" s="28"/>
+      <c r="F17" s="34"/>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="44" t="s">
+      <c r="D18" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="45">
+      <c r="E18" s="51">
         <v>0.2</v>
       </c>
-      <c r="F18" s="28"/>
+      <c r="F18" s="34"/>
     </row>
     <row r="19" ht="16" spans="2:6">
       <c r="B19" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="44" t="s">
+      <c r="D19" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="45">
+      <c r="E19" s="51">
         <v>0.2</v>
       </c>
-      <c r="F19" s="28"/>
+      <c r="F19" s="34"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="39" t="s">
+      <c r="C20" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="44" t="s">
+      <c r="D20" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="45">
+      <c r="E20" s="51">
         <v>0.5</v>
       </c>
-      <c r="F20" s="28"/>
+      <c r="F20" s="34"/>
     </row>
     <row r="21" ht="16" spans="2:6">
       <c r="B21" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="44" t="s">
+      <c r="D21" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="45">
+      <c r="E21" s="51">
         <v>0.8</v>
       </c>
-      <c r="F21" s="28"/>
+      <c r="F21" s="34"/>
     </row>
     <row r="22" ht="16" spans="2:6">
       <c r="B22" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="44" t="s">
+      <c r="D22" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="39"/>
-      <c r="F22" s="28"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="34"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="44" t="s">
+      <c r="D23" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="34">
         <v>1</v>
       </c>
-      <c r="F23" s="28"/>
+      <c r="F23" s="34"/>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="44" t="s">
+      <c r="D24" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="34">
         <v>1</v>
       </c>
-      <c r="F24" s="28"/>
+      <c r="F24" s="34"/>
     </row>
     <row r="25" ht="16" spans="2:6">
       <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="44" t="s">
+      <c r="D25" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="34">
         <v>1</v>
       </c>
-      <c r="F25" s="28"/>
+      <c r="F25" s="34"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="44" t="s">
+      <c r="D26" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="39">
+      <c r="E26" s="45">
         <v>0.05</v>
       </c>
-      <c r="F26" s="28"/>
+      <c r="F26" s="34"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="46" t="s">
+      <c r="B27" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="47" t="s">
+      <c r="C27" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="47" t="s">
+      <c r="D27" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="47">
+      <c r="E27" s="53">
         <v>2020</v>
       </c>
-      <c r="F27" s="28"/>
+      <c r="F27" s="34"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="47" t="s">
+      <c r="D28" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="37">
         <v>2020</v>
       </c>
-      <c r="F28" s="28"/>
+      <c r="F28" s="34"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
     </row>
     <row r="38" spans="3:5">
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="48" t="s">
+      <c r="C54" s="54" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="48"/>
-      <c r="E56" s="48"/>
-      <c r="F56" s="48"/>
-      <c r="G56" s="48"/>
-      <c r="H56" s="48"/>
-      <c r="I56" s="48"/>
-      <c r="J56" s="48"/>
-      <c r="K56" s="48"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="54"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="54"/>
+      <c r="I56" s="54"/>
+      <c r="J56" s="54"/>
+      <c r="K56" s="54"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="48" t="s">
+      <c r="C57" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="48" t="s">
+      <c r="D57" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="48" t="s">
+      <c r="E57" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="F57" s="48" t="s">
+      <c r="F57" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="G57" s="48" t="s">
+      <c r="G57" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="48" t="s">
+      <c r="H57" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="48" t="s">
+      <c r="I57" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="J57" s="48" t="s">
+      <c r="J57" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="K57" s="48" t="s">
+      <c r="K57" s="54" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="48"/>
-      <c r="D58" s="48"/>
-      <c r="E58" s="48"/>
-      <c r="F58" s="48"/>
-      <c r="G58" s="48"/>
-      <c r="H58" s="48"/>
-      <c r="I58" s="48"/>
-      <c r="J58" s="48"/>
-      <c r="K58" s="48"/>
+      <c r="C58" s="54"/>
+      <c r="D58" s="54"/>
+      <c r="E58" s="54"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="54"/>
+      <c r="H58" s="54"/>
+      <c r="I58" s="54"/>
+      <c r="J58" s="54"/>
+      <c r="K58" s="54"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="48"/>
-      <c r="D59" s="48"/>
-      <c r="E59" s="48"/>
-      <c r="F59" s="48"/>
-      <c r="G59" s="48"/>
-      <c r="H59" s="48"/>
-      <c r="I59" s="48"/>
-      <c r="J59" s="48"/>
-      <c r="K59" s="48"/>
+      <c r="C59" s="54"/>
+      <c r="D59" s="54"/>
+      <c r="E59" s="54"/>
+      <c r="F59" s="54"/>
+      <c r="G59" s="54"/>
+      <c r="H59" s="54"/>
+      <c r="I59" s="54"/>
+      <c r="J59" s="54"/>
+      <c r="K59" s="54"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="48"/>
-      <c r="D60" s="48"/>
-      <c r="E60" s="48"/>
-      <c r="F60" s="48"/>
-      <c r="G60" s="48"/>
-      <c r="H60" s="48"/>
-      <c r="I60" s="48"/>
-      <c r="J60" s="48"/>
-      <c r="K60" s="48"/>
+      <c r="C60" s="54"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="54"/>
+      <c r="F60" s="54"/>
+      <c r="G60" s="54"/>
+      <c r="H60" s="54"/>
+      <c r="I60" s="54"/>
+      <c r="J60" s="54"/>
+      <c r="K60" s="54"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="48"/>
-      <c r="D61" s="48"/>
-      <c r="E61" s="48"/>
-      <c r="F61" s="48"/>
-      <c r="G61" s="48"/>
-      <c r="H61" s="48"/>
-      <c r="I61" s="48"/>
-      <c r="J61" s="48"/>
-      <c r="K61" s="48"/>
+      <c r="C61" s="54"/>
+      <c r="D61" s="54"/>
+      <c r="E61" s="54"/>
+      <c r="F61" s="54"/>
+      <c r="G61" s="54"/>
+      <c r="H61" s="54"/>
+      <c r="I61" s="54"/>
+      <c r="J61" s="54"/>
+      <c r="K61" s="54"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="48"/>
-      <c r="D62" s="48"/>
-      <c r="E62" s="48"/>
-      <c r="F62" s="48"/>
-      <c r="G62" s="48"/>
-      <c r="H62" s="48"/>
-      <c r="I62" s="48"/>
-      <c r="J62" s="48"/>
-      <c r="K62" s="48"/>
+      <c r="C62" s="54"/>
+      <c r="D62" s="54"/>
+      <c r="E62" s="54"/>
+      <c r="F62" s="54"/>
+      <c r="G62" s="54"/>
+      <c r="H62" s="54"/>
+      <c r="I62" s="54"/>
+      <c r="J62" s="54"/>
+      <c r="K62" s="54"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="48"/>
-      <c r="D63" s="48"/>
-      <c r="E63" s="48"/>
-      <c r="F63" s="48"/>
-      <c r="G63" s="48"/>
-      <c r="H63" s="48"/>
-      <c r="I63" s="48"/>
-      <c r="J63" s="48"/>
-      <c r="K63" s="48"/>
+      <c r="C63" s="54"/>
+      <c r="D63" s="54"/>
+      <c r="E63" s="54"/>
+      <c r="F63" s="54"/>
+      <c r="G63" s="54"/>
+      <c r="H63" s="54"/>
+      <c r="I63" s="54"/>
+      <c r="J63" s="54"/>
+      <c r="K63" s="54"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="48"/>
-      <c r="D64" s="48"/>
-      <c r="E64" s="48"/>
-      <c r="F64" s="48"/>
-      <c r="G64" s="48"/>
-      <c r="H64" s="48"/>
-      <c r="I64" s="48"/>
-      <c r="J64" s="48"/>
-      <c r="K64" s="48"/>
+      <c r="C64" s="54"/>
+      <c r="D64" s="54"/>
+      <c r="E64" s="54"/>
+      <c r="F64" s="54"/>
+      <c r="G64" s="54"/>
+      <c r="H64" s="54"/>
+      <c r="I64" s="54"/>
+      <c r="J64" s="54"/>
+      <c r="K64" s="54"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="48"/>
-      <c r="D65" s="48"/>
-      <c r="E65" s="48"/>
-      <c r="F65" s="48"/>
-      <c r="G65" s="48"/>
-      <c r="H65" s="48"/>
-      <c r="I65" s="48"/>
-      <c r="J65" s="48"/>
-      <c r="K65" s="48"/>
+      <c r="C65" s="54"/>
+      <c r="D65" s="54"/>
+      <c r="E65" s="54"/>
+      <c r="F65" s="54"/>
+      <c r="G65" s="54"/>
+      <c r="H65" s="54"/>
+      <c r="I65" s="54"/>
+      <c r="J65" s="54"/>
+      <c r="K65" s="54"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="48"/>
-      <c r="D66" s="48"/>
-      <c r="E66" s="48"/>
-      <c r="F66" s="48"/>
-      <c r="G66" s="48"/>
-      <c r="H66" s="48"/>
-      <c r="I66" s="48"/>
-      <c r="J66" s="48"/>
-      <c r="K66" s="48"/>
+      <c r="C66" s="54"/>
+      <c r="D66" s="54"/>
+      <c r="E66" s="54"/>
+      <c r="F66" s="54"/>
+      <c r="G66" s="54"/>
+      <c r="H66" s="54"/>
+      <c r="I66" s="54"/>
+      <c r="J66" s="54"/>
+      <c r="K66" s="54"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="48"/>
-      <c r="D67" s="48"/>
-      <c r="E67" s="48"/>
-      <c r="F67" s="48"/>
-      <c r="G67" s="48"/>
-      <c r="H67" s="48"/>
-      <c r="I67" s="48"/>
-      <c r="J67" s="48"/>
-      <c r="K67" s="48"/>
+      <c r="C67" s="54"/>
+      <c r="D67" s="54"/>
+      <c r="E67" s="54"/>
+      <c r="F67" s="54"/>
+      <c r="G67" s="54"/>
+      <c r="H67" s="54"/>
+      <c r="I67" s="54"/>
+      <c r="J67" s="54"/>
+      <c r="K67" s="54"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="48"/>
-      <c r="D68" s="48"/>
-      <c r="E68" s="48"/>
-      <c r="F68" s="48"/>
-      <c r="G68" s="48"/>
-      <c r="H68" s="48"/>
-      <c r="I68" s="48"/>
-      <c r="J68" s="48"/>
-      <c r="K68" s="48"/>
+      <c r="C68" s="54"/>
+      <c r="D68" s="54"/>
+      <c r="E68" s="54"/>
+      <c r="F68" s="54"/>
+      <c r="G68" s="54"/>
+      <c r="H68" s="54"/>
+      <c r="I68" s="54"/>
+      <c r="J68" s="54"/>
+      <c r="K68" s="54"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="48"/>
-      <c r="D69" s="48"/>
-      <c r="E69" s="48"/>
-      <c r="F69" s="48"/>
-      <c r="G69" s="48"/>
-      <c r="H69" s="48"/>
-      <c r="I69" s="48"/>
-      <c r="J69" s="48"/>
-      <c r="K69" s="48"/>
+      <c r="C69" s="54"/>
+      <c r="D69" s="54"/>
+      <c r="E69" s="54"/>
+      <c r="F69" s="54"/>
+      <c r="G69" s="54"/>
+      <c r="H69" s="54"/>
+      <c r="I69" s="54"/>
+      <c r="J69" s="54"/>
+      <c r="K69" s="54"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="48"/>
-      <c r="D70" s="48"/>
-      <c r="E70" s="48"/>
-      <c r="F70" s="48"/>
-      <c r="G70" s="48"/>
-      <c r="H70" s="48"/>
-      <c r="I70" s="48"/>
-      <c r="J70" s="48"/>
-      <c r="K70" s="48"/>
+      <c r="C70" s="54"/>
+      <c r="D70" s="54"/>
+      <c r="E70" s="54"/>
+      <c r="F70" s="54"/>
+      <c r="G70" s="54"/>
+      <c r="H70" s="54"/>
+      <c r="I70" s="54"/>
+      <c r="J70" s="54"/>
+      <c r="K70" s="54"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="48"/>
-      <c r="D71" s="48"/>
-      <c r="E71" s="48"/>
-      <c r="F71" s="48"/>
-      <c r="G71" s="48"/>
-      <c r="H71" s="48"/>
-      <c r="I71" s="48"/>
-      <c r="J71" s="48"/>
-      <c r="K71" s="48"/>
+      <c r="C71" s="54"/>
+      <c r="D71" s="54"/>
+      <c r="E71" s="54"/>
+      <c r="F71" s="54"/>
+      <c r="G71" s="54"/>
+      <c r="H71" s="54"/>
+      <c r="I71" s="54"/>
+      <c r="J71" s="54"/>
+      <c r="K71" s="54"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="48"/>
-      <c r="D72" s="48"/>
-      <c r="E72" s="48"/>
-      <c r="F72" s="48"/>
-      <c r="G72" s="48"/>
-      <c r="H72" s="48"/>
-      <c r="I72" s="48"/>
-      <c r="J72" s="48"/>
-      <c r="K72" s="48"/>
+      <c r="C72" s="54"/>
+      <c r="D72" s="54"/>
+      <c r="E72" s="54"/>
+      <c r="F72" s="54"/>
+      <c r="G72" s="54"/>
+      <c r="H72" s="54"/>
+      <c r="I72" s="54"/>
+      <c r="J72" s="54"/>
+      <c r="K72" s="54"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="48"/>
-      <c r="D73" s="48"/>
-      <c r="E73" s="48"/>
-      <c r="F73" s="48"/>
-      <c r="G73" s="48"/>
-      <c r="H73" s="48"/>
-      <c r="I73" s="48"/>
-      <c r="J73" s="48"/>
-      <c r="K73" s="48"/>
+      <c r="C73" s="54"/>
+      <c r="D73" s="54"/>
+      <c r="E73" s="54"/>
+      <c r="F73" s="54"/>
+      <c r="G73" s="54"/>
+      <c r="H73" s="54"/>
+      <c r="I73" s="54"/>
+      <c r="J73" s="54"/>
+      <c r="K73" s="54"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="48"/>
-      <c r="D74" s="48"/>
-      <c r="E74" s="48"/>
-      <c r="F74" s="48"/>
-      <c r="G74" s="48"/>
-      <c r="H74" s="48"/>
-      <c r="I74" s="48"/>
-      <c r="J74" s="48"/>
-      <c r="K74" s="48"/>
+      <c r="C74" s="54"/>
+      <c r="D74" s="54"/>
+      <c r="E74" s="54"/>
+      <c r="F74" s="54"/>
+      <c r="G74" s="54"/>
+      <c r="H74" s="54"/>
+      <c r="I74" s="54"/>
+      <c r="J74" s="54"/>
+      <c r="K74" s="54"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="48"/>
-      <c r="D75" s="48"/>
-      <c r="E75" s="48"/>
-      <c r="F75" s="48"/>
-      <c r="G75" s="48"/>
-      <c r="H75" s="48"/>
-      <c r="I75" s="48"/>
-      <c r="J75" s="48"/>
-      <c r="K75" s="48"/>
+      <c r="C75" s="54"/>
+      <c r="D75" s="54"/>
+      <c r="E75" s="54"/>
+      <c r="F75" s="54"/>
+      <c r="G75" s="54"/>
+      <c r="H75" s="54"/>
+      <c r="I75" s="54"/>
+      <c r="J75" s="54"/>
+      <c r="K75" s="54"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="48"/>
-      <c r="D76" s="48"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="48"/>
-      <c r="G76" s="48"/>
-      <c r="H76" s="48"/>
-      <c r="I76" s="48"/>
-      <c r="J76" s="48"/>
-      <c r="K76" s="48"/>
+      <c r="C76" s="54"/>
+      <c r="D76" s="54"/>
+      <c r="E76" s="54"/>
+      <c r="F76" s="54"/>
+      <c r="G76" s="54"/>
+      <c r="H76" s="54"/>
+      <c r="I76" s="54"/>
+      <c r="J76" s="54"/>
+      <c r="K76" s="54"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="48"/>
-      <c r="D77" s="48"/>
-      <c r="E77" s="48"/>
-      <c r="F77" s="48"/>
-      <c r="G77" s="48"/>
-      <c r="H77" s="48"/>
-      <c r="I77" s="48"/>
-      <c r="J77" s="48"/>
-      <c r="K77" s="48"/>
+      <c r="C77" s="54"/>
+      <c r="D77" s="54"/>
+      <c r="E77" s="54"/>
+      <c r="F77" s="54"/>
+      <c r="G77" s="54"/>
+      <c r="H77" s="54"/>
+      <c r="I77" s="54"/>
+      <c r="J77" s="54"/>
+      <c r="K77" s="54"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="48"/>
-      <c r="D78" s="48"/>
-      <c r="E78" s="48"/>
-      <c r="F78" s="48"/>
-      <c r="G78" s="48"/>
-      <c r="H78" s="48"/>
-      <c r="I78" s="48"/>
-      <c r="J78" s="48"/>
-      <c r="K78" s="48"/>
+      <c r="C78" s="54"/>
+      <c r="D78" s="54"/>
+      <c r="E78" s="54"/>
+      <c r="F78" s="54"/>
+      <c r="G78" s="54"/>
+      <c r="H78" s="54"/>
+      <c r="I78" s="54"/>
+      <c r="J78" s="54"/>
+      <c r="K78" s="54"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="48"/>
-      <c r="D79" s="48"/>
-      <c r="E79" s="48"/>
-      <c r="F79" s="48"/>
-      <c r="G79" s="48"/>
-      <c r="H79" s="48"/>
-      <c r="I79" s="48"/>
-      <c r="J79" s="48"/>
-      <c r="K79" s="48"/>
+      <c r="C79" s="54"/>
+      <c r="D79" s="54"/>
+      <c r="E79" s="54"/>
+      <c r="F79" s="54"/>
+      <c r="G79" s="54"/>
+      <c r="H79" s="54"/>
+      <c r="I79" s="54"/>
+      <c r="J79" s="54"/>
+      <c r="K79" s="54"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="48"/>
-      <c r="D80" s="48"/>
-      <c r="E80" s="48"/>
-      <c r="F80" s="48"/>
-      <c r="G80" s="48"/>
-      <c r="H80" s="48"/>
-      <c r="I80" s="48"/>
-      <c r="J80" s="48"/>
-      <c r="K80" s="48"/>
+      <c r="C80" s="54"/>
+      <c r="D80" s="54"/>
+      <c r="E80" s="54"/>
+      <c r="F80" s="54"/>
+      <c r="G80" s="54"/>
+      <c r="H80" s="54"/>
+      <c r="I80" s="54"/>
+      <c r="J80" s="54"/>
+      <c r="K80" s="54"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="48"/>
-      <c r="D81" s="48"/>
-      <c r="E81" s="48"/>
-      <c r="F81" s="48"/>
-      <c r="G81" s="48"/>
-      <c r="H81" s="48"/>
-      <c r="I81" s="48"/>
-      <c r="J81" s="48"/>
-      <c r="K81" s="48"/>
+      <c r="C81" s="54"/>
+      <c r="D81" s="54"/>
+      <c r="E81" s="54"/>
+      <c r="F81" s="54"/>
+      <c r="G81" s="54"/>
+      <c r="H81" s="54"/>
+      <c r="I81" s="54"/>
+      <c r="J81" s="54"/>
+      <c r="K81" s="54"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="48"/>
-      <c r="D82" s="48"/>
-      <c r="E82" s="48"/>
-      <c r="F82" s="48"/>
-      <c r="G82" s="48"/>
-      <c r="H82" s="48"/>
-      <c r="I82" s="48"/>
-      <c r="J82" s="48"/>
-      <c r="K82" s="48"/>
+      <c r="C82" s="54"/>
+      <c r="D82" s="54"/>
+      <c r="E82" s="54"/>
+      <c r="F82" s="54"/>
+      <c r="G82" s="54"/>
+      <c r="H82" s="54"/>
+      <c r="I82" s="54"/>
+      <c r="J82" s="54"/>
+      <c r="K82" s="54"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="48"/>
-      <c r="D83" s="48"/>
-      <c r="E83" s="48"/>
-      <c r="F83" s="48"/>
-      <c r="G83" s="48"/>
-      <c r="H83" s="48"/>
-      <c r="I83" s="48"/>
-      <c r="J83" s="48"/>
-      <c r="K83" s="48"/>
+      <c r="C83" s="54"/>
+      <c r="D83" s="54"/>
+      <c r="E83" s="54"/>
+      <c r="F83" s="54"/>
+      <c r="G83" s="54"/>
+      <c r="H83" s="54"/>
+      <c r="I83" s="54"/>
+      <c r="J83" s="54"/>
+      <c r="K83" s="54"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="48" t="s">
+      <c r="C84" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="D84" s="48">
+      <c r="D84" s="54">
         <v>1</v>
       </c>
-      <c r="E84" s="48"/>
-      <c r="F84" s="48"/>
-      <c r="G84" s="48"/>
-      <c r="H84" s="48"/>
-      <c r="I84" s="48"/>
-      <c r="J84" s="48"/>
-      <c r="K84" s="48"/>
+      <c r="E84" s="54"/>
+      <c r="F84" s="54"/>
+      <c r="G84" s="54"/>
+      <c r="H84" s="54"/>
+      <c r="I84" s="54"/>
+      <c r="J84" s="54"/>
+      <c r="K84" s="54"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="48"/>
-      <c r="D85" s="48"/>
-      <c r="E85" s="48"/>
-      <c r="F85" s="48"/>
-      <c r="G85" s="48"/>
-      <c r="H85" s="48"/>
-      <c r="I85" s="48"/>
-      <c r="J85" s="48"/>
-      <c r="K85" s="48"/>
+      <c r="C85" s="54"/>
+      <c r="D85" s="54"/>
+      <c r="E85" s="54"/>
+      <c r="F85" s="54"/>
+      <c r="G85" s="54"/>
+      <c r="H85" s="54"/>
+      <c r="I85" s="54"/>
+      <c r="J85" s="54"/>
+      <c r="K85" s="54"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3052,568 +3138,568 @@
   </cols>
   <sheetData>
     <row r="13" spans="5:21">
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-      <c r="U13" s="5"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
     </row>
     <row r="14" spans="5:21">
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
     </row>
     <row r="15" spans="5:21">
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="5"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
     </row>
     <row r="16" spans="5:21">
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
-      <c r="U16" s="5"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
     </row>
     <row r="17" spans="5:23">
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-      <c r="S17" s="5"/>
-      <c r="T17" s="5"/>
-      <c r="U17" s="5"/>
-      <c r="V17" s="5"/>
-      <c r="W17" s="5"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
     </row>
     <row r="18" spans="5:23">
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
-      <c r="U18" s="5"/>
-      <c r="V18" s="5"/>
-      <c r="W18" s="5"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
     </row>
     <row r="19" spans="5:23">
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-      <c r="U19" s="5"/>
-      <c r="V19" s="5"/>
-      <c r="W19" s="5"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
     </row>
     <row r="20" spans="5:23">
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="5"/>
-      <c r="V20" s="5"/>
-      <c r="W20" s="5"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
     </row>
     <row r="21" spans="5:23">
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="5"/>
-      <c r="V21" s="5"/>
-      <c r="W21" s="5"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
     </row>
     <row r="22" spans="5:23">
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-      <c r="V22" s="5"/>
-      <c r="W22" s="5"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
     </row>
     <row r="23" spans="5:23">
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
-      <c r="U23" s="5"/>
-      <c r="V23" s="5"/>
-      <c r="W23" s="5"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1"/>
+      <c r="W23" s="1"/>
     </row>
     <row r="24" spans="5:23">
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5"/>
-      <c r="S24" s="5"/>
-      <c r="T24" s="5"/>
-      <c r="U24" s="5"/>
-      <c r="V24" s="5"/>
-      <c r="W24" s="5"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
     </row>
     <row r="25" spans="5:23">
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
-      <c r="S25" s="5"/>
-      <c r="T25" s="5"/>
-      <c r="U25" s="5"/>
-      <c r="V25" s="5"/>
-      <c r="W25" s="5"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
     </row>
     <row r="26" spans="5:23">
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
-      <c r="T26" s="5"/>
-      <c r="U26" s="5"/>
-      <c r="V26" s="5"/>
-      <c r="W26" s="5"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
     </row>
     <row r="27" spans="5:23">
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-      <c r="S27" s="5"/>
-      <c r="T27" s="5"/>
-      <c r="U27" s="5"/>
-      <c r="V27" s="5"/>
-      <c r="W27" s="5"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
     </row>
     <row r="28" spans="5:23">
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-      <c r="S28" s="5"/>
-      <c r="T28" s="5"/>
-      <c r="U28" s="5"/>
-      <c r="V28" s="5"/>
-      <c r="W28" s="5"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
     </row>
     <row r="29" spans="5:23">
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5" t="s">
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
-      <c r="R29" s="5"/>
-      <c r="S29" s="5"/>
-      <c r="T29" s="5"/>
-      <c r="U29" s="5"/>
-      <c r="V29" s="5"/>
-      <c r="W29" s="5"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
     </row>
     <row r="30" ht="15.25" spans="5:23">
-      <c r="F30" s="5" t="s">
+      <c r="F30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="G30" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I30" s="5" t="s">
+      <c r="I30" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J30" s="5" t="s">
+      <c r="J30" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K30" s="5" t="s">
+      <c r="K30" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="L30" s="5" t="s">
+      <c r="L30" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M30" s="5" t="s">
+      <c r="M30" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="N30" s="5" t="s">
+      <c r="N30" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="O30" s="5" t="s">
+      <c r="O30" s="1" t="s">
         <v>64</v>
       </c>
       <c r="P30" t="s">
         <v>65</v>
       </c>
-      <c r="Q30" s="5" t="s">
+      <c r="Q30" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="R30" s="5"/>
-      <c r="S30" s="5"/>
-      <c r="T30" s="5"/>
-      <c r="U30" s="5"/>
-      <c r="V30" s="5"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+      <c r="V30" s="1"/>
     </row>
     <row r="31" ht="16" spans="5:23">
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="G31" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="H31" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="I31" s="5" t="s">
+      <c r="I31" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5">
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1">
         <v>-0.25</v>
       </c>
-      <c r="N31" s="5"/>
-      <c r="O31" s="5">
+      <c r="N31" s="1"/>
+      <c r="O31" s="1">
         <v>0</v>
       </c>
-      <c r="P31" s="5">
+      <c r="P31" s="1">
         <v>3</v>
       </c>
-      <c r="Q31" s="5" t="s">
+      <c r="Q31" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="R31" s="5"/>
-      <c r="S31" s="5"/>
-      <c r="T31" s="5"/>
-      <c r="U31" s="5"/>
-      <c r="V31" s="5"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
     </row>
     <row r="32" ht="15.25" spans="5:23">
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5" t="s">
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5">
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1">
         <v>-0.1</v>
       </c>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5"/>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="5"/>
-      <c r="R32" s="5"/>
-      <c r="S32" s="5"/>
-      <c r="T32" s="5"/>
-      <c r="U32" s="5"/>
-      <c r="V32" s="5"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
     </row>
     <row r="33" spans="6:22">
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5" t="s">
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5" t="s">
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5">
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1">
         <v>1</v>
       </c>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
-      <c r="R33" s="5"/>
-      <c r="S33" s="5"/>
-      <c r="T33" s="5"/>
-      <c r="U33" s="5"/>
-      <c r="V33" s="5"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
     </row>
     <row r="34" spans="6:22">
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="5"/>
-      <c r="R34" s="5"/>
-      <c r="S34" s="5"/>
-      <c r="T34" s="5"/>
-      <c r="U34" s="5"/>
-      <c r="V34" s="5"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
     </row>
     <row r="35" spans="6:22">
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="5"/>
-      <c r="P35" s="5"/>
-      <c r="Q35" s="5"/>
-      <c r="R35" s="5"/>
-      <c r="S35" s="5"/>
-      <c r="T35" s="5"/>
-      <c r="U35" s="5"/>
-      <c r="V35" s="5"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1"/>
     </row>
     <row r="36" spans="6:22">
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="5"/>
-      <c r="R36" s="5"/>
-      <c r="S36" s="5"/>
-      <c r="T36" s="5"/>
-      <c r="U36" s="5"/>
-      <c r="V36" s="5"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
     </row>
     <row r="37" spans="6:22">
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5"/>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="5"/>
-      <c r="S37" s="5"/>
-      <c r="T37" s="5"/>
-      <c r="U37" s="5"/>
-      <c r="V37" s="5"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1"/>
     </row>
     <row r="38" spans="6:22">
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="5"/>
-      <c r="S38" s="5"/>
-      <c r="T38" s="5"/>
-      <c r="U38" s="5"/>
-      <c r="V38" s="5"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3649,755 +3735,755 @@
       </c>
     </row>
     <row r="4" spans="2:14">
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23" t="s">
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
     </row>
     <row r="5" spans="2:14">
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="24" t="s">
+      <c r="I8" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="J8" s="24" t="s">
+      <c r="J8" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="K8" s="24" t="s">
+      <c r="K8" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="L8" s="25" t="s">
+      <c r="L8" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="M8" s="25" t="s">
+      <c r="M8" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="N8" s="24" t="s">
+      <c r="N8" s="30" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="9" spans="2:14">
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="E9" s="23"/>
-      <c r="F9" s="26" t="s">
+      <c r="E9" s="29"/>
+      <c r="F9" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="H9" s="26" t="s">
+      <c r="H9" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="I9" s="26" t="s">
+      <c r="I9" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="J9" s="23">
+      <c r="J9" s="29">
         <v>1</v>
       </c>
-      <c r="K9" s="26">
+      <c r="K9" s="32">
         <v>1.25</v>
       </c>
-      <c r="L9" s="23">
+      <c r="L9" s="29">
         <v>0.05</v>
       </c>
-      <c r="M9" s="26">
+      <c r="M9" s="32">
         <v>1</v>
       </c>
-      <c r="N9" s="26"/>
+      <c r="N9" s="32"/>
     </row>
     <row r="10" spans="2:14">
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="E10" s="23"/>
-      <c r="F10" s="26" t="s">
+      <c r="E10" s="29"/>
+      <c r="F10" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="G10" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="H10" s="26" t="s">
+      <c r="H10" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="I10" s="26" t="s">
+      <c r="I10" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="J10" s="23">
+      <c r="J10" s="29">
         <v>1</v>
       </c>
-      <c r="K10" s="26">
+      <c r="K10" s="32">
         <v>1.11</v>
       </c>
-      <c r="L10" s="23">
+      <c r="L10" s="29">
         <v>0.05</v>
       </c>
-      <c r="M10" s="26">
+      <c r="M10" s="32">
         <v>1</v>
       </c>
-      <c r="N10" s="26"/>
+      <c r="N10" s="32"/>
     </row>
     <row r="11" spans="2:14">
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="23"/>
-      <c r="F11" s="26" t="s">
+      <c r="E11" s="29"/>
+      <c r="F11" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="G11" s="26" t="s">
+      <c r="G11" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="H11" s="26" t="s">
+      <c r="H11" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="I11" s="26" t="s">
+      <c r="I11" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="J11" s="23">
+      <c r="J11" s="29">
         <v>1</v>
       </c>
-      <c r="K11" s="26">
+      <c r="K11" s="32">
         <v>1.15</v>
       </c>
-      <c r="L11" s="23">
+      <c r="L11" s="29">
         <v>0.08</v>
       </c>
-      <c r="M11" s="26">
+      <c r="M11" s="32">
         <v>1</v>
       </c>
-      <c r="N11" s="26"/>
+      <c r="N11" s="32"/>
     </row>
     <row r="12" ht="16" spans="2:14">
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="23"/>
-      <c r="F12" s="27" t="s">
+      <c r="E12" s="29"/>
+      <c r="F12" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="26" t="s">
+      <c r="G12" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="H12" s="26" t="s">
+      <c r="H12" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="I12" s="26" t="s">
+      <c r="I12" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="J12" s="23">
+      <c r="J12" s="29">
         <v>1</v>
       </c>
-      <c r="K12" s="26">
+      <c r="K12" s="32">
         <v>1.12</v>
       </c>
-      <c r="L12" s="23">
+      <c r="L12" s="29">
         <v>0.03</v>
       </c>
-      <c r="M12" s="26">
+      <c r="M12" s="32">
         <v>1</v>
       </c>
-      <c r="N12" s="26"/>
+      <c r="N12" s="32"/>
     </row>
     <row r="13" spans="2:14">
-      <c r="D13" s="26" t="s">
+      <c r="D13" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="E13" s="23"/>
-      <c r="F13" s="26" t="s">
+      <c r="E13" s="29"/>
+      <c r="F13" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="G13" s="26" t="s">
+      <c r="G13" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="H13" s="26" t="s">
+      <c r="H13" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="I13" s="26" t="s">
+      <c r="I13" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="J13" s="23">
+      <c r="J13" s="29">
         <v>1</v>
       </c>
-      <c r="K13" s="26">
+      <c r="K13" s="32">
         <v>1.2</v>
       </c>
-      <c r="L13" s="23">
+      <c r="L13" s="29">
         <v>0.1</v>
       </c>
-      <c r="M13" s="26">
+      <c r="M13" s="32">
         <v>1</v>
       </c>
-      <c r="N13" s="26"/>
+      <c r="N13" s="32"/>
     </row>
     <row r="14" spans="2:14">
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="E14" s="23"/>
-      <c r="F14" s="26" t="s">
+      <c r="E14" s="29"/>
+      <c r="F14" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="G14" s="26" t="s">
+      <c r="G14" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="H14" s="26" t="s">
+      <c r="H14" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="I14" s="26" t="s">
+      <c r="I14" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="29">
         <v>1</v>
       </c>
-      <c r="K14" s="26">
+      <c r="K14" s="32">
         <v>1.06</v>
       </c>
-      <c r="L14" s="23">
+      <c r="L14" s="29">
         <v>0.15</v>
       </c>
-      <c r="M14" s="26">
+      <c r="M14" s="32">
         <v>1</v>
       </c>
-      <c r="N14" s="26"/>
+      <c r="N14" s="32"/>
     </row>
     <row r="15" spans="2:14">
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="E15" s="23"/>
-      <c r="F15" s="26" t="s">
+      <c r="E15" s="29"/>
+      <c r="F15" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="G15" s="26" t="s">
+      <c r="G15" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="H15" s="26" t="s">
+      <c r="H15" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="I15" s="26" t="s">
+      <c r="I15" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="J15" s="23">
+      <c r="J15" s="29">
         <v>1</v>
       </c>
-      <c r="K15" s="26">
+      <c r="K15" s="32">
         <v>1.06</v>
       </c>
-      <c r="L15" s="23">
+      <c r="L15" s="29">
         <v>0.3</v>
       </c>
-      <c r="M15" s="26">
+      <c r="M15" s="32">
         <v>1</v>
       </c>
-      <c r="N15" s="26"/>
+      <c r="N15" s="32"/>
     </row>
     <row r="16" ht="16" spans="2:14">
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="E16" s="23"/>
-      <c r="F16" s="27" t="s">
+      <c r="E16" s="29"/>
+      <c r="F16" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="23" t="str">
+      <c r="G16" s="29" t="str">
         <f xml:space="preserve">G15</f>
         <v>CAP,GROWTH</v>
       </c>
-      <c r="H16" s="23" t="str">
+      <c r="H16" s="29" t="str">
         <f xml:space="preserve">H15</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I16" s="26" t="s">
+      <c r="I16" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="J16" s="23">
+      <c r="J16" s="29">
         <f t="shared" ref="J16:L16" si="0" xml:space="preserve">J12</f>
         <v>1</v>
       </c>
-      <c r="K16" s="23">
+      <c r="K16" s="29">
         <f t="shared" si="0"/>
         <v>1.12</v>
       </c>
-      <c r="L16" s="23">
+      <c r="L16" s="29">
         <f t="shared" si="0"/>
         <v>0.03</v>
       </c>
-      <c r="M16" s="23">
+      <c r="M16" s="29">
         <f xml:space="preserve">M15</f>
         <v>1</v>
       </c>
-      <c r="N16" s="23"/>
+      <c r="N16" s="29"/>
     </row>
     <row r="17" ht="16" spans="4:14">
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="E17" s="23"/>
-      <c r="F17" s="27" t="s">
+      <c r="E17" s="29"/>
+      <c r="F17" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="G17" s="23" t="str">
+      <c r="G17" s="29" t="str">
         <f t="shared" ref="G17:M17" si="1" xml:space="preserve">G16</f>
         <v>CAP,GROWTH</v>
       </c>
-      <c r="H17" s="23" t="str">
+      <c r="H17" s="29" t="str">
         <f t="shared" si="1"/>
         <v>2025, 2150</v>
       </c>
-      <c r="I17" s="26" t="s">
+      <c r="I17" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="J17" s="23">
+      <c r="J17" s="29">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K17" s="23">
+      <c r="K17" s="29">
         <f t="shared" si="1"/>
         <v>1.12</v>
       </c>
-      <c r="L17" s="23">
+      <c r="L17" s="29">
         <f t="shared" si="1"/>
         <v>0.03</v>
       </c>
-      <c r="M17" s="23">
+      <c r="M17" s="29">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N17" s="23"/>
+      <c r="N17" s="29"/>
     </row>
     <row r="18" ht="16" spans="4:14">
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="E18" s="23"/>
-      <c r="F18" s="27" t="s">
+      <c r="E18" s="29"/>
+      <c r="F18" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="G18" s="23" t="str">
+      <c r="G18" s="29" t="str">
         <f xml:space="preserve">G17</f>
         <v>CAP,GROWTH</v>
       </c>
-      <c r="H18" s="23" t="str">
+      <c r="H18" s="29" t="str">
         <f xml:space="preserve">H17</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I18" s="26" t="s">
+      <c r="I18" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="J18" s="23">
+      <c r="J18" s="29">
         <v>1</v>
       </c>
-      <c r="K18" s="23">
+      <c r="K18" s="29">
         <v>1</v>
       </c>
-      <c r="L18" s="23">
+      <c r="L18" s="29">
         <v>0</v>
       </c>
-      <c r="M18" s="23">
+      <c r="M18" s="29">
         <v>1</v>
       </c>
-      <c r="N18" s="23"/>
+      <c r="N18" s="29"/>
     </row>
     <row r="25" spans="4:14">
       <c r="K25" t="s">
         <v>105</v>
       </c>
-      <c r="L25" s="16" t="s">
+      <c r="L25" s="22" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="27" spans="4:14">
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="28"/>
-      <c r="M27" s="28"/>
-      <c r="N27" s="28"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="34"/>
+      <c r="K27" s="34"/>
+      <c r="L27" s="34"/>
+      <c r="M27" s="34"/>
+      <c r="N27" s="34"/>
     </row>
     <row r="28" spans="4:14">
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28" t="s">
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="28"/>
-      <c r="N28" s="28"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
     </row>
     <row r="29" spans="4:14">
-      <c r="D29" s="28" t="s">
+      <c r="D29" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="E29" s="28" t="s">
+      <c r="E29" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="F29" s="28" t="s">
+      <c r="F29" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="28" t="s">
+      <c r="G29" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="H29" s="28" t="s">
+      <c r="H29" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="I29" s="28" t="s">
+      <c r="I29" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="J29" s="28" t="s">
+      <c r="J29" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="K29" s="28" t="s">
+      <c r="K29" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="L29" s="28" t="s">
+      <c r="L29" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="M29" s="28" t="s">
+      <c r="M29" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="N29" s="28" t="s">
+      <c r="N29" s="34" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="30" ht="16" spans="4:14">
-      <c r="D30" s="28" t="s">
+      <c r="D30" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="28"/>
-      <c r="F30" s="29" t="s">
+      <c r="E30" s="34"/>
+      <c r="F30" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="G30" s="28" t="s">
+      <c r="G30" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="H30" s="28" t="s">
+      <c r="H30" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="I30" s="28" t="s">
+      <c r="I30" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="28">
+      <c r="J30" s="34">
         <v>1</v>
       </c>
-      <c r="K30" s="28">
+      <c r="K30" s="34">
         <v>1</v>
       </c>
-      <c r="L30" s="28">
+      <c r="L30" s="34">
         <v>0.01</v>
       </c>
-      <c r="M30" s="28">
+      <c r="M30" s="34">
         <v>1</v>
       </c>
-      <c r="N30" s="28"/>
+      <c r="N30" s="34"/>
     </row>
     <row r="31" ht="16" spans="4:14">
-      <c r="D31" s="28" t="s">
+      <c r="D31" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="28"/>
-      <c r="F31" s="30" t="s">
+      <c r="E31" s="34"/>
+      <c r="F31" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="G31" s="28" t="s">
+      <c r="G31" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="H31" s="28" t="s">
+      <c r="H31" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="I31" s="28" t="s">
+      <c r="I31" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="J31" s="28">
+      <c r="J31" s="34">
         <v>1</v>
       </c>
-      <c r="K31" s="28">
+      <c r="K31" s="34">
         <v>1</v>
       </c>
-      <c r="L31" s="28">
+      <c r="L31" s="34">
         <f t="shared" ref="L31:L36" si="2" xml:space="preserve">L30</f>
         <v>0.01</v>
       </c>
-      <c r="M31" s="28">
+      <c r="M31" s="34">
         <v>1</v>
       </c>
-      <c r="N31" s="28"/>
+      <c r="N31" s="34"/>
     </row>
     <row r="32" ht="16" spans="4:14">
-      <c r="D32" s="28" t="s">
+      <c r="D32" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="E32" s="28"/>
-      <c r="F32" s="30" t="s">
+      <c r="E32" s="34"/>
+      <c r="F32" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="G32" s="28" t="s">
+      <c r="G32" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="H32" s="28" t="s">
+      <c r="H32" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="I32" s="28" t="s">
+      <c r="I32" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="J32" s="28">
+      <c r="J32" s="34">
         <v>1</v>
       </c>
-      <c r="K32" s="28">
+      <c r="K32" s="34">
         <v>1</v>
       </c>
-      <c r="L32" s="28">
+      <c r="L32" s="34">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M32" s="28">
+      <c r="M32" s="34">
         <v>1</v>
       </c>
-      <c r="N32" s="28"/>
+      <c r="N32" s="34"/>
     </row>
     <row r="33" ht="16" spans="4:14">
-      <c r="D33" s="28" t="s">
+      <c r="D33" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="28"/>
-      <c r="F33" s="29" t="s">
+      <c r="E33" s="34"/>
+      <c r="F33" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="G33" s="28" t="s">
+      <c r="G33" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="H33" s="28" t="s">
+      <c r="H33" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="I33" s="28" t="s">
+      <c r="I33" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="J33" s="28">
+      <c r="J33" s="34">
         <v>1</v>
       </c>
-      <c r="K33" s="28">
+      <c r="K33" s="34">
         <f xml:space="preserve">K32</f>
         <v>1</v>
       </c>
-      <c r="L33" s="28">
+      <c r="L33" s="34">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M33" s="28">
+      <c r="M33" s="34">
         <v>1</v>
       </c>
-      <c r="N33" s="28"/>
+      <c r="N33" s="34"/>
     </row>
     <row r="34" ht="16" spans="4:14">
-      <c r="D34" s="28" t="s">
+      <c r="D34" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="E34" s="28"/>
-      <c r="F34" s="29" t="s">
+      <c r="E34" s="34"/>
+      <c r="F34" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="G34" s="28" t="s">
+      <c r="G34" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="H34" s="28" t="s">
+      <c r="H34" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="I34" s="28" t="s">
+      <c r="I34" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="J34" s="28">
+      <c r="J34" s="34">
         <v>1</v>
       </c>
-      <c r="K34" s="28">
+      <c r="K34" s="34">
         <f xml:space="preserve">K33</f>
         <v>1</v>
       </c>
-      <c r="L34" s="28">
+      <c r="L34" s="34">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M34" s="28">
+      <c r="M34" s="34">
         <v>1</v>
       </c>
-      <c r="N34" s="28"/>
+      <c r="N34" s="34"/>
     </row>
     <row r="35" ht="16" spans="4:14">
-      <c r="D35" s="28" t="s">
+      <c r="D35" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="E35" s="28"/>
-      <c r="F35" s="29" t="s">
+      <c r="E35" s="34"/>
+      <c r="F35" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="28" t="s">
+      <c r="G35" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="H35" s="28" t="s">
+      <c r="H35" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="I35" s="28" t="s">
+      <c r="I35" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="J35" s="28">
+      <c r="J35" s="34">
         <v>1</v>
       </c>
-      <c r="K35" s="28">
+      <c r="K35" s="34">
         <f xml:space="preserve">K34</f>
         <v>1</v>
       </c>
-      <c r="L35" s="28">
+      <c r="L35" s="34">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M35" s="28">
+      <c r="M35" s="34">
         <v>1</v>
       </c>
-      <c r="N35" s="28"/>
+      <c r="N35" s="34"/>
     </row>
     <row r="36" ht="16" spans="4:14">
-      <c r="D36" s="28" t="s">
+      <c r="D36" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="E36" s="28"/>
-      <c r="F36" s="29" t="s">
+      <c r="E36" s="34"/>
+      <c r="F36" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="G36" s="28" t="s">
+      <c r="G36" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="H36" s="28" t="s">
+      <c r="H36" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="I36" s="28" t="s">
+      <c r="I36" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="J36" s="28">
+      <c r="J36" s="34">
         <v>1</v>
       </c>
-      <c r="K36" s="28">
+      <c r="K36" s="34">
         <f xml:space="preserve">K35</f>
         <v>1</v>
       </c>
-      <c r="L36" s="28">
+      <c r="L36" s="34">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M36" s="28">
+      <c r="M36" s="34">
         <v>1</v>
       </c>
-      <c r="N36" s="28"/>
+      <c r="N36" s="34"/>
     </row>
     <row r="37" ht="16" spans="4:14">
-      <c r="D37" s="31" t="s">
+      <c r="D37" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="E37" s="31"/>
-      <c r="F37" s="32" t="s">
+      <c r="E37" s="37"/>
+      <c r="F37" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="G37" s="31" t="s">
+      <c r="G37" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="H37" s="31" t="s">
+      <c r="H37" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="I37" s="31" t="s">
+      <c r="I37" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="J37" s="31">
+      <c r="J37" s="37">
         <v>1</v>
       </c>
-      <c r="K37" s="31">
+      <c r="K37" s="37">
         <v>1</v>
       </c>
-      <c r="L37" s="31">
+      <c r="L37" s="37">
         <v>0</v>
       </c>
-      <c r="M37" s="31">
+      <c r="M37" s="37">
         <v>3</v>
       </c>
-      <c r="N37" s="28"/>
+      <c r="N37" s="34"/>
     </row>
     <row r="38" ht="16" spans="4:14">
-      <c r="D38" s="33" t="s">
+      <c r="D38" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="F38" s="32" t="s">
+      <c r="F38" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="G38" s="31" t="s">
+      <c r="G38" s="37" t="s">
         <v>84</v>
       </c>
       <c r="H38" t="str">
@@ -4419,469 +4505,469 @@
       <c r="M38">
         <v>3</v>
       </c>
-      <c r="N38" s="28"/>
+      <c r="N38" s="34"/>
     </row>
     <row r="39" ht="16" spans="4:14">
-      <c r="D39" s="33" t="s">
+      <c r="D39" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="E39" s="34"/>
-      <c r="F39" s="32" t="s">
+      <c r="E39" s="40"/>
+      <c r="F39" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="G39" s="31" t="s">
+      <c r="G39" s="37" t="s">
         <v>84</v>
       </c>
       <c r="H39" t="str">
         <f t="shared" ref="H39:M39" si="3" xml:space="preserve">H38</f>
         <v>2019, 2150</v>
       </c>
-      <c r="I39" s="34" t="str">
+      <c r="I39" s="40" t="str">
         <f t="shared" si="3"/>
         <v>UP</v>
       </c>
-      <c r="J39" s="34">
+      <c r="J39" s="40">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K39" s="34">
+      <c r="K39" s="40">
         <f t="shared" si="3"/>
         <v>1.1</v>
       </c>
-      <c r="L39" s="34">
+      <c r="L39" s="40">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M39" s="34">
+      <c r="M39" s="40">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="N39" s="34"/>
+      <c r="N39" s="40"/>
     </row>
     <row r="40" ht="16" spans="4:14">
-      <c r="D40" s="33" t="s">
+      <c r="D40" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="E40" s="34"/>
-      <c r="F40" s="32" t="s">
+      <c r="E40" s="40"/>
+      <c r="F40" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="G40" s="31" t="s">
+      <c r="G40" s="37" t="s">
         <v>84</v>
       </c>
       <c r="H40" t="str">
         <f t="shared" ref="H40:M40" si="4" xml:space="preserve">H39</f>
         <v>2019, 2150</v>
       </c>
-      <c r="I40" s="34" t="str">
+      <c r="I40" s="40" t="str">
         <f t="shared" si="4"/>
         <v>UP</v>
       </c>
-      <c r="J40" s="34">
+      <c r="J40" s="40">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="K40" s="34">
+      <c r="K40" s="40">
         <f t="shared" si="4"/>
         <v>1.1</v>
       </c>
-      <c r="L40" s="34">
+      <c r="L40" s="40">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M40" s="34">
+      <c r="M40" s="40">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="N40" s="34"/>
+      <c r="N40" s="40"/>
     </row>
     <row r="41" ht="16" spans="4:14">
-      <c r="D41" s="33" t="s">
+      <c r="D41" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="E41" s="34"/>
-      <c r="F41" s="32" t="s">
+      <c r="E41" s="40"/>
+      <c r="F41" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="G41" s="31" t="s">
+      <c r="G41" s="37" t="s">
         <v>84</v>
       </c>
       <c r="H41" t="str">
         <f t="shared" ref="H41:M41" si="5" xml:space="preserve">H40</f>
         <v>2019, 2150</v>
       </c>
-      <c r="I41" s="34" t="str">
+      <c r="I41" s="40" t="str">
         <f t="shared" si="5"/>
         <v>UP</v>
       </c>
-      <c r="J41" s="34">
+      <c r="J41" s="40">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="K41" s="34">
+      <c r="K41" s="40">
         <f t="shared" si="5"/>
         <v>1.1</v>
       </c>
-      <c r="L41" s="34">
+      <c r="L41" s="40">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M41" s="34">
+      <c r="M41" s="40">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="N41" s="34"/>
+      <c r="N41" s="40"/>
     </row>
     <row r="42" ht="16" spans="4:14">
-      <c r="D42" s="33" t="s">
+      <c r="D42" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="F42" s="32" t="s">
+      <c r="F42" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="G42" s="31" t="s">
+      <c r="G42" s="37" t="s">
         <v>84</v>
       </c>
       <c r="H42" t="str">
         <f t="shared" ref="H42:M42" si="6" xml:space="preserve">H41</f>
         <v>2019, 2150</v>
       </c>
-      <c r="I42" s="34" t="str">
+      <c r="I42" s="40" t="str">
         <f t="shared" si="6"/>
         <v>UP</v>
       </c>
-      <c r="J42" s="34">
+      <c r="J42" s="40">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="K42" s="34">
+      <c r="K42" s="40">
         <f t="shared" si="6"/>
         <v>1.1</v>
       </c>
-      <c r="L42" s="34">
+      <c r="L42" s="40">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M42" s="34">
+      <c r="M42" s="40">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="N42" s="34"/>
+      <c r="N42" s="40"/>
     </row>
     <row r="43" spans="4:14">
-      <c r="D43" s="31" t="s">
+      <c r="D43" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="E43" s="31"/>
-      <c r="F43" s="35" t="s">
+      <c r="E43" s="37"/>
+      <c r="F43" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="G43" s="31" t="s">
+      <c r="G43" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="H43" s="31" t="s">
+      <c r="H43" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="I43" s="31" t="s">
+      <c r="I43" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="J43" s="31">
+      <c r="J43" s="37">
         <v>1</v>
       </c>
-      <c r="K43" s="31">
+      <c r="K43" s="37">
         <v>1</v>
       </c>
-      <c r="L43" s="31">
+      <c r="L43" s="37">
         <v>0</v>
       </c>
-      <c r="M43" s="31">
+      <c r="M43" s="37">
         <v>3</v>
       </c>
-      <c r="N43" s="34"/>
+      <c r="N43" s="40"/>
     </row>
     <row r="44" spans="4:14">
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
-      <c r="M44" s="5"/>
-      <c r="N44" s="34"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="40"/>
     </row>
     <row r="45" spans="4:14">
-      <c r="D45" s="34"/>
-      <c r="E45" s="34"/>
-      <c r="F45" s="36"/>
-      <c r="G45" s="34"/>
-      <c r="H45" s="34"/>
-      <c r="I45" s="34"/>
-      <c r="J45" s="34"/>
-      <c r="K45" s="34"/>
-      <c r="L45" s="34"/>
-      <c r="M45" s="34"/>
-      <c r="N45" s="34"/>
+      <c r="D45" s="40"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="40"/>
+      <c r="J45" s="40"/>
+      <c r="K45" s="40"/>
+      <c r="L45" s="40"/>
+      <c r="M45" s="40"/>
+      <c r="N45" s="40"/>
     </row>
     <row r="46" spans="4:14">
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="34"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="40"/>
     </row>
     <row r="47" spans="4:14">
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5"/>
-      <c r="L47" s="5"/>
-      <c r="M47" s="5"/>
-      <c r="N47" s="34"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="40"/>
     </row>
     <row r="48" spans="4:14">
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="5"/>
-      <c r="M48" s="5"/>
-      <c r="N48" s="34"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="40"/>
     </row>
     <row r="49" spans="4:14">
-      <c r="N49" s="28"/>
+      <c r="N49" s="34"/>
     </row>
     <row r="50" spans="4:14">
-      <c r="D50" s="28"/>
-      <c r="E50" s="28"/>
-      <c r="F50" s="28"/>
-      <c r="G50" s="28"/>
-      <c r="H50" s="28" t="s">
+      <c r="D50" s="34"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="34"/>
+      <c r="G50" s="34"/>
+      <c r="H50" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="I50" s="28"/>
-      <c r="J50" s="28"/>
-      <c r="K50" s="28"/>
-      <c r="L50" s="28"/>
-      <c r="M50" s="28"/>
-      <c r="N50" s="28"/>
+      <c r="I50" s="34"/>
+      <c r="J50" s="34"/>
+      <c r="K50" s="34"/>
+      <c r="L50" s="34"/>
+      <c r="M50" s="34"/>
+      <c r="N50" s="34"/>
     </row>
     <row r="51" ht="16" spans="4:14">
-      <c r="D51" s="28" t="s">
+      <c r="D51" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="E51" s="28" t="s">
+      <c r="E51" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="F51" s="28" t="s">
+      <c r="F51" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="G51" s="28" t="s">
+      <c r="G51" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="H51" s="34" t="s">
+      <c r="H51" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="I51" s="28" t="s">
+      <c r="I51" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="J51" s="6" t="s">
+      <c r="J51" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="K51" s="28" t="s">
+      <c r="K51" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="L51" s="28" t="s">
+      <c r="L51" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="M51" s="28" t="s">
+      <c r="M51" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="N51" s="28" t="s">
+      <c r="N51" s="34" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="52" spans="4:14">
-      <c r="D52" s="28" t="s">
+      <c r="D52" s="34" t="s">
         <v>141</v>
       </c>
-      <c r="E52" s="28"/>
-      <c r="F52" s="37" t="s">
+      <c r="E52" s="34"/>
+      <c r="F52" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="G52" s="28" t="s">
+      <c r="G52" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="H52" s="34" t="s">
+      <c r="H52" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="I52" s="28" t="s">
+      <c r="I52" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="J52" s="28">
+      <c r="J52" s="34">
         <v>1</v>
       </c>
-      <c r="K52" s="28">
+      <c r="K52" s="34">
         <v>1</v>
       </c>
-      <c r="L52" s="28">
+      <c r="L52" s="34">
         <v>0</v>
       </c>
-      <c r="M52" s="28">
+      <c r="M52" s="34">
         <v>5</v>
       </c>
-      <c r="N52" s="28"/>
+      <c r="N52" s="34"/>
     </row>
     <row r="53" spans="4:14">
-      <c r="D53" s="28" t="s">
+      <c r="D53" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="E53" s="28"/>
-      <c r="F53" s="37" t="s">
+      <c r="E53" s="34"/>
+      <c r="F53" s="43" t="s">
         <v>146</v>
       </c>
-      <c r="G53" s="28" t="s">
+      <c r="G53" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="H53" s="38" t="s">
+      <c r="H53" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="I53" s="28" t="s">
+      <c r="I53" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="J53" s="28">
+      <c r="J53" s="34">
         <v>1</v>
       </c>
-      <c r="K53" s="28">
+      <c r="K53" s="34">
         <v>1</v>
       </c>
-      <c r="L53" s="28">
+      <c r="L53" s="34">
         <f t="shared" ref="L53:L55" si="7" xml:space="preserve">L52</f>
         <v>0</v>
       </c>
-      <c r="M53" s="28">
+      <c r="M53" s="34">
         <v>5</v>
       </c>
-      <c r="N53" s="28"/>
+      <c r="N53" s="34"/>
     </row>
     <row r="54" spans="4:14">
-      <c r="D54" s="28" t="s">
+      <c r="D54" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="E54" s="28"/>
-      <c r="F54" s="37" t="s">
+      <c r="E54" s="34"/>
+      <c r="F54" s="43" t="s">
         <v>148</v>
       </c>
-      <c r="G54" s="28" t="s">
+      <c r="G54" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="H54" s="34" t="s">
+      <c r="H54" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="I54" s="28" t="s">
+      <c r="I54" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="J54" s="28">
+      <c r="J54" s="34">
         <v>1</v>
       </c>
-      <c r="K54" s="28">
+      <c r="K54" s="34">
         <v>1</v>
       </c>
-      <c r="L54" s="28">
+      <c r="L54" s="34">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M54" s="28">
+      <c r="M54" s="34">
         <v>5</v>
       </c>
-      <c r="N54" s="28"/>
+      <c r="N54" s="34"/>
     </row>
     <row r="55" ht="16" spans="4:14">
-      <c r="D55" s="28" t="s">
+      <c r="D55" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="E55" s="28"/>
-      <c r="F55" s="29" t="s">
+      <c r="E55" s="34"/>
+      <c r="F55" s="35" t="s">
         <v>151</v>
       </c>
-      <c r="G55" s="28" t="s">
+      <c r="G55" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="H55" s="34" t="s">
+      <c r="H55" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="I55" s="28" t="s">
+      <c r="I55" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="J55" s="28">
+      <c r="J55" s="34">
         <v>1</v>
       </c>
-      <c r="K55" s="28">
+      <c r="K55" s="34">
         <v>1</v>
       </c>
-      <c r="L55" s="28">
+      <c r="L55" s="34">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M55" s="28">
+      <c r="M55" s="34">
         <v>5</v>
       </c>
-      <c r="N55" s="28"/>
+      <c r="N55" s="34"/>
     </row>
     <row r="56" ht="16" spans="4:14">
-      <c r="D56" s="28"/>
-      <c r="E56" s="28"/>
-      <c r="F56" s="29"/>
-      <c r="G56" s="28"/>
-      <c r="H56" s="34"/>
-      <c r="I56" s="28"/>
-      <c r="J56" s="28"/>
-      <c r="K56" s="28"/>
-      <c r="L56" s="28"/>
-      <c r="M56" s="28"/>
-      <c r="N56" s="28"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="34"/>
+      <c r="F56" s="35"/>
+      <c r="G56" s="34"/>
+      <c r="H56" s="40"/>
+      <c r="I56" s="34"/>
+      <c r="J56" s="34"/>
+      <c r="K56" s="34"/>
+      <c r="L56" s="34"/>
+      <c r="M56" s="34"/>
+      <c r="N56" s="34"/>
     </row>
     <row r="57" ht="16" spans="4:14">
-      <c r="D57" s="28"/>
-      <c r="E57" s="28"/>
-      <c r="F57" s="29"/>
-      <c r="G57" s="28"/>
-      <c r="H57" s="28"/>
-      <c r="I57" s="28"/>
-      <c r="J57" s="28"/>
-      <c r="K57" s="28"/>
-      <c r="L57" s="28"/>
-      <c r="M57" s="28"/>
-      <c r="N57" s="28"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="34"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="34"/>
+      <c r="H57" s="34"/>
+      <c r="I57" s="34"/>
+      <c r="J57" s="34"/>
+      <c r="K57" s="34"/>
+      <c r="L57" s="34"/>
+      <c r="M57" s="34"/>
+      <c r="N57" s="34"/>
     </row>
     <row r="58" ht="16" spans="4:14">
-      <c r="D58" s="28"/>
-      <c r="E58" s="28"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="28"/>
-      <c r="H58" s="28"/>
-      <c r="I58" s="28"/>
-      <c r="J58" s="28"/>
-      <c r="K58" s="28"/>
-      <c r="L58" s="28"/>
-      <c r="M58" s="28"/>
-      <c r="N58" s="28"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="34"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="34"/>
+      <c r="H58" s="34"/>
+      <c r="I58" s="34"/>
+      <c r="J58" s="34"/>
+      <c r="K58" s="34"/>
+      <c r="L58" s="34"/>
+      <c r="M58" s="34"/>
+      <c r="N58" s="34"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4915,26 +5001,26 @@
       </c>
     </row>
     <row r="11" spans="6:18">
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
     </row>
     <row r="12" spans="6:18">
-      <c r="K12" s="5"/>
-      <c r="L12" s="5" t="s">
+      <c r="K12" s="1"/>
+      <c r="L12" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
     </row>
     <row r="13" spans="6:18">
       <c r="F13" t="s">
@@ -4952,28 +5038,28 @@
       <c r="J13" t="s">
         <v>33</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="L13" s="5" t="s">
+      <c r="L13" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M13" s="5" t="s">
+      <c r="M13" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="N13" s="5" t="s">
+      <c r="N13" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="O13" s="5" t="s">
+      <c r="O13" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="P13" s="5" t="s">
+      <c r="P13" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="Q13" s="5" t="s">
+      <c r="Q13" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="R13" s="5"/>
+      <c r="R13" s="1"/>
     </row>
     <row r="14" spans="6:18">
       <c r="F14" t="s">
@@ -4982,147 +5068,147 @@
       <c r="H14" t="s">
         <v>154</v>
       </c>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5">
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1">
         <v>0.25</v>
       </c>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5">
+      <c r="N14" s="1"/>
+      <c r="O14" s="1">
         <v>0</v>
       </c>
-      <c r="P14" s="5">
+      <c r="P14" s="1">
         <v>5</v>
       </c>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
     </row>
     <row r="15" spans="6:18">
       <c r="H15" t="s">
         <v>155</v>
       </c>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5">
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1">
         <v>-1</v>
       </c>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
     </row>
     <row r="16" spans="6:18">
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
     </row>
     <row r="17" spans="6:18">
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
     </row>
     <row r="18" spans="6:18">
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
     </row>
     <row r="19" spans="6:18">
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
     </row>
     <row r="20" spans="6:18">
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
     </row>
     <row r="21" spans="6:18">
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
     </row>
     <row r="22" spans="6:18">
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
     </row>
     <row r="23" spans="6:18">
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
     </row>
     <row r="24" spans="6:18">
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
     </row>
     <row r="25" spans="6:18">
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
     </row>
     <row r="26" spans="6:18">
-      <c r="K26" s="5"/>
-      <c r="L26" s="5" t="s">
+      <c r="K26" s="1"/>
+      <c r="L26" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
     </row>
     <row r="27" spans="6:18">
       <c r="F27" t="s">
@@ -5140,126 +5226,126 @@
       <c r="J27" t="s">
         <v>33</v>
       </c>
-      <c r="K27" s="5" t="s">
+      <c r="K27" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="L27" s="5" t="s">
+      <c r="L27" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M27" s="5" t="s">
+      <c r="M27" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="N27" s="5" t="s">
+      <c r="N27" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="O27" s="5" t="s">
+      <c r="O27" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="P27" s="5" t="s">
+      <c r="P27" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="Q27" s="5" t="s">
+      <c r="Q27" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="R27" s="5"/>
+      <c r="R27" s="1"/>
     </row>
     <row r="28" ht="16" spans="6:18">
       <c r="F28" t="s">
         <v>156</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="H28" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5">
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1">
         <v>-0.1</v>
       </c>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5">
+      <c r="N28" s="1"/>
+      <c r="O28" s="1">
         <v>0</v>
       </c>
-      <c r="P28" s="5">
+      <c r="P28" s="1">
         <v>5</v>
       </c>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
     </row>
     <row r="29" spans="6:18">
       <c r="H29" t="s">
         <v>158</v>
       </c>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5">
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1">
         <v>1</v>
       </c>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
-      <c r="R29" s="5"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
     </row>
     <row r="30" spans="6:18">
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
-      <c r="Q30" s="5"/>
-      <c r="R30" s="5"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
     </row>
     <row r="31" spans="6:18">
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
-      <c r="R31" s="5"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
     </row>
     <row r="32" spans="6:18">
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5"/>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="5"/>
-      <c r="R32" s="5"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
     </row>
     <row r="33" spans="6:18">
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
-      <c r="R33" s="5"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
     </row>
     <row r="34" spans="6:18">
-      <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="5"/>
-      <c r="R34" s="5"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
     </row>
     <row r="35" spans="6:18">
-      <c r="K35" s="5"/>
-      <c r="L35" s="5" t="s">
+      <c r="K35" s="1"/>
+      <c r="L35" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="5"/>
-      <c r="P35" s="5"/>
-      <c r="Q35" s="5"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
     </row>
     <row r="36" spans="6:18">
       <c r="F36" t="s">
@@ -5277,25 +5363,25 @@
       <c r="J36" t="s">
         <v>33</v>
       </c>
-      <c r="K36" s="5" t="s">
+      <c r="K36" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="5" t="s">
+      <c r="L36" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M36" s="5" t="s">
+      <c r="M36" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="N36" s="5" t="s">
+      <c r="N36" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="O36" s="5" t="s">
+      <c r="O36" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="P36" s="5" t="s">
+      <c r="P36" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="Q36" s="5" t="s">
+      <c r="Q36" s="1" t="s">
         <v>66</v>
       </c>
     </row>
@@ -5306,550 +5392,550 @@
       <c r="H37" t="s">
         <v>160</v>
       </c>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5">
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1">
         <v>-0.1</v>
       </c>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5">
+      <c r="N37" s="1"/>
+      <c r="O37" s="1">
         <v>0</v>
       </c>
-      <c r="P37" s="5">
+      <c r="P37" s="1">
         <v>5</v>
       </c>
-      <c r="Q37" s="5"/>
+      <c r="Q37" s="1"/>
     </row>
     <row r="38" spans="6:18">
       <c r="H38" t="s">
         <v>161</v>
       </c>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5">
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1">
         <v>1</v>
       </c>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
     </row>
     <row r="51" spans="6:44">
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="8" t="s">
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="J51" s="9"/>
-      <c r="K51" s="9"/>
-      <c r="L51" s="9"/>
-      <c r="M51" s="9"/>
-      <c r="N51" s="9"/>
-      <c r="O51" s="9"/>
-      <c r="P51" s="9"/>
-      <c r="Q51" s="9"/>
-      <c r="R51" s="10"/>
-      <c r="S51" s="10"/>
-      <c r="T51" s="10"/>
-      <c r="U51" s="10"/>
-      <c r="V51" s="10"/>
-      <c r="W51" s="10"/>
-      <c r="X51" s="10"/>
-      <c r="Y51" s="10"/>
-      <c r="Z51" s="10"/>
-      <c r="AA51" s="10"/>
-      <c r="AB51" s="10"/>
-      <c r="AC51" s="10"/>
-      <c r="AD51" s="10"/>
-      <c r="AE51" s="10"/>
-      <c r="AF51" s="10"/>
-      <c r="AG51" s="10"/>
-      <c r="AH51" s="10"/>
-      <c r="AI51" s="10"/>
-      <c r="AJ51" s="10"/>
-      <c r="AK51" s="10"/>
-      <c r="AL51" s="10"/>
-      <c r="AM51" s="10"/>
+      <c r="J51" s="15"/>
+      <c r="K51" s="15"/>
+      <c r="L51" s="15"/>
+      <c r="M51" s="15"/>
+      <c r="N51" s="15"/>
+      <c r="O51" s="15"/>
+      <c r="P51" s="15"/>
+      <c r="Q51" s="15"/>
+      <c r="R51" s="16"/>
+      <c r="S51" s="16"/>
+      <c r="T51" s="16"/>
+      <c r="U51" s="16"/>
+      <c r="V51" s="16"/>
+      <c r="W51" s="16"/>
+      <c r="X51" s="16"/>
+      <c r="Y51" s="16"/>
+      <c r="Z51" s="16"/>
+      <c r="AA51" s="16"/>
+      <c r="AB51" s="16"/>
+      <c r="AC51" s="16"/>
+      <c r="AD51" s="16"/>
+      <c r="AE51" s="16"/>
+      <c r="AF51" s="16"/>
+      <c r="AG51" s="16"/>
+      <c r="AH51" s="16"/>
+      <c r="AI51" s="16"/>
+      <c r="AJ51" s="16"/>
+      <c r="AK51" s="16"/>
+      <c r="AL51" s="16"/>
+      <c r="AM51" s="16"/>
     </row>
     <row r="52" spans="6:44">
-      <c r="G52" s="7" t="s">
+      <c r="G52" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="H52" s="7" t="s">
+      <c r="H52" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="I52" s="11" t="s">
+      <c r="I52" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="J52" s="9" t="s">
+      <c r="J52" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="K52" s="7" t="s">
+      <c r="K52" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="L52" s="7" t="s">
+      <c r="L52" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="M52" s="9" t="s">
+      <c r="M52" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N52" s="7" t="s">
+      <c r="N52" s="13" t="s">
         <v>61</v>
       </c>
       <c r="O52" t="s">
         <v>62</v>
       </c>
-      <c r="P52" s="5" t="s">
+      <c r="P52" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="Q52" s="5" t="s">
+      <c r="Q52" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="T52" s="10"/>
-      <c r="U52" s="10"/>
-      <c r="V52" s="10"/>
-      <c r="W52" s="10"/>
-      <c r="X52" s="10"/>
-      <c r="Y52" s="10"/>
-      <c r="Z52" s="10"/>
-      <c r="AA52" s="10"/>
-      <c r="AB52" s="10"/>
-      <c r="AC52" s="10"/>
-      <c r="AD52" s="10"/>
-      <c r="AE52" s="10"/>
-      <c r="AF52" s="10"/>
-      <c r="AG52" s="10"/>
-      <c r="AH52" s="10"/>
-      <c r="AI52" s="10"/>
-      <c r="AJ52" s="10"/>
-      <c r="AK52" s="10"/>
-      <c r="AL52" s="10"/>
-      <c r="AM52" s="10"/>
-      <c r="AN52" s="10"/>
-      <c r="AO52" s="10"/>
-      <c r="AP52" s="10"/>
-      <c r="AQ52" s="10"/>
-      <c r="AR52" s="10"/>
+      <c r="T52" s="16"/>
+      <c r="U52" s="16"/>
+      <c r="V52" s="16"/>
+      <c r="W52" s="16"/>
+      <c r="X52" s="16"/>
+      <c r="Y52" s="16"/>
+      <c r="Z52" s="16"/>
+      <c r="AA52" s="16"/>
+      <c r="AB52" s="16"/>
+      <c r="AC52" s="16"/>
+      <c r="AD52" s="16"/>
+      <c r="AE52" s="16"/>
+      <c r="AF52" s="16"/>
+      <c r="AG52" s="16"/>
+      <c r="AH52" s="16"/>
+      <c r="AI52" s="16"/>
+      <c r="AJ52" s="16"/>
+      <c r="AK52" s="16"/>
+      <c r="AL52" s="16"/>
+      <c r="AM52" s="16"/>
+      <c r="AN52" s="16"/>
+      <c r="AO52" s="16"/>
+      <c r="AP52" s="16"/>
+      <c r="AQ52" s="16"/>
+      <c r="AR52" s="16"/>
     </row>
     <row r="53" ht="16" spans="6:44">
-      <c r="F53" s="12"/>
-      <c r="G53" s="7" t="s">
+      <c r="F53" s="18"/>
+      <c r="G53" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="H53" s="7" t="s">
+      <c r="H53" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="I53" s="13">
+      <c r="I53" s="19">
         <v>2019</v>
       </c>
-      <c r="J53" s="14">
+      <c r="J53" s="20">
         <v>-1</v>
       </c>
-      <c r="K53" s="7"/>
-      <c r="L53" s="6" t="s">
+      <c r="K53" s="13"/>
+      <c r="L53" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="M53" s="15" t="s">
+      <c r="M53" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="N53" s="6" t="s">
+      <c r="N53" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="O53" s="7">
+      <c r="O53" s="13">
         <v>10</v>
       </c>
-      <c r="P53" s="5">
+      <c r="P53" s="1">
         <v>0</v>
       </c>
-      <c r="Q53" s="5">
+      <c r="Q53" s="1">
         <v>3</v>
       </c>
-      <c r="T53" s="10"/>
-      <c r="U53" s="10"/>
-      <c r="V53" s="10"/>
-      <c r="W53" s="10"/>
-      <c r="X53" s="10"/>
-      <c r="Y53" s="10"/>
-      <c r="Z53" s="10"/>
-      <c r="AA53" s="10"/>
-      <c r="AB53" s="10"/>
-      <c r="AC53" s="10"/>
-      <c r="AD53" s="10"/>
-      <c r="AE53" s="10"/>
-      <c r="AF53" s="10"/>
-      <c r="AG53" s="10"/>
-      <c r="AH53" s="10"/>
-      <c r="AI53" s="10"/>
-      <c r="AJ53" s="10"/>
-      <c r="AK53" s="10"/>
-      <c r="AL53" s="10"/>
-      <c r="AM53" s="10"/>
-      <c r="AN53" s="10"/>
-      <c r="AO53" s="10"/>
-      <c r="AP53" s="10"/>
-      <c r="AQ53" s="10"/>
-      <c r="AR53" s="10"/>
+      <c r="T53" s="16"/>
+      <c r="U53" s="16"/>
+      <c r="V53" s="16"/>
+      <c r="W53" s="16"/>
+      <c r="X53" s="16"/>
+      <c r="Y53" s="16"/>
+      <c r="Z53" s="16"/>
+      <c r="AA53" s="16"/>
+      <c r="AB53" s="16"/>
+      <c r="AC53" s="16"/>
+      <c r="AD53" s="16"/>
+      <c r="AE53" s="16"/>
+      <c r="AF53" s="16"/>
+      <c r="AG53" s="16"/>
+      <c r="AH53" s="16"/>
+      <c r="AI53" s="16"/>
+      <c r="AJ53" s="16"/>
+      <c r="AK53" s="16"/>
+      <c r="AL53" s="16"/>
+      <c r="AM53" s="16"/>
+      <c r="AN53" s="16"/>
+      <c r="AO53" s="16"/>
+      <c r="AP53" s="16"/>
+      <c r="AQ53" s="16"/>
+      <c r="AR53" s="16"/>
     </row>
     <row r="54" spans="6:44">
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
-      <c r="K54" s="7"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="K54" s="13"/>
     </row>
     <row r="55" spans="6:44">
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
-      <c r="K55" s="7"/>
-      <c r="L55" s="7"/>
-      <c r="M55" s="7"/>
-      <c r="N55" s="7"/>
-      <c r="O55" s="7"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="K55" s="13"/>
+      <c r="L55" s="13"/>
+      <c r="M55" s="13"/>
+      <c r="N55" s="13"/>
+      <c r="O55" s="13"/>
     </row>
     <row r="56" spans="6:44">
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="7"/>
-      <c r="K56" s="7"/>
-      <c r="L56" s="7"/>
-      <c r="M56" s="7"/>
-      <c r="N56" s="7"/>
-      <c r="O56" s="7"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="K56" s="13"/>
+      <c r="L56" s="13"/>
+      <c r="M56" s="13"/>
+      <c r="N56" s="13"/>
+      <c r="O56" s="13"/>
     </row>
     <row r="61" spans="6:44">
-      <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
-      <c r="I61" s="8" t="s">
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="J61" s="9"/>
-      <c r="K61" s="9"/>
-      <c r="L61" s="9"/>
-      <c r="M61" s="9"/>
-      <c r="N61" s="9"/>
-      <c r="O61" s="9"/>
-      <c r="P61" s="10"/>
-      <c r="Q61" s="10"/>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15"/>
+      <c r="L61" s="15"/>
+      <c r="M61" s="15"/>
+      <c r="N61" s="15"/>
+      <c r="O61" s="15"/>
+      <c r="P61" s="16"/>
+      <c r="Q61" s="16"/>
     </row>
     <row r="62" spans="6:44">
-      <c r="G62" s="7" t="s">
+      <c r="G62" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="H62" s="7" t="s">
+      <c r="H62" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="I62" s="11" t="s">
+      <c r="I62" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="J62" s="9" t="s">
+      <c r="J62" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="K62" s="7" t="s">
+      <c r="K62" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="L62" s="7" t="s">
+      <c r="L62" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="M62" s="9" t="s">
+      <c r="M62" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N62" s="7" t="s">
+      <c r="N62" s="13" t="s">
         <v>61</v>
       </c>
       <c r="O62" t="s">
         <v>62</v>
       </c>
-      <c r="P62" s="5" t="s">
+      <c r="P62" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="Q62" s="5" t="s">
+      <c r="Q62" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="63" ht="16" spans="6:44">
-      <c r="G63" s="7" t="s">
+      <c r="G63" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="H63" s="7" t="s">
+      <c r="H63" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="I63" s="13">
+      <c r="I63" s="19">
         <v>2019</v>
       </c>
-      <c r="J63" s="14">
+      <c r="J63" s="20">
         <v>-1</v>
       </c>
-      <c r="K63" s="7"/>
-      <c r="L63" s="6" t="s">
+      <c r="K63" s="13"/>
+      <c r="L63" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="M63" s="15" t="s">
+      <c r="M63" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="N63" s="6" t="s">
+      <c r="N63" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="O63" s="7">
+      <c r="O63" s="13">
         <v>10</v>
       </c>
-      <c r="P63" s="5">
+      <c r="P63" s="1">
         <v>0</v>
       </c>
-      <c r="Q63" s="5">
+      <c r="Q63" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="64" spans="6:44">
-      <c r="G64" s="7"/>
-      <c r="H64" s="7"/>
-      <c r="I64" s="7"/>
-      <c r="J64" s="7"/>
-      <c r="K64" s="7"/>
+      <c r="G64" s="13"/>
+      <c r="H64" s="13"/>
+      <c r="I64" s="13"/>
+      <c r="J64" s="13"/>
+      <c r="K64" s="13"/>
     </row>
     <row r="66" ht="15.25" spans="7:20">
-      <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="5"/>
-      <c r="K66" s="5"/>
-      <c r="L66" s="5"/>
-      <c r="M66" s="5"/>
-      <c r="N66" s="5"/>
-      <c r="O66" s="5"/>
-      <c r="P66" s="5"/>
-      <c r="Q66" s="5"/>
-      <c r="T66" s="5"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
+      <c r="P66" s="1"/>
+      <c r="Q66" s="1"/>
+      <c r="T66" s="1"/>
     </row>
     <row r="67" ht="16" spans="7:20">
-      <c r="G67" s="5"/>
-      <c r="H67" s="5"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="5"/>
-      <c r="K67" s="5"/>
-      <c r="L67" s="5"/>
-      <c r="M67" s="5"/>
-      <c r="O67" s="5"/>
-      <c r="P67" s="5"/>
-      <c r="Q67" s="5"/>
-      <c r="T67" s="5"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="O67" s="1"/>
+      <c r="P67" s="1"/>
+      <c r="Q67" s="1"/>
+      <c r="T67" s="1"/>
     </row>
     <row r="68" ht="15.25" spans="7:20">
-      <c r="G68" s="5"/>
-      <c r="H68" s="5"/>
-      <c r="I68" s="5"/>
-      <c r="J68" s="5"/>
-      <c r="K68" s="5"/>
-      <c r="L68" s="5"/>
-      <c r="M68" s="5"/>
-      <c r="N68" s="5"/>
-      <c r="O68" s="5"/>
-      <c r="P68" s="5"/>
-      <c r="Q68" s="5"/>
-      <c r="T68" s="5"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+      <c r="N68" s="1"/>
+      <c r="O68" s="1"/>
+      <c r="P68" s="1"/>
+      <c r="Q68" s="1"/>
+      <c r="T68" s="1"/>
     </row>
     <row r="69" spans="7:20">
-      <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
-      <c r="I69" s="5"/>
-      <c r="J69" s="5"/>
-      <c r="K69" s="5"/>
-      <c r="L69" s="5"/>
-      <c r="M69" s="5"/>
-      <c r="N69" s="5"/>
-      <c r="O69" s="5"/>
-      <c r="P69" s="5"/>
-      <c r="Q69" s="5"/>
-      <c r="T69" s="5"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1"/>
+      <c r="O69" s="1"/>
+      <c r="P69" s="1"/>
+      <c r="Q69" s="1"/>
+      <c r="T69" s="1"/>
     </row>
     <row r="70" spans="7:20">
-      <c r="G70" s="16"/>
-      <c r="H70" s="16"/>
-      <c r="I70" s="17" t="s">
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="J70" s="18"/>
-      <c r="K70" s="18"/>
-      <c r="L70" s="18"/>
-      <c r="M70" s="18"/>
-      <c r="N70" s="18"/>
-      <c r="O70" s="18"/>
-      <c r="P70" s="18"/>
-      <c r="Q70" s="18"/>
-      <c r="T70" s="5"/>
+      <c r="J70" s="24"/>
+      <c r="K70" s="24"/>
+      <c r="L70" s="24"/>
+      <c r="M70" s="24"/>
+      <c r="N70" s="24"/>
+      <c r="O70" s="24"/>
+      <c r="P70" s="24"/>
+      <c r="Q70" s="24"/>
+      <c r="T70" s="1"/>
     </row>
     <row r="71" spans="7:20">
-      <c r="G71" s="16" t="s">
+      <c r="G71" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="H71" s="16" t="s">
+      <c r="H71" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="I71" s="19" t="s">
+      <c r="I71" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="J71" s="18" t="s">
+      <c r="J71" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="K71" s="16" t="s">
+      <c r="K71" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="L71" s="16" t="s">
+      <c r="L71" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="M71" s="18" t="s">
+      <c r="M71" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="N71" s="16" t="s">
+      <c r="N71" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="O71" s="16" t="s">
+      <c r="O71" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="P71" s="16" t="s">
+      <c r="P71" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="Q71" s="16" t="s">
+      <c r="Q71" s="22" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="72" ht="16" spans="7:20">
-      <c r="G72" s="16" t="s">
+      <c r="G72" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="H72" s="16" t="s">
+      <c r="H72" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="I72" s="20">
+      <c r="I72" s="26">
         <v>2019</v>
       </c>
-      <c r="J72" s="21">
+      <c r="J72" s="27">
         <v>-1</v>
       </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="22" t="s">
+      <c r="K72" s="22"/>
+      <c r="L72" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="M72" s="22" t="s">
+      <c r="M72" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="N72" s="22" t="s">
+      <c r="N72" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="O72" s="16">
+      <c r="O72" s="22">
         <v>10</v>
       </c>
-      <c r="P72" s="16">
+      <c r="P72" s="22">
         <v>0</v>
       </c>
-      <c r="Q72" s="16">
+      <c r="Q72" s="22">
         <v>3</v>
       </c>
     </row>
     <row r="73" spans="7:20">
-      <c r="G73" s="16"/>
-      <c r="H73" s="16"/>
-      <c r="I73" s="16"/>
-      <c r="J73" s="16"/>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
-      <c r="N73" s="16"/>
-      <c r="O73" s="16"/>
-      <c r="P73" s="16"/>
-      <c r="Q73" s="16"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="22"/>
+      <c r="J73" s="22"/>
+      <c r="K73" s="22"/>
+      <c r="L73" s="22"/>
+      <c r="M73" s="22"/>
+      <c r="N73" s="22"/>
+      <c r="O73" s="22"/>
+      <c r="P73" s="22"/>
+      <c r="Q73" s="22"/>
     </row>
     <row r="80" spans="7:20">
-      <c r="G80" s="7"/>
-      <c r="H80" s="7"/>
-      <c r="I80" s="8" t="s">
+      <c r="G80" s="13"/>
+      <c r="H80" s="13"/>
+      <c r="I80" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="J80" s="9"/>
-      <c r="K80" s="9"/>
-      <c r="L80" s="9"/>
-      <c r="M80" s="9"/>
-      <c r="N80" s="9"/>
-      <c r="O80" s="9"/>
-      <c r="P80" s="10"/>
-      <c r="Q80" s="10"/>
+      <c r="J80" s="15"/>
+      <c r="K80" s="15"/>
+      <c r="L80" s="15"/>
+      <c r="M80" s="15"/>
+      <c r="N80" s="15"/>
+      <c r="O80" s="15"/>
+      <c r="P80" s="16"/>
+      <c r="Q80" s="16"/>
     </row>
     <row r="81" spans="7:17">
-      <c r="G81" s="7" t="s">
+      <c r="G81" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="H81" s="7" t="s">
+      <c r="H81" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="I81" s="11" t="s">
+      <c r="I81" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="J81" s="9" t="s">
+      <c r="J81" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="K81" s="7" t="s">
+      <c r="K81" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="L81" s="7" t="s">
+      <c r="L81" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="M81" s="9" t="s">
+      <c r="M81" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N81" s="7" t="s">
+      <c r="N81" s="13" t="s">
         <v>61</v>
       </c>
       <c r="O81" t="s">
         <v>62</v>
       </c>
-      <c r="P81" s="5" t="s">
+      <c r="P81" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="Q81" s="5" t="s">
+      <c r="Q81" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="82" ht="16" spans="7:17">
-      <c r="G82" s="7" t="s">
+      <c r="G82" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="H82" s="7" t="s">
+      <c r="H82" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="I82" s="13">
+      <c r="I82" s="19">
         <v>2019</v>
       </c>
-      <c r="J82" s="14">
+      <c r="J82" s="20">
         <v>-1</v>
       </c>
-      <c r="K82" s="7"/>
-      <c r="L82" s="6" t="s">
+      <c r="K82" s="13"/>
+      <c r="L82" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="M82" s="15" t="s">
+      <c r="M82" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="N82" s="6" t="s">
+      <c r="N82" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="O82" s="7">
+      <c r="O82" s="13">
         <v>10</v>
       </c>
-      <c r="P82" s="5">
+      <c r="P82" s="1">
         <v>0</v>
       </c>
-      <c r="Q82" s="5">
+      <c r="Q82" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="83" spans="7:17">
-      <c r="G83" s="7"/>
-      <c r="H83" s="7"/>
-      <c r="I83" s="7"/>
-      <c r="J83" s="7"/>
-      <c r="K83" s="7"/>
+      <c r="G83" s="13"/>
+      <c r="H83" s="13"/>
+      <c r="I83" s="13"/>
+      <c r="J83" s="13"/>
+      <c r="K83" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5860,26 +5946,30 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:M26"/>
+  <dimension ref="B1:X87"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="25.0909090909091" customWidth="1"/>
-    <col min="4" max="4" width="34.4545454545455" customWidth="1"/>
+    <col min="4" max="4" width="51.9090909090909" customWidth="1"/>
     <col min="5" max="5" width="43.7272727272727" customWidth="1"/>
     <col min="7" max="7" width="11.1818181818182" customWidth="1"/>
     <col min="8" max="8" width="10.1818181818182" customWidth="1"/>
+    <col min="9" max="9" width="12.8181818181818"/>
     <col min="10" max="10" width="12.8181818181818" customWidth="1"/>
     <col min="11" max="11" width="11.3636363636364" customWidth="1"/>
     <col min="12" max="12" width="13.6363636363636" customWidth="1"/>
     <col min="13" max="13" width="56.8181818181818" customWidth="1"/>
+    <col min="14" max="23" width="12.8181818181818"/>
   </cols>
   <sheetData>
+    <row r="1" customHeight="1"/>
     <row r="2" spans="2:13">
       <c r="B2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="3" customHeight="1"/>
+    <row r="4" customHeight="1" spans="2:13">
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -5890,11 +5980,11 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" customHeight="1" spans="2:13">
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I5" s="1"/>
@@ -5903,7 +5993,7 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" ht="15.25" spans="2:13">
+    <row r="6" ht="16" customHeight="1" spans="2:13">
       <c r="B6" t="s">
         <v>59</v>
       </c>
@@ -5941,14 +6031,14 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" ht="16" spans="2:13">
+    <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>175</v>
       </c>
       <c r="C7" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E7" s="1"/>
@@ -5998,21 +6088,49 @@
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="2:13">
-      <c r="E9" s="1"/>
+      <c r="C9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="F9" s="1"/>
-      <c r="G9"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="2"/>
+      <c r="G9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="1">
+        <v>-1.05</v>
+      </c>
+      <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="2:13">
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+      <c r="C10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -6045,7 +6163,7 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="2"/>
+      <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -6070,8 +6188,8 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
-      <c r="M15" s="4" t="s">
-        <v>178</v>
+      <c r="M15" s="3" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="2:13">
@@ -6120,7 +6238,7 @@
     </row>
     <row r="23" spans="5:13">
       <c r="G23" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1">
@@ -6136,7 +6254,7 @@
         <v>14</v>
       </c>
       <c r="I24" s="1"/>
-      <c r="J24" s="2">
+      <c r="J24" s="1">
         <v>1.5</v>
       </c>
       <c r="K24" s="1"/>
@@ -6155,7 +6273,1317 @@
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
     </row>
+    <row r="44" ht="15.25"/>
+    <row r="45" ht="15.25" spans="7:23">
+      <c r="G45" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="4">
+        <v>2019</v>
+      </c>
+      <c r="J45" s="4">
+        <v>2020</v>
+      </c>
+      <c r="K45" s="4">
+        <v>2025</v>
+      </c>
+      <c r="L45" s="4">
+        <v>2030</v>
+      </c>
+      <c r="M45" s="4">
+        <v>2035</v>
+      </c>
+      <c r="N45" s="4">
+        <v>2040</v>
+      </c>
+      <c r="O45" s="4">
+        <v>2050</v>
+      </c>
+      <c r="P45" s="4">
+        <v>2060</v>
+      </c>
+      <c r="Q45" s="4">
+        <v>2070</v>
+      </c>
+      <c r="R45" s="4">
+        <v>2080</v>
+      </c>
+      <c r="S45" s="4">
+        <v>2090</v>
+      </c>
+      <c r="T45" s="4">
+        <v>2100</v>
+      </c>
+      <c r="U45" s="4">
+        <v>2110</v>
+      </c>
+      <c r="V45" s="4">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="46" ht="15.25" spans="7:23">
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="5"/>
+      <c r="R46" s="5"/>
+      <c r="S46" s="5"/>
+      <c r="T46" s="5"/>
+      <c r="U46" s="5"/>
+      <c r="V46" s="5"/>
+      <c r="W46" s="5"/>
+    </row>
+    <row r="47" ht="15.25" spans="7:23">
+      <c r="G47" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I47" s="7">
+        <v>23147.55</v>
+      </c>
+      <c r="J47" s="7">
+        <v>24048.86</v>
+      </c>
+      <c r="K47" s="7">
+        <v>25614.9</v>
+      </c>
+      <c r="L47" s="7">
+        <v>26682.27</v>
+      </c>
+      <c r="M47" s="7">
+        <v>27327.39</v>
+      </c>
+      <c r="N47" s="7">
+        <v>29455.19</v>
+      </c>
+      <c r="O47" s="7">
+        <v>36120.9</v>
+      </c>
+      <c r="P47" s="7">
+        <v>37765.053</v>
+      </c>
+      <c r="Q47" s="7">
+        <v>39347.27</v>
+      </c>
+      <c r="R47" s="7">
+        <v>40254.43</v>
+      </c>
+      <c r="S47" s="7">
+        <v>41140.93</v>
+      </c>
+      <c r="T47" s="7">
+        <v>41608.6</v>
+      </c>
+      <c r="U47" s="7">
+        <v>41639.07</v>
+      </c>
+      <c r="V47" s="7">
+        <v>41578.8</v>
+      </c>
+      <c r="W47" s="8"/>
+    </row>
+    <row r="48" ht="15.25" spans="7:23">
+      <c r="G48" s="6"/>
+      <c r="H48" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="I48" s="7">
+        <v>25707.66</v>
+      </c>
+      <c r="J48" s="7">
+        <v>26708.54</v>
+      </c>
+      <c r="K48" s="7">
+        <v>28281.61</v>
+      </c>
+      <c r="L48" s="7">
+        <v>29288.31</v>
+      </c>
+      <c r="M48" s="7">
+        <v>29823.36</v>
+      </c>
+      <c r="N48" s="7">
+        <v>31961.62</v>
+      </c>
+      <c r="O48" s="7">
+        <v>38751.23</v>
+      </c>
+      <c r="P48" s="7">
+        <v>40061.58</v>
+      </c>
+      <c r="Q48" s="7">
+        <v>41281.95</v>
+      </c>
+      <c r="R48" s="7">
+        <v>42233.66</v>
+      </c>
+      <c r="S48" s="7">
+        <v>43166.25</v>
+      </c>
+      <c r="T48" s="7">
+        <v>43657.5</v>
+      </c>
+      <c r="U48" s="7">
+        <v>43687.063</v>
+      </c>
+      <c r="V48" s="7">
+        <v>43626.04</v>
+      </c>
+      <c r="W48" s="8"/>
+    </row>
+    <row r="49" ht="15.25" spans="7:23">
+      <c r="G49" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I49" s="7">
+        <v>17208.23</v>
+      </c>
+      <c r="J49" s="7">
+        <v>17167.02</v>
+      </c>
+      <c r="K49" s="7">
+        <v>17588.94</v>
+      </c>
+      <c r="L49" s="7">
+        <v>17552.39</v>
+      </c>
+      <c r="M49" s="7">
+        <v>17929.042</v>
+      </c>
+      <c r="N49" s="7">
+        <v>21788.048</v>
+      </c>
+      <c r="O49" s="7">
+        <v>37977.74</v>
+      </c>
+      <c r="P49" s="7">
+        <v>41150.28</v>
+      </c>
+      <c r="Q49" s="7">
+        <v>44299.82</v>
+      </c>
+      <c r="R49" s="7">
+        <v>46519.5</v>
+      </c>
+      <c r="S49" s="7">
+        <v>48652.58</v>
+      </c>
+      <c r="T49" s="7">
+        <v>50075.57</v>
+      </c>
+      <c r="U49" s="7">
+        <v>50118.11</v>
+      </c>
+      <c r="V49" s="7">
+        <v>50033.62</v>
+      </c>
+      <c r="W49" s="8"/>
+    </row>
+    <row r="50" ht="15.25" spans="7:23">
+      <c r="G50" s="6"/>
+      <c r="H50" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="I50" s="7">
+        <v>18874.63</v>
+      </c>
+      <c r="J50" s="7">
+        <v>18829.43</v>
+      </c>
+      <c r="K50" s="7">
+        <v>19204.8</v>
+      </c>
+      <c r="L50" s="7">
+        <v>19078.4</v>
+      </c>
+      <c r="M50" s="7">
+        <v>19400.24</v>
+      </c>
+      <c r="N50" s="7">
+        <v>23470.59</v>
+      </c>
+      <c r="O50" s="7">
+        <v>40548.24</v>
+      </c>
+      <c r="P50" s="7">
+        <v>43549.64</v>
+      </c>
+      <c r="Q50" s="7">
+        <v>46485.71</v>
+      </c>
+      <c r="R50" s="7">
+        <v>48816.36</v>
+      </c>
+      <c r="S50" s="7">
+        <v>51054.94</v>
+      </c>
+      <c r="T50" s="7">
+        <v>52548.3</v>
+      </c>
+      <c r="U50" s="7">
+        <v>52592.9</v>
+      </c>
+      <c r="V50" s="7">
+        <v>52504.13</v>
+      </c>
+      <c r="W50" s="8"/>
+    </row>
+    <row r="52" spans="7:23">
+      <c r="I52">
+        <f xml:space="preserve">(I48-I47)/I47</f>
+        <v>0.11059960989392</v>
+      </c>
+      <c r="J52">
+        <f xml:space="preserve">(J48-J47)/J47</f>
+        <v>0.110594847323324</v>
+      </c>
+      <c r="K52">
+        <f xml:space="preserve">(K48-K47)/K47</f>
+        <v>0.104107765402168</v>
+      </c>
+      <c r="L52">
+        <f xml:space="preserve">(L48-L47)/L47</f>
+        <v>0.0976693512208669</v>
+      </c>
+      <c r="M52">
+        <f xml:space="preserve">(M48-M47)/M47</f>
+        <v>0.0913358355847376</v>
+      </c>
+      <c r="N52">
+        <f t="shared" ref="N52:S52" si="0" xml:space="preserve">(N48-N47)/N47</f>
+        <v>0.0850929836134141</v>
+      </c>
+      <c r="O52">
+        <f t="shared" si="0"/>
+        <v>0.0728201678252757</v>
+      </c>
+      <c r="P52">
+        <f t="shared" si="0"/>
+        <v>0.0608109036680023</v>
+      </c>
+      <c r="Q52">
+        <f t="shared" si="0"/>
+        <v>0.0491693578741295</v>
+      </c>
+      <c r="R52">
+        <f t="shared" si="0"/>
+        <v>0.0491680046146475</v>
+      </c>
+      <c r="S52">
+        <f t="shared" si="0"/>
+        <v>0.0492288336700216</v>
+      </c>
+      <c r="T52">
+        <f xml:space="preserve">(T48-T47)/T47</f>
+        <v>0.0492422239633153</v>
+      </c>
+      <c r="U52">
+        <f xml:space="preserve">(U48-U47)/U47</f>
+        <v>0.0491844078169854</v>
+      </c>
+      <c r="V52">
+        <f xml:space="preserve">(V48-V47)/V47</f>
+        <v>0.0492375922345041</v>
+      </c>
+    </row>
+    <row r="54" ht="15.25"/>
+    <row r="55" ht="15.25" spans="7:23">
+      <c r="G55" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I55" s="4">
+        <v>2019</v>
+      </c>
+      <c r="J55" s="4">
+        <v>2020</v>
+      </c>
+      <c r="K55" s="4">
+        <v>2025</v>
+      </c>
+      <c r="L55" s="4">
+        <v>2030</v>
+      </c>
+      <c r="M55" s="4">
+        <v>2035</v>
+      </c>
+      <c r="N55" s="4">
+        <v>2040</v>
+      </c>
+      <c r="O55" s="4">
+        <v>2050</v>
+      </c>
+      <c r="P55" s="4">
+        <v>2060</v>
+      </c>
+      <c r="Q55" s="4">
+        <v>2070</v>
+      </c>
+      <c r="R55" s="4">
+        <v>2080</v>
+      </c>
+      <c r="S55" s="4">
+        <v>2090</v>
+      </c>
+      <c r="T55" s="4">
+        <v>2100</v>
+      </c>
+      <c r="U55" s="4">
+        <v>2110</v>
+      </c>
+      <c r="V55" s="4">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="56" ht="15.25" spans="7:23">
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5"/>
+      <c r="K56" s="5"/>
+      <c r="L56" s="5"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="5"/>
+      <c r="Q56" s="5"/>
+      <c r="R56" s="5"/>
+      <c r="S56" s="5"/>
+      <c r="T56" s="5"/>
+      <c r="U56" s="5"/>
+      <c r="V56" s="5"/>
+      <c r="W56" s="5"/>
+    </row>
+    <row r="57" ht="15.25" spans="7:23">
+      <c r="G57" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I57" s="7">
+        <v>23143.15</v>
+      </c>
+      <c r="J57" s="7">
+        <v>24043.23</v>
+      </c>
+      <c r="K57" s="7">
+        <v>25605.6</v>
+      </c>
+      <c r="L57" s="7">
+        <v>26661.51</v>
+      </c>
+      <c r="M57" s="7">
+        <v>27302.64</v>
+      </c>
+      <c r="N57" s="7">
+        <v>29430.44</v>
+      </c>
+      <c r="O57" s="7">
+        <v>36096.16</v>
+      </c>
+      <c r="P57" s="7">
+        <v>37740.31</v>
+      </c>
+      <c r="Q57" s="7">
+        <v>39322.52</v>
+      </c>
+      <c r="R57" s="7">
+        <v>40229.67</v>
+      </c>
+      <c r="S57" s="7">
+        <v>41116.14</v>
+      </c>
+      <c r="T57" s="7">
+        <v>41583.77</v>
+      </c>
+      <c r="U57" s="7">
+        <v>41614.22</v>
+      </c>
+      <c r="V57" s="7">
+        <v>41553.81</v>
+      </c>
+      <c r="W57" s="8"/>
+    </row>
+    <row r="58" ht="15.25" spans="7:23">
+      <c r="G58" s="6"/>
+      <c r="H58" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="I58" s="7">
+        <v>24300.3</v>
+      </c>
+      <c r="J58" s="7">
+        <v>25245.39</v>
+      </c>
+      <c r="K58" s="7">
+        <v>26885.88</v>
+      </c>
+      <c r="L58" s="7">
+        <v>27994.58</v>
+      </c>
+      <c r="M58" s="7">
+        <v>28667.77</v>
+      </c>
+      <c r="N58" s="7">
+        <v>30901.97</v>
+      </c>
+      <c r="O58" s="7">
+        <v>37900.97</v>
+      </c>
+      <c r="P58" s="7">
+        <v>39627.32</v>
+      </c>
+      <c r="Q58" s="7">
+        <v>41262.11</v>
+      </c>
+      <c r="R58" s="7">
+        <v>42213.82</v>
+      </c>
+      <c r="S58" s="7">
+        <v>43146.41</v>
+      </c>
+      <c r="T58" s="7">
+        <v>43637.66</v>
+      </c>
+      <c r="U58" s="7">
+        <v>43667.22</v>
+      </c>
+      <c r="V58" s="7">
+        <v>43606.2</v>
+      </c>
+      <c r="W58" s="8"/>
+    </row>
+    <row r="59" ht="15.25" spans="7:23">
+      <c r="G59" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I59" s="7">
+        <v>17204.75</v>
+      </c>
+      <c r="J59" s="7">
+        <v>17163.54</v>
+      </c>
+      <c r="K59" s="7">
+        <v>17585.44</v>
+      </c>
+      <c r="L59" s="7">
+        <v>17548.31</v>
+      </c>
+      <c r="M59" s="7">
+        <v>17924.42</v>
+      </c>
+      <c r="N59" s="7">
+        <v>21783.38</v>
+      </c>
+      <c r="O59" s="7">
+        <v>37973.078</v>
+      </c>
+      <c r="P59" s="7">
+        <v>41145.61</v>
+      </c>
+      <c r="Q59" s="7">
+        <v>44295.14</v>
+      </c>
+      <c r="R59" s="7">
+        <v>46514.82</v>
+      </c>
+      <c r="S59" s="7">
+        <v>48647.87</v>
+      </c>
+      <c r="T59" s="7">
+        <v>50070.83</v>
+      </c>
+      <c r="U59" s="7">
+        <v>50113.32</v>
+      </c>
+      <c r="V59" s="7">
+        <v>50028.74</v>
+      </c>
+      <c r="W59" s="8"/>
+    </row>
+    <row r="60" ht="15.25" spans="7:23">
+      <c r="G60" s="6"/>
+      <c r="H60" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="I60" s="7">
+        <v>18064.98</v>
+      </c>
+      <c r="J60" s="7">
+        <v>18021.71</v>
+      </c>
+      <c r="K60" s="7">
+        <v>18464.72</v>
+      </c>
+      <c r="L60" s="7">
+        <v>18425.72</v>
+      </c>
+      <c r="M60" s="7">
+        <v>18820.64</v>
+      </c>
+      <c r="N60" s="7">
+        <v>22872.55</v>
+      </c>
+      <c r="O60" s="7">
+        <v>39871.73</v>
+      </c>
+      <c r="P60" s="7">
+        <v>43202.89</v>
+      </c>
+      <c r="Q60" s="7">
+        <v>46481.91</v>
+      </c>
+      <c r="R60" s="7">
+        <v>48812.56</v>
+      </c>
+      <c r="S60" s="7">
+        <v>51051.14</v>
+      </c>
+      <c r="T60" s="7">
+        <v>52544.5</v>
+      </c>
+      <c r="U60" s="7">
+        <v>52589.1</v>
+      </c>
+      <c r="V60" s="7">
+        <v>52500.33</v>
+      </c>
+      <c r="W60" s="8"/>
+    </row>
+    <row r="62" spans="7:23">
+      <c r="I62">
+        <f xml:space="preserve">(I58-I57)/I57</f>
+        <v>0.0499996759300267</v>
+      </c>
+      <c r="J62">
+        <f xml:space="preserve">(J58-J57)/J57</f>
+        <v>0.0499999376123757</v>
+      </c>
+      <c r="K62">
+        <f xml:space="preserve">(K58-K57)/K57</f>
+        <v>0.0500000000000001</v>
+      </c>
+      <c r="L62">
+        <f xml:space="preserve">(L58-L57)/L57</f>
+        <v>0.0499997937101088</v>
+      </c>
+    </row>
+    <row r="65" ht="15.25"/>
+    <row r="66" ht="15.25" spans="7:24">
+      <c r="G66" s="8"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="4"/>
+      <c r="R66" s="4"/>
+      <c r="S66" s="4"/>
+      <c r="T66" s="4"/>
+      <c r="U66" s="4"/>
+      <c r="V66" s="4"/>
+      <c r="W66" s="4"/>
+      <c r="X66" s="4"/>
+    </row>
+    <row r="67" ht="15.25" spans="7:24">
+      <c r="G67" s="8"/>
+      <c r="H67" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J67" s="4">
+        <v>2019</v>
+      </c>
+      <c r="K67" s="4">
+        <v>2020</v>
+      </c>
+      <c r="L67" s="4">
+        <v>2025</v>
+      </c>
+      <c r="M67" s="4">
+        <v>2030</v>
+      </c>
+      <c r="N67" s="4">
+        <v>2035</v>
+      </c>
+      <c r="O67" s="4">
+        <v>2040</v>
+      </c>
+      <c r="P67" s="4">
+        <v>2050</v>
+      </c>
+      <c r="Q67" s="4">
+        <v>2060</v>
+      </c>
+      <c r="R67" s="4">
+        <v>2070</v>
+      </c>
+      <c r="S67" s="4">
+        <v>2080</v>
+      </c>
+      <c r="T67" s="4">
+        <v>2090</v>
+      </c>
+      <c r="U67" s="4">
+        <v>2100</v>
+      </c>
+      <c r="V67" s="4">
+        <v>2110</v>
+      </c>
+      <c r="W67" s="4">
+        <v>2130</v>
+      </c>
+      <c r="X67" s="8"/>
+    </row>
+    <row r="68" ht="15.25" spans="7:24">
+      <c r="G68" s="8"/>
+      <c r="H68" s="9"/>
+      <c r="I68" s="9"/>
+      <c r="J68" s="9"/>
+      <c r="K68" s="9"/>
+      <c r="L68" s="9"/>
+      <c r="M68" s="9"/>
+      <c r="N68" s="9"/>
+      <c r="O68" s="9"/>
+      <c r="P68" s="9"/>
+      <c r="Q68" s="9"/>
+      <c r="R68" s="9"/>
+      <c r="S68" s="9"/>
+      <c r="T68" s="9"/>
+      <c r="U68" s="9"/>
+      <c r="V68" s="9"/>
+      <c r="W68" s="9"/>
+      <c r="X68" s="9"/>
+    </row>
+    <row r="69" ht="15.25" spans="7:24">
+      <c r="G69" s="8"/>
+      <c r="H69" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="I69" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="J69" s="11">
+        <v>23143.15</v>
+      </c>
+      <c r="K69" s="11">
+        <v>24043.23</v>
+      </c>
+      <c r="L69" s="11">
+        <v>25605.6</v>
+      </c>
+      <c r="M69" s="11">
+        <v>26661.51</v>
+      </c>
+      <c r="N69" s="11">
+        <v>27302.64</v>
+      </c>
+      <c r="O69" s="11">
+        <v>29430.44</v>
+      </c>
+      <c r="P69" s="11">
+        <v>36096.16</v>
+      </c>
+      <c r="Q69" s="11">
+        <v>37740.31</v>
+      </c>
+      <c r="R69" s="11">
+        <v>39322.53</v>
+      </c>
+      <c r="S69" s="11">
+        <v>40229.69</v>
+      </c>
+      <c r="T69" s="11">
+        <v>41116.19</v>
+      </c>
+      <c r="U69" s="11">
+        <v>41583.86</v>
+      </c>
+      <c r="V69" s="11">
+        <v>41614.32</v>
+      </c>
+      <c r="W69" s="11">
+        <v>41554.059</v>
+      </c>
+      <c r="X69" s="8"/>
+    </row>
+    <row r="70" ht="15.25" spans="7:24">
+      <c r="G70" s="8"/>
+      <c r="H70" s="10"/>
+      <c r="I70" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J70" s="11">
+        <v>24300.3</v>
+      </c>
+      <c r="K70" s="11">
+        <v>25245.39</v>
+      </c>
+      <c r="L70" s="11">
+        <v>26885.88</v>
+      </c>
+      <c r="M70" s="11">
+        <v>27994.58</v>
+      </c>
+      <c r="N70" s="11">
+        <v>28667.77</v>
+      </c>
+      <c r="O70" s="11">
+        <v>30901.97</v>
+      </c>
+      <c r="P70" s="11">
+        <v>37900.97</v>
+      </c>
+      <c r="Q70" s="11">
+        <v>39627.32</v>
+      </c>
+      <c r="R70" s="11">
+        <v>41262.11</v>
+      </c>
+      <c r="S70" s="11">
+        <v>42213.82</v>
+      </c>
+      <c r="T70" s="11">
+        <v>43146.41</v>
+      </c>
+      <c r="U70" s="11">
+        <v>43637.66</v>
+      </c>
+      <c r="V70" s="11">
+        <v>43667.22</v>
+      </c>
+      <c r="W70" s="11">
+        <v>43606.2</v>
+      </c>
+      <c r="X70" s="8"/>
+    </row>
+    <row r="71" ht="15.25" spans="7:24">
+      <c r="G71" s="8"/>
+      <c r="H71" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="I71" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="J71" s="11">
+        <v>17204.75</v>
+      </c>
+      <c r="K71" s="11">
+        <v>17163.54</v>
+      </c>
+      <c r="L71" s="11">
+        <v>17585.44</v>
+      </c>
+      <c r="M71" s="11">
+        <v>17548.31</v>
+      </c>
+      <c r="N71" s="11">
+        <v>17924.42</v>
+      </c>
+      <c r="O71" s="11">
+        <v>21783.38</v>
+      </c>
+      <c r="P71" s="11">
+        <v>37973.078</v>
+      </c>
+      <c r="Q71" s="11">
+        <v>41145.61</v>
+      </c>
+      <c r="R71" s="11">
+        <v>44295.15</v>
+      </c>
+      <c r="S71" s="11">
+        <v>46514.84</v>
+      </c>
+      <c r="T71" s="11">
+        <v>48647.92</v>
+      </c>
+      <c r="U71" s="11">
+        <v>50070.91</v>
+      </c>
+      <c r="V71" s="11">
+        <v>50113.45</v>
+      </c>
+      <c r="W71" s="11">
+        <v>50028.95</v>
+      </c>
+      <c r="X71" s="8"/>
+    </row>
+    <row r="72" ht="15.25" spans="7:24">
+      <c r="H72" s="10"/>
+      <c r="I72" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="J72" s="11">
+        <v>18064.98</v>
+      </c>
+      <c r="K72" s="11">
+        <v>18021.71</v>
+      </c>
+      <c r="L72" s="11">
+        <v>18464.72</v>
+      </c>
+      <c r="M72" s="11">
+        <v>18425.72</v>
+      </c>
+      <c r="N72" s="11">
+        <v>18820.64</v>
+      </c>
+      <c r="O72" s="11">
+        <v>22872.55</v>
+      </c>
+      <c r="P72" s="11">
+        <v>39871.73</v>
+      </c>
+      <c r="Q72" s="11">
+        <v>43202.89</v>
+      </c>
+      <c r="R72" s="11">
+        <v>46481.91</v>
+      </c>
+      <c r="S72" s="11">
+        <v>48812.56</v>
+      </c>
+      <c r="T72" s="11">
+        <v>51051.14</v>
+      </c>
+      <c r="U72" s="11">
+        <v>52544.5</v>
+      </c>
+      <c r="V72" s="11">
+        <v>52589.1</v>
+      </c>
+      <c r="W72" s="11">
+        <v>52500.33</v>
+      </c>
+      <c r="X72" s="8"/>
+    </row>
+    <row r="74" spans="7:24">
+      <c r="J74">
+        <f xml:space="preserve">(J70-J69)/J69</f>
+        <v>0.0499996759300267</v>
+      </c>
+      <c r="K74">
+        <f xml:space="preserve">(K70-K69)/K69</f>
+        <v>0.0499999376123757</v>
+      </c>
+      <c r="L74">
+        <f xml:space="preserve">(L70-L69)/L69</f>
+        <v>0.0500000000000001</v>
+      </c>
+      <c r="M74">
+        <f xml:space="preserve">(M70-M69)/M69</f>
+        <v>0.0499997937101088</v>
+      </c>
+      <c r="N74">
+        <f xml:space="preserve">(N70-N69)/N69</f>
+        <v>0.0499999267470106</v>
+      </c>
+      <c r="O74">
+        <f t="shared" ref="O74:W74" si="1" xml:space="preserve">(O70-O69)/O69</f>
+        <v>0.0500002718274006</v>
+      </c>
+      <c r="P74">
+        <f t="shared" si="1"/>
+        <v>0.0500000554075557</v>
+      </c>
+      <c r="Q74">
+        <f t="shared" si="1"/>
+        <v>0.0499998542672279</v>
+      </c>
+      <c r="R74">
+        <f t="shared" si="1"/>
+        <v>0.0493249035603762</v>
+      </c>
+      <c r="S74">
+        <f t="shared" si="1"/>
+        <v>0.0493200419888892</v>
+      </c>
+      <c r="T74">
+        <f t="shared" si="1"/>
+        <v>0.0493776295906795</v>
+      </c>
+      <c r="U74">
+        <f t="shared" si="1"/>
+        <v>0.0493893544274149</v>
+      </c>
+      <c r="V74">
+        <f t="shared" si="1"/>
+        <v>0.0493315762458692</v>
+      </c>
+      <c r="W74">
+        <f t="shared" si="1"/>
+        <v>0.049384850707364</v>
+      </c>
+    </row>
+    <row r="79" ht="15.25"/>
+    <row r="80" ht="15.25" spans="7:24">
+      <c r="H80" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J80" s="4">
+        <v>2019</v>
+      </c>
+      <c r="K80" s="4">
+        <v>2020</v>
+      </c>
+      <c r="L80" s="4">
+        <v>2025</v>
+      </c>
+      <c r="M80" s="4">
+        <v>2030</v>
+      </c>
+      <c r="N80" s="4">
+        <v>2035</v>
+      </c>
+      <c r="O80" s="4">
+        <v>2040</v>
+      </c>
+      <c r="P80" s="4">
+        <v>2050</v>
+      </c>
+      <c r="Q80" s="4">
+        <v>2060</v>
+      </c>
+      <c r="R80" s="4">
+        <v>2070</v>
+      </c>
+      <c r="S80" s="4">
+        <v>2080</v>
+      </c>
+      <c r="T80" s="4">
+        <v>2090</v>
+      </c>
+      <c r="U80" s="4">
+        <v>2100</v>
+      </c>
+      <c r="V80" s="4">
+        <v>2110</v>
+      </c>
+      <c r="W80" s="4">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="81" ht="15.25" spans="8:24">
+      <c r="H81" s="5"/>
+      <c r="I81" s="5"/>
+      <c r="J81" s="5"/>
+      <c r="K81" s="5"/>
+      <c r="L81" s="5"/>
+      <c r="M81" s="5"/>
+      <c r="N81" s="5"/>
+      <c r="O81" s="5"/>
+      <c r="P81" s="5"/>
+      <c r="Q81" s="5"/>
+      <c r="R81" s="5"/>
+      <c r="S81" s="5"/>
+      <c r="T81" s="5"/>
+      <c r="U81" s="5"/>
+      <c r="V81" s="5"/>
+      <c r="W81" s="5"/>
+      <c r="X81" s="5"/>
+    </row>
+    <row r="82" ht="15.25" spans="8:24">
+      <c r="H82" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="J82" s="7">
+        <v>23143.15</v>
+      </c>
+      <c r="K82" s="7">
+        <v>24043.23</v>
+      </c>
+      <c r="L82" s="7">
+        <v>25605.6</v>
+      </c>
+      <c r="M82" s="7">
+        <v>26661.51</v>
+      </c>
+      <c r="N82" s="7">
+        <v>27302.64</v>
+      </c>
+      <c r="O82" s="7">
+        <v>29430.44</v>
+      </c>
+      <c r="P82" s="7">
+        <v>36096.16</v>
+      </c>
+      <c r="Q82" s="7">
+        <v>37740.31</v>
+      </c>
+      <c r="R82" s="7">
+        <v>39322.53</v>
+      </c>
+      <c r="S82" s="7">
+        <v>40229.69</v>
+      </c>
+      <c r="T82" s="7">
+        <v>41116.19</v>
+      </c>
+      <c r="U82" s="7">
+        <v>41583.86</v>
+      </c>
+      <c r="V82" s="7">
+        <v>41614.32</v>
+      </c>
+      <c r="W82" s="7">
+        <v>41554.059</v>
+      </c>
+      <c r="X82" s="8"/>
+    </row>
+    <row r="83" ht="15.25" spans="8:24">
+      <c r="H83" s="6"/>
+      <c r="I83" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="J83" s="7">
+        <v>25704.066</v>
+      </c>
+      <c r="K83" s="7">
+        <v>26703.96</v>
+      </c>
+      <c r="L83" s="7">
+        <v>28274.092</v>
+      </c>
+      <c r="M83" s="7">
+        <v>29271.63</v>
+      </c>
+      <c r="N83" s="7">
+        <v>29803.51</v>
+      </c>
+      <c r="O83" s="7">
+        <v>31941.78</v>
+      </c>
+      <c r="P83" s="7">
+        <v>38731.39</v>
+      </c>
+      <c r="Q83" s="7">
+        <v>40041.74</v>
+      </c>
+      <c r="R83" s="7">
+        <v>41262.11</v>
+      </c>
+      <c r="S83" s="7">
+        <v>42213.82</v>
+      </c>
+      <c r="T83" s="7">
+        <v>43146.41</v>
+      </c>
+      <c r="U83" s="7">
+        <v>43637.66</v>
+      </c>
+      <c r="V83" s="7">
+        <v>43667.22</v>
+      </c>
+      <c r="W83" s="7">
+        <v>43606.2</v>
+      </c>
+      <c r="X83" s="8"/>
+    </row>
+    <row r="84" ht="15.25" spans="8:24">
+      <c r="H84" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="J84" s="7">
+        <v>17204.75</v>
+      </c>
+      <c r="K84" s="7">
+        <v>17163.54</v>
+      </c>
+      <c r="L84" s="7">
+        <v>17585.44</v>
+      </c>
+      <c r="M84" s="7">
+        <v>17548.31</v>
+      </c>
+      <c r="N84" s="7">
+        <v>17924.42</v>
+      </c>
+      <c r="O84" s="7">
+        <v>21783.38</v>
+      </c>
+      <c r="P84" s="7">
+        <v>37973.078</v>
+      </c>
+      <c r="Q84" s="7">
+        <v>41145.61</v>
+      </c>
+      <c r="R84" s="7">
+        <v>44295.15</v>
+      </c>
+      <c r="S84" s="7">
+        <v>46514.84</v>
+      </c>
+      <c r="T84" s="7">
+        <v>48647.92</v>
+      </c>
+      <c r="U84" s="7">
+        <v>50070.91</v>
+      </c>
+      <c r="V84" s="7">
+        <v>50113.45</v>
+      </c>
+      <c r="W84" s="7">
+        <v>50028.95</v>
+      </c>
+      <c r="X84" s="8"/>
+    </row>
+    <row r="85" ht="15.25" spans="8:24">
+      <c r="H85" s="6"/>
+      <c r="I85" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="J85" s="7">
+        <v>18871.74</v>
+      </c>
+      <c r="K85" s="7">
+        <v>18826.53</v>
+      </c>
+      <c r="L85" s="7">
+        <v>19201.9</v>
+      </c>
+      <c r="M85" s="7">
+        <v>19075.04</v>
+      </c>
+      <c r="N85" s="7">
+        <v>19396.47</v>
+      </c>
+      <c r="O85" s="7">
+        <v>23466.79</v>
+      </c>
+      <c r="P85" s="7">
+        <v>40544.44</v>
+      </c>
+      <c r="Q85" s="7">
+        <v>43545.84</v>
+      </c>
+      <c r="R85" s="7">
+        <v>46481.91</v>
+      </c>
+      <c r="S85" s="7">
+        <v>48812.56</v>
+      </c>
+      <c r="T85" s="7">
+        <v>51051.14</v>
+      </c>
+      <c r="U85" s="7">
+        <v>52544.5</v>
+      </c>
+      <c r="V85" s="7">
+        <v>52589.1</v>
+      </c>
+      <c r="W85" s="7">
+        <v>52500.33</v>
+      </c>
+      <c r="X85" s="8"/>
+    </row>
+    <row r="87" spans="8:24">
+      <c r="J87">
+        <f t="shared" ref="J87:W87" si="2" xml:space="preserve">(J83-J82)/J82</f>
+        <v>0.110655463927771</v>
+      </c>
+      <c r="K87">
+        <f t="shared" si="2"/>
+        <v>0.110664415721182</v>
+      </c>
+      <c r="L87">
+        <f t="shared" si="2"/>
+        <v>0.104215171681195</v>
+      </c>
+      <c r="M87">
+        <f t="shared" si="2"/>
+        <v>0.0978984311091158</v>
+      </c>
+      <c r="N87">
+        <f t="shared" si="2"/>
+        <v>0.0915981018685372</v>
+      </c>
+      <c r="O87">
+        <f t="shared" si="2"/>
+        <v>0.0853313779882326</v>
+      </c>
+      <c r="P87">
+        <f t="shared" si="2"/>
+        <v>0.0730058266585697</v>
+      </c>
+      <c r="Q87">
+        <f t="shared" si="2"/>
+        <v>0.0609806861681846</v>
+      </c>
+      <c r="R87">
+        <f t="shared" si="2"/>
+        <v>0.0493249035603762</v>
+      </c>
+      <c r="S87">
+        <f t="shared" si="2"/>
+        <v>0.0493200419888892</v>
+      </c>
+      <c r="T87">
+        <f t="shared" si="2"/>
+        <v>0.0493776295906795</v>
+      </c>
+      <c r="U87">
+        <f t="shared" si="2"/>
+        <v>0.0493893544274149</v>
+      </c>
+      <c r="V87">
+        <f t="shared" si="2"/>
+        <v>0.0493315762458692</v>
+      </c>
+      <c r="W87">
+        <f t="shared" si="2"/>
+        <v>0.049384850707364</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="H66:X66"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="G57:G58"/>
+    <mergeCell ref="G59:G60"/>
+    <mergeCell ref="G66:G71"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="H82:H83"/>
+    <mergeCell ref="H84:H85"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="8"/>
+    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
@@ -251,6 +251,28 @@
     <author>xli9</author>
   </authors>
   <commentList>
+    <comment ref="H3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t>xli9:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">
+contrdict other limits, and does not work for storage projections so removed</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D7" authorId="0">
       <text>
         <r>
@@ -278,7 +300,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="187">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -484,330 +506,330 @@
     <t>UCE_MaxOutput-of-gidstorage</t>
   </si>
   <si>
+    <t>elcagg_spv*</t>
+  </si>
+  <si>
+    <t>Discharge of batteries should lower than a proportion of wind+pv</t>
+  </si>
+  <si>
+    <t>elcagg_w*</t>
+  </si>
+  <si>
+    <t>E*, Uti*, Tra_BEV_Batt_VtoG</t>
+  </si>
+  <si>
+    <t>AuxStoOUT</t>
+  </si>
+  <si>
+    <t>~UC_Sets: R_S: AllRegions</t>
+  </si>
+  <si>
+    <t>~UC_Sets: T_SUC:</t>
+  </si>
+  <si>
+    <t>~UC_T</t>
+  </si>
+  <si>
+    <t>Pset_Set</t>
+  </si>
+  <si>
+    <t>UC_ATTR~RHS</t>
+  </si>
+  <si>
+    <t>UC_CAP</t>
+  </si>
+  <si>
+    <t>UC_CAP~RHS</t>
+  </si>
+  <si>
+    <t>UC_Grow_LI</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_LI</t>
+  </si>
+  <si>
+    <t>CAP,GROWTH</t>
+  </si>
+  <si>
+    <t>2025, 2150</t>
+  </si>
+  <si>
+    <t>UP</t>
+  </si>
+  <si>
+    <t>UC_Grow_GR</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_GR</t>
+  </si>
+  <si>
+    <t>UC_Grow_NI</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_NI</t>
+  </si>
+  <si>
+    <t>UC_Grow_COB_byCop</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_COB_byCop</t>
+  </si>
+  <si>
+    <t>UC_Grow_MN</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_MN</t>
+  </si>
+  <si>
+    <t>UC_Grow_COP</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_COP</t>
+  </si>
+  <si>
+    <t>UC_Grow_AL</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_AL</t>
+  </si>
+  <si>
+    <t>UC_Grow_COB_byNI_HPAL</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_COB_byNI_HPAL</t>
+  </si>
+  <si>
+    <t>UC_Grow_COB_byNI_sulfide</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_COB_byNI_sulfide</t>
+  </si>
+  <si>
+    <t>UC_Grow_COB_direct</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_COB_direct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original : </t>
+  </si>
+  <si>
+    <t>RHSTS</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy1</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-LFP_fromrecy</t>
+  </si>
+  <si>
+    <t>2030, 2150</t>
+  </si>
+  <si>
+    <t>LO</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy2</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-LMO_fromrecy</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy3</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-NCA_fromrecy</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy4</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-NMC111_fromrecy</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy5</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-NMC532_fromrecy</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy6</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-NMC622_fromrecy</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy7</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-NMC811_fromrecy</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy8</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt</t>
+  </si>
+  <si>
+    <t>2019, 2150</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy9</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_LMO</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy10</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_NCA</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy11</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_NMC111</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy12</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_NMC532</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy13</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_NMC622</t>
+  </si>
+  <si>
+    <t>UC_Grow_Recy14</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt_NMC811</t>
+  </si>
+  <si>
+    <t>Cset_Set</t>
+  </si>
+  <si>
+    <t>UC_COMNET</t>
+  </si>
+  <si>
+    <t>UC_COMNET~RHS</t>
+  </si>
+  <si>
+    <t>UC_coalEmi1</t>
+  </si>
+  <si>
+    <t>ELCCO2Nc</t>
+  </si>
+  <si>
+    <t>COMNET,GROWTH</t>
+  </si>
+  <si>
+    <t>2040, 2150</t>
+  </si>
+  <si>
+    <t>UC_OilEmi2</t>
+  </si>
+  <si>
+    <t>ELCCO2No</t>
+  </si>
+  <si>
+    <t>UC_gasEmi3</t>
+  </si>
+  <si>
+    <t>ELCCO2Ng</t>
+  </si>
+  <si>
+    <t>2050, 2150</t>
+  </si>
+  <si>
+    <t>UC_totco2Emi4</t>
+  </si>
+  <si>
+    <t>TOTCO2</t>
+  </si>
+  <si>
+    <t>~UC_T: LO</t>
+  </si>
+  <si>
+    <t>UCE_MaxUtility_scale</t>
+  </si>
+  <si>
+    <t>Tra_E*fromrecy, Tra_EV_Bat*virgin_pack</t>
+  </si>
+  <si>
+    <t>Util_Rep_B*</t>
+  </si>
+  <si>
+    <t>UCE_2</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-LFP_fromrecy, Tra_EV_Batt-LFP_virgin_pack</t>
+  </si>
+  <si>
+    <t>Tra_E*fromrecy, Tra_EV_Bat*virgin_pack, -Tra_EV_Batt-LFP_fromrecy, -Tra_EV_Batt-LFP_virgin_pack</t>
+  </si>
+  <si>
+    <t>UCE_3</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt, Util_Rep_Batt-LFP</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt*, Util_Rep_Bat*, -EN_STG_4hBatt, -Util_Rep_Batt-LFP</t>
+  </si>
+  <si>
+    <t>~UC_T: UC_CAP</t>
+  </si>
+  <si>
+    <t>limtype</t>
+  </si>
+  <si>
+    <t>Allregions</t>
+  </si>
+  <si>
+    <t>UCE_MinAct_of_EVBattery</t>
+  </si>
+  <si>
+    <t>AuxStoIN</t>
+  </si>
+  <si>
+    <t>Tra_EV_Bat*fromrecy, Tra_EV_Bat*virgin_pack</t>
+  </si>
+  <si>
+    <t>UCE_MinAct_of_GRIDBattery</t>
+  </si>
+  <si>
+    <t>EN_STG_4hBatt*, Util_Rep_Bat*</t>
+  </si>
+  <si>
+    <t>UCE_MinAct_of_HPS</t>
+  </si>
+  <si>
+    <t>UCE_MinAct_of_vtog</t>
+  </si>
+  <si>
+    <t>Tra_BEV_Batt_VtoG</t>
+  </si>
+  <si>
+    <t>UC_RHSRTS</t>
+  </si>
+  <si>
+    <t>UC_RHSRTS~0</t>
+  </si>
+  <si>
+    <t>UCE_ElcBalance</t>
+  </si>
+  <si>
     <t>ELE,CHP</t>
   </si>
   <si>
     <t>E*</t>
   </si>
   <si>
-    <t>ELCSPV</t>
-  </si>
-  <si>
-    <t>Discharge of batteries should lower than a level</t>
-  </si>
-  <si>
-    <t>ELCWIN</t>
-  </si>
-  <si>
-    <t>E*, Uti*, Tra_BEV_Batt_VtoG</t>
-  </si>
-  <si>
-    <t>AuxStoOUT</t>
-  </si>
-  <si>
-    <t>~UC_Sets: R_S: AllRegions</t>
-  </si>
-  <si>
-    <t>~UC_Sets: T_SUC:</t>
-  </si>
-  <si>
-    <t>~UC_T</t>
-  </si>
-  <si>
-    <t>Pset_Set</t>
-  </si>
-  <si>
-    <t>UC_ATTR~RHS</t>
-  </si>
-  <si>
-    <t>UC_CAP</t>
-  </si>
-  <si>
-    <t>UC_CAP~RHS</t>
-  </si>
-  <si>
-    <t>UC_Grow_LI</t>
-  </si>
-  <si>
-    <t>MINBatMaterials_LI</t>
-  </si>
-  <si>
-    <t>CAP,GROWTH</t>
-  </si>
-  <si>
-    <t>2025, 2150</t>
-  </si>
-  <si>
-    <t>UP</t>
-  </si>
-  <si>
-    <t>UC_Grow_GR</t>
-  </si>
-  <si>
-    <t>MINBatMaterials_GR</t>
-  </si>
-  <si>
-    <t>UC_Grow_NI</t>
-  </si>
-  <si>
-    <t>MINBatMaterials_NI</t>
-  </si>
-  <si>
-    <t>UC_Grow_COB_byCop</t>
-  </si>
-  <si>
-    <t>MINBatMaterials_COB_byCop</t>
-  </si>
-  <si>
-    <t>UC_Grow_MN</t>
-  </si>
-  <si>
-    <t>MINBatMaterials_MN</t>
-  </si>
-  <si>
-    <t>UC_Grow_COP</t>
-  </si>
-  <si>
-    <t>MINBatMaterials_COP</t>
-  </si>
-  <si>
-    <t>UC_Grow_AL</t>
-  </si>
-  <si>
-    <t>MINBatMaterials_AL</t>
-  </si>
-  <si>
-    <t>UC_Grow_COB_byNI_HPAL</t>
-  </si>
-  <si>
-    <t>MINBatMaterials_COB_byNI_HPAL</t>
-  </si>
-  <si>
-    <t>UC_Grow_COB_byNI_sulfide</t>
-  </si>
-  <si>
-    <t>MINBatMaterials_COB_byNI_sulfide</t>
-  </si>
-  <si>
-    <t>UC_Grow_COB_direct</t>
-  </si>
-  <si>
-    <t>MINBatMaterials_COB_direct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Original : </t>
-  </si>
-  <si>
-    <t>RHSTS</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy1</t>
-  </si>
-  <si>
-    <t>Tra_EV_Batt-LFP_fromrecy</t>
-  </si>
-  <si>
-    <t>2030, 2150</t>
-  </si>
-  <si>
-    <t>LO</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy2</t>
-  </si>
-  <si>
-    <t>Tra_EV_Batt-LMO_fromrecy</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy3</t>
-  </si>
-  <si>
-    <t>Tra_EV_Batt-NCA_fromrecy</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy4</t>
-  </si>
-  <si>
-    <t>Tra_EV_Batt-NMC111_fromrecy</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy5</t>
-  </si>
-  <si>
-    <t>Tra_EV_Batt-NMC532_fromrecy</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy6</t>
-  </si>
-  <si>
-    <t>Tra_EV_Batt-NMC622_fromrecy</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy7</t>
-  </si>
-  <si>
-    <t>Tra_EV_Batt-NMC811_fromrecy</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy8</t>
-  </si>
-  <si>
-    <t>EN_STG_4hBatt</t>
-  </si>
-  <si>
-    <t>2019, 2150</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy9</t>
-  </si>
-  <si>
-    <t>EN_STG_4hBatt_LMO</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy10</t>
-  </si>
-  <si>
-    <t>EN_STG_4hBatt_NCA</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy11</t>
-  </si>
-  <si>
-    <t>EN_STG_4hBatt_NMC111</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy12</t>
-  </si>
-  <si>
-    <t>EN_STG_4hBatt_NMC532</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy13</t>
-  </si>
-  <si>
-    <t>EN_STG_4hBatt_NMC622</t>
-  </si>
-  <si>
-    <t>UC_Grow_Recy14</t>
-  </si>
-  <si>
-    <t>EN_STG_4hBatt_NMC811</t>
-  </si>
-  <si>
-    <t>Cset_Set</t>
-  </si>
-  <si>
-    <t>UC_COMNET</t>
-  </si>
-  <si>
-    <t>UC_COMNET~RHS</t>
-  </si>
-  <si>
-    <t>UC_coalEmi1</t>
-  </si>
-  <si>
-    <t>ELCCO2Nc</t>
-  </si>
-  <si>
-    <t>COMNET,GROWTH</t>
-  </si>
-  <si>
-    <t>2040, 2150</t>
-  </si>
-  <si>
-    <t>UC_OilEmi2</t>
-  </si>
-  <si>
-    <t>ELCCO2No</t>
-  </si>
-  <si>
-    <t>UC_gasEmi3</t>
-  </si>
-  <si>
-    <t>ELCCO2Ng</t>
-  </si>
-  <si>
-    <t>2050, 2150</t>
-  </si>
-  <si>
-    <t>UC_totco2Emi4</t>
-  </si>
-  <si>
-    <t>TOTCO2</t>
-  </si>
-  <si>
-    <t>~UC_T: LO</t>
-  </si>
-  <si>
-    <t>UCE_MaxUtility_scale</t>
-  </si>
-  <si>
-    <t>Tra_E*fromrecy, Tra_EV_Bat*virgin_pack</t>
-  </si>
-  <si>
-    <t>Util_Rep_B*</t>
-  </si>
-  <si>
-    <t>UCE_2</t>
-  </si>
-  <si>
-    <t>Tra_EV_Batt-LFP_fromrecy, Tra_EV_Batt-LFP_virgin_pack</t>
-  </si>
-  <si>
-    <t>Tra_E*fromrecy, Tra_EV_Bat*virgin_pack, -Tra_EV_Batt-LFP_fromrecy, -Tra_EV_Batt-LFP_virgin_pack</t>
-  </si>
-  <si>
-    <t>UCE_3</t>
-  </si>
-  <si>
-    <t>EN_STG_4hBatt, Util_Rep_Batt-LFP</t>
-  </si>
-  <si>
-    <t>EN_STG_4hBatt*, Util_Rep_Bat*, -EN_STG_4hBatt, -Util_Rep_Batt-LFP</t>
-  </si>
-  <si>
-    <t>~UC_T: UC_CAP</t>
-  </si>
-  <si>
-    <t>limtype</t>
-  </si>
-  <si>
-    <t>Allregions</t>
-  </si>
-  <si>
-    <t>UCE_MinAct_of_EVBattery</t>
-  </si>
-  <si>
-    <t>AuxStoIN</t>
-  </si>
-  <si>
-    <t>Tra_EV_Bat*fromrecy, Tra_EV_Bat*virgin_pack</t>
-  </si>
-  <si>
-    <t>UCE_MinAct_of_GRIDBattery</t>
-  </si>
-  <si>
-    <t>EN_STG_4hBatt*, Util_Rep_Bat*</t>
-  </si>
-  <si>
-    <t>UCE_MinAct_of_HPS</t>
-  </si>
-  <si>
-    <t>UCE_MinAct_of_vtog</t>
-  </si>
-  <si>
-    <t>Tra_BEV_Batt_VtoG</t>
-  </si>
-  <si>
-    <t>UC_RHSRTS</t>
-  </si>
-  <si>
-    <t>UC_RHSRTS~0</t>
-  </si>
-  <si>
-    <t>UCE_ElcBalance</t>
-  </si>
-  <si>
     <t xml:space="preserve">ELc curtailment not beyond 5% of demand </t>
   </si>
   <si>
@@ -815,6 +837,9 @@
   </si>
   <si>
     <t>STG</t>
+  </si>
+  <si>
+    <t>IMPNRGZ</t>
   </si>
   <si>
     <t>*Need to test if ElcDemand's UC_FLO can be captured or not</t>
@@ -857,6 +882,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
+      <color rgb="FF3974D2"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -866,12 +897,6 @@
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF3974D2"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
@@ -1085,8 +1110,9 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <name val="Times New Roman"/>
+      <name val="Tahoma"/>
       <charset val="0"/>
     </font>
     <font>
@@ -1096,9 +1122,8 @@
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
@@ -1113,6 +1138,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.35"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1141,12 +1172,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.35"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1556,7 +1581,7 @@
     <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1635,68 +1660,69 @@
   </cellStyleXfs>
   <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="51" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1705,12 +1731,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
@@ -2309,7 +2334,7 @@
       </c>
     </row>
     <row r="4" ht="16" spans="1:11">
-      <c r="A4" s="12"/>
+      <c r="A4" s="14"/>
     </row>
     <row r="7" spans="1:11">
       <c r="D7" t="s">
@@ -2366,10 +2391,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="22"/>
+      <c r="K10" s="24"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="22"/>
+      <c r="K11" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2390,12 +2415,12 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:13">
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="41" t="s">
         <v>23</v>
       </c>
       <c r="D5" s="45"/>
       <c r="E5" s="45"/>
-      <c r="F5" s="34"/>
+      <c r="F5" s="35"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
@@ -2446,7 +2471,7 @@
       <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="14" t="s">
         <v>37</v>
       </c>
       <c r="D9" s="45" t="s">
@@ -2470,13 +2495,13 @@
         <v>8</v>
       </c>
       <c r="K10" s="48"/>
-      <c r="L10" s="43"/>
+      <c r="L10" s="4"/>
     </row>
     <row r="11" ht="16" spans="2:13">
       <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="14" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="45" t="s">
@@ -2490,7 +2515,7 @@
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="14" t="s">
         <v>32</v>
       </c>
       <c r="D12" s="45" t="s">
@@ -2504,13 +2529,13 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" s="35" t="s">
         <v>39</v>
       </c>
       <c r="D13" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="35">
         <v>2</v>
       </c>
     </row>
@@ -2518,13 +2543,13 @@
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="35" t="s">
         <v>40</v>
       </c>
       <c r="D14" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="35">
         <v>0</v>
       </c>
     </row>
@@ -2532,13 +2557,13 @@
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="35" t="s">
+      <c r="C15" s="36" t="s">
         <v>41</v>
       </c>
       <c r="D15" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="35">
         <v>0</v>
       </c>
     </row>
@@ -2569,7 +2594,7 @@
       <c r="E17" s="51">
         <v>0.2</v>
       </c>
-      <c r="F17" s="34"/>
+      <c r="F17" s="35"/>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
@@ -2584,13 +2609,13 @@
       <c r="E18" s="51">
         <v>0.2</v>
       </c>
-      <c r="F18" s="34"/>
+      <c r="F18" s="35"/>
     </row>
     <row r="19" ht="16" spans="2:6">
       <c r="B19" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="14" t="s">
         <v>37</v>
       </c>
       <c r="D19" s="50" t="s">
@@ -2599,7 +2624,7 @@
       <c r="E19" s="51">
         <v>0.2</v>
       </c>
-      <c r="F19" s="34"/>
+      <c r="F19" s="35"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
@@ -2614,13 +2639,13 @@
       <c r="E20" s="51">
         <v>0.5</v>
       </c>
-      <c r="F20" s="34"/>
+      <c r="F20" s="35"/>
     </row>
     <row r="21" ht="16" spans="2:6">
       <c r="B21" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="14" t="s">
         <v>31</v>
       </c>
       <c r="D21" s="50" t="s">
@@ -2629,65 +2654,65 @@
       <c r="E21" s="51">
         <v>0.8</v>
       </c>
-      <c r="F21" s="34"/>
+      <c r="F21" s="35"/>
     </row>
     <row r="22" ht="16" spans="2:6">
       <c r="B22" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="14" t="s">
         <v>32</v>
       </c>
       <c r="D22" s="50" t="s">
         <v>43</v>
       </c>
       <c r="E22" s="45"/>
-      <c r="F22" s="34"/>
+      <c r="F22" s="35"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" s="35" t="s">
         <v>39</v>
       </c>
       <c r="D23" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="35">
         <v>1</v>
       </c>
-      <c r="F23" s="34"/>
+      <c r="F23" s="35"/>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" s="35" t="s">
         <v>44</v>
       </c>
       <c r="D24" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="35">
         <v>1</v>
       </c>
-      <c r="F24" s="34"/>
+      <c r="F24" s="35"/>
     </row>
     <row r="25" ht="16" spans="2:6">
       <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="35" t="s">
+      <c r="C25" s="36" t="s">
         <v>41</v>
       </c>
       <c r="D25" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="35">
         <v>1</v>
       </c>
-      <c r="F25" s="34"/>
+      <c r="F25" s="35"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
@@ -2702,7 +2727,7 @@
       <c r="E26" s="45">
         <v>0.05</v>
       </c>
-      <c r="F26" s="34"/>
+      <c r="F26" s="35"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="52" t="s">
@@ -2717,48 +2742,48 @@
       <c r="E27" s="53">
         <v>2020</v>
       </c>
-      <c r="F27" s="34"/>
+      <c r="F27" s="35"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="C28" s="34" t="s">
+      <c r="C28" s="35" t="s">
         <v>46</v>
       </c>
       <c r="D28" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="37">
+      <c r="E28" s="38">
         <v>2020</v>
       </c>
-      <c r="F28" s="34"/>
+      <c r="F28" s="35"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
     </row>
     <row r="38" spans="3:5">
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
     </row>
     <row r="54" spans="3:11">
       <c r="C54" s="54" t="s">
@@ -3129,577 +3154,573 @@
   <dimension ref="E13:W38"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
-    <col min="6" max="6" width="25.0909090909091" customWidth="1"/>
+    <col min="6" max="6" width="29.2727272727273" customWidth="1"/>
     <col min="8" max="8" width="27" customWidth="1"/>
     <col min="9" max="9" width="43.7272727272727" customWidth="1"/>
     <col min="12" max="12" width="10.2727272727273" customWidth="1"/>
     <col min="14" max="14" width="12.8181818181818" customWidth="1"/>
     <col min="15" max="15" width="11.3636363636364" customWidth="1"/>
+    <col min="16" max="16" width="12.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="13" spans="5:21">
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
     </row>
     <row r="14" spans="5:21">
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
     </row>
     <row r="15" spans="5:21">
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
     </row>
     <row r="16" spans="5:21">
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
     </row>
     <row r="17" spans="5:23">
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1"/>
-      <c r="W17" s="1"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
     </row>
     <row r="18" spans="5:23">
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="1"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
     </row>
     <row r="19" spans="5:23">
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
-      <c r="W19" s="1"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
     </row>
     <row r="20" spans="5:23">
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
     </row>
     <row r="21" spans="5:23">
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="1"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
     </row>
     <row r="22" spans="5:23">
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
-      <c r="W22" s="1"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
     </row>
     <row r="23" spans="5:23">
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
-      <c r="W23" s="1"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
     </row>
     <row r="24" spans="5:23">
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-      <c r="W24" s="1"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
     </row>
     <row r="25" spans="5:23">
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="1"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
     </row>
     <row r="26" spans="5:23">
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="1"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
     </row>
     <row r="27" spans="5:23">
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="1"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
     </row>
     <row r="28" spans="5:23">
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
     </row>
     <row r="29" spans="5:23">
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1" t="s">
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
     </row>
     <row r="30" ht="15.25" spans="5:23">
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="I30" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="J30" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="K30" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="L30" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M30" s="1" t="s">
+      <c r="M30" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="N30" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="O30" s="1" t="s">
+      <c r="O30" s="2" t="s">
         <v>64</v>
       </c>
       <c r="P30" t="s">
         <v>65</v>
       </c>
-      <c r="Q30" s="1" t="s">
+      <c r="Q30" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
     </row>
     <row r="31" ht="16" spans="5:23">
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="2"/>
+      <c r="H31" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2">
+        <v>-0.25</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q31" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+    </row>
+    <row r="32" ht="15.25" spans="5:23">
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1">
-        <v>-0.25</v>
-      </c>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1">
-        <v>0</v>
-      </c>
-      <c r="P31" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q31" s="1" t="s">
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+    </row>
+    <row r="33" spans="6:22">
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
-    </row>
-    <row r="32" ht="15.25" spans="5:23">
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1" t="s">
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1">
-        <v>-0.1</v>
-      </c>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
-    </row>
-    <row r="33" spans="6:22">
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1">
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2">
         <v>1</v>
       </c>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-      <c r="R33" s="1"/>
-      <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
-      <c r="U33" s="1"/>
-      <c r="V33" s="1"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2"/>
     </row>
     <row r="34" spans="6:22">
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
-      <c r="R34" s="1"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
     </row>
     <row r="35" spans="6:22">
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="2"/>
     </row>
     <row r="36" spans="6:22">
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
-      <c r="R36" s="1"/>
-      <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
-      <c r="U36" s="1"/>
-      <c r="V36" s="1"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
     </row>
     <row r="37" spans="6:22">
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
-      <c r="R37" s="1"/>
-      <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="2"/>
     </row>
     <row r="38" spans="6:22">
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-      <c r="R38" s="1"/>
-      <c r="S38" s="1"/>
-      <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3726,772 +3747,772 @@
   <sheetData>
     <row r="2" spans="2:14">
       <c r="B2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="2:14">
       <c r="B3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14">
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" spans="2:14">
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="2:14">
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" spans="2:14">
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" spans="2:14">
+      <c r="D8" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="31" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="4" spans="2:14">
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29" t="s">
+      <c r="F8" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-    </row>
-    <row r="5" spans="2:14">
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-    </row>
-    <row r="6" spans="2:14">
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-    </row>
-    <row r="7" spans="2:14">
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-    </row>
-    <row r="8" spans="2:14">
-      <c r="D8" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" s="30" t="s">
+      <c r="H8" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="J8" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="30" t="s">
+      <c r="K8" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="I8" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="J8" s="30" t="s">
+      <c r="L8" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="M8" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="N8" s="31" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14">
+      <c r="D9" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="K8" s="30" t="s">
+      <c r="E9" s="1"/>
+      <c r="F9" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="L8" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="M8" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="N8" s="30" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14">
-      <c r="D9" s="32" t="s">
+      <c r="G9" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="32" t="s">
+      <c r="H9" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="I9" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="J9" s="1">
+        <v>1</v>
+      </c>
+      <c r="K9" s="33">
+        <v>1.25</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="M9" s="33">
+        <v>1</v>
+      </c>
+      <c r="N9" s="33"/>
+    </row>
+    <row r="10" spans="2:14">
+      <c r="D10" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="I9" s="32" t="s">
+      <c r="E10" s="1"/>
+      <c r="F10" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="J9" s="29">
+      <c r="G10" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="I10" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="J10" s="1">
         <v>1</v>
       </c>
-      <c r="K9" s="32">
-        <v>1.25</v>
-      </c>
-      <c r="L9" s="29">
+      <c r="K10" s="33">
+        <v>1.11</v>
+      </c>
+      <c r="L10" s="1">
         <v>0.05</v>
       </c>
-      <c r="M9" s="32">
+      <c r="M10" s="33">
         <v>1</v>
       </c>
-      <c r="N9" s="32"/>
-    </row>
-    <row r="10" spans="2:14">
-      <c r="D10" s="32" t="s">
+      <c r="N10" s="33"/>
+    </row>
+    <row r="11" spans="2:14">
+      <c r="D11" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="E10" s="29"/>
-      <c r="F10" s="32" t="s">
+      <c r="E11" s="1"/>
+      <c r="F11" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G11" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="I11" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="H10" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="I10" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="J10" s="29">
+      <c r="J11" s="1">
         <v>1</v>
       </c>
-      <c r="K10" s="32">
-        <v>1.11</v>
-      </c>
-      <c r="L10" s="29">
-        <v>0.05</v>
-      </c>
-      <c r="M10" s="32">
+      <c r="K11" s="33">
+        <v>1.15</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="M11" s="33">
         <v>1</v>
       </c>
-      <c r="N10" s="32"/>
-    </row>
-    <row r="11" spans="2:14">
-      <c r="D11" s="32" t="s">
+      <c r="N11" s="33"/>
+    </row>
+    <row r="12" ht="16" spans="2:14">
+      <c r="D12" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="32" t="s">
+      <c r="E12" s="1"/>
+      <c r="F12" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="G11" s="32" t="s">
+      <c r="G12" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="I12" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="H11" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="I11" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="J11" s="29">
+      <c r="J12" s="1">
         <v>1</v>
       </c>
-      <c r="K11" s="32">
-        <v>1.15</v>
-      </c>
-      <c r="L11" s="29">
-        <v>0.08</v>
-      </c>
-      <c r="M11" s="32">
+      <c r="K12" s="33">
+        <v>1.12</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="M12" s="33">
         <v>1</v>
       </c>
-      <c r="N11" s="32"/>
-    </row>
-    <row r="12" ht="16" spans="2:14">
-      <c r="D12" s="32" t="s">
+      <c r="N12" s="33"/>
+    </row>
+    <row r="13" spans="2:14">
+      <c r="D13" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="29"/>
-      <c r="F12" s="33" t="s">
+      <c r="E13" s="1"/>
+      <c r="F13" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="32" t="s">
+      <c r="G13" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="I13" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="H12" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="I12" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="J12" s="29">
+      <c r="J13" s="1">
         <v>1</v>
       </c>
-      <c r="K12" s="32">
-        <v>1.12</v>
-      </c>
-      <c r="L12" s="29">
-        <v>0.03</v>
-      </c>
-      <c r="M12" s="32">
+      <c r="K13" s="33">
+        <v>1.2</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="M13" s="33">
         <v>1</v>
       </c>
-      <c r="N12" s="32"/>
-    </row>
-    <row r="13" spans="2:14">
-      <c r="D13" s="32" t="s">
+      <c r="N13" s="33"/>
+    </row>
+    <row r="14" spans="2:14">
+      <c r="D14" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="32" t="s">
+      <c r="E14" s="1"/>
+      <c r="F14" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G14" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="I14" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="H13" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="I13" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="J13" s="29">
+      <c r="J14" s="1">
         <v>1</v>
       </c>
-      <c r="K13" s="32">
-        <v>1.2</v>
-      </c>
-      <c r="L13" s="29">
-        <v>0.1</v>
-      </c>
-      <c r="M13" s="32">
+      <c r="K14" s="33">
+        <v>1.06</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="M14" s="33">
         <v>1</v>
       </c>
-      <c r="N13" s="32"/>
-    </row>
-    <row r="14" spans="2:14">
-      <c r="D14" s="32" t="s">
+      <c r="N14" s="33"/>
+    </row>
+    <row r="15" spans="2:14">
+      <c r="D15" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="E14" s="29"/>
-      <c r="F14" s="32" t="s">
+      <c r="E15" s="1"/>
+      <c r="F15" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G15" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="I15" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="H14" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="I14" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="J14" s="29">
+      <c r="J15" s="1">
         <v>1</v>
       </c>
-      <c r="K14" s="32">
+      <c r="K15" s="33">
         <v>1.06</v>
       </c>
-      <c r="L14" s="29">
-        <v>0.15</v>
-      </c>
-      <c r="M14" s="32">
+      <c r="L15" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="M15" s="33">
         <v>1</v>
       </c>
-      <c r="N14" s="32"/>
-    </row>
-    <row r="15" spans="2:14">
-      <c r="D15" s="32" t="s">
+      <c r="N15" s="33"/>
+    </row>
+    <row r="16" ht="16" spans="2:14">
+      <c r="D16" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="32" t="s">
+      <c r="E16" s="1"/>
+      <c r="F16" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="G15" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="H15" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="I15" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="J15" s="29">
-        <v>1</v>
-      </c>
-      <c r="K15" s="32">
-        <v>1.06</v>
-      </c>
-      <c r="L15" s="29">
-        <v>0.3</v>
-      </c>
-      <c r="M15" s="32">
-        <v>1</v>
-      </c>
-      <c r="N15" s="32"/>
-    </row>
-    <row r="16" ht="16" spans="2:14">
-      <c r="D16" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="G16" s="29" t="str">
+      <c r="G16" s="1" t="str">
         <f xml:space="preserve">G15</f>
         <v>CAP,GROWTH</v>
       </c>
-      <c r="H16" s="29" t="str">
+      <c r="H16" s="1" t="str">
         <f xml:space="preserve">H15</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I16" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="J16" s="29">
+      <c r="I16" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="J16" s="1">
         <f t="shared" ref="J16:L16" si="0" xml:space="preserve">J12</f>
         <v>1</v>
       </c>
-      <c r="K16" s="29">
+      <c r="K16" s="1">
         <f t="shared" si="0"/>
         <v>1.12</v>
       </c>
-      <c r="L16" s="29">
+      <c r="L16" s="1">
         <f t="shared" si="0"/>
         <v>0.03</v>
       </c>
-      <c r="M16" s="29">
+      <c r="M16" s="1">
         <f xml:space="preserve">M15</f>
         <v>1</v>
       </c>
-      <c r="N16" s="29"/>
+      <c r="N16" s="1"/>
     </row>
     <row r="17" ht="16" spans="4:14">
-      <c r="D17" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="E17" s="29"/>
-      <c r="F17" s="33" t="s">
-        <v>102</v>
-      </c>
-      <c r="G17" s="29" t="str">
+      <c r="D17" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="G17" s="1" t="str">
         <f t="shared" ref="G17:M17" si="1" xml:space="preserve">G16</f>
         <v>CAP,GROWTH</v>
       </c>
-      <c r="H17" s="29" t="str">
+      <c r="H17" s="1" t="str">
         <f t="shared" si="1"/>
         <v>2025, 2150</v>
       </c>
-      <c r="I17" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="J17" s="29">
+      <c r="I17" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="J17" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K17" s="29">
+      <c r="K17" s="1">
         <f t="shared" si="1"/>
         <v>1.12</v>
       </c>
-      <c r="L17" s="29">
+      <c r="L17" s="1">
         <f t="shared" si="1"/>
         <v>0.03</v>
       </c>
-      <c r="M17" s="29">
+      <c r="M17" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N17" s="29"/>
+      <c r="N17" s="1"/>
     </row>
     <row r="18" ht="16" spans="4:14">
-      <c r="D18" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18" s="29"/>
-      <c r="F18" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="G18" s="29" t="str">
+      <c r="D18" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" s="1" t="str">
         <f xml:space="preserve">G17</f>
         <v>CAP,GROWTH</v>
       </c>
-      <c r="H18" s="29" t="str">
+      <c r="H18" s="1" t="str">
         <f xml:space="preserve">H17</f>
         <v>2025, 2150</v>
       </c>
-      <c r="I18" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="J18" s="29">
+      <c r="I18" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="J18" s="1">
         <v>1</v>
       </c>
-      <c r="K18" s="29">
+      <c r="K18" s="1">
         <v>1</v>
       </c>
-      <c r="L18" s="29">
+      <c r="L18" s="1">
         <v>0</v>
       </c>
-      <c r="M18" s="29">
+      <c r="M18" s="1">
         <v>1</v>
       </c>
-      <c r="N18" s="29"/>
+      <c r="N18" s="1"/>
     </row>
     <row r="25" spans="4:14">
       <c r="K25" t="s">
+        <v>103</v>
+      </c>
+      <c r="L25" s="24" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="4:14">
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="35"/>
+      <c r="N27" s="35"/>
+    </row>
+    <row r="28" spans="4:14">
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="35"/>
+    </row>
+    <row r="29" spans="4:14">
+      <c r="D29" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="G29" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="H29" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="I29" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="J29" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="K29" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="L29" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="M29" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="N29" s="35" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" ht="16" spans="4:14">
+      <c r="D30" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="L25" s="22" t="s">
+      <c r="E30" s="35"/>
+      <c r="F30" s="36" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="27" spans="4:14">
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="34"/>
-      <c r="K27" s="34"/>
-      <c r="L27" s="34"/>
-      <c r="M27" s="34"/>
-      <c r="N27" s="34"/>
-    </row>
-    <row r="28" spans="4:14">
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-    </row>
-    <row r="29" spans="4:14">
-      <c r="D29" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="F29" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="G29" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="H29" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="I29" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="J29" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="K29" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="L29" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="M29" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="N29" s="34" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" ht="16" spans="4:14">
-      <c r="D30" s="34" t="s">
+      <c r="G30" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="H30" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="34"/>
-      <c r="F30" s="35" t="s">
+      <c r="I30" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="G30" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H30" s="34" t="s">
+      <c r="J30" s="35">
+        <v>1</v>
+      </c>
+      <c r="K30" s="35">
+        <v>1</v>
+      </c>
+      <c r="L30" s="35">
+        <v>0.01</v>
+      </c>
+      <c r="M30" s="35">
+        <v>1</v>
+      </c>
+      <c r="N30" s="35"/>
+    </row>
+    <row r="31" ht="16" spans="4:14">
+      <c r="D31" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="I30" s="34" t="s">
+      <c r="E31" s="35"/>
+      <c r="F31" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="34">
+      <c r="G31" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="H31" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="I31" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="J31" s="35">
         <v>1</v>
       </c>
-      <c r="K30" s="34">
+      <c r="K31" s="35">
         <v>1</v>
       </c>
-      <c r="L30" s="34">
-        <v>0.01</v>
-      </c>
-      <c r="M30" s="34">
-        <v>1</v>
-      </c>
-      <c r="N30" s="34"/>
-    </row>
-    <row r="31" ht="16" spans="4:14">
-      <c r="D31" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="E31" s="34"/>
-      <c r="F31" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="G31" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H31" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="I31" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="J31" s="34">
-        <v>1</v>
-      </c>
-      <c r="K31" s="34">
-        <v>1</v>
-      </c>
-      <c r="L31" s="34">
+      <c r="L31" s="35">
         <f t="shared" ref="L31:L36" si="2" xml:space="preserve">L30</f>
         <v>0.01</v>
       </c>
-      <c r="M31" s="34">
+      <c r="M31" s="35">
         <v>1</v>
       </c>
-      <c r="N31" s="34"/>
+      <c r="N31" s="35"/>
     </row>
     <row r="32" ht="16" spans="4:14">
-      <c r="D32" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="E32" s="34"/>
-      <c r="F32" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="G32" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H32" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="I32" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="J32" s="34">
+      <c r="D32" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="E32" s="35"/>
+      <c r="F32" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="G32" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="H32" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="I32" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="J32" s="35">
         <v>1</v>
       </c>
-      <c r="K32" s="34">
+      <c r="K32" s="35">
         <v>1</v>
       </c>
-      <c r="L32" s="34">
+      <c r="L32" s="35">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M32" s="34">
+      <c r="M32" s="35">
         <v>1</v>
       </c>
-      <c r="N32" s="34"/>
+      <c r="N32" s="35"/>
     </row>
     <row r="33" ht="16" spans="4:14">
-      <c r="D33" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="E33" s="34"/>
-      <c r="F33" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="G33" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H33" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="I33" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="J33" s="34">
+      <c r="D33" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="E33" s="35"/>
+      <c r="F33" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="G33" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="H33" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="I33" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="J33" s="35">
         <v>1</v>
       </c>
-      <c r="K33" s="34">
+      <c r="K33" s="35">
         <f xml:space="preserve">K32</f>
         <v>1</v>
       </c>
-      <c r="L33" s="34">
+      <c r="L33" s="35">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M33" s="34">
+      <c r="M33" s="35">
         <v>1</v>
       </c>
-      <c r="N33" s="34"/>
+      <c r="N33" s="35"/>
     </row>
     <row r="34" ht="16" spans="4:14">
-      <c r="D34" s="34" t="s">
-        <v>117</v>
-      </c>
-      <c r="E34" s="34"/>
-      <c r="F34" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="G34" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H34" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="I34" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="J34" s="34">
+      <c r="D34" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="E34" s="35"/>
+      <c r="F34" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="G34" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="H34" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="I34" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="J34" s="35">
         <v>1</v>
       </c>
-      <c r="K34" s="34">
+      <c r="K34" s="35">
         <f xml:space="preserve">K33</f>
         <v>1</v>
       </c>
-      <c r="L34" s="34">
+      <c r="L34" s="35">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M34" s="34">
+      <c r="M34" s="35">
         <v>1</v>
       </c>
-      <c r="N34" s="34"/>
+      <c r="N34" s="35"/>
     </row>
     <row r="35" ht="16" spans="4:14">
-      <c r="D35" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="E35" s="34"/>
-      <c r="F35" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="G35" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H35" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="I35" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="J35" s="34">
+      <c r="D35" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="E35" s="35"/>
+      <c r="F35" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="G35" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="H35" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="I35" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="J35" s="35">
         <v>1</v>
       </c>
-      <c r="K35" s="34">
+      <c r="K35" s="35">
         <f xml:space="preserve">K34</f>
         <v>1</v>
       </c>
-      <c r="L35" s="34">
+      <c r="L35" s="35">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M35" s="34">
+      <c r="M35" s="35">
         <v>1</v>
       </c>
-      <c r="N35" s="34"/>
+      <c r="N35" s="35"/>
     </row>
     <row r="36" ht="16" spans="4:14">
-      <c r="D36" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="E36" s="34"/>
-      <c r="F36" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="G36" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H36" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="I36" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="J36" s="34">
+      <c r="D36" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="E36" s="35"/>
+      <c r="F36" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="G36" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="H36" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="I36" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="J36" s="35">
         <v>1</v>
       </c>
-      <c r="K36" s="34">
+      <c r="K36" s="35">
         <f xml:space="preserve">K35</f>
         <v>1</v>
       </c>
-      <c r="L36" s="34">
+      <c r="L36" s="35">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="M36" s="34">
+      <c r="M36" s="35">
         <v>1</v>
       </c>
-      <c r="N36" s="34"/>
+      <c r="N36" s="35"/>
     </row>
     <row r="37" ht="16" spans="4:14">
-      <c r="D37" s="37" t="s">
+      <c r="D37" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="E37" s="38"/>
+      <c r="F37" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="G37" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="H37" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="E37" s="37"/>
-      <c r="F37" s="38" t="s">
+      <c r="I37" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="J37" s="38">
+        <v>1</v>
+      </c>
+      <c r="K37" s="38">
+        <v>1</v>
+      </c>
+      <c r="L37" s="38">
+        <v>0</v>
+      </c>
+      <c r="M37" s="38">
+        <v>3</v>
+      </c>
+      <c r="N37" s="35"/>
+    </row>
+    <row r="38" ht="16" spans="4:14">
+      <c r="D38" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="G37" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="H37" s="37" t="s">
+      <c r="F38" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="I37" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="J37" s="37">
-        <v>1</v>
-      </c>
-      <c r="K37" s="37">
-        <v>1</v>
-      </c>
-      <c r="L37" s="37">
-        <v>0</v>
-      </c>
-      <c r="M37" s="37">
-        <v>3</v>
-      </c>
-      <c r="N37" s="34"/>
-    </row>
-    <row r="38" ht="16" spans="4:14">
-      <c r="D38" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="F38" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="G38" s="37" t="s">
-        <v>84</v>
+      <c r="G38" s="38" t="s">
+        <v>82</v>
       </c>
       <c r="H38" t="str">
         <f xml:space="preserve">H37</f>
         <v>2019, 2150</v>
       </c>
       <c r="I38" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -4505,469 +4526,469 @@
       <c r="M38">
         <v>3</v>
       </c>
-      <c r="N38" s="34"/>
+      <c r="N38" s="35"/>
     </row>
     <row r="39" ht="16" spans="4:14">
-      <c r="D39" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="E39" s="40"/>
-      <c r="F39" s="38" t="s">
-        <v>129</v>
-      </c>
-      <c r="G39" s="37" t="s">
-        <v>84</v>
+      <c r="D39" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="E39" s="41"/>
+      <c r="F39" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="G39" s="38" t="s">
+        <v>82</v>
       </c>
       <c r="H39" t="str">
         <f t="shared" ref="H39:M39" si="3" xml:space="preserve">H38</f>
         <v>2019, 2150</v>
       </c>
-      <c r="I39" s="40" t="str">
+      <c r="I39" s="41" t="str">
         <f t="shared" si="3"/>
         <v>UP</v>
       </c>
-      <c r="J39" s="40">
+      <c r="J39" s="41">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K39" s="40">
+      <c r="K39" s="41">
         <f t="shared" si="3"/>
         <v>1.1</v>
       </c>
-      <c r="L39" s="40">
+      <c r="L39" s="41">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M39" s="40">
+      <c r="M39" s="41">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="N39" s="40"/>
+      <c r="N39" s="41"/>
     </row>
     <row r="40" ht="16" spans="4:14">
-      <c r="D40" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="E40" s="40"/>
-      <c r="F40" s="38" t="s">
-        <v>131</v>
-      </c>
-      <c r="G40" s="37" t="s">
-        <v>84</v>
+      <c r="D40" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="E40" s="41"/>
+      <c r="F40" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="G40" s="38" t="s">
+        <v>82</v>
       </c>
       <c r="H40" t="str">
         <f t="shared" ref="H40:M40" si="4" xml:space="preserve">H39</f>
         <v>2019, 2150</v>
       </c>
-      <c r="I40" s="40" t="str">
+      <c r="I40" s="41" t="str">
         <f t="shared" si="4"/>
         <v>UP</v>
       </c>
-      <c r="J40" s="40">
+      <c r="J40" s="41">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="K40" s="40">
+      <c r="K40" s="41">
         <f t="shared" si="4"/>
         <v>1.1</v>
       </c>
-      <c r="L40" s="40">
+      <c r="L40" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M40" s="40">
+      <c r="M40" s="41">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="N40" s="40"/>
+      <c r="N40" s="41"/>
     </row>
     <row r="41" ht="16" spans="4:14">
-      <c r="D41" s="39" t="s">
-        <v>132</v>
-      </c>
-      <c r="E41" s="40"/>
-      <c r="F41" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="G41" s="37" t="s">
-        <v>84</v>
+      <c r="D41" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="E41" s="41"/>
+      <c r="F41" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="G41" s="38" t="s">
+        <v>82</v>
       </c>
       <c r="H41" t="str">
         <f t="shared" ref="H41:M41" si="5" xml:space="preserve">H40</f>
         <v>2019, 2150</v>
       </c>
-      <c r="I41" s="40" t="str">
+      <c r="I41" s="41" t="str">
         <f t="shared" si="5"/>
         <v>UP</v>
       </c>
-      <c r="J41" s="40">
+      <c r="J41" s="41">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="K41" s="40">
+      <c r="K41" s="41">
         <f t="shared" si="5"/>
         <v>1.1</v>
       </c>
-      <c r="L41" s="40">
+      <c r="L41" s="41">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M41" s="40">
+      <c r="M41" s="41">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="N41" s="40"/>
+      <c r="N41" s="41"/>
     </row>
     <row r="42" ht="16" spans="4:14">
-      <c r="D42" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="F42" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="G42" s="37" t="s">
-        <v>84</v>
+      <c r="D42" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F42" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G42" s="38" t="s">
+        <v>82</v>
       </c>
       <c r="H42" t="str">
         <f t="shared" ref="H42:M42" si="6" xml:space="preserve">H41</f>
         <v>2019, 2150</v>
       </c>
-      <c r="I42" s="40" t="str">
+      <c r="I42" s="41" t="str">
         <f t="shared" si="6"/>
         <v>UP</v>
       </c>
-      <c r="J42" s="40">
+      <c r="J42" s="41">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="K42" s="40">
+      <c r="K42" s="41">
         <f t="shared" si="6"/>
         <v>1.1</v>
       </c>
-      <c r="L42" s="40">
+      <c r="L42" s="41">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M42" s="40">
+      <c r="M42" s="41">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="N42" s="40"/>
+      <c r="N42" s="41"/>
     </row>
     <row r="43" spans="4:14">
-      <c r="D43" s="37" t="s">
+      <c r="D43" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="E43" s="38"/>
+      <c r="F43" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="G43" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="H43" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="I43" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="J43" s="38">
+        <v>1</v>
+      </c>
+      <c r="K43" s="38">
+        <v>1</v>
+      </c>
+      <c r="L43" s="38">
+        <v>0</v>
+      </c>
+      <c r="M43" s="38">
+        <v>3</v>
+      </c>
+      <c r="N43" s="41"/>
+    </row>
+    <row r="44" spans="4:14">
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="41"/>
+    </row>
+    <row r="45" spans="4:14">
+      <c r="D45" s="41"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="41"/>
+      <c r="I45" s="41"/>
+      <c r="J45" s="41"/>
+      <c r="K45" s="41"/>
+      <c r="L45" s="41"/>
+      <c r="M45" s="41"/>
+      <c r="N45" s="41"/>
+    </row>
+    <row r="46" spans="4:14">
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+      <c r="N46" s="41"/>
+    </row>
+    <row r="47" spans="4:14">
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="41"/>
+    </row>
+    <row r="48" spans="4:14">
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+      <c r="N48" s="41"/>
+    </row>
+    <row r="49" spans="4:14">
+      <c r="N49" s="35"/>
+    </row>
+    <row r="50" spans="4:14">
+      <c r="D50" s="35"/>
+      <c r="E50" s="35"/>
+      <c r="F50" s="35"/>
+      <c r="G50" s="35"/>
+      <c r="H50" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="I50" s="35"/>
+      <c r="J50" s="35"/>
+      <c r="K50" s="35"/>
+      <c r="L50" s="35"/>
+      <c r="M50" s="35"/>
+      <c r="N50" s="35"/>
+    </row>
+    <row r="51" ht="16" spans="4:14">
+      <c r="D51" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="E51" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="E43" s="37"/>
-      <c r="F43" s="41" t="s">
+      <c r="F51" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="G51" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="H51" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="I51" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="J51" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="G43" s="37" t="s">
+      <c r="K51" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="L51" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="M51" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="N51" s="35" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="4:14">
+      <c r="D52" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="E52" s="35"/>
+      <c r="F52" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G52" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="H52" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="I52" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="H43" s="37" t="s">
-        <v>125</v>
-      </c>
-      <c r="I43" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="J43" s="37">
+      <c r="J52" s="35">
         <v>1</v>
       </c>
-      <c r="K43" s="37">
+      <c r="K52" s="35">
         <v>1</v>
       </c>
-      <c r="L43" s="37">
+      <c r="L52" s="35">
         <v>0</v>
       </c>
-      <c r="M43" s="37">
-        <v>3</v>
-      </c>
-      <c r="N43" s="40"/>
-    </row>
-    <row r="44" spans="4:14">
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="40"/>
-    </row>
-    <row r="45" spans="4:14">
-      <c r="D45" s="40"/>
-      <c r="E45" s="40"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="40"/>
-      <c r="H45" s="40"/>
-      <c r="I45" s="40"/>
-      <c r="J45" s="40"/>
-      <c r="K45" s="40"/>
-      <c r="L45" s="40"/>
-      <c r="M45" s="40"/>
-      <c r="N45" s="40"/>
-    </row>
-    <row r="46" spans="4:14">
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="40"/>
-    </row>
-    <row r="47" spans="4:14">
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="40"/>
-    </row>
-    <row r="48" spans="4:14">
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="40"/>
-    </row>
-    <row r="49" spans="4:14">
-      <c r="N49" s="34"/>
-    </row>
-    <row r="50" spans="4:14">
-      <c r="D50" s="34"/>
-      <c r="E50" s="34"/>
-      <c r="F50" s="34"/>
-      <c r="G50" s="34"/>
-      <c r="H50" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="I50" s="34"/>
-      <c r="J50" s="34"/>
-      <c r="K50" s="34"/>
-      <c r="L50" s="34"/>
-      <c r="M50" s="34"/>
-      <c r="N50" s="34"/>
-    </row>
-    <row r="51" ht="16" spans="4:14">
-      <c r="D51" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="E51" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="F51" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="G51" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="H51" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="I51" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="J51" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="K51" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="L51" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="M51" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="N51" s="34" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="52" spans="4:14">
-      <c r="D52" s="34" t="s">
+      <c r="M52" s="35">
+        <v>5</v>
+      </c>
+      <c r="N52" s="35"/>
+    </row>
+    <row r="53" spans="4:14">
+      <c r="D53" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="E53" s="35"/>
+      <c r="F53" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G53" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="E52" s="34"/>
-      <c r="F52" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="G52" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="H52" s="40" t="s">
-        <v>144</v>
-      </c>
-      <c r="I52" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="J52" s="34">
+      <c r="H53" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="I53" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="J53" s="35">
         <v>1</v>
       </c>
-      <c r="K52" s="34">
+      <c r="K53" s="35">
         <v>1</v>
       </c>
-      <c r="L52" s="34">
-        <v>0</v>
-      </c>
-      <c r="M52" s="34">
-        <v>5</v>
-      </c>
-      <c r="N52" s="34"/>
-    </row>
-    <row r="53" spans="4:14">
-      <c r="D53" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="E53" s="34"/>
-      <c r="F53" s="43" t="s">
-        <v>146</v>
-      </c>
-      <c r="G53" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="H53" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="I53" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="J53" s="34">
-        <v>1</v>
-      </c>
-      <c r="K53" s="34">
-        <v>1</v>
-      </c>
-      <c r="L53" s="34">
+      <c r="L53" s="35">
         <f t="shared" ref="L53:L55" si="7" xml:space="preserve">L52</f>
         <v>0</v>
       </c>
-      <c r="M53" s="34">
+      <c r="M53" s="35">
         <v>5</v>
       </c>
-      <c r="N53" s="34"/>
+      <c r="N53" s="35"/>
     </row>
     <row r="54" spans="4:14">
-      <c r="D54" s="34" t="s">
+      <c r="D54" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="E54" s="35"/>
+      <c r="F54" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G54" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="H54" s="41" t="s">
         <v>147</v>
       </c>
-      <c r="E54" s="34"/>
-      <c r="F54" s="43" t="s">
-        <v>148</v>
-      </c>
-      <c r="G54" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="H54" s="40" t="s">
-        <v>149</v>
-      </c>
-      <c r="I54" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="J54" s="34">
+      <c r="I54" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="J54" s="35">
         <v>1</v>
       </c>
-      <c r="K54" s="34">
+      <c r="K54" s="35">
         <v>1</v>
       </c>
-      <c r="L54" s="34">
+      <c r="L54" s="35">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M54" s="34">
+      <c r="M54" s="35">
         <v>5</v>
       </c>
-      <c r="N54" s="34"/>
+      <c r="N54" s="35"/>
     </row>
     <row r="55" ht="16" spans="4:14">
-      <c r="D55" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="E55" s="34"/>
-      <c r="F55" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="G55" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="H55" s="40" t="s">
-        <v>144</v>
-      </c>
-      <c r="I55" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="J55" s="34">
+      <c r="D55" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="E55" s="35"/>
+      <c r="F55" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="G55" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="H55" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="I55" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="J55" s="35">
         <v>1</v>
       </c>
-      <c r="K55" s="34">
+      <c r="K55" s="35">
         <v>1</v>
       </c>
-      <c r="L55" s="34">
+      <c r="L55" s="35">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M55" s="34">
+      <c r="M55" s="35">
         <v>5</v>
       </c>
-      <c r="N55" s="34"/>
+      <c r="N55" s="35"/>
     </row>
     <row r="56" ht="16" spans="4:14">
-      <c r="D56" s="34"/>
-      <c r="E56" s="34"/>
-      <c r="F56" s="35"/>
-      <c r="G56" s="34"/>
-      <c r="H56" s="40"/>
-      <c r="I56" s="34"/>
-      <c r="J56" s="34"/>
-      <c r="K56" s="34"/>
-      <c r="L56" s="34"/>
-      <c r="M56" s="34"/>
-      <c r="N56" s="34"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="36"/>
+      <c r="G56" s="35"/>
+      <c r="H56" s="41"/>
+      <c r="I56" s="35"/>
+      <c r="J56" s="35"/>
+      <c r="K56" s="35"/>
+      <c r="L56" s="35"/>
+      <c r="M56" s="35"/>
+      <c r="N56" s="35"/>
     </row>
     <row r="57" ht="16" spans="4:14">
-      <c r="D57" s="34"/>
-      <c r="E57" s="34"/>
-      <c r="F57" s="35"/>
-      <c r="G57" s="34"/>
-      <c r="H57" s="34"/>
-      <c r="I57" s="34"/>
-      <c r="J57" s="34"/>
-      <c r="K57" s="34"/>
-      <c r="L57" s="34"/>
-      <c r="M57" s="34"/>
-      <c r="N57" s="34"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="36"/>
+      <c r="G57" s="35"/>
+      <c r="H57" s="35"/>
+      <c r="I57" s="35"/>
+      <c r="J57" s="35"/>
+      <c r="K57" s="35"/>
+      <c r="L57" s="35"/>
+      <c r="M57" s="35"/>
+      <c r="N57" s="35"/>
     </row>
     <row r="58" ht="16" spans="4:14">
-      <c r="D58" s="34"/>
-      <c r="E58" s="34"/>
-      <c r="F58" s="35"/>
-      <c r="G58" s="34"/>
-      <c r="H58" s="34"/>
-      <c r="I58" s="34"/>
-      <c r="J58" s="34"/>
-      <c r="K58" s="34"/>
-      <c r="L58" s="34"/>
-      <c r="M58" s="34"/>
-      <c r="N58" s="34"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="36"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="35"/>
+      <c r="I58" s="35"/>
+      <c r="J58" s="35"/>
+      <c r="K58" s="35"/>
+      <c r="L58" s="35"/>
+      <c r="M58" s="35"/>
+      <c r="N58" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5001,26 +5022,26 @@
       </c>
     </row>
     <row r="11" spans="6:18">
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
     </row>
     <row r="12" spans="6:18">
-      <c r="K12" s="1"/>
-      <c r="L12" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
     </row>
     <row r="13" spans="6:18">
       <c r="F13" t="s">
@@ -5038,177 +5059,177 @@
       <c r="J13" t="s">
         <v>33</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="L13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="N13" s="1" t="s">
+      <c r="M13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N13" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="O13" s="1" t="s">
+      <c r="O13" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="P13" s="1" t="s">
+      <c r="P13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Q13" s="1" t="s">
+      <c r="Q13" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="R13" s="1"/>
+      <c r="R13" s="2"/>
     </row>
     <row r="14" spans="6:18">
       <c r="F14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H14" t="s">
-        <v>154</v>
-      </c>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1">
+        <v>152</v>
+      </c>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2">
         <v>0.25</v>
       </c>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1">
+      <c r="N14" s="2"/>
+      <c r="O14" s="2">
         <v>0</v>
       </c>
-      <c r="P14" s="1">
+      <c r="P14" s="2">
         <v>5</v>
       </c>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
     </row>
     <row r="15" spans="6:18">
       <c r="H15" t="s">
-        <v>155</v>
-      </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1">
+        <v>153</v>
+      </c>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2">
         <v>-1</v>
       </c>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
     </row>
     <row r="16" spans="6:18">
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
     </row>
     <row r="17" spans="6:18">
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
     </row>
     <row r="18" spans="6:18">
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
     </row>
     <row r="19" spans="6:18">
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
     </row>
     <row r="20" spans="6:18">
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
     </row>
     <row r="21" spans="6:18">
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
     </row>
     <row r="22" spans="6:18">
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
     </row>
     <row r="23" spans="6:18">
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
     </row>
     <row r="24" spans="6:18">
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
     </row>
     <row r="25" spans="6:18">
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
     </row>
     <row r="26" spans="6:18">
-      <c r="K26" s="1"/>
-      <c r="L26" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
     </row>
     <row r="27" spans="6:18">
       <c r="F27" t="s">
@@ -5226,126 +5247,126 @@
       <c r="J27" t="s">
         <v>33</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="K27" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="L27" s="1" t="s">
+      <c r="L27" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M27" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="N27" s="1" t="s">
+      <c r="M27" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N27" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="O27" s="1" t="s">
+      <c r="O27" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="P27" s="1" t="s">
+      <c r="P27" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Q27" s="1" t="s">
+      <c r="Q27" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="R27" s="1"/>
+      <c r="R27" s="2"/>
     </row>
     <row r="28" ht="16" spans="6:18">
       <c r="F28" t="s">
-        <v>156</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1">
+        <v>154</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2">
         <v>-0.1</v>
       </c>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1">
+      <c r="N28" s="2"/>
+      <c r="O28" s="2">
         <v>0</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P28" s="2">
         <v>5</v>
       </c>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
     </row>
     <row r="29" spans="6:18">
       <c r="H29" t="s">
-        <v>158</v>
-      </c>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1">
+        <v>156</v>
+      </c>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2">
         <v>1</v>
       </c>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
     </row>
     <row r="30" spans="6:18">
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
     </row>
     <row r="31" spans="6:18">
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
     </row>
     <row r="32" spans="6:18">
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
     </row>
     <row r="33" spans="6:18">
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-      <c r="R33" s="1"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
     </row>
     <row r="34" spans="6:18">
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
-      <c r="R34" s="1"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
     </row>
     <row r="35" spans="6:18">
-      <c r="K35" s="1"/>
-      <c r="L35" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
     </row>
     <row r="36" spans="6:18">
       <c r="F36" t="s">
@@ -5363,579 +5384,579 @@
       <c r="J36" t="s">
         <v>33</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="K36" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="1" t="s">
+      <c r="L36" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M36" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="N36" s="1" t="s">
+      <c r="M36" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N36" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="O36" s="1" t="s">
+      <c r="O36" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="P36" s="1" t="s">
+      <c r="P36" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Q36" s="1" t="s">
+      <c r="Q36" s="2" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="37" spans="6:18">
       <c r="F37" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H37" t="s">
-        <v>160</v>
-      </c>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1">
+        <v>158</v>
+      </c>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2">
         <v>-0.1</v>
       </c>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1">
+      <c r="N37" s="2"/>
+      <c r="O37" s="2">
         <v>0</v>
       </c>
-      <c r="P37" s="1">
+      <c r="P37" s="2">
         <v>5</v>
       </c>
-      <c r="Q37" s="1"/>
+      <c r="Q37" s="2"/>
     </row>
     <row r="38" spans="6:18">
       <c r="H38" t="s">
+        <v>159</v>
+      </c>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2">
+        <v>1</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="51" spans="6:44">
+      <c r="G51" s="15"/>
+      <c r="H51" s="15"/>
+      <c r="I51" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="17"/>
+      <c r="M51" s="17"/>
+      <c r="N51" s="17"/>
+      <c r="O51" s="17"/>
+      <c r="P51" s="17"/>
+      <c r="Q51" s="17"/>
+      <c r="R51" s="18"/>
+      <c r="S51" s="18"/>
+      <c r="T51" s="18"/>
+      <c r="U51" s="18"/>
+      <c r="V51" s="18"/>
+      <c r="W51" s="18"/>
+      <c r="X51" s="18"/>
+      <c r="Y51" s="18"/>
+      <c r="Z51" s="18"/>
+      <c r="AA51" s="18"/>
+      <c r="AB51" s="18"/>
+      <c r="AC51" s="18"/>
+      <c r="AD51" s="18"/>
+      <c r="AE51" s="18"/>
+      <c r="AF51" s="18"/>
+      <c r="AG51" s="18"/>
+      <c r="AH51" s="18"/>
+      <c r="AI51" s="18"/>
+      <c r="AJ51" s="18"/>
+      <c r="AK51" s="18"/>
+      <c r="AL51" s="18"/>
+      <c r="AM51" s="18"/>
+    </row>
+    <row r="52" spans="6:44">
+      <c r="G52" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="H52" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1">
-        <v>1</v>
-      </c>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-    </row>
-    <row r="51" spans="6:44">
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="14" t="s">
+      <c r="I52" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="J51" s="15"/>
-      <c r="K51" s="15"/>
-      <c r="L51" s="15"/>
-      <c r="M51" s="15"/>
-      <c r="N51" s="15"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="15"/>
-      <c r="R51" s="16"/>
-      <c r="S51" s="16"/>
-      <c r="T51" s="16"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="16"/>
-      <c r="W51" s="16"/>
-      <c r="X51" s="16"/>
-      <c r="Y51" s="16"/>
-      <c r="Z51" s="16"/>
-      <c r="AA51" s="16"/>
-      <c r="AB51" s="16"/>
-      <c r="AC51" s="16"/>
-      <c r="AD51" s="16"/>
-      <c r="AE51" s="16"/>
-      <c r="AF51" s="16"/>
-      <c r="AG51" s="16"/>
-      <c r="AH51" s="16"/>
-      <c r="AI51" s="16"/>
-      <c r="AJ51" s="16"/>
-      <c r="AK51" s="16"/>
-      <c r="AL51" s="16"/>
-      <c r="AM51" s="16"/>
-    </row>
-    <row r="52" spans="6:44">
-      <c r="G52" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="H52" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="I52" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="J52" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="K52" s="13" t="s">
+      <c r="K52" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="L52" s="13" t="s">
+      <c r="L52" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="M52" s="15" t="s">
+      <c r="M52" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="N52" s="13" t="s">
+      <c r="N52" s="15" t="s">
         <v>61</v>
       </c>
       <c r="O52" t="s">
         <v>62</v>
       </c>
-      <c r="P52" s="1" t="s">
+      <c r="P52" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="Q52" s="1" t="s">
+      <c r="Q52" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="T52" s="16"/>
-      <c r="U52" s="16"/>
-      <c r="V52" s="16"/>
-      <c r="W52" s="16"/>
-      <c r="X52" s="16"/>
-      <c r="Y52" s="16"/>
-      <c r="Z52" s="16"/>
-      <c r="AA52" s="16"/>
-      <c r="AB52" s="16"/>
-      <c r="AC52" s="16"/>
-      <c r="AD52" s="16"/>
-      <c r="AE52" s="16"/>
-      <c r="AF52" s="16"/>
-      <c r="AG52" s="16"/>
-      <c r="AH52" s="16"/>
-      <c r="AI52" s="16"/>
-      <c r="AJ52" s="16"/>
-      <c r="AK52" s="16"/>
-      <c r="AL52" s="16"/>
-      <c r="AM52" s="16"/>
-      <c r="AN52" s="16"/>
-      <c r="AO52" s="16"/>
-      <c r="AP52" s="16"/>
-      <c r="AQ52" s="16"/>
-      <c r="AR52" s="16"/>
+      <c r="T52" s="18"/>
+      <c r="U52" s="18"/>
+      <c r="V52" s="18"/>
+      <c r="W52" s="18"/>
+      <c r="X52" s="18"/>
+      <c r="Y52" s="18"/>
+      <c r="Z52" s="18"/>
+      <c r="AA52" s="18"/>
+      <c r="AB52" s="18"/>
+      <c r="AC52" s="18"/>
+      <c r="AD52" s="18"/>
+      <c r="AE52" s="18"/>
+      <c r="AF52" s="18"/>
+      <c r="AG52" s="18"/>
+      <c r="AH52" s="18"/>
+      <c r="AI52" s="18"/>
+      <c r="AJ52" s="18"/>
+      <c r="AK52" s="18"/>
+      <c r="AL52" s="18"/>
+      <c r="AM52" s="18"/>
+      <c r="AN52" s="18"/>
+      <c r="AO52" s="18"/>
+      <c r="AP52" s="18"/>
+      <c r="AQ52" s="18"/>
+      <c r="AR52" s="18"/>
     </row>
     <row r="53" ht="16" spans="6:44">
-      <c r="F53" s="18"/>
-      <c r="G53" s="13" t="s">
+      <c r="F53" s="20"/>
+      <c r="G53" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="H53" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="I53" s="21">
+        <v>2019</v>
+      </c>
+      <c r="J53" s="22">
+        <v>-1</v>
+      </c>
+      <c r="K53" s="15"/>
+      <c r="L53" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="M53" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="H53" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="I53" s="19">
-        <v>2019</v>
-      </c>
-      <c r="J53" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K53" s="13"/>
-      <c r="L53" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="M53" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="N53" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="O53" s="13">
+      <c r="N53" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="O53" s="15">
         <v>10</v>
       </c>
-      <c r="P53" s="1">
+      <c r="P53" s="2">
         <v>0</v>
       </c>
-      <c r="Q53" s="1">
+      <c r="Q53" s="2">
         <v>3</v>
       </c>
-      <c r="T53" s="16"/>
-      <c r="U53" s="16"/>
-      <c r="V53" s="16"/>
-      <c r="W53" s="16"/>
-      <c r="X53" s="16"/>
-      <c r="Y53" s="16"/>
-      <c r="Z53" s="16"/>
-      <c r="AA53" s="16"/>
-      <c r="AB53" s="16"/>
-      <c r="AC53" s="16"/>
-      <c r="AD53" s="16"/>
-      <c r="AE53" s="16"/>
-      <c r="AF53" s="16"/>
-      <c r="AG53" s="16"/>
-      <c r="AH53" s="16"/>
-      <c r="AI53" s="16"/>
-      <c r="AJ53" s="16"/>
-      <c r="AK53" s="16"/>
-      <c r="AL53" s="16"/>
-      <c r="AM53" s="16"/>
-      <c r="AN53" s="16"/>
-      <c r="AO53" s="16"/>
-      <c r="AP53" s="16"/>
-      <c r="AQ53" s="16"/>
-      <c r="AR53" s="16"/>
+      <c r="T53" s="18"/>
+      <c r="U53" s="18"/>
+      <c r="V53" s="18"/>
+      <c r="W53" s="18"/>
+      <c r="X53" s="18"/>
+      <c r="Y53" s="18"/>
+      <c r="Z53" s="18"/>
+      <c r="AA53" s="18"/>
+      <c r="AB53" s="18"/>
+      <c r="AC53" s="18"/>
+      <c r="AD53" s="18"/>
+      <c r="AE53" s="18"/>
+      <c r="AF53" s="18"/>
+      <c r="AG53" s="18"/>
+      <c r="AH53" s="18"/>
+      <c r="AI53" s="18"/>
+      <c r="AJ53" s="18"/>
+      <c r="AK53" s="18"/>
+      <c r="AL53" s="18"/>
+      <c r="AM53" s="18"/>
+      <c r="AN53" s="18"/>
+      <c r="AO53" s="18"/>
+      <c r="AP53" s="18"/>
+      <c r="AQ53" s="18"/>
+      <c r="AR53" s="18"/>
     </row>
     <row r="54" spans="6:44">
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="13"/>
-      <c r="K54" s="13"/>
+      <c r="G54" s="15"/>
+      <c r="H54" s="15"/>
+      <c r="I54" s="15"/>
+      <c r="J54" s="15"/>
+      <c r="K54" s="15"/>
     </row>
     <row r="55" spans="6:44">
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="13"/>
-      <c r="J55" s="13"/>
-      <c r="K55" s="13"/>
-      <c r="L55" s="13"/>
-      <c r="M55" s="13"/>
-      <c r="N55" s="13"/>
-      <c r="O55" s="13"/>
+      <c r="G55" s="15"/>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="15"/>
+      <c r="K55" s="15"/>
+      <c r="L55" s="15"/>
+      <c r="M55" s="15"/>
+      <c r="N55" s="15"/>
+      <c r="O55" s="15"/>
     </row>
     <row r="56" spans="6:44">
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="13"/>
-      <c r="J56" s="13"/>
-      <c r="K56" s="13"/>
-      <c r="L56" s="13"/>
-      <c r="M56" s="13"/>
-      <c r="N56" s="13"/>
-      <c r="O56" s="13"/>
+      <c r="G56" s="15"/>
+      <c r="H56" s="15"/>
+      <c r="I56" s="15"/>
+      <c r="J56" s="15"/>
+      <c r="K56" s="15"/>
+      <c r="L56" s="15"/>
+      <c r="M56" s="15"/>
+      <c r="N56" s="15"/>
+      <c r="O56" s="15"/>
     </row>
     <row r="61" spans="6:44">
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="14" t="s">
+      <c r="G61" s="15"/>
+      <c r="H61" s="15"/>
+      <c r="I61" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="J61" s="17"/>
+      <c r="K61" s="17"/>
+      <c r="L61" s="17"/>
+      <c r="M61" s="17"/>
+      <c r="N61" s="17"/>
+      <c r="O61" s="17"/>
+      <c r="P61" s="18"/>
+      <c r="Q61" s="18"/>
+    </row>
+    <row r="62" spans="6:44">
+      <c r="G62" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="H62" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="I62" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="J61" s="15"/>
-      <c r="K61" s="15"/>
-      <c r="L61" s="15"/>
-      <c r="M61" s="15"/>
-      <c r="N61" s="15"/>
-      <c r="O61" s="15"/>
-      <c r="P61" s="16"/>
-      <c r="Q61" s="16"/>
-    </row>
-    <row r="62" spans="6:44">
-      <c r="G62" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="H62" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="I62" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="J62" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="K62" s="13" t="s">
+      <c r="K62" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="L62" s="13" t="s">
+      <c r="L62" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="M62" s="15" t="s">
+      <c r="M62" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="N62" s="13" t="s">
+      <c r="N62" s="15" t="s">
         <v>61</v>
       </c>
       <c r="O62" t="s">
         <v>62</v>
       </c>
-      <c r="P62" s="1" t="s">
+      <c r="P62" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="Q62" s="1" t="s">
+      <c r="Q62" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="63" ht="16" spans="6:44">
-      <c r="G63" s="13" t="s">
+      <c r="G63" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="H63" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="I63" s="21">
+        <v>2019</v>
+      </c>
+      <c r="J63" s="22">
+        <v>-1</v>
+      </c>
+      <c r="K63" s="15"/>
+      <c r="L63" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="M63" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="N63" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="O63" s="15">
+        <v>10</v>
+      </c>
+      <c r="P63" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="6:44">
+      <c r="G64" s="15"/>
+      <c r="H64" s="15"/>
+      <c r="I64" s="15"/>
+      <c r="J64" s="15"/>
+      <c r="K64" s="15"/>
+    </row>
+    <row r="66" ht="15.25" spans="7:20">
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" s="2"/>
+      <c r="Q66" s="2"/>
+      <c r="T66" s="2"/>
+    </row>
+    <row r="67" ht="16" spans="7:20">
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" s="2"/>
+      <c r="Q67" s="2"/>
+      <c r="T67" s="2"/>
+    </row>
+    <row r="68" ht="15.25" spans="7:20">
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+      <c r="T68" s="2"/>
+    </row>
+    <row r="69" spans="7:20">
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" s="2"/>
+      <c r="Q69" s="2"/>
+      <c r="T69" s="2"/>
+    </row>
+    <row r="70" spans="7:20">
+      <c r="G70" s="24"/>
+      <c r="H70" s="24"/>
+      <c r="I70" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="J70" s="26"/>
+      <c r="K70" s="26"/>
+      <c r="L70" s="26"/>
+      <c r="M70" s="26"/>
+      <c r="N70" s="26"/>
+      <c r="O70" s="26"/>
+      <c r="P70" s="26"/>
+      <c r="Q70" s="26"/>
+      <c r="T70" s="2"/>
+    </row>
+    <row r="71" spans="7:20">
+      <c r="G71" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="H71" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="I71" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="J71" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="K71" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="L71" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="M71" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="N71" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="O71" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="P71" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q71" s="24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="72" ht="16" spans="7:20">
+      <c r="G72" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="H63" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="I63" s="19">
+      <c r="H72" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="I72" s="28">
         <v>2019</v>
       </c>
-      <c r="J63" s="20">
+      <c r="J72" s="29">
         <v>-1</v>
       </c>
-      <c r="K63" s="13"/>
-      <c r="L63" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="M63" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="N63" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="O63" s="13">
+      <c r="K72" s="24"/>
+      <c r="L72" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="M72" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="N72" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="O72" s="24">
         <v>10</v>
       </c>
-      <c r="P63" s="1">
+      <c r="P72" s="24">
         <v>0</v>
       </c>
-      <c r="Q63" s="1">
+      <c r="Q72" s="24">
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="6:44">
-      <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="13"/>
-      <c r="J64" s="13"/>
-      <c r="K64" s="13"/>
-    </row>
-    <row r="66" ht="15.25" spans="7:20">
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
-      <c r="M66" s="1"/>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
-      <c r="P66" s="1"/>
-      <c r="Q66" s="1"/>
-      <c r="T66" s="1"/>
-    </row>
-    <row r="67" ht="16" spans="7:20">
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
-      <c r="M67" s="1"/>
-      <c r="O67" s="1"/>
-      <c r="P67" s="1"/>
-      <c r="Q67" s="1"/>
-      <c r="T67" s="1"/>
-    </row>
-    <row r="68" ht="15.25" spans="7:20">
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-      <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
-      <c r="P68" s="1"/>
-      <c r="Q68" s="1"/>
-      <c r="T68" s="1"/>
-    </row>
-    <row r="69" spans="7:20">
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
-      <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
-      <c r="P69" s="1"/>
-      <c r="Q69" s="1"/>
-      <c r="T69" s="1"/>
-    </row>
-    <row r="70" spans="7:20">
-      <c r="G70" s="22"/>
-      <c r="H70" s="22"/>
-      <c r="I70" s="23" t="s">
+    <row r="73" spans="7:20">
+      <c r="G73" s="24"/>
+      <c r="H73" s="24"/>
+      <c r="I73" s="24"/>
+      <c r="J73" s="24"/>
+      <c r="K73" s="24"/>
+      <c r="L73" s="24"/>
+      <c r="M73" s="24"/>
+      <c r="N73" s="24"/>
+      <c r="O73" s="24"/>
+      <c r="P73" s="24"/>
+      <c r="Q73" s="24"/>
+    </row>
+    <row r="80" spans="7:20">
+      <c r="G80" s="15"/>
+      <c r="H80" s="15"/>
+      <c r="I80" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="J80" s="17"/>
+      <c r="K80" s="17"/>
+      <c r="L80" s="17"/>
+      <c r="M80" s="17"/>
+      <c r="N80" s="17"/>
+      <c r="O80" s="17"/>
+      <c r="P80" s="18"/>
+      <c r="Q80" s="18"/>
+    </row>
+    <row r="81" spans="7:17">
+      <c r="G81" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="H81" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="I81" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J81" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="J70" s="24"/>
-      <c r="K70" s="24"/>
-      <c r="L70" s="24"/>
-      <c r="M70" s="24"/>
-      <c r="N70" s="24"/>
-      <c r="O70" s="24"/>
-      <c r="P70" s="24"/>
-      <c r="Q70" s="24"/>
-      <c r="T70" s="1"/>
-    </row>
-    <row r="71" spans="7:20">
-      <c r="G71" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="H71" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="I71" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="J71" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="K71" s="22" t="s">
+      <c r="K81" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="L71" s="22" t="s">
+      <c r="L81" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="M71" s="24" t="s">
+      <c r="M81" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="N71" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="O71" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="P71" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q71" s="22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="72" ht="16" spans="7:20">
-      <c r="G72" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="H72" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="I72" s="26">
-        <v>2019</v>
-      </c>
-      <c r="J72" s="27">
-        <v>-1</v>
-      </c>
-      <c r="K72" s="22"/>
-      <c r="L72" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="M72" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="N72" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="O72" s="22">
-        <v>10</v>
-      </c>
-      <c r="P72" s="22">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="7:20">
-      <c r="G73" s="22"/>
-      <c r="H73" s="22"/>
-      <c r="I73" s="22"/>
-      <c r="J73" s="22"/>
-      <c r="K73" s="22"/>
-      <c r="L73" s="22"/>
-      <c r="M73" s="22"/>
-      <c r="N73" s="22"/>
-      <c r="O73" s="22"/>
-      <c r="P73" s="22"/>
-      <c r="Q73" s="22"/>
-    </row>
-    <row r="80" spans="7:20">
-      <c r="G80" s="13"/>
-      <c r="H80" s="13"/>
-      <c r="I80" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="J80" s="15"/>
-      <c r="K80" s="15"/>
-      <c r="L80" s="15"/>
-      <c r="M80" s="15"/>
-      <c r="N80" s="15"/>
-      <c r="O80" s="15"/>
-      <c r="P80" s="16"/>
-      <c r="Q80" s="16"/>
-    </row>
-    <row r="81" spans="7:17">
-      <c r="G81" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="H81" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="I81" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="J81" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="K81" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="L81" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="M81" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="N81" s="13" t="s">
+      <c r="N81" s="15" t="s">
         <v>61</v>
       </c>
       <c r="O81" t="s">
         <v>62</v>
       </c>
-      <c r="P81" s="1" t="s">
+      <c r="P81" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="Q81" s="1" t="s">
+      <c r="Q81" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="82" ht="16" spans="7:17">
-      <c r="G82" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="H82" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="I82" s="19">
+      <c r="G82" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="H82" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="I82" s="21">
         <v>2019</v>
       </c>
-      <c r="J82" s="20">
+      <c r="J82" s="22">
         <v>-1</v>
       </c>
-      <c r="K82" s="13"/>
-      <c r="L82" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="M82" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="N82" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="O82" s="13">
+      <c r="K82" s="15"/>
+      <c r="L82" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="M82" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="N82" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="O82" s="15">
         <v>10</v>
       </c>
-      <c r="P82" s="1">
+      <c r="P82" s="2">
         <v>0</v>
       </c>
-      <c r="Q82" s="1">
+      <c r="Q82" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="83" spans="7:17">
-      <c r="G83" s="13"/>
-      <c r="H83" s="13"/>
-      <c r="I83" s="13"/>
-      <c r="J83" s="13"/>
-      <c r="K83" s="13"/>
+      <c r="G83" s="15"/>
+      <c r="H83" s="15"/>
+      <c r="I83" s="15"/>
+      <c r="J83" s="15"/>
+      <c r="K83" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5968,30 +5989,31 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" customHeight="1"/>
+    <row r="3" customHeight="1" spans="2:13">
+      <c r="H3" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
     <row r="4" customHeight="1" spans="2:13">
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
     </row>
     <row r="5" customHeight="1" spans="2:13">
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
     </row>
     <row r="6" ht="16" customHeight="1" spans="2:13">
       <c r="B6" t="s">
@@ -6003,65 +6025,65 @@
       <c r="D6" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" ht="16" spans="2:13">
+      <c r="B7" t="s">
         <v>173</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="C7" t="s">
         <v>174</v>
       </c>
-      <c r="M6" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13">
-      <c r="B7" t="s">
+      <c r="D7" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1" t="s">
+      <c r="E7" s="2"/>
+      <c r="F7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7" s="2">
         <v>1</v>
       </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1">
+      <c r="J7" s="2"/>
+      <c r="K7" s="2">
         <v>0</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L7" s="2">
         <v>3</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="2" t="s">
         <v>176</v>
       </c>
     </row>
@@ -6069,479 +6091,491 @@
       <c r="D8" t="s">
         <v>177</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="1"/>
+      <c r="F8" s="2"/>
       <c r="G8" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="2">
         <v>-1.05</v>
       </c>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
     </row>
     <row r="9" spans="2:13">
       <c r="C9" t="s">
         <v>178</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="1"/>
+      <c r="F9" s="2"/>
       <c r="G9" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="2">
         <v>-1.05</v>
       </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
     </row>
     <row r="10" spans="2:13">
       <c r="C10" t="s">
         <v>178</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
-      </c>
-      <c r="F10" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="2">
         <v>1</v>
       </c>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
     </row>
     <row r="11" spans="2:13">
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
+      <c r="D11" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
     </row>
     <row r="12" spans="2:13">
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
     </row>
     <row r="13" spans="2:13">
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
     </row>
     <row r="14" spans="2:13">
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
     </row>
     <row r="15" spans="2:13">
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="3" t="s">
-        <v>179</v>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="5" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="2:13">
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
     </row>
     <row r="17" spans="5:13">
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
     </row>
     <row r="18" spans="5:13">
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
     </row>
     <row r="19" spans="5:13">
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
     </row>
     <row r="23" spans="5:13">
-      <c r="G23" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1">
+      <c r="G23" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2">
         <v>-1</v>
       </c>
-      <c r="K23" s="1"/>
+      <c r="K23" s="2"/>
     </row>
     <row r="24" spans="5:13">
-      <c r="G24" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H24" s="1" t="s">
+      <c r="G24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1">
+      <c r="I24" s="2"/>
+      <c r="J24" s="2">
         <v>1.5</v>
       </c>
-      <c r="K24" s="1"/>
+      <c r="K24" s="2"/>
     </row>
     <row r="25" spans="5:13">
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
     </row>
     <row r="26" spans="5:13">
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
     </row>
     <row r="44" ht="15.25"/>
     <row r="45" ht="15.25" spans="7:23">
-      <c r="G45" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="H45" s="4" t="s">
+      <c r="G45" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H45" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="4">
+      <c r="I45" s="6">
         <v>2019</v>
       </c>
-      <c r="J45" s="4">
+      <c r="J45" s="6">
         <v>2020</v>
       </c>
-      <c r="K45" s="4">
+      <c r="K45" s="6">
         <v>2025</v>
       </c>
-      <c r="L45" s="4">
+      <c r="L45" s="6">
         <v>2030</v>
       </c>
-      <c r="M45" s="4">
+      <c r="M45" s="6">
         <v>2035</v>
       </c>
-      <c r="N45" s="4">
+      <c r="N45" s="6">
         <v>2040</v>
       </c>
-      <c r="O45" s="4">
+      <c r="O45" s="6">
         <v>2050</v>
       </c>
-      <c r="P45" s="4">
+      <c r="P45" s="6">
         <v>2060</v>
       </c>
-      <c r="Q45" s="4">
+      <c r="Q45" s="6">
         <v>2070</v>
       </c>
-      <c r="R45" s="4">
+      <c r="R45" s="6">
         <v>2080</v>
       </c>
-      <c r="S45" s="4">
+      <c r="S45" s="6">
         <v>2090</v>
       </c>
-      <c r="T45" s="4">
+      <c r="T45" s="6">
         <v>2100</v>
       </c>
-      <c r="U45" s="4">
+      <c r="U45" s="6">
         <v>2110</v>
       </c>
-      <c r="V45" s="4">
+      <c r="V45" s="6">
         <v>2130</v>
       </c>
     </row>
     <row r="46" ht="15.25" spans="7:23">
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
-      <c r="Q46" s="5"/>
-      <c r="R46" s="5"/>
-      <c r="S46" s="5"/>
-      <c r="T46" s="5"/>
-      <c r="U46" s="5"/>
-      <c r="V46" s="5"/>
-      <c r="W46" s="5"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
+      <c r="M46" s="7"/>
+      <c r="N46" s="7"/>
+      <c r="O46" s="7"/>
+      <c r="P46" s="7"/>
+      <c r="Q46" s="7"/>
+      <c r="R46" s="7"/>
+      <c r="S46" s="7"/>
+      <c r="T46" s="7"/>
+      <c r="U46" s="7"/>
+      <c r="V46" s="7"/>
+      <c r="W46" s="7"/>
     </row>
     <row r="47" ht="15.25" spans="7:23">
-      <c r="G47" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="H47" s="6" t="s">
+      <c r="G47" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="I47" s="7">
+      <c r="H47" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="I47" s="9">
         <v>23147.55</v>
       </c>
-      <c r="J47" s="7">
+      <c r="J47" s="9">
         <v>24048.86</v>
       </c>
-      <c r="K47" s="7">
+      <c r="K47" s="9">
         <v>25614.9</v>
       </c>
-      <c r="L47" s="7">
+      <c r="L47" s="9">
         <v>26682.27</v>
       </c>
-      <c r="M47" s="7">
+      <c r="M47" s="9">
         <v>27327.39</v>
       </c>
-      <c r="N47" s="7">
+      <c r="N47" s="9">
         <v>29455.19</v>
       </c>
-      <c r="O47" s="7">
+      <c r="O47" s="9">
         <v>36120.9</v>
       </c>
-      <c r="P47" s="7">
+      <c r="P47" s="9">
         <v>37765.053</v>
       </c>
-      <c r="Q47" s="7">
+      <c r="Q47" s="9">
         <v>39347.27</v>
       </c>
-      <c r="R47" s="7">
+      <c r="R47" s="9">
         <v>40254.43</v>
       </c>
-      <c r="S47" s="7">
+      <c r="S47" s="9">
         <v>41140.93</v>
       </c>
-      <c r="T47" s="7">
+      <c r="T47" s="9">
         <v>41608.6</v>
       </c>
-      <c r="U47" s="7">
+      <c r="U47" s="9">
         <v>41639.07</v>
       </c>
-      <c r="V47" s="7">
+      <c r="V47" s="9">
         <v>41578.8</v>
       </c>
-      <c r="W47" s="8"/>
+      <c r="W47" s="10"/>
     </row>
     <row r="48" ht="15.25" spans="7:23">
-      <c r="G48" s="6"/>
-      <c r="H48" s="6" t="s">
+      <c r="G48" s="8"/>
+      <c r="H48" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="I48" s="9">
+        <v>25707.66</v>
+      </c>
+      <c r="J48" s="9">
+        <v>26708.54</v>
+      </c>
+      <c r="K48" s="9">
+        <v>28281.61</v>
+      </c>
+      <c r="L48" s="9">
+        <v>29288.31</v>
+      </c>
+      <c r="M48" s="9">
+        <v>29823.36</v>
+      </c>
+      <c r="N48" s="9">
+        <v>31961.62</v>
+      </c>
+      <c r="O48" s="9">
+        <v>38751.23</v>
+      </c>
+      <c r="P48" s="9">
+        <v>40061.58</v>
+      </c>
+      <c r="Q48" s="9">
+        <v>41281.95</v>
+      </c>
+      <c r="R48" s="9">
+        <v>42233.66</v>
+      </c>
+      <c r="S48" s="9">
+        <v>43166.25</v>
+      </c>
+      <c r="T48" s="9">
+        <v>43657.5</v>
+      </c>
+      <c r="U48" s="9">
+        <v>43687.063</v>
+      </c>
+      <c r="V48" s="9">
+        <v>43626.04</v>
+      </c>
+      <c r="W48" s="10"/>
+    </row>
+    <row r="49" ht="15.25" spans="7:23">
+      <c r="G49" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="H49" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="I48" s="7">
-        <v>25707.66</v>
-      </c>
-      <c r="J48" s="7">
-        <v>26708.54</v>
-      </c>
-      <c r="K48" s="7">
-        <v>28281.61</v>
-      </c>
-      <c r="L48" s="7">
-        <v>29288.31</v>
-      </c>
-      <c r="M48" s="7">
-        <v>29823.36</v>
-      </c>
-      <c r="N48" s="7">
-        <v>31961.62</v>
-      </c>
-      <c r="O48" s="7">
-        <v>38751.23</v>
-      </c>
-      <c r="P48" s="7">
-        <v>40061.58</v>
-      </c>
-      <c r="Q48" s="7">
-        <v>41281.95</v>
-      </c>
-      <c r="R48" s="7">
-        <v>42233.66</v>
-      </c>
-      <c r="S48" s="7">
-        <v>43166.25</v>
-      </c>
-      <c r="T48" s="7">
-        <v>43657.5</v>
-      </c>
-      <c r="U48" s="7">
-        <v>43687.063</v>
-      </c>
-      <c r="V48" s="7">
-        <v>43626.04</v>
-      </c>
-      <c r="W48" s="8"/>
-    </row>
-    <row r="49" ht="15.25" spans="7:23">
-      <c r="G49" s="6" t="s">
+      <c r="I49" s="9">
+        <v>17208.23</v>
+      </c>
+      <c r="J49" s="9">
+        <v>17167.02</v>
+      </c>
+      <c r="K49" s="9">
+        <v>17588.94</v>
+      </c>
+      <c r="L49" s="9">
+        <v>17552.39</v>
+      </c>
+      <c r="M49" s="9">
+        <v>17929.042</v>
+      </c>
+      <c r="N49" s="9">
+        <v>21788.048</v>
+      </c>
+      <c r="O49" s="9">
+        <v>37977.74</v>
+      </c>
+      <c r="P49" s="9">
+        <v>41150.28</v>
+      </c>
+      <c r="Q49" s="9">
+        <v>44299.82</v>
+      </c>
+      <c r="R49" s="9">
+        <v>46519.5</v>
+      </c>
+      <c r="S49" s="9">
+        <v>48652.58</v>
+      </c>
+      <c r="T49" s="9">
+        <v>50075.57</v>
+      </c>
+      <c r="U49" s="9">
+        <v>50118.11</v>
+      </c>
+      <c r="V49" s="9">
+        <v>50033.62</v>
+      </c>
+      <c r="W49" s="10"/>
+    </row>
+    <row r="50" ht="15.25" spans="7:23">
+      <c r="G50" s="8"/>
+      <c r="H50" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="H49" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="I49" s="7">
-        <v>17208.23</v>
-      </c>
-      <c r="J49" s="7">
-        <v>17167.02</v>
-      </c>
-      <c r="K49" s="7">
-        <v>17588.94</v>
-      </c>
-      <c r="L49" s="7">
-        <v>17552.39</v>
-      </c>
-      <c r="M49" s="7">
-        <v>17929.042</v>
-      </c>
-      <c r="N49" s="7">
-        <v>21788.048</v>
-      </c>
-      <c r="O49" s="7">
-        <v>37977.74</v>
-      </c>
-      <c r="P49" s="7">
-        <v>41150.28</v>
-      </c>
-      <c r="Q49" s="7">
-        <v>44299.82</v>
-      </c>
-      <c r="R49" s="7">
-        <v>46519.5</v>
-      </c>
-      <c r="S49" s="7">
-        <v>48652.58</v>
-      </c>
-      <c r="T49" s="7">
-        <v>50075.57</v>
-      </c>
-      <c r="U49" s="7">
-        <v>50118.11</v>
-      </c>
-      <c r="V49" s="7">
-        <v>50033.62</v>
-      </c>
-      <c r="W49" s="8"/>
-    </row>
-    <row r="50" ht="15.25" spans="7:23">
-      <c r="G50" s="6"/>
-      <c r="H50" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="I50" s="7">
+      <c r="I50" s="9">
         <v>18874.63</v>
       </c>
-      <c r="J50" s="7">
+      <c r="J50" s="9">
         <v>18829.43</v>
       </c>
-      <c r="K50" s="7">
+      <c r="K50" s="9">
         <v>19204.8</v>
       </c>
-      <c r="L50" s="7">
+      <c r="L50" s="9">
         <v>19078.4</v>
       </c>
-      <c r="M50" s="7">
+      <c r="M50" s="9">
         <v>19400.24</v>
       </c>
-      <c r="N50" s="7">
+      <c r="N50" s="9">
         <v>23470.59</v>
       </c>
-      <c r="O50" s="7">
+      <c r="O50" s="9">
         <v>40548.24</v>
       </c>
-      <c r="P50" s="7">
+      <c r="P50" s="9">
         <v>43549.64</v>
       </c>
-      <c r="Q50" s="7">
+      <c r="Q50" s="9">
         <v>46485.71</v>
       </c>
-      <c r="R50" s="7">
+      <c r="R50" s="9">
         <v>48816.36</v>
       </c>
-      <c r="S50" s="7">
+      <c r="S50" s="9">
         <v>51054.94</v>
       </c>
-      <c r="T50" s="7">
+      <c r="T50" s="9">
         <v>52548.3</v>
       </c>
-      <c r="U50" s="7">
+      <c r="U50" s="9">
         <v>52592.9</v>
       </c>
-      <c r="V50" s="7">
+      <c r="V50" s="9">
         <v>52504.13</v>
       </c>
-      <c r="W50" s="8"/>
+      <c r="W50" s="10"/>
     </row>
     <row r="52" spans="7:23">
       <c r="I52">
@@ -6565,7 +6599,7 @@
         <v>0.0913358355847376</v>
       </c>
       <c r="N52">
-        <f t="shared" ref="N52:S52" si="0" xml:space="preserve">(N48-N47)/N47</f>
+        <f t="shared" ref="N52:V52" si="0" xml:space="preserve">(N48-N47)/N47</f>
         <v>0.0850929836134141</v>
       </c>
       <c r="O52">
@@ -6589,287 +6623,287 @@
         <v>0.0492288336700216</v>
       </c>
       <c r="T52">
-        <f xml:space="preserve">(T48-T47)/T47</f>
+        <f t="shared" si="0"/>
         <v>0.0492422239633153</v>
       </c>
       <c r="U52">
-        <f xml:space="preserve">(U48-U47)/U47</f>
+        <f t="shared" si="0"/>
         <v>0.0491844078169854</v>
       </c>
       <c r="V52">
-        <f xml:space="preserve">(V48-V47)/V47</f>
+        <f t="shared" si="0"/>
         <v>0.0492375922345041</v>
       </c>
     </row>
     <row r="54" ht="15.25"/>
     <row r="55" ht="15.25" spans="7:23">
-      <c r="G55" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="H55" s="4" t="s">
+      <c r="G55" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H55" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="I55" s="4">
+      <c r="I55" s="6">
         <v>2019</v>
       </c>
-      <c r="J55" s="4">
+      <c r="J55" s="6">
         <v>2020</v>
       </c>
-      <c r="K55" s="4">
+      <c r="K55" s="6">
         <v>2025</v>
       </c>
-      <c r="L55" s="4">
+      <c r="L55" s="6">
         <v>2030</v>
       </c>
-      <c r="M55" s="4">
+      <c r="M55" s="6">
         <v>2035</v>
       </c>
-      <c r="N55" s="4">
+      <c r="N55" s="6">
         <v>2040</v>
       </c>
-      <c r="O55" s="4">
+      <c r="O55" s="6">
         <v>2050</v>
       </c>
-      <c r="P55" s="4">
+      <c r="P55" s="6">
         <v>2060</v>
       </c>
-      <c r="Q55" s="4">
+      <c r="Q55" s="6">
         <v>2070</v>
       </c>
-      <c r="R55" s="4">
+      <c r="R55" s="6">
         <v>2080</v>
       </c>
-      <c r="S55" s="4">
+      <c r="S55" s="6">
         <v>2090</v>
       </c>
-      <c r="T55" s="4">
+      <c r="T55" s="6">
         <v>2100</v>
       </c>
-      <c r="U55" s="4">
+      <c r="U55" s="6">
         <v>2110</v>
       </c>
-      <c r="V55" s="4">
+      <c r="V55" s="6">
         <v>2130</v>
       </c>
     </row>
     <row r="56" ht="15.25" spans="7:23">
-      <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="5"/>
-      <c r="K56" s="5"/>
-      <c r="L56" s="5"/>
-      <c r="M56" s="5"/>
-      <c r="N56" s="5"/>
-      <c r="O56" s="5"/>
-      <c r="P56" s="5"/>
-      <c r="Q56" s="5"/>
-      <c r="R56" s="5"/>
-      <c r="S56" s="5"/>
-      <c r="T56" s="5"/>
-      <c r="U56" s="5"/>
-      <c r="V56" s="5"/>
-      <c r="W56" s="5"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+      <c r="K56" s="7"/>
+      <c r="L56" s="7"/>
+      <c r="M56" s="7"/>
+      <c r="N56" s="7"/>
+      <c r="O56" s="7"/>
+      <c r="P56" s="7"/>
+      <c r="Q56" s="7"/>
+      <c r="R56" s="7"/>
+      <c r="S56" s="7"/>
+      <c r="T56" s="7"/>
+      <c r="U56" s="7"/>
+      <c r="V56" s="7"/>
+      <c r="W56" s="7"/>
     </row>
     <row r="57" ht="15.25" spans="7:23">
-      <c r="G57" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="H57" s="6" t="s">
+      <c r="G57" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="I57" s="7">
+      <c r="H57" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="I57" s="9">
         <v>23143.15</v>
       </c>
-      <c r="J57" s="7">
+      <c r="J57" s="9">
         <v>24043.23</v>
       </c>
-      <c r="K57" s="7">
+      <c r="K57" s="9">
         <v>25605.6</v>
       </c>
-      <c r="L57" s="7">
+      <c r="L57" s="9">
         <v>26661.51</v>
       </c>
-      <c r="M57" s="7">
+      <c r="M57" s="9">
         <v>27302.64</v>
       </c>
-      <c r="N57" s="7">
+      <c r="N57" s="9">
         <v>29430.44</v>
       </c>
-      <c r="O57" s="7">
+      <c r="O57" s="9">
         <v>36096.16</v>
       </c>
-      <c r="P57" s="7">
+      <c r="P57" s="9">
         <v>37740.31</v>
       </c>
-      <c r="Q57" s="7">
+      <c r="Q57" s="9">
         <v>39322.52</v>
       </c>
-      <c r="R57" s="7">
+      <c r="R57" s="9">
         <v>40229.67</v>
       </c>
-      <c r="S57" s="7">
+      <c r="S57" s="9">
         <v>41116.14</v>
       </c>
-      <c r="T57" s="7">
+      <c r="T57" s="9">
         <v>41583.77</v>
       </c>
-      <c r="U57" s="7">
+      <c r="U57" s="9">
         <v>41614.22</v>
       </c>
-      <c r="V57" s="7">
+      <c r="V57" s="9">
         <v>41553.81</v>
       </c>
-      <c r="W57" s="8"/>
+      <c r="W57" s="10"/>
     </row>
     <row r="58" ht="15.25" spans="7:23">
-      <c r="G58" s="6"/>
-      <c r="H58" s="6" t="s">
+      <c r="G58" s="8"/>
+      <c r="H58" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="I58" s="9">
+        <v>24300.3</v>
+      </c>
+      <c r="J58" s="9">
+        <v>25245.39</v>
+      </c>
+      <c r="K58" s="9">
+        <v>26885.88</v>
+      </c>
+      <c r="L58" s="9">
+        <v>27994.58</v>
+      </c>
+      <c r="M58" s="9">
+        <v>28667.77</v>
+      </c>
+      <c r="N58" s="9">
+        <v>30901.97</v>
+      </c>
+      <c r="O58" s="9">
+        <v>37900.97</v>
+      </c>
+      <c r="P58" s="9">
+        <v>39627.32</v>
+      </c>
+      <c r="Q58" s="9">
+        <v>41262.11</v>
+      </c>
+      <c r="R58" s="9">
+        <v>42213.82</v>
+      </c>
+      <c r="S58" s="9">
+        <v>43146.41</v>
+      </c>
+      <c r="T58" s="9">
+        <v>43637.66</v>
+      </c>
+      <c r="U58" s="9">
+        <v>43667.22</v>
+      </c>
+      <c r="V58" s="9">
+        <v>43606.2</v>
+      </c>
+      <c r="W58" s="10"/>
+    </row>
+    <row r="59" ht="15.25" spans="7:23">
+      <c r="G59" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="H59" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="I58" s="7">
-        <v>24300.3</v>
-      </c>
-      <c r="J58" s="7">
-        <v>25245.39</v>
-      </c>
-      <c r="K58" s="7">
-        <v>26885.88</v>
-      </c>
-      <c r="L58" s="7">
-        <v>27994.58</v>
-      </c>
-      <c r="M58" s="7">
-        <v>28667.77</v>
-      </c>
-      <c r="N58" s="7">
-        <v>30901.97</v>
-      </c>
-      <c r="O58" s="7">
-        <v>37900.97</v>
-      </c>
-      <c r="P58" s="7">
-        <v>39627.32</v>
-      </c>
-      <c r="Q58" s="7">
-        <v>41262.11</v>
-      </c>
-      <c r="R58" s="7">
-        <v>42213.82</v>
-      </c>
-      <c r="S58" s="7">
-        <v>43146.41</v>
-      </c>
-      <c r="T58" s="7">
-        <v>43637.66</v>
-      </c>
-      <c r="U58" s="7">
-        <v>43667.22</v>
-      </c>
-      <c r="V58" s="7">
-        <v>43606.2</v>
-      </c>
-      <c r="W58" s="8"/>
-    </row>
-    <row r="59" ht="15.25" spans="7:23">
-      <c r="G59" s="6" t="s">
+      <c r="I59" s="9">
+        <v>17204.75</v>
+      </c>
+      <c r="J59" s="9">
+        <v>17163.54</v>
+      </c>
+      <c r="K59" s="9">
+        <v>17585.44</v>
+      </c>
+      <c r="L59" s="9">
+        <v>17548.31</v>
+      </c>
+      <c r="M59" s="9">
+        <v>17924.42</v>
+      </c>
+      <c r="N59" s="9">
+        <v>21783.38</v>
+      </c>
+      <c r="O59" s="9">
+        <v>37973.078</v>
+      </c>
+      <c r="P59" s="9">
+        <v>41145.61</v>
+      </c>
+      <c r="Q59" s="9">
+        <v>44295.14</v>
+      </c>
+      <c r="R59" s="9">
+        <v>46514.82</v>
+      </c>
+      <c r="S59" s="9">
+        <v>48647.87</v>
+      </c>
+      <c r="T59" s="9">
+        <v>50070.83</v>
+      </c>
+      <c r="U59" s="9">
+        <v>50113.32</v>
+      </c>
+      <c r="V59" s="9">
+        <v>50028.74</v>
+      </c>
+      <c r="W59" s="10"/>
+    </row>
+    <row r="60" ht="15.25" spans="7:23">
+      <c r="G60" s="8"/>
+      <c r="H60" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="H59" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="I59" s="7">
-        <v>17204.75</v>
-      </c>
-      <c r="J59" s="7">
-        <v>17163.54</v>
-      </c>
-      <c r="K59" s="7">
-        <v>17585.44</v>
-      </c>
-      <c r="L59" s="7">
-        <v>17548.31</v>
-      </c>
-      <c r="M59" s="7">
-        <v>17924.42</v>
-      </c>
-      <c r="N59" s="7">
-        <v>21783.38</v>
-      </c>
-      <c r="O59" s="7">
-        <v>37973.078</v>
-      </c>
-      <c r="P59" s="7">
-        <v>41145.61</v>
-      </c>
-      <c r="Q59" s="7">
-        <v>44295.14</v>
-      </c>
-      <c r="R59" s="7">
-        <v>46514.82</v>
-      </c>
-      <c r="S59" s="7">
-        <v>48647.87</v>
-      </c>
-      <c r="T59" s="7">
-        <v>50070.83</v>
-      </c>
-      <c r="U59" s="7">
-        <v>50113.32</v>
-      </c>
-      <c r="V59" s="7">
-        <v>50028.74</v>
-      </c>
-      <c r="W59" s="8"/>
-    </row>
-    <row r="60" ht="15.25" spans="7:23">
-      <c r="G60" s="6"/>
-      <c r="H60" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="I60" s="7">
+      <c r="I60" s="9">
         <v>18064.98</v>
       </c>
-      <c r="J60" s="7">
+      <c r="J60" s="9">
         <v>18021.71</v>
       </c>
-      <c r="K60" s="7">
+      <c r="K60" s="9">
         <v>18464.72</v>
       </c>
-      <c r="L60" s="7">
+      <c r="L60" s="9">
         <v>18425.72</v>
       </c>
-      <c r="M60" s="7">
+      <c r="M60" s="9">
         <v>18820.64</v>
       </c>
-      <c r="N60" s="7">
+      <c r="N60" s="9">
         <v>22872.55</v>
       </c>
-      <c r="O60" s="7">
+      <c r="O60" s="9">
         <v>39871.73</v>
       </c>
-      <c r="P60" s="7">
+      <c r="P60" s="9">
         <v>43202.89</v>
       </c>
-      <c r="Q60" s="7">
+      <c r="Q60" s="9">
         <v>46481.91</v>
       </c>
-      <c r="R60" s="7">
+      <c r="R60" s="9">
         <v>48812.56</v>
       </c>
-      <c r="S60" s="7">
+      <c r="S60" s="9">
         <v>51051.14</v>
       </c>
-      <c r="T60" s="7">
+      <c r="T60" s="9">
         <v>52544.5</v>
       </c>
-      <c r="U60" s="7">
+      <c r="U60" s="9">
         <v>52589.1</v>
       </c>
-      <c r="V60" s="7">
+      <c r="V60" s="9">
         <v>52500.33</v>
       </c>
-      <c r="W60" s="8"/>
+      <c r="W60" s="10"/>
     </row>
     <row r="62" spans="7:23">
       <c r="I62">
@@ -6891,299 +6925,299 @@
     </row>
     <row r="65" ht="15.25"/>
     <row r="66" ht="15.25" spans="7:24">
-      <c r="G66" s="8"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="4"/>
-      <c r="L66" s="4"/>
-      <c r="M66" s="4"/>
-      <c r="N66" s="4"/>
-      <c r="O66" s="4"/>
-      <c r="P66" s="4"/>
-      <c r="Q66" s="4"/>
-      <c r="R66" s="4"/>
-      <c r="S66" s="4"/>
-      <c r="T66" s="4"/>
-      <c r="U66" s="4"/>
-      <c r="V66" s="4"/>
-      <c r="W66" s="4"/>
-      <c r="X66" s="4"/>
+      <c r="G66" s="10"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="6"/>
+      <c r="N66" s="6"/>
+      <c r="O66" s="6"/>
+      <c r="P66" s="6"/>
+      <c r="Q66" s="6"/>
+      <c r="R66" s="6"/>
+      <c r="S66" s="6"/>
+      <c r="T66" s="6"/>
+      <c r="U66" s="6"/>
+      <c r="V66" s="6"/>
+      <c r="W66" s="6"/>
+      <c r="X66" s="6"/>
     </row>
     <row r="67" ht="15.25" spans="7:24">
-      <c r="G67" s="8"/>
-      <c r="H67" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="I67" s="4" t="s">
+      <c r="G67" s="10"/>
+      <c r="H67" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="I67" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J67" s="4">
+      <c r="J67" s="6">
         <v>2019</v>
       </c>
-      <c r="K67" s="4">
+      <c r="K67" s="6">
         <v>2020</v>
       </c>
-      <c r="L67" s="4">
+      <c r="L67" s="6">
         <v>2025</v>
       </c>
-      <c r="M67" s="4">
+      <c r="M67" s="6">
         <v>2030</v>
       </c>
-      <c r="N67" s="4">
+      <c r="N67" s="6">
         <v>2035</v>
       </c>
-      <c r="O67" s="4">
+      <c r="O67" s="6">
         <v>2040</v>
       </c>
-      <c r="P67" s="4">
+      <c r="P67" s="6">
         <v>2050</v>
       </c>
-      <c r="Q67" s="4">
+      <c r="Q67" s="6">
         <v>2060</v>
       </c>
-      <c r="R67" s="4">
+      <c r="R67" s="6">
         <v>2070</v>
       </c>
-      <c r="S67" s="4">
+      <c r="S67" s="6">
         <v>2080</v>
       </c>
-      <c r="T67" s="4">
+      <c r="T67" s="6">
         <v>2090</v>
       </c>
-      <c r="U67" s="4">
+      <c r="U67" s="6">
         <v>2100</v>
       </c>
-      <c r="V67" s="4">
+      <c r="V67" s="6">
         <v>2110</v>
       </c>
-      <c r="W67" s="4">
+      <c r="W67" s="6">
         <v>2130</v>
       </c>
-      <c r="X67" s="8"/>
+      <c r="X67" s="10"/>
     </row>
     <row r="68" ht="15.25" spans="7:24">
-      <c r="G68" s="8"/>
-      <c r="H68" s="9"/>
-      <c r="I68" s="9"/>
-      <c r="J68" s="9"/>
-      <c r="K68" s="9"/>
-      <c r="L68" s="9"/>
-      <c r="M68" s="9"/>
-      <c r="N68" s="9"/>
-      <c r="O68" s="9"/>
-      <c r="P68" s="9"/>
-      <c r="Q68" s="9"/>
-      <c r="R68" s="9"/>
-      <c r="S68" s="9"/>
-      <c r="T68" s="9"/>
-      <c r="U68" s="9"/>
-      <c r="V68" s="9"/>
-      <c r="W68" s="9"/>
-      <c r="X68" s="9"/>
+      <c r="G68" s="10"/>
+      <c r="H68" s="11"/>
+      <c r="I68" s="11"/>
+      <c r="J68" s="11"/>
+      <c r="K68" s="11"/>
+      <c r="L68" s="11"/>
+      <c r="M68" s="11"/>
+      <c r="N68" s="11"/>
+      <c r="O68" s="11"/>
+      <c r="P68" s="11"/>
+      <c r="Q68" s="11"/>
+      <c r="R68" s="11"/>
+      <c r="S68" s="11"/>
+      <c r="T68" s="11"/>
+      <c r="U68" s="11"/>
+      <c r="V68" s="11"/>
+      <c r="W68" s="11"/>
+      <c r="X68" s="11"/>
     </row>
     <row r="69" ht="15.25" spans="7:24">
-      <c r="G69" s="8"/>
-      <c r="H69" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I69" s="10" t="s">
+      <c r="G69" s="10"/>
+      <c r="H69" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="J69" s="11">
+      <c r="I69" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="J69" s="13">
         <v>23143.15</v>
       </c>
-      <c r="K69" s="11">
+      <c r="K69" s="13">
         <v>24043.23</v>
       </c>
-      <c r="L69" s="11">
+      <c r="L69" s="13">
         <v>25605.6</v>
       </c>
-      <c r="M69" s="11">
+      <c r="M69" s="13">
         <v>26661.51</v>
       </c>
-      <c r="N69" s="11">
+      <c r="N69" s="13">
         <v>27302.64</v>
       </c>
-      <c r="O69" s="11">
+      <c r="O69" s="13">
         <v>29430.44</v>
       </c>
-      <c r="P69" s="11">
+      <c r="P69" s="13">
         <v>36096.16</v>
       </c>
-      <c r="Q69" s="11">
+      <c r="Q69" s="13">
         <v>37740.31</v>
       </c>
-      <c r="R69" s="11">
+      <c r="R69" s="13">
         <v>39322.53</v>
       </c>
-      <c r="S69" s="11">
+      <c r="S69" s="13">
         <v>40229.69</v>
       </c>
-      <c r="T69" s="11">
+      <c r="T69" s="13">
         <v>41116.19</v>
       </c>
-      <c r="U69" s="11">
+      <c r="U69" s="13">
         <v>41583.86</v>
       </c>
-      <c r="V69" s="11">
+      <c r="V69" s="13">
         <v>41614.32</v>
       </c>
-      <c r="W69" s="11">
+      <c r="W69" s="13">
         <v>41554.059</v>
       </c>
-      <c r="X69" s="8"/>
+      <c r="X69" s="10"/>
     </row>
     <row r="70" ht="15.25" spans="7:24">
-      <c r="G70" s="8"/>
-      <c r="H70" s="10"/>
-      <c r="I70" s="10" t="s">
+      <c r="G70" s="10"/>
+      <c r="H70" s="12"/>
+      <c r="I70" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="J70" s="13">
+        <v>24300.3</v>
+      </c>
+      <c r="K70" s="13">
+        <v>25245.39</v>
+      </c>
+      <c r="L70" s="13">
+        <v>26885.88</v>
+      </c>
+      <c r="M70" s="13">
+        <v>27994.58</v>
+      </c>
+      <c r="N70" s="13">
+        <v>28667.77</v>
+      </c>
+      <c r="O70" s="13">
+        <v>30901.97</v>
+      </c>
+      <c r="P70" s="13">
+        <v>37900.97</v>
+      </c>
+      <c r="Q70" s="13">
+        <v>39627.32</v>
+      </c>
+      <c r="R70" s="13">
+        <v>41262.11</v>
+      </c>
+      <c r="S70" s="13">
+        <v>42213.82</v>
+      </c>
+      <c r="T70" s="13">
+        <v>43146.41</v>
+      </c>
+      <c r="U70" s="13">
+        <v>43637.66</v>
+      </c>
+      <c r="V70" s="13">
+        <v>43667.22</v>
+      </c>
+      <c r="W70" s="13">
+        <v>43606.2</v>
+      </c>
+      <c r="X70" s="10"/>
+    </row>
+    <row r="71" ht="15.25" spans="7:24">
+      <c r="G71" s="10"/>
+      <c r="H71" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="I71" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="J70" s="11">
-        <v>24300.3</v>
-      </c>
-      <c r="K70" s="11">
-        <v>25245.39</v>
-      </c>
-      <c r="L70" s="11">
-        <v>26885.88</v>
-      </c>
-      <c r="M70" s="11">
-        <v>27994.58</v>
-      </c>
-      <c r="N70" s="11">
-        <v>28667.77</v>
-      </c>
-      <c r="O70" s="11">
-        <v>30901.97</v>
-      </c>
-      <c r="P70" s="11">
-        <v>37900.97</v>
-      </c>
-      <c r="Q70" s="11">
-        <v>39627.32</v>
-      </c>
-      <c r="R70" s="11">
-        <v>41262.11</v>
-      </c>
-      <c r="S70" s="11">
-        <v>42213.82</v>
-      </c>
-      <c r="T70" s="11">
-        <v>43146.41</v>
-      </c>
-      <c r="U70" s="11">
-        <v>43637.66</v>
-      </c>
-      <c r="V70" s="11">
-        <v>43667.22</v>
-      </c>
-      <c r="W70" s="11">
-        <v>43606.2</v>
-      </c>
-      <c r="X70" s="8"/>
-    </row>
-    <row r="71" ht="15.25" spans="7:24">
-      <c r="G71" s="8"/>
-      <c r="H71" s="10" t="s">
+      <c r="J71" s="13">
+        <v>17204.75</v>
+      </c>
+      <c r="K71" s="13">
+        <v>17163.54</v>
+      </c>
+      <c r="L71" s="13">
+        <v>17585.44</v>
+      </c>
+      <c r="M71" s="13">
+        <v>17548.31</v>
+      </c>
+      <c r="N71" s="13">
+        <v>17924.42</v>
+      </c>
+      <c r="O71" s="13">
+        <v>21783.38</v>
+      </c>
+      <c r="P71" s="13">
+        <v>37973.078</v>
+      </c>
+      <c r="Q71" s="13">
+        <v>41145.61</v>
+      </c>
+      <c r="R71" s="13">
+        <v>44295.15</v>
+      </c>
+      <c r="S71" s="13">
+        <v>46514.84</v>
+      </c>
+      <c r="T71" s="13">
+        <v>48647.92</v>
+      </c>
+      <c r="U71" s="13">
+        <v>50070.91</v>
+      </c>
+      <c r="V71" s="13">
+        <v>50113.45</v>
+      </c>
+      <c r="W71" s="13">
+        <v>50028.95</v>
+      </c>
+      <c r="X71" s="10"/>
+    </row>
+    <row r="72" ht="15.25" spans="7:24">
+      <c r="H72" s="12"/>
+      <c r="I72" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="I71" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J71" s="11">
-        <v>17204.75</v>
-      </c>
-      <c r="K71" s="11">
-        <v>17163.54</v>
-      </c>
-      <c r="L71" s="11">
-        <v>17585.44</v>
-      </c>
-      <c r="M71" s="11">
-        <v>17548.31</v>
-      </c>
-      <c r="N71" s="11">
-        <v>17924.42</v>
-      </c>
-      <c r="O71" s="11">
-        <v>21783.38</v>
-      </c>
-      <c r="P71" s="11">
-        <v>37973.078</v>
-      </c>
-      <c r="Q71" s="11">
-        <v>41145.61</v>
-      </c>
-      <c r="R71" s="11">
-        <v>44295.15</v>
-      </c>
-      <c r="S71" s="11">
-        <v>46514.84</v>
-      </c>
-      <c r="T71" s="11">
-        <v>48647.92</v>
-      </c>
-      <c r="U71" s="11">
-        <v>50070.91</v>
-      </c>
-      <c r="V71" s="11">
-        <v>50113.45</v>
-      </c>
-      <c r="W71" s="11">
-        <v>50028.95</v>
-      </c>
-      <c r="X71" s="8"/>
-    </row>
-    <row r="72" ht="15.25" spans="7:24">
-      <c r="H72" s="10"/>
-      <c r="I72" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="J72" s="11">
+      <c r="J72" s="13">
         <v>18064.98</v>
       </c>
-      <c r="K72" s="11">
+      <c r="K72" s="13">
         <v>18021.71</v>
       </c>
-      <c r="L72" s="11">
+      <c r="L72" s="13">
         <v>18464.72</v>
       </c>
-      <c r="M72" s="11">
+      <c r="M72" s="13">
         <v>18425.72</v>
       </c>
-      <c r="N72" s="11">
+      <c r="N72" s="13">
         <v>18820.64</v>
       </c>
-      <c r="O72" s="11">
+      <c r="O72" s="13">
         <v>22872.55</v>
       </c>
-      <c r="P72" s="11">
+      <c r="P72" s="13">
         <v>39871.73</v>
       </c>
-      <c r="Q72" s="11">
+      <c r="Q72" s="13">
         <v>43202.89</v>
       </c>
-      <c r="R72" s="11">
+      <c r="R72" s="13">
         <v>46481.91</v>
       </c>
-      <c r="S72" s="11">
+      <c r="S72" s="13">
         <v>48812.56</v>
       </c>
-      <c r="T72" s="11">
+      <c r="T72" s="13">
         <v>51051.14</v>
       </c>
-      <c r="U72" s="11">
+      <c r="U72" s="13">
         <v>52544.5</v>
       </c>
-      <c r="V72" s="11">
+      <c r="V72" s="13">
         <v>52589.1</v>
       </c>
-      <c r="W72" s="11">
+      <c r="W72" s="13">
         <v>52500.33</v>
       </c>
-      <c r="X72" s="8"/>
+      <c r="X72" s="10"/>
     </row>
     <row r="74" spans="7:24">
       <c r="J74">
@@ -7245,273 +7279,273 @@
     </row>
     <row r="79" ht="15.25"/>
     <row r="80" ht="15.25" spans="7:24">
-      <c r="H80" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="I80" s="4" t="s">
+      <c r="H80" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="I80" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J80" s="4">
+      <c r="J80" s="6">
         <v>2019</v>
       </c>
-      <c r="K80" s="4">
+      <c r="K80" s="6">
         <v>2020</v>
       </c>
-      <c r="L80" s="4">
+      <c r="L80" s="6">
         <v>2025</v>
       </c>
-      <c r="M80" s="4">
+      <c r="M80" s="6">
         <v>2030</v>
       </c>
-      <c r="N80" s="4">
+      <c r="N80" s="6">
         <v>2035</v>
       </c>
-      <c r="O80" s="4">
+      <c r="O80" s="6">
         <v>2040</v>
       </c>
-      <c r="P80" s="4">
+      <c r="P80" s="6">
         <v>2050</v>
       </c>
-      <c r="Q80" s="4">
+      <c r="Q80" s="6">
         <v>2060</v>
       </c>
-      <c r="R80" s="4">
+      <c r="R80" s="6">
         <v>2070</v>
       </c>
-      <c r="S80" s="4">
+      <c r="S80" s="6">
         <v>2080</v>
       </c>
-      <c r="T80" s="4">
+      <c r="T80" s="6">
         <v>2090</v>
       </c>
-      <c r="U80" s="4">
+      <c r="U80" s="6">
         <v>2100</v>
       </c>
-      <c r="V80" s="4">
+      <c r="V80" s="6">
         <v>2110</v>
       </c>
-      <c r="W80" s="4">
+      <c r="W80" s="6">
         <v>2130</v>
       </c>
     </row>
     <row r="81" ht="15.25" spans="8:24">
-      <c r="H81" s="5"/>
-      <c r="I81" s="5"/>
-      <c r="J81" s="5"/>
-      <c r="K81" s="5"/>
-      <c r="L81" s="5"/>
-      <c r="M81" s="5"/>
-      <c r="N81" s="5"/>
-      <c r="O81" s="5"/>
-      <c r="P81" s="5"/>
-      <c r="Q81" s="5"/>
-      <c r="R81" s="5"/>
-      <c r="S81" s="5"/>
-      <c r="T81" s="5"/>
-      <c r="U81" s="5"/>
-      <c r="V81" s="5"/>
-      <c r="W81" s="5"/>
-      <c r="X81" s="5"/>
+      <c r="H81" s="7"/>
+      <c r="I81" s="7"/>
+      <c r="J81" s="7"/>
+      <c r="K81" s="7"/>
+      <c r="L81" s="7"/>
+      <c r="M81" s="7"/>
+      <c r="N81" s="7"/>
+      <c r="O81" s="7"/>
+      <c r="P81" s="7"/>
+      <c r="Q81" s="7"/>
+      <c r="R81" s="7"/>
+      <c r="S81" s="7"/>
+      <c r="T81" s="7"/>
+      <c r="U81" s="7"/>
+      <c r="V81" s="7"/>
+      <c r="W81" s="7"/>
+      <c r="X81" s="7"/>
     </row>
     <row r="82" ht="15.25" spans="8:24">
-      <c r="H82" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="I82" s="6" t="s">
+      <c r="H82" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="J82" s="7">
+      <c r="I82" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="J82" s="9">
         <v>23143.15</v>
       </c>
-      <c r="K82" s="7">
+      <c r="K82" s="9">
         <v>24043.23</v>
       </c>
-      <c r="L82" s="7">
+      <c r="L82" s="9">
         <v>25605.6</v>
       </c>
-      <c r="M82" s="7">
+      <c r="M82" s="9">
         <v>26661.51</v>
       </c>
-      <c r="N82" s="7">
+      <c r="N82" s="9">
         <v>27302.64</v>
       </c>
-      <c r="O82" s="7">
+      <c r="O82" s="9">
         <v>29430.44</v>
       </c>
-      <c r="P82" s="7">
+      <c r="P82" s="9">
         <v>36096.16</v>
       </c>
-      <c r="Q82" s="7">
+      <c r="Q82" s="9">
         <v>37740.31</v>
       </c>
-      <c r="R82" s="7">
+      <c r="R82" s="9">
         <v>39322.53</v>
       </c>
-      <c r="S82" s="7">
+      <c r="S82" s="9">
         <v>40229.69</v>
       </c>
-      <c r="T82" s="7">
+      <c r="T82" s="9">
         <v>41116.19</v>
       </c>
-      <c r="U82" s="7">
+      <c r="U82" s="9">
         <v>41583.86</v>
       </c>
-      <c r="V82" s="7">
+      <c r="V82" s="9">
         <v>41614.32</v>
       </c>
-      <c r="W82" s="7">
+      <c r="W82" s="9">
         <v>41554.059</v>
       </c>
-      <c r="X82" s="8"/>
+      <c r="X82" s="10"/>
     </row>
     <row r="83" ht="15.25" spans="8:24">
-      <c r="H83" s="6"/>
-      <c r="I83" s="6" t="s">
+      <c r="H83" s="8"/>
+      <c r="I83" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="J83" s="9">
+        <v>25704.066</v>
+      </c>
+      <c r="K83" s="9">
+        <v>26703.96</v>
+      </c>
+      <c r="L83" s="9">
+        <v>28274.092</v>
+      </c>
+      <c r="M83" s="9">
+        <v>29271.63</v>
+      </c>
+      <c r="N83" s="9">
+        <v>29803.51</v>
+      </c>
+      <c r="O83" s="9">
+        <v>31941.78</v>
+      </c>
+      <c r="P83" s="9">
+        <v>38731.39</v>
+      </c>
+      <c r="Q83" s="9">
+        <v>40041.74</v>
+      </c>
+      <c r="R83" s="9">
+        <v>41262.11</v>
+      </c>
+      <c r="S83" s="9">
+        <v>42213.82</v>
+      </c>
+      <c r="T83" s="9">
+        <v>43146.41</v>
+      </c>
+      <c r="U83" s="9">
+        <v>43637.66</v>
+      </c>
+      <c r="V83" s="9">
+        <v>43667.22</v>
+      </c>
+      <c r="W83" s="9">
+        <v>43606.2</v>
+      </c>
+      <c r="X83" s="10"/>
+    </row>
+    <row r="84" ht="15.25" spans="8:24">
+      <c r="H84" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="I84" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="J83" s="7">
-        <v>25704.066</v>
-      </c>
-      <c r="K83" s="7">
-        <v>26703.96</v>
-      </c>
-      <c r="L83" s="7">
-        <v>28274.092</v>
-      </c>
-      <c r="M83" s="7">
-        <v>29271.63</v>
-      </c>
-      <c r="N83" s="7">
-        <v>29803.51</v>
-      </c>
-      <c r="O83" s="7">
-        <v>31941.78</v>
-      </c>
-      <c r="P83" s="7">
-        <v>38731.39</v>
-      </c>
-      <c r="Q83" s="7">
-        <v>40041.74</v>
-      </c>
-      <c r="R83" s="7">
-        <v>41262.11</v>
-      </c>
-      <c r="S83" s="7">
-        <v>42213.82</v>
-      </c>
-      <c r="T83" s="7">
-        <v>43146.41</v>
-      </c>
-      <c r="U83" s="7">
-        <v>43637.66</v>
-      </c>
-      <c r="V83" s="7">
-        <v>43667.22</v>
-      </c>
-      <c r="W83" s="7">
-        <v>43606.2</v>
-      </c>
-      <c r="X83" s="8"/>
-    </row>
-    <row r="84" ht="15.25" spans="8:24">
-      <c r="H84" s="6" t="s">
+      <c r="J84" s="9">
+        <v>17204.75</v>
+      </c>
+      <c r="K84" s="9">
+        <v>17163.54</v>
+      </c>
+      <c r="L84" s="9">
+        <v>17585.44</v>
+      </c>
+      <c r="M84" s="9">
+        <v>17548.31</v>
+      </c>
+      <c r="N84" s="9">
+        <v>17924.42</v>
+      </c>
+      <c r="O84" s="9">
+        <v>21783.38</v>
+      </c>
+      <c r="P84" s="9">
+        <v>37973.078</v>
+      </c>
+      <c r="Q84" s="9">
+        <v>41145.61</v>
+      </c>
+      <c r="R84" s="9">
+        <v>44295.15</v>
+      </c>
+      <c r="S84" s="9">
+        <v>46514.84</v>
+      </c>
+      <c r="T84" s="9">
+        <v>48647.92</v>
+      </c>
+      <c r="U84" s="9">
+        <v>50070.91</v>
+      </c>
+      <c r="V84" s="9">
+        <v>50113.45</v>
+      </c>
+      <c r="W84" s="9">
+        <v>50028.95</v>
+      </c>
+      <c r="X84" s="10"/>
+    </row>
+    <row r="85" ht="15.25" spans="8:24">
+      <c r="H85" s="8"/>
+      <c r="I85" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="I84" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="J84" s="7">
-        <v>17204.75</v>
-      </c>
-      <c r="K84" s="7">
-        <v>17163.54</v>
-      </c>
-      <c r="L84" s="7">
-        <v>17585.44</v>
-      </c>
-      <c r="M84" s="7">
-        <v>17548.31</v>
-      </c>
-      <c r="N84" s="7">
-        <v>17924.42</v>
-      </c>
-      <c r="O84" s="7">
-        <v>21783.38</v>
-      </c>
-      <c r="P84" s="7">
-        <v>37973.078</v>
-      </c>
-      <c r="Q84" s="7">
-        <v>41145.61</v>
-      </c>
-      <c r="R84" s="7">
-        <v>44295.15</v>
-      </c>
-      <c r="S84" s="7">
-        <v>46514.84</v>
-      </c>
-      <c r="T84" s="7">
-        <v>48647.92</v>
-      </c>
-      <c r="U84" s="7">
-        <v>50070.91</v>
-      </c>
-      <c r="V84" s="7">
-        <v>50113.45</v>
-      </c>
-      <c r="W84" s="7">
-        <v>50028.95</v>
-      </c>
-      <c r="X84" s="8"/>
-    </row>
-    <row r="85" ht="15.25" spans="8:24">
-      <c r="H85" s="6"/>
-      <c r="I85" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="J85" s="7">
+      <c r="J85" s="9">
         <v>18871.74</v>
       </c>
-      <c r="K85" s="7">
+      <c r="K85" s="9">
         <v>18826.53</v>
       </c>
-      <c r="L85" s="7">
+      <c r="L85" s="9">
         <v>19201.9</v>
       </c>
-      <c r="M85" s="7">
+      <c r="M85" s="9">
         <v>19075.04</v>
       </c>
-      <c r="N85" s="7">
+      <c r="N85" s="9">
         <v>19396.47</v>
       </c>
-      <c r="O85" s="7">
+      <c r="O85" s="9">
         <v>23466.79</v>
       </c>
-      <c r="P85" s="7">
+      <c r="P85" s="9">
         <v>40544.44</v>
       </c>
-      <c r="Q85" s="7">
+      <c r="Q85" s="9">
         <v>43545.84</v>
       </c>
-      <c r="R85" s="7">
+      <c r="R85" s="9">
         <v>46481.91</v>
       </c>
-      <c r="S85" s="7">
+      <c r="S85" s="9">
         <v>48812.56</v>
       </c>
-      <c r="T85" s="7">
+      <c r="T85" s="9">
         <v>51051.14</v>
       </c>
-      <c r="U85" s="7">
+      <c r="U85" s="9">
         <v>52544.5</v>
       </c>
-      <c r="V85" s="7">
+      <c r="V85" s="9">
         <v>52589.1</v>
       </c>
-      <c r="W85" s="7">
+      <c r="W85" s="9">
         <v>52500.33</v>
       </c>
-      <c r="X85" s="8"/>
+      <c r="X85" s="10"/>
     </row>
     <row r="87" spans="8:24">
       <c r="J87">

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -1110,7 +1110,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -1122,13 +1121,14 @@
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <name val="Times New Roman"/>
+      <name val="Tahoma"/>
       <charset val="0"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
   </fonts>
@@ -3451,6 +3451,9 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
+      <c r="L27" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3490,9 +3493,6 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-      <c r="L29" s="5" t="s">
-        <v>58</v>
-      </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3505,7 +3505,7 @@
       <c r="V29" s="2"/>
       <c r="W29" s="2"/>
     </row>
-    <row r="30" ht="15.25" spans="5:23">
+    <row r="30" spans="5:23">
       <c r="F30" s="2" t="s">
         <v>59</v>
       </c>

--- a/SuppXLS/Scen_zAK_fixes.xlsx
+++ b/SuppXLS/Scen_zAK_fixes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="4" activeTab="5"/>
+    <workbookView windowWidth="19200" windowHeight="8710" firstSheet="5" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="INS" sheetId="2" r:id="rId1"/>
@@ -16,6 +16,7 @@
     <sheet name="Growth_rate" sheetId="12" r:id="rId7"/>
     <sheet name="util_limit" sheetId="14" r:id="rId8"/>
     <sheet name="Elc_limit" sheetId="15" r:id="rId9"/>
+    <sheet name="Demand_variation" sheetId="16" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="IQ_FWD_Q" hidden="1">501</definedName>
@@ -300,7 +301,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="239">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -861,6 +862,162 @@
   </si>
   <si>
     <t>NorthAm</t>
+  </si>
+  <si>
+    <t>CommName</t>
+  </si>
+  <si>
+    <t>Timeslices</t>
+  </si>
+  <si>
+    <t>COM_FR</t>
+  </si>
+  <si>
+    <t>ELCDem</t>
+  </si>
+  <si>
+    <t>S1H1</t>
+  </si>
+  <si>
+    <t>S1H2</t>
+  </si>
+  <si>
+    <t>S1H3</t>
+  </si>
+  <si>
+    <t>S1H4</t>
+  </si>
+  <si>
+    <t>S1H5</t>
+  </si>
+  <si>
+    <t>S1H6</t>
+  </si>
+  <si>
+    <t>S1H7</t>
+  </si>
+  <si>
+    <t>S1H8</t>
+  </si>
+  <si>
+    <t>S2H1</t>
+  </si>
+  <si>
+    <t>S2H2</t>
+  </si>
+  <si>
+    <t>S2H3</t>
+  </si>
+  <si>
+    <t>S2H4</t>
+  </si>
+  <si>
+    <t>S2H5</t>
+  </si>
+  <si>
+    <t>S2H6</t>
+  </si>
+  <si>
+    <t>S2H7</t>
+  </si>
+  <si>
+    <t>S2H8</t>
+  </si>
+  <si>
+    <t>S3H1</t>
+  </si>
+  <si>
+    <t>S3H2</t>
+  </si>
+  <si>
+    <t>S3H3</t>
+  </si>
+  <si>
+    <t>S3H4</t>
+  </si>
+  <si>
+    <t>S3H5</t>
+  </si>
+  <si>
+    <t>S3H6</t>
+  </si>
+  <si>
+    <t>S3H7</t>
+  </si>
+  <si>
+    <t>S3H8</t>
+  </si>
+  <si>
+    <t>S4H1</t>
+  </si>
+  <si>
+    <t>S4H2</t>
+  </si>
+  <si>
+    <t>S4H3</t>
+  </si>
+  <si>
+    <t>S4H4</t>
+  </si>
+  <si>
+    <t>S4H5</t>
+  </si>
+  <si>
+    <t>S4H6</t>
+  </si>
+  <si>
+    <t>S4H7</t>
+  </si>
+  <si>
+    <t>S4H8</t>
+  </si>
+  <si>
+    <t>S5H1</t>
+  </si>
+  <si>
+    <t>S5H2</t>
+  </si>
+  <si>
+    <t>S5H3</t>
+  </si>
+  <si>
+    <t>S5H4</t>
+  </si>
+  <si>
+    <t>S5H5</t>
+  </si>
+  <si>
+    <t>S5H6</t>
+  </si>
+  <si>
+    <t>S5H7</t>
+  </si>
+  <si>
+    <t>S5H8</t>
+  </si>
+  <si>
+    <t>S6H1</t>
+  </si>
+  <si>
+    <t>S6H2</t>
+  </si>
+  <si>
+    <t>S6H3</t>
+  </si>
+  <si>
+    <t>S6H4</t>
+  </si>
+  <si>
+    <t>S6H5</t>
+  </si>
+  <si>
+    <t>S6H6</t>
+  </si>
+  <si>
+    <t>S6H7</t>
+  </si>
+  <si>
+    <t>S6H8</t>
   </si>
 </sst>
 </file>
@@ -873,10 +1030,24 @@
     <numFmt numFmtId="176" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1110,14 +1281,19 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
       <charset val="0"/>
     </font>
     <font>
@@ -1126,18 +1302,19 @@
       <name val="Tahoma"/>
       <charset val="0"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
   </fonts>
-  <fills count="41">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1524,226 +1701,228 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="51" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="51" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="52" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="53">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2277,7 +2456,7 @@
       <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="52">
+      <c r="F21" s="54">
         <v>0.5</v>
       </c>
       <c r="G21" t="str">
@@ -2289,6 +2468,715 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D50"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="12.1818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="12.8181818181818" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="C1" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.037057043</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.01431031</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.031935713</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.031333153</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.015967293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.008888083</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.025307249</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.01431031</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.032602373</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.012590036</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.028096701</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.027566575</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.014047829</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0.007819075</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.022264484</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0.012590036</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.032675781</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0.012618696</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.028159616</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.027628302</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0.014079808</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0.007836311</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0.022314633</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0.012618696</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0.036459292</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0.014079808</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0.031420203</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0.030827369</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0.015710101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0.008743674</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0.024898433</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0.014079808</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0.03508347</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0.013548494</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0.030234535</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0.029664072</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0.015117267</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0.008413724</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0.023958869</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0.013548494</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0.033019736</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0.012751524</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D45" s="1">
+        <v>0.028456033</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D46" s="1">
+        <v>0.027919127</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0.014228016</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0.007918799</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D49" s="1">
+        <v>0.022549524</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D50" s="1">
+        <v>0.012751524</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -2334,7 +3222,7 @@
       </c>
     </row>
     <row r="4" ht="16" spans="1:11">
-      <c r="A4" s="14"/>
+      <c r="A4" s="17"/>
     </row>
     <row r="7" spans="1:11">
       <c r="D7" t="s">
@@ -2391,10 +3279,10 @@
       <c r="H10">
         <v>0.48</v>
       </c>
-      <c r="K10" s="24"/>
+      <c r="K10" s="27"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="K11" s="24"/>
+      <c r="K11" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2415,12 +3303,12 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:13">
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="35"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="38"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
@@ -2435,19 +3323,19 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="46"/>
+      <c r="K6" s="48"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="C7" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="45" t="s">
+      <c r="D7" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="49">
         <v>10</v>
       </c>
     </row>
@@ -2455,29 +3343,29 @@
       <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="C8" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="45" t="s">
+      <c r="D8" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="49">
         <v>7</v>
       </c>
-      <c r="L8" s="45"/>
-      <c r="M8" s="45"/>
+      <c r="L8" s="47"/>
+      <c r="M8" s="47"/>
     </row>
     <row r="9" ht="16" spans="2:13">
       <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="45" t="s">
+      <c r="D9" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="49">
         <v>10</v>
       </c>
     </row>
@@ -2485,29 +3373,29 @@
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="D10" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="47">
+      <c r="E10" s="49">
         <v>8</v>
       </c>
-      <c r="K10" s="48"/>
-      <c r="L10" s="4"/>
+      <c r="K10" s="50"/>
+      <c r="L10" s="7"/>
     </row>
     <row r="11" ht="16" spans="2:13">
       <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="45" t="s">
+      <c r="D11" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="45">
+      <c r="E11" s="47">
         <v>1.5</v>
       </c>
     </row>
@@ -2515,13 +3403,13 @@
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="45" t="s">
+      <c r="D12" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="45">
+      <c r="E12" s="47">
         <v>1.5</v>
       </c>
     </row>
@@ -2529,13 +3417,13 @@
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="45" t="s">
+      <c r="D13" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="38">
         <v>2</v>
       </c>
     </row>
@@ -2543,13 +3431,13 @@
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="35" t="s">
+      <c r="C14" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="45" t="s">
+      <c r="D14" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="38">
         <v>0</v>
       </c>
     </row>
@@ -2557,13 +3445,13 @@
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="45" t="s">
+      <c r="D15" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="38">
         <v>0</v>
       </c>
     </row>
@@ -2571,13 +3459,13 @@
       <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="45" t="s">
+      <c r="C16" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="45" t="s">
+      <c r="D16" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="51">
         <v>12</v>
       </c>
     </row>
@@ -2585,561 +3473,561 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="45" t="s">
+      <c r="C17" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="50" t="s">
+      <c r="D17" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="53">
         <v>0.2</v>
       </c>
-      <c r="F17" s="35"/>
+      <c r="F17" s="38"/>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="45" t="s">
+      <c r="C18" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="50" t="s">
+      <c r="D18" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="51">
+      <c r="E18" s="53">
         <v>0.2</v>
       </c>
-      <c r="F18" s="35"/>
+      <c r="F18" s="38"/>
     </row>
     <row r="19" ht="16" spans="2:6">
       <c r="B19" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="50" t="s">
+      <c r="D19" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="51">
+      <c r="E19" s="53">
         <v>0.2</v>
       </c>
-      <c r="F19" s="35"/>
+      <c r="F19" s="38"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="45" t="s">
+      <c r="C20" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="50" t="s">
+      <c r="D20" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="53">
         <v>0.5</v>
       </c>
-      <c r="F20" s="35"/>
+      <c r="F20" s="38"/>
     </row>
     <row r="21" ht="16" spans="2:6">
       <c r="B21" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="50" t="s">
+      <c r="D21" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="53">
         <v>0.8</v>
       </c>
-      <c r="F21" s="35"/>
+      <c r="F21" s="38"/>
     </row>
     <row r="22" ht="16" spans="2:6">
       <c r="B22" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="50" t="s">
+      <c r="D22" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="45"/>
-      <c r="F22" s="35"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="38"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="35" t="s">
+      <c r="C23" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="50" t="s">
+      <c r="D23" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="35">
+      <c r="E23" s="38">
         <v>1</v>
       </c>
-      <c r="F23" s="35"/>
+      <c r="F23" s="38"/>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="35" t="s">
+      <c r="C24" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="50" t="s">
+      <c r="D24" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="35">
+      <c r="E24" s="38">
         <v>1</v>
       </c>
-      <c r="F24" s="35"/>
+      <c r="F24" s="38"/>
     </row>
     <row r="25" ht="16" spans="2:6">
       <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="36" t="s">
+      <c r="C25" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="50" t="s">
+      <c r="D25" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="35">
+      <c r="E25" s="38">
         <v>1</v>
       </c>
-      <c r="F25" s="35"/>
+      <c r="F25" s="38"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="45" t="s">
+      <c r="C26" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="50" t="s">
+      <c r="D26" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="45">
+      <c r="E26" s="47">
         <v>0.05</v>
       </c>
-      <c r="F26" s="35"/>
+      <c r="F26" s="38"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="52" t="s">
+      <c r="B27" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="53" t="s">
+      <c r="C27" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="53" t="s">
+      <c r="D27" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="53">
+      <c r="E27" s="55">
         <v>2020</v>
       </c>
-      <c r="F27" s="35"/>
+      <c r="F27" s="38"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="53" t="s">
+      <c r="D28" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="38">
+      <c r="E28" s="41">
         <v>2020</v>
       </c>
-      <c r="F28" s="35"/>
+      <c r="F28" s="38"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="C30" s="35"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="35"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
     </row>
     <row r="38" spans="3:5">
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
     </row>
     <row r="54" spans="3:11">
-      <c r="C54" s="54" t="s">
+      <c r="C54" s="56" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="56" spans="3:11">
-      <c r="D56" s="54"/>
-      <c r="E56" s="54"/>
-      <c r="F56" s="54"/>
-      <c r="G56" s="54"/>
-      <c r="H56" s="54"/>
-      <c r="I56" s="54"/>
-      <c r="J56" s="54"/>
-      <c r="K56" s="54"/>
+      <c r="D56" s="56"/>
+      <c r="E56" s="56"/>
+      <c r="F56" s="56"/>
+      <c r="G56" s="56"/>
+      <c r="H56" s="56"/>
+      <c r="I56" s="56"/>
+      <c r="J56" s="56"/>
+      <c r="K56" s="56"/>
     </row>
     <row r="57" spans="3:11">
-      <c r="C57" s="54" t="s">
+      <c r="C57" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="54" t="s">
+      <c r="D57" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="54" t="s">
+      <c r="E57" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="F57" s="54" t="s">
+      <c r="F57" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="G57" s="54" t="s">
+      <c r="G57" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="54" t="s">
+      <c r="H57" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="54" t="s">
+      <c r="I57" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="J57" s="54" t="s">
+      <c r="J57" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="K57" s="54" t="s">
+      <c r="K57" s="56" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="3:11">
-      <c r="C58" s="54"/>
-      <c r="D58" s="54"/>
-      <c r="E58" s="54"/>
-      <c r="F58" s="54"/>
-      <c r="G58" s="54"/>
-      <c r="H58" s="54"/>
-      <c r="I58" s="54"/>
-      <c r="J58" s="54"/>
-      <c r="K58" s="54"/>
+      <c r="C58" s="56"/>
+      <c r="D58" s="56"/>
+      <c r="E58" s="56"/>
+      <c r="F58" s="56"/>
+      <c r="G58" s="56"/>
+      <c r="H58" s="56"/>
+      <c r="I58" s="56"/>
+      <c r="J58" s="56"/>
+      <c r="K58" s="56"/>
     </row>
     <row r="59" spans="3:11">
-      <c r="C59" s="54"/>
-      <c r="D59" s="54"/>
-      <c r="E59" s="54"/>
-      <c r="F59" s="54"/>
-      <c r="G59" s="54"/>
-      <c r="H59" s="54"/>
-      <c r="I59" s="54"/>
-      <c r="J59" s="54"/>
-      <c r="K59" s="54"/>
+      <c r="C59" s="56"/>
+      <c r="D59" s="56"/>
+      <c r="E59" s="56"/>
+      <c r="F59" s="56"/>
+      <c r="G59" s="56"/>
+      <c r="H59" s="56"/>
+      <c r="I59" s="56"/>
+      <c r="J59" s="56"/>
+      <c r="K59" s="56"/>
     </row>
     <row r="60" spans="3:11">
-      <c r="C60" s="54"/>
-      <c r="D60" s="54"/>
-      <c r="E60" s="54"/>
-      <c r="F60" s="54"/>
-      <c r="G60" s="54"/>
-      <c r="H60" s="54"/>
-      <c r="I60" s="54"/>
-      <c r="J60" s="54"/>
-      <c r="K60" s="54"/>
+      <c r="C60" s="56"/>
+      <c r="D60" s="56"/>
+      <c r="E60" s="56"/>
+      <c r="F60" s="56"/>
+      <c r="G60" s="56"/>
+      <c r="H60" s="56"/>
+      <c r="I60" s="56"/>
+      <c r="J60" s="56"/>
+      <c r="K60" s="56"/>
     </row>
     <row r="61" spans="3:11">
-      <c r="C61" s="54"/>
-      <c r="D61" s="54"/>
-      <c r="E61" s="54"/>
-      <c r="F61" s="54"/>
-      <c r="G61" s="54"/>
-      <c r="H61" s="54"/>
-      <c r="I61" s="54"/>
-      <c r="J61" s="54"/>
-      <c r="K61" s="54"/>
+      <c r="C61" s="56"/>
+      <c r="D61" s="56"/>
+      <c r="E61" s="56"/>
+      <c r="F61" s="56"/>
+      <c r="G61" s="56"/>
+      <c r="H61" s="56"/>
+      <c r="I61" s="56"/>
+      <c r="J61" s="56"/>
+      <c r="K61" s="56"/>
     </row>
     <row r="62" spans="3:11">
-      <c r="C62" s="54"/>
-      <c r="D62" s="54"/>
-      <c r="E62" s="54"/>
-      <c r="F62" s="54"/>
-      <c r="G62" s="54"/>
-      <c r="H62" s="54"/>
-      <c r="I62" s="54"/>
-      <c r="J62" s="54"/>
-      <c r="K62" s="54"/>
+      <c r="C62" s="56"/>
+      <c r="D62" s="56"/>
+      <c r="E62" s="56"/>
+      <c r="F62" s="56"/>
+      <c r="G62" s="56"/>
+      <c r="H62" s="56"/>
+      <c r="I62" s="56"/>
+      <c r="J62" s="56"/>
+      <c r="K62" s="56"/>
     </row>
     <row r="63" spans="3:11">
-      <c r="C63" s="54"/>
-      <c r="D63" s="54"/>
-      <c r="E63" s="54"/>
-      <c r="F63" s="54"/>
-      <c r="G63" s="54"/>
-      <c r="H63" s="54"/>
-      <c r="I63" s="54"/>
-      <c r="J63" s="54"/>
-      <c r="K63" s="54"/>
+      <c r="C63" s="56"/>
+      <c r="D63" s="56"/>
+      <c r="E63" s="56"/>
+      <c r="F63" s="56"/>
+      <c r="G63" s="56"/>
+      <c r="H63" s="56"/>
+      <c r="I63" s="56"/>
+      <c r="J63" s="56"/>
+      <c r="K63" s="56"/>
     </row>
     <row r="64" spans="3:11">
-      <c r="C64" s="54"/>
-      <c r="D64" s="54"/>
-      <c r="E64" s="54"/>
-      <c r="F64" s="54"/>
-      <c r="G64" s="54"/>
-      <c r="H64" s="54"/>
-      <c r="I64" s="54"/>
-      <c r="J64" s="54"/>
-      <c r="K64" s="54"/>
+      <c r="C64" s="56"/>
+      <c r="D64" s="56"/>
+      <c r="E64" s="56"/>
+      <c r="F64" s="56"/>
+      <c r="G64" s="56"/>
+      <c r="H64" s="56"/>
+      <c r="I64" s="56"/>
+      <c r="J64" s="56"/>
+      <c r="K64" s="56"/>
     </row>
     <row r="65" spans="3:11">
-      <c r="C65" s="54"/>
-      <c r="D65" s="54"/>
-      <c r="E65" s="54"/>
-      <c r="F65" s="54"/>
-      <c r="G65" s="54"/>
-      <c r="H65" s="54"/>
-      <c r="I65" s="54"/>
-      <c r="J65" s="54"/>
-      <c r="K65" s="54"/>
+      <c r="C65" s="56"/>
+      <c r="D65" s="56"/>
+      <c r="E65" s="56"/>
+      <c r="F65" s="56"/>
+      <c r="G65" s="56"/>
+      <c r="H65" s="56"/>
+      <c r="I65" s="56"/>
+      <c r="J65" s="56"/>
+      <c r="K65" s="56"/>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="54"/>
-      <c r="D66" s="54"/>
-      <c r="E66" s="54"/>
-      <c r="F66" s="54"/>
-      <c r="G66" s="54"/>
-      <c r="H66" s="54"/>
-      <c r="I66" s="54"/>
-      <c r="J66" s="54"/>
-      <c r="K66" s="54"/>
+      <c r="C66" s="56"/>
+      <c r="D66" s="56"/>
+      <c r="E66" s="56"/>
+      <c r="F66" s="56"/>
+      <c r="G66" s="56"/>
+      <c r="H66" s="56"/>
+      <c r="I66" s="56"/>
+      <c r="J66" s="56"/>
+      <c r="K66" s="56"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="54"/>
-      <c r="D67" s="54"/>
-      <c r="E67" s="54"/>
-      <c r="F67" s="54"/>
-      <c r="G67" s="54"/>
-      <c r="H67" s="54"/>
-      <c r="I67" s="54"/>
-      <c r="J67" s="54"/>
-      <c r="K67" s="54"/>
+      <c r="C67" s="56"/>
+      <c r="D67" s="56"/>
+      <c r="E67" s="56"/>
+      <c r="F67" s="56"/>
+      <c r="G67" s="56"/>
+      <c r="H67" s="56"/>
+      <c r="I67" s="56"/>
+      <c r="J67" s="56"/>
+      <c r="K67" s="56"/>
     </row>
     <row r="68" spans="3:11">
-      <c r="C68" s="54"/>
-      <c r="D68" s="54"/>
-      <c r="E68" s="54"/>
-      <c r="F68" s="54"/>
-      <c r="G68" s="54"/>
-      <c r="H68" s="54"/>
-      <c r="I68" s="54"/>
-      <c r="J68" s="54"/>
-      <c r="K68" s="54"/>
+      <c r="C68" s="56"/>
+      <c r="D68" s="56"/>
+      <c r="E68" s="56"/>
+      <c r="F68" s="56"/>
+      <c r="G68" s="56"/>
+      <c r="H68" s="56"/>
+      <c r="I68" s="56"/>
+      <c r="J68" s="56"/>
+      <c r="K68" s="56"/>
     </row>
     <row r="69" spans="3:11">
-      <c r="C69" s="54"/>
-      <c r="D69" s="54"/>
-      <c r="E69" s="54"/>
-      <c r="F69" s="54"/>
-      <c r="G69" s="54"/>
-      <c r="H69" s="54"/>
-      <c r="I69" s="54"/>
-      <c r="J69" s="54"/>
-      <c r="K69" s="54"/>
+      <c r="C69" s="56"/>
+      <c r="D69" s="56"/>
+      <c r="E69" s="56"/>
+      <c r="F69" s="56"/>
+      <c r="G69" s="56"/>
+      <c r="H69" s="56"/>
+      <c r="I69" s="56"/>
+      <c r="J69" s="56"/>
+      <c r="K69" s="56"/>
     </row>
     <row r="70" spans="3:11">
-      <c r="C70" s="54"/>
-      <c r="D70" s="54"/>
-      <c r="E70" s="54"/>
-      <c r="F70" s="54"/>
-      <c r="G70" s="54"/>
-      <c r="H70" s="54"/>
-      <c r="I70" s="54"/>
-      <c r="J70" s="54"/>
-      <c r="K70" s="54"/>
+      <c r="C70" s="56"/>
+      <c r="D70" s="56"/>
+      <c r="E70" s="56"/>
+      <c r="F70" s="56"/>
+      <c r="G70" s="56"/>
+      <c r="H70" s="56"/>
+      <c r="I70" s="56"/>
+      <c r="J70" s="56"/>
+      <c r="K70" s="56"/>
     </row>
     <row r="71" spans="3:11">
-      <c r="C71" s="54"/>
-      <c r="D71" s="54"/>
-      <c r="E71" s="54"/>
-      <c r="F71" s="54"/>
-      <c r="G71" s="54"/>
-      <c r="H71" s="54"/>
-      <c r="I71" s="54"/>
-      <c r="J71" s="54"/>
-      <c r="K71" s="54"/>
+      <c r="C71" s="56"/>
+      <c r="D71" s="56"/>
+      <c r="E71" s="56"/>
+      <c r="F71" s="56"/>
+      <c r="G71" s="56"/>
+      <c r="H71" s="56"/>
+      <c r="I71" s="56"/>
+      <c r="J71" s="56"/>
+      <c r="K71" s="56"/>
     </row>
     <row r="72" spans="3:11">
-      <c r="C72" s="54"/>
-      <c r="D72" s="54"/>
-      <c r="E72" s="54"/>
-      <c r="F72" s="54"/>
-      <c r="G72" s="54"/>
-      <c r="H72" s="54"/>
-      <c r="I72" s="54"/>
-      <c r="J72" s="54"/>
-      <c r="K72" s="54"/>
+      <c r="C72" s="56"/>
+      <c r="D72" s="56"/>
+      <c r="E72" s="56"/>
+      <c r="F72" s="56"/>
+      <c r="G72" s="56"/>
+      <c r="H72" s="56"/>
+      <c r="I72" s="56"/>
+      <c r="J72" s="56"/>
+      <c r="K72" s="56"/>
     </row>
     <row r="73" spans="3:11">
-      <c r="C73" s="54"/>
-      <c r="D73" s="54"/>
-      <c r="E73" s="54"/>
-      <c r="F73" s="54"/>
-      <c r="G73" s="54"/>
-      <c r="H73" s="54"/>
-      <c r="I73" s="54"/>
-      <c r="J73" s="54"/>
-      <c r="K73" s="54"/>
+      <c r="C73" s="56"/>
+      <c r="D73" s="56"/>
+      <c r="E73" s="56"/>
+      <c r="F73" s="56"/>
+      <c r="G73" s="56"/>
+      <c r="H73" s="56"/>
+      <c r="I73" s="56"/>
+      <c r="J73" s="56"/>
+      <c r="K73" s="56"/>
     </row>
     <row r="74" spans="3:11">
-      <c r="C74" s="54"/>
-      <c r="D74" s="54"/>
-      <c r="E74" s="54"/>
-      <c r="F74" s="54"/>
-      <c r="G74" s="54"/>
-      <c r="H74" s="54"/>
-      <c r="I74" s="54"/>
-      <c r="J74" s="54"/>
-      <c r="K74" s="54"/>
+      <c r="C74" s="56"/>
+      <c r="D74" s="56"/>
+      <c r="E74" s="56"/>
+      <c r="F74" s="56"/>
+      <c r="G74" s="56"/>
+      <c r="H74" s="56"/>
+      <c r="I74" s="56"/>
+      <c r="J74" s="56"/>
+      <c r="K74" s="56"/>
     </row>
     <row r="75" spans="3:11">
-      <c r="C75" s="54"/>
-      <c r="D75" s="54"/>
-      <c r="E75" s="54"/>
-      <c r="F75" s="54"/>
-      <c r="G75" s="54"/>
-      <c r="H75" s="54"/>
-      <c r="I75" s="54"/>
-      <c r="J75" s="54"/>
-      <c r="K75" s="54"/>
+      <c r="C75" s="56"/>
+      <c r="D75" s="56"/>
+      <c r="E75" s="56"/>
+      <c r="F75" s="56"/>
+      <c r="G75" s="56"/>
+      <c r="H75" s="56"/>
+      <c r="I75" s="56"/>
+      <c r="J75" s="56"/>
+      <c r="K75" s="56"/>
     </row>
     <row r="76" spans="3:11">
-      <c r="C76" s="54"/>
-      <c r="D76" s="54"/>
-      <c r="E76" s="54"/>
-      <c r="F76" s="54"/>
-      <c r="G76" s="54"/>
-      <c r="H76" s="54"/>
-      <c r="I76" s="54"/>
-      <c r="J76" s="54"/>
-      <c r="K76" s="54"/>
+      <c r="C76" s="56"/>
+      <c r="D76" s="56"/>
+      <c r="E76" s="56"/>
+      <c r="F76" s="56"/>
+      <c r="G76" s="56"/>
+      <c r="H76" s="56"/>
+      <c r="I76" s="56"/>
+      <c r="J76" s="56"/>
+      <c r="K76" s="56"/>
     </row>
     <row r="77" spans="3:11">
-      <c r="C77" s="54"/>
-      <c r="D77" s="54"/>
-      <c r="E77" s="54"/>
-      <c r="F77" s="54"/>
-      <c r="G77" s="54"/>
-      <c r="H77" s="54"/>
-      <c r="I77" s="54"/>
-      <c r="J77" s="54"/>
-      <c r="K77" s="54"/>
+      <c r="C77" s="56"/>
+      <c r="D77" s="56"/>
+      <c r="E77" s="56"/>
+      <c r="F77" s="56"/>
+      <c r="G77" s="56"/>
+      <c r="H77" s="56"/>
+      <c r="I77" s="56"/>
+      <c r="J77" s="56"/>
+      <c r="K77" s="56"/>
     </row>
     <row r="78" spans="3:11">
-      <c r="C78" s="54"/>
-      <c r="D78" s="54"/>
-      <c r="E78" s="54"/>
-      <c r="F78" s="54"/>
-      <c r="G78" s="54"/>
-      <c r="H78" s="54"/>
-      <c r="I78" s="54"/>
-      <c r="J78" s="54"/>
-      <c r="K78" s="54"/>
+      <c r="C78" s="56"/>
+      <c r="D78" s="56"/>
+      <c r="E78" s="56"/>
+      <c r="F78" s="56"/>
+      <c r="G78" s="56"/>
+      <c r="H78" s="56"/>
+      <c r="I78" s="56"/>
+      <c r="J78" s="56"/>
+      <c r="K78" s="56"/>
     </row>
     <row r="79" spans="3:11">
-      <c r="C79" s="54"/>
-      <c r="D79" s="54"/>
-      <c r="E79" s="54"/>
-      <c r="F79" s="54"/>
-      <c r="G79" s="54"/>
-      <c r="H79" s="54"/>
-      <c r="I79" s="54"/>
-      <c r="J79" s="54"/>
-      <c r="K79" s="54"/>
+      <c r="C79" s="56"/>
+      <c r="D79" s="56"/>
+      <c r="E79" s="56"/>
+      <c r="F79" s="56"/>
+      <c r="G79" s="56"/>
+      <c r="H79" s="56"/>
+      <c r="I79" s="56"/>
+      <c r="J79" s="56"/>
+      <c r="K79" s="56"/>
     </row>
     <row r="80" spans="3:11">
-      <c r="C80" s="54"/>
-      <c r="D80" s="54"/>
-      <c r="E80" s="54"/>
-      <c r="F80" s="54"/>
-      <c r="G80" s="54"/>
-      <c r="H80" s="54"/>
-      <c r="I80" s="54"/>
-      <c r="J80" s="54"/>
-      <c r="K80" s="54"/>
+      <c r="C80" s="56"/>
+      <c r="D80" s="56"/>
+      <c r="E80" s="56"/>
+      <c r="F80" s="56"/>
+      <c r="G80" s="56"/>
+      <c r="H80" s="56"/>
+      <c r="I80" s="56"/>
+      <c r="J80" s="56"/>
+      <c r="K80" s="56"/>
     </row>
     <row r="81" spans="3:11">
-      <c r="C81" s="54"/>
-      <c r="D81" s="54"/>
-      <c r="E81" s="54"/>
-      <c r="F81" s="54"/>
-      <c r="G81" s="54"/>
-      <c r="H81" s="54"/>
-      <c r="I81" s="54"/>
-      <c r="J81" s="54"/>
-      <c r="K81" s="54"/>
+      <c r="C81" s="56"/>
+      <c r="D81" s="56"/>
+      <c r="E81" s="56"/>
+      <c r="F81" s="56"/>
+      <c r="G81" s="56"/>
+      <c r="H81" s="56"/>
+      <c r="I81" s="56"/>
+      <c r="J81" s="56"/>
+      <c r="K81" s="56"/>
     </row>
     <row r="82" spans="3:11">
-      <c r="C82" s="54"/>
-      <c r="D82" s="54"/>
-      <c r="E82" s="54"/>
-      <c r="F82" s="54"/>
-      <c r="G82" s="54"/>
-      <c r="H82" s="54"/>
-      <c r="I82" s="54"/>
-      <c r="J82" s="54"/>
-      <c r="K82" s="54"/>
+      <c r="C82" s="56"/>
+      <c r="D82" s="56"/>
+      <c r="E82" s="56"/>
+      <c r="F82" s="56"/>
+      <c r="G82" s="56"/>
+      <c r="H82" s="56"/>
+      <c r="I82" s="56"/>
+      <c r="J82" s="56"/>
+      <c r="K82" s="56"/>
     </row>
     <row r="83" spans="3:11">
-      <c r="C83" s="54"/>
-      <c r="D83" s="54"/>
-      <c r="E83" s="54"/>
-      <c r="F83" s="54"/>
-      <c r="G83" s="54"/>
-      <c r="H83" s="54"/>
-      <c r="I83" s="54"/>
-      <c r="J83" s="54"/>
-      <c r="K83" s="54"/>
+      <c r="C83" s="56"/>
+      <c r="D83" s="56"/>
+      <c r="E83" s="56"/>
+      <c r="F83" s="56"/>
+      <c r="G83" s="56"/>
+      <c r="H83" s="56"/>
+      <c r="I83" s="56"/>
+      <c r="J83" s="56"/>
+      <c r="K83" s="56"/>
     </row>
     <row r="84" spans="3:11">
-      <c r="C84" s="54" t="s">
+      <c r="C84" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="D84" s="54">
+      <c r="D84" s="56">
         <v>1</v>
       </c>
-      <c r="E84" s="54"/>
-      <c r="F84" s="54"/>
-      <c r="G84" s="54"/>
-      <c r="H84" s="54"/>
-      <c r="I84" s="54"/>
-      <c r="J84" s="54"/>
-      <c r="K84" s="54"/>
+      <c r="E84" s="56"/>
+      <c r="F84" s="56"/>
+      <c r="G84" s="56"/>
+      <c r="H84" s="56"/>
+      <c r="I84" s="56"/>
+      <c r="J84" s="56"/>
+      <c r="K84" s="56"/>
     </row>
     <row r="85" spans="3:11">
-      <c r="C85" s="54"/>
-      <c r="D85" s="54"/>
-      <c r="E85" s="54"/>
-      <c r="F85" s="54"/>
-      <c r="G85" s="54"/>
-      <c r="H85" s="54"/>
-      <c r="I85" s="54"/>
-      <c r="J85" s="54"/>
-      <c r="K85" s="54"/>
+      <c r="C85" s="56"/>
+      <c r="D85" s="56"/>
+      <c r="E85" s="56"/>
+      <c r="F85" s="56"/>
+      <c r="G85" s="56"/>
+      <c r="H85" s="56"/>
+      <c r="I85" s="56"/>
+      <c r="J85" s="56"/>
+      <c r="K85" s="56"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3164,563 +4052,563 @@
   </cols>
   <sheetData>
     <row r="13" spans="5:21">
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
     </row>
     <row r="14" spans="5:21">
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
     </row>
     <row r="15" spans="5:21">
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
     </row>
     <row r="16" spans="5:21">
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P